--- a/bandi_campania.xlsx
+++ b/bandi_campania.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPVDGroXpPoAVZiqWR'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eij29DRSYSSA7Lr9b'}</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSSPSjnQvLzk1apDqu'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hoDET9bxFTez9A1CX'}</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSUctbQ3s7TgTnNRUa'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hrebpgF4WTkGFMPXB'}</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTCfEA2UJAHBw3shzz'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2it5hXyBVBYpLMb3gT'}</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTDHBXnLTPA89z5PHQ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2itjeBiynxdHgfEMJU'}</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPVoVbgmeFjVwDz6jA'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ejRCFdx67TDSorerf'}</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPWHWo11Hgh2qn7L2g'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ekNjvGrvWsp9dXo4D'}</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQTj1GT89eQxCGidzf'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fVixYrdiBPJgo2S1G'}</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQUGkDHsS8oHvKQthe'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fWJgiZuUJowkSsFgZ'}</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQUwgAKQk24soHF9hB'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fWv9XBdNN3rZMuJ66'}</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQVebXDnofQRT1e3iQ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fXtvzy8CntdrfGiWF'}</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQWcPGdg6RKGqrVNbe'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fYTQqE3RKDujd6g7Z'}</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQXEbVs4aovhzKv4Lv'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fZ1enqbkFGpg77QWj'}</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQXmqUNDqczR6bSnaD'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fZc7oAUzNvusm3LXo'}</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQYHbRh8ATRcoQqysu'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2faC6B8iehFjC1VHH4'}</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQYqq6PTjakbFMHZSh'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fbA8wfs23AqmBddDn'}</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQZQozgEgrGRNyDDL3'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fc9uwbMLU2FGDe1xx'}</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQa8y1sK4HwLdXEHuV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fck8hBzDtYKjgsxL6'}</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQagTiLXE2tNonhu3L'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fdL7JfXhVmfQMBpAU'}</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSU5PdW7MsL929uQqF'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hq8pNXstsuJ41WAV9'}</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPd1aSSuBKZ8V18vm1'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eto12GGB5Gd5aGzJK'}</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPHNdWd9srBv1j74Rm'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eZpjzaNSvqFD1Z8Bo'}</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT7VReAJAQx8EBxJUp'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2imXZQMH2ERrdq1c3k'}</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSbFzPkVYDNEtkHrQz'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hz5awzv5vwpYW6VZe'}</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRkTbvQxtqCtk5kNgy'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hEvHDGA9xKRNCeR3Y'}</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzS423HZpEp4D7fcMZF'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hZzVWihupHM2t8byz'}</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSFmECpv1Z6rspKiUw'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2heBWKvdE6nqzLYwcT'}</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPJbo5zdQY46x4Lnyg'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ec1CiYxVTajFZPAnw'}</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPKRQtqWN2c7TmYRqj'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eccv87XNHjmGjDjMs'}</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPKz92E78tfsg6qdeq'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2edDP32ZLHtURnuV2z'}</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPLrjK9hrEwvTJRQw5'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eds5DsfyPNDXyeCzT'}</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPNRjnSXEj8r1g8P1s'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eeVmn3sMC9cCPKc9G'}</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPNyj7cMSBF3Uqycco'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ef7Efcm17LL6P1W6K'}</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPPcvTcTfT96ccPsxE'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2efmRh42J2NxxE8bkh'}</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPSK9PPyNNxXgcycws'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2egL9x2fiZg92HoeAo'}</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPSpuPqmuKvBVty5hK'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2egxMhYG73wKq6Fn2S'}</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPTWaRiFx8nNq3iXZV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ehYLUj55Wmv8zdbYV'}</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPU8XmxCtastMFsKxR'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ei7ox4UPaWBd1ZB8T'}</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPWwxC5MvzFDjRfzwC'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ekyTKvLWq5oY5wKxk'}</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSJNjn84HvdRckPwMg'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hgeqS2R35Ra5gx3xd'}</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSJxxnHvoabeEA2B4N'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hhNVhCa4ihWBLUG6t'}</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSKUTzqQvHLbw7efre'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hhuVjBCCf8Vao2Gpv'}</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPmr9Dqw4o5HrPvVpr'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2euRTGyaMyqt36wG38'}</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPY4g2AMno2ybRcUzC'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eobxxyKrr72HE8fMe'}</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRSoxrMLyfc5W25Uyc'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2grvwnMTx1576xSPvb'}</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTBY1FkwzLP2YGgGHC'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2irj6YgR5gGRZoKb2a'}</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTC5zmqU9vW96hUXLX'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2isK4rJsgpv8X8noQc'}</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTKAteMoXdSeHUdnmD'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2izh5Kbp3JWTbWhfit'}</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTMKd1NnZSBH1Ht2gB'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j4fwVeWUy4HfhUors'}</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTQkVjpeQjNvk2QG6r'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j8sSrpuQRSbU5R11c'}</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTRGkfsNwBX2rSoViV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j9Sg4Wvxf9yiN2e28'}</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPHyqc72VJ93wZibfE'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ebRjSEA21qiPpy6f2'}</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSFBFpMn64C2eCfpbe'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hdbnKEjjB5p3x3v6a'}</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRTea8bX1WitFc7JWQ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gsbNvvoCvJhtPvLia'}</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRUBKC2fT46eAYNY9J'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gtK2wsV1kSso2Zbue'}</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTLo7j9sLFhBbvQBqT'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j2ZgjyvG9exM9RxWa'}</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTMscWHNNB2x7J8g91'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j5EftZpKWFLyU24Uk'}</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTNb29TWvAKMcsfwu8'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j6MtHn2vnr661CU4h'}</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTP6HLvsurQA2H5J1y'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j74YzLhRD6k95d4GR'}</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTPeGpJ9AgKFhvVjJb'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j7dHT1q3a8a514FA3'}</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTQBX33M5p2fUKqugV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j8EFgYvnvee17fR6w'}</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTRpzGLnFm2EV8kmhN'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2jA1ucXuPuBgBPTmuc'}</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPbq8wbWvGT9cDShhw'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2erUrQpWvXr46sR27i'}</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQbEwax484moyX9Vhw'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fdwZnp7oUKkurPXz2'}</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQbnSDzkwCcVfUCQJN'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fyVK1kU1J6XvbohfV'}</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQcNfFZuKKUQKa9mgM'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fzruVQ8tfjm8rrx5X'}</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQczNGj5C8uCVsvNm9'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g1WrNHoJTX3vcpthe'}</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQdYbvYTzJrm7y9Lpp'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g2FkMqPjFJGT91MtP'}</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQeAZTUZjPXKZJdZqC'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g32soZCjeuq23tfzL'}</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQehoYXAgSZ4e3UajV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g3brtg79CGN8xSwDQ'}</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQfWvGd1n7JmbB2KkP'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g4BauZgWtH7zfqthq'}</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT8c974sMPsdXdMmgn'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ioWcgBgTSHXC5SaP8'}</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTKisin2DHk2BznebC'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j1JXpFGRfjVhbHrXQ'}</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTLFsYH8QPjSpDNwnd'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2j1rmZUdmp5U8T4CtX'}</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTGpkQTh1BKrdGcxht'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ixGUJRTuRtjmgiCBm'}</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRJwh495mMmxdx8eMk'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gj9dN3BcgdbHfjhdZ'}</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRKWg7c72mWBJMH6Ex'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gjkqVdLUkiiwfyPXx'}</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPrd8QkTsXaSsDc1qq'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ezpu1puqfjKNJYzRg'}</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPscAPfmr1NUcQBkxh'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f2NR5z4EiXSwsbest'}</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPtn7La3i9QnRWi5U2'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f336iBXPu4WvFPg3n'}</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPuLbNsRR1fN1xioE4'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f3bLXha6xrsF94UQF'}</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPurMZBEfb7Pb8fvoM'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f4A4yFmDqFo2t7G4P'}</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPvSaNjW6BAA1Fn4fg'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f4nGhTw8dF1JPVQhU'}</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPvypCYMVRcSsdWhdh'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f5aQ7Ln8jNJ747S6d'}</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPwa3MBFfUFo1i1UBy'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f7NYRoiEXsXubvi7y'}</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPxX68tEUDKjDckbj5'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f7y1xnUfDdMrThede'}</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPy5aM1Tj8neBdtNHs'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f8gg8DYisnWCXHMTr'}</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPycpNMJHyowiEqXKN'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f9Lch8mTj8Z4M6PZn'}</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQg9NSrEhGho6CWrJF'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g4kov3Hopd446omAm'}</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQgj6RtCiLCfMBwHCm'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g5PWhGvS3gyVeu1Ct'}</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRLH4FYedxvjs24oYW'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gkNnzfUmXXU6zYBam'}</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRMLJqnnei9798hbEH'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gkyGGE7UhfzQDYJuH'}</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRN1VNJdLXabQJhqDW'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gmzmyqdaijYGVHjjf'}</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRNW1JKJ2U4iiF4FZZ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gnaFzgLdYezaz5SQK'}</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRP3VujR4MPbg7eojL'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2go9jSQe3dsEWnjahN'}</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRPqdHy4cYmNwUd7A5'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gojCujzmNzU5iaNgY'}</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRQcWVVU5DT8bDTg3E'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gpJgf1dwEDSLyTX7j'}</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRRCUnV3EVvaCe7B3p'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gpx8XJtGBwiyiQLei'}</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRmEVE3krAuqWY5Ex9'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hFYjNBTa4Xff9ASQn'}</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSEZnyJAEVUZLybz8T'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hd2ohPuhujHcWEpEs'}</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSL6RjeDmCcncVmNvP'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hiUyTeBwS6AVU8pFt'}</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSLh96kxPQgfocjDU3'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hj4SjPmXMYM7Bn7a2'}</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSMH7gkk6emo9JQ97U'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hjgtxQ4Ev3YUNgLs5'}</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSMs5nDW7Yoyvz8oCg'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hkK7C41F7qkLwLJAY'}</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSNVYPeiyU8uKeTm1J'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hkua2Anryz3t4UHcF'}</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSQ1Kn4aJMivtVJRkh'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hmUoUcTGtQvh83tfL'}</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSQfWWtxAj5xL9ge1r'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hn42eQKPzq8QhJGwA'}</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSRMgdiM7QW8n13mZy'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hndWXCJQrKQXuAceh'}</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT99dxDVzTmcTxNRnP'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ip9597bqueHFpSit4'}</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT9feJXnnrVpfn5jWE'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ipvhZus6J8pCCbykf'}</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTDvNiZwze1h5uMLKF'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iuLcNMebcmnNho4Jc'}</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTEVrNNpxchaqrgJHt'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iuy4TwYzPBZ6BqhB8'}</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTF17n764L8yW5XsZw'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ivXnz1osQJR8g93Td'}</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTFXcTx91Reo2j3WPW'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iw729bzMQHFXjuQ12'}</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSHZNo8MQF2gVyAc5h'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hg6MHHbpUJqmWtRy4'}</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSobePgEmY6MF5Tjdn'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iFDfWjJCptcyAXujY'}</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSpQGeoSMPPz5P8Xfc'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iFpdCgZd62tfyeUNZ'}</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSpwGDA7RiaAUcbWjy'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iGQ78Lh7D97yYM3YA'}</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSqVzqydsS2fwY1exP'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iH1p3fnShMSA1XrBF'}</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSr2zWMPD2MHdkQsAS'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iHcHMUPed6kJtDwRN'}</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSrmPoBthHcDLXSBPL'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iJDVMVGywPLGifDur'}</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSsHQ5jenKowHtXxSS'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iJoxu8KBDMCcFXscr'}</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSsouTEz4smyeunEFQ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iKSumFajXJFKVaFz3'}</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzStQsJ215aKwpo9rUh'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iL4NV6ewLujGmNcxn'}</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSu82uhYCjGpycZQ6g'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iLdqtq2eEfAHiBbMM'}</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSudnTYRfSCmwpKJar'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iMFZEJXGUu9jNVpVQ'}</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSvBn1wD4gHE9c73ZU'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iP6gDzkhnoigkUPbk'}</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSw5rTDFJTWE3D7wdf'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iQ1W5VY2qpTzRCVvH'}</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPcPNaZZDTAvHekE7z'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2esB2AstHE5wqAMz6V'}</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPzAoiy7zQpGbH4PXv'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2f9wLMKMNR9gAPgZJL'}</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPzkHB9SatotD2orTy'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fAgEAnHpsjhmmCt4r'}</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ1PyQEzKZo5mNtU86'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fBJBxR73MGQ4wpzQc'}</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ2UTvEBBJB4Wq3XEa'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fBsfZGkSArh2qykBz'}</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ32hrYRS4gAuxatxv'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fCVNeB1mwSRqtaTvG'}</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ3cRdwWFt9kfnpqZB'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fDHzP9E23AotEccuy'}</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ4AAjjuUjixajRzSe'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fDrixGhfTp3Az4sHU'}</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ4hAVt5ur7xEg4phy'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fEWfarY2Uu3HvfFDo'}</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ5FtqL1SNg3ChfPtM'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fFSDxe3ycz1uzhATo'}</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ6Fg2KhFnAUF5aNiy'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fG4Rx4Qr5gtSPsGNa'}</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ8Nv6JWt1rLir4Y3y'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fGdfS1pnV1mnG5ga9'}</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ95arkLhuQ931wmiV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fHTGThWgwruP5FDpb'}</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQ9cae4SunrgqKAWa3'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fJAC1DfyBDQbbfcU2'}</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQAE3LeUhbXxNxsMr8'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fJkA4abAboweboQrW'}</t>
         </is>
       </c>
     </row>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQAkYKuHcpTMmdKEK2'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fKL8Zw5KNFJ4dEexF'}</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQBJXxdyFRYTZ6ffv4'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fKwLuM5WCAEidSUPb'}</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQBp3CEmDdmhHPR7vj'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fLXpC6V6NYUcYyn8z'}</t>
         </is>
       </c>
     </row>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQCQWmLjFFEHJhz7Vu'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fM92XZTuqZ8SqQtRx'}</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQCzEZLSY7LmFnXXK3'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fMzNhDwhkVZrRToWB'}</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQDi9H1b6wjwVWdyXj'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fNbqAfyc6B1P7uR9s'}</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRimAQge6nTjCpp3mb'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hELYotjYBJTBxnye5'}</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPXYv1FAor5iE32JEF'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2emwVzFs4jnzjfuBjq'}</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSbnz6i3suzyDZDzvn'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i11tRX56oVz1eVw5u'}</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzScMy4JbsU37E8EQuD'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i4E879tFLz1Bg9GQf'}</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSctidEGyGzxCeNgqs'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i5ynnGZ2gdXQYUFuT'}</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSdRxeJcWMhYswXg15'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i6ghey8Q3eACJWP1j'}</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSeyUjda5CQHhNuBnR'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i7QNLYNTcSJtUM98U'}</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSiGg496jTXXXJvqQn'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i9mVig8dPi5Gxsppg'}</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSjY5F62nhsj4PQ1iN'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iANi2emirQ4FoM1kC'}</t>
         </is>
       </c>
     </row>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSk551kR1rK24vJVm7'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iAyvRaatzoopX9aWV'}</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSkcohvgXTHtj7urq1'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iBZPqD8rZv4wFdBa5'}</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSmD2a2mQBjqNgxpVY'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iC8NzutvnkKusG3SA'}</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSmqV7owy4J6GR1vcr'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iCibiZgss82bQi4kX'}</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSnPxtQuifALxLinxD'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iDbgNUcP8CLZtBvWm'}</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSnuE67bheTNngiJ1W'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iES37ENvSJRoaj6RN'}</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSxSTX5wrTxgSW5Haw'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iR9i9jnSkGPbirWkW'}</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSyCMEynEXeVu3GWgg'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iRnQZDh9dDFM6gGX3'}</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSynZuZYHmM4dB29eW'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2idVrfukumVPvk2dvm'}</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSzQ2yWz2QMa8yV8DF'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ieRvEANaAvCjbTSu8'}</t>
         </is>
       </c>
     </row>
@@ -8465,7 +8465,7 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT1G8DKseGaN9sW2tJ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iezejF98YimM7Yxhh'}</t>
         </is>
       </c>
     </row>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT2kAifZbf1f2ceVGW'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ifbcc4CzZt2GBR1fY'}</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT3GvPATCEDRmdwbHE'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2igB6TuZtrVCEFKfkg'}</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT3nvNbMEYYAq3Q8Jy'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2igiqPnPx6ejf8XR7r'}</t>
         </is>
       </c>
     </row>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT4Vb8nLSJR3PAsrnP'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ihHKNmgPNWsnsQ25E'}</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT5Mvy8HogJiQpKQK3'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ihsY5f97QikzXjBkK'}</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT5uRgEND6b26TAYzf'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iiahYAbrHY1yAw3p5'}</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT6TuiVVFKUb9aNMHd'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ijQ4fy7zs3QsMc37H'}</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT6yujuYwY7oVytrWr'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ijzHYkwHF1B2Apveo'}</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTGFGkiNyoyA7MP2n4'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iwfkqFP9t3rfTUfeb'}</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPpF1H4avGDS2es1MP'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2exDPNv9gAkvWbBRTn'}</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPpm1mM2MnHaw92CrN'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2exqLsQV9BvKV7bBFJ'}</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPqGX7BTbvYQ1miy1Y'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eySJXQ6PhvadzU4Mi'}</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPquUF9pBLLfm8uyLb'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ez4kiFSfBHNwQ9hk2'}</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQhrZeU75yMNf3q3Pe'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g6ff2rkz6PsvqBuPL'}</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQiX14WT3iUCy7mviJ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g7E9MZ8A6M428nAsF'}</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQjJdMc76kQMmcQDx3'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g7oNNmMXLrwXhJKQg'}</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQjp8jxmrtWHeJs3b2'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g8PLs5SmXw9PJDSxi'}</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQkN8BoVep4ppGH2sz'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g93XuDrWq4YRp4owU'}</t>
         </is>
       </c>
     </row>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQku8556csiNTGQW9t'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g9fF2W3QeNh6JPdeF'}</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQmS7eYSFc77HVfWfd'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gAmiSJLZPtUsYP8Vo'}</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQn2LPhLWVgtnrWkFA'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gBNg9YuxH2NT9s1P2'}</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQnZ5mYkNMAgkcmqga'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gCLUYPzT7Cmaw7BiV'}</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQo84eiNXDbhnCzDyw'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gDDoZZGCCc694K8uT'}</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQogYpUKT6snfUJbxx'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gDtzA1LxzpJSVcAAs'}</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQpbNGv5o6wn4DNoUc'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gEuWQpEWJyTKVGfVS'}</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQqB6Fma5qtece6RsE'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gFXDJnNHtnMoGnoyj'}</t>
         </is>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQqmopjbtYmRGcyrq9'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gGdBrHaF6sNSBKuF2'}</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQrKoGQZu37tJwMN23'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gHZVdV41yYrDzC8xa'}</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQsZxWxyMQkYt17Q3p'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gJ9UJZcseos3dJWPD'}</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQtDQKBwBYnrydbxr8'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gJhhxsqyFrKYFtm2t'}</t>
         </is>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQuRqFq5mqDW14k5j9'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gKFwik1Qhu9pNz7ms'}</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQvDTXDju2yMvawZEA'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gKteDwLiyiwo3VzHT'}</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQvkhXjTYDP1Ak2672'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gLcoKGQhMQWvPtC6J'}</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQwHCwovFpbSm255Mi'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gMCXKnhyLMs51NygQ'}</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQwqw8FxZYCc2JSNNw'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gMnVqEK6yAk9QHUCF'}</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQxQuwdeVCL9YEbcER'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gNZt2GKQLwtk21N6Z'}</t>
         </is>
       </c>
     </row>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQxyQHwWmjKFdvmt9Y'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gPYATRES79Rk1HBVG'}</t>
         </is>
       </c>
     </row>
@@ -10251,7 +10251,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQyW9WGgGJC7v6S4VZ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gS2jTQDunHhfmTzGE'}</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQz3PtDf7LFG4CVT1y'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gSxYcGcPdquC89MrD'}</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRUjoUiEYM6EQv787A'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2h6RJkRVci1PgNwEFC'}</t>
         </is>
       </c>
     </row>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRVHJ3MSvxMuSqEAk1'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2h7azvLiEcAjLnJvyT'}</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRVr2huQk1kQGRvAX9'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2h88VXpWRqieRRWB6B'}</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRWM38E3xKHHi8Rfwo'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2h8mC8zBPTFCLJWGUX'}</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRWs3bK9yvZXtjwsKB'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2h9LRWBXgR5iFGK64v'}</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRXPoEyKYFZq2sZxMo'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2h9vtT7SZrz6LpebCu'}</t>
         </is>
       </c>
     </row>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRXyWzq86jKR2yKdPx'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hAcZeSWkWZxUnCMzc'}</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRZEg5wkvkVCgtfT3V'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hBBoHPvncHuaaqLC8'}</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRbMv2gYR9YqqwBtvc'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hBoFy1pHwMmQsLRQS'}</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRcdoyYWpPtjEnabep'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hCRD5VXPSA9U9NXHu'}</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRdH1NWkigybwkjyvH'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hD4fB5aNKPpfzmMH6'}</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRgnMLsG8qLhfCKsCD'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hDkpxdBunKkZZ6AWh'}</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRmjkfJhb8W4nMjTs5'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hG9waJZ1YnbXcPMU6'}</t>
         </is>
       </c>
     </row>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzT83ugpLjuL3yxrvLg'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2insfqiVK2zsEZbNRE'}</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQze7LFFU5qEW7mKkp'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gTiSCPQoxTVg14TkZ'}</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRHuw7sa7kSFCueZcz'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ghqW1vxkAJixGoueG'}</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRJRwQ3Efy4hgQzY1i'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2giYfdQ1s7CtxQ6qFH'}</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTJXweNMZTNXThQUm2'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iz8axEhyR2wefbibe'}</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRnRgAPioPLnSFXfuj'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hGmtuQeXp28wwUcs9'}</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRnwBS6vZmq9ZfY76U'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hHNcXPgDin4km7Egb'}</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRocrrgbNxJPBHsqwQ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hJ1ZaKZrSc5RjD1i6'}</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRpTxSyxu6yBaQ8N7W'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hJbHdhrMugTSMMGe8'}</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRq6ALpzmdmHE1M7ja'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hKNfeJiKnyLkpJhai'}</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRqwkmdFpbcoZfr2pL'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hLWsnhXW5BfGJKxAw'}</t>
         </is>
       </c>
     </row>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRrTGeSkeLg4w4aMTD'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hMKzLwF3TtBMwULX7'}</t>
         </is>
       </c>
     </row>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRs1W22xYD26DHrh67'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hMxh2i5N1oF7RjKUL'}</t>
         </is>
       </c>
     </row>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRsZVfFWcRHZ7Vj6SG'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hNb9WN6g9HTfJqZ77'}</t>
         </is>
       </c>
     </row>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRt5zebcn7qNsz9BPw'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hP9PFKEvsbAqrKcAn'}</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRtcViquo7KQv65R8d'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hPicWowjnf4xemmWX'}</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRuy6tBzKe4K4qwCRp'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hQJ629qwnnS9J2KAB'}</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRvYai22xSKeDUz7tm'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hQsZWJa8xNYS9PoXG'}</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRwAnUZJMmXWDoMbF4'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hRS3WHXnSCpXV3G2m'}</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRwi2UuV1dkeMTUrBu'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hRzn3QLdkidqyzSRQ'}</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRxc6tk6aqVd2P91bo'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hSbVxWv3pnRScZmQe'}</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRy7cTh4pKgMUHYpvQ'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hTECb7E4hQ1MJKp5E'}</t>
         </is>
       </c>
     </row>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRyecFYqwP5cqRtq9v'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hTrenJhDEnd6jr61P'}</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRzELWrCb1cvR8UoG4'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hUTcN8s3Rm9wYst6U'}</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRzjbSLvc2L6y3W51n'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hVHiormB8F85z6vN9'}</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzS1GbURU2hk8SbiUNi'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hWA4MFFWzAAxR18W8'}</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzS1r4kADe5ztKV3xi2'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hX29k7pDC2GB5QGAs'}</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzS2PZSGtRWJNf8JP65'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hXfLz29wW8qr4x2mz'}</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzS2voYo3kWC3MnqPfn'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hYYgRXjDhtHXiJdTf'}</t>
         </is>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzS3UYYt6xzzF7La5Wz'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hZ7uUttyP4BVmMKjB'}</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSGUe6iUsH3HF5i4Lo'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2heoU9DCihX82M1UUH'}</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSH38AKvdLFybTVgAx'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hfXNgxg8Rsa2XZnhC'}</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTAVVr6DYXgEE22tEb'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iqXundcAg7GQoyKY6'}</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTB1FxZv1KmZB3mbsP'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ir791i552MzLc1RcW'}</t>
         </is>
       </c>
     </row>
@@ -12554,7 +12554,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzS4ZXnvY8dtQBSMwxr'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hbHdbdaufkTYtSeeX'}</t>
         </is>
       </c>
     </row>
@@ -12601,7 +12601,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSVAP1rWooYdKJNgjR'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hsdPbCxXicxtwY1uq'}</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSVgt2M2tuZJXcSVRa'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2htKZdiAMhYZKLWcZu'}</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSWDNtRb3sCqn6wTe7'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2htvmeVVLwLuqkwfaM'}</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSWorFvF55q7cUPs57'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hus5XJaVGkZxZiuNE'}</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSXx4W48utquKGpiG2'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hvvagjUX5JBKKgmwE'}</t>
         </is>
       </c>
     </row>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSYoACts1mqcXzuzwa'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hwnRFjwTkFK7VVssF'}</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSZJv3e56169d6XJwE'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hxM9vDcbQ8hvo7j4c'}</t>
         </is>
       </c>
     </row>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSZudPZABaQ7rcu8VL'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hxueApAARd4XrGYnq'}</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSajF4jnGSz297F2Ga'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hyVrfcxZt2tP8ApSA'}</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSwi432LK9KwwJsPiN'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iQayPuHKuVGWVbjRN'}</t>
         </is>
       </c>
     </row>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPnMQCDg4twgzsMBEs'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ev1fzPAmTcgQQtoxM'}</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPnu9Ra1H48NjXHjDh'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2evd92fsY4At4d9VtB'}</t>
         </is>
       </c>
     </row>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPogmtrBrnSaXRFWM2'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eweA7xPq9GLg9ayY2'}</t>
         </is>
       </c>
     </row>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQhKoxtRsEfbwktt4f'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2g61iZowwY5CgVoQXa'}</t>
         </is>
       </c>
     </row>
@@ -13259,7 +13259,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSSvC6KiRmkUT9y3wA'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hovPqKr7pmbrBdVdM'}</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSTVfnYAysawFHQ61D'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2hpYbiccSYVEW6nNaG'}</t>
         </is>
       </c>
     </row>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR1MH8vp3qLorvXe2m'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gUSqrad7DR1PeXNKA'}</t>
         </is>
       </c>
     </row>
@@ -13400,7 +13400,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR4Bw3zkbtdsqmEgvC'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gUzLYx764A1juNQr6'}</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR4mekHm81v2Emqdxo'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gVcYAu86Ca2wWzZUk'}</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR5KeTJU8HBqtZevB9'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gWHE4zbqh1Hf3pcBb'}</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR5rtKtyQLpB1kXFEx'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gX6LpGLBdDgAVs59r'}</t>
         </is>
       </c>
     </row>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR6TrGJMNHUXVaTivE'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gXtxd3RAfR6eVYNsw'}</t>
         </is>
       </c>
     </row>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR7SeAECM8R4FtBNdV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gYUBirPzKLdrTXVjX'}</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR8Rg55F6BTdFDrQzt'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gZGZEExPDGd3GncWw'}</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR92dx4VicM6kqrrN1'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gZrXw1VpfCXf9UdTT'}</t>
         </is>
       </c>
     </row>
@@ -13776,7 +13776,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzR9e6dyT8Mg6RfxhnN'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gaUz3P8pHdV2MFbXD'}</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRBftKnZcoytAkpihY'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gb5hPrro7Y8cWQZ1X'}</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRCEs6oavTTtENV4VF'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gbfv9LGVe2Rs2B8qn'}</t>
         </is>
       </c>
     </row>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRCrpgBRz4dWp7s6dH'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gcGt7e6T8ipG7LJgC'}</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRDSJViR2y8JAEaWCn'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gcs6r4wJZpa4EBcev'}</t>
         </is>
       </c>
     </row>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRDwK15SJD9sEZY2o7'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gdUoxpsLtHHdfsvwh'}</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzREV44NWNDAAzatXvv'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ge3o6metqcbzJDSS6'}</t>
         </is>
       </c>
     </row>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRF2YiwiPbVMJXbqnx'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gebXpc2U63412uyqu'}</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRFaHedNU7d1MWraHH'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gfNuvyygbq7VEJ7FG'}</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRG9Gbqu7qY5gvVXHV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gg3M8PwMMuAxfmR4e'}</t>
         </is>
       </c>
     </row>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRGfGmPdnmPju37LAR'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ggcLHvKCHxg56sgiM'}</t>
         </is>
       </c>
     </row>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRHC29a4fDEEb48deA'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ghF2x1mTn5Ws5rrVK'}</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTHUwPG1B81GGUq16M'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2ixx9eTYX2Sjgcs59U'}</t>
         </is>
       </c>
     </row>
@@ -14387,7 +14387,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTJ1SRsjUGJdSxSPta'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2iyYceX347PqThtxZ1'}</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRRjEELuCktk8qN2RD'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2gqdonoSHubquaMgF1'}</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzRSFyrSXC3hx1Sbq5d'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2grNDC7rw8sgRq6hTH'}</t>
         </is>
       </c>
     </row>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPbGex7F9dzqHTQ7sq'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2equ8DbPBqBrcpzG2n'}</t>
         </is>
       </c>
     </row>
@@ -14575,7 +14575,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQEJcW6x3yb3Jq8mMc'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fPG1yjZwfh7vDpFEA'}</t>
         </is>
       </c>
     </row>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQEqN2wXBBDRjmYUVV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fPtUQzh2Jqt6qpprt'}</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQPrbBji2ToZBWS4a3'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fQZQV5sGYwoAi3hkD'}</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14716,7 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQQN6N5R8Dsk8fdVhW'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fRzUVgYgofp3nV1uT'}</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQQz42nSjrqsEik6qX'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fSaCcB3UNQjixQovY'}</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQRWYwsvGXMFvbYm6n'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fTEdxq3zcaN5iGLEz'}</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQS3oA9puXgRbZA7Bs'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fTvZVE8pujXTwY9wN'}</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQSbYEiBBX72piYGUV'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fUWY9jTw7Zuc3Yv7D'}</t>
         </is>
       </c>
     </row>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzQT92mYW8iZ8FPzCps'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2fV5m933v6ZL7u4xqh'}</t>
         </is>
       </c>
     </row>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPaARYoEkEWs3rwjGP'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2eqKu9c5KwQWNxKTih'}</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTSzw23LsFjLYz8DpY'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2jBF5LFW7U67dhp45n'}</t>
         </is>
       </c>
     </row>
@@ -15092,7 +15092,7 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTSQTuDmtmTQNDwTJX'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2jAd7iVbsTydkohj5B'}</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTTkpZbcJRe2MZQiu4'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2jBwjxSAPBFNd1xcJi'}</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzTUiNX9eM6bZ64ZkNt'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2jCeuWcEsxrPGcvT55'}</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPYxkKBBvgDf1vFKyX'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2epCvrUvFfWbMxZFtH'}</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzPZdBWVyYAeBEwinuH'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2epmuRdG1GqGaS7LqL'}</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzSgdCmeSUhDdC7Jcbg'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i82KfDUgc5V163ABi'}</t>
         </is>
       </c>
     </row>
@@ -15374,7 +15374,7 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzShDv5STk6UZNWNYdv'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i8bo2hFgQAnXhpThG'}</t>
         </is>
       </c>
     </row>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011CbfzShmAFUTdWbFkaGHA4'}</t>
+          <t>Error code: 400 - {'type': 'error', 'error': {'type': 'invalid_request_error', 'message': 'Your credit balance is too low to access the Anthropic API. Please go to Plans &amp; Billing to upgrade or purchase credits.'}, 'request_id': 'req_011Cbg2i9C22qewpy4C3JHaZ'}</t>
         </is>
       </c>
     </row>
@@ -16403,7 +16403,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>03/06/2026 08:13</t>
+          <t>03/06/2026 08:43</t>
         </is>
       </c>
     </row>

--- a/bandi_campania.xlsx
+++ b/bandi_campania.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia l'acquisizione di competenze specialistiche per il personale delle PMI, coprendo costi di formazione tecnica e manageriale: particolarmente utile per le piccole imprese del Cilento che vogliono rafforzare le proprie risorse umane in settori come turismo, agroalimentare o artigianato. La gestione tramite Invitalia e la scadenza ampia (giugno 2026) garantiscono tempo sufficiente per strutturare un progetto formativo mirato.</t>
+          <t>Il bando finanzia l'acquisizione di competenze specialistiche tramite inserimento temporaneo di figure professionali qualificate (manager e consulenti) in PMI, coprendo i relativi costi: uno strumento direttamente accessibile a piccole imprese del Cilento che vogliono rafforzare capacità in aree come marketing, internazionalizzazione o innovazione senza sostenere il costo pieno di una figura senior. La scadenza al giugno 2026 lascia ampio margine per strutturare il progetto.</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia azioni promozionali dei vini campani sui mercati extra-UE (fiere, campagne di comunicazione, missioni commerciali), rendendolo direttamente accessibile alle PMI vitivinicole del Cilento — area DOC Cilento e IGT Paestum — che vogliono aprire canali di export verso Paesi come USA, Canada o Asia. Le spese ammissibili coprono tipicamente partecipazione a manifestazioni internazionali, materiali promozionali e attività di incoming, ambiti gestibili anche da cantine di piccole dimensioni.</t>
+          <t>Il bando finanzia azioni promozionali sui mercati extra-UE (fiere, campagne di comunicazione, incoming buyer) direttamente accessibili a cantine e produttori vitivinicoli di piccola e media dimensione, settore particolarmente radicato nel Cilento con DOC come Cilento e Castel San Lorenzo. Una PMI vinicola campana può coprire costi di partecipazione a eventi internazionali e materiali promozionali altrimenti difficilmente sostenibili.</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia pratiche di produzione integrata per aziende agricole campane, con contributi diretti a sostegno della riduzione dei fitofarmaci e della gestione sostenibile delle colture tipiche del Cilento come l'olivo, i cereali e gli ortaggi. Una PMI agricola del territorio può accedere a pagamenti annuali per ettaro impegnandosi a rispettare disciplinari di produzione integrata, riducendo i costi di produzione e migliorando la competitività sui mercati premium.</t>
+          <t>Il bando finanzia pratiche di produzione integrata per aziende agricole campane, con contributi diretti per l'adozione di metodi a basso impatto ambientale su colture tipiche del Cilento come olivicoltura, orticoltura e frutticoltura. Una PMI agricola del territorio può accedere a pagamenti annuali per ettaro semplicemente rispettando i disciplinari di produzione integrata, senza investimenti strutturali complessi.</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia pratiche agricole a ridotta lavorazione del suolo (minimum tillage, no-till) nell'ambito del PSR Campania, con pagamenti annuali per ettaro accessibili anche a piccole aziende agricole: particolarmente rilevante per le PMI agricole del Cilento che coltivano seminativi o oliveti su terreni collinari, dove queste tecniche riducono costi di carburante e macchinari e migliorano la fertilità del suolo.</t>
+          <t>Il bando finanzia direttamente le aziende agricole del territorio campano, incluso il Cilento, per l'adozione di tecniche di lavorazione ridotta del suolo (minimum tillage, no-till), con pagamenti annuali per ettaro che compensano i costi di adeguamento delle pratiche colturali. Per una PMI agricola cilentana, rappresenta un'opportunità concreta di ridurre i costi operativi (carburante, manodopera) e accedere a contributi PSR senza necessità di investimenti strutturali complessi.</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia direttamente gli allevatori che conservano razze animali locali a rischio di erosione genetica, una realtà diffusa nel Cilento con specie autoctone come la Podolica e la capra Cilentana; copre i costi aggiuntivi e i mancati redditi legati alla gestione di queste razze, rendendolo concreto e accessibile per piccole aziende zootecniche del territorio.</t>
+          <t>Il bando finanzia direttamente gli allevatori che conservano razze animali locali a rischio di estinzione, una realtà diffusa nel Cilento con specie come la Podolica o il Cavallo Salernitano; i pagamenti sono a superficie/capo animale e non richiedono investimenti iniziali, rendendoli accessibili anche alle piccole aziende zootecniche. Per un'azienda agricola cilentana già dedita all'allevamento tradizionale, rappresenta un sostegno economico diretto per pratiche già in atto.</t>
         </is>
       </c>
     </row>
@@ -802,14 +802,14 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia impegni silvoambientali e climatici per aziende agricole e forestali, rendendo il Cilento – territorio ricco di superfici boschive e colture tradizionali – un contesto ideale per accedere ai contributi; una PMI agricola o agro-forestale locale può ottenere pagamenti annuali per pratiche di gestione sostenibile del bosco e del suolo, con scadenza ordinaria al 30 giugno 2026 e possibilità di presentare domanda fino al 25 luglio con penale progressiva.</t>
+          <t>Il bando finanzia impegni silvoambientali e climatici per aziende agricole e forestali, rendendo il Cilento – territorio con forte vocazione boschiva e agroforestale – un'area particolarmente eleggibile; una PMI agricola o agro-forestale campana può accedere a pagamenti annuali per pratiche di gestione sostenibile di boschi e superfici agricole, con scadenza al 30 giugno 2026 (presentazione senza penale).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA 29 - Pagamento al fine di adottare e mantenere pratiche e metodi di produzione biologica - domande annualità 2026</t>
+          <t>Intervento SRA28 (Sostegno per mantenimento della forestazione/imboschimento e sistemi agroforestali) - annualità 2026 - impegni precedenti programmazioni</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA29.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA28.html</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -849,14 +849,14 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia direttamente le aziende agricole che adottano metodi di produzione biologica, con pagamenti annuali a compensazione dei maggiori costi e dei mancati redditi: particolarmente rilevante per le PMI agricole del Cilento, territorio vocato all'agricoltura biologica di qualità (olio, ortaggi, cereali antichi). La scadenza al 30 giugno 2026, con finestra suppletiva fino al 25 luglio, lascia tempo sufficiente per strutturare la domanda.</t>
+          <t>Il bando sostiene imprenditori agricoli e forestali del territorio campano – incluso il Cilento, ricco di superfici boscate e sistemi agroforestali – attraverso pagamenti per il mantenimento di impianti di forestazione e imboschimento già avviati nelle precedenti programmazioni PSR. Una PMI agricola che ha aderito agli impegni nelle programmazioni 2007-2013 o 2014-2022 può continuare a percepire i contributi annuali senza nuovi investimenti, garantendosi un flusso di cassa stabile a fronte della gestione ordinaria delle superfici impegnate.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA30 Azione B (benessere animale) - domande annualità 2026</t>
+          <t>Intervento SRA 29 - Pagamento al fine di adottare e mantenere pratiche e metodi di produzione biologica - domande annualità 2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA30.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA29.html</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -896,14 +896,14 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Il bando SRA30 Azione B finanzia imprese agricole che adottano pratiche di benessere animale superiori agli standard obbligatori, con pagamenti annuali per chi alleva bovini, suini, ovini o avicoli: particolarmente rilevante per le aziende zootecniche del Cilento, area vocata all'allevamento di razze autoctone come il podolico e la bufala. Una PMI agricola della zona può accedere a contributi annuali a superficie/capo animale senza dover sostenere spese di investimento immediato, rendendo il bando accessibile anche a realtà di piccola dimensione.</t>
+          <t>Il pagamento agroambientale SRA29 remunera direttamente le aziende agricole che adottano o mantengono la produzione biologica certificata, rappresentando un incentivo economico annuale concreto per le PMI agricole del Cilento già operative in biologico o intenzionate a convertirsi, in un territorio vocato a colture tipiche come olivo, vite e ortaggi.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRB01 (Sostegno zone con svantaggi naturali di montagna) - domande annualità 2026</t>
+          <t>Intervento SRA30 Azione B (benessere animale) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB01.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA30.html</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -943,14 +943,14 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Il bando sostiene direttamente le aziende agricole localizzate in zone montane svantaggiate, categoria che include ampie aree del Cilento: eroga indennità compensative per i maggiori costi e le minori rese derivanti da vincoli naturali, rappresentando un contributo diretto al reddito aziendale senza necessità di investimenti specifici. Una PMI agricola operante nei comuni montani del Parco Nazionale del Cilento può accedere a pagamenti annuali per ettaro di superficie agricola utilizzata.</t>
+          <t>Il bando finanzia pratiche di benessere animale per allevatori nell'ambito del PSR Campania, rendendo eleggibili le aziende zootecniche del Cilento (area vocata all'allevamento ovicaprino e bovino) per premi annuali a fronte di impegni volontari migliorativi rispetto agli standard obbligatori. Una PMI agricola con allevamenti attivi può accedere a pagamenti compensativi per i costi aggiuntivi sostenuti, con domanda entro giugno 2026 e possibilità di presentazione con penale fino a luglio 2026.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRB02 (Sostegno zone con altri svantaggi naturali significativi) - domande annualità 2026</t>
+          <t>Intervento SRB01 (Sostegno zone con svantaggi naturali di montagna) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB02.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB01.html</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -990,14 +990,14 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Il bando SRB02 sostiene direttamente le aziende agricole operanti in zone con svantaggi naturali significativi, categoria in cui rientra gran parte del territorio del Cilento: le PMI agricole locali possono ricevere pagamenti compensativi annuali per i maggiori costi e i minori redditi derivanti dall'operare in aree svantaggiate, rendendo questo intervento particolarmente rilevante per chi coltiva terreni collinari o montani tipici di quella zona.</t>
+          <t>Il bando sostiene direttamente le aziende agricole localizzate in zone montane svantaggiate, come gran parte del territorio del Cilento, erogando indennità compensative per i maggiori costi e i minori redditi derivanti dalle difficoltà naturali. Una PMI agricola cilentana può accedere a pagamenti annuali per ettaro di superficie agricola utilizzata, compensando concretamente gli svantaggi strutturali del territorio montano.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRB03 (Sostegno zone con vincoli specifici) - domande annualità 2026</t>
+          <t>Intervento SRB02 (Sostegno zone con altri svantaggi naturali significativi) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB03.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB02.html</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1037,14 +1037,14 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Il bando SRB03 sostiene le aziende agricole operanti in zone con svantaggi naturali specifici, tra cui molte aree del Cilento (zona montana e rurale svantaggiata), erogando pagamenti compensativi annuali per ettaro di superficie agricola utilizzata. Una PMI agricola del Cilento può accedere a contributi diretti a compensazione dei costi aggiuntivi legati ai vincoli territoriali, senza necessità di investimenti specifici.</t>
+          <t>Il bando SRB02 sostiene le aziende agricole localizzate in zone con svantaggi naturali significativi, categoria che comprende ampie aree del Cilento: i pagamenti compensativi erogati per ettaro aiutano le PMI agricole a mantenere l'attività in territori montani o collinari svantaggiati, compensando i maggiori costi produttivi. Una PMI agricola cilentana attiva su superfici ammissibili può accedere a contributi annuali a superficie senza necessità di investimenti specifici, rendendo il bando particolarmente conveniente e a bassa complessità amministrativa.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Tipologia di intervento 8.1.1: Imboschimento di superfici agricole e non agricole (per i premi a superficie)</t>
+          <t>Intervento SRB03 (Sostegno zone con vincoli specifici) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/comunicati/comunicato_23-12-25B.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB03.html</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1084,34 +1084,34 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia l'imboschimento di superfici agricole e non agricole tramite premi a superficie, risultando particolarmente rilevante per PMI agricole e forestali del Cilento, territorio con ampie disponibilità di terreni marginali o abbandonati. Le aziende del settore primario possono accedere a contributi diretti per interventi di forestazione, con scadenza estesa al luglio 2026 (seppur con penale progressiva), garantendo tempo sufficiente per la pianificazione degli interventi.</t>
+          <t>Il bando SRB03 sostiene le imprese agricole localizzate in zone con vincoli naturali specifici, categoria in cui ricade gran parte del territorio del Cilento (area protetta del Parco Nazionale): le PMI agricole cilentane possono accedere a pagamenti compensativi annuali per i maggiori costi e i minori redditi derivanti dall'operare in queste aree svantaggiate. La scadenza al 30 giugno 2026 (con finestra fino al 25 luglio con penale progressiva) lascia tempo sufficiente per predisporre la domanda tramite il CAA o un consulente agricolo abilitato.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Smart Social Economy Model in Tourism (Long Distance Trails)</t>
+          <t>Tipologia di intervento 8.1.1: Imboschimento di superfici agricole e non agricole (per i premi a superficie)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-SOCIAL-ECONOMY-TOURISM</t>
+          <t>https://agricoltura.regione.campania.it/comunicati/comunicato_23-12-25B.html</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>Regione Campania - Agricoltura</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1126,39 +1126,39 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia modelli di economia sociale legati al turismo slow e ai cammini a lunga percorrenza, settore in cui il Cilento eccelle grazie al Sentiero degli Dei e ai percorsi del Parco Nazionale: una PMI locale attiva in ospitalità, guide turistiche o servizi escursionistici può accedere a fondi per sviluppare prodotti turistici innovativi e reti di collaborazione territoriale. Le spese finanziabili tipicamente includono progettazione di itinerari, digitalizzazione dell'offerta e formazione degli operatori.</t>
+          <t>Il bando finanzia l'imboschimento di superfici agricole e non agricole attraverso premi a superficie, risultando particolarmente rilevante per PMI agricole e forestali del Cilento, territorio ricco di terreni marginali o incolti che possono essere valorizzati. Le aziende possono accedere a contributi per la piantumazione di specie arboree, con ricadute concrete su sostenibilità ambientale e diversificazione del reddito aziendale.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GreenTour</t>
+          <t>Smart Social Economy Model in Tourism (Long Distance Trails)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>15 settembre 2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/fondo-greentour</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-SOCIAL-ECONOMY-TOURISM</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Invitalia</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1178,19 +1178,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>GreenTour di Invitalia sostiene investimenti per la valorizzazione del turismo sostenibile e dell'ecoturismo, settori centrali per le PMI del Cilento grazie alla presenza del Parco Nazionale e delle aree costiere protette. Sono finanziabili spese per strutture ricettive, percorsi naturalistici e servizi turistici eco-compatibili, rendendolo particolarmente rilevante per operatori locali del settore hospitality e turismo esperienziale.</t>
+          <t>Il bando finanzia modelli di economia sociale nel turismo legati ai percorsi a lunga percorrenza, un settore in cui il Cilento eccelle grazie al Sentiero degli Dei e al Cammino di San Nilo: una PMI locale attiva in ospitalità, guide turistiche o servizi connessi può accedere a fondi per sviluppare offerte innovative e sostenibili lungo questi tracciati. Sono potenzialmente finanziabili attività di co-progettazione, formazione degli operatori e creazione di reti tra imprese del territorio.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA28 (Sostegno per mantenimento della forestazione/imboschimento e sistemi agroforestali) - annualità 2026 - impegni precedenti programmazioni</t>
+          <t>GreenTour</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
+          <t>15 settembre 2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA28.html</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/fondo-greentour</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Regione Campania - Agricoltura</t>
+          <t>Invitalia</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Il bando sostiene imprenditori agricoli con impegni di forestazione o agroforestali già assunti nelle precedenti programmazioni PAC, finanziando il mantenimento di superfici boschive e sistemi agroforestali: pertinente per PMI agricole del Cilento che gestiscono terreni con queste caratteristiche, ma limitato a chi ha già attivato impegni precedenti e non aperto a nuovi beneficiari.</t>
+          <t>GreenTour di Invitalia finanzia progetti di turismo sostenibile, settore strategico per il Cilento grazie al Parco Nazionale e alla sua vocazione naturalistico-culturale; una PMI locale può accedere a contributi per infrastrutture ricettive eco-compatibili, servizi turistici innovativi e valorizzazione del territorio, con scadenza ampia (settembre 2026) che consente una progettazione accurata.</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Il Fondo di partecipazione MUR finanzia progetti di ricerca e innovazione attraverso strumenti finanziari agevolati (equity, quasi-equity o debito), rendendolo accessibile a PMI campane con vocazione tecnologica o spin-off universitari, incluse realtà del Cilento attive in settori come agroalimentare innovativo o turismo sostenibile. La pertinenza non è massima perché richiede una componente di ricerca strutturata che può risultare onerosa da documentare per microimprese.</t>
+          <t>Il Fondo di partecipazione MUR gestito da Invitalia finanzia progetti di ricerca e innovazione tramite strumenti finanziari rotativi (equity, quasi-equity, garanzie), accessibili anche a PMI che sviluppano attività di R&amp;S in collaborazione con università o centri di ricerca. Per una PMI del Cilento, la pertinenza è media perché richiede una struttura minima orientata all'innovazione e la capacità di co-investire, ma rappresenta un'opportunità concreta per imprese nei settori agroalimentare, turismo sostenibile o tecnologie ambientali tipici del territorio.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia la redazione di Piani di Gestione Forestale, strumento obbligatorio per accedere a molti incentivi europei e regionali legati al settore forestale e agroforestale: particolarmente rilevante per PMI del Cilento attive nella gestione boschiva, nella filiera del legno o nell'agriturismo con superfici forestali, che possono coprire i costi di progettazione e consulenza tecnica specialistica. La pertinenza è Media e non Alta perché si tratta di un contributo indiretto alla gestione aziendale, utile solo per imprese con patrimonio forestale proprio o in gestione.</t>
+          <t>Il bando finanzia la redazione di Piani di Gestione Forestale, strumento obbligatorio per accedere a molti incentivi agro-forestali, e risulta rilevante per PMI del Cilento che gestiscono boschi o terreni forestali, area con ampia copertura boschiva. La pertinenza è media perché si tratta di un contributo tecnico-pianificatorio, non di un investimento produttivo diretto, e richiede che l'azienda possieda o gestisca superfici forestali idonee.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Il bando Vita &amp; Opportunità di Invitalia supporta iniziative legate all'inclusione sociale e alla creazione di impresa in aree svantaggiate, potenzialmente accessibile a PMI del Cilento operanti nel welfare, servizi alla persona o economia sociale. Tuttavia, la natura spesso selettiva e progettuale di questi strumenti Invitalia richiede una verifica puntuale dei requisiti soggettivi e delle spese ammissibili prima di candidarsi.</t>
+          <t>Il bando 'Vita &amp; Opportunità' di Invitalia supporta iniziative legate all'inclusione sociale e allo sviluppo territoriale, potenzialmente accessibile a PMI del Cilento che operano nei settori del welfare, servizi alla persona o economia sociale. Tuttavia, la natura generica del titolo e la gestione centralizzata tramite Invitalia richiedono una verifica puntuale dei requisiti settoriali e dimensionali prima di procedere.</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Il meccanismo finanzia tecnologie specifiche per le energie rinnovabili, potenzialmente accessibile a PMI del Cilento che intendono investire in impianti fotovoltaici, eolici o da biomasse, settori strategici in un territorio ricco di risorse naturali. La pertinenza è media perché i meccanismi UE di questo tipo spesso richiedono capacità progettuali e finanziarie non banali per una piccola impresa, rendendo consigliabile l'aggregazione con altri soggetti o il supporto di un intermediario finanziario.</t>
+          <t>Il meccanismo finanzia tecnologie specifiche per le energie rinnovabili, potenzialmente accessibile a PMI del Cilento che operano nei settori agricolo, turistico o industriale e intendono installare impianti fotovoltaici, eolici o da biomasse per ridurre i costi energetici. La complessità burocratica tipica dei bandi UE diretti e la necessità di specifiche competenze tecniche possono rappresentare una barriera per le imprese di piccola dimensione senza supporto consulenziale.</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Il bando ESF sostiene l'inclusione finanziaria e l'incubazione di nuovi imprenditori, potenzialmente utile per PMI del Cilento che vogliono accedere a strumenti di finanza alternativa o percorsi di accompagnamento all'imprenditorialità, ma la natura europea e la focalizzazione sull'inclusione potrebbero limitare l'accesso diretto alle imprese già costituite.</t>
+          <t>Il bando ESF sostiene l'accesso a servizi di incubazione e finanza inclusiva per nuovi imprenditori e micro/piccole imprese, coprendo potenzialmente costi di avvio, mentoring e accesso al credito agevolato. Per una PMI del Cilento già operativa è meno diretto, ma rappresenta un'opportunità concreta per chi vuole avviare nuove attività o spin-off in aree a rischio di esclusione economica.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca e sviluppo su prodotti bio-based derivati da organismi marini, settore strategico per una PMI del Cilento con attività legate alla pesca, acquacoltura o trasformazione di prodotti ittici. Tuttavia, la complessità dei bandi Horizon e la necessità di partecipare in consorzio europeo rendono l'accesso impegnativo per una piccola impresa senza esperienza pregressa in progetti UE.</t>
+          <t>Il bando Horizon finanzia ricerca e sviluppo su prodotti bio-based derivati da organismi marini, settore strategico per il Cilento grazie alla sua tradizione ittica e alle risorse costiere. Una PMI del settore pesca, acquacoltura o biotech marino può partecipare in consorzio europeo, finanziando attività di R&amp;S, prototipazione e valorizzazione di biomasse marine, ma la complessità progettuale Horizon richiede partner accademici e capacità di gestione elevata.</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti di ricerca e innovazione su filiere alimentari sostenibili, bioeconomia e biodiversità, ambiti in cui le PMI del Cilento (produzione olivicola, cerealicola, zootecnica, pesca) possono partecipare come partner industriali in consorzi europei. La pertinenza è media perché Horizon richiede partenariati transnazionali complessi e capacità progettuali elevate, rendendo l'accesso diretto difficile senza il supporto di enti di ricerca o reti di cluster.</t>
+          <t>Il bando finanzia progetti di ricerca e innovazione per catene del valore sostenibili nel settore agroalimentare, con focus su biodiversità e bioeconomia: una PMI del Cilento attiva nella filiera agroalimentare (es. produzione di olio DOP, legumi tipici, pesca) può partecipare come partner di un consorzio europeo, coprendo costi di R&amp;S e sperimentazione. La pertinenza è Media perché Horizon richiede partnership transnazionali strutturate e capacità progettuali elevate, spesso difficili per PMI molto piccole senza supporto di enti di ricerca.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e innovazione sulla biodiversità agraria e la sicurezza alimentare, temi centrali per le PMI agricole del Cilento, ricco di produzioni tradizionali e cultivar autoctone (es. fagioli, fichi, olio). Tuttavia, i bandi Horizon richiedono tipicamente la partecipazione in partenariato europeo e una capacità progettuale elevata, rendendo l'accesso diretto più complesso per una piccola impresa senza il supporto di enti di ricerca o consorzi.</t>
+          <t>Il bando Horizon finanzia progetti di ricerca e innovazione sulla biodiversità agricola e la sicurezza alimentare, settori strategici per le PMI agroalimentari del Cilento (DOP, IGP, produzioni tradizionali). Tuttavia, la complessità dei requisiti Horizon e la necessità di partecipare in consorzio europeo rendono l'accesso impegnativo per una PMI di piccola dimensione, che dovrebbe cercare un partner accademico o un centro di ricerca come capofila.</t>
         </is>
       </c>
     </row>
@@ -1648,29 +1648,29 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia lo sviluppo di tecniche di ricarica gestita delle falde acquifere in contesti rurali, settore strategico per il Cilento dove la siccità stagionale penalizza le imprese agricole e zootecniche. Una PMI agricola o una cooperativa del territorio può partecipare come partner in un consorzio europeo, accedendo a finanziamenti per R&amp;S su gestione idrica sostenibile, con ricadute concrete sulla resilienza produttiva.</t>
+          <t>Il bando finanzia lo sviluppo di tecniche di ricarica artificiale delle falde acquifere (MAR) in contesti rurali, con forte rilevanza per il Cilento dove la gestione idrica agricola è critica: una PMI agricola o una società di servizi ambientali può candidarsi per sviluppare o testare soluzioni innovative per l'irrigazione sostenibile. La complessità dei bandi Horizon richiede tuttavia partnership con enti di ricerca, il che può rappresentare una barriera per le PMI più piccole senza esperienza europea.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SSbD bio-based alternatives for fertilising and/or crop protection products</t>
+          <t>Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1690,19 +1690,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Internazionalizzazione</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia ricerca e sviluppo di alternative bio-based a fertilizzanti e prodotti fitosanitari secondo il principio Safe-and-Sustainable-by-Design, settore rilevante per le PMI agricole del Cilento che operano in aree protette con vincoli sull'uso di agrofarmaci. Tuttavia, i requisiti tecnici elevati e la natura competitiva di Horizon Europe rendono l'accesso difficile per una PMI senza partnership con enti di ricerca o università.</t>
+          <t>Il bando Horizon finanzia partenariati internazionali nel settore culturale e delle industrie creative (CCI), ambiti in cui il Cilento ha risorse identitarie forti (artigianato, patrimonio UNESCO, enogastronomia). Tuttavia, i requisiti consorziali e la complessità progettuale tipica di Horizon rendono l'accesso difficile per una PMI senza un partner capofila accademico o istituzionale già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
+          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1737,19 +1737,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti per monitorare la salute del suolo attraverso campionamento, analisi e interpretazione di indicatori, ambito direttamente rilevante per PMI agricole del Cilento (olivicoltura, viticoltura, orticoltura) che vogliono migliorare la gestione sostenibile dei terreni. La complessità procedurale di Horizon e la necessità di partecipare in consorzio internazionale limitano l'accesso diretto, ma una PMI può entrare come partner operativo portando competenze territoriali concrete.</t>
+          <t>Il bando finanzia progetti di co-gestione degli ecosistemi marini e delle acque dolci con il coinvolgimento diretto dei pescatori, rendendo potenzialmente eleggibili cooperative e PMI della pesca del Cilento (es. flotte di Agropoli, Pisciotta, Camerota) per attività di ricerca partecipativa, monitoraggio delle risorse ittiche e sviluppo di modelli di governance sostenibile. La pertinenza è media perché si tratta di un bando Horizon UE che richiede la partecipazione a consorzi internazionali e capacità progettuali elevate, solitamente non alla portata di una PMI locale senza il supporto di un ente di ricerca capofila.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
+          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-05</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1784,39 +1784,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Internazionalizzazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e innovazione nel settore delle industrie culturali e creative (CCI), favorendo partnership internazionali: una PMI del Cilento attiva in ambito culturale, artigianato creativo o turismo esperienziale può partecipare come partner (non capofila) in consorzi europei, accedendo a fondi per attività di networking, sviluppo di modelli innovativi e scambi transnazionali. Tuttavia, la complessità procedurale di Horizon e la necessità di costruire consorzi internazionali rendono l'accesso impegnativo per strutture aziendali di piccole dimensioni senza supporto specializzato.</t>
+          <t>Il bando finanzia soluzioni dimostrative per proteggere il patrimonio culturale dagli impatti del cambiamento climatico, settore rilevante per una PMI del Cilento (area ricca di siti UNESCO e beni archeologici come Paestum e Velia). Tuttavia, essendo un bando Horizon UE, richiede partecipazione in consorzi internazionali e capacità di R&amp;S elevata, il che rende l'accesso diretto complesso per una PMI piccola, che dovrebbe considerare un ruolo di partner tecnico specializzato.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
+          <t>EdTech Accelerator</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-SKILLS-10-EDTECH</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - DIGITAL</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1831,39 +1831,39 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di co-gestione delle risorse marine e delle acque interne, rilevante per PMI della pesca e acquacoltura del Cilento (area costiera e laghi/fiumi del Parco Nazionale). La partecipazione richiede però la costituzione di consorzi europei, il che rende l'accesso diretto complesso per una piccola impresa, che dovrebbe inserirsi come partner in un progetto coordinato da enti di ricerca.</t>
+          <t>Il bando finanzia soluzioni tecnologiche applicate all'educazione (EdTech), quindi è rilevante per PMI campane attive nello sviluppo di software, e-learning o servizi formativi digitali. Le PMI del Cilento con vocazione turistica o rurale potrebbero trovare difficoltà di accesso se non hanno un profilo tecnologico specifico nel settore education.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
+          <t>EU support to Stakeholders to improve measurement of food waste and help implement food waste prevention in their operations and organisation - 2026-2027</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SMP-FOOD-2026-FW-STAKEHOLDERS-PJ</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - SMP</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1878,24 +1878,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia soluzioni innovative per proteggere il patrimonio culturale dagli impatti climatici, settore rilevante per il Cilento con i suoi siti UNESCO e beni storici vulnerabili. Tuttavia, i bandi Horizon richiedono tipicamente consorzi internazionali e capacità di ricerca elevata, rendendo l'accesso diretto complesso per una PMI senza partner accademici o tecnologici già consolidati.</t>
+          <t>Il bando supporta operatori della filiera alimentare (produttori, trasformatori, distributori, ristorazione) nell'implementare sistemi di misurazione e prevenzione degli sprechi alimentari: particolarmente rilevante per le PMI agroalimentari del Cilento (es. produttori DOP/IGP, agriturismi, piccole industrie di trasformazione) che vogliono migliorare l'efficienza operativa e rispondere alle crescenti richieste di sostenibilità. La pertinenza è Media perché si tratta di un bando UE-SMP con procedure spesso complesse e criteri competitivi che possono penalizzare realtà molto piccole senza struttura amministrativa adeguata.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
+          <t>Accessible and available travel facilitation</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-06-CLIMA-SOIL</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1925,39 +1925,39 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti dimostrativi per aumentare la resilienza del suolo agli eventi climatici estremi e garantire la sicurezza alimentare, temi centrali per le PMI agricole del Cilento esposte a siccità e dissesto idrogeologico. L'accesso richiede però la partecipazione a consorzi internazionali e una capacità progettuale elevata, il che rende necessario affidarsi a partner di ricerca o intermediari per candidarsi efficacemente.</t>
+          <t>Il bando finanzia soluzioni per rendere i viaggi più accessibili e inclusivi, un tema rilevante per operatori turistici del Cilento che vogliono sviluppare offerte per persone con mobilità ridotta o esigenze speciali. Tuttavia, Horizon richiede generalmente consorzi internazionali e capacità di R&amp;S, rendendo l'accesso diretto complesso per una PMI senza partner di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EU support to Stakeholders to improve measurement of food waste and help implement food waste prevention in their operations and organisation - 2026-2027</t>
+          <t>Cooperation of Artificial Intelligence Factories and Factories Antennas</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SMP-FOOD-2026-FW-STAKEHOLDERS-PJ</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-COAIF-03</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>UE - SMP</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1967,44 +1967,44 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Bassa</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Il bando supporta stakeholder della filiera alimentare — incluse PMI della trasformazione, ristorazione e distribuzione — nell'adottare strumenti di misurazione e prevenzione degli sprechi alimentari, con potenziale rilevanza per le imprese agroalimentari del Cilento (olio, conserve, prodotti ittici). L'accessibilità è media perché il programma SMP tende a privilegiare associazioni di categoria e organizzazioni rappresentative piuttosto che singole PMI.</t>
+          <t>Il bando Horizon finanzia la creazione e cooperazione tra grandi infrastrutture europee di intelligenza artificiale (AI Factories), strutture di scala nazionale/continentale che richiedono consorzi di ricerca avanzati e capacità computazionali enormi, del tutto fuori dalla portata diretta di una PMI del Cilento. Una piccola impresa campana potrebbe al massimo beneficiarne indirettamente come utente finale dei servizi AI generati, ma non come soggetto proponente o beneficiario diretto dei fondi.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Accessible and available travel facilitation</t>
+          <t>Information and training measures for workers' organisations</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-INFO-WK</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - SOCPL</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2014,39 +2014,39 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Bassa</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia soluzioni per rendere i viaggi più accessibili e inclusivi, un tema rilevante per operatori turistici del Cilento che possono sviluppare servizi per persone con mobilità ridotta o esigenze speciali. Tuttavia, Horizon richiede tipicamente consorzi transnazionali e capacità di R&amp;I elevata, il che rende l'accesso diretto difficile per una PMI senza partner di ricerca.</t>
+          <t>Il bando è destinato alle organizzazioni dei lavoratori (sindacati e simili) per attività informative e formative rivolte ai propri rappresentanti, non alle PMI in quanto imprese. Una piccola impresa del Cilento non rientra tra i beneficiari diretti ammissibili.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Cooperation of Artificial Intelligence Factories and Factories Antennas</t>
+          <t>Renewable energy technology (RET) solutions in energy communities</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>18/12/2025</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-COAIF-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-2-PRIZE</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2071,34 +2071,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia la creazione di infrastrutture di supercalcolo e AI su scala europea (AI Factories), con requisiti tecnici e consorziali fuori dalla portata di una PMI del Cilento. L'accesso diretto è riservato a grandi centri di ricerca e consorzi nazionali, rendendo la partecipazione di una piccola impresa locale praticamente impossibile senza un ruolo marginale in un consorzio già strutturato.</t>
+          <t>Il bando Horizon UE richiede consorzi internazionali di ricerca con capacità tecnico-scientifiche avanzate e budget elevati, difficilmente accessibili a una PMI del Cilento in autonomia. Tuttavia, una PMI attiva nel settore energetico potrebbe partecipare come partner industriale in un consorzio guidato da università o centri di ricerca, con spese ammissibili per attività di sviluppo tecnologico legate alle comunità energetiche rinnovabili.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Information and training measures for workers' organisations</t>
+          <t>Call for proposals to national data protection authorities on reaching out to stakeholders in data protection legislation</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-INFO-WK</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-DATA</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>UE - SOCPL</t>
+          <t>UE - CERV</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2113,19 +2113,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto specificamente alle organizzazioni dei lavoratori (sindacati e associazioni di rappresentanza), non alle PMI in quanto tali, rendendo di fatto inaccessibile la partecipazione diretta per una piccola o media impresa del Cilento. Una PMI potrebbe al massimo beneficiarne indirettamente tramite accordi con organizzazioni sindacali partner, ma non come soggetto beneficiario principale.</t>
+          <t>Il bando è rivolto esclusivamente alle Autorità nazionali per la protezione dei dati (come il Garante Privacy), non alle PMI: una piccola o media impresa del Cilento non è beneficiaria ammissibile e non può presentare domanda. Non sono finanziabili attività aziendali né spese tipiche delle PMI.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Renewable energy technology (RET) solutions in energy communities</t>
+          <t>HORIZON-EIC-2026-BAS-02-SCLATEUP</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>18/12/2025</t>
+          <t>03/03/2026</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-2-PRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-BAS-02-SCALEUP</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2165,34 +2165,35 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede consorzi internazionali, capacità di ricerca avanzata e budget elevati tipicamente fuori portata per una PMI del Cilento senza un partner capofila istituzionale; tuttavia, una PMI del settore energetico potrebbe partecipare come soggetto associato in progetti sulle comunità energetiche rinnovabili, tema molto rilevante per aree rurali come il Cilento.</t>
+          <t>Il bando EIC Scale-Up finanzia PMI innovative ad alto potenziale tecnologico in fase di crescita accelerata, con ticket di investimento tipicamente superiori ai 10 milioni di euro, richiedendo già validazione di mercato internazionale e capacità di scaling globale. Una PMI campana del Cilento, salvo casi eccezionali di deep-tech già internazionalizzato, difficilmente soddisfa i requisiti di maturità tecnologica e finanziaria richiesti.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Call for proposals to national data protection authorities on reaching out to stakeholders in data protection legislation</t>
+          <t>Istituzione dell'elenco degli Organismi di Formazione e di Consulenza Qualificati ai fini
+dell'attuazione degli interventi SRH 01, SRH 03, e SRG 09</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>30 giugno 2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-DATA</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/AKIS-avviso.html</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>UE - CERV</t>
+          <t>Regione Campania - Agricoltura</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2207,39 +2208,39 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto esclusivamente alle autorità nazionali per la protezione dei dati (come il Garante Privacy), non alle PMI: una piccola o media impresa del Cilento non può candidarsi né beneficiare direttamente di questi fondi. Non sono finanziabili attività aziendali, formazione interna o adeguamento normativo per imprese private.</t>
+          <t>Il bando non finanzia le PMI direttamente, ma istituisce un elenco di Organismi di Formazione e Consulenza abilitati a erogare servizi nell'ambito del PSR Campania: è quindi rilevante solo per enti accreditati o società di consulenza che vogliono operare come fornitori qualificati. Una PMI agricola del Cilento beneficia indirettamente solo se si rivolge successivamente a questi organismi per accedere agli interventi SRH01, SRH03 e SRG09.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-EIC-2026-BAS-02-SCLATEUP</t>
+          <t>Backbone connectivity for Digital Global Gateways - Works</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-BAS-02-SCALEUP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-WORKS</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - CEF2027</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2254,40 +2255,39 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Il bando EIC Scale-Up è destinato a startup e PMI ad alto contenuto tecnologico con ambizioni di crescita europea, richiedendo innovazioni deep-tech già validate e capacità di raccolta fondi privati: barriere difficilmente superabili per una PMI tradizionale del Cilento. I finanziamenti (equity e grants fino a milioni di euro) presuppongono un profilo di impresa innovativa con track record internazionale, lontano dal tessuto produttivo locale.</t>
+          <t>Il bando CEF2 finanzia opere infrastrutturali di connettività backbone a scala europea, destinate a grandi operatori di telecomunicazioni o consorzi pubblici/privati di rilevanza transnazionale. Una PMI del Cilento non ha né la capacità tecnica né la dimensione finanziaria per partecipare a progetti di questa portata.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Istituzione dell'elenco degli Organismi di Formazione e di Consulenza Qualificati ai fini
-dell'attuazione degli interventi SRH 01, SRH 03, e SRG 09</t>
+          <t>Backbone connectivity for Digital Global Gateways - Studies</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30 giugno 2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/AKIS-avviso.html</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-STUDIES</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Regione Campania - Agricoltura</t>
+          <t>UE - CEF2027</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Il bando non finanzia imprese ma istituisce un elenco di organismi qualificati per erogare formazione e consulenza nel settore agricolo (interventi del PSR Campania): è rilevante solo per enti di formazione o società di consulenza agricola che vogliono accreditarsi, non per una PMI che cerca finanziamenti diretti.</t>
+          <t>Il bando CEF 2027 finanzia studi su infrastrutture di connettività backbone a scala europea (Digital Global Gateways), rivolto a grandi operatori di telecomunicazioni, consorzi internazionali o enti pubblici con capacità progettuali di alto livello tecnico e finanziario. Una PMI del Cilento non ha i requisiti dimensionali, tecnici né il profilo istituzionale per accedere a questo tipo di call.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Backbone connectivity for Digital Global Gateways - Works</t>
+          <t>Equipment for smart European cable systems - Works</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-WORKS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-SMART-CABLES-WORKS</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2354,34 +2354,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 per la connettività backbone dei Digital Global Gateways finanzia grandi infrastrutture di rete transfrontaliera, con requisiti tecnici e finanziari accessibili solo a grandi operatori TLC o consorzi pubblici. Una PMI del Cilento non ha né la dimensione né il profilo per partecipare direttamente a progetti di questa natura.</t>
+          <t>Il bando CEF2027 per sistemi di cavi europei (infrastrutture di connettività transeuropee) è destinato a grandi operatori del settore delle telecomunicazioni e infrastrutture, con requisiti tecnici e finanziari del tutto fuori portata per una PMI del Cilento. Le opere su cavi sottomarini o reti dorsali europee richiedono capacità esecutive e finanziarie incompatibili con la dimensione di una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Backbone connectivity for Digital Global Gateways - Studies</t>
+          <t>Networks of European Cinemas</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-STUDIES</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-CINNET</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>UE - CEF2027</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2396,39 +2396,39 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2 finanzia studi su infrastrutture di connettività backbone a scala europea (cavi sottomarini, reti ad alta capacità transazionali), rivolti tipicamente a grandi operatori TLC, consorzi pubblici o organismi istituzionali. Una PMI campana, anche del settore ICT, non ha i requisiti dimensionali né la capacità tecnico-finanziaria per partecipare a progetti di questa portata.</t>
+          <t>Il bando MEDIA/CREA2027 'Networks of European Cinemas' è destinato a reti di esercenti cinematografici su scala europea, richiedendo partenariati transnazionali strutturati e capacità di programmazione di film europei non nazionali: una PMI isolata del Cilento difficilmente soddisfa i requisiti minimi di aggregazione e volume di attività richiesti. Solo una sala cinematografica già inserita in un circuito europeo (es. Europa Cinemas) potrebbe beneficiarne concretamente.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Equipment for smart European cable systems - Works</t>
+          <t>Films on the Move</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-SMART-CABLES-WORKS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-FILMOVE</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>UE - CEF2027</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2443,39 +2443,39 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 riguarda infrastrutture di cablaggio europeo su larga scala e si rivolge a grandi operatori di telecomunicazioni o consorzi infrastrutturali, non a PMI locali. Una piccola impresa del Cilento non ha le dimensioni tecniche né finanziarie per partecipare a progetti di questa natura.</t>
+          <t>Il programma MEDIA 'Films on the Move' finanzia la distribuzione internazionale di film europei ed è rivolto a distributori cinematografici professionali, non a PMI generiche del Cilento o della Campania. Una piccola impresa locale difficilmente possiede i requisiti settoriali e strutturali richiesti (distribuzione di opere audiovisive in mercati esteri europei).</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Networks of European Cinemas</t>
+          <t>Safeguarding Europe’s Born-digital Heritage</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-CINNET</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-BORN-DIGITAL-HERITAGE</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia reti di sale cinematografiche europee nell'ambito del programma Creative Europe, richiedendo la costituzione di consorzi transnazionali tra esercenti cinema: una PMI del Cilento non operante nel settore dell'esercizio cinematografico non ha accesso diretto, e anche per una sala cinema locale la complessità della rete europea richiesta rende la partecipazione molto difficile senza partner consolidati.</t>
+          <t>Il bando riguarda la salvaguardia del patrimonio culturale digitale europeo ed è orientato a istituzioni pubbliche, archivi, biblioteche e grandi enti culturali, non a PMI commerciali. Una piccola impresa del Cilento avrebbe difficoltà a qualificarsi come beneficiaria diretta e i requisiti tecnici e istituzionali risultano inaccessibili per realtà di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Films on the Move</t>
+          <t>Support for social dialogue</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-FILMOVE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-SOC-DIALOG</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - SOCPL</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2542,34 +2542,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Films on the Move è un programma MEDIA/Creative Europe destinato a distributori cinematografici europei per la circolazione transnazionale di film non nazionali: non è accessibile a PMI generiche del Cilento o della Campania, ma solo a società di distribuzione cinematografica con track record specifico nel settore audiovisivo europeo. Una piccola impresa locale difficilmente possiede i requisiti settoriali e strutturali richiesti.</t>
+          <t>Il bando UE SOCPL sul dialogo sociale è destinato a organizzazioni sindacali, datoriali e parti sociali a livello europeo, non a PMI individuali: una piccola impresa del Cilento non ha i requisiti soggettivi né la struttura per candidarsi direttamente. L'unico coinvolgimento possibile sarebbe indiretto, tramite associazioni di categoria che partecipano ai progetti finanziati.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Europe’s Born-digital Heritage</t>
+          <t>Empowering youth in the EU Outermost Regions – YOUTH 4 OUTERMOST REGIONS (#YOUTH4ORS)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-BORN-DIGITAL-HERITAGE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-YOUTH4OR2</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>UE - ERDFTA</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2584,39 +2584,39 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Digitalizzazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la salvaguardia del patrimonio culturale digitale europeo ed è tipicamente rivolto a istituzioni pubbliche, archivi, biblioteche o consorzi di ricerca, rendendo molto difficile per una PMI campana del Cilento accedere direttamente come beneficiaria principale. Le spese finanziabili (digitalizzazione e conservazione di heritage digitale) sono lontane dalle attività produttive tipiche delle piccole imprese locali.</t>
+          <t>Il bando è specificamente rivolto alle Regioni Ultraperiferiche dell'UE (come Azzorre, Canarie, Martinica, ecc.), territori che non includono la Campania né il Cilento, rendendo di fatto inaccessibile questo finanziamento per qualsiasi PMI del territorio campano.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Support for social dialogue</t>
+          <t>The European Capital of Innovation Award Rising Innovator Category HORIZON-EIC-2026-PRIZE-ICAPITAL</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-SOC-DIALOG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-02</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>UE - SOCPL</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2631,39 +2631,39 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Il bando UE 'Support for social dialogue' finanzia organizzazioni di rappresentanza (sindacati, associazioni datoriali) per attività di dialogo sociale a livello europeo, non è accessibile direttamente a una PMI operativa del Cilento. Una piccola o media impresa non rientra tra i beneficiari ammissibili e non può presentare domanda autonomamente.</t>
+          <t>Il premio European Capital of Innovation è rivolto esclusivamente a città e autorità locali europee che dimostrano capacità di innovazione urbana, non a PMI o imprese private. Una PMI del Cilento non ha titolarità per candidarsi direttamente a questo bando.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Empowering youth in the EU Outermost Regions – YOUTH 4 OUTERMOST REGIONS (#YOUTH4ORS)</t>
+          <t>The European Capital of Innovation Award iCapital Category HORIZON-EIC-2026-ICAPITAL</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-YOUTH4OR2</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-01</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>UE - ERDFTA</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2678,39 +2678,39 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Il bando è specificamente destinato alle Regioni Ultraperiferiche dell'UE (Azzorre, Canarie, Guadalupa, ecc.), territori che non includono la Campania né il Cilento, rendendo le PMI campane non eleggibili come beneficiarie dirette. Non esistono opportunità concrete di accesso per imprese localizzate nel Sud Italia continentale.</t>
+          <t>Il bando premia intere città europee per le loro politiche di innovazione urbana, non è accessibile a singole PMI o territori rurali come il Cilento. Una piccola impresa campana non può candidarsi direttamente e difficilmente trae benefici concreti da questo riconoscimento istituzionale.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>The European Capital of Innovation Award Rising Innovator Category HORIZON-EIC-2026-PRIZE-ICAPITAL</t>
+          <t>Support to awareness raising about the Arctic communities, including Indigenous People</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EMFAF-2026-PIA-ARCTIC</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - EMFAF</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2725,39 +2725,39 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Il premio European Capital of Innovation è destinato a città e autorità locali che promuovono ecosistemi di innovazione urbana, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né ricevere finanziamenti da questo bando. L'unica utilità indiretta sarebbe partecipare a iniziative di un comune candidato, scenario poco probabile per territori rurali come il Cilento.</t>
+          <t>Il bando riguarda la sensibilizzazione sulle comunità artiche e i popoli indigeni, un tema completamente estraneo al contesto produttivo, geografico e settoriale di una PMI campana o del Cilento. Non esistono spese finanziabili né attività riconducibili alle realtà imprenditoriali locali.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>The European Capital of Innovation Award iCapital Category HORIZON-EIC-2026-ICAPITAL</t>
+          <t>Industrial Readiness for Affordable Ka-band User Terminals</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-IRIS2-UT-IND-READINESS</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2777,34 +2777,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Il bando premia intere città europee per le loro politiche di innovazione urbana e non è accessibile direttamente alle PMI: i destinatari sono enti municipali e amministrazioni locali. Una PMI del Cilento non può candidarsi autonomamente e difficilmente trarrebbe un beneficio diretto da questo premio.</t>
+          <t>Il bando riguarda lo sviluppo industriale di terminali utente in banda Ka per comunicazioni satellitari, un settore altamente specializzato che richiede competenze aerospaziali e capacità produttive avanzate difficilmente disponibili in una PMI del Cilento o della Campania in generale. Le risorse e i requisiti tecnici richiesti sono orientati a grandi player dell'industria spaziale europea, rendendo l'accesso sostanzialmente inaccessibile per una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Support to awareness raising about the Arctic communities, including Indigenous People</t>
+          <t>Capacity building for Ukrainian regional policy stakeholders</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EMFAF-2026-PIA-ARCTIC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-UAACQUIS22</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>UE - EMFAF</t>
+          <t>UE - ERDFTA</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2819,39 +2819,39 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la sensibilizzazione sulle comunità artiche e i popoli indigeni del Grande Nord, un tema completamente estraneo al contesto territoriale e produttivo del Cilento e della Campania. Non esistono attività finanziabili rilevanti per una PMI locale di qualsiasi settore operante in quest'area.</t>
+          <t>Il bando è destinato a stakeholder della politica regionale ucraina per attività di capacity building istituzionale, quindi non è accessibile a PMI italiane del Cilento o della Campania. Non prevede finanziamenti diretti per imprese private né spese tipicamente sostenibili da una piccola o media impresa.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Industrial Readiness for Affordable Ka-band User Terminals</t>
+          <t>ERC ADVANCED GRANTS</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-IRIS2-UT-IND-READINESS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-ADG</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2871,34 +2871,34 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo industriale di terminali utente in banda Ka per comunicazioni satellitari, un settore altamente specializzato che richiede competenze avanzate in ingegneria delle telecomunicazioni e capacità produttive difficilmente reperibili in una PMI del Cilento. L'accesso è praticamente precluso a realtà locali di piccola dimensione senza una filiera consolidata nel settore spaziale o aerospaziale.</t>
+          <t>Gli ERC Advanced Grants sono destinati esclusivamente a ricercatori individuali di eccellenza con track record scientifico consolidato, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né rientra tra i beneficiari ammissibili. Il bando finanzia ricerca di frontiera in ambito accademico, rendendo l'accesso concreto per una PMI praticamente nullo salvo partecipazione marginale come partner di un ente di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Capacity building for Ukrainian regional policy stakeholders</t>
+          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-UAACQUIS22</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>UE - ERDFTA</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2913,34 +2913,34 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Internazionalizzazione</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Il bando è destinato a stakeholder istituzionali ucraini nell'ambito delle politiche regionali e non prevede la partecipazione diretta di PMI italiane come beneficiari. Una piccola impresa del Cilento non ha accesso diretto a questi fondi né un profilo compatibile con le attività finanziabili.</t>
+          <t>Il bando Horizon è focalizzato su ricerca sanitaria digitale e AI in Africa sub-sahariana, richiedendo consorzi internazionali complessi e capacità di ricerca avanzata difficilmente accessibili a una PMI del Cilento. Non sono previste attività o mercati di sbocco rilevanti per il tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ERC ADVANCED GRANTS</t>
+          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-ADG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2960,19 +2960,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Gli ERC Advanced Grants sono destinati esclusivamente a ricercatori individuali con track record scientifico eccezionale, non a PMI: una piccola o media impresa del Cilento non può candidarsi direttamente né beneficiare dei fondi. Il bando richiede strutture di ricerca accademica di alto livello, rendendo l'accesso di fatto impossibile per una PMI tradizionale.</t>
+          <t>Il bando Horizon è orientato a grandi reti accademiche e istituzionali nel settore farmaceutico/regolatorio, con requisiti consortili e capacità progettuali difficilmente accessibili a una PMI del Cilento. Le attività finanziate riguardano formazione avanzata su etica, farmacovigilanza e piattaforme digitali regolatorie, ambiti lontani dal tessuto produttivo locale prevalentemente orientato a turismo, agricoltura e artigianato.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
+          <t>HORIZON-JU-EDCTP3-2026-Dr Pascoal Mocumbi Prize</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-DRPASCOALMOCUMBIPRIZE</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3007,19 +3007,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è focalizzato su ricerca sanitaria e AI in Africa subsahariana, richiedendo partnership internazionali strutturate e capacità di ricerca avanzata difficilmente accessibili a una PMI campana del Cilento. Non vi è alcuna connessione con il tessuto produttivo locale né con i settori prevalenti nell'area.</t>
+          <t>Il Premio Dr Pascoal Mocumbi è un riconoscimento nell'ambito della ricerca sulle malattie infettive della povertà in Africa subsahariana, destinato a ricercatori o istituzioni scientifiche, non a PMI. Una piccola impresa del Cilento non ha né il profilo né le attività richieste per candidarsi a questo tipo di premio accademico-scientifico.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
+          <t>HORIZON-JU-EDCTP3-2026-Outstanding Female Scientist Prize</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSFEMALESCIENTISTPRIZE</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3054,19 +3054,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia reti di formazione e innovazione nel settore farmaceutico e della farmacovigilanza, richiedendo consorzi internazionali e competenze altamente specializzate difficilmente accessibili a una PMI del Cilento. La struttura tipica di questi progetti Horizon privilegia grandi enti di ricerca, università e multinazionali del farmaco, rendendo la partecipazione diretta di una piccola impresa locale molto improbabile senza un ruolo marginale in un consorzio già strutturato.</t>
+          <t>Si tratta di un premio individuale destinato a ricercatrici eccellenti nell'ambito della ricerca su malattie infettive nei paesi a basso reddito: non è uno strumento finanziario accessibile a una PMI campana e non prevede finanziamenti per attività aziendali, spese operative o progetti d'impresa.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Dr Pascoal Mocumbi Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Outstanding Research Team Prize</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-DRPASCOALMOCUMBIPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSRESEARCHTEAMPRIZE</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Il Premio Dr Pascoal Mocumbi è un riconoscimento internazionale nell'ambito della ricerca clinica sulle malattie infettive in Africa subsahariana, destinato a ricercatori e istituzioni scientifiche, non a PMI. Una piccola impresa del Cilento non ha né il profilo né l'operatività richiesta per partecipare a questo tipo di premio nell'ecosistema EDCTP3.</t>
+          <t>Si tratta di un premio europeo dedicato a team di ricerca di eccellenza nell'ambito della salute globale e delle malattie infettive (programma EDCTP3), strutturato per riconoscere risultati scientifici outstanding e non per finanziare attività operative di impresa. Una PMI del Cilento, salvo rarissimi casi di spin-off biomedici con track record di ricerca internazionale certificato, non ha i requisiti né il profilo per candidarsi.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Outstanding Female Scientist Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Man EU Prize</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSFEMALESCIENTISTPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPMANEUPRIZE</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3153,14 +3153,14 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio internazionale destinato a ricercatrici scientifiche eccellenti, non a PMI: non finanzia progetti aziendali, spese operative o attività produttive. Una PMI del Cilento non ha né i requisiti soggettivi né un vantaggio concreto da questo bando.</t>
+          <t>Si tratta di un premio europeo nell'ambito della ricerca medica e delle malattie infettive (EDCTP3), rivolto a ricercatori scientifici di eccellenza a livello internazionale, non a PMI. Una piccola impresa del Cilento non ha i requisiti né il profilo scientifico necessari per accedere a questo tipo di riconoscimento.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Outstanding Research Team Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman EU Prize</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSRESEARCHTEAMPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANEUPRIZE</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3200,14 +3200,14 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio per team di ricerca eccellente nell'ambito della ricerca globale su malattie infettive (programma EDCTP3), destinato a istituzioni di ricerca e non a PMI operative. Una piccola impresa del Cilento non ha i requisiti strutturali né il profilo scientifico richiesto per accedere a questo tipo di riconoscimento.</t>
+          <t>Si tratta di un premio europeo dedicato alla leadership scientifica femminile nell'ambito del partenariato EDCTP3 (ricerca su malattie infettive in paesi a basso reddito), non un bando a finanziamento diretto per PMI. Una PMI del Cilento non ha concrete possibilità di accesso né spese finanziabili, essendo rivolto a ricercatrici o istituzioni scientifiche di eccellenza.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Man EU Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman SSA Prize</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPMANEUPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANSSAPRIZE</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Il premio EDCTP3 è destinato a ricercatori e istituzioni scientifiche attive nella ricerca su malattie infettive in contesti globali, con requisiti di leadership scientifica difficilmente compatibili con una PMI del Cilento. Non prevede finanziamenti diretti per attività produttive, commerciali o di sviluppo aziendale tipiche delle piccole imprese campane.</t>
+          <t>Si tratta di un premio (Prize) nell'ambito di EDCTP3 focalizzato sulla leadership scientifica femminile in ambito sanitario/ricerca globale, destinato a ricercatrici individuali e non a PMI. Una piccola impresa del Cilento non ha né i requisiti soggettivi né il profilo scientifico richiesto per accedere a questo tipo di riconoscimento.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman EU Prize</t>
+          <t>ERC PLUS GRANTS</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANEUPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-PLUS</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3289,39 +3289,39 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo dedicato alla leadership scientifica femminile nell'ambito del programma EDCTP3, rivolto a ricercatrici nel campo delle malattie infettive della povertà: non è uno strumento di finanziamento diretto per PMI campane e non prevede spese ammissibili tipiche per imprese di piccola dimensione. Una PMI del Cilento non ha concreta possibilità di accesso né beneficio operativo da questo bando.</t>
+          <t>Gli ERC Plus Grants sono destinati a ricercatori con progetti ERC già finanziati, non a PMI: per accedere una piccola impresa del Cilento dovrebbe essere partner di un progetto ERC esistente, scenario praticamente impraticabile senza una struttura di ricerca consolidata. Il bando non finanzia direttamente attività produttive o commerciali tipiche di una PMI campana.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman SSA Prize</t>
+          <t>Centres of Vocational Excellence</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANSSAPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2026-PEX-COVE</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ERASMUS2027</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3336,34 +3336,34 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio (Prize) destinato a ricercatrici con ruoli di leadership scientifica nell'ambito della ricerca su malattie infettive nei Paesi a basso e medio reddito: non finanzia attività aziendali né progetti di PMI. Una piccola impresa del Cilento non ha accesso diretto né benefici concreti da questo bando.</t>
+          <t>Il bando Erasmus+ Centres of Vocational Excellence è rivolto principalmente a istituzioni di formazione professionale (IFP), enti pubblici e consorzi transnazionali, non a PMI singole; una piccola impresa del Cilento potrebbe partecipare solo come partner secondario in un consorzio già strutturato, ruolo difficile da costruire senza una rete istituzionale preesistente.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ERC PLUS GRANTS</t>
+          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-PLUS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-31</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3388,14 +3388,14 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>I grant ERC (European Research Council) sono destinati a ricercatori individuali di eccellenza affiliati a istituzioni accademiche o di ricerca, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né beneficiare facilmente di questi fondi senza una partnership strutturata con un ente di ricerca. Il meccanismo ERC Plus mira a valorizzare risultati ERC esistenti, rendendo l'accesso ancora più indiretto e complesso per realtà imprenditoriali di piccola dimensione.</t>
+          <t>Il bando Horizon Europe richiede capacità di ricerca e sviluppo avanzate nel settore spaziale (osservazione della Terra, telecomunicazioni satellitari), competenze altamente specializzate e partnership internazionali, requisiti difficilmente soddisfabili da una PMI del Cilento senza un solido track record in R&amp;D spaziale. L'accesso è realistico solo come partner junior in un consorzio europeo, non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Centres of Vocational Excellence</t>
+          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2026-PEX-COVE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-32</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>UE - ERASMUS2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Il bando Erasmus+ Centres of Vocational Excellence è rivolto principalmente a consorzi di istituti di istruzione e formazione professionale (IFP), enti pubblici e organizzazioni del settore educativo, non direttamente a PMI; una piccola impresa del Cilento potrebbe partecipare solo come partner secondario di un consorzio guidato da un istituto formativo, con ruolo marginale e oneri burocratici elevati.</t>
+          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata in tecnologie spaziali, osservazione della Terra e telecomunicazioni satellitari, competenze difficilmente presenti in una PMI del Cilento o della Campania senza un solido track record europeo nel settore. L'accesso è realistico solo per PMI altamente specializzate in deep-tech spaziale, tipicamente in partnership con enti di ricerca o grandi player del settore aerospaziale.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-31</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-82</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3482,14 +3482,14 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca e sviluppo avanzate nel settore spaziale (osservazione della Terra, telecomunicazioni satellitari), con requisiti tecnici e consorzî internazionali difficilmente accessibili per una PMI tradizionale del Cilento. Solo PMI altamente specializzate in tecnologie digitali o aerospaziali potrebbero partecipare, tipicamente come partner junior in progetti con grandi enti di ricerca.</t>
+          <t>Il bando richiede capacità industriali avanzate nello sviluppo di substrati SiC semi-isolanti e componenti GaN per applicazioni spaziali, un settore altamente specializzato con barriere tecnologiche e finanziarie elevatissime, di fatto inaccessibile per una PMI del Cilento priva di infrastrutture di ricerca nel settore dei semiconduttori. La natura critica dei componenti spaziali e i requisiti di qualificazione ESA/difesa rendono questo bando destinato a grandi player industriali o centri di ricerca con decennale esperienza nel settore EEE spaziale.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-32</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-11</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3524,19 +3524,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata nel settore spaziale (Earth Observation e telecomunicazioni satellitari), con requisiti tecnici e amministrativi difficilmente accessibili per una PMI di piccola dimensione del Cilento, che dovrebbe partecipare come partner in consorzi internazionali con centri di ricerca e grandi industrie aerospaziali. Solo PMI altamente specializzate in tecnologie spaziali o geospaziali potrebbero candidarsi in modo realistico.</t>
+          <t>Il bando riguarda lo sviluppo di infrastrutture spaziali europee (spazioporti) e si rivolge a grandi consorzi con capacità tecnologiche e finanziarie nel settore aerospaziale, del tutto estranee al tessuto produttivo di una PMI campana o cilentana. Non esistono attività finanziabili rilevanti per imprese locali di piccola-media dimensione operanti in settori tradizionali.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
+          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-82</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-85</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di substrati in carburo di silicio semi-isolante per componenti elettronici spaziali ad altissima specializzazione (GaN MMICs in banda millimetrica), richiedendo capacità di R&amp;D avanzatissime tipiche di grandi player aerospaziali o laboratori di ricerca. Una PMI del Cilento o della Campania difficilmente possiede le infrastrutture, le certificazioni spaziali e il know-how tecnologico necessari per partecipare competitivamente a questo tipo di progetto Horizon.</t>
+          <t>Il bando riguarda lo sviluppo di infrastrutture critiche per test di irradiazione ad alta energia di componenti elettronici spaziali (EEE), un settore altamente specializzato che richiede capacità tecnologiche avanzate tipiche di grandi operatori industriali o enti di ricerca. Una PMI del Cilento o della Campania difficilmente possiede i requisiti tecnici e strutturali per partecipare competitivamente a questo tipo di progetto Horizon legato all'autonomia spaziale europea.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
+          <t>Scientific analysis and exploitation of space data</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-11</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-61</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3618,19 +3618,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di spazioporti europei e l'accesso autonomo dell'UE allo spazio, un settore che richiede investimenti enormi e competenze altamente specializzate tipiche di grandi player aerospaziali. Una PMI del Cilento o della Campania, salvo rarissime eccezioni nel settore aerospaziale avanzato, non ha le dimensioni né il profilo tecnico per candidarsi competitivamente a questo tipo di progetto Horizon.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata, partenariati internazionali e competenze specifiche nell'analisi di dati spaziali, barriere difficilmente superabili per una PMI del Cilento senza un solido track record in R&amp;S spaziale. L'accesso è più realistico solo come partner minore in un consorzio guidato da università o grandi aziende del settore aerospaziale.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
+          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-85</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-86</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3670,14 +3670,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di infrastrutture di test per irradiazione ad alta energia di componenti elettronici spaziali (EEE), un settore altamente specializzato che richiede competenze e attrezzature di livello scientifico-industriale avanzato, tipico di grandi player aerospaziali o laboratori di ricerca. Una PMI del Cilento o della Campania difficilmente dispone delle capacità tecniche e finanziarie necessarie per partecipare in modo competitivo, salvo come partner junior in un consorzio con attori del settore spaziale.</t>
+          <t>Il bando riguarda lo sviluppo di tecnologie critiche per il rifornimento di carburante nello spazio nell'ambito del programma Horizon UE, un settore altamente specializzato che richiede competenze aerospaziali avanzate e strutture di ricerca difficilmente accessibili a una PMI del Cilento o della Campania in generale. Le risorse finanziabili sono orientate a R&amp;S su componentistica spaziale, rendendo il bando sostanzialmente inaccessibile per imprese di piccola o media dimensione senza un profilo tecnologico aerospaziale consolidato.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Scientific analysis and exploitation of space data</t>
+          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-61</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-81</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata in telerilevamento e analisi di dati satellitari, con consorzî internazionali e budget elevati, strutturalmente difficili da gestire per una PMI del Cilento senza un dipartimento R&amp;D dedicato o partnership con enti di ricerca. Solo PMI tecnologiche specializzate in geospaziario o agricoltura di precisione potrebbero candidarsi come partner junior in un consorzio capofila universitario.</t>
+          <t>Il bando richiede lo sviluppo di componenti elettronici spaziali ad altissima specializzazione (FPGA su nodo tecnologico 7nm con resistenza alle radiazioni), un settore di nicchia che presuppone capacità R&amp;D avanzate, infrastrutture di test specifiche e competenze in elettronica spaziale difficilmente reperibili in una PMI del Cilento o della Campania. L'orientamento è verso grandi player dell'industria spaziale europea o laboratori di ricerca altamente specializzati, rendendo l'accesso concreto quasi impossibile per una PMI locale di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
+          <t>Microelectronic – Front-End Module (FEM)</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-86</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di tecnologie spaziali critiche per l'autonomia strategica europea, in particolare interfacce per il rifornimento di satelliti in orbita: si tratta di un settore altamente specializzato che richiede competenze aerospaziali avanzate, certificazioni specifiche e capacità R&amp;D difficilmente presenti in una PMI del Cilento o della Campania non operante nel comparto spazio-difesa. Una PMI locale potrebbe partecipare solo come partner minoritario di un consorzio guidato da grandi player aerospaziali.</t>
+          <t>Il bando Horizon focalizzato sui moduli front-end per microelettronica richiede capacità di R&amp;D avanzata e infrastrutture tecnologiche tipiche di grandi aziende o centri di ricerca specializzati, rendendo l'accesso molto difficile per una PMI del Cilento che opera in settori tradizionali. Solo PMI già inserite in filiere dell'elettronica o della componentistica ad alta tecnologia potrebbero partecipare, preferibilmente in consorzio con università o grandi imprese.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
+          <t>Trafficking in human beings</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-81</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-THB</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ISF</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3806,19 +3806,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di componenti elettronici spaziali radiation-hard su tecnologia 7nm, un settore altamente specializzato che richiede capacità di R&amp;D avanzate nel campo aerospaziale e microelettronica, del tutto fuori dalla portata di una PMI del Cilento o della Campania in generale. Le risorse necessarie (laboratori, know-how certificato per componenti spaziali, partnership con agenzie come ESA) rendono questo bando accessibile solo a grandi player industriali o centri di ricerca dedicati.</t>
+          <t>Il bando ISF (Internal Security Fund) sulla tratta di esseri umani è destinato principalmente a enti pubblici, forze dell'ordine, ONG e organismi specializzati nel contrasto alla criminalità organizzata, non a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti soggettivi né le competenze istituzionali richieste per partecipare a questo tipo di finanziamento europeo in materia di sicurezza interna.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Microelectronic – Front-End Module (FEM)</t>
+          <t>Organised crime and drug trafficking</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-OCDT</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ISF</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3853,39 +3853,39 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su moduli a radiofrequenza per microelettronica (Front-End Module) richiede capacità di R&amp;D avanzata, infrastrutture di prototipazione e competenze di ingegneria elettronica difficilmente presenti in una PMI del Cilento, territorio a vocazione agroalimentare e turistica. I requisiti tecnici e la struttura consorziale tipica di Horizon lo rendono accessibile solo a imprese high-tech o spin-off universitari specializzati nel settore dei semiconduttori.</t>
+          <t>Il bando ISF (Internal Security Fund) sulla criminalità organizzata e traffico di droga è destinato tipicamente a forze dell'ordine, autorità pubbliche e organismi istituzionali, non a PMI private. Una piccola impresa del Cilento non ha accesso diretto né profilo adeguato per candidarsi a finanziamenti di sicurezza interna UE di questa natura.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Trafficking in human beings</t>
+          <t>Framework Partnership Agreements for operating grants to support non-profit organisations</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-THB</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-FPA</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>UE - ISF</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3905,34 +3905,34 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sulla tratta di esseri umani è destinato principalmente a forze dell'ordine, enti pubblici e ONG specializzate, non a PMI commerciali del Cilento o della Campania. Non finanzia attività produttive, innovazione o sviluppo aziendale, rendendo di fatto inaccessibile il bando per una piccola o media impresa.</t>
+          <t>Il bando LIFE 2027 eroga operating grants tramite Framework Partnership Agreements esclusivamente a organizzazioni non profit operanti nel settore ambientale e climatico a livello europeo: le PMI, in quanto soggetti for-profit, sono strutturalmente escluse dalla partecipazione diretta. Una PMI del Cilento potrebbe al massimo partecipare indirettamente come fornitore di servizi a un'organizzazione beneficiaria, ma senza accesso diretto ai fondi.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Organised crime and drug trafficking</t>
+          <t>MSCA Postdoctoral Fellowships 2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-OCDT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-PF-01-01</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>UE - ISF</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3947,39 +3947,39 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sulla criminalità organizzata e il traffico di droga è destinato principalmente a forze dell'ordine, autorità pubbliche e grandi organizzazioni specializzate nel settore della sicurezza interna, non a PMI. Una piccola impresa del Cilento non dispone dei requisiti soggettivi né delle competenze operative richieste per accedere a questo tipo di finanziamento europeo.</t>
+          <t>Le MSCA Postdoctoral Fellowships sono destinate a ricercatori individuali post-dottorato e richiedono come host institution strutture con capacità di supervisione accademica, il che rende il bando strutturalmente inadatto per una PMI del Cilento priva di un dipartimento R&amp;D strutturato. L'unica finestra di accesso sarebbe ospitare un ricercatore come ente secondario, scenario complesso e raro per realtà di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Framework Partnership Agreements for operating grants to support non-profit organisations</t>
+          <t>ERA Fellowships</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-FPA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-05-WIDENING-01</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3994,24 +3994,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è riservato esclusivamente a organizzazioni non profit tramite accordi quadro di partenariato per sovvenzioni operative: una PMI con scopo di lucro è strutturalmente esclusa dalla partecipazione diretta. Non sono previste spese finanziabili né settori di intervento applicabili a imprese private del Cilento o della Campania.</t>
+          <t>Le ERA Fellowships finanziano mobilità e formazione di ricercatori nell'ambito del programma Horizon Europe, rivolte principalmente a università, enti di ricerca e grandi organizzazioni con strutture R&amp;D dedicate. Una PMI del Cilento difficilmente possiede i requisiti istituzionali e la capacità amministrativa per candidarsi autonomamente, potendo al massimo partecipare come partner secondario in un consorzio guidato da un ente di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>MSCA Postdoctoral Fellowships 2026</t>
+          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-PF-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2026-02-DISEASE-12</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4041,24 +4041,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Le MSCA Postdoctoral Fellowships sono destinate a ricercatori individuali post-dottorato e richiedono come organismo ospitante strutture con capacità di supervisione accademica avanzata, rendendole di fatto inaccessibili alla quasi totalità delle PMI campane e del Cilento senza un partner universitario consolidato. Una PMI potrebbe teoricamente partecipare come ente ospitante nel settore privato, ma i requisiti burocratici, la competitività internazionale e l'assenza di finanziamento diretto all'impresa rendono questa opportunità concretamente non perseguibile senza un ecosistema di ricerca strutturato.</t>
+          <t>Il bando ERDERA riguarda la ricerca sulle malattie rare nell'ambito del programma Horizon Europa e richiede capacità di ricerca biomedica avanzata, consorzi internazionali e competenze specialistiche difficilmente disponibili in una PMI del Cilento. Non finanzia attività produttive o commerciali tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ERA Fellowships</t>
+          <t>Earlier and more precise palliative care</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-05-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-04</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4088,19 +4088,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Le ERA Fellowships finanziano mobilità e ricerca di singoli ricercatori in istituzioni accademiche o di ricerca, non PMI: una piccola impresa del Cilento non può candidarsi direttamente e difficilmente rientra tra i soggetti ospitanti eleggibili. Il bando è strutturato per enti di ricerca, rendendo l'accesso concreto per una PMI estremamente limitato salvo partenariati con università.</t>
+          <t>Il bando Horizon Europe sulle cure palliative precoci è destinato a consorzi di ricerca accademica e grandi organizzazioni sanitarie europee, richiedendo competenze scientifiche specializzate e capacità di gestione di progetti multinazionali difficilmente compatibili con una PMI del Cilento. Non finanzia attività produttive o commerciali tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
+          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2026-02-DISEASE-12</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-01</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4135,19 +4135,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Il bando ERDERA riguarda la ricerca sulle malattie rare nell'ambito di Horizon Europe e richiede competenze scientifiche altamente specializzate, consorzi internazionali e strutture di ricerca avanzate, caratteristiche difficilmente riscontrabili in una PMI del Cilento. Una piccola impresa campana non ha i requisiti tecnici né la capacità progettuale per partecipare competitivamente a una European Partnership di questo livello.</t>
+          <t>Il bando Horizon richiede competenze altamente specializzate in modellazione biomedica computazionale e ricerca oncologica, con consorzî internazionali e capacità di R&amp;S avanzata difficilmente accessibili a una PMI del Cilento. Non è previsto un supporto diretto a imprese di piccola dimensione senza un solido track record nella ricerca sul cancro o nelle tecnologie di digital twin in ambito medico.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Earlier and more precise palliative care</t>
+          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-05</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU sulle cure palliative precoci è orientato a consorzi di ricerca accademica e ospedali di grandi dimensioni, richiedendo competenze cliniche specialistiche e capacità di gestione di progetti di ricerca transnazionale che esulano dal profilo tipico di una PMI campana, soprattutto nel Cilento. Non sono previste spese finanziabili rilevanti per attività produttive o di servizio locale.</t>
+          <t>Il bando Horizon è focalizzato sulla salute mentale dei giovani sopravvissuti al cancro tramite una piattaforma digitale europea, richiedendo competenze specialistiche in oncologia, psicologia e ricerca clinica che esulano dall'attività tipica di una PMI campana. I progetti Horizon richiedono inoltre consorzi internazionali strutturati e capacità di rendicontazione scientifica difficilmente accessibili per una piccola impresa del Cilento.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
+          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-03</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4229,19 +4229,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su modelli digitali gemelli virtuali umani per la ricerca oncologica richiede capacità di ricerca avanzata, partnership con enti accademici e infrastrutture scientifiche difficilmente disponibili per una PMI del Cilento. L'accesso è praticamente riservato a grandi consorzi di ricerca biomedica o università, rendendo la partecipazione diretta di una piccola impresa campana quasi impossibile senza un ruolo marginale come partner tecnologico specializzato.</t>
+          <t>Il bando finanzia trial clinici pragmatici sull'immunoterapia oncologica nell'ambito di Horizon Europe, richiedendo competenze altamente specializzate in ricerca clinica e oncologia che esulano completamente dal profilo tipico di una PMI campana, specialmente nel Cilento. L'accesso è di fatto riservato a grandi consorzi con centri ospedalieri universitari e strutture di ricerca avanzata.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
+          <t>Microbiome for early cancer prediction before the onset of disease</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-02</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4276,19 +4276,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la salute mentale dei giovani sopravvissuti al cancro tramite una piattaforma digitale europea, richiedendo competenze cliniche, di ricerca oncologica e capacità di partecipare a consorzi europei complessi. Una PMI del Cilento difficilmente possiede i requisiti tecnico-scientifici e la struttura organizzativa necessari per partecipare competitivamente a questo tipo di progetto di ricerca sanitaria su scala europea.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata sul microbioma per la predizione precoce dei tumori, con requisiti progettuali e consortili di alto livello difficilmente accessibili per una PMI del Cilento senza un solido track record in R&amp;S biomedica. Una piccola impresa campana potrebbe partecipare solo come partner junior in un consorzio europeo guidato da istituti di ricerca o grandi player del settore health-tech.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
+          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-06</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia sperimentazioni cliniche pragmatiche su immunoterapie oncologiche, richiedendo competenze altamente specializzate in ambito medico-scientifico e strutture di ricerca clinica che esulano completamente dalla capacità operativa di una PMI campana, specialmente nel Cilento. Si tratta di un'opportunità destinata a grandi centri ospedalieri universitari o consorzi di ricerca biomedica, non a piccole e medie imprese del territorio.</t>
+          <t>Il bando è focalizzato sulla ricerca oncologica in collaborazione con l'Ucraina e richiede capacità istituzionali di alto livello tipiche di università, ospedali e centri di ricerca, rendendo di fatto inaccessibile la partecipazione a una PMI del Cilento o di qualsiasi altra area periferica. Non sono previste attività finanziabili rilevanti per imprese di piccola dimensione operanti in settori produttivi locali.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Microbiome for early cancer prediction before the onset of disease</t>
+          <t>Improve the Quality of Life of older cancer patients</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-07</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4370,19 +4370,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede consorzi internazionali con forte componente di ricerca scientifica avanzata (microbioma e oncologia predittiva), rendendo l'accesso estremamente complesso per una PMI del Cilento priva di strutture R&amp;S dedicate o partnership con università/centri di ricerca. Unica finestra realistica è il ruolo di partner industriale in un consorzio già formato, ma richiede competenze molto specializzate in biotecnologie o diagnostica medica.</t>
+          <t>Il bando Horizon EU sulla qualità della vita dei pazienti oncologici anziani è destinato a consorzi di ricerca europei e istituzioni scientifiche, non a PMI generiche del Cilento; richiederebbe competenze cliniche/sanitarie specialistiche e la capacità di gestire progetti internazionali complessi con budget multimilionari, barriere di fatto insormontabili per una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
+          <t>Approaches and tools for security in software and hardware development and assessment</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-01</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4417,19 +4417,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Il bando è focalizzato sulla ricerca oncologica in contesto internazionale con e per l'Ucraina, richiedendo competenze scientifiche altamente specializzate e strutture di ricerca avanzate che esulano dal profilo tipico di una PMI campana, specialmente nel Cilento. Non sono previste attività finanziabili compatibili con imprese di piccola dimensione operanti in settori tradizionali o locali.</t>
+          <t>Il bando Horizon EU sulla sicurezza in software e hardware richiede capacità di ricerca avanzata, consorzio internazionale e competenze tecniche specializzate difficilmente disponibili in una PMI del Cilento. Le risorse necessarie per partecipare (co-finanziamento, personale R&amp;D, gestione progettuale europea) rendono questo bando inaccessibile senza partnership con grandi enti di ricerca o università.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Improve the Quality of Life of older cancer patients</t>
+          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-03</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4464,19 +4464,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi internazionali di ricerca con forte componente accademica e clinica specializzata in oncologia geriatrica, struttura progettuale complessa e capacità amministrative avanzate difficilmente compatibili con una PMI campana di piccole-medie dimensioni. Una PMI del Cilento potrebbe partecipare solo in ruolo marginale all'interno di un consorzio già formato, ma senza una rete di partner scientifici consolidata le chances di accesso sono estremamente ridotte.</t>
+          <t>Il bando Horizon focalizzato su schemi crittografici avanzati e implementazioni ad alta velocità richiede competenze altamente specializzate in ricerca e sviluppo crittografico, strutture di ricerca certificate e capacità di partecipazione a consorzi europei complessi, requisiti difficilmente soddisfatti da una PMI del Cilento operante in settori tradizionali. Solo PMI con un profilo tech avanzato e già inserite in reti di ricerca europee potrebbero candidarsi come partner tecnologici.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Approaches and tools for security in software and hardware development and assessment</t>
+          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-02</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4516,14 +4516,14 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla sicurezza in ambito software e hardware richiede capacità di ricerca avanzata, consorzi internazionali e competenze tecniche specialistiche difficilmente disponibili in una PMI del Cilento. L'elevata complessità progettuale e la concorrenza con grandi centri di ricerca europei rendono questo bando di fatto inaccessibile senza una partnership strutturata con università o grandi imprese tech.</t>
+          <t>Il bando Horizon focalizzato sulla sicurezza e robustezza dei modelli AI richiede capacità di ricerca avanzata, consorzi internazionali e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. I costi di partecipazione, la complessità progettuale e la necessità di partner europei lo rendono poco accessibile senza una struttura dedicata alla ricerca e sviluppo.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
+          <t>R&amp;I in Support of the Clean Industrial Deal: Clean Technologies for Climate Action</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-02</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4563,14 +4563,14 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca avanzata in crittografia ad alte prestazioni, un settore altamente specializzato che richiede competenze tecniche di livello accademico/industriale avanzato e strutture di R&amp;D difficilmente presenti in una PMI del Cilento. L'accesso è praticamente limitato a grandi aziende tech o consorzi con università, rendendo questo bando non realistico per una piccola impresa campana.</t>
+          <t>Il bando Horizon Europe richiede progetti di ricerca e innovazione ad alta intensità tecnologica con budget elevati e partnership internazionali, strutturalmente pensati per grandi consorzi tra università, centri di ricerca e industrie. Una PMI del Cilento difficilmente possiede le capacità progettuali, la massa critica tecnologica e le reti europee necessarie per candidarsi autonomamente o come partner capofila.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
+          <t>R&amp;I in Support of the Clean Industrial Deal: Decarbonisation of energy intensive industries (IA) (Processes4Planet and Clean Steel partnerships)</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-01</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4610,14 +4610,14 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU sulla sicurezza e robustezza dei modelli AI richiede capacità di ricerca avanzata, consorzi internazionali e competenze tecniche altamente specializzate, barriere difficilmente superabili per una PMI del Cilento senza un solido track record in R&amp;D sull'intelligenza artificiale. L'accesso è realistico solo se la PMI partecipa come partner in un consorzio guidato da università o grandi player tech, con un ruolo marginale e risorse dedicate alla gestione progettuale europea.</t>
+          <t>Il bando finanzia progetti di ricerca e innovazione su larga scala per la decarbonizzazione di industrie energivore come acciaio e chimica, nell'ambito di partnership europee (Processes4Planet e Clean Steel) che richiedono consorzi internazionali e investimenti ingenti, risultando di fatto inaccessibile per una PMI del Cilento che non opera in settori industriali pesanti. Le soglie di progetto, la complessità consortile e la specificità settoriale escludono praticamente qualsiasi piccola o media impresa del territorio campano.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>R&amp;I in Support of the Clean Industrial Deal: Clean Technologies for Climate Action</t>
+          <t>Validating policies and business models for affordable and sustainable housing (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-04</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4657,14 +4657,14 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE su clean technologies richiede capacità di ricerca e sviluppo avanzate, partnership internazionali e budget progettuali elevati, strutturalmente incompatibili con le dimensioni e le risorse tipiche di una PMI del Cilento. L'accesso è realisticamente riservato a grandi consorzi con centri di ricerca o multinazionali, rendendo la partecipazione diretta di una piccola impresa campana molto difficile senza un ruolo marginale in un consorzio già strutturato.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali con forte componente di ricerca applicata sull'edilizia sostenibile e accessibile, struttura progettuale complessa difficilmente gestibile da una PMI di piccola dimensione senza un partner capofila accademico o industriale. Una PMI edile o di costruzioni del Cilento potrebbe partecipare solo come partner junior in un consorzio già formato, con ruolo marginale e oneri amministrativi elevati.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>R&amp;I in Support of the Clean Industrial Deal: Decarbonisation of energy intensive industries (IA) (Processes4Planet and Clean Steel partnerships)</t>
+          <t>Coordinated topic with India on recycling of EV batteries</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-04</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4704,14 +4704,14 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti di ricerca e innovazione industriale per la decarbonizzazione di settori ad alta intensità energetica (siderurgia, chimica, cemento) nell'ambito di grandi partnership europee come Processes4Planet e Clean Steel, con requisiti tecnici, consorziali e finanziari difficilmente compatibili con una PMI campana di piccole dimensioni, specialmente nel contesto del Cilento, privo di industrie energivore di rilievo. Una PMI potrebbe partecipare solo come partner di un consorzio internazionale guidato da grandi imprese o centri di ricerca, scenario molto improbabile senza relazioni consolidate in tali network.</t>
+          <t>Il bando Horizon richiede partnership internazionali con India, capacità di ricerca avanzata e budget di progetto elevati, strutture tipicamente fuori dalla portata di una PMI del Cilento senza un solido consorzio con università o grandi imprese. Il focus specifico sul riciclo di batterie EV presuppone competenze tecnologiche di nicchia difficilmente presenti nel tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Validating policies and business models for affordable and sustainable housing (Built4People Partnership)</t>
+          <t>Innovative technologies and solutions to improve wind energy systems supporting the Strategic Energy Technology (SET) Plan on wind</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D3-03</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi europei con forte componente di ricerca e sviluppo su modelli abitativi sostenibili, con oneri amministrativi e capacità progettuali difficilmente sostenibili per una PMI campana di piccole dimensioni. Per una realtà del Cilento, lontana dai principali hub di ricerca e senza esperienza pregressa in progetti europei strutturati, le barriere di accesso (co-finanziamento, partnership internazionali, rendicontazione Horizon) rendono la partecipazione diretta poco praticabile.</t>
+          <t>Il bando Horizon Europe richiede consorzi internazionali con forte componente di ricerca avanzata nel settore eolico, con budget e competenze tecniche difficilmente accessibili per una PMI campana di piccola dimensione. Il Cilento, pur avendo potenziale eolico, non dispone di un tessuto industriale specializzato in tecnologie per l'energia eolica che possa competere a livello europeo in questo tipo di bando.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Coordinated topic with India on recycling of EV batteries</t>
+          <t>Low disturbance prefabrication approaches for deep renovation of multi-storey buildings (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-02</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4798,14 +4798,14 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede partnership internazionali con India, capacità di ricerca avanzata e consorzio europeo strutturato per il riciclo di batterie per veicoli elettrici: requisiti difficilmente accessibili per una PMI del Cilento senza una solida componente R&amp;D e reti internazionali consolidate. Il settore specifico (batterie EV) è inoltre lontano dal tessuto produttivo locale, prevalentemente orientato a turismo, agricoltura e artigianato.</t>
+          <t>Il bando Horizon Europe richiede consorzi internazionali con forte componente di ricerca applicata sulla prefabbricazione a bassa invasività per la ristrutturazione profonda di edifici multipiano: una PMI campana del Cilento difficilmente dispone delle competenze tecnologiche certificate e dei partner europei necessari per candidarsi autonomamente. Potrebbe partecipare solo come soggetto associato in un consorzio già strutturato, con un ruolo marginale e costi di accesso elevati.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Innovative technologies and solutions to improve wind energy systems supporting the Strategic Energy Technology (SET) Plan on wind</t>
+          <t>Producing battery-grade materials for electrodes through sustainable processing and refining of raw materials or developing bio-based materials (BATT4EU Partnership)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D3-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-01</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di R&amp;S avanzata nel settore eolico e la partecipazione a consorzi internazionali, requisiti difficilmente sostenibili da una PMI campana di piccole dimensioni; il Cilento inoltre non presenta infrastrutture o filiere industriali legate all'energia eolica tali da giustificare un coinvolgimento diretto. Solo PMI con competenze tecnologiche specializzate e già inserite in reti europee potrebbero candidarsi come partner di progetto.</t>
+          <t>Il bando BATT4EU richiede capacità di ricerca avanzata nella produzione di materiali per batterie (elettrodi, materiali bio-based) tipicamente accessibili a grandi consorzi industriali o centri di ricerca specializzati, rendendo la partecipazione di una PMI del Cilento estremamente difficile senza partnership consolidate. Il settore manifatturiero avanzato richiesto è pressoché assente nel tessuto produttivo locale, che è orientato prevalentemente ad agricoltura, turismo e piccolo artigianato.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Low disturbance prefabrication approaches for deep renovation of multi-storey buildings (Built4People Partnership)</t>
+          <t>Researching the technical, social &amp; economic factors impacting the energy performance of Smart Buildings (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-01</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4892,14 +4892,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali con capacità di R&amp;S avanzata e cofinanziamento significativo, struttura difficilmente accessibile per una PMI campana di piccole dimensioni. Una PMI edile del Cilento potrebbe partecipare solo come partner secondario in un consorzio già formato, con ruolo marginale nella prefabbricazione a basso impatto per ristrutturazioni profonde di edifici multipiano.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali di ricerca con capacità progettuali elevate, budget significativi e competenze in ricerca applicata sull'efficienza energetica degli edifici intelligenti: requisiti difficilmente soddisfabili da una PMI del Cilento senza un solido network europeo preesistente. Una piccola impresa edile o impiantistica locale potrebbe partecipare solo come partner junior in un consorzio già formato, ruolo che richiede comunque risorse amministrative e tecniche dedicate non sempre disponibili.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Producing battery-grade materials for electrodes through sustainable processing and refining of raw materials or developing bio-based materials (BATT4EU Partnership)</t>
+          <t>Advanced data platforms to integrate whole life carbon in building information tools, assessments, and certification (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-03</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Il bando BATT4EU richiede capacità di ricerca avanzata nella chimica dei materiali per batterie (elettrodi, raffinazione di materie prime critiche, bio-materiali), con consorzio internazionale e budget tipicamente superiori ai 5-10M€: barriere progettuali e tecnologiche molto elevate per una PMI del Cilento, che difficilmente dispone di laboratori R&amp;D specializzati in questo settore. L'unica via di accesso realistico sarebbe come partner secondario di un consorzio guidato da un grande ente di ricerca, ma il territorio non presenta filiere industriali legate alla mobilità elettrica o alla metallurgia delle batterie.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali di ricerca con elevata capacità tecnico-scientifica e amministrativa, rendendo l'accesso estremamente complesso per una PMI del Cilento senza esperienza pregressa in progetti europei. Il focus su piattaforme dati avanzate per il carbonio nell'edilizia (BIM, certificazioni whole life carbon) è lontano dal tessuto produttivo locale, prevalentemente orientato a turismo, agricoltura e artigianato.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Researching the technical, social &amp; economic factors impacting the energy performance of Smart Buildings (Built4People Partnership)</t>
+          <t>Full-scale demonstration of heat upgrade solutions in industrial processes</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-08</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4986,14 +4986,14 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi di ricerca europei con elevate competenze tecniche in efficienza energetica e smart buildings, strutture difficilmente accessibili per una PMI del Cilento senza un partner universitario o centro di ricerca già consolidato. I costi di gestione del progetto, la complessità burocratica e la necessità di cofinanziamento rendono questo strumento poco praticabile per realtà di piccola dimensione senza esperienza pregressa in progetti UE.</t>
+          <t>Il bando Horizon richiede la dimostrazione su scala reale di soluzioni avanzate di upgrading termico in processi industriali, con complessità tecnica, consorzio internazionale e capacità di R&amp;D difficilmente compatibili con una PMI di piccole dimensioni del Cilento, territorio a vocazione prevalentemente agricola e turistica, privo di grandi insediamenti industriali ad alta intensità energetica.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Advanced data platforms to integrate whole life carbon in building information tools, assessments, and certification (Built4People Partnership)</t>
+          <t>European Nuclear Skills Initiative – towards European Nuclear Skills Academy</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-NRT-01-01</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - EURATOM2027</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5028,19 +5028,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali di ricerca con elevate competenze tecniche in modellazione BIM e calcolo del carbonio sull'intero ciclo di vita degli edifici, barriere difficilmente superabili per una PMI del Cilento priva di un profilo R&amp;D strutturato. I requisiti amministrativi, la competizione europea e la necessità di partner accademici rendono questo strumento di fatto inaccessibile senza un ruolo subordinato in un consorzio già formato.</t>
+          <t>Il bando è focalizzato sullo sviluppo di competenze nel settore nucleare a livello europeo, un ambito altamente specializzato e del tutto estraneo al tessuto produttivo del Cilento e della Campania, dove non esistono impianti né filiere nucleari. Una PMI locale non possiede i requisiti tecnici né il profilo settoriale per partecipare a questa iniziativa EURATOM.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Full-scale demonstration of heat upgrade solutions in industrial processes</t>
+          <t>Protection of the euro against counterfeiting</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PERI-2026-ANTI-COUNTERFEIT</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - PERI</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5075,19 +5075,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede dimostrazioni su scala reale di tecnologie avanzate per l'aggiornamento termico nei processi industriali, con consorzio internazionale e capacità di ricerca elevata, requisiti difficilmente soddisfacibili da una PMI del Cilento priva di infrastrutture industriali e partner R&amp;D consolidati. Una piccola impresa campana potrebbe partecipare solo come partner secondario all'interno di un consorzio europeo già strutturato, ruolo che richiede competenze tecniche specializzate nel settore energetico-industriale.</t>
+          <t>Il bando riguarda la protezione dell'euro dalla contraffazione ed è rivolto principalmente a forze dell'ordine, istituti di credito e autorità nazionali competenti, non a PMI commerciali o produttive. Una piccola impresa del Cilento non ha titolo né struttura per partecipare a programmi di contrasto alla contraffazione monetaria a livello europeo.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>European Nuclear Skills Initiative – towards European Nuclear Skills Academy</t>
+          <t>Strengthening a European user facility for nuclear research</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-NRT-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-04</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5122,19 +5122,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Il bando è focalizzato sullo sviluppo di competenze nel settore nucleare a livello europeo, un ambito altamente specializzato e distante dal tessuto produttivo del Cilento e della Campania, dove non esistono infrastrutture o filiere nucleari. Una PMI locale difficilmente possiede i requisiti tecnici e istituzionali richiesti da un'iniziativa EURATOM di questa portata.</t>
+          <t>Il bando EURATOM riguarda il potenziamento di infrastrutture di ricerca nucleare a livello europeo, un settore altamente specializzato che richiede competenze scientifiche avanzate e strutture di ricerca istituzionali, rendendo di fatto inaccessibile la partecipazione a una PMI del Cilento o della Campania priva di tali requisiti tecnici e infrastrutturali.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Protection of the euro against counterfeiting</t>
+          <t>Co-funded European partnership for research in nuclear materials</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PERI-2026-ANTI-COUNTERFEIT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-08</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>UE - PERI</t>
+          <t>UE - EURATOM2027</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5174,14 +5174,14 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la protezione dell'euro dalla contraffazione ed è destinato principalmente a forze dell'ordine, istituti finanziari e autorità pubbliche competenti in materia valutaria, non a PMI del Cilento o della Campania. Non sono previste spese o attività finanziabili rilevanti per una piccola o media impresa operante in settori produttivi o commerciali tipici del territorio.</t>
+          <t>Il bando riguarda la ricerca sui materiali nucleari nell'ambito del programma EURATOM, un settore altamente specializzato che richiede infrastrutture di ricerca avanzate e competenze scientifiche di livello europeo, del tutto estranee al tessuto produttivo tipico del Cilento e delle PMI campane. Non esistono filiere nucleari o centri di ricerca nucleare nel territorio di riferimento che possano candidarsi con reali prospettive di successo.</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Strengthening a European user facility for nuclear research</t>
+          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-06</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda il potenziamento di infrastrutture di ricerca nucleare a livello europeo, un ambito altamente specializzato riservato a grandi enti di ricerca, università e laboratori nazionali. Una PMI del Cilento o della Campania non dispone delle competenze nucleari, delle certificazioni e della struttura organizzativa richieste per partecipare competitivamente a questo tipo di finanziamento.</t>
+          <t>Il bando EURATOM riguarda tecnologie nucleari avanzate e applicazioni delle radiazioni ionizzanti, ambiti altamente specializzati che richiedono competenze scientifiche e infrastrutture di ricerca difficilmente disponibili in una PMI del Cilento o della Campania in generale. Le risorse sono destinate prevalentemente a grandi enti di ricerca, università e operatori del settore nucleare, escludendo di fatto le piccole e medie imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Co-funded European partnership for research in nuclear materials</t>
+          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-05</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5268,14 +5268,14 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda ricerca in materiali nucleari nell'ambito del programma EURATOM, un settore altamente specializzato che richiede infrastrutture di ricerca avanzate e competenze tecnico-scientifiche difficilmente presenti in una PMI del Cilento o della Campania in generale. Le partnership co-finanziate europee di questo tipo sono strutturalmente orientate a grandi enti di ricerca, università e laboratori nazionali, escludendo di fatto le piccole e medie imprese senza un profilo R&amp;D nucleare consolidato.</t>
+          <t>Il bando EURATOM riguarda la produzione di isotopi stabili per terapie di medicina nucleare avanzata, un settore altamente specializzato che richiede infrastrutture di ricerca nucleare e competenze scientifiche difficilmente disponibili in una PMI del Cilento o della Campania in generale. Le risorse finanziabili riguardano R&amp;S in ambito nucleare-medico, accessibili quasi esclusivamente a grandi centri di ricerca o consorzi universitari con laboratori certificati.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
+          <t>Enhancing the European nuclear competence  area</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-03</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5310,19 +5310,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la ricerca sull'energia nucleare e le applicazioni delle radiazioni ionizzanti, settori altamente specializzati che richiedono infrastrutture scientifiche e competenze tecnico-nucleari del tutto estranee al tessuto produttivo delle PMI campane, incluso il Cilento. Non esistono filiere locali attinenti e i requisiti di partecipazione sono orientati a grandi enti di ricerca e organizzazioni scientifiche internazionali.</t>
+          <t>Il bando EURATOM è focalizzato sul settore nucleare europeo, un comparto altamente specializzato e regolamentato che non ha applicabilità concreta per le PMI del Cilento o della Campania in generale, prive di infrastrutture o competenze in ambito nucleare. Le risorse finanziabili riguardano ricerca, formazione e sviluppo di competenze nucleari, settori strutturalmente assenti nel tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
+          <t>Safety of operating nuclear power plants and research reactors</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-01</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5357,19 +5357,19 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la produzione industriale di isotopi stabili per terapie nucleari avanzate, un settore altamente specializzato che richiede infrastrutture radiologiche, competenze nucleari e capacità di ricerca difficilmente presenti in una PMI del Cilento o della Campania in generale. Le risorse finanziabili (R&amp;S, impianti di produzione isotopica, validazione clinica) sono accessibili quasi esclusivamente a grandi enti di ricerca, ospedali universitari o imprese del settore farmaceutico-nucleare.</t>
+          <t>Il bando EURATOM riguarda esclusivamente la sicurezza di impianti nucleari e reattori di ricerca, settore altamente specializzato che non ha applicabilità per le PMI del Cilento o della Campania, territorio privo di infrastrutture nucleari e con economia basata su turismo, agricoltura e agroalimentare. Partecipare richiederebbe competenze nucleari certificate e partnership con enti di ricerca specializzati del tutto estranei al tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the European nuclear competence  area</t>
+          <t>European Partnership for research in radiation protection and detection of ionising radiation</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-09</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5404,19 +5404,19 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM è focalizzato sul settore nucleare europeo, un ambito altamente specializzato e regolamentato che non ha applicabilità concreta per le PMI del Cilento o della Campania in generale, dove non esistono infrastrutture o filiere produttive legate all'energia nucleare. Le risorse finanziate riguardano ricerca, formazione e competenze nucleari, settori inaccessibili per PMI generaliste del territorio.</t>
+          <t>Il bando EURATOM riguarda la ricerca sulla protezione dalle radiazioni ionizzanti e richiede competenze scientifiche altamente specializzate e strutture di ricerca avanzate, tipiche di enti pubblici o grandi laboratori nucleari. Una PMI del Cilento o della Campania difficilmente possiede i requisiti tecnici e il profilo istituzionale necessari per partecipare a partenariati europei di questo livello.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Safety of operating nuclear power plants and research reactors</t>
+          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-02</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5456,14 +5456,14 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda esclusivamente la sicurezza di reattori nucleari e reattori di ricerca, un settore altamente specializzato privo di qualsiasi rilevanza per le PMI del Cilento o della Campania, dove non esistono impianti nucleari né filiere industriali connesse. Le risorse richieste (competenze nucleari certificate, infrastrutture di ricerca dedicate) sono strutturalmente incompatibili con una piccola o media impresa del territorio.</t>
+          <t>Il bando EURATOM riguarda la sicurezza dei reattori nucleari avanzati e dei combustibili innovativi, un settore altamente specializzato che richiede competenze nucleari certificate e infrastrutture di ricerca non accessibili a una PMI standard del Cilento o della Campania. Non esistono aziende del territorio con profilo adeguato per partecipare in modo competitivo a questo tipo di call europea.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>European Partnership for research in radiation protection and detection of ionising radiation</t>
+          <t>Raising awareness of and building capacity for the EU Charter of Fundamental Rights</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5473,17 +5473,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-09</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CHARTER</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>UE - EURATOM2027</t>
+          <t>UE - CERV</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -5498,19 +5498,19 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM è destinato a consorzi di ricerca in ambito nucleare e radioprotazione, richiedendo competenze altamente specializzate e strutture di ricerca avanzate difficilmente compatibili con una PMI campana del Cilento. Le spese finanziabili riguardano ricerca applicata su radiazioni ionizzanti, un settore con scarsa rilevanza per il tessuto produttivo locale prevalentemente orientato a turismo, agricoltura e agroalimentare.</t>
+          <t>Il bando CERV è orientato a organizzazioni della società civile, enti pubblici e ONG impegnate nella promozione dei diritti fondamentali UE, non a PMI commerciali. Una piccola impresa del Cilento non avrebbe i requisiti tipici né le attività istituzionali richieste per accedere a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
+          <t>Promoting an enabling civic space</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5520,17 +5520,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CIVIC</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>UE - EURATOM2027</t>
+          <t>UE - CERV</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -5550,14 +5550,14 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la sicurezza dei reattori nucleari SMR e combustibili avanzati, un settore altamente specializzato che richiede competenze nucleari certificate e infrastrutture di ricerca non accessibili a una PMI standard del Cilento o della Campania. Non esistono filiere produttive o di servizio nucleare nel territorio di riferimento che possano beneficiare concretamente di questo finanziamento.</t>
+          <t>Il programma CERV (Citizens, Equality, Rights and Values) finanzia principalmente organizzazioni della società civile, ONG e enti pubblici per progetti legati a democrazia, diritti fondamentali e partecipazione civica, non attività imprenditoriali o produttive. Una PMI del Cilento non rientra nei beneficiari tipici e non troverebbe spese operative o investimenti aziendali finanziabili in questo bando.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Raising awareness of and building capacity for the EU Charter of Fundamental Rights</t>
+          <t>Safety of operating nuclear power plants and research reactors</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5567,17 +5567,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CHARTER</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-01</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>UE - CERV</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5592,19 +5592,19 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Il bando CERV è orientato a organizzazioni della società civile, enti pubblici e ONG impegnate nella promozione dei diritti fondamentali UE, non a PMI commerciali del Cilento o della Campania. Una piccola impresa manifatturiera o di servizi non rientra tra i beneficiari tipici e difficilmente può strutturare un progetto coerente con le finalità di sensibilizzazione alla Carta dei Diritti Fondamentali richieste dal programma.</t>
+          <t>Il bando riguarda la sicurezza di reattori nucleari e reattori di ricerca, un settore altamente specializzato che non ha alcuna applicazione concreta per una PMI del Cilento o della Campania, regione priva di impianti nucleari. Le competenze tecniche richieste e la natura del programma Horizon escludono di fatto le piccole e medie imprese non operanti nel settore nucleare.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Promoting an enabling civic space</t>
+          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5614,17 +5614,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CIVIC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-06</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>UE - CERV</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5639,19 +5639,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Il bando CERV 'Promoting an enabling civic space' è destinato principalmente a organizzazioni della società civile, ONG e soggetti no-profit impegnati nella promozione della democrazia e dei diritti fondamentali, contesti in cui una PMI commerciale del Cilento difficilmente rientra come beneficiario eleggibile. Le attività finanziabili riguardano advocacy, partecipazione civica e capacity building di organizzazioni non lucrative, ambiti estranei alla normale operatività aziendale di una piccola o media impresa.</t>
+          <t>Il bando riguarda la piattaforma tecnologica per l'energia nucleare sostenibile e le applicazioni non energetiche delle radiazioni ionizzanti, settori altamente specializzati che richiedono competenze scientifiche avanzate e infrastrutture di ricerca difficilmente compatibili con una PMI del Cilento. L'accesso è di fatto riservato a grandi enti di ricerca, università o industrie nucleari strutturate, rendendo la partecipazione di una piccola impresa campana estremamente improbabile.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Safety of operating nuclear power plants and research reactors</t>
+          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-05</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5686,19 +5686,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la sicurezza di reattori nucleari e impianti di ricerca, un settore altamente specializzato che non ha applicabilità concreta per le PMI campane, tantomeno per quelle del Cilento, territorio privo di infrastrutture nucleari e vocato principalmente ad agricoltura, turismo e pesca. Le competenze tecniche e i requisiti richiesti sono incompatibili con la struttura tipica di una piccola o media impresa locale.</t>
+          <t>Il bando riguarda la produzione europea di isotopi stabili per terapie di medicina nucleare avanzata, un settore altamente specializzato che richiede infrastrutture di ricerca nucleare e competenze scientifiche di alto livello difficilmente disponibili in una PMI del Cilento. L'ambito applicativo è limitato a laboratori, centri di ricerca nucleare e grandi player farmaceutici, escludendo di fatto le piccole imprese del territorio campano.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
+          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-02</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5733,34 +5733,34 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la piattaforma tecnologica per l'energia nucleare sostenibile e applicazioni delle radiazioni ionizzanti, settori altamente specializzati che richiedono competenze scientifiche avanzate e infrastrutture di ricerca fuori dalla portata di una PMI del Cilento. Non esistono attività finanziabili rilevanti per le tipologie produttive prevalenti nell'area (turismo, agricoltura, agroalimentare).</t>
+          <t>Il bando riguarda la sicurezza dei reattori nucleari avanzati e dei combustibili innovativi, un settore altamente specializzato che richiede competenze scientifiche e infrastrutture di ricerca difficilmente compatibili con le dimensioni e il profilo produttivo tipico di una PMI campana, specialmente nel Cilento dove il tessuto economico è orientato ad agricoltura, turismo e piccolo commercio. L'accesso richiede inoltre partnership con centri di ricerca nucleare certificati e capacità progettuali europee di alto livello.</t>
         </is>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
+          <t>EIC Transition Open</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-TRANSITIONOPEN</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5785,34 +5785,34 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon SAMIRA/ERVI riguarda la produzione europea di isotopi stabili per terapie nucleari avanzate, un settore altamente specializzato che richiede infrastrutture di ricerca nucleare, know-how scientifico di frontiera e partnership con grandi enti di ricerca: barriere praticamente insuperabili per una PMI del Cilento o della Campania non già inserita in reti di ricerca nucleare o farmaceutica avanzata. Non vi è un aggancio concreto con i settori produttivi tipici del territorio.</t>
+          <t>EIC Transition finanzia progetti di ricerca e trasferimento tecnologico derivanti da risultati ERC o FET/EIC Pathfinder, richiedendo competenze scientifiche avanzate e strutture di ricerca che raramente una PMI del Cilento possiede autonomamente. La complessità burocratica e i requisiti tecnici elevati rendono questo bando poco accessibile senza un consorzio con università o centri di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
+          <t>Supporting digitalisation of Distribution System Operators for a smart energy transition (Smart Grid Academy)</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-DIGITAL</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5827,19 +5827,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la sicurezza dei reattori nucleari di nuova generazione (SMR) e dei combustibili avanzati, un settore altamente specializzato che richiede competenze scientifiche e infrastrutture di ricerca nucleare del tutto estranee al tessuto produttivo delle PMI campane e del Cilento. Non esistono filiere locali né competenze territoriali spendibili in questo ambito.</t>
+          <t>Il bando LIFE 2027 è orientato a operatori di reti di distribuzione energetica (DSO) e grandi enti del settore energia per progetti di smart grid, non a PMI generiche del Cilento o della Campania. Le PMI potrebbero partecipare solo in qualità di partner tecnici specializzati in soluzioni digitali per reti energetiche, ruolo difficilmente accessibile per realtà di piccola dimensione senza competenze specifiche nel settore.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>EIC Transition Open</t>
+          <t>Scaling up smart and clean energy solutions for affordability in EU cities</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5849,17 +5849,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-TRANSITIONOPEN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-EMPOWER</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -5874,19 +5874,19 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>EIC Transition finanzia progetti di trasferimento tecnologico da ricerca di base a applicazioni di mercato (TRL 3-6), richiedendo tipicamente partnership con enti di ricerca e risultati da progetti ERC o FET precedenti: una PMI del Cilento difficilmente soddisfa questi prerequisiti tecnici e burocratici molto selettivi. Il bando è orientato a spin-off e deep-tech con forte componente scientifica, lontano dalle esigenze operative tipiche delle PMI locali.</t>
+          <t>Il bando LIFE è orientato a progetti su scala urbana e di sistema per soluzioni energetiche pulite e accessibili nelle città UE, con requisiti di partnership complessi e budget elevati tipicamente gestiti da enti pubblici o grandi consorzi. Una PMI del Cilento, territorio prevalentemente rurale e non urbano, difficilmente risponde ai criteri di ammissibilità come soggetto capofila, potendo al massimo partecipare come partner in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Supporting digitalisation of Distribution System Operators for a smart energy transition (Smart Grid Academy)</t>
+          <t>Supporting the delivery of actionable, integrated, and comprehensive local heating and cooling plans</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-DIGITAL</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-HEATCOOLPLAN</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5921,19 +5921,19 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 2027 è orientato a supportare i gestori delle reti di distribuzione energetica (DSO) nella digitalizzazione delle smart grid, un settore altamente specializzato che difficilmente coinvolge PMI del Cilento come beneficiari diretti. Una piccola impresa campana potrebbe partecipare solo in qualità di partner tecnologico in un consorzio europeo, scenario complesso e poco accessibile per realtà di dimensioni limitate.</t>
+          <t>Il bando LIFE 2027 è orientato a enti pubblici, autorità locali e grandi consorzi per la pianificazione strategica del riscaldamento e raffreddamento urbano, con requisiti di partenariato transnazionale e capacità progettuali complesse difficilmente gestibili da una PMI del Cilento. Una piccola impresa campana potrebbe al massimo partecipare come partner secondario in un consorzio, ma difficilmente come beneficiario principale.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Scaling up smart and clean energy solutions for affordability in EU cities</t>
+          <t>One-Stop-Shops - Integrated services for clean energy transition in private buildings</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-EMPOWER</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-OSS</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5973,14 +5973,14 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a progetti di scala urbana su energia pulita e accessibile nelle città UE, con requisiti tecnici, finanziari e di partenariato molto elevati, tipicamente accessibili a consorzi pubblico-privati o grandi enti. Una PMI del Cilento, territorio a bassa urbanizzazione, difficilmente soddisfa i criteri di scala e impatto richiesti senza essere parte di un consorzio strutturato.</t>
+          <t>Il bando LIFE finanzia progetti di sistema per la creazione di sportelli unici ('one-stop-shops') dedicati alla transizione energetica negli edifici privati, richiedendo partnership europee strutturate e capacità progettuali complesse che difficilmente una PMI campana può sostenere autonomamente. Una piccola impresa del Cilento potrebbe partecipare solo come partner di un consorzio più ampio, con ruolo marginale e oneri amministrativi elevati.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Supporting the delivery of actionable, integrated, and comprehensive local heating and cooling plans</t>
+          <t>Energy renovation solutions – Boosting building renovation through effective markets and instruments</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-HEATCOOLPLAN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BETTERRENO</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6020,14 +6020,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE richiede la redazione di piani locali integrati per il riscaldamento e il raffrescamento urbano, un'attività tipicamente destinata a enti pubblici, agenzie energetiche o consorzi istituzionali con competenze di pianificazione territoriale. Una PMI del Cilento difficilmente possiede i requisiti tecnici, la scala operativa e la capacità progettuale per candidarsi autonomamente a un bando europeo di questa complessità.</t>
+          <t>Il bando LIFE è orientato a progetti sistemici di policy, mercato e strumenti finanziari per la riqualificazione energetica degli edifici, richiedendo partnership transnazionali e capacità progettuali elevate difficilmente accessibili a una PMI del Cilento. Una piccola impresa edile o di efficienza energetica potrebbe al massimo partecipare come partner secondario, ma difficilmente come capofila o beneficiario diretto.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>One-Stop-Shops - Integrated services for clean energy transition in private buildings</t>
+          <t>Towards an effective implementation of key legislation in the field of sustainable energy</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-OSS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-POLICY</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6067,14 +6067,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE finanzia progetti di sistema per la creazione di sportelli integrati ('one-stop-shop') che accompagnano privati nella transizione energetica degli edifici, richiedendo partnership europee complesse e capacità progettuali avanzate difficilmente accessibili a una PMI del Cilento. Una piccola impresa edile o di efficienza energetica potrebbe al massimo partecipare come partner di un consorzio più ampio, ma difficilmente come capofila.</t>
+          <t>Il programma LIFE è orientato a progetti di scala europea con forte componente tecnico-normativa e istituzionale, richiedendo partenariati transnazionali e capacità progettuali elevate difficilmente accessibili a una PMI del Cilento senza un consorzio strutturato. L'obiettivo specifico sull'implementazione della legislazione sull'energia sostenibile riguarda principalmente enti pubblici, agenzie e grandi organizzazioni, rendendo marginale il ruolo diretto di una piccola impresa campana.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Energy renovation solutions – Boosting building renovation through effective markets and instruments</t>
+          <t>Alleviating household energy poverty in Europe</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BETTERRENO</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERPOV</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6114,14 +6114,14 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti dimostrativi su larga scala per la diffusione di soluzioni di efficienza energetica negli edifici, con budget elevati e requisiti di partenariato transnazionale che lo rendono difficilmente accessibile a una PMI campana di piccola dimensione senza un consorzio strutturato. Una PMI del Cilento potrebbe partecipare solo come partner secondario in un consorzio europeo, ma difficilmente come capofila.</t>
+          <t>Il programma LIFE è orientato a enti pubblici, ONG e consorzi di ricerca per progetti di ampio respiro sulla povertà energetica domestica; una PMI del Cilento avrebbe difficoltà a candidarsi autonomamente, potrebbe al massimo partecipare come partner junior in un consorzio, senza benefici diretti significativi.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Towards an effective implementation of key legislation in the field of sustainable energy</t>
+          <t>Strengthening national frameworks for renewable and efficient heating and cooling in existing buildings</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-POLICY</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-RENEWHC</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6161,14 +6161,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti di scala europea con forte componente tecnico-scientifica e iter burocratico complesso, difficilmente gestibile da una PMI senza un consorzio o partner istituzionali. Per una PMI del Cilento, l'accesso diretto è poco praticabile, anche se il settore energia sostenibile è rilevante per il territorio.</t>
+          <t>Il bando LIFE è orientato a soggetti istituzionali e organismi di ricerca per sviluppare politiche nazionali su riscaldamento/raffrescamento rinnovabile negli edifici esistenti, non a PMI operative. Una piccola impresa del Cilento difficilmente possiede la struttura progettuale e i partner transnazionali richiesti per accedere a questo tipo di finanziamento europeo diretto.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Alleviating household energy poverty in Europe</t>
+          <t>BUILD UP Skills - National Platforms on energy efficiency skills for the clean energy transition</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERPOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BUILDSKILLS</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6203,19 +6203,19 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a enti pubblici, ONG e consorzi di ricerca per progetti di scala europea sulla povertà energetica domestica; una PMI del Cilento difficilmente ha la struttura progettuale e i partner transnazionali richiesti per accedere competitivamente a questo tipo di bando. L'oggetto del bando non finanzia attività produttive o commerciali tipiche delle PMI, ma interventi dimostrativi e policy-oriented.</t>
+          <t>Il bando BUILD UP Skills è orientato alla creazione di piattaforme nazionali per la formazione professionale nel settore dell'efficienza energetica, coinvolgendo principalmente enti di formazione, associazioni di categoria e istituzioni pubbliche, non PMI come beneficiari diretti. Una piccola impresa edile o impiantistica del Cilento difficilmente può candidarsi autonomamente, pur potendo beneficiare indirettamente dei percorsi formativi che ne derivano.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Strengthening national frameworks for renewable and efficient heating and cooling in existing buildings</t>
+          <t>Crowding in private finance</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-RENEWHC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PRIVAFIN</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6250,19 +6250,19 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Credito/Finanza</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a enti pubblici, istituzioni e grandi organizzazioni per lo sviluppo di framework normativi nazionali su riscaldamento/raffrescamento rinnovabile: una PMI del Cilento difficilmente ha la struttura progettuale e istituzionale richiesta per candidarsi autonomamente. L'accesso potrebbe avvenire solo come partner secondario in un consorzio guidato da enti di ricerca o pubbliche amministrazioni.</t>
+          <t>Il bando LIFE 'Crowding in private finance' è orientato a strumenti finanziari e meccanismi di blending per attrarre capitali privati su progetti ambientali su larga scala, risultando di fatto inaccessibile per una PMI del Cilento senza struttura finanziaria dedicata e capacità progettuale europea. Il target reale sono intermediari finanziari, fondi e grandi operatori, non imprese di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>BUILD UP Skills - National Platforms on energy efficiency skills for the clean energy transition</t>
+          <t>Facilitating cooperation among energy communities</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BUILDSKILLS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERCOM</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6297,19 +6297,19 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Il bando BUILD UP Skills finanzia piattaforme nazionali per la formazione di lavoratori edili nell'efficienza energetica, ma è rivolto principalmente a consorzi istituzionali, associazioni di categoria e enti di formazione su scala nazionale, non a singole PMI. Una piccola impresa edile o impiantistica del Cilento potrebbe beneficiarne solo indirettamente, come destinataria delle azioni formative finanziate, non come soggetto candidato.</t>
+          <t>Il bando LIFE 2027 è orientato a progetti di cooperazione tra comunità energetiche a scala europea, richiedendo partnership transnazionali e capacità progettuali complesse difficilmente accessibili a una PMI di piccola dimensione del Cilento. Una PMI potrebbe partecipare solo in qualità di partner secondario all'interno di un consorzio più ampio, con ruolo marginale e oneri amministrativi elevati.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Crowding in private finance</t>
+          <t>Supporting the clean energy transition of European industry and businesses</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PRIVAFIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-INDUSTRY</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6344,19 +6344,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Credito/Finanza</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 'Crowding in private finance' è orientato a strumenti finanziari e meccanismi di blending per attrarre capitali privati in progetti ambientali su scala europea, rivolto principalmente a intermediari finanziari e grandi operatori istituzionali. Una PMI del Cilento difficilmente può accedere direttamente, mancando della struttura finanziaria e della capacità progettuale richiesta per questo tipo di strumento.</t>
+          <t>Il programma LIFE è orientato a progetti di scala europea con budget elevati e partnership istituzionali complesse, risultando difficilmente accessibile per una PMI del Cilento senza solide competenze progettuali europee e un consorzio internazionale. Le PMI potrebbero partecipare solo come partner junior in progetti coordinati da enti di ricerca o grandi organizzazioni, non come beneficiari diretti.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Facilitating cooperation among energy communities</t>
+          <t>Project Development Assistance for sustainable energy investments</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERCOM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PDA</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a progetti di cooperazione transnazionale tra comunità energetiche, richiedendo partnership complesse, capacità progettuali elevate e co-finanziamento significativo, elementi difficilmente gestibili da una PMI singola del Cilento. Una piccola impresa potrebbe partecipare solo come partner secondario in un consorzio guidato da enti pubblici o grandi organizzazioni del settore energetico.</t>
+          <t>Il bando LIFE PDA è orientato principalmente ad enti pubblici, autorità locali e grandi organizzatori di portafogli di investimento energetico, con requisiti tecnico-amministrativi complessi difficilmente sostenibili da una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe al più partecipare come soggetto associato, ma difficilmente come beneficiario diretto.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Supporting the clean energy transition of European industry and businesses</t>
+          <t>RFCS-2026-01-RPJ Coal Research projects</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-INDUSTRY</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-RPJ</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - RFCS2027</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -6438,19 +6438,19 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti di scala europea con requisiti tecnici e burocratici elevati, budget minimi consistenti e necessità di partnership transnazionali, caratteristiche che lo rendono difficilmente accessibile a una PMI del Cilento senza un consorzio strutturato. Finanzia interventi dimostrativi sulla transizione energetica pulita, ma la complessità progettuale e la concorrenza a livello UE scoraggiano candidature autonome di piccole imprese locali.</t>
+          <t>Il bando RFCS finanzia esclusivamente ricerca nel settore carbonifero (estrazione, uso pulito del carbone, sicurezza nelle miniere), un ambito del tutto estraneo al tessuto produttivo del Cilento e della Campania in generale, dove non esistono attività minerarie legate al carbone. Una PMI locale non avrebbe né i requisiti tecnici né il profilo settoriale per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Project Development Assistance for sustainable energy investments</t>
+          <t>RFCS-2026-01-AM Coal Accompanying measures</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6460,17 +6460,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PDA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-AM</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - RFCS2027</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -6485,19 +6485,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE PDA è orientato a supportare la fase di sviluppo progettuale per investimenti in energia sostenibile di scala medio-grande, con procedure europee complesse e requisiti tecnici elevati difficilmente gestibili da una PMI senza un partner istituzionale. Per una piccola impresa del Cilento, l'accesso diretto è poco praticabile senza il coinvolgimento di enti pubblici o agenzie energetiche come capofila.</t>
+          <t>Il bando RFCS riguarda misure di accompagnamento per le regioni carbonifere europee in transizione e si rivolge principalmente a enti di ricerca, università e grandi organizzatori istituzionali, non a PMI. Il Cilento e la Campania non hanno un tessuto produttivo legato al carbone, rendendo questo bando di fatto inaccessibile e non pertinente per una PMI locale.</t>
         </is>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-RPJ Coal Research projects</t>
+          <t>RFCS-2026-02-AM Steel Accompanying measures</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-RPJ</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-AM</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia esclusivamente ricerca tecnica nel settore carbonifero (estrazione, utilizzo pulito del carbone, sicurezza nelle miniere), un ambito industriale del tutto assente nel territorio cilentano e marginale per le PMI campane. Una piccola o media impresa del Cilento non possiede né i requisiti settoriali né le capacità di ricerca specialistica richieste per partecipare competitivamente.</t>
+          <t>Il bando RFCS (Research Fund for Coal and Steel) finanzia misure di accompagnamento legate alla ricerca nell'industria siderurgica europea, un settore quasi assente nel tessuto produttivo del Cilento e della Campania interna, dominato da agricoltura, turismo e piccolo artigianato. Una PMI locale non avrebbe né il profilo industriale né la capacità tecnica per competere in un programma UE destinato a grandi consorzi di ricerca del comparto acciaio.</t>
         </is>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-AM Coal Accompanying measures</t>
+          <t>RFCS-2026-02-RPJ Steel Research projects</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-AM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-RPJ</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6579,19 +6579,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS riguarda misure di accompagnamento per le comunità e i lavoratori colpiti dalla transizione fuori dal carbone, un settore industriale assente nel Cilento e marginale in Campania. Una PMI locale non ha i requisiti settoriali né il profilo di ricerca necessario per accedere a questo tipo di finanziamento europeo.</t>
+          <t>Il bando RFCS finanzia esclusivamente progetti di ricerca nel settore siderurgico (acciaio e carbone) destinati prevalentemente a grandi consorzi industriali e istituti di ricerca europei, con requisiti tecnici e finanziari difficilmente compatibili con una PMI del Cilento, territorio a vocazione turistica e agricola privo di filiere metallurgiche rilevanti.</t>
         </is>
       </c>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-AM Steel Accompanying measures</t>
+          <t>RFCS-2026-02-PDP Steel Pilot and demonstration projects</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-AM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-PDP</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6626,19 +6626,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS riguarda misure di accompagnamento per il settore siderurgico europeo (ricerca, formazione e riconversione legate all'industria dell'acciaio) ed è destinato principalmente a grandi consorzi industriali e centri di ricerca. Una PMI del Cilento, territorio a vocazione turistica e agricola, non ha praticamente possibilità di accesso né un profilo settoriale compatibile.</t>
+          <t>Il bando RFCS finanzia progetti pilota e dimostrativi nel settore siderurgico europeo, richiedendo consorzi di ricerca con laboratori accreditati e grandi imprese industriali: una PMI del Cilento, priva di attività manifatturiere legate all'acciaio e senza le capacità tecniche e finanziarie richieste, non ha concrete possibilità di accesso né come capofila né come partner rilevante.</t>
         </is>
       </c>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-RPJ Steel Research projects</t>
+          <t>RFCS-2026-01-PDP Coal Pilot and demonstration projects</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-RPJ</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-PDP</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6678,14 +6678,14 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia esclusivamente progetti di ricerca industriale nel settore siderurgico (acciaio e carbone), richiedendo consorzi di grandi operatori industriali e centri di ricerca specializzati: una PMI del Cilento, in un territorio a vocazione turistica e agricola, non ha i requisiti tecnici né settoriali per partecipare. I costi ammissibili riguardano R&amp;S avanzata sull'acciaio, ambito del tutto estraneo al tessuto produttivo locale.</t>
+          <t>Il bando RFCS finanzia progetti pilota e dimostrativi legati all'industria carbonifera e alle tecnologie del carbone, settore del tutto assente nel tessuto produttivo del Cilento e della Campania in generale. Una PMI locale non ha le competenze tecniche né il profilo industriale richiesto per partecipare a questo tipo di progetto europeo ad alta specializzazione.</t>
         </is>
       </c>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-PDP Steel Pilot and demonstration projects</t>
+          <t>RFCS-2026-Steel-Big Tickets under the steel and metals action plan dual-use</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-PDP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-BT-STEEL-SMAP-DUAL-USE</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6725,34 +6725,34 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia progetti pilota e dimostrativi nel settore siderurgico (acciaio) a livello europeo, richiedendo consorzi di ricerca con capacità tecniche e finanziarie elevate, del tutto incompatibili con le dimensioni e il tessuto produttivo di una PMI del Cilento, area vocata a turismo, agricoltura e agroalimentare. Le PMI campane di piccola dimensione non hanno né la base industriale siderurgica né le risorse per partecipare a progetti di questa complessità.</t>
+          <t>Il bando RFCS finanzia progetti di ricerca di grande scala nel settore siderurgico e dei metalli con focus su applicazioni dual-use (civile/difesa), richiedendo consorzi internazionali e capacità tecnico-finanziarie elevate incompatibili con le dimensioni tipiche di una PMI del Cilento, area peraltro non caratterizzata da industria pesante metallurgica.</t>
         </is>
       </c>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-PDP Coal Pilot and demonstration projects</t>
+          <t>European mini-slate development</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-PDP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-DEVMINISLATE</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>UE - RFCS2027</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -6767,39 +6767,39 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia progetti pilota e dimostrativi legati all'industria carbonifera e all'acciaio, settori assenti nel tessuto produttivo del Cilento e della Campania in generale. Una PMI locale non ha le caratteristiche tecniche né il profilo industriale richiesto per accedere a questo tipo di finanziamento europeo altamente specializzato.</t>
+          <t>Il bando CREA2027 'European mini-slate development' è rivolto principalmente a operatori del settore audiovisivo e cinematografico per lo sviluppo di pacchetti di progetti (mini-slate), con requisiti dimensionali e di fatturato specifici del comparto creativo europeo che difficilmente si adattano a una PMI generalista del Cilento. Le spese finanziabili riguardano sviluppo di sceneggiature, ricerca di co-produttori internazionali e preparazione di progetti audiovisivi, ambito molto di nicchia.</t>
         </is>
       </c>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-Steel-Big Tickets under the steel and metals action plan dual-use</t>
+          <t>Toward a comprehensive assessment of the disturbance of marine ecosystems by anthropogenic underwater noise</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-BT-STEEL-SMAP-DUAL-USE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-01</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>UE - RFCS2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -6814,19 +6814,19 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia progetti di ricerca industriale su larga scala nel settore siderurgico e dei metalli, con budget tipicamente nell'ordine di milioni di euro e requisiti di consorzio internazionale, rendendolo inaccessibile per una PMI del Cilento che non operi direttamente nella produzione di acciaio o metalli. Una piccola impresa campana difficilmente possiede la capacità tecnica e finanziaria per partecipare come partner significativo in progetti 'Big Ticket' di questa natura.</t>
+          <t>Il bando Horizon riguarda la ricerca scientifica sull'impatto del rumore antropico sottomarino sugli ecosistemi marini, un ambito altamente specializzato che richiede capacità di ricerca avanzata e partenariati internazionali difficilmente accessibili a una PMI campana di piccole dimensioni. Anche per realtà del Cilento legate alla pesca o al mare, la struttura del bando Horizon presuppone consorzi di enti di ricerca e università, rendendo la partecipazione diretta di una PMI marginale e complessa.</t>
         </is>
       </c>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>European mini-slate development</t>
+          <t>Improving circularity of multilayer flexible plastic food contact packaging</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6836,17 +6836,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-DEVMINISLATE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-01</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -6861,19 +6861,19 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Il bando CREA2027 'European mini-slate development' è orientato a soggetti del settore audiovisivo/cinematografico per lo sviluppo di cataloghi di contenuti europei, ambito molto specifico e lontano dal tessuto produttivo tipico del Cilento e delle PMI campane. L'accesso richiede competenze e strutture proprie dell'industria creativa e culturale organizzata, rendendo il bando poco praticabile per una PMI locale di piccola dimensione.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, partnership internazionali e strutture di R&amp;S difficilmente disponibili in una PMI del Cilento; il focus sulla circolarità degli imballaggi plastici multistrato alimentari è altamente specialistico e più adatto a grandi imprese o centri di ricerca. Una PMI locale del settore food packaging potrebbe partecipare solo come partner secondario in un consorzio europeo strutturato.</t>
         </is>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Toward a comprehensive assessment of the disturbance of marine ecosystems by anthropogenic underwater noise</t>
+          <t>Supporting pre-normative research for standardization of the bio-based products</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-08</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6908,19 +6908,19 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca scientifica avanzata sull'impatto del rumore antropico sugli ecosistemi marini, richiedendo capacità di ricerca specializzate e consorzi internazionali tipicamente composti da università ed enti di ricerca. Una PMI campana, anche operante nel settore marittimo o turistico del Cilento, difficilmente dispone delle competenze tecniche e della struttura progettuale necessarie per partecipare competitivamente, salvo come partner secondario di un consorzio guidato da istituti di ricerca.</t>
+          <t>Il bando Horizon finanzia ricerca pre-normativa sulla standardizzazione dei bio-based products, richiedendo capacità di ricerca scientifica avanzata e partnership con enti di ricerca europei, strutturalmente difficili da costruire per una PMI del Cilento. L'impegno amministrativo, la competizione a livello europeo e l'assenza di focus territoriale rendono questo bando poco accessibile per realtà produttive locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Improving circularity of multilayer flexible plastic food contact packaging</t>
+          <t>Understanding biomass flows in Europe</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-05</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6960,14 +6960,14 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzio internazionale e competenze specifiche sul packaging alimentare multistrato: barriere tecniche e burocratiche elevate rendono l'accesso diretto quasi impraticabile per una PMI del Cilento senza un partner universitario o un grande industriale del settore. Solo aziende del comparto imballaggio alimentare con un ufficio R&amp;D strutturato potrebbero partecipare in qualità di partner secondari.</t>
+          <t>Il bando Horizon focalizzato sui flussi di biomassa in Europa richiede capacità di ricerca scientifica avanzata e partecipazione a consorzi internazionali, strutture tipicamente fuori dalla portata di una PMI del Cilento. Pur operando in un territorio con risorse agricole e forestali rilevanti, una piccola impresa difficilmente dispone delle competenze tecniche e della struttura amministrativa necessarie per gestire un progetto di questa complessità.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Supporting pre-normative research for standardization of the bio-based products</t>
+          <t>Developing methods to assess the presence, functions and sensitivity of groundwater ecosystems</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-02</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7007,14 +7007,14 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca pre-normativa sulla standardizzazione dei prodotti bio-based, un'attività tipicamente svolta da enti di ricerca e grandi consorzi industriali: una PMI del Cilento potrebbe partecipare solo come partner secondario in progetti complessi, con oneri amministrativi elevati e scarsa possibilità di guidare il consorzio. Il settore agro-alimentare e bio-based del territorio non trova un accesso diretto e pratico a questo tipo di call.</t>
+          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sugli ecosistemi delle acque sotterranee, con consorzio internazionale e competenze altamente specializzate difficilmente disponibili in una PMI standard. Sebbene il Cilento abbia risorse idriche rilevanti, questo tipo di progetto è accessibile quasi esclusivamente a università, enti di ricerca o grandi imprese con divisioni R&amp;D strutturate.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Understanding biomass flows in Europe</t>
+          <t>Advanced recovery of critical raw materials from Waste from Electrical and Electronic Equipment (WEEE)</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-03</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7054,14 +7054,14 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sui flussi di biomassa in Europa richiede capacità di ricerca scientifica avanzata, consorzio internazionale e competenze tecniche difficilmente disponibili in una PMI del Cilento; le risorse finanziabili (ricerca, modellazione dati, networking europeo) sono orientate a enti di ricerca e grandi imprese con strutture R&amp;D consolidate.</t>
+          <t>Il bando Horizon UE sul recupero avanzato di materie prime critiche dai RAEE richiede capacità di ricerca industriale avanzata, consorzi internazionali e budget elevati, risultando di fatto inaccessibile per una PMI del Cilento senza una specializzazione specifica nel settore del riciclo elettronico o della metallurgia estrattiva. Una piccola impresa campana potrebbe partecipare solo in qualità di partner junior in un consorzio già strutturato, scenario poco probabile senza reti di collaborazione preesistenti con centri di ricerca o grandi aziende del settore.</t>
         </is>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Developing methods to assess the presence, functions and sensitivity of groundwater ecosystems</t>
+          <t>Understanding and tackling the decline of insects</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-01</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sugli ecosistemi delle acque sotterranee, richiedendo consorzio con università e centri di ricerca, rendicontazione complessa e competenze altamente specializzate difficilmente disponibili in una PMI standard. Sebbene il Cilento presenti acquiferi e zone di rilevanza idrogeologica, solo PMI con forte vocazione ambientale/scientifica e già inserite in reti di ricerca europee potrebbero candidarsi realisticamente.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca scientifica avanzata, consorzio internazionale e strutture di R&amp;S difficilmente accessibili a una PMI di piccola dimensione del Cilento; il focus sul declino degli insetti impollinatori potrebbe teoricamente coinvolgere aziende agricole locali, ma solo come partner secondari di grandi enti di ricerca, rendendo l'accesso diretto estremamente improbabile.</t>
         </is>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Advanced recovery of critical raw materials from Waste from Electrical and Electronic Equipment (WEEE)</t>
+          <t>Advancing integrated scenarios and prediction models for informing transition to a nature positive society</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-05</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7148,14 +7148,14 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata sul recupero di materie prime critiche dai RAEE, con consorzialità internazionale e competenze tecnologiche specialistiche difficilmente presenti in una PMI del Cilento. La struttura del programma Horizon è orientata a grandi enti di ricerca e aziende con laboratori R&amp;D consolidati, rendendo l'accesso diretto praticamente inaccessibile per una piccola impresa locale.</t>
+          <t>Il bando Horizon richiede la partecipazione a consorzi internazionali di ricerca con capacità scientifica avanzata, rendicontazione complessa e co-finanziamento elevato, requisiti difficilmente compatibili con una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio guidato da università o enti di ricerca, senza possibilità di candidatura autonoma.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Understanding and tackling the decline of insects</t>
+          <t>Pushing the frontier of knowledge and conservation action for deep sea ecosystems</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-03</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7195,14 +7195,14 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU sul declino degli insetti è orientato a consorzi di ricerca accademica e istituti scientifici, con requisiti tecnici e amministrativi difficilmente accessibili a una PMI campana. Anche per realtà agricole del Cilento interessate all'apicoltura o alla biodiversità, la partecipazione diretta come capofila è praticamente esclusa, mentre il ruolo di partner richiede competenze di ricerca avanzate raramente presenti in una piccola impresa.</t>
+          <t>Il bando Horizon Europe sulla ricerca e conservazione degli ecosistemi delle profondità marine è destinato principalmente a enti di ricerca, università e consorzi scientifici internazionali, richiedendo competenze altamente specializzate e strutture di ricerca avanzate che una PMI campana tipicamente non possiede. Anche per realtà del Cilento legate alla pesca o al turismo marino, le barriere di accesso (budget, requisiti tecnici, partenariati transnazionali) rendono la partecipazione diretta praticamente inaccessibile senza un ruolo marginale come partner secondario.</t>
         </is>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Advancing integrated scenarios and prediction models for informing transition to a nature positive society</t>
+          <t>Advancing recycling technologies for mixed post-consumer textiles waste from blended products</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-02</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7242,14 +7242,14 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi europei di ricerca con forte componente scientifica e modellistica per scenari 'nature positive', struttura progettuale complessa e capacità amministrative difficilmente sostenibili da una PMI campana di piccole dimensioni. Il Cilento, pur essendo territorio ad alta valenza naturalistica, non offre vantaggi competitivi specifici per questo tipo di call orientata a centri di ricerca e università.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata e partnership internazionali per sviluppare tecnologie di riciclo di tessuti post-consumo misti, con requisiti tecnici e amministrativi difficilmente sostenibili da una PMI del Cilento non specializzata nel settore tessile o R&amp;D. Salvo che la PMI operi specificamente nel riciclo tessile e possa entrare come partner in un consorzio europeo, l'accesso pratico rimane molto limitato.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Pushing the frontier of knowledge and conservation action for deep sea ecosystems</t>
+          <t>Bioremediation of Ukraine’s ecosystems contaminated by conflicts</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-02</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7284,19 +7284,19 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato alla ricerca scientifica avanzata sugli ecosistemi degli abissi marini, con requisiti tecnici e consorziali tipici di enti di ricerca e università, rendendo l'accesso diretto per una PMI del Cilento estremamente complesso e improbabile senza un ruolo marginale in un consorzio. Non sono previste spese tipicamente sostenibili da una piccola impresa locale né attività commerciali finanziabili nel breve termine.</t>
+          <t>Il bando Horizon riguarda la bonifica biologica degli ecosistemi ucraini contaminati da conflitti bellici: un ambito altamente specializzato e geograficamente lontano dalla Campania, che richiede partnership internazionali e competenze di ricerca avanzata difficilmente accessibili a una PMI del Cilento. Le risorse finanziabili riguardano progetti di R&amp;S su larga scala, non attività produttive o commerciali tipiche delle PMI locali.</t>
         </is>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Advancing recycling technologies for mixed post-consumer textiles waste from blended products</t>
+          <t>Demonstrating and deploying innovative collection, sorting-for-reuse and repair systems for textiles at city/region level (Circular Cities and Regions Initiative topic)</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-04</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7331,19 +7331,19 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede attività di ricerca avanzata su tecnologie di riciclaggio per tessuti misti post-consumo, con consorzio internazionale e capacità R&amp;D elevate, requisiti difficilmente soddisfabili da una PMI campana di piccole dimensioni. Il Cilento non ha un tessuto industriale tessile strutturato in grado di partecipare competitivamente a progetti di questa complessità tecnica e finanziaria.</t>
+          <t>Il bando Horizon richiede la dimostrazione e il deployment di sistemi innovativi di raccolta e riparazione tessile su scala urbana/regionale, con consorziate di ricerca e budget tipicamente superiori a 3-5 milioni di euro: una PMI del Cilento difficilmente può guidare o partecipare competitivamente senza un solido partenariato europeo già strutturato. Il settore tessile non è un comparto produttivo rilevante nel territorio cilentano, rendendo ancora più difficile giustificare una candidatura territorialmente radicata.</t>
         </is>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Bioremediation of Ukraine’s ecosystems contaminated by conflicts</t>
+          <t>Bio-based innovation in society: supporting the sustainable way of living</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-10</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7383,14 +7383,14 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è focalizzato sulla bonifica di ecosistemi contaminati da conflitti in Ucraina, richiedendo competenze altamente specializzate in biorisanamento e partnership internazionali di ricerca difficilmente accessibili a una PMI campana del Cilento. I requisiti consortili e la complessità progettuale di Horizon Europe lo rendono praticamente inaccessibile senza un ente di ricerca capofila.</t>
+          <t>Il bando Horizon Europe richiede consorzi internazionali e capacità di ricerca avanzata difficilmente accessibili a una PMI di piccola dimensione del Cilento; tuttavia, aziende agricole o agroalimentari locali con prodotti bio-based potrebbero partecipare come partner di un consorzio guidato da un ente di ricerca, contribuendo alla validazione di soluzioni sostenibili sul territorio.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating and deploying innovative collection, sorting-for-reuse and repair systems for textiles at city/region level (Circular Cities and Regions Initiative topic)</t>
+          <t>Ensuring continuous effectiveness of protected areas in conserving habitats and species while facing intensifying drivers of biodiversity loss</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-04</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7430,14 +7430,14 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede progetti dimostrativi su larga scala (città/regione) per sistemi innovativi di raccolta e riuso di tessili, con consorziaizioni internazionali e budget tipicamente superiori ai 3-5 milioni di euro: struttura inaccessibile per una PMI del Cilento senza un partenariato solido già costruito. Solo un'azienda del settore tessile o della gestione rifiuti con esperienza in progetti europei potrebbe partecipare come partner junior in un consorzio più ampio.</t>
+          <t>Il bando Horizon si rivolge prevalentemente a enti di ricerca, università e consorzi internazionali per progetti scientifici su biodiversità e aree protette; una PMI campana, pur operando nel Cilento (Parco Nazionale), difficilmente può guidare un progetto di questa complessità e non copre spese operative ordinarie. L'accesso è realistico solo come partner secondario in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Bio-based innovation in society: supporting the sustainable way of living</t>
+          <t>Advancing the European bio-based innovation enabled by biotechnology and biomanufacturing concepts</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-10</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-07</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7477,14 +7477,14 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla bio-based innovation richiede consorzi internazionali e capacità di ricerca avanzata, rendendolo difficilmente accessibile per una PMI del Cilento senza partnership consolidate con università o centri di ricerca. Le spese finanziabili (R&amp;S, prototipazione, disseminazione) richiedono strutture organizzative e competenze progettuali che le piccole imprese locali raramente possiedono autonomamente.</t>
+          <t>Il bando Horizon finanzia progetti di ricerca avanzata in biotecnologia e biomanufacturing, richiedendo capacità di R&amp;D strutturata, partnership internazionali e competenze scientifiche specialistiche difficilmente disponibili in una PMI di piccola dimensione del Cilento. L'accesso è realistico solo per PMI innovative con laboratori propri o già integrate in reti di ricerca europee.</t>
         </is>
       </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Ensuring continuous effectiveness of protected areas in conserving habitats and species while facing intensifying drivers of biodiversity loss</t>
+          <t>Bioeconomy policy support hub for Member States, regions and sectors</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-06</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -7519,19 +7519,19 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo è orientato a consorzi di ricerca e istituzioni scientifiche per la conservazione della biodiversità nelle aree protette, con requisiti di partnership transnazionale e capacità di ricerca difficilmente compatibili con una PMI campana di piccole dimensioni. Sebbene il Cilento, con il suo Parco Nazionale, rappresenti un contesto territorialmente rilevante, una PMI avrebbe accesso solo come partner secondario in un consorzio già strutturato, rendendo la partecipazione diretta poco praticabile.</t>
+          <t>Il bando Horizon è orientato a enti di ricerca, istituzioni pubbliche e grandi consorzi per supportare policy sulla bioeconomia a livello europeo, non è direttamente accessibile a una PMI campana come beneficiario principale. Una PMI del Cilento, anche operante in agricoltura o agroalimentare, difficilmente può partecipare senza far parte di un consorzio coordinato da soggetti istituzionali o università.</t>
         </is>
       </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Advancing the European bio-based innovation enabled by biotechnology and biomanufacturing concepts</t>
+          <t>ERC PROOF OF CONCEPT GRANTS</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-POC</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -7571,34 +7571,34 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede consorzi internazionali, capacità di ricerca avanzata in biotecnologie e biomanufacturing e budget progettuali elevati, barriere difficilmente superabili per una PMI del Cilento senza un partner universitario o un centro R&amp;S strutturato. Solo PMI con laboratori interni o già inserite in reti europee di bioeconomia potrebbero candidarsi come partner secondari.</t>
+          <t>L'ERC Proof of Concept è riservato esclusivamente a ricercatori già beneficiari di un grant ERC attivo o recente, rendendo di fatto inaccessibile il bando a una PMI del Cilento che non abbia già un rapporto diretto con il Consiglio Europeo della Ricerca. Non finanzia direttamente imprese, ma attività di valorizzazione commerciale di ricerche ERC già finanziate.</t>
         </is>
       </c>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Bioeconomy policy support hub for Member States, regions and sectors</t>
+          <t>Quality Label Humanitarian Aid - Full Procedure</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>10/06/2021</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESC-HUMAID-2021-QUAL-LABEL-FP</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ESC2027</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -7613,34 +7613,34 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a enti di ricerca, istituzioni pubbliche e grandi consorzi europei per sviluppare policy sulla bioeconomia, non a PMI operative. Una piccola impresa del Cilento, anche in settori agricoli o agroalimentari affini alla bioeconomia, difficilmente accede direttamente senza essere partner junior di un consorzio internazionale già strutturato.</t>
+          <t>Il bando riguarda la certificazione di qualità per organizzazioni attive negli aiuti umanitari (Quality Label), un ambito riservato a ONG e soggetti del terzo settore con esperienza specifica in contesti di crisi internazionali. Una PMI del Cilento o della Campania non rientra nei soggetti ammissibili e non ha accesso a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>ERC PROOF OF CONCEPT GRANTS</t>
+          <t>From lab to market: Strengthening the role of Technology Transfer Offices in bringing knowledge to the market</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-POC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIE-2026-03-CONNECT-01</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -7665,14 +7665,14 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Il grant ERC Proof of Concept è riservato esclusivamente a ricercatori già beneficiari di un grant ERC attivo, rendendo di fatto inaccessibile il bando a una PMI del Cilento che non abbia un principal investigator ERC associato. Non finanzia direttamente attività aziendali ordinarie, ma la commercializzazione di risultati di ricerca accademica.</t>
+          <t>Il bando è rivolto principalmente agli Uffici di Trasferimento Tecnologico (TTO) di università ed enti di ricerca, non alle PMI in quanto beneficiarie dirette. Una PMI del Cilento non può candidarsi autonomamente, ma potrebbe al limite essere coinvolta come partner industriale in un consorzio guidato da un ente di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Quality Label Humanitarian Aid - Full Procedure</t>
+          <t>Environment governance</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -7682,17 +7682,17 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESC-HUMAID-2021-QUAL-LABEL-FP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-ENV-GOV</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>UE - ESC2027</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -7707,19 +7707,19 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Il bando ESC2027 Quality Label per gli Aiuti Umanitari è destinato a organizzazioni no-profit e ONG che operano nel settore dell'aiuto umanitario internazionale, non a PMI commerciali. Una piccola o media impresa del Cilento non rientra nei soggetti ammissibili e non trarrebbe benefici concreti da questa opportunità.</t>
+          <t>Il programma LIFE - Environment Governance è orientato principalmente a enti pubblici, ONG e organismi di ricerca per progetti di governance ambientale su scala europea; le PMI del Cilento difficilmente possono accedere autonomamente, data la complessità progettuale, la necessità di partenariati transnazionali e la mancanza di finanziamento diretto per attività produttive o commerciali.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>From lab to market: Strengthening the role of Technology Transfer Offices in bringing knowledge to the market</t>
+          <t>Circular Economy and Zero Pollution</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7729,17 +7729,17 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIE-2026-03-CONNECT-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-ENV-ENVIRONMENT</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -7754,19 +7754,19 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto principalmente a uffici di trasferimento tecnologico (TTO) di università e centri di ricerca, non a PMI come beneficiari diretti. Una PMI del Cilento potrebbe al massimo beneficiarne indirettamente come partner o destinataria di servizi di technology transfer, ma non può accedere autonomamente ai fondi.</t>
+          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, centri di ricerca e grandi consorzi, con requisiti progettuali complessi e budget elevati difficilmente gestibili da una PMI del Cilento in autonomia. Una piccola impresa potrebbe partecipare solo come partner secondario in un consorzio, non come beneficiario principale.</t>
         </is>
       </c>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Environment governance</t>
+          <t>Climate Governance and Information</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-ENV-GOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-GOV</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -7806,14 +7806,14 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE - Environment Governance è orientato a progetti di scala europea con focus su policy ambientali e governance istituzionale, richiedendo partnership transnazionali e capacità progettuali elevate difficilmente accessibili a una PMI del Cilento senza un ente capofila qualificato. Le risorse finanziabili riguardano attività di monitoraggio ambientale, sviluppo normativo e capacity building istituzionale, ambiti lontani dalle esigenze operative tipiche di una piccola impresa locale.</t>
+          <t>Il programma LIFE Climate Governance and Information finanzia principalmente campagne di sensibilizzazione, reti e progetti di governance climatica su scala europea, rivolti a enti pubblici, ONG e grandi organizzazioni, rendendo l'accesso diretto per una PMI del Cilento estremamente complesso senza un partenariato transnazionale strutturato. Le spese ammissibili riguardano comunicazione e advocacy climatica, settori difficilmente coerenti con l'operatività ordinaria di una piccola impresa manifatturiera o di servizi locale.</t>
         </is>
       </c>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Circular Economy and Zero Pollution</t>
+          <t>Climate Change Adaptation</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-ENV-ENVIRONMENT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-CCA</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7853,14 +7853,14 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti pilota e dimostrativi su larga scala in materia di economia circolare e riduzione dell'inquinamento, con iter burocratici complessi e budget minimi elevati che lo rendono di difficile accesso per una PMI campana autonomamente; una partecipazione in qualità di partner in un consorzio europeo rimane teoricamente possibile ma richiede competenze progettuali avanzate e reti transnazionali raramente disponibili in realtà locali del Cilento.</t>
+          <t>Il programma LIFE è orientato principalmente a enti pubblici, università e organizzazioni no-profit con forte capacità progettuale europea; una PMI del Cilento difficilmente può accedere direttamente senza essere partner di un consorzio strutturato, e i costi di progettazione e rendicontazione sono elevati rispetto alle dimensioni tipiche di una piccola impresa locale. L'adattamento ai cambiamenti climatici finanziato riguarda per lo più interventi territoriali e dimostrativi su larga scala, non attività produttive ordinarie di una PMI.</t>
         </is>
       </c>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Climate Governance and Information</t>
+          <t>Climate Change Mitigation</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-GOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-CCM</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Climate Governance and Information finanzia principalmente campagne di comunicazione, disseminazione e governance climatica a scala europea o nazionale, risultando difficilmente accessibile per una PMI del Cilento che non abbia struttura progettuale e capacità di gestione di fondi UE diretti. I beneficiari tipici sono enti pubblici, ONG e grandi organizzazioni ambientali, non imprese private di piccola dimensione.</t>
+          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e grandi consorzi con capacità progettuali complesse e cofinanziamento significativo; una PMI del Cilento difficilmente può accedere autonomamente senza essere parte di un partenariato europeo consolidato. Le spese finanziabili riguardano azioni dimostrative e pilota sulla mitigazione climatica, settori distanti dalle attività produttive tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Climate Change Adaptation</t>
+          <t>Nature and Biodiversity</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-CCA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-NAT-NATURE</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -7947,14 +7947,14 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e grandi consorzi, con procedure complesse e cofinanziamenti elevati difficilmente sostenibili da una PMI del Cilento; inoltre i progetti di adattamento climatico richiedono capacità progettuali e partnership istituzionali che raramente una piccola impresa possiede autonomamente.</t>
+          <t>Il programma LIFE Nature and Biodiversity finanzia principalmente enti pubblici, ONG e istituti di ricerca per progetti di conservazione degli habitat e delle specie protette, con budget minimi elevati e procedure di candidatura complesse che rendono l'accesso diretto per una PMI del Cilento molto difficile. Una PMI potrebbe partecipare solo come partner secondario in un consorzio guidato da enti come Parco Nazionale del Cilento, ma raramente come beneficiario principale.</t>
         </is>
       </c>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Climate Change Mitigation</t>
+          <t>Nature Governance and Information</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-CCM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-NAT-GOV</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7994,14 +7994,14 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e grandi consorzi, con procedure complesse e co-finanziamenti elevati difficilmente sostenibili da una PMI campana; le PMI del Cilento potrebbero partecipare solo come partner secondari in progetti guidati da soggetti capofila istituzionali, senza accesso diretto ai fondi.</t>
+          <t>Il programma LIFE Nature Governance and Information finanzia prevalentemente enti pubblici, ONG ambientali e organismi di ricerca per progetti di governance della natura e biodiversità; una PMI del Cilento potrebbe partecipare solo come partner secondario in progetti coordinati da soggetti istituzionali, con accesso indiretto ai fondi e complessità gestionale elevata.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Nature and Biodiversity</t>
+          <t>Projects on Legislative and Policy Priorities in the fields of Nature &amp; Biodiversity and Circular Economy &amp; Quality of Life</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-NAT-NATURE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-NAT-ENV</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Nature and Biodiversity finanzia principalmente enti pubblici, ONG e istituti di ricerca per progetti di conservazione degli habitat e delle specie; una PMI campana, anche nel Cilento (area ad alta biodiversità e Parco Nazionale), difficilmente accede direttamente senza un consorzio di progetto strutturato e competenze tecniche specifiche in campo naturalistico. I costi di progettazione e la complessità burocratica europea rendono l'accesso poco praticabile per una piccola impresa autonoma.</t>
+          <t>Il programma LIFE finanzia progetti su biodiversità ed economia circolare, ma è prevalentemente orientato a enti pubblici, ONG e grandi consorzi con capacità di gestione europea; una PMI del Cilento potrebbe partecipare solo come partner junior in un consorzio strutturato, con accesso indiretto ai fondi e complessità gestionale elevata.</t>
         </is>
       </c>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Nature Governance and Information</t>
+          <t>Ecodesign and energy labelling compliance support facility for suppliers and retailers</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-NAT-GOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-ENER-COMPLIANCE</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8088,14 +8088,14 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Nature Governance and Information finanzia principalmente progetti di governance ambientale, monitoraggio ecosistemi e diffusione di buone pratiche naturalistiche, con procedure europee complesse e budget elevati che richiedono partenariati internazionali. Una PMI del Cilento potrebbe partecipare solo in qualità di partner secondario di un consorzio guidato da enti pubblici o ONG ambientali, rendendo l'accesso diretto estremamente difficile.</t>
+          <t>Il bando LIFE è orientato a grandi progetti di sistema europei per supportare fornitori e retailer nella conformità all'ecodesign e all'etichettatura energetica, con strutture progettuali complesse che richiedono partnership transnazionali e capacità tecniche specialistiche difficilmente accessibili per una PMI campana di piccole dimensioni, specialmente nel contesto rurale del Cilento. Non finanzia investimenti produttivi diretti ma attività di supporto normativo-tecnico a livello di filiera, con scarsa applicabilità concreta per realtà locali.</t>
         </is>
       </c>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Projects on Legislative and Policy Priorities in the fields of Nature &amp; Biodiversity and Circular Economy &amp; Quality of Life</t>
+          <t>Multilevel climate and energy dialogue to deliver the Governance Regulation and the post–2030 energy and climate policy framework</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-NAT-ENV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-ENER-GOV</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8130,19 +8130,19 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti di policy e legislazione europea su natura, biodiversità ed economia circolare, con focus su enti pubblici, ONG e organizzazioni di ricerca; una PMI del Cilento avrebbe difficoltà ad accedere come capofila e troverebbe limitata rilevanza diretta, salvo partecipare come partner in consorzi con soggetti istituzionali già strutturati.</t>
+          <t>Il bando LIFE riguarda il dialogo multilivello su governance climatica ed energetica post-2030, destinato principalmente a enti pubblici, organizzazioni no-profit e grandi consorzi istituzionali: una PMI del Cilento difficilmente può candidarsi come soggetto capofila o partner rilevante. Non sono previste spese operative aziendali tipiche delle PMI né settori produttivi locali direttamente coinvolti.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Ecodesign and energy labelling compliance support facility for suppliers and retailers</t>
+          <t>Technical Assistance preparation of SNaPs</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-ENER-COMPLIANCE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-NAT-SNAP</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8177,19 +8177,19 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a progetti di sistema su scala europea per supportare fornitori e retailer nella conformità all'ecodesign e all'etichettatura energetica, con requisiti tecnici e capacità progettuali difficilmente accessibili per una PMI del Cilento. Le PMI di piccola dimensione raramente possono candidarsi direttamente a bandi LIFE, che richiedono consorzi strutturati, co-finanziamento significativo e competenze specialistiche in normativa UE sull'efficienza energetica dei prodotti.</t>
+          <t>Si tratta di un bando LIFE dedicato alla preparazione di Piani Nazionali di Conservazione della Natura (SNaPs), rivolto principalmente a enti pubblici, autorità nazionali e organizzazioni ambientali, non a PMI. Una piccola impresa del Cilento non ha i requisiti soggettivi né le competenze istituzionali richieste per partecipare come beneficiario diretto.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Multilevel climate and energy dialogue to deliver the Governance Regulation and the post–2030 energy and climate policy framework</t>
+          <t>Technical Assistance preparation of ENV SIPs</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-ENER-GOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-ENV-SIP</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE riguarda il dialogo multilivello su clima ed energia per supportare la governance regolatoria europea post-2030: si tratta di progetti di advocacy istituzionale e policy-making, non di interventi produttivi o investimenti aziendali. Una PMI del Cilento non ha struttura né profilo per candidarsi come soggetto capofila o partner rilevante in questo tipo di progetto.</t>
+          <t>Si tratta di un bando di assistenza tecnica UE destinato a supportare la preparazione di Strategic Integrated Projects in campo ambientale (ENV SIPs), rivolto tipicamente a enti pubblici, autorità nazionali o grandi organizzazioni, non a PMI. Una piccola impresa del Cilento non ha i requisiti strutturali né il profilo istituzionale per accedere direttamente a questo tipo di strumento LIFE.</t>
         </is>
       </c>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Technical Assistance preparation of SNaPs</t>
+          <t>technical Assistance preparation of CLIMA SIPs</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-NAT-SNAP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-CLIMA-SIP</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -8276,14 +8276,14 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 2027 per l'assistenza tecnica alla preparazione di SNaPs (Strategic Nature Plans) è destinato principalmente a enti pubblici, autorità nazionali e organizzazioni ambientali di scala nazionale, non a PMI. Una piccola impresa del Cilento non ha i requisiti tecnici né la dimensione istituzionale per candidarsi direttamente a questo tipo di strumento.</t>
+          <t>Il bando LIFE TA per la preparazione di CLIMA SIPs (Strategic Integrated Projects sul clima) è destinato principalmente a enti pubblici, autorità regionali o grandi organizzazioni con capacità di coordinamento istituzionale, non a PMI. Una piccola impresa del Cilento non ha né i requisiti soggettivi né le capacità amministrative per candidarsi come beneficiario diretto di assistenza tecnica di questa natura.</t>
         </is>
       </c>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Technical Assistance preparation of ENV SIPs</t>
+          <t>SSbD bio-based solutions for home and/or personal care</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -8293,17 +8293,17 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-ENV-SIP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-03</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -8318,19 +8318,19 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un bando LIFE per assistenza tecnica alla preparazione di Piani di Investimento Strategici Ambientali (SIPs), destinato principalmente a enti pubblici, autorità ambientali e grandi organizzazioni specializzate in policy ambientale europea, non a PMI operative. Una piccola impresa del Cilento non dispone tipicamente delle competenze istituzionali e della struttura necessarie per candidarsi come beneficiario diretto.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, consorzi internazionali e risorse progettuali difficilmente accessibili a una PMI di piccole dimensioni del Cilento, a meno che non operi specificamente nel settore chimico-verde o cosmetico con un dipartimento R&amp;D strutturato. Le soluzioni bio-based per cura della casa e della persona finanziate riguardano sviluppo scientifico ad alto contenuto tecnologico, lontano dal tessuto produttivo tipico dell'area.</t>
         </is>
       </c>
     </row>
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>technical Assistance preparation of CLIMA SIPs</t>
+          <t>Bio-based chemicals and/or materials from woody residues</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8340,17 +8340,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-CLIMA-SIP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-03</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -8365,19 +8365,19 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 2027 per l'assistenza tecnica alla preparazione di Strategic Integrated Projects (SIPs) sul clima è destinato principalmente a enti pubblici, autorità nazionali/regionali e grandi organizzazioni ambientali, non a PMI. Una piccola impresa del Cilento non ha né la struttura né i requisiti istituzionali per candidarsi come soggetto proponente in questo tipo di strumento europeo.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzi internazionali e investimenti significativi in R&amp;D difficilmente sostenibili da una PMI del Cilento; tuttavia, aziende del territorio attive nella filiera forestale o agricola (es. trasformazione di scarti legnosi di oliveti o castagneti) potrebbero partecipare come partner industriali di un consorzio guidato da un ente di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SSbD bio-based solutions for home and/or personal care</t>
+          <t>Develop breakthrough and sustainable bio-based textile fibres</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-03</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8417,14 +8417,14 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzi internazionali e competenze in chimica verde e bio-based, barriere difficilmente superabili per una PMI del Cilento senza un solido track record in R&amp;D europeo. Una piccola impresa locale potrebbe partecipare solo come partner junior in un consorzio guidato da università o grandi aziende del settore care.</t>
+          <t>Il bando Horizon richiede attività di ricerca di frontiera su fibre tessili bio-based, con consorzialità internazionale e capacità R&amp;D elevate tipiche di grandi imprese o università; una PMI campana, anche del distretto tessile, difficilmente possiede le competenze tecnico-scientifiche e le risorse amministrative per partecipare autonomamente o come partner capofila. Il Cilento non presenta filiere tessili strutturate che rendano il bando territorialmente rilevante.</t>
         </is>
       </c>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Bio-based chemicals and/or materials from woody residues</t>
+          <t>High-performance, circular-by-design, bio-based thermosets</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-04</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8464,14 +8464,14 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede attività di ricerca e sviluppo ad alto contenuto tecnologico sulla valorizzazione di residui legnosi in prodotti chimici e materiali bio-based, con budget elevati e necessità di consorzio europeo, rendendo l'accesso diretto molto difficile per una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo come partner in un consorzio internazionale, apportando competenze specifiche nella filiera forestale o agroalimentare locale.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata su materiali bio-based e termoindurenti circolari, tipicamente accessibile solo a grandi imprese o centri di ricerca con competenze specialistiche; una PMI campana del Cilento difficilmente dispone delle risorse tecniche e del partenariato internazionale necessari per competere, salvo ruolo di partner industriale in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Develop breakthrough and sustainable bio-based textile fibres</t>
+          <t>Bio-based additives as alternatives to unlock and increase recyclability and/or biodegradability</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-02</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europa richiede progetti di ricerca breakthrough su fibre tessili bio-based, con consorzî internazionali e capacità di R&amp;D avanzata difficilmente compatibili con una PMI di piccola dimensione del Cilento. L'accesso è praticabile solo come partner junior in un consorzio europeo, con competenze specifiche nel settore biotessile o biomateriali.</t>
+          <t>Il bando Horizon UE richiede attività di ricerca avanzata su additivi bio-based per migliorare riciclabilità e biodegradabilità dei materiali, con budget elevati e necessità di consorzi internazionali, rendendo l'accesso molto complesso per una PMI del Cilento senza struttura R&amp;D dedicata. Può essere rilevante solo se la PMI opera nel settore chimico, packaging o materiali avanzati ed è già inserita in reti di ricerca europee.</t>
         </is>
       </c>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>High-performance, circular-by-design, bio-based thermosets</t>
+          <t>SSbD bio-based alternatives for fertilising and/or crop protection products</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-02</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -8553,19 +8553,19 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede attività di ricerca avanzata su materiali biobasati e termoindurenti circolari, con consorzio internazionale e capacità R&amp;D strutturata che difficilmente una PMI campana di piccola dimensione possiede autonomamente. Il Cilento non presenta un tessuto industriale chimico-manifatturiero allineato a questo specifico ambito tecnologico, rendendo l'accesso concreto molto limitato salvo partecipazione come partner secondario in progetti già strutturati.</t>
+          <t>Il bando Horizon UE richiede consorzi di ricerca internazionali con elevata capacità tecnico-scientifica e budget di progetto nell'ordine di milioni di euro, rendendo l'accesso diretto estremamente difficile per una PMI del Cilento senza partnership con università o centri di ricerca. Pur essendo tematicamente rilevante per aziende agricole locali interessate a fertilizzanti e prodotti fitosanitari bio-based, una piccola impresa campana potrebbe al massimo partecipare come partner secondario in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Bio-based additives as alternatives to unlock and increase recyclability and/or biodegradability</t>
+          <t>Addressing separation and purification challenges in biorefineries</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-01</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -8605,14 +8605,14 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzi internazionali e competenze specifiche in chimica dei materiali bio-based, rendendo l'accesso diretto estremamente difficile per una PMI campana di piccola dimensione senza un partner universitario o un laboratorio R&amp;D strutturato. Una PMI del Cilento potrebbe partecipare solo come partner junior in un consorzio europeo, con ruolo marginale e bassa probabilità di ottenere finanziamenti significativi.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata in bioraffinerie e processi di separazione/purificazione, con consorzî internazionali e investimenti ingenti, difficilmente accessibili a una PMI del Cilento priva di strutture R&amp;D dedicate. Potrebbe risultare marginalmente rilevante solo per PMI già inserite in reti di ricerca o con competenze specifiche in biotecnologie industriali.</t>
         </is>
       </c>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Addressing separation and purification challenges in biorefineries</t>
+          <t>SSbD bio-based polymers from alternative sources</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-02</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8652,14 +8652,14 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede capacità di ricerca avanzata in bioraffinerie e processi di separazione/purificazione, con consorzî internazionali e competenze scientifiche difficilmente accessibili a una PMI campana di piccola dimensione, specialmente nel Cilento dove il tessuto produttivo è prevalentemente agricolo e turistico. Le PMI del territorio potrebbero partecipare solo come partner secondari di grandi enti di ricerca, con ruolo marginale e oneri amministrativi elevati.</t>
+          <t>Il bando Horizon Europe richiede consorzi internazionali, capacità di ricerca avanzata e budget elevati, strutturalmente inadatti a una PMI di piccole dimensioni del Cilento senza esperienza pregressa in progetti europei di ricerca sui polimeri bio-based. Una PMI campana potrebbe partecipare solo come partner junior in un consorzio già formato, ruolo difficile da ottenere senza reti consolidate nel settore.</t>
         </is>
       </c>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>SSbD bio-based polymers from alternative sources</t>
+          <t>Supporting industry in the switch to sustainable and circular bio-based products and processes</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-CSA-01</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -8699,14 +8699,14 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata, consorzi internazionali e competenze specifiche in chimica dei polimeri bio-based, strutture tipicamente fuori dalla portata di una PMI del Cilento senza un solido track record europeo. Le PMI campane del settore potrebbero partecipare solo come partner junior in consorzi guidati da grandi centri di ricerca, con ruoli marginali e oneri burocratici molto elevati.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca e sviluppo avanzate, consorzio europeo e risorse amministrative difficilmente sostenibili da una PMI di piccola dimensione nel Cilento; il focus su processi bio-based industriali è lontano dal tessuto produttivo locale, prevalentemente orientato ad agricoltura tradizionale, turismo e artigianato.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Supporting industry in the switch to sustainable and circular bio-based products and processes</t>
+          <t>Films and coatings for circular packaging</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-CSA-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-05</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8746,14 +8746,14 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo richiede capacità di ricerca e sviluppo avanzate, consorzio internazionale e risorse amministrative che difficilmente una PMI del Cilento può sostenere autonomamente; è accessibile solo in qualità di partner junior in progetti guidati da grandi enti di ricerca. Il focus su prodotti e processi bio-based potrebbe in teoria coinvolgere aziende agricole o agroalimentari del territorio, ma le barriere di accesso restano molto elevate.</t>
+          <t>Il bando Horizon UE richiede attività di ricerca e sviluppo ad alto contenuto tecnologico su film e rivestimenti per imballaggi circolari, con consorzio internazionale e capacità di R&amp;D difficilmente accessibili a una PMI di piccola dimensione del Cilento. Le risorse necessarie in termini di competenze tecniche, partner europei e budget di progetto rendono questo bando sostanzialmente inaccessibile senza una struttura dedicata all'innovazione.</t>
         </is>
       </c>
     </row>
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Films and coatings for circular packaging</t>
+          <t>Biotech routes for valorisation of residual biomass</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-01</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca e sviluppo avanzate su materiali per imballaggi circolari, con consorzialità internazionale e risorse progettuali difficilmente accessibili a una PMI di piccola dimensione del Cilento. Salvo che l'azienda operi nel settore packaging o chimica dei materiali con un dipartimento R&amp;S strutturato, le barriere di accesso (consorzio europeo, rendicontazione complessa, competenze tecniche specialistiche) rendono questo bando poco praticabile.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzi internazionali e competenze biotecnologiche difficilmente accessibili a una PMI di piccola dimensione del Cilento; le PMI del territorio potrebbero partecipare solo come partner secondari in progetti guidati da università o grandi centri di ricerca, con oneri burocratici e finanziari molto elevati.</t>
         </is>
       </c>
     </row>
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Biotech routes for valorisation of residual biomass</t>
+          <t>Boosting biorefinery competitiveness through biotech</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-01</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8840,14 +8840,14 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzi internazionali e competenze biotech difficilmente accessibili a una PMI di piccola dimensione del Cilento; le spese finanziabili (R&amp;S, personale scientifico, infrastrutture di laboratorio) presuppongono strutture organizzative e finanziarie tipiche di grandi imprese o spin-off universitari. Una PMI del territorio potrebbe partecipare solo come partner minore in un consorzio guidato da enti di ricerca, con ruolo e budget marginali.</t>
+          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata in biotecnologie e bioraffinerie, con requisiti di consorzio internazionale e competenze scientifiche difficilmente accessibili a una PMI di piccola dimensione del Cilento. Il settore agricolo-forestale locale potrebbe in teoria fornire biomasse, ma il bando è orientato a grandi player industriali e centri di ricerca, non a realtà produttive locali.</t>
         </is>
       </c>
     </row>
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Boosting biorefinery competitiveness through biotech</t>
+          <t>Diversification of nutritional food ingredient sources for increased EU resilience and strategic autonomy</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-04</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8887,14 +8887,14 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla bioraffineria richiede capacità di ricerca avanzata, consorzi internazionali e investimenti elevati, barriere difficilmente superabili per una PMI del Cilento. Solo realtà già inserite in reti di ricerca biotech o con competenze specifiche in biomasse e biotecnologie industriali potrebbero partecipare come partner secondari.</t>
+          <t>Il bando Horizon richiede consorzi transnazionali con forte componente di ricerca applicata e budget elevati, strutture difficilmente accessibili per una PMI campana di piccole dimensioni senza un partner universitario o un grande integratore. Una PMI del Cilento attiva nell'agroalimentare (es. trasformazione di legumi, cereali antichi o prodotti tipici) potrebbe partecipare solo come partner minoritario in un consorzio già formato, non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Diversification of nutritional food ingredient sources for increased EU resilience and strategic autonomy</t>
+          <t>LIFE Operating Grants</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -8904,17 +8904,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-SGA</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -8929,39 +8929,39 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede consorzi internazionali e capacità di ricerca avanzata difficilmente accessibili a una PMI di piccole dimensioni del Cilento; tuttavia, un'azienda agroalimentare locale specializzata in ingredienti tipici (es. fichi, legumi, oli) potrebbe partecipare come partner industriale in un consorzio guidato da un ente di ricerca, contribuendo alla diversificazione delle fonti di ingredienti nutrizionali.</t>
+          <t>I LIFE Operating Grants sono destinati a organizzazioni non governative e enti no-profit attivi nella tutela ambientale e climatica, non a PMI commerciali; una piccola impresa del Cilento non rientra tra i beneficiari eleggibili e non può accedere direttamente a questo strumento di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>LIFE Operating Grants</t>
+          <t>Leveraging long-term field experiments and other datasets to develop AI-ready decision support systems for sustainable soil management</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-SGA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-04</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -8976,19 +8976,19 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>I LIFE Operating Grants sono destinati esclusivamente a organizzazioni non governative attive nella tutela ambientale e climatica, non a PMI commerciali; una piccola impresa del Cilento non rientra tra i beneficiari ammissibili e non può accedere a questo strumento per finanziare attività produttive o investimenti aziendali.</t>
+          <t>Il bando Horizon richiede la costruzione di consorzi di ricerca internazionali e competenze altamente specializzate in AI e gestione del suolo, strutture tipicamente lontane dalle capacità operative di una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario affiancando università o centri di ricerca, ma difficilmente come capofila o beneficiario diretto delle risorse.</t>
         </is>
       </c>
     </row>
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Leveraging long-term field experiments and other datasets to develop AI-ready decision support systems for sustainable soil management</t>
+          <t>Enabling user-centred and open innovation initiatives to enhance soil health in Ukraine</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-03</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9028,14 +9028,14 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la costruzione di consorzi di ricerca internazionali e competenze avanzate in AI e sperimentazione agronomica di lungo periodo, barriere difficilmente superabili per una PMI campana del Cilento senza un partner universitario o un centro di ricerca già strutturato. Le spese finanziabili riguardano sviluppo di sistemi di supporto decisionale AI per la gestione sostenibile del suolo, ambito altamente specialistico che esclude di fatto imprese agricole o agroindustriali di piccola dimensione come beneficiari diretti.</t>
+          <t>Il bando si concentra sulla salute del suolo in Ucraina nell'ambito del programma Horizon, richiedendo capacità di ricerca avanzata e partnership internazionali difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento, pur operando in ambito agricolo, non dispone tipicamente delle strutture progettuali e dei requisiti consortili richiesti da questo tipo di call europea.</t>
         </is>
       </c>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Enabling user-centred and open innovation initiatives to enhance soil health in Ukraine</t>
+          <t>Antimicrobial resistance and antibiotic biosynthesis in soils: developing key understanding and counteractive strategies using a One-Health approach</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-02</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9070,19 +9070,19 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la salute del suolo in Ucraina e richiede consorzi di ricerca internazionali con elevata capacità progettuale, rendendo l'accesso diretto di una PMI campana estremamente difficile senza un partner coordinatore. Il focus geografico sull'Ucraina esclude ricadute immediate sul territorio del Cilento o su attività agricole locali.</t>
+          <t>Il bando Horizon focalizzato sulla resistenza antimicrobica e biosintesi di antibiotici nel suolo richiede capacità di ricerca scientifica avanzata, partnership internazionali e strutture di laboratorio difficilmente disponibili in una PMI del Cilento; le risorse finanziabili riguardano attività di R&amp;S ad alto contenuto scientifico che presuppongono competenze specialistiche non tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Antimicrobial resistance and antibiotic biosynthesis in soils: developing key understanding and counteractive strategies using a One-Health approach</t>
+          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-01</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla resistenza antimicrobica nei suoli richiede capacità di ricerca scientifica avanzata e partnership internazionali tipiche di enti universitari o grandi laboratori, rendendo l'accesso diretto da parte di una PMI del Cilento estremamente difficile senza un consorzio strutturato. Solo PMI specializzate in biotecnologie, microbiologia agraria o diagnostica ambientale potrebbero partecipare come partner secondari, ma non come capofila.</t>
+          <t>Il bando Horizon è orientato a consorzi di ricerca e istituzioni accademiche per sviluppare metodologie di monitoraggio della salute del suolo, rendendo difficile la partecipazione diretta di una PMI senza un partenariato strutturato con enti di ricerca. Una PMI agricola del Cilento potrebbe avere interesse indiretto solo come partner associato in progetti legati alla viticoltura o olivicoltura tipica del territorio, ma i costi di gestione progettuale e i requisiti consortili lo rendono poco accessibile in autonomia.</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sui 'beni comuni globali' è orientato a consorzi di ricerca accademica e grandi enti internazionali, con requisiti di partnership transnazionale e capacità di ricerca scientifica difficilmente compatibili con una PMI del Cilento. Le tematiche di governance ambientale globale non trovano applicazione diretta nelle attività produttive tipiche del territorio.</t>
+          <t>Il bando Horizon Europe sulla governance dei beni comuni globali è orientato a grandi consorzi di ricerca accademica e istituzionale, con requisiti di partnership internazionale e capacità progettuali elevate difficilmente accessibili a una PMI del Cilento. Non sono previste spese tipicamente rilevanti per una piccola impresa locale né settori produttivi specifici del territorio campano.</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla long-term care policy è orientato a enti di ricerca, università e consorzi pubblici per analisi delle politiche demografiche europee, rendendo l'accesso diretto per una PMI campana estremamente difficile senza un ruolo marginale in un consorzio. Una PMI del Cilento, anche operante nel settore socio-sanitario o dell'assistenza agli anziani, difficilmente avrebbe il profilo tecnico-scientifico richiesto per guidare o co-finanziare un progetto di questa natura.</t>
+          <t>Il bando Horizon Europe sulla long-term care policy è orientato a consorzi di ricerca accademici e istituzionali a livello europeo, con requisiti di partenariato transnazionale complessi e budget elevati difficilmente gestibili da una PMI del Cilento. Una piccola impresa campana potrebbe al massimo partecipare come partner secondario in un consorzio, ma difficilmente come soggetto capofila o beneficiario diretto.</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca accademica sulla trasformazione della pubblica amministrazione e della funzione pubblica, un ambito riservato a enti di ricerca, università e istituzioni governative. Una PMI campana, anche del Cilento, non ha profilo né struttura per partecipare a questo tipo di progetto europeo.</t>
+          <t>Il bando Horizon è focalizzato sulla ricerca accademica e istituzionale relativa alla trasformazione della pubblica amministrazione e alla formazione della dirigenza pubblica, settori nei quali una PMI campana, incluse quelle del Cilento, non rientra tra i beneficiari tipici né può facilmente partecipare come soggetto capofila. L'accesso richiederebbe una partnership con enti di ricerca o università, rendendo il coinvolgimento della PMI marginale e poco remunerativo.</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a startup creative ad alto potenziale di innovazione dirompente, con requisiti di ricerca e sviluppo che difficilmente si adattano a una PMI tradizionale del Cilento. La complessità progettuale, la necessità di partnership europee e i criteri di valutazione tecnico-scientifici rendono l'accesso poco praticabile senza un consorzio strutturato o un ente di ricerca come partner.</t>
+          <t>Il bando Horizon europeo è orientato a startup creative con vocazione disruptiva e richiede capacità di ricerca e sviluppo, partnership internazionali e strutture progettuali complesse, difficilmente compatibili con le dimensioni e le risorse tipiche di una PMI del Cilento. L'accesso diretto a fondi Horizon è generalmente precluso alle micro e piccole imprese senza un consorzio strutturato con enti di ricerca.</t>
         </is>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si concentra su ricerca accademica e policy sulla violenza di genere contro donne politicamente attive e persone LGBTIQ+, richiedendo consorzi internazionali con capacità di ricerca avanzata. Una PMI del Cilento non ha i requisiti né il profilo tematico per partecipare utilmente a questo tipo di progetto.</t>
+          <t>Il bando Horizon è orientato a consorzi di ricerca, università e organizzazioni del terzo settore specializzate in studi di genere e diritti LGBTIQ+, con requisiti tecnici e amministrativi difficilmente soddisfabili da una PMI del Cilento. Non finanzia attività produttive o servizi tipici delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda l'implementazione del Patto UE su Migrazione e Asilo, con focus su inclusione, integrazione e salute: temi rivolti principalmente a enti pubblici, ONG e centri di ricerca. Una PMI del Cilento non ha quasi possibilità di accesso diretto né ricade nei settori produttivi tipici del territorio come turismo, agricoltura o agroalimentare.</t>
+          <t>Il bando Horizon si focalizza su politiche migratorie europee, inclusione e salute dei migranti, ambiti tipicamente riservati a enti pubblici, università e grandi organizzazioni no-profit. Una PMI del Cilento difficilmente possiede i requisiti progettuali, la capacità di rendicontazione europea e i partner transnazionali richiesti da questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sul contrasto al traffico illecito di beni culturali è orientato a consorzi di ricerca, università e istituzioni pubbliche, rendendo l'accesso diretto per una PMI del Cilento estremamente complesso senza un partenariato strutturato. Anche in caso di partecipazione come partner, le attività finanziabili (ricerca, sviluppo tecnologico, analisi forensi) difficilmente rientrano nel core business di una piccola impresa locale.</t>
+          <t>Il bando Horizon UE sul contrasto al traffico illecito di beni culturali è orientato a consorzi di ricerca, università e istituzioni pubbliche, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un ruolo marginale in un partenariato più ampio. Pur essendo il Cilento un'area ricca di patrimonio archeologico (es. Paestum, Velia), le attività finanziabili riguardano ricerca scientifica e cooperazione istituzionale, non servizi o prodotti commerciali tipici di una PMI locale.</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulla democrazia locale in paesi a basso reddito è destinato a enti di ricerca e università, non a PMI campane. Non prevede spese finanziabili rilevanti per imprese del Cilento né attività commerciali o produttive.</t>
+          <t>Il bando Horizon finanzia ricerca accademica sulla democrazia locale nei paesi a basso reddito, un ambito completamente estraneo alle attività tipiche di una PMI campana o cilentana. Non prevede spese finanziabili né settori beneficiari rilevanti per imprese di piccola o media dimensione operanti in ambiti produttivi, turistici o agricoli.</t>
         </is>
       </c>
     </row>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon mira a integrare ricerca umanistica/sociale con ricerca STEM a livello europeo, richiedendo consorzi internazionali e capacità di ricerca avanzata difficilmente gestibili da una PMI del Cilento senza un forte partenariato con università o centri di ricerca. Le PMI di piccola dimensione non sono il target primario e i requisiti progettuali superano le capacità operative tipiche di queste realtà.</t>
+          <t>Il bando Horizon europeo promuove l'integrazione tra scienze sociali/umanistiche e STEM in progetti di ricerca su scala UE, richiedendo consorzi internazionali e capacità di ricerca strutturata difficilmente compatibili con una PMI del Cilento. Le spese finanziabili riguardano attività di R&amp;S avanzata, non operative o produttive, rendendo l'accesso diretto praticamente inaccessibile senza partnership con università o centri di ricerca.</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un bando Horizon EU focalizzato su ricerca accademica e policy europee sul modello sociale e la competitività, orientato a consorzi di ricerca e grandi istituzioni. Una PMI del Cilento avrebbe difficoltà ad accedere autonomamente, mancando dei requisiti di partnership internazionale e capacità di ricerca richieste da questo tipo di call.</t>
+          <t>Il bando Horizon Europe è orientato a consorzi di ricerca accademica e grandi organizzazioni, con requisiti di partnership transnazionale e capacità di ricerca avanzata difficilmente accessibili a una PMI del Cilento. Le spese finanziabili riguardano attività di ricerca su modelli sociali e competitività su scala europea, lontane dalle esigenze operative di una piccola impresa locale.</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sul supporto alla democrazia post-conflitto e alla ricostruzione è destinato principalmente a enti di ricerca, università e organizzazioni internazionali, con tematiche geopolitiche lontane dal tessuto produttivo di una PMI campana o cilentana. Non sono previste spese finanziabili rilevanti per attività imprenditoriali ordinarie né settori merceologici tipici delle PMI locali.</t>
+          <t>Il bando Horizon focalizzato su democrazia post-conflitto e ricostruzione è orientato a enti di ricerca, università e organizzazioni internazionali, non a PMI operative in settori produttivi del Cilento. Non prevede tipologie di spesa o attività riconducibili all'operatività quotidiana di una piccola o media impresa campana.</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si focalizza sulla ricerca accademica e politiche pubbliche per contrastare la povertà infantile e migliorare l'accesso ai servizi educativi per la prima infanzia, con destinatari tipici quali università, enti di ricerca e organizzazioni no-profit. Una PMI campana, anche operante in settori educativi o sociali nel Cilento, difficilmente possiede i requisiti di capacità di ricerca e i partenariati transnazionali richiesti da Horizon per accedere concretamente ai finanziamenti.</t>
+          <t>Il bando Horizon è orientato a consorzi di ricerca, università e grandi organizzazioni del terzo settore impegnate in studi sulla povertà infantile e l'accesso all'educazione della prima infanzia: una PMI campana difficilmente possiede i requisiti tecnici e il profilo istituzionale richiesto per guidare o partecipare utilmente a progetti di questa natura. L'unica finestra di accesso per una piccola impresa sarebbe come partner specializzato in soluzioni educative o tecnologie per l'infanzia, ma il Cilento non presenta un tessuto imprenditoriale strutturato in questo settore.</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a enti di ricerca e università per studi sull'impatto degli strumenti digitali su salute mentale e rendimento scolastico, con requisiti progettuali e amministrativi difficilmente compatibili con una PMI del Cilento. Una piccola impresa potrebbe partecipare solo come partner in un consorzio guidato da istituti accademici, con un ruolo marginale e limitato accesso ai fondi.</t>
+          <t>Il bando Horizon è destinato principalmente a consorzi di ricerca accademica e istituti universitari per studi sull'impatto dei digital tool su salute mentale e rendimento scolastico, ambito lontano dalle attività tipiche di una PMI campana o cilentana. Una piccola impresa difficilmente possiede i requisiti tecnici e la capacità progettuale per competere in questo tipo di call europea ad alto contenuto scientifico.</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sulla salvaguardia della diversità linguistica è orientato a consorzi di ricerca accademica e istituti specializzati, con requisiti progettuali e burocratici difficilmente sostenibili da una PMI campana. Non finanzia attività produttive o commerciali tipiche delle piccole imprese del Cilento.</t>
+          <t>Il bando Horizon sulla diversità linguistica finanzia principalmente consorzi di ricerca accademica e istituti specializzati, con requisiti progettuali complessi e budget elevati difficilmente accessibili a una PMI del Cilento. Non prevede spese tipicamente sostenibili da piccole imprese locali né si rivolge a settori produttivi del territorio.</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla alfabetizzazione digitale e mediatica per la resilienza democratica è orientato a consorzi di ricerca, università e grandi organizzazioni, con procedure complesse e requisiti di partenariato internazionale difficilmente gestibili da una PMI del Cilento. Una piccola impresa campana non trova spazi diretti di finanziamento per attività produttive o commerciali concrete.</t>
+          <t>Il bando Horizon europeo sulla media literacy e resilienza democratica è orientato a consorzi di ricerca, università e grandi organizzazioni con capacità progettuali internazionali, rendendo l'accesso diretto di una PMI del Cilento estremamente difficile senza un ruolo da partner in un consorzio strutturato. Le PMI potrebbero partecipare solo come partner secondari in progetti guidati da enti di ricerca, con benefici indiretti e limitata autonomia gestionale dei fondi.</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sull'integrità elettorale in contesti digitali è destinato a enti di ricerca, università e consorzi specializzati in scienze politiche e cybersecurity, non a PMI generiche del Cilento. Le PMI campane di piccola dimensione non dispongono né dei requisiti tecnici né della capacità progettuale per competere in questo ambito di ricerca istituzionale europeo.</t>
+          <t>Il bando Horizon riguarda la ricerca accademica sull'integrità elettorale in contesti digitali, un tema altamente specialistico che richiede competenze in scienze politiche, cybersecurity avanzata e consorzi di ricerca internazionali, ben al di fuori del profilo tipico di una PMI campana o cilentana. Non sono previste attività finanziabili rilevanti per imprese locali di piccola dimensione operanti in settori produttivi tradizionali.</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Research and Innovation Network for a Union of Equality' è orientato principalmente a enti di ricerca, università e consorzi transnazionali, con requisiti di partnership complessi e capacità progettuali elevate difficilmente sostenibili da una PMI del Cilento senza un solido network europeo preesistente. Una piccola impresa campana potrebbe partecipare solo come partner secondario in un consorzio già strutturato, ruolo che richiede contatti internazionali e risorse amministrative raramente disponibili a livello locale.</t>
+          <t>Il bando Horizon focalizzato su ricerca e uguaglianza è orientato principalmente a università, enti di ricerca e grandi consorzi europei, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un partner accademico capofila. Le PMI possono partecipare solo in ruolo subordinato all'interno di reti di ricerca complesse, con oneri amministrativi e rendicontativi sproporzionati rispetto alle capacità strutturali di una piccola impresa.</t>
         </is>
       </c>
     </row>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sull'integrazione dell'AI nei processi CCSI (Customer Care e Servizi alle Imprese) richiede tipicamente consorzi internazionali, capacità di ricerca avanzata e una struttura amministrativa complessa, requisiti difficilmente soddisfabili da una PMI del Cilento senza partnership con enti di ricerca. L'accesso diretto è ostacolato dall'elevata competizione europea e dalla necessità di cofinanziamento e rendicontazione specializzata.</t>
+          <t>Il bando Horizon UE sull'integrazione dell'AI nei settori CCSI (Cultural, Creative and Social Innovation) richiede partnership internazionali, capacità di rendicontazione europea e una struttura progettuale complessa, difficilmente accessibile per una PMI di piccola dimensione del Cilento senza un consorzio già strutturato. Una PMI potrebbe partecipare solo come partner junior in un consorzio guidato da università o grandi organizzazioni, con ruolo marginale e benefici limitati.</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi di ricerca internazionali con elevata capacità progettuale e scientifica, rendendo l'accesso diretto molto difficile per una PMI del Cilento. Il focus su AI generativa e diritti d'autore nei contenuti culturali è lontano dalle attività produttive tipiche delle PMI campane di piccola dimensione.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzio internazionale e competenze specifiche sull'IA generativa nel settore culturale-creativo, requisiti difficilmente sostenibili da una PMI del Cilento senza un solido network europeo e struttura dedicata alla R&amp;S. Una PMI locale potrebbe partecipare solo come partner junior in un consorzio guidato da università o grandi organizzazioni, con ruolo marginale e bassa probabilità di successo autonomo.</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a consorzi di ricerca e università che sviluppano progetti su scala europea sull'uso delle arti per l'innovazione e le soft skills: una PMI del Cilento difficilmente può accedere in modo diretto senza essere parte di un partenariato internazionale strutturato. L'onere gestionale e la complessità rendicontativa di Horizon rendono questo strumento poco praticabile per realtà di piccola dimensione senza un ente capofila accademico o un centro di ricerca come partner.</t>
+          <t>Il bando Horizon richiede la partecipazione in consorzi internazionali con forte componente di ricerca, strutture gestionali complesse e capacità di rendicontazione europea difficilmente sostenibili da una PMI del Cilento senza un partner accademico o una rete già consolidata. Il focus sull'uso delle arti per sviluppare soft skills e innovazione è settorialmente distante dalle filiere produttive prevalenti nell'area (agroalimentare, turismo, artigianato).</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla cittadinanza attiva e l'apprendimento permanente è orientato principalmente a enti di ricerca, università e organizzazioni no-profit, con requisiti di consorzio transnazionale e capacità progettuali complesse difficilmente gestibili da una PMI del Cilento. Le spese finanziabili riguardano ricerca applicata e sviluppo di metodologie educative, ambiti lontani dall'operatività tipica di una piccola impresa campana.</t>
+          <t>Il bando Horizon europeo sulla cittadinanza attiva e l'apprendimento permanente è orientato a consorzi di ricerca, università e organizzazioni del terzo settore, rendendo l'accesso diretto per una PMI campana molto complesso e improbabile senza un ruolo marginale in partenariato. Le PMI del Cilento, tipicamente operanti in turismo, agricoltura o artigianato, non trovano in questo bando un'applicazione concreta alle proprie attività produttive.</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo è orientato a grandi consorzi di ricerca e università per sviluppare competenze legate alla transizione verde, con requisiti progettuali e capacità amministrative difficilmente compatibili con una PMI di piccola dimensione del Cilento. Le PMI possono partecipare solo come partner in consorzi strutturati, rendendo l'accesso diretto praticamente impraticabile senza un capofila istituzionale.</t>
+          <t>Il bando Horizon europeo sulla transizione verde è orientato a enti di ricerca, università e grandi consorzi internazionali, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un partenariato strutturato. Una piccola impresa campana potrebbe partecipare solo come partner secondario in progetti coordinati da soggetti accademici, con oneri amministrativi e competitivi sproporzionati rispetto alle capacità tipiche di una PMI locale.</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a politiche sistemiche per attrarre talenti internazionali nell'UE, destinato tipicamente a università, enti di ricerca e grandi organizzazioni, non a PMI. Una piccola impresa del Cilento non ha le capacità strutturali né il profilo istituzionale per competere in questo tipo di progetto europeo complesso.</t>
+          <t>Il bando Horizon è orientato a politiche sistemiche per attrarre talenti internazionali nell'UE, con destinatari tipici come università, centri di ricerca e grandi consorzi istituzionali, rendendo di fatto inaccessibile la partecipazione diretta a una PMI del Cilento. Non finanzia attività aziendali concrete come assunzioni, tirocini o formazione interna, ma progetti di ricerca e policy su scala europea.</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla contribuzione delle competenze di base alla produttività è orientato a enti di ricerca, università e grandi consorzi, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un partner accademico strutturato. Una piccola impresa campana avrebbe margini di partecipazione solo come partner secondario in un consorzio internazionale, con oneri amministrativi e competitivi sproporzionati rispetto alle proprie capacità.</t>
+          <t>Il bando Horizon Europe sulla contribuzione delle competenze di base a produttività e innovazione è orientato principalmente a enti di ricerca, università e consorzi accademici, rendendo l'accesso diretto per una PMI campana del Cilento molto difficile senza un partenariato strutturato. Una PMI potrebbe partecipare solo come partner secondario in un consorzio europeo, con costi organizzativi elevati e ritorni incerti rispetto a strumenti più accessibili.</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Sustainable paths to media viability' è indirizzato a organizzazioni media, editori e istituti di ricerca europei per sviluppare modelli di sostenibilità per il settore dell'informazione, escludendo di fatto le PMI generiche del Cilento non operanti nel comparto mediatico. La complessità progettuale Horizon e la necessità di partnership internazionali rendono questo bando praticamente inaccessibile per una piccola impresa campana non specializzata nel settore dei media.</t>
+          <t>Il bando Horizon 'Sustainable paths to media viability' è destinato a organizzazioni del settore mediatico e della ricerca per sviluppare modelli di sostenibilità economica per i media: difficilmente accessibile per una PMI generica del Cilento, che non opera tipicamente nel comparto editoriale o giornalistico. I requisiti di consorzio internazionale e le procedure Horizon lo rendono ulteriormente complesso per realtà di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe per il Digital Twin Ocean è orientato a consorzi di ricerca e grandi enti tecnico-scientifici per sviluppare gemelli digitali degli oceani e mari regionali: richiede capacità di R&amp;D avanzata, infrastrutture tecnologiche e partnership internazionali difficilmente accessibili a una PMI del Cilento. Una piccola impresa locale potrebbe partecipare solo in qualità di partner minore in un consorzio già strutturato, ma non come beneficiario diretto o capofila.</t>
+          <t>Il bando Horizon Europe per il Digital Twin Ocean è orientato a grandi consorzi di ricerca e istituti scientifici per sviluppare infrastrutture digitali marine su scala europea, rendendo l'accesso diretto per una PMI campana molto difficile senza un ruolo marginale in un consorzio internazionale. Una PMI del Cilento potrebbe al massimo partecipare come partner tecnologico o fornitore di dati marini locali, ma i costi di partecipazione e la complessità progettuale superano le capacità tipiche di una piccola impresa.</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede consorzi internazionali, capacità di ricerca avanzata e budget elevati, rendendo l'accesso diretto molto difficile per una PMI campana di piccole dimensioni; una PMI del Cilento potrebbe partecipare solo in qualità di partner tecnico specializzato in soluzioni per la tutela delle acque costiere o della biodiversità marina, ma difficilmente come capofila.</t>
+          <t>Il bando Horizon EU richiede consorzi internazionali di ricerca con elevata capacità scientifica e progettuale, strutture difficilmente accessibili per una PMI del Cilento senza partnership con università o centri di ricerca. Tuttavia, una PMI operante in acquacoltura, pesca o tutela ambientale marina potrebbe partecipare come partner tecnico in un consorzio guidato da enti di ricerca, contribuendo con soluzioni pratiche per la riduzione dell'inquinamento idrico e la biodiversità costiera.</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzio internazionale e competenze specialistiche in mappatura degli habitat marini, struttura tipicamente accessibile solo a centri di ricerca o grandi imprese con dipartimenti R&amp;D dedicati. Una PMI del Cilento potrebbe partecipare solo come partner minore in un consorzio già formato, con ruolo marginale e difficoltà gestionali legate alla rendicontazione Horizon.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzio internazionale e competenze tecniche specializzate nella mappatura di habitat marini su larga scala, requisiti difficilmente compatibili con una PMI campana di piccole dimensioni. Anche le PMI del Cilento operanti nel settore marittimo o ambientale potrebbero partecipare solo come partner junior di grandi consorzi, con ruolo marginale e bassa probabilità di successo autonomo.</t>
         </is>
       </c>
     </row>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon mira a costruire una rete europea di siti di test per tecnologie oceaniche, richiedendo capacità di ricerca avanzata, infrastrutture marine certificate e partenariati internazionali consolidati: requisiti difficilmente soddisfabili da una PMI campana di piccole dimensioni. Anche se il Cilento ha costa tirrenica, la complessità tecnica e amministrativa di un progetto Horizon di questo tipo lo rende accessibile quasi esclusivamente a grandi enti di ricerca o consorzi specializzati nel settore marittimo-tecnologico.</t>
+          <t>Il bando Horizon richiede la creazione di reti europee per siti di test di tecnologie oceaniche, con requisiti consortili complessi e capacità tecniche avanzate difficilmente accessibili a una PMI campana di piccole dimensioni. Sebbene il Cilento sia area costiera con potenziale interesse per tecnologie marine, la natura del progetto (infrastrutture di testing su scala europea) lo rende di fatto inaccessibile senza partnership con grandi enti di ricerca o istituzioni accademiche internazionali.</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede la partecipazione in consorzi internazionali di ricerca con elevate capacità tecniche e amministrative, strutture difficilmente accessibili per una PMI del Cilento senza un partner universitario o un centro di ricerca capofila. Pur essendo il territorio del Cilento esposto a rischi idrogeologici e climatici rilevanti, la complessità progettuale e i requisiti di rendicontazione Horizon lo rendono di fatto inaccessibile a una PMI autonomamente.</t>
+          <t>Il bando Horizon richiede la partecipazione in consorzi internazionali con forte componente di ricerca scientifica su gestione del rischio disastri e adattamento climatico, struttura tipicamente adatta a enti di ricerca e grandi imprese. Una PMI del Cilento potrebbe essere coinvolta solo come partner secondario in un progetto già strutturato, con elevati oneri burocratici e nessuna garanzia di accesso diretto ai finanziamenti.</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a enti di ricerca, autorità pubbliche e grandi consorzi che sviluppano modelli finanziari per l'adattamento climatico locale, non a PMI come beneficiarie dirette. Una piccola impresa del Cilento non ha le capacità progettuali né il profilo richiesto per partecipare autonomamente a questo tipo di call.</t>
+          <t>Il bando Horizon si rivolge principalmente a enti di ricerca, istituzioni finanziarie e autorità pubbliche per sviluppare strumenti finanziari misti (pubblico-privato) per l'adattamento climatico locale, non a PMI come beneficiarie dirette. Una piccola impresa del Cilento non avrebbe né i requisiti tecnici né la capacità progettuale per candidarsi autonomamente a questo tipo di call.</t>
         </is>
       </c>
     </row>
@@ -10621,12 +10621,12 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe è orientato a consorzi di ricerca, enti pubblici e grandi organizzazioni con capacità di gestione progettuale europea; una PMI del Cilento potrebbe partecipare solo come partner secondario in un consorzio già strutturato, rendendo l'accesso diretto sostanzialmente impraticabile senza un lead partner accademico o istituzionale.</t>
+          <t>Il bando Horizon europeo per l'adattamento climatico delle regioni è orientato a consorzi di ricerca, enti pubblici e grandi organizzazioni, con requisiti di partnership transnazionale complessi e budget elevati difficilmente gestibili da una PMI. Una piccola impresa del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio guidato da un'università o ente locale, senza accesso diretto ai finanziamenti principali.</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a grandi consorzi di ricerca e enti pubblici per la resilienza climatica di vie navigabili interne, un tema scarsamente rilevante per il territorio del Cilento (prevalentemente costiero e montano, privo di significative vie d'acqua navigabili). Una PMI campana avrebbe difficoltà oggettive di accesso per la complessità progettuale e la necessità di partnership internazionali strutturate.</t>
+          <t>Il bando Horizon EU riguarda la resilienza climatica delle vie navigabili interne e delle infrastrutture idriche correlate, un ambito molto specifico e lontano dal contesto del Cilento, territorio privo di vie navigabili rilevanti. Inoltre, i bandi Horizon sono tipicamente accessibili a consorzi di ricerca e grandi enti, rendendo la partecipazione diretta di una PMI campana di piccole dimensioni estremamente difficile senza un partenariato strutturato.</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzio internazionale e competenze tecniche specializzate sui servizi climatici, barriere difficilmente superabili per una PMI del Cilento senza un partner universitario o scientifico consolidato. L'unica opportunità concreta sarebbe partecipare come partner secondario in un consorzio europeo, ma i costi di accesso e la complessità progettuale rendono il bando poco praticabile per realtà di piccola dimensione.</t>
+          <t>Il bando Horizon richiede consorzi internazionali con forte componente di ricerca scientifica sui servizi climatici, rendendo l'accesso diretto da parte di una PMI del Cilento estremamente complesso senza partnership con enti di ricerca qualificati. Una piccola impresa potrebbe partecipare solo come partner secondario in un consorzio europeo già strutturato, con risorse e capacità di progettazione europea difficilmente disponibili a livello locale.</t>
         </is>
       </c>
     </row>
@@ -10767,14 +10767,14 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia hub istituzionali multi-livello per la governance dell'adattamento climatico, rivolto principalmente a enti pubblici, agenzie nazionali e consorzi di ricerca: una PMI del Cilento non ha i requisiti soggettivi né la struttura per candidarsi come capofila o partner rilevante. L'accesso indiretto come subappaltatore è teoricamente possibile ma estremamente marginale e incerto.</t>
+          <t>Il bando Horizon finanzia hub istituzionali per la governance multilivello sull'adattamento climatico, destinati principalmente a enti pubblici, agenzie nazionali e organizzazioni di ricerca: una PMI del Cilento non rientra tra i beneficiari diretti e difficilmente può candidarsi autonomamente. L'unico accesso possibile sarebbe come partner secondario in un consorzio guidato da istituzioni, scenario poco praticabile per una piccola impresa.</t>
         </is>
       </c>
     </row>
     <row r="220" ht="30" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Call Town Twinning 2026</t>
+          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -10784,17 +10784,17 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CITIZENS-TOWN-TT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-06-CLIMA-SOIL</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>UE - CERV</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -10809,19 +10809,19 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>Il programma CERV Town Twinning finanzia gemellaggi tra comuni europei e attività di cittadinanza attiva rivolte a enti locali e organizzazioni della società civile, non a imprese private. Una PMI del Cilento non rientra tra i beneficiari diretti ammissibili e non può presentare domanda in autonomia.</t>
+          <t>Il bando Horizon richiede la costruzione di consorzi internazionali e capacità di ricerca avanzata difficilmente accessibili a una PMI di piccole dimensioni; tuttavia, un'azienda agricola o agroalimentare del Cilento potrebbe partecipare come partner operativo in progetti dimostrativi sulla resilienza del suolo e la sicurezza alimentare, settori strategici per quest'area. La complessità burocratica e la necessità di cofinanziamento rendono questa opportunità più adatta a PMI strutturate con esperienza pregressa in progetti europei o in collaborazione con università/centri di ricerca campani.</t>
         </is>
       </c>
     </row>
     <row r="221" ht="30" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Transaction Costs Support for social finance intermediaries</t>
+          <t>Call Town Twinning 2026</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -10831,17 +10831,17 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESF-2026-AG-TCS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CITIZENS-TOWN-TT</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>UE - ESF</t>
+          <t>UE - CERV</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
@@ -10856,39 +10856,39 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>Credito/Finanza</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto a intermediari finanziari specializzati in finanza sociale (fondi di impatto, banche etiche, veicoli di investimento ESG), non a PMI dirette: una piccola impresa del Cilento non può candidarsi direttamente. L'unico beneficio indiretto potrebbe derivare dall'accesso futuro a strumenti finanziari agevolati creati grazie a questi intermediari, ma non c'è un vantaggio immediato e concreto per una PMI campana.</t>
+          <t>Il programma CERV Town Twinning finanzia gemellaggi tra comuni e attività di cittadinanza europea rivolte ad enti locali e organizzazioni della società civile, non a PMI. Una piccola impresa del Cilento non può accedere direttamente a questo bando, salvo partecipare come partner secondario in un progetto guidato da un Comune.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="30" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Hop-On Facility</t>
+          <t>Transaction Costs Support for social finance intermediaries</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-03-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESF-2026-AG-TCS</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ESF</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -10903,19 +10903,19 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Credito/Finanza</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>Il bando Hop-On Facility è destinato a enti di ricerca e istituti accademici che vogliono agganciarsi a progetti Horizon Europe già finanziati, non a PMI in quanto beneficiari diretti; una piccola impresa del Cilento difficilmente ha i requisiti tecnico-scientifici e la capacità amministrativa per accedere autonomamente a questo strumento europeo.</t>
+          <t>Il bando è destinato agli intermediari finanziari della finanza sociale (fondi, banche, cooperative di credito) che sostengono iniziative ad impatto sociale, non alle PMI in modo diretto. Una piccola impresa del Cilento non può candidarsi come beneficiaria principale, ma potrebbe indirettamente accedere a strumenti finanziari agevolati se opera nel settore dei servizi sociali o dell'economia sociale.</t>
         </is>
       </c>
     </row>
     <row r="223" ht="30" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Teaming Synergies</t>
+          <t>Hop-On Facility</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-01-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-03-WIDENING-01</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -10955,14 +10955,14 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>Teaming Synergies è uno strumento Horizon Europe pensato per creare o potenziare centri di eccellenza in ricerca e innovazione, richiedendo partnership istituzionali tra enti di ricerca e regioni, con budget multimilionari e governance complessa: una PMI del Cilento può partecipare solo come partner secondario in consorzi già strutturati, rendendo l'accesso diretto praticamente impraticabile senza un coordinamento con università o centri di ricerca campani.</t>
+          <t>Il programma Hop-On Facility è destinato a ricercatori e istituzioni di paesi con bassa partecipazione a Horizon Europe, non a PMI ordinarie: richiede un profilo altamente scientifico e un consorzio europeo già attivo. Una PMI del Cilento difficilmente soddisfa i requisiti di accesso senza un partner di ricerca qualificato e una base consolidata in progetti R&amp;S europei.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="30" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Research Management Facility</t>
+          <t>Teaming Synergies</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-04-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-01-WIDENING-01</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -11002,14 +11002,14 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>Il bando Research Management Facility di Horizon UE è orientato a strutture di gestione della ricerca istituzionale (università, enti pubblici, grandi organizzazioni R&amp;I) e non a PMI operative; una piccola impresa del Cilento difficilmente possiede i requisiti amministrativi e la capacità progettuale per accedere autonomamente a questo tipo di strumento.</t>
+          <t>Teaming Synergies è uno strumento Horizon Europe pensato per costruire o potenziare centri di eccellenza in ricerca e innovazione, richiedendo partnership istituzionali complesse tra università, enti di ricerca e regioni: una PMI del Cilento difficilmente può guidare o beneficiare direttamente di questo tipo di progetto, che richiede capacità amministrative e scientifiche di scala europea. Il bando è strutturalmente orientato a istituzioni pubbliche di ricerca, non a imprese di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="225" ht="30" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Call for proposals on the fight against corruption.</t>
+          <t>Research Management Facility</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -11019,17 +11019,17 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-CORRUPT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-04-WIDENING-01</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>UE - ISF</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
@@ -11049,34 +11049,34 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sulla lotta alla corruzione è destinato principalmente a enti pubblici, forze dell'ordine e organizzazioni specializzate nel settore della sicurezza e antifrode, non a PMI commerciali. Una piccola impresa del Cilento non rientra nei beneficiari tipici di questa tipologia di call europea.</t>
+          <t>Il bando Horizon 'Research Management Facility' è orientato a grandi strutture di ricerca e istituti accademici per potenziare la gestione amministrativa dei progetti R&amp;S, rendendo l'accesso estremamente complesso per una PMI del Cilento priva di un dipartimento dedicato alla ricerca. I requisiti di consorzio, la burocrazia europea e la necessità di competenze specifiche in project management scientifico lo rendono di fatto inaccessibile senza un partenariato strutturato con università o centri di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="226" ht="30" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Non-thematic development actions by SMEs</t>
+          <t>Call for proposals on the fight against corruption.</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DA-SME-NT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-CORRUPT</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>UE - EDF</t>
+          <t>UE - ISF</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
@@ -11096,14 +11096,14 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia azioni di sviluppo nel settore della difesa europea, richiedendo capacità tecnologiche avanzate, consorzio con partner europei e competenze in ambito militare/dual-use: requisiti difficilmente compatibili con una PMI del Cilento non specializzata in difesa o aerospazio. Le spese finanziabili riguardano R&amp;S su sistemi d'arma, tecnologie militari e prototipazione difensiva, settori estranei al tessuto produttivo locale.</t>
+          <t>Il bando ISF (Internal Security Fund) sulla lotta alla corruzione è destinato principalmente a enti pubblici, forze dell'ordine e organizzazioni no-profit specializzate in sicurezza e giustizia, non a PMI commerciali. Una piccola impresa del Cilento non rientra nei beneficiari tipici e non troverebbe finanziamenti per attività produttive o di sviluppo aziendale.</t>
         </is>
       </c>
     </row>
     <row r="227" ht="30" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>New abilities in over-the-horizon sensing</t>
+          <t>Non-thematic development actions by SMEs</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DA-DIS-OTHR</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DA-SME-NT</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -11143,14 +11143,14 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF 'New abilities in over-the-horizon sensing' finanzia ricerca e sviluppo tecnologico nel settore della difesa (sistemi di rilevamento oltre l'orizzonte), richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze militari del tutto estranee al tessuto produttivo tipico di una PMI del Cilento. I requisiti di accesso, i volumi di investimento e la natura dual-use del programma lo rendono inaccessibile per la quasi totalità delle piccole e medie imprese campane.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia azioni di sviluppo nel settore della difesa europeo, richiedendo capacità tecnologiche avanzate, consorzi multinazionali e competenze in ambito militare/aerospaziale che esulano completamente dal profilo tipico di una PMI cilentana. I requisiti minimi di partecipazione e i settori ammissibili rendono questo bando di fatto inaccessibile per le realtà produttive locali del territorio campano.</t>
         </is>
       </c>
     </row>
     <row r="228" ht="30" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>AI-based tactical situational awareness using swarms of small robots and drones – organisation of a  technological challenge"</t>
+          <t>New abilities in over-the-horizon sensing</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-CHALLENGE-DIGIT-AISAO</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DA-DIS-OTHR</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -11185,19 +11185,19 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di tecnologie militari avanzate (sciami di robot e droni per la situational awareness tattica), richiede competenze altamente specializzate in difesa e robotica avanzata, e tipicamente coinvolge grandi aziende del settore difesa o consorzi con università tecniche. Una PMI del Cilento, anche tecnologica, difficilmente possiede i requisiti tecnici, le certificazioni di sicurezza e i partner istituzionali necessari per partecipare competitivamente.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa su tecnologie di rilevamento oltre l'orizzonte, richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze militari/aerospaziali del tutto estranee al tessuto produttivo di una PMI del Cilento. I requisiti tecnici e burocratici lo rendono di fatto inaccessibile per imprese di piccola-media dimensione senza specializzazione nel comparto difesa.</t>
         </is>
       </c>
     </row>
     <row r="229" ht="30" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>AI-based tactical situational awareness using swarms of small robots and drones – participation in a  technological challenge"</t>
+          <t>AI-based tactical situational awareness using swarms of small robots and drones – organisation of a  technological challenge"</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-CHALLENGE-DIGIT-AISAP-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-CHALLENGE-DIGIT-AISAO</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -11237,14 +11237,14 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo avanzato su sistemi di intelligenza artificiale per la difesa con sciami di robot e droni, richiedendo capacità tecnologiche e consorziate di alto livello tipiche di grandi aziende del settore difesa o centri di ricerca specializzati. Una PMI del Cilento difficilmente possiede le competenze tecnico-militari, le certificazioni di sicurezza e la massa critica progettuale necessarie per competere in questo contesto, salvo come partner junior in un consorzio internazionale già strutturato.</t>
+          <t>Il bando EDF finanzia lo sviluppo di tecnologie militari avanzate basate su sciami di robot e droni per la consapevolezza situazionale tattica, richiedendo competenze altamente specializzate in difesa e robotica avanzata che difficilmente una PMI del Cilento possiede. Inoltre, i bandi EDF sono tipicamente accessibili a grandi consorzi industriali della difesa, rendendo la partecipazione di una piccola impresa campana estremamente improbabile senza un ruolo marginale in un consorzio guidato da player nazionali o europei del settore difesa.</t>
         </is>
       </c>
     </row>
     <row r="230" ht="30" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CBRN decontamination systems and technologies</t>
+          <t>AI-based tactical situational awareness using swarms of small robots and drones – participation in a  technological challenge"</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -11254,12 +11254,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-MCBRN-DST</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-CHALLENGE-DIGIT-AISAP-STEP</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -11279,19 +11279,19 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per sistemi di decontaminazione CBRN (Chimico, Biologico, Radiologico, Nucleare) è destinato a consorzi industriali con capacità di ricerca e sviluppo nel settore difesa, richiedendo competenze tecnologiche altamente specializzate e investimenti ingenti non compatibili con una PMI del Cilento. L'accesso è praticamente precluso senza partnership con grandi player della difesa o centri di ricerca militare accreditati.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo avanzato su sistemi di intelligenza artificiale applicati a sciami di robot e droni per uso tattico-militare, richiedendo capacità tecnologiche e consorziate tipiche di grandi contractor della difesa o centri di ricerca specializzati. Una PMI del Cilento o della Campania difficilmente dispone delle competenze in robotica avanzata, AI militare e delle certificazioni di sicurezza necessarie per partecipare competitivamente a questa tipologia di challenge europea.</t>
         </is>
       </c>
     </row>
     <row r="231" ht="30" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Future multirole light aircraft</t>
+          <t>CBRN decontamination systems and technologies</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-PROTMOB-FMLA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-MCBRN-DST</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -11331,14 +11331,14 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per aeromobili leggeri multiruolo è destinato a consorzi industriali del settore difesa e aerospaziale con elevate capacità tecnologiche e finanziarie, rendendo praticamente inaccessibile la partecipazione diretta a una PMI del Cilento. L'unica via sarebbe come subfornitore di un grande prime contractor aerospaziale, scenario molto improbabile per realtà produttive locali di piccola dimensione.</t>
+          <t>Il bando EDF per sistemi di decontaminazione CBRN (Chimico, Biologico, Radiologico, Nucleare) è destinato a consorzi di difesa con capacità R&amp;D avanzate e requisiti di sicurezza militare, rendendo praticamente inaccessibile la partecipazione diretta a una PMI del Cilento priva di certificazioni NATO/difesa e delle strutture tecniche richieste. Una piccola impresa campana potrebbe al massimo aspirare a un ruolo marginale come subfornitore in un consorzio guidato da grandi player della difesa, scenario comunque molto improbabile senza relazioni consolidate nel settore.</t>
         </is>
       </c>
     </row>
     <row r="232" ht="30" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Modelling &amp; simulation supported AI framework for military decision-making and training</t>
+          <t>Future multirole light aircraft</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SIMTRAIN-MSAI</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-PROTMOB-FMLA</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -11373,19 +11373,19 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo in ambito difesa militare su tecnologie AI e simulazione avanzata, richiedendo consorzi internazionali con capacità tecnologiche e certificazioni difficilmente accessibili a una PMI del Cilento. Le spese finanziabili riguardano R&amp;S ad alta intensità tecnologica in settori (difesa, sistemi decisionali militari) lontani dal tessuto produttivo locale.</t>
+          <t>Il bando EDF per aeromobili leggeri multiruolo è destinato a consorzi industriali del settore difesa/aerospaziale con capacità di R&amp;S avanzata, richiedendo investimenti e competenze tecniche difficilmente compatibili con una PMI del Cilento. L'accesso è praticamente precluso senza partnership con grandi prime contractor aeronautici.</t>
         </is>
       </c>
     </row>
     <row r="233" ht="30" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Multidomain sensors demonstrator and test</t>
+          <t>Modelling &amp; simulation supported AI framework for military decision-making and training</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SENS-MSDT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SIMTRAIN-MSAI</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -11420,19 +11420,19 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia progetti di R&amp;S nel settore della difesa su tecnologie avanzate di sensoristica multidominio, richiedendo consorzi internazionali con capacità tecnologiche e industriali di alto livello difficilmente accessibili per una PMI del Cilento. I requisiti di compliance difensiva, la complessità gestionale europea e l'orientamento a grandi contractor rendono questo bando sostanzialmente inaccessibile per una piccola impresa locale senza un posizionamento specifico nella filiera della difesa.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa militare (AI per simulazione e decision-making), richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni di sicurezza difficilmente accessibili a una PMI del Cilento. I requisiti di conformità normativa europea in ambito difesa e gli investimenti necessari per partecipare rendono questo bando di fatto inaccessibile per realtà produttive locali di piccola o media dimensione.</t>
         </is>
       </c>
     </row>
     <row r="234" ht="30" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Quantum secured tactical networks</t>
+          <t>Multidomain sensors demonstrator and test</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-CYBER-QSTN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SENS-MSDT</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -11472,14 +11472,14 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sulle reti tattiche sicure quantisticamente è destinato a consorzi di difesa con capacità tecnologiche avanzate nel settore quantistico e militare, requisiti difficilmente soddisfabili da una PMI del Cilento. Le risorse richieste in termini di R&amp;S specializzata e le procedure di accesso ai fondi EDF rendono questo bando di fatto inaccessibile per una piccola o media impresa locale.</t>
+          <t>Il bando EDF finanzia lo sviluppo di dimostratori e sistemi di test per sensori multidominio in ambito difesa, richiedendo capacità tecnologiche avanzate, consorzi multinazionali e competenze specifiche nel settore della difesa europea: barriere di accesso quasi insormontabili per una PMI del Cilento priva di un posizionamento consolidato nella supply chain della difesa. Solo PMI altamente specializzate in sensoristica, elettronica di difesa o sistemi embedded potrebbero partecipare come partner junior in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="235" ht="30" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Autonomous and automatic air-to-air refuelling</t>
+          <t>Quantum secured tactical networks</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-AIR-A4R</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-CYBER-QSTN</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -11514,19 +11514,19 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di sistemi avanzati di rifornimento aereo autonomo in volo, un settore altamente specializzato della difesa aerospaziale che richiede competenze tecnologiche e infrastrutture industriali tipiche di grandi contractor della difesa. Una PMI del Cilento o della Campania in generale difficilmente possiede le certificazioni, i requisiti di sicurezza e le capacità R&amp;S necessarie per partecipare, se non come partner minoritario di un consorzio guidato da prime contractor aerospaziali.</t>
+          <t>Il bando EDF sulle reti tattiche quantistiche è destinato a consorzi di difesa con elevate capacità tecnologiche e finanziarie, richiedendo competenze in crittografia quantistica e sistemi militari che esulano completamente dal profilo tipico di una PMI del Cilento o della Campania. I requisiti di accesso, i costi di partecipazione e la natura dual-use militare rendono questo bando di fatto inaccessibile per realtà produttive locali di piccola e media dimensione.</t>
         </is>
       </c>
     </row>
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Development and validation of models predicting flow-related underwater noise</t>
+          <t>Autonomous and automatic air-to-air refuelling</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-UWW-FUWN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-AIR-A4R</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -11566,14 +11566,14 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF richiede competenze altamente specializzate in modellazione acustica subacquea e fluidodinamica per applicazioni di difesa navale, ambiti tipici di grandi contractor della difesa o centri di ricerca avanzati. Una PMI del Cilento difficilmente dispone delle qualifiche tecniche, dei requisiti consortili e della capacità finanziaria richiesti per partecipare a programmi EDF.</t>
+          <t>Il bando EDF riguarda lo sviluppo di sistemi avanzati di rifornimento aereo autonomo aria-aria, un settore di difesa ad altissima specializzazione tecnologica che richiede competenze aerospaziali e capacità industriali difficilmente accessibili a una PMI del Cilento o della Campania senza un radicato posizionamento nella filiera della difesa europea. Le risorse finanziabili riguardano R&amp;S in ambito militare/aerospaziale, escludendo di fatto realtà produttive locali non già inserite in consorzi industriali del settore difesa.</t>
         </is>
       </c>
     </row>
     <row r="237" ht="30" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Layered critical seabed infrastructure protection</t>
+          <t>Development and validation of models predicting flow-related underwater noise</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SI-UWW-CSBI-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-UWW-FUWN</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -11608,19 +11608,19 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sulla protezione delle infrastrutture sottomarine critiche è destinato a consorzi industriali e centri di ricerca specializzati in tecnologie di difesa navale, con requisiti tecnici e finanziari del tutto incompatibili con una PMI campana del Cilento. Non esistono spese finanziabili pertinenti per realtà produttive locali di piccola o media dimensione.</t>
+          <t>Il bando EDF richiede competenze altamente specializzate in modellazione acustica subacquea e fluidodinamica per applicazioni di difesa navale, ambiti tipicamente appannaggio di grandi contractor della difesa o centri di ricerca avanzati. Una PMI del Cilento difficilmente dispone delle qualifiche tecniche, dei requisiti di sicurezza e della capacità consortile necessari per partecipare a progetti europei di difesa di questa natura.</t>
         </is>
       </c>
     </row>
     <row r="238" ht="30" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>New turbofan engine</t>
+          <t>Layered critical seabed infrastructure protection</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-SI-ENERENV-NTFE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SI-UWW-CSBI-STEP</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -11660,14 +11660,14 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per lo sviluppo di nuovi motori turbofan è destinato a grandi consorzi industriali della difesa aerospaziale, con requisiti tecnologici e finanziari del tutto incompatibili con una PMI del Cilento o della Campania in generale. Non esistono filiere locali rilevanti né capacità produttive adeguate a questo tipo di appalto europeo di difesa.</t>
+          <t>Il bando EDF per la protezione delle infrastrutture sottomarine critiche è destinato a consorzi di difesa e grandi industrie del settore aerospace/defence, con requisiti tecnici e finanziari del tutto incompatibili con una PMI campana del Cilento. Non esistono linee di spesa o sottotematiche accessibili a realtà locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="239" ht="30" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>High-end endo-atmospheric interception</t>
+          <t>New turbofan engine</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ACC-AIRDEF-EATMI</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-SI-ENERENV-NTFE</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -11707,14 +11707,14 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di sistemi avanzati di intercettazione endo-atmosferica ad alta quota, un settore della difesa missilistica che richiede capacità industriali, tecnologiche e finanziarie tipiche di grandi contractor della difesa. Una PMI del Cilento o della Campania non dispone delle certificazioni, infrastrutture e requisiti tecnici necessari per partecipare, nemmeno come subappaltatore di secondo livello.</t>
+          <t>Il bando EDF per lo sviluppo di nuovi motori turbofan è destinato a grandi consorzi industriali del settore aerospaziale e difesa, con requisiti tecnici, finanziari e di sicurezza (es. security clearance) del tutto incompatibili con le capacità di una PMI del Cilento o della Campania in generale. Non esistono spese finanziabili rilevanti per realtà produttive locali di piccola dimensione estranee alla filiera aeronautica militare.</t>
         </is>
       </c>
     </row>
     <row r="240" ht="30" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Smart and multifunctional textiles</t>
+          <t>High-end endo-atmospheric interception</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-MATCOMP-SMT-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ACC-AIRDEF-EATMI</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -11749,19 +11749,19 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa su tessuti intelligenti e multifunzionali, richiedendo consorzi internazionali con capacità tecnologiche avanzate e legami con l'industria della difesa: requisiti molto lontani dalla realtà di una PMI tessile o manifatturiera del Cilento. I costi di partecipazione, la complessità burocratica e i prerequisiti tecnico-militari lo rendono di fatto inaccessibile per una piccola impresa locale.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa missilistica e intercettazione atmosferica ad alto livello tecnologico, ambiti riservati a grandi contractor della difesa o consorzi industriali specializzati. Una PMI del Cilento o della Campania non dispone delle certificazioni, delle infrastrutture di sicurezza NATO/UE né delle capacità tecniche richieste per partecipare a progetti di questa natura.</t>
         </is>
       </c>
     </row>
     <row r="241" ht="30" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Integration of Galileo PRS receivers on weapon systems and NAVWAR operational centres in military C2</t>
+          <t>Smart and multifunctional textiles</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-SPACE-PRS-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-MATCOMP-SMT-STEP</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -11796,19 +11796,19 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di ricevitori Galileo PRS per sistemi d'arma e centri operativi militari C2, un settore altamente specializzato della difesa che richiede certificazioni NATO/UE, capacità industriali avanzate e requisiti di sicurezza inaccessibili a una PMI standard del Cilento o della Campania. Le opportunità concrete si limitano a grandi prime contractor della difesa o a spin-off tecnologici con specifiche abilitazioni di sicurezza.</t>
+          <t>Il bando EDF (Fondo Europeo per la Difesa) finanzia ricerca e sviluppo nel settore tessile ad uso militare/difesa, richiedendo consorzi internazionali con capacità industriali avanzate e requisiti di sicurezza che escludono di fatto le PMI del Cilento non operanti nel comparto difesa. Le spese ammissibili riguardano R&amp;S tecnologica su materiali intelligenti per applicazioni militari, ambito del tutto estraneo al tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="242" ht="30" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Ammunition Waste Collection and Disposal Unmanned Platform</t>
+          <t>Integration of Galileo PRS receivers on weapon systems and NAVWAR operational centres in military C2</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ENERENV-AWC-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-SPACE-PRS-STEP</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -11848,14 +11848,14 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di piattaforme unmanned per la raccolta e smaltimento di munizioni, richiedendo capacità tecnologiche avanzate in robotica, difesa e sistemi autonomi tipiche di grandi contractor della difesa o consorzi industriali specializzati. Una PMI del Cilento o della Campania difficilmente possiede le certificazioni militari, le competenze sistemistiche e la massa critica finanziaria necessarie per partecipare, nemmeno come partner secondario.</t>
+          <t>Il bando EDF finanzia progetti di ricerca e sviluppo militare ad alta tecnologia per l'integrazione di ricevitori PRS Galileo su sistemi d'arma e centri C2, richiedendo competenze difensive specialistiche e capacità industriali del settore aerospaziale-militare del tutto estranee al tessuto produttivo di una PMI campana del Cilento. I requisiti tecnici, i vincoli di sicurezza classificata e la necessità di partnership con grandi contractor della difesa rendono questo bando di fatto inaccessibile per una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="243" ht="30" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Self-protection systems</t>
+          <t>Ammunition Waste Collection and Disposal Unmanned Platform</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-AIR-SPS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ENERENV-AWC-STEP</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -11895,14 +11895,14 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) sui sistemi di auto-protezione è destinato a consorzi di grandi aziende della difesa e centri di ricerca militare, con requisiti tecnici, finanziari e di sicurezza (es. nulla osta NATO/UE) del tutto inaccessibili per una PMI del Cilento priva di specializzazione nel settore difesa. Le risorse necessarie per partecipare a progetti di R&amp;S militare di questa scala rendono la candidatura non praticabile in autonomia.</t>
+          <t>Il bando EDF finanzia lo sviluppo di piattaforme robotiche/droni per la raccolta e smaltimento di residuati bellici, richiedendo competenze altamente specializzate in difesa, robotica e sistemi autonomi difficilmente presenti in una PMI del Cilento. I requisiti tecnici, i costi di partecipazione e la natura consortile tipica dei progetti EDF rendono questo bando sostanzialmente inaccessibile per una piccola impresa campana senza un posizionamento già consolidato nel settore difesa.</t>
         </is>
       </c>
     </row>
     <row r="244" ht="30" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Multiple rocket launcher</t>
+          <t>Self-protection systems</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-GROUND-MRL</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-AIR-SPS</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -11942,14 +11942,14 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF 'Multiple Rocket Launcher' riguarda lo sviluppo di sistemi d'arma avanzati nell'ambito della difesa europea, un settore che richiede capacità industriali altamente specializzate, certificazioni militari e investimenti strutturali incompatibili con le dimensioni e il profilo tipico di una PMI del Cilento. L'accesso è di fatto riservato a grandi contractor della difesa o consorzi industriali con competenze balistiche e sistemistiche specifiche.</t>
+          <t>Il bando EDF (European Defence Fund) sui sistemi di auto-protezione è destinato a consorzi di ricerca e industrie della difesa con capacità tecnologiche avanzate, requisiti di sicurezza certificati e strutture R&amp;S dedicate, caratteristiche difficilmente compatibili con una PMI del Cilento. L'accesso richiede partnership internazionali in ambito difesa e budget di progetto nell'ordine di milioni di euro, rendendo il bando di fatto inaccessibile per realtà produttive locali di piccola-media dimensione.</t>
         </is>
       </c>
     </row>
     <row r="245" ht="30" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>High-performance energy systems</t>
+          <t>Multiple rocket launcher</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ENERENV-HPES-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-GROUND-MRL</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -11989,14 +11989,14 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) su sistemi energetici ad alte prestazioni è destinato a consorzi di ricerca e industria della difesa, con requisiti di partecipazione multi-paese e tecnologie militari che escludono di fatto le PMI del Cilento non operanti nel settore difesa. I costi di partecipazione, la complessità burocratica e i requisiti di sicurezza/certificazione rendono questo strumento inaccessibile per una piccola impresa campana.</t>
+          <t>Il bando EDF riguarda lo sviluppo di sistemi missilistici multipli, un settore della difesa ad altissima specializzazione tecnica e con requisiti di sicurezza stringenti, totalmente fuori dalla portata di una PMI del Cilento o della Campania senza competenze specifiche nell'industria militare. Le risorse richieste, i partner istituzionali necessari e i vincoli normativi del settore difesa rendono questo bando inaccessibile per una piccola o media impresa del territorio.</t>
         </is>
       </c>
     </row>
     <row r="246" ht="30" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Secure digital military mobility system</t>
+          <t>High-performance energy systems</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-PROTMOB-DMM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ENERENV-HPES-STEP</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -12036,14 +12036,14 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa militare, richiedendo consorzi internazionali con capacità tecnologiche e certificazioni specifiche del comparto difesa difficilmente accessibili a una PMI del Cilento. I requisiti di compliance militare, i costi di partecipazione e la natura altamente specializzata del tema (mobilità militare sicura e digitale) rendono questo bando di fatto inaccessibile per una piccola o media impresa locale senza esperienza pregressa nel settore difesa.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia sistemi energetici ad alte prestazioni in ambito difesa, richiedendo capacità tecnologiche avanzate, partenariati internazionali e accreditamenti nel settore militare difficilmente accessibili a una PMI del Cilento. La natura strettamente legata alla difesa europea esclude di fatto le piccole imprese locali non inserite in filiere industriali della difesa.</t>
         </is>
       </c>
     </row>
     <row r="247" ht="30" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Enhanced cognitive EW system with intelligent RESM CESM signal analysis</t>
+          <t>Secure digital military mobility system</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-SENS-CEW-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-PROTMOB-DMM</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia sistemi avanzati di guerra elettronica cognitiva (EW) e analisi di segnali RESM/CESM, un settore ad altissima specializzazione tecnologica e difensiva riservato di fatto a grandi contractor della difesa o a spin-off con competenze molto specifiche in elettronica militare. Una PMI del Cilento o della Campania difficilmente possiede i requisiti tecnici, le certificazioni di sicurezza e la capacità consortile necessaria per partecipare competitivamente a questo tipo di call europea.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa militare, richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni di sicurezza difficilmente accessibili a una PMI del Cilento. Le tematiche di mobilità militare digitale sicura sono estranee al tessuto produttivo locale, orientato prevalentemente su turismo, agricoltura e artigianato.</t>
         </is>
       </c>
     </row>
     <row r="248" ht="30" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Enhanced medium-size semi-autonomous surface vessels</t>
+          <t>Enhanced cognitive EW system with intelligent RESM CESM signal analysis</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-NAVAL-EMSAS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-SENS-CEW-STEP</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -12130,14 +12130,14 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di natanti semi-autonomi di media grandezza per applicazioni difensive, richiedendo capacità tecnologiche avanzate, consorzi internazionali e risorse tipiche di grandi industrie della difesa o centri di ricerca specializzati. Una PMI del Cilento, anche operante nel settore nautico o marittimo, difficilmente dispone dei requisiti tecnici, finanziari e di clearance necessari per partecipare competitivamente.</t>
+          <t>Il bando EDF finanzia sistemi avanzati di guerra elettronica cognitiva (EW) con analisi intelligente dei segnali RESM/CESM, un ambito che richiede competenze altamente specializzate in difesa e tecnologie militari tipiche di grandi contractor o centri di ricerca aerospaziali. Una PMI del Cilento o della Campania difficilmente possiede i requisiti tecnici, i nulla osta di sicurezza e la capacità finanziaria per partecipare a consorzi EDF di questo tipo.</t>
         </is>
       </c>
     </row>
     <row r="249" ht="30" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Smart technologies for next generation fighter systems</t>
+          <t>Enhanced medium-size semi-autonomous surface vessels</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-AIR-STFS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-NAVAL-EMSAS</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -12172,19 +12172,19 @@
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia R&amp;S per tecnologie avanzate destinate a sistemi d'arma di nuova generazione, richiedendo capacità industriali e tecnologiche tipiche di grandi prime contractor della difesa o di PMI altamente specializzate in aerospazio/difesa. Una PMI del Cilento non dispone in genere né dei requisiti tecnici né della rete di partnership internazionali necessarie per partecipare competitivamente a questo tipo di consorzio europeo.</t>
+          <t>Il bando EDF finanzia lo sviluppo di navi di superficie semi-autonome di media taglia per scopi difensivi, richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze militari-navali difficilmente accessibili a una PMI del Cilento. Il settore nautico locale è orientato alla piccola pesca e al turismo costiero, lontano dai requisiti industriali e certificativi richiesti da questo programma europeo per la difesa.</t>
         </is>
       </c>
     </row>
     <row r="250" ht="30" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Future main battle tank platform systems</t>
+          <t>Smart technologies for next generation fighter systems</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-GROUND-MBT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-AIR-STFS</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -12219,19 +12219,19 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi per carri armati da combattimento di nuova generazione richiede capacità industriali e tecnologiche nel settore della difesa pesante, tipiche di grandi contractor militari e consorzi internazionali. Una PMI del Cilento non dispone delle certificazioni, infrastrutture e partnership necessarie per partecipare competitivamente a progetti di questo livello.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo per sistemi d'arma di nuova generazione nel settore della difesa aeronautica, richiedendo competenze altamente specializzate, consorzi internazionali e capacità industriali difficilmente compatibili con una PMI del Cilento. Le barriere di accesso tecniche, burocratiche e finanziarie rendono questo bando sostanzialmente inaccessibile per realtà locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="251" ht="30" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Non-thematic research actions by SMEs and research organisations</t>
+          <t>Future main battle tank platform systems</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DIS-RA-SMERO-NT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-GROUND-MBT</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -12266,19 +12266,19 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca nel settore della difesa in consorzio con enti di ricerca, con requisiti tecnici, burocratici e di sicurezza molto elevati che rendono la partecipazione diretta di una PMI del Cilento estremamente difficile senza un solido network europeo nel settore difesa. Le spese finanziabili riguardano R&amp;S per tecnologie militari e dual-use, ambiti lontani dalla struttura produttiva tipica delle PMI campane di quella area.</t>
+          <t>Il bando EDF riguarda lo sviluppo di sistemi per carri armati da combattimento di nuova generazione, un settore della difesa ad altissima intensità tecnologica e capitalistica riservato a grandi consorzi industriali del comparto militare. Una PMI del Cilento o della Campania non dispone delle certificazioni, delle infrastrutture e della capacità finanziaria necessarie per partecipare competitivamente a progetti di questo tipo.</t>
         </is>
       </c>
     </row>
     <row r="252" ht="30" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Non-thematic actions targeting disruptive technologies for defence</t>
+          <t>Non-thematic research actions by SMEs and research organisations</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DIS-NT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DIS-RA-SMERO-NT</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -12313,19 +12313,19 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo su tecnologie dirompenti per la difesa (es. AI, quantum, spazio), richiedendo consorzi internazionali e capacità tecnologiche altamente specializzate difficilmente accessibili a una PMI del Cilento senza solide partnership con centri di ricerca o grandi imprese del settore difesa. I requisiti di ammissibilità, la complessità progettuale e la natura militare dell'obiettivo rendono questo strumento di fatto inaccessibile per la maggior parte delle PMI campane di piccola dimensione.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca nel settore della difesa europea, richiedendo capacità tecnologiche avanzate, consorzi multinazionali e competenze in ambito militare/sicurezza che sono tipicamente fuori dalla portata di una PMI del Cilento operante in settori tradizionali. I requisiti burocratici, i costi di partecipazione e la natura altamente specializzata dei progetti rendono questo strumento di fatto inaccessibile per la quasi totalità delle piccole imprese campane.</t>
         </is>
       </c>
     </row>
     <row r="253" ht="30" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Gender Equality Champions</t>
+          <t>Non-thematic actions targeting disruptive technologies for defence</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -12335,17 +12335,17 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DIS-NT</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - EDF</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
@@ -12360,19 +12360,19 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Sustainable Gender Equality Champions' è orientato a consorzi di ricerca e grandi organizzazioni con capacità di progettazione europea complessa, richiedendo partnership internazionali e competenze amministrative difficilmente accessibili a una PMI del Cilento. Le PMI di piccola dimensione possono al massimo partecipare come partner secondari, ma raramente come beneficiari diretti con ritorno economico concreto.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo su tecnologie dirompenti per la difesa (es. quantum, AI militare, materiali avanzati), richiedendo consorzi transnazionali con capacità R&amp;D certificate e conformità a requisiti di sicurezza NATO/UE che una PMI del Cilento difficilmente soddisfa autonomamente. L'accesso è realisticamente limitato a grandi contractor della difesa o spin-off universitari con esperienza specifica nel settore militare.</t>
         </is>
       </c>
     </row>
     <row r="254" ht="30" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Newcomer Gender Equality Champions</t>
+          <t>Sustainable Gender Equality Champions</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-01</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -12412,14 +12412,14 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Newcomer Gender Equality Champions' è orientato a enti di ricerca, università e organizzazioni di grandi dimensioni con capacità di gestire progetti europei complessi, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un ruolo da partner secondario. Inoltre, il focus tematico sulla parità di genere per 'newcomer' non intercetta le esigenze operative tipiche delle PMI locali nei settori trainanti del territorio come turismo, agricoltura e artigianato.</t>
+          <t>Il bando Horizon 'Sustainable Gender Equality Champions' è orientato a consorzi di ricerca europei e grandi organizzazioni con capacità di progettazione complessa, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un ruolo da partner in un consorzio internazionale. Le spese finanziabili riguardano attività di ricerca e disseminazione sull'uguaglianza di genere, ambito distante dalle priorità operative tipiche delle PMI locali nei settori turismo, agricoltura o artigianato.</t>
         </is>
       </c>
     </row>
     <row r="255" ht="30" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Inclusive Gender Equality Champions</t>
+          <t>Newcomer Gender Equality Champions</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-02</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -12459,34 +12459,34 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU 'Inclusive Gender Equality Champions' è orientato prevalentemente a consorzi di ricerca, università e grandi organizzazioni con capacità di progettazione europea; una PMI del Cilento difficilmente ha le strutture amministrative e i partner richiesti per partecipare come capofila. L'accesso è possibile solo come partner secondario in un consorzio transnazionale, rendendo il percorso poco praticabile senza intermediari specializzati.</t>
+          <t>Il bando Horizon focalizzato sulla parità di genere è orientato principalmente a enti di ricerca, università e grandi organizzazioni con capacità progettuale europea, rendendo l'accesso estremamente complesso per una PMI del Cilento priva di strutture dedicate alla rendicontazione UE. Le spese finanziabili riguardano attività di ricerca e disseminazione su tematiche di genere, lontane dal core business tipico delle PMI locali (turismo, agricoltura, artigianato).</t>
         </is>
       </c>
     </row>
     <row r="256" ht="30" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Works</t>
+          <t>Inclusive Gender Equality Champions</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-WORKS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-03</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>UE - CEF2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -12501,19 +12501,19 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 per reti energetiche (smart grid, idrogeno, CO₂) finanzia opere infrastrutturali di interesse europeo destinate principalmente a grandi operatori del settore energetico e gestori di reti, con requisiti tecnici e finanziari del tutto inaccessibili per una PMI campana, incluse quelle del Cilento. Non sono previste linee dedicate a imprese di piccola dimensione né attività tipicamente svolte da PMI locali.</t>
+          <t>Il bando Horizon europeo sulla parità di genere è orientato principalmente a enti di ricerca, università e grandi organizzazioni con capacità di gestione progettuale complessa; una PMI del Cilento difficilmente dispone delle risorse amministrative e del partenariato internazionale richiesto per partecipare direttamente come capofila o partner qualificato.</t>
         </is>
       </c>
     </row>
     <row r="257" ht="30" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Studies</t>
+          <t>Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Works</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-STUDIES</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-WORKS</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -12553,34 +12553,34 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia studi su reti energetiche transeuropee (smart grid, idrogeno, CO₂) con requisiti tecnici, burocratici e di scala tipici di grandi operatori del settore energetico o consorzi pubblici, rendendo l'accesso di una PMI del Cilento estremamente difficile senza un ruolo di partner secondario in progetti già strutturati.</t>
+          <t>Il bando CEF2027 finanzia grandi opere infrastrutturali su reti energetiche transeuropee (smart grid, idrogeno, CO₂, gas), rivolte tipicamente a operatori di sistema, utility e consorzi pubblici-privati di scala europea. Una PMI del Cilento non ha né la dimensione né il profilo tecnico-istituzionale richiesto per accedere direttamente a questi fondi.</t>
         </is>
       </c>
     </row>
     <row r="258" ht="30" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Apply AI: Piloting AI-based image screening in medical centres</t>
+          <t>Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Studies</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-AI-PILOTING-10-SCREENING</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-STUDIES</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>UE - DIGITAL</t>
+          <t>UE - CEF2027</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -12595,19 +12595,19 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato a progetti pilota di AI applicata allo screening di immagini mediche in centri sanitari, richiedendo capacità tecnologiche avanzate e partnership strutturate difficilmente accessibili a una PMI del Cilento. Le PMI di piccola dimensione del territorio, salvo rare realtà specializzate in healthtech o AI, non hanno i requisiti tecnici e finanziari per competere in un bando europeo di questa natura.</t>
+          <t>Il bando CEF 2027 finanzia studi su reti energetiche transeuropee (smart grid, idrogeno, CO₂) ed è orientato a grandi operatori di rete, enti pubblici e consorzi europei, con requisiti tecnici e finanziari fuori portata per una PMI del Cilento. Una piccola impresa campana non ha né la scala operativa né il profilo istituzionale richiesto per accedere a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="259" ht="30" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Digital solutions for regulatory compliance  through data</t>
+          <t>Apply AI: Piloting AI-based image screening in medical centres</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-AI-DATA-10-COMPLIANCE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-AI-PILOTING-10-SCREENING</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -12642,19 +12642,19 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>Digitalizzazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>Il bando UE DIGITAL è orientato a soluzioni tecnologiche avanzate per la conformità normativa tramite gestione dei dati, con requisiti tecnici e dimensionali tipicamente adatti a grandi operatori o consorzi tecnologici. Una PMI del Cilento difficilmente possiede le competenze interne e la struttura progettuale necessarie per competere in un bando europeo diretto di questa complessità, senza un partenariato internazionale strutturato.</t>
+          <t>Il bando finanzia progetti pilota di AI applicata allo screening di immagini mediche, richiedendo competenze tecnologiche avanzate e partnership con centri medici, il che lo rende difficilmente accessibile per una PMI generica del Cilento. Solo aziende specializzate in health-tech o imaging diagnostico potrebbero candidarsi concretamente.</t>
         </is>
       </c>
     </row>
     <row r="260" ht="30" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Support to Dissemination and Exploitation (D&amp;E) for the Digital Europe Programme</t>
+          <t>Digital solutions for regulatory compliance  through data</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-SUPPORT-10-DISSEMINATION</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-AI-DATA-10-COMPLIANCE</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -12694,14 +12694,14 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia attività di disseminazione e sfruttamento dei risultati del Programma Digital Europe, rivolgendosi principalmente a consorzi, enti di ricerca e grandi organizzazioni con capacità di comunicazione istituzionale a livello europeo. Una PMI del Cilento difficilmente possiede i requisiti strutturali e la dimensione progettuale per partecipare direttamente a questo tipo di azione.</t>
+          <t>Il bando UE DIGITAL su soluzioni digitali per la compliance normativa tramite dati è orientato tipicamente a consorzi internazionali, grandi player tecnologici o enti di ricerca, richiedendo capacità progettuali e finanziarie difficilmente accessibili a una PMI del Cilento senza un solido partner capofila. Una piccola impresa locale troverebbe barriere significative in termini di requisiti tecnici, co-finanziamento e gestione burocratica europea diretta.</t>
         </is>
       </c>
     </row>
     <row r="261" ht="30" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Research Support Framework for Situational Awareness on information integrity</t>
+          <t>Support to Dissemination and Exploitation (D&amp;E) for the Digital Europe Programme</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-RSF-10-AWARENESS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-SUPPORT-10-DISSEMINATION</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -12736,19 +12736,19 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia attività di ricerca avanzata sulla verifica dell'integrità delle informazioni e la lotta alla disinformazione, ambiti tipicamente riservati a enti di ricerca, università o grandi consorzi tecnologici. Una PMI del Cilento, salvo rari casi di aziende specializzate in cybersecurity o media analysis, difficilmente possiede le competenze tecniche e la struttura progettuale richiesta per competere in questo tipo di call europea.</t>
+          <t>Il bando finanzia attività di disseminazione e valorizzazione dei risultati del programma Digital Europe, rivolto tipicamente a grandi consorzi, enti di ricerca o organismi intermediari, non a PMI che cercano finanziamenti diretti per i propri progetti aziendali. Una piccola impresa del Cilento difficilmente possiede la struttura organizzativa e le competenze tecniche necessarie per gestire progetti di comunicazione istituzionale a livello europeo.</t>
         </is>
       </c>
     </row>
     <row r="262" ht="30" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Support to the implementation of Multi-Country Projects: EDIC Support Hub</t>
+          <t>Research Support Framework for Situational Awareness on information integrity</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-MCP-10-HUB</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-RSF-10-AWARENESS</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -12783,19 +12783,19 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>Digitalizzazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto a soggetti capaci di gestire progetti multi-paese nell'ambito degli EDIC (European Digital Innovation Consortia), strutture consortili transnazionali che esulano dalla capacità operativa e amministrativa di una PMI del Cilento. Non sono previste linee di finanziamento diretto per singole imprese di piccola dimensione.</t>
+          <t>Il bando finanzia attività di ricerca avanzata sulla verifica dell'integrità delle informazioni e la consapevolezza situazionale nell'ecosistema digitale, ambiti altamente specialistici che richiedono competenze di ricerca accademica o grandi strutture tecnologiche. Una PMI del Cilento difficilmente possiede i requisiti tecnici e organizzativi per partecipare competitivamente a un framework europeo di questo livello.</t>
         </is>
       </c>
     </row>
     <row r="263" ht="30" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Building capacity to deploy the EEHRxF and digital  health services and systems to support the rights of  citizens and reuse of health data under EHDS</t>
+          <t>Support to the implementation of Multi-Country Projects: EDIC Support Hub</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-10-EHDS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-MCP-10-HUB</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -12835,14 +12835,14 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo dell'infrastruttura europea per la condivisione di dati sanitari (EHDS) e i sistemi di cartella clinica elettronica, destinato principalmente a enti pubblici, autorità sanitarie nazionali e grandi organizzazioni IT sanitarie. Una PMI del Cilento difficilmente possiede i requisiti tecnici e istituzionali per partecipare come soggetto capofila o partner rilevante in un progetto di questa complessità e scala europea.</t>
+          <t>Il bando è rivolto principalmente a enti pubblici e consorzi transnazionali che supportano la creazione di EDIC (European Digital Infrastructure Consortia), strutture di governance complessa difficilmente accessibili a una PMI del Cilento. Una piccola impresa campana non può partecipare direttamente come beneficiaria, ma potrebbe al massimo essere coinvolta indirettamente come fornitore di servizi digitali in un progetto già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Ensuring comprehensive geographical coverage of the Network of Safer Internet Centres (SICs)</t>
+          <t>Building capacity to deploy the EEHRxF and digital  health services and systems to support the rights of  citizens and reuse of health data under EHDS</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-10-NETWORKSICs</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-10-EHDS</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -12877,19 +12877,19 @@
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia la creazione e gestione di Centri per un Internet Sicuro (SICs) a copertura geografica europea, rivolgendosi a enti pubblici, organizzazioni no-profit o consorzi specializzati nella protezione online dei minori, non a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti strutturali né il profilo istituzionale richiesto per candidarsi come beneficiario diretto.</t>
+          <t>Il bando UE riguarda lo sviluppo dell'infrastruttura europea per la condivisione di dati sanitari (EHDS) e si rivolge principalmente a grandi enti pubblici sanitari, autorità nazionali e organizzazioni con capacità tecniche avanzate in health IT. Una PMI del Cilento, anche operante in ambito digitale o sanitario, difficilmente possiede i requisiti tecnici, la scala operativa e le partnership istituzionali richieste per partecipare a un progetto di questa complessità europea.</t>
         </is>
       </c>
     </row>
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>EdTech Accelerator</t>
+          <t>Ensuring comprehensive geographical coverage of the Network of Safer Internet Centres (SICs)</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-SKILLS-10-EDTECH</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-10-NETWORKSICs</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato a startup e scaleup nel settore EdTech (tecnologie per l'educazione), con logiche da acceleratore che privilegiano modelli di business scalabili digitalmente, poco adatti a PMI tradizionali del Cilento. Una piccola impresa campana non operante nel settore istruzione/formazione digitale avrebbe difficoltà concrete a candidarsi e a soddisfare i requisiti di innovazione tecnologica richiesti.</t>
+          <t>Il bando è destinato alla creazione e gestione di Centri per un Internet Sicuro (SIC) su scala europea, richiede capacità organizzative e strutturali tipiche di enti pubblici, istituzioni o grandi organizzazioni no-profit, rendendo di fatto inaccessibile la partecipazione a una PMI del Cilento o della Campania. Non sono previste attività finanziabili direttamente compatibili con la natura produttiva o commerciale di una piccola o media impresa.</t>
         </is>
       </c>
     </row>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto principalmente a coalizioni nazionali e grandi enti aggregatori per lo sviluppo di competenze digitali su scala nazionale, non a singole PMI; una piccola impresa del Cilento non può accedere direttamente ma solo come partner secondario di una coalizione strutturata, rendendo l'accesso concreto molto difficile.</t>
+          <t>Il bando è rivolto a coalizioni nazionali e grandi soggetti aggregatori per lo sviluppo di competenze digitali su scala sistemica, non a singole PMI: una micro o piccola impresa del Cilento non può accedervi direttamente né rendicontare spese proprie. L'unica opportunità indiretta sarebbe partecipare come partner in un consorzio già strutturato, scenario poco realistico per realtà locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti su larga scala per lo sviluppo di competenze digitali avanzate in ambito AI e salute, rivolti principalmente a università, ospedali, grandi consorzi e istituzioni pubbliche europee. Una PMI del Cilento difficilmente ha la struttura per guidare o partecipare attivamente a questi network transnazionali complessi.</t>
+          <t>Il bando finanzia progetti europei su larga scala per lo sviluppo di competenze digitali avanzate legate all'IA in ambito sanitario, rivolto principalmente a università, ospedali e grandi consorzi istituzionali. Una PMI del Cilento difficilmente può accedere direttamente senza essere partner di un consorzio strutturato con capofila istituzionale.</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la cooperazione amministrativa tra autorità pubbliche sul distacco transnazionale dei lavoratori (Direttiva 96/71/CE), con beneficiari tipicamente ministeri, ispettorati del lavoro e organismi istituzionali. Una PMI del Cilento non ha accesso diretto a questi fondi né rientra tra i destinatari previsti.</t>
+          <t>Il bando riguarda la cooperazione amministrativa tra autorità pubbliche sul distacco transnazionale dei lavoratori (direttiva 2014/67/UE), destinato principalmente a enti pubblici e ispettorati del lavoro, non a PMI. Una piccola impresa del Cilento non ha titolo diretto per candidarsi né beneficia di finanziamenti per attività aziendali concrete.</t>
         </is>
       </c>
     </row>
@@ -13117,7 +13117,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 per il settore ferroviario finanzia studi e lavori su infrastrutture di trasporto transeuropee, con importi e requisiti tecnico-amministrativi pensati per enti pubblici, gestori di rete e grandi consorzi, rendendo di fatto inaccessibile la partecipazione diretta a una PMI del Cilento. Il territorio del Cilento, già marginale rispetto alle grandi direttrici ferroviarie TEN-T, non beneficerebbe nemmeno indirettamente di questo strumento nel breve periodo.</t>
+          <t>Il bando CEF2027 Rail finanzia studi e lavori infrastrutturali sulla rete ferroviaria trans-europea (TEN-T), destinati principalmente a Stati membri, gestori dell'infrastruttura ferroviaria e grandi enti pubblici: una PMI del Cilento non ha i requisiti soggettivi né la capacità progettuale per accedervi direttamente. Il territorio del Cilento, inoltre, è scarsamente integrato nella rete TEN-T, rendendo ancora più remota qualsiasi ricaduta diretta sul tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF (Connecting Europe Facility) per infrastrutture ferroviarie finanzia studi di fattibilità e lavori su reti ferroviarie transeuropee, destinati principalmente a gestori di infrastrutture, enti pubblici e grandi consorzi: una PMI del Cilento non ha né la dimensione né il profilo istituzionale per candidarsi direttamente. L'area del Cilento, inoltre, è marginale rispetto alle reti TEN-T prioritarie, rendendo ancora più remota qualsiasi applicabilità locale.</t>
+          <t>Il bando CEF2027 Rail finanzia studi e opere infrastrutturali ferroviarie di scala europea, rivolto principalmente a gestori di rete, enti pubblici e grandi consorzi: una PMI del Cilento non ha né i requisiti dimensionali né le competenze tecniche per candidarsi autonomamente a progetti di infrastruttura ferroviaria transeuropea.</t>
         </is>
       </c>
     </row>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 per le vie navigabili interne finanzia grandi opere infrastrutturali transeuropee destinate a soggetti pubblici o grandi consorzi, con requisiti tecnici e finanziari incompatibili con una PMI del Cilento, territorio privo di vie navigabili interne rilevanti. Non esistono spese finanziabili né settori di applicazione concretamente accessibili per una piccola o media impresa locale.</t>
+          <t>Il bando CEF 2027 finanzia grandi opere infrastrutturali per vie navigabili interne della rete TEN-T europea, rivolto a Stati membri e grandi enti pubblici/concessionari: una PMI campana, e in particolare del Cilento (area priva di vie navigabili interne rilevanti), non ha accesso diretto né requisiti tecnico-finanziari compatibili con questo tipo di appalto.</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia opere infrastrutturali per la digitalizzazione del trasporto stradale a scala europea, con requisiti tecnici e finanziari accessibili solo a grandi consorzi o enti pubblici. Una PMI del Cilento non ha le dimensioni né le capacità progettuali per partecipare direttamente a bandi di questa portata.</t>
+          <t>Il bando CEF 2027 finanzia opere infrastrutturali per la digitalizzazione del trasporto stradale su scala europea, con requisiti tecnici e finanziari tipici di grandi consorzi o enti pubblici, del tutto inaccessibili a una PMI del Cilento. Non è previsto un coinvolgimento diretto di piccole imprese come beneficiarie principali.</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 'External Borders' finanzia studi e opere infrastrutturali alle frontiere esterne dell'UE, con destinatari tipici quali autorità statali, agenzie doganali e operatori di grandi infrastrutture: una PMI del Cilento non ha i requisiti soggettivi né la scala operativa per accedervi. Non sono previste linee di finanziamento per imprese private di piccola dimensione.</t>
+          <t>Il bando CEF 2027 - External Borders finanzia studi e lavori infrastrutturali legati alla gestione delle frontiere esterne dell'UE, destinato principalmente a Stati membri e grandi enti pubblici. Una PMI del Cilento non ha accesso diretto a questi fondi né rientra tra i beneficiari tipici di questa linea di finanziamento.</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF (Connecting Europe Facility) finanzia grandi opere infrastrutturali nel settore marittimo e portuale, con investimenti tipicamente nell'ordine di decine di milioni di euro, destinati a soggetti pubblici o grandi operatori del settore dei trasporti. Una PMI del Cilento non ha né la dimensione né il profilo istituzionale per accedere direttamente a questo tipo di finanziamento.</t>
+          <t>Il bando CEF 2027 finanzia opere infrastrutturali per porti marittimi e vie navigabili interne, con importi tipicamente nell'ordine di milioni di euro destinati a enti pubblici, autorità portuali e grandi operatori logistici. Una PMI del Cilento non ha i requisiti dimensionali né la natura giuridica per accedere direttamente a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 finanzia studi e lavori per adattare la rete TEN-T all'uso duale civile-militare, destinato principalmente a enti pubblici, gestori di infrastrutture e grandi operatori del trasporto: una PMI del Cilento non ha i requisiti tecnici né la scala operativa per candidarsi direttamente. L'unica opportunità indiretta sarebbe partecipare come subappaltatore in un consorzio guidato da grandi imprese di ingegneria o costruzioni.</t>
+          <t>Il bando CEF (Connecting Europe Facility) finanzia studi e lavori su infrastrutture di trasporto della rete TEN-T ad uso duale civile-militare, ed è rivolto principalmente a Stati membri, gestori di infrastrutture e grandi enti pubblici. Una PMI del Cilento non ha accesso diretto a questo tipo di finanziamento, né rientra tra i soggetti beneficiari ammissibili.</t>
         </is>
       </c>
     </row>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2 finanzia opere infrastrutturali per carburanti alternativi nel trasporto stradale e aereo, con investimenti tipicamente nell'ordine di milioni di euro riservati a grandi operatori, gestori aeroportuali o consorzi pubblico-privati. Una PMI del Cilento non ha i requisiti tecnici né la capacità finanziaria per accedere direttamente a questo tipo di appalto europeo.</t>
+          <t>Il bando CEF finanzia infrastrutture per carburanti alternativi nel trasporto stradale e aereo (stazioni di ricarica/rifornimento su reti TEN-T), ma è rivolto a grandi operatori infrastrutturali, enti pubblici o consorzi con capacità tecnico-finanziaria elevata. Una PMI del Cilento non ha struttura né scala per candidarsi direttamente a lavori infrastrutturali di questa portata europea.</t>
         </is>
       </c>
     </row>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede consorzi internazionali, capacità di ricerca avanzata e budget elevati, rendendolo di fatto inaccessibile per una PMI edile del Cilento che operi autonomamente. Una PMI potrebbe partecipare solo come partner junior in un consorzio già strutturato con università o grandi imprese, ruolo difficile da costruire senza reti europee consolidate.</t>
+          <t>Il bando Horizon UE richiede progetti di ricerca e innovazione su scala urbana/edilizia con consorzio internazionale e capacità di R&amp;D avanzata, requisiti difficilmente compatibili con una PMI del Cilento. Una piccola impresa edile o costruttrice campana potrebbe partecipare solo come partner secondario in un consorzio già strutturato, senza possibilità di essere capofila.</t>
         </is>
       </c>
     </row>
@@ -13540,7 +13540,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca e innovazione sul trasporto pubblico urbano ad alta efficienza energetica e mobilità condivisa, ambiti tipicamente gestiti da enti pubblici, grandi consorzi o università. Una PMI del Cilento difficilmente possiede i requisiti tecnici, la capacità progettuale e i partner istituzionali necessari per partecipare competitivamente a questo tipo di call europea.</t>
+          <t>Il bando Horizon si focalizza su sistemi di trasporto pubblico urbano e suburbano ad alta efficienza energetica e mobilità condivisa, ambiti tipicamente gestiti da enti pubblici, grandi consorzi o operatori di trasporto strutturati. Una PMI del Cilento difficilmente possiede i requisiti tecnici, la capacità progettuale europea e le partnership istituzionali necessarie per competere in questo tipo di call, che richiede inoltre rendicontazione complessa in inglese e co-finanziamento significativo.</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca e sviluppo avanzate, partnership internazionali e rendicontazione complessa, barriere difficilmente superabili per una PMI del Cilento. Il focus su soluzioni di riscaldamento a bassa temperatura per edifici multi-appartamento è settorialmente distante dal tessuto produttivo locale, prevalentemente orientato a turismo, agricoltura e piccolo commercio.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca e sviluppo avanzate, consorzi internazionali e competenze tecniche specifiche sulle soluzioni di riscaldamento a bassa temperatura per edifici condominiali, requisiti difficilmente soddisfabili da una PMI del Cilento senza partner universitari o centri di ricerca. Il territorio del Cilento, prevalentemente rurale e con scarsa infrastruttura di R&amp;S, rende ulteriormente complessa la partecipazione competitiva a questo tipo di call europea.</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>Il bando CCAM finanzia dimostrazioni su larga scala di mobilità connessa e automatizzata, richiedendo consorzi internazionali con capacità tecniche e finanziarie elevate, tipiche di grandi aziende automotive o centri di ricerca. Una PMI del Cilento difficilmente possiede i requisiti tecnici e la massa critica per guidare o partecipare attivamente a progetti di questa complessità e scala.</t>
+          <t>Il bando CCAM finanzia dimostrazioni su larga scala di mobilità connessa e automatizzata, richiedendo consorzi di grandi dimensioni con capacità tecnologiche e finanziarie elevate, del tutto fuori dalla portata di una PMI campana o cilentana. Le risorse necessarie per partecipare come partner rilevante (infrastrutture, R&amp;S avanzata, testing su scala) rendono questo bando sostanzialmente inaccessibile senza il supporto di grandi player industriali o centri di ricerca strutturati.</t>
         </is>
       </c>
     </row>
@@ -13676,12 +13676,12 @@
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU è orientato a progetti di ricerca e innovazione su scala europea nel settore della logistica e dei trasporti multimodali, richiedendo consorzi internazionali e capacità progettuali elevate difficilmente alla portata di una PMI del Cilento. Una piccola impresa campana del settore trasporti potrebbe partecipare solo come partner junior in un consorzio più ampio, con margini di accesso molto limitati.</t>
+          <t>Il bando Horizon UE sulla competitività del trasporto merci multimodale è orientato a grandi consorzi di ricerca e attori logistici su scala europea, rendendo l'accesso diretto molto difficile per una PMI del Cilento, territorio peraltro marginale rispetto alle rotte di trasporto merci strategiche. Una PMI potrebbe al limite partecipare come partner junior in un consorzio, ma i requisiti progettuali e amministrativi di Horizon restano proibitivi per strutture di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>Il bando CCAM (Connected, Cooperative and Automated Mobility) finanzia ricerca avanzata sulla mobilità autonoma e connessa in un contesto geopolitico europeo, richiedendo consorzi internazionali complessi e competenze altamente specializzate difficilmente accessibili a una PMI del Cilento. Il territorio e il tessuto produttivo locale non esprimono filiere della mobilità automatizzata rilevanti per rispondere competitivamente a questa call Horizon.</t>
+          <t>Il bando CCAM (Connected, Cooperative and Automated Mobility) di Horizon Europe è orientato a grandi consorzi di ricerca su mobilità autonoma e geopolitica dell'innovazione, con requisiti tecnici e amministrativi difficilmente accessibili per una PMI campana del Cilento, territorio privo di infrastrutture di mobilità avanzata rilevanti per questo contesto. Le PMI locali non dispongono generalmente delle competenze R&amp;S o dei partner internazionali necessari per competere in questo tipo di call.</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulla sicurezza stradale e resilienza delle aree rurali è orientato a consorzi di ricerca e grandi enti pubblici, con requisiti tecnici e finanziari difficilmente accessibili per una PMI campana di piccole dimensioni. Sebbene il Cilento sia un'area rurale che potrebbe beneficiare tematicamente, la complessità progettuale e la necessità di partnership internazionali rendono questo bando praticamente inaccessibile senza un ruolo da subappaltatore in un consorzio già strutturato.</t>
+          <t>Il bando Horizon focalizzato sulla sicurezza stradale e resilienza delle aree rurali è orientato a consorzi di ricerca, università ed enti pubblici, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un ruolo di partner tecnico specializzato. Le attività finanziabili riguardano ricerca applicata e sviluppo tecnologico su infrastrutture stradali, settori lontani dalle tipiche attività produttive delle PMI locali.</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo richiede consorzi internazionali, capacità di ricerca avanzata in AI e trasporti multimodali, e budget progettuali nell'ordine dei milioni di euro, requisiti difficilmente sostenibili da una PMI campana di piccola dimensione senza un partner capofila universitario o industriale strutturato. Una PMI del Cilento, territorio a vocazione turistica con trasporti prevalentemente locali, avrebbe difficoltà a posizionarsi come soggetto rilevante in un progetto di questa complessità tecnologica.</t>
+          <t>Il bando Horizon Europe richiede consorzi internazionali con forte componente di ricerca avanzata su AI e trasporto multimodale, strutture troppo complesse e costose per una PMI del Cilento; il territorio inoltre non presenta infrastrutture di trasporto multimodale di scala sufficiente a giustificare la partecipazione come soggetto capofila o partner rilevante.</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>Il bando CIVITAS di Horizon Europe è orientato a consorzi di grandi enti pubblici, municipalità e istituti di ricerca per progetti di mobilità urbana sostenibile su scala europea, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile. Inoltre, il contesto rurale e a bassa densità abitativa del Cilento mal si adatta ai requisiti di 'urban mobility' che caratterizzano questo specifico programma.</t>
+          <t>Il bando CIVITAS di Horizon Europe è orientato a consorzi di grandi enti pubblici, autorità urbane e centri di ricerca per progetti di mobilità sostenibile su scala cittadina, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile. Il territorio cilentano, prevalentemente rurale e a bassa densità urbana, non rientra nel profilo target di intervento che richiede contesti metropolitani con sfide complesse di mobilità urbana.</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon CCAM riguarda la ricerca avanzata sull'intelligenza artificiale generativa applicata alla mobilità connessa e autonoma, richiedendo capacità R&amp;D di alto livello, partnership internazionali strutturate e risorse tecniche difficilmente compatibili con una PMI del Cilento. L'accesso è realisticamente riservato a grandi consorzi con centri di ricerca e aziende tech specializzate.</t>
+          <t>Il bando Horizon CCAM riguarda la ricerca avanzata sull'intelligenza artificiale generativa applicata alla mobilità connessa e automatizzata, un settore altamente specializzato che richiede capacità di R&amp;S strutturate, consorziate a livello europeo e difficilmente accessibili a una PMI del Cilento senza un solido network scientifico preesistente. Le spese finanziabili (ricerca, sviluppo tecnologico, dimostrazione) sono orientate a grandi consorzi con laboratori e competenze specifiche in AI e sistemi di trasporto autonomo, lontane dal tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulle batterie al litio di nuova generazione richiede capacità di R&amp;D avanzata, infrastrutture industriali e competenze altamente specializzate nel settore energetico-automotive, del tutto estranee al tessuto produttivo del Cilento e delle PMI campane di piccola dimensione. Consorziarsi con grandi player europei del settore è tecnicamente e organizzativamente fuori portata per la quasi totalità delle PMI locali.</t>
+          <t>Il bando Horizon Europe sulle batterie al litio di nuova generazione è orientato a grandi consorzi industriali e centri di ricerca con capacità tecnologiche avanzate nel settore della mobilità elettrica, settore praticamente assente nel tessuto produttivo del Cilento e delle PMI campane tipiche. I requisiti tecnici, finanziari e di partnership transnazionale rendono questo bando di fatto inaccessibile per una PMI locale di piccola o media dimensione senza una specializzazione specifica in chimica delle batterie o componentistica automotive.</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un partenariato europeo co-finanziato nell'ambito di Horizon Europe, orientato a istituzioni di ricerca, università e grandi enti pubblici che operano su trasformazioni sociali e resilienza: una PMI del Cilento difficilmente possiede i requisiti di accesso (consorzio transnazionale, capacità di ricerca strutturata) e i costi di partecipazione superano ampiamente le possibilità operative di una piccola impresa.</t>
+          <t>Il bando Horizon su trasformazioni sociali e resilienza è orientato a consorzi di ricerca accademici e istituzionali su scala europea, con requisiti di partenariato transnazionale complessi e capacità di ricerca avanzata che una PMI del Cilento difficilmente possiede autonomamente. Non sono previsti finanziamenti diretti per attività produttive o commerciali tipiche delle piccole imprese.</t>
         </is>
       </c>
     </row>
@@ -14057,7 +14057,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa (munizioni, missili e armi esplosive), ambito riservato a grandi industrie della difesa con certificazioni specifiche e capacità produttive militari. Una PMI del Cilento, tipicamente attiva in turismo, agricoltura o artigianato, non dispone dei requisiti tecnici, industriali e di sicurezza necessari per partecipare.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa (munizioni, missili e armi esplosive), un ambito riservato a grandi imprese della difesa, consorzi industriali specializzati e centri di ricerca militare. Una PMI del Cilento o della Campania non dispone delle certificazioni di sicurezza, delle capacità produttive né dei requisiti tecnici necessari per partecipare.</t>
         </is>
       </c>
     </row>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi counter-drone richiede capacità di R&amp;S in tecnologie di difesa avanzate, consorzio europeo e investimenti ingenti, barriere che rendono l'accesso diretto praticamente impossibile per una PMI del Cilento senza essere già inserita in filiere industriali della difesa. Una piccola impresa campana potrebbe al massimo partecipare come subfornitore di un grande prime contractor, ma le probabilità restano molto basse.</t>
+          <t>Il bando EDF (European Defence Fund) sui sistemi anti-drone è destinato a consorzi di grandi imprese della difesa con capacità tecnologiche avanzate e storici nel settore militare: difficilmente accessibile a una PMI del Cilento senza specifiche competenze aerospaziali o difensive certificate. Le PMI possono partecipare solo come subappaltatori o partner minori in consorzi già strutturati, rendendo l'accesso concreto estremamente complesso e incerto.</t>
         </is>
       </c>
     </row>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda missili, munizioni e bombe, settore della difesa ad altissima specializzazione tecnica e normativa, accessibile quasi esclusivamente a grandi prime contractor o laboratori di ricerca militare certificati. Una PMI del Cilento o della Campania, salvo rarissime eccezioni con specifiche certificazioni NATO/difesa, non ha i requisiti tecnici, industriali e di sicurezza necessari per partecipare.</t>
+          <t>Il bando EDF riguarda missili, munizioni e bombe, settore della difesa ad altissima specializzazione che richiede certificazioni NATO, infrastrutture industriali e capacità tecnologiche del tutto estranee al tessuto produttivo delle PMI cilentane e campane in generale. Le procedure di accesso prevedono consorzi internazionali e requisiti di sicurezza che escludono di fatto realtà di piccola e media dimensione.</t>
         </is>
       </c>
     </row>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sulla sorveglianza avanzata delle frontiere richiede competenze altamente specializzate in tecnologie di difesa e sicurezza, oltre a capacità di partecipazione a consorzi europei complessi, caratteristiche difficilmente compatibili con una PMI di piccole dimensioni del Cilento. L'ambito tematico (border surveillance, situational awareness) è lontano dal tessuto produttivo locale, orientato prevalentemente a turismo, agricoltura e agroalimentare.</t>
+          <t>Il bando Horizon sulla sorveglianza avanzata delle frontiere richiede capacità di ricerca e sviluppo tecnologico altamente specializzato (es. sistemi di rilevamento, AI, droni, sensori) tipico di grandi consorzi internazionali o centri di ricerca, rendendo l'accesso estremamente difficile per una PMI del Cilento priva di competenze specifiche in sicurezza e difesa. Il profilo industriale prevalente nella zona (turismo, agricoltura, artigianato) è del tutto disallineato con i requisiti tematici e le partnership necessarie per candidarsi con successo.</t>
         </is>
       </c>
     </row>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede progetti di ricerca e innovazione su larga scala con consorzi internazionali e capacità tecnico-scientifiche elevate, rendendo la partecipazione diretta di una PMI del Cilento molto difficile senza un ruolo da partner in un consorzio già strutturato. Il focus sulla gestione del rischio da disastri naturali potrebbe in teoria riguardare il territorio cilentano (rischio idrogeologico, sismico), ma i requisiti progettuali e amministrativi di Horizon restano proibitivi per una piccola impresa locale senza esperienza pregressa in programmi europei.</t>
+          <t>Il bando Horizon si rivolge principalmente a consorzi di ricerca e grandi organizzazioni con capacità di progettazione europea, rendendo l'accesso diretto per una PMI del Cilento molto complesso senza partner istituzionali. Il focus sulla gestione del rischio da catastrofi naturali potrebbe in teoria coinvolgere imprese del settore tecnologico o ambientale, ma la struttura del programma e i requisiti di rendicontazione Horizon scoraggiano la partecipazione autonoma di piccole realtà locali.</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla consapevolezza del rischio e la preparazione ai disastri è orientato a consorzi di ricerca e grandi enti pubblici, richiedendo capacità progettuali e finanziarie difficilmente accessibili a una PMI del Cilento senza un partner capofila accademico o istituzionale. Sebbene il territorio cilentano sia esposto a rischi idrogeologici e sismici, una PMI non avrebbe i requisiti tecnici per candidarsi autonomamente né le risorse per gestire un progetto Horizon.</t>
+          <t>Il bando Horizon richiede la formazione di consorzi internazionali di ricerca con capacità progettuali e amministrative elevate, tipicamente accessibili a università, enti pubblici o grandi imprese con dipartimenti R&amp;D strutturati. Una PMI del Cilento difficilmente possiede i requisiti tecnici e la rete europea necessaria per candidarsi autonomamente su temi di gestione del rischio e disaster preparedness.</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si focalizza su ricerca avanzata per contrastare l'uso criminale di tecnologie emergenti e accesso lecito ai dati, ambiti tipicamente presidiati da grandi consorzi di ricerca, università e forze dell'ordine. Una PMI del Cilento difficilmente possiede le competenze tecnico-forensi e la struttura progettuale necessarie per competere in questo topic altamente specializzato e a vocazione istituzionale.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata su tecnologie emergenti applicate alla sicurezza e al contrasto criminale, con requisiti di consorzio internazionale e competenze specialistiche difficilmente disponibili in una PMI del Cilento. I costi di partecipazione, la complessità progettuale e il focus su tematiche di lawful access e cybercrime lo rendono accessibile quasi esclusivamente a grandi player tecnologici o enti di ricerca.</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca avanzata sulla valutazione dell'età in contesti di sicurezza e gestione delle frontiere, un ambito altamente specializzato che richiede capacità di ricerca scientifica, partnership con enti accademici e competenze forensi difficilmente disponibili in una PMI del Cilento. Non vi è alcuna attinenza con i settori produttivi prevalenti nell'area (turismo, agricoltura, agroalimentare).</t>
+          <t>Il bando Horizon riguarda la ricerca avanzata sui metodi di valutazione dell'età in contesti di sicurezza e gestione delle frontiere, un ambito altamente specialistico che richiede capacità di ricerca scientifica e partnership con enti accademici o istituzionali difficilmente accessibili a una PMI del Cilento. Non vi è alcuna connessione diretta con i settori produttivi prevalenti nell'area (turismo, agricoltura, artigianato) né con le tipiche competenze di una piccola o media impresa campana.</t>
         </is>
       </c>
     </row>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si focalizza su ricerca avanzata per la sicurezza contro il terrorismo in spazi confinati come le scuole, richiedendo capacità tecnico-scientifiche elevate e partnership con enti di ricerca europei che difficilmente una PMI del Cilento può strutturare autonomamente. Le risorse necessarie e la complessità progettuale lo rendono accessibile quasi esclusivamente a grandi consorzi internazionali o spin-off universitari specializzati in cybersecurity e sicurezza fisica.</t>
+          <t>Il bando Horizon richiede capacità di ricerca e sviluppo tecnologico in ambito sicurezza anti-terrorismo, con consorzialità europea e competenze altamente specializzate difficilmente possedute da una PMI campana di piccole dimensioni. Il contesto del Cilento, a vocazione prevalentemente turistica e agricola, rende ulteriormente remota la rilevanza operativa di questo specifico topic.</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14480,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU sulla prevenzione e investigazione delle persone scomparse è orientato a consorzi di ricerca, forze dell'ordine e grandi enti pubblici, rendendo l'accesso estremamente difficile per una PMI campana del Cilento senza specifiche competenze in sicurezza pubblica o tecnologie forensi. Non finanzia attività produttive o commerciali tipiche delle PMI locali.</t>
+          <t>Il bando Horizon europeo sulle persone scomparse (prevenzione e indagini) è orientato a consorzi di ricerca, forze dell'ordine e grandi organizzazioni specializzate in sicurezza pubblica, rendendo l'accesso estremamente difficile per una PMI del Cilento priva di specifiche competenze forensi o di sicurezza. Non finanzia attività produttive o servizi tipici delle PMI campane, né presenta connessioni con i settori trainanti del territorio come turismo, agricoltura o artigianato.</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e innovazione sulla prevenzione della criminalità e il nesso tra dipendenze e reati, rivolti principalmente a enti di ricerca, università e istituzioni pubbliche con forte capacità progettuale europea. Una PMI del Cilento difficilmente possiede i requisiti tecnici e i partner internazionali necessari per competere in questo tipo di consorzio transnazionale.</t>
+          <t>Il bando Horizon si focalizza su ricerca e prevenzione del crimine legata alle dipendenze, con requisiti consortili complessi e budget elevati tipici di enti di ricerca e istituzioni pubbliche. Una PMI del Cilento difficilmente possiede le competenze scientifiche e la struttura progettuale per competere in questo tipo di call europea.</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su innovazioni tecnologiche dirompenti per la sicurezza civile è orientato a grandi consorzi di ricerca e aziende con capacità R&amp;D strutturate, rendendo molto difficile l'accesso per una PMI del Cilento priva di partnership scientifiche consolidate e delle risorse necessarie per gestire la complessità progettuale e amministrativa di un bando europeo di questa portata.</t>
+          <t>Il bando Horizon finanzia ricerca disruptiva sulla sicurezza civile con requisiti di consorzio internazionale e capacità R&amp;D avanzate, strutturalmente pensato per grandi enti di ricerca e aziende tecnologiche consolidate. Una PMI del Cilento difficilmente dispone delle risorse progettuali, dei partner europei e delle competenze specialistiche richieste per competere in questo tipo di call.</t>
         </is>
       </c>
     </row>
@@ -14616,12 +14616,12 @@
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi europei di ricerca con elevata capacità progettuale e scientifica, risultando di fatto inaccessibile per una PMI del Cilento senza una consolidata rete di partner internazionali e competenze specifiche in climate security e gestione delle crisi climatiche. Le risorse finanziabili riguardano attività di ricerca e sviluppo di scenari pre/post crisi climatica, ambito distante dalle operatività tipiche delle piccole imprese locali.</t>
+          <t>Il bando Horizon richiede la costituzione di consorzi europei con forte componente di ricerca e sviluppo su scenari di sicurezza climatica e preparazione civile, strutture tipicamente accessibili a università, enti di ricerca e grandi organizzazioni, non a PMI campane di piccola dimensione. Una PMI del Cilento potrebbe partecipare solo in qualità di partner secondario all'interno di un consorzio già strutturato, con ruoli marginali e oneri amministrativi elevati.</t>
         </is>
       </c>
     </row>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione in consorzi internazionali con elevata capacità di ricerca e sviluppo, budget e competenze tecniche difficilmente accessibili per una PMI campana di piccole dimensioni, specialmente nel settore della resilienza a disastri naturali e scenari ibridi. Una PMI del Cilento potrebbe partecipare solo come partner junior in un consorzio già strutturato, con ruolo marginale e oneri amministrativi molto elevati.</t>
+          <t>Il bando Horizon EU richiede la partecipazione in consorzi internazionali con forte componente di ricerca e sviluppo su resilienza a disastri naturali e ibridi, strutture tipicamente accessibili a grandi enti di ricerca o aziende con capacità R&amp;D consolidate. Una PMI del Cilento difficilmente possiede i requisiti tecnici e amministrativi per guidare o partecipare competitivamente a progetti di questa complessità, salvo come partner junior in un consorzio già formato.</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi europei con elevata capacità di R&amp;S e risorse per la rendicontazione, barriere difficilmente superabili per una PMI campana di piccole dimensioni. Il focus su tecnologie avanzate per ricerca e soccorso in ambienti pericolosi è molto settoriale e lontano dal tessuto produttivo tipico del Cilento, orientato a turismo, agricoltura e agroalimentare.</t>
+          <t>Il bando Horizon richiede attività di ricerca e sviluppo ad alto contenuto tecnologico in ambito search &amp; rescue e gestione delle emergenze, con consorzî internazionali e capacità progettuali elevate, difficilmente accessibili per una PMI campana di piccole dimensioni senza partner qualificati come università o grandi imprese. Una PMI del Cilento potrebbe partecipare solo in qualità di partner specializzato, ad esempio nel settore delle tecnologie ambientali o del monitoraggio del territorio, ma con probabilità di successo limitata.</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sulla gestione multi-rischio e impatti a cascata (alluvioni, frane, sismi) è orientato a consorzi di ricerca e università, con requisiti di partnership internazionale e capacità tecnico-scientifiche elevate che una PMI del Cilento difficilmente soddisfa autonomamente. L'accesso è realistico solo come partner junior in un consorzio europeo, non come capofila o beneficiario diretto.</t>
+          <t>Il bando Horizon EU sui rischi multi-hazard e impatti a cascata (es. frane, alluvioni, sismi) è orientato a consorzi di ricerca e grandi enti scientifici, con requisiti di partnership internazionale e capacità di R&amp;S difficilmente sostenibili da una PMI campana. Una PMI del Cilento potrebbe partecipare solo in ruolo marginale di partner tecnico-locale, ma la complessità gestionale e i costi di progettazione rendono l'accesso poco pratico senza il supporto di un ente di ricerca capofila.</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe riguarda lo sviluppo di sistemi di comunicazione critica per la sicurezza civile a livello europeo, richiedendo competenze altamente specializzate in cybersecurity e telecomunicazioni e la partecipazione a consorzi internazionali complessi. Una PMI del Cilento difficilmente possiede i requisiti tecnici e le capacità progettuali per competere in questo tipo di chiamata, orientata a grandi centri di ricerca e industrie della difesa/sicurezza.</t>
+          <t>Il bando Horizon EU riguarda lo sviluppo di sistemi critici di comunicazione per la sicurezza civile in ambito europeo, richiedendo competenze altamente specializzate in cybersecurity e telecomunicazioni e la partecipazione a consorzi internazionali. Una PMI del Cilento difficilmente dispone delle capacità tecniche e della rete di partner necessarie per competere in questo tipo di progetto di ricerca avanzata.</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede competenze altamente specializzate in sicurezza delle infrastrutture critiche e stress testing, oltre a capacità di partecipazione a consorzi europei con risorse dedicate alla rendicontazione: barriere difficilmente superabili per una PMI del Cilento senza esperienza pregressa in progetti UE di ricerca e sviluppo. L'ambito tematico (resilienza infrastrutturale) è inoltre distante dai settori produttivi prevalenti nel territorio cilentano come turismo, agricoltura e artigianato.</t>
+          <t>Il bando Horizon richiede competenze altamente specializzate in cybersecurity e resilienza delle infrastrutture critiche, con consorzî internazionali e capacità di R&amp;D avanzata difficilmente accessibili a una PMI del Cilento. Le PMI di piccola dimensione possono partecipare solo come partner secondari in progetti guidati da grandi enti di ricerca o università.</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è destinato a consorzi di ricerca e forze dell'ordine per sviluppare capacità operative contro sfide climatiche in ambito sicurezza pubblica, un contesto molto distante dalle attività tipiche di una PMI campana o cilentana. L'accesso richiede partnership istituzionali complesse e competenze specialistiche in sicurezza/difesa difficilmente disponibili in una piccola impresa locale.</t>
+          <t>Il bando Horizon è destinato a consorzi di ricerca, università e forze dell'ordine per sviluppare tecnologie e metodologie di contrasto alle sfide climatiche in ambito sicurezza pubblica: una PMI del Cilento difficilmente possiede i requisiti tecnici e la rete di partner istituzionali necessari per partecipare competitivamente. Non finanzia attività produttive, turistiche o agricole tipiche del tessuto imprenditoriale locale.</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla demand-led innovation in security è orientato a grandi consorzi di ricerca, enti pubblici e industrie della difesa/sicurezza, con requisiti tecnici e burocratici elevati difficilmente sostenibili da una PMI campana di piccola dimensione. Le PMI del Cilento, prevalentemente attive in turismo, agricoltura e artigianato, non hanno tipicamente profilo né capacità progettuale adeguati per competere in ambiti come sicurezza tecnologica o cyber-security a livello europeo.</t>
+          <t>Il bando Horizon 'Demand-led innovation in security' è orientato a grandi consorzi di ricerca e soggetti istituzionali nel settore della sicurezza pubblica, con requisiti tecnici e amministrativi difficilmente sostenibili per una PMI del Cilento senza un partner capofila strutturato. Le spese finanziabili riguardano R&amp;S avanzata in ambiti come cybersecurity e sicurezza delle infrastrutture critiche, settori lontani dal tessuto produttivo locale prevalentemente basato su turismo, agricoltura e artigianato.</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la prevenzione del bioterrorismo legato alla biologia sintetica, un ambito altamente specializzato che richiede competenze di ricerca avanzata e infrastrutture di sicurezza difficilmente disponibili in una PMI del Cilento o della Campania in generale. Non sono finanziabili attività produttive o servizi tipici delle piccole imprese locali, rendendo l'accesso concreto quasi impossibile senza partnership con enti di ricerca o università.</t>
+          <t>Il bando riguarda la prevenzione del bioterrorismo tramite biologia sintetica, un ambito altamente specializzato che richiede competenze di ricerca avanzata e infrastrutture di sicurezza difficilmente presenti in una PMI campana, soprattutto nel contesto rurale e turistico del Cilento. Non sono previste attività finanziabili rilevanti per le tipologie produttive o di servizio tipiche di questa area geografica.</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda appalti pubblici pre-commerciali per soluzioni innovative nel settore della sicurezza, rivolti principalmente a grandi soggetti pubblici e consorzi di ricerca come acquirenti, non a PMI come fornitori diretti di fondi. Una PMI del Cilento potrebbe partecipare solo indirettamente come subfornitore tecnologico, ma la complessità procedurale e la dimensione europea del bando lo rendono poco accessibile senza partnership strutturate.</t>
+          <t>Il bando riguarda il procurement pubblico di innovazione nel settore sicurezza, strumento pensato principalmente per grandi imprese tecnologiche e consorzi con capacità di risposta a commesse pubbliche europee complesse. Una PMI del Cilento difficilmente possiede le competenze specifiche nel settore security o la struttura organizzativa per partecipare a procedure di appalto pre-commerciale a livello UE.</t>
         </is>
       </c>
     </row>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si concentra su ricerca e sicurezza della transizione verde in aree urbane e peri-urbane, richiedendo consorzi internazionali con elevata capacità di ricerca: difficilmente accessibile per una PMI del Cilento, territorio prevalentemente rurale e privo di strutture di ricerca avanzata necessarie per competere in questi programmi.</t>
+          <t>Il bando Horizon focalizzato sulla sicurezza della transizione verde in aree urbane e periurbane richiede consorzi internazionali con capacità di ricerca avanzata, budget elevati e strutture progettuali complesse, difficilmente accessibili per una PMI del Cilento operante in un contesto prevalentemente rurale e privo di infrastrutture urbane rilevanti. Una piccola impresa campana potrebbe partecipare solo come partner junior in un consorzio europeo, ma le barriere di accesso restano molto alte.</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>Il programma I3 finanzia investimenti per l'innovazione interregionale con focus su reti tra regioni europee e grandi ecosistemi, richiedendo capacità progettuali e partenariati internazionali difficilmente accessibili per una PMI del Cilento senza intermediari. Le spese finanziabili riguardano R&amp;S e trasferimento tecnologico su scala sovranazionale, contesto strutturalmente sfavorevole per micro e piccole imprese locali.</t>
+          <t>Il bando I3 Strand 1 finanzia investimenti interregionali in innovazione con focus su ecosistemi e reti transregionali, richiedendo partnership tra più regioni europee e capacità progettuali elevate, difficilmente accessibili per una PMI del Cilento senza un coordinatore istituzionale. Le PMI possono partecipare solo come partner di consorzi strutturati, non come soggetti capofila, il che limita fortemente l'accesso diretto e il controllo sui fondi.</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>Il bando I3 Strand 2a è uno strumento interregionale europeo orientato a investimenti in innovazione su scala macro-regionale, tipicamente rivolto a grandi partenariati istituzionali o cluster, con requisiti di capacità progettuale e finanziaria difficilmente compatibili con una PMI singola del Cilento. L'accesso realistico richiederebbe la partecipazione come soggetto in un consorzio strutturato, rendendo il percorso complesso e incerto per realtà di piccola dimensione.</t>
+          <t>Il programma I3 finanzia investimenti in innovazione interregionale con focus su grandi ecosistemi e reti transregionali, richiedendo partnership complesse tra regioni e soggetti pubblici/privati strutturati: una PMI del Cilento difficilmente può accedere autonomamente senza essere integrata in un consorzio o cluster già attivo. Le spese finanziabili riguardano R&amp;S e trasferimento tecnologico avanzato, settori in cui le micro e piccole imprese locali hanno raramente la capacità progettuale richiesta.</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>Il programma MSCA Doctoral Networks finanzia reti transnazionali per la formazione di dottorandi e richiede la costituzione di consorzi internazionali con università e centri di ricerca, strutture organizzative e capacità amministrative del tutto estranee alla tipica PMI del Cilento. Una piccola impresa potrebbe al massimo partecipare come partner associato, ma senza accesso diretto ai fondi e con oneri burocratici sproporzionati.</t>
+          <t>Le MSCA Doctoral Networks finanziano consorzi internazionali per la formazione di dottorandi, richiedendo partnership con università e centri di ricerca europei: una PMI del Cilento difficilmente ha le strutture amministrative e la rete accademica per guidare o partecipare attivamente a tali consorzi. Il bando è pensato principalmente per istituzioni accademiche e grandi organizzazioni con capacità di gestione di progetti H2020/Horizon.</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia reti dottorali europee per la ricerca in intelligenza artificiale applicata alla scienza, richiedendo la costituzione di consorzi internazionali con università e centri di ricerca: una struttura organizzativa e amministrativa fuori dalla portata di una PMI del Cilento. Non sono previsti finanziamenti diretti per attività produttive o di innovazione aziendale tipiche delle piccole imprese locali.</t>
+          <t>Il bando finanzia reti dottorali europee per la ricerca in intelligenza artificiale applicata alla scienza, richiedendo la costituzione di consorzi accademici transnazionali: una PMI del Cilento difficilmente dispone delle strutture di ricerca e dei partner universitari necessari per candidarsi come soggetto proponente. L'unica finestra di partecipazione sarebbe come partner industriale in un consorzio già strutturato, ruolo che richiede competenze specializzate in AI e risorse dedicate alla supervisione di dottorandi.</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>Il programma EIC STEP Scale Up è rivolto a startup e PMI innovative già selezionate dall'European Innovation Council con un track record tecnologico avanzato, requisiti difficilmente soddisfatti da una PMI tipica del Cilento. Le risorse finanziano scale-up tecnologici ad alto rischio in settori strategici europei (deep tech, biotech, cleantech), escludendo di fatto le PMI tradizionali del territorio.</t>
+          <t>Il programma EIC STEP Scale Up è orientato a startup e PMI ad alto contenuto tecnologico già selezionate dall'European Innovation Council, con requisiti di scala e track record innovativo difficilmente raggiungibili da una PMI tradizionale del Cilento. Le risorse finanziate riguardano sviluppo tecnologico deeptech e scale-up internazionale, contesti lontani dalla struttura media delle imprese locali campane.</t>
         </is>
       </c>
     </row>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si focalizza sulla ricerca e innovazione nel contrasto al disagio abitativo e ai senza dimora attraverso infrastrutture sociali coordinate, un ambito molto distante dalle attività tipiche di una PMI del Cilento. I destinatari privilegiati sono enti pubblici, università e organizzazioni no-profit, rendendo l'accesso di una piccola impresa privata campana estremamente difficile e poco strategico.</t>
+          <t>Il bando Horizon si focalizza su infrastrutture sociali coordinate per il contrasto al disagio abitativo grave (senza fissa dimora) in contesti urbani, con target tipicamente rivolto a enti pubblici, università e organizzazioni no-profit. Una PMI del Cilento non rientra tra i beneficiari naturali e il tema è distante dalle attività produttive tipiche del territorio.</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi internazionali con forte componente di ricerca e sviluppo, budget elevati e capacità progettuali complesse, difficilmente accessibili per una PMI del Cilento senza un solido network europeo. Una piccola impresa edile o dell'impiantistica locale potrebbe partecipare solo come partner junior in un consorzio già strutturato, con ruolo marginale.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca e sviluppo avanzata, partnership internazionali e strutture amministrative complesse, difficilmente accessibili per una PMI del Cilento senza esperienza pregressa in progetti europei. Le soluzioni di comfort termico negli edifici potrebbero teoricamente interessare imprese edili o di efficienza energetica, ma i requisiti consortili e la competizione globale rendono la partecipazione diretta poco praticabile senza un capofila universitario o un grande partner industriale.</t>
         </is>
       </c>
     </row>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede progetti di ricerca e innovazione su scala europea con partnership internazionali e capacità di gestione amministrativa complessa, strutturalmente difficile da sostenere per una PMI del Cilento senza esperienza pregressa in progetti UE. Il focus sulla progettazione spaziale di quartieri urbani è inoltre poco rilevante per il tessuto economico locale, prevalentemente orientato a turismo, agricoltura e piccolo commercio.</t>
+          <t>Il bando Horizon focalizzato sulla progettazione spaziale dei quartieri richiede capacità di ricerca avanzata, consorzio internazionale e risorse progettuali difficilmente accessibili a una PMI di piccola dimensione del Cilento, territorio a bassa densità urbana e lontano dai cluster di ricerca europei. Una PMI locale difficilmente possiede i requisiti tecnici e amministrativi per partecipare autonomamente a un progetto di questa natura.</t>
         </is>
       </c>
     </row>
@@ -15514,7 +15514,7 @@
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a consorzi di ricerca e grandi enti pubblici per progetti di rigenerazione urbana e riuso di spazi abbandonati, con requisiti di partenariato internazionale difficilmente accessibili a una PMI del Cilento in autonomia. Una piccola impresa potrebbe partecipare solo come partner junior di un consorzio guidato da università o comuni, con ruolo marginale e bassa probabilità di successo.</t>
+          <t>Il bando Horizon UE richiede consorzi internazionali, capacità di ricerca avanzata e rendicontazione complessa, barriere difficilmente superabili da una PMI del Cilento in autonomia. L'obiettivo sul riuso di spazi vacanti o sottoutilizzati potrebbe teoricamente interessare operatori immobiliari o del turismo locale, ma l'accesso pratico resta subordinato alla partecipazione a partenariati europei già strutturati.</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca accademica e istituzionale sulla comprensione dei mercati dei capitali applicati ai progetti New European Bauhaus, richiedendo consorzi di ricerca e competenze altamente specializzate in finanza urbana. Una PMI del Cilento non ha né il profilo istituzionale né le capacità di ricerca richieste per partecipare come soggetto beneficiario diretto.</t>
+          <t>Il bando Horizon finanzia ricerca accademica e istituzionale sulla comprensione dei meccanismi dei mercati di capitali applicati ai progetti New European Bauhaus, con focus su quartieri urbani: non è uno strumento diretto per PMI operative in aree rurali come il Cilento, e richiede consorzi di ricerca qualificati difficilmente accessibili a una piccola impresa campana. Una PMI del settore edilizio o della rigenerazione urbana potrebbe al massimo partecipare come partner associato, ma senza benefici finanziari diretti.</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, partnership internazionali e progettazione complessa, barriere difficilmente superabili per una PMI del Cilento senza esperienza pregressa in progetti europei. Il focus sullo 'spazio verticale' (es. facciate verdi, infrastrutture urbane) è poco allineato con il tessuto produttivo locale, prevalentemente agricolo, turistico e artigianale.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzio internazionale e risorse amministrative difficilmente sostenibili da una PMI del Cilento senza partner strutturati; il focus sulle 'soluzioni innovative per lo spazio verticale' è molto tecnico-specialistico e lontano dal tessuto produttivo locale (agricoltura, turismo, artigianato).</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi europei, capacità di ricerca avanzata e gestione progettuale complessa, rendendo l'accesso diretto da parte di una PMI del Cilento molto difficile senza un partner capofila strutturato. Il focus su manutenzione sostenibile degli edifici esistenti potrebbe in teoria interessare imprese edili o energetiche locali, ma solo come partner junior in progetti già costruiti da enti di ricerca o grandi aziende.</t>
+          <t>Il bando Horizon UE richiede partnership europee, capacità di ricerca avanzata e rendicontazione complessa, barriere difficilmente superabili per una PMI campana di piccole dimensioni. Una piccola impresa del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio, ma difficilmente come capofila o beneficiario diretto.</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a consorzi di ricerca accademica e istituzionale focalizzati sullo studio dell'esperienza dei residenti nei quartieri urbani in relazione alla salute e al benessere, con requisiti di partnership transnazionale complessi e capacità di ricerca scientifica difficilmente compatibili con una PMI del Cilento. Non sono previste tipologie di spesa o settori beneficiari rilevanti per attività produttive o commerciali tipiche delle piccole imprese campane.</t>
+          <t>Il bando Horizon focalizzato sulla ricerca accademica sull'esperienza degli abitanti nei quartieri e il loro benessere richiede competenze di ricerca scientifica avanzata e partnership con università o enti di ricerca, strutture difficilmente accessibili per una PMI campana del Cilento. Non sono previste attività tipicamente finanziabili per le PMI locali come sviluppo prodotto, servizi o investimenti produttivi.</t>
         </is>
       </c>
     </row>
@@ -15744,12 +15744,12 @@
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sul contrasto al disagio abitativo tramite approcci housing-led è orientato a consorzi di ricerca, università ed enti pubblici con forte componente scientifica, rendendo l'accesso diretto per una PMI del Cilento estremamente complesso e improbabile senza un ruolo marginale in un partenariato internazionale strutturato. Il tema (homelessness e New European Bauhaus) non corrisponde alle attività tipiche di una piccola impresa campana operante in settori produttivi o di servizi locali.</t>
+          <t>Il bando Horizon si concentra su approcci innovativi al disagio abitativo ispirati al New European Bauhaus, con requisiti consortili complessi e budget tipicamente nell'ordine dei milioni di euro, rendendolo di fatto inaccessibile per una PMI campana senza una rete consolidata di partner accademici e istituzionali europei. Per una PMI del Cilento, il tema del senza fissa dimora è inoltre lontano dal tessuto produttivo locale, orientato prevalentemente verso turismo, agricoltura e artigianato.</t>
         </is>
       </c>
     </row>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>L'EIC Accelerator è rivolto a startup e PMI deep-tech con tecnologie altamente innovative e scalabili a livello europeo, con grant fino a 2,5M€ e investimenti equity fino a 15M€, ma richiede un profilo di innovazione dirompente e capacità di internazionalizzazione difficilmente compatibili con le PMI tradizionali del Cilento. Il processo selettivo è estremamente competitivo e complesso, con tassi di successo inferiori al 5%, rendendolo poco accessibile per realtà locali di piccola dimensione prive di un team dedicato alla ricerca e sviluppo.</t>
+          <t>L'EIC Accelerator è orientato a startup e PMI ad alto contenuto tecnologico con ambizioni di scala europea o globale, con finanziamenti misti (grant fino a 2,5M€ + equity fino a 15M€) che richiedono innovazioni breakthrough difficilmente raggiungibili da PMI tradizionali del Cilento. Il processo selettivo è estremamente competitivo e richiede capacità di presentazione in inglese, roadmap di internazionalizzazione e profili di rischio/rendimento tipici di tech company, lontani dalla struttura media delle PMI campane.</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di sensori quantistici per la navigazione inerziale, un settore ad altissima intensità tecnologica e di ricerca che richiede competenze specialistiche avanzate (fisica quantistica, ingegneria aerospaziale) tipicamente non presenti in una PMI del Cilento o della Campania in generale. Le sfide 'Grand Challenge' di Horizon sono orientate a grandi consorzi di ricerca e aziende deep-tech, rendendo la partecipazione diretta di una piccola o media impresa locale estremamente difficile e improbabile.</t>
+          <t>Il bando finanzia ricerca avanzata su sensori quantistici per la navigazione inerziale, un settore altamente specializzato che richiede competenze scientifiche di frontiera e infrastrutture da laboratorio, difficilmente accessibili a una PMI del Cilento priva di un dipartimento R&amp;D dedicato. Le opportunità per le PMI locali si limiterebbero a un ruolo di partner marginale in consorzi guidati da grandi player tecnologici o università, rendendo la partecipazione diretta praticamente impraticabile.</t>
         </is>
       </c>
     </row>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulle tecnologie quantistiche e la loro standardizzazione richiede competenze altamente specializzate e strutture di ricerca avanzate, tipiche di grandi aziende tech o enti accademici. Una PMI del Cilento, anche tecnologicamente orientata, difficilmente dispone delle capacità tecniche e dei partner internazionali necessari per competere in questo ambito.</t>
+          <t>Il bando riguarda lo sviluppo di standard tecnici per le tecnologie quantistiche nell'ambito di Horizon Europe, un settore altamente specializzato che richiede competenze di ricerca avanzata e strutture da laboratorio difficilmente disponibili in una PMI del Cilento. L'accesso è di fatto limitato a grandi consorzi di ricerca, università e aziende tech di scala europea, escludendo nella pratica le piccole imprese locali.</t>
         </is>
       </c>
     </row>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia lo sviluppo di piattaforme tecnologiche per il quantum computing fotonico su larga scala, un settore altamente specializzato che richiede infrastrutture di ricerca avanzate e competenze scientifiche di frontiera, tipicamente accessibili solo a grandi consorzi industriali o centri di ricerca europei. Una PMI del Cilento o della Campania, salvo rarissime eccezioni in nicchie di fotonica o tecnologie quantistiche, non possiede i requisiti tecnici né la capacità finanziaria per partecipare competitivamente a questo tipo di progetto Horizon.</t>
+          <t>Il bando riguarda lo sviluppo di piattaforme tecnologiche per il quantum computing fotonico su larga scala, un settore altamente specializzato che richiede competenze di ricerca avanzata e investimenti enormi, tipici di grandi consorzi industriali o centri di ricerca europei. Una PMI del Cilento o della Campania difficilmente possiede le capacità tecniche e la massa critica necessarie per partecipare competitivamente a questo tipo di progetto Horizon.</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su Quantum Machine Learning richiede capacità di ricerca avanzata, partnership internazionali e competenze altamente specialistiche che difficilmente una PMI del Cilento può sostenere autonomamente. Le risorse necessarie per partecipare competitivamente a bandi Horizon di questa natura superano le possibilità strutturali e finanziarie della maggior parte delle piccole e medie imprese campane.</t>
+          <t>Il programma Horizon UE su Quantum Machine Learning richiede capacità di ricerca avanzata, partnership internazionali e strutture di R&amp;D difficilmente disponibili in una PMI del Cilento; i costi di partecipazione e la complessità tecnica lo rendono di fatto inaccessibile senza un consorzio con università o grandi aziende tech.</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>I Framework Loans BEI sono strumenti finanziari destinati tipicamente a intermediari bancari o grandi enti pubblici, con soglie minime di accesso elevate che rendono molto difficile per una PMI del Cilento accedervi direttamente senza passare per programmi nazionali o regionali dedicati. Una piccola impresa campana dovrebbe cercare strumenti derivati (es. prestiti agevolati veicolati da banche convenzionate) piuttosto che candidarsi direttamente a questo bando.</t>
+          <t>I Framework Loans BEI/JTM sono strumenti finanziari destinati tipicamente a intermediari bancari o grandi progetti infrastrutturali nelle regioni in transizione, con soglie minime di accesso e procedure complesse che li rendono difficilmente fruibili direttamente da una PMI del Cilento senza il tramite di un istituto finanziario abilitato. Una PMI dovrebbe verificare se banche locali o Confidi campani abbiano attivato linee di credito agevolate a valere su questi fondi, che rappresenterebbe l'unico canale praticabile.</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>I bandi 'Standalone Projects' del Just Transition Mechanism UE sono tipicamente rivolti a grandi investimenti in territori di transizione industriale (come aree carbonifere), con soglie minime di finanziamento elevate e requisiti tecnico-amministrativi complessi; la Campania e il Cilento non rientrano tra le aree prioritarie JTM italiane, rendendo questo strumento difficilmente accessibile per una PMI locale di piccole dimensioni.</t>
+          <t>I bandi 'Standalone projects' del Just Transition Mechanism UE sono tipicamente rivolti a grandi progetti infrastrutturali o industriali in territori di transizione energetica, con soglie di investimento elevate difficilmente accessibili a una PMI del Cilento, area peraltro non classificata tra le zone JTM prioritarie italiane. La complessità procedurale e i requisiti di capacità finanziaria rendono questo strumento poco praticabile per realtà di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi di difesa aerea e missilistica è destinato a grandi consorzi industriali del settore difesa con capacità tecnologiche e finanziarie molto elevate, escludendo di fatto le PMI del Cilento o della Campania prive di specializzazione aerospaziale/militare. I requisiti tecnici, le certificazioni di sicurezza NATO/UE e i volumi di investimento richiesti rendono questo bando inaccessibile per una piccola o media impresa locale.</t>
+          <t>Il bando EDF per sistemi di difesa aerea e missilistica è destinato a grandi consorzi industriali del settore difesa con capacità tecnologiche e finanziarie avanzate, del tutto inaccessibili per una PMI del Cilento. Le PMI campane di piccola dimensione non dispongono delle certificazioni, infrastrutture e requisiti tecnici richiesti per partecipare a programmi europei di armamenti ad alta complessità.</t>
         </is>
       </c>
     </row>
@@ -16172,7 +16172,7 @@
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa spaziale e sistemi C5ISR (Command, Control, Communications, Computers, Combat Systems, Intelligence, Surveillance and Reconnaissance), richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. L'accesso è praticamente precluso a realtà locali di piccole dimensioni senza partnership consolidate con grandi player della difesa o dell'aerospazio.</t>
+          <t>Il bando EDF su sistemi C5ISR (Command, Control, Communications, Computers, Cyber, Intelligence, Surveillance and Reconnaissance) e prodotti spaziali è orientato a grandi player della difesa e dell'aerospazio, richiedendo capacità tecnologiche, certificazioni e partnership consorziali difficilmente accessibili a una PMI del Cilento. Le PMI di piccola dimensione possono partecipare solo come subfornitori di grandi prime contractor, rendendo l'accesso diretto estremamente improbabile.</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per piattaforme terrestri e navali richiede capacità tecnologiche avanzate nel settore della difesa, consorzi multinazionali e investimenti in R&amp;S difficilmente sostenibili da una PMI del Cilento senza una filiera industriale difensiva consolidata. L'accesso è praticamente riservato a grandi contractor o PMI già integrate in supply chain militari europee.</t>
+          <t>Il bando EDF per piattaforme terrestri e navali richiede capacità industriali di difesa, consorzi internazionali e investimenti in R&amp;S difficilmente sostenibili da una PMI del Cilento. L'accesso è realisticamente riservato a grandi player della difesa o a PMI altamente specializzate in componentistica militare, categoria quasi assente nel tessuto produttivo campano meridionale.</t>
         </is>
       </c>
     </row>
@@ -16261,12 +16261,12 @@
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi unmanned e counter-unmanned è destinato a consorzi di ricerca e difesa con elevate capacità tecnologiche e finanziarie, richiedendo competenze aerospaziali/militari specialistiche difficilmente presenti in una PMI del Cilento. I requisiti di partecipazione transnazionale e gli investimenti necessari in R&amp;S avanzata lo rendono sostanzialmente inaccessibile per realtà produttive di piccola dimensione senza un solido posizionamento nel settore difesa.</t>
+          <t>Il bando EDF sui sistemi unmanned e counter-unmanned è destinato a consorzi di ricerca e industria della difesa con capacità tecnologiche avanzate e requisiti di sicurezza NATO/UE, del tutto estranei al profilo tipico di una PMI campana del Cilento. I costi di partecipazione, la complessità burocratica e i requisiti di clearance di sicurezza rendono questo bando inaccessibile per realtà di piccola-media dimensione senza esperienza nel settore difesa.</t>
         </is>
       </c>
     </row>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia la ricerca e sviluppo di componenti elettronici chiave per la difesa, richiedendo capacità tecnologiche avanzate e consorzi multinazionali che escludono di fatto le PMI di piccola dimensione del Cilento. Le spese finanziabili riguardano R&amp;S in ambito difesa, settore altamente specializzato e lontano dal tessuto produttivo locale.</t>
+          <t>Il bando EDF (European Defence Fund) sui componenti elettronici chiave è destinato a consorzi di grandi imprese e centri di ricerca nel settore della difesa, con requisiti tecnici, finanziari e di sicurezza molto elevati che rendono l'accesso praticamente impossibile per una PMI del Cilento senza una filiera industriale difesa già consolidata. Una piccola o media impresa campana potrebbe al massimo partecipare come subappaltatore di un consorzio, ma solo se già attiva nella produzione di componentistica elettronica certificata per applicazioni militari.</t>
         </is>
       </c>
     </row>
@@ -16360,7 +16360,7 @@
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF 'Platforms and end-products' finanzia lo sviluppo di sistemi d'arma e piattaforme militari complesse, richiedendo capacità industriali di difesa, consorzi internazionali e investimenti ingenti che esulano completamente dalle possibilità di una PMI del Cilento. Il settore difesa europeo è dominato da grandi prime contractor come Leonardo o Thales, rendendo la partecipazione diretta di una piccola impresa campana praticamente inaccessibile.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia lo sviluppo di piattaforme e prodotti finali nel settore della difesa, richiedendo consorzi multinazionali con capacità tecnologiche e industriali avanzate del comparto difesa. Una PMI del Cilento difficilmente possiede le competenze specifiche, le certificazioni di sicurezza e la rete di partner internazionali necessarie per partecipare competitivamente a questo tipo di call.</t>
         </is>
       </c>
     </row>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>I Strategic Nature Projects LIFE sono strumenti complessi destinati principalmente a enti pubblici, autorità di gestione e grandi organizzazioni ambientali, con requisiti di partenariato transnazionale e capacità amministrative elevate che escludono di fatto le PMI come beneficiarie dirette. Una piccola impresa del Cilento potrebbe al massimo partecipare come partner associato in progetti legati alla biodiversità o alla gestione di aree Natura 2000, ma difficilmente come capofila o beneficiario principale.</t>
+          <t>Il programma LIFE Strategic Nature Projects è orientato a grandi interventi sistemici di conservazione della natura e biodiversità, tipicamente gestiti da enti pubblici, autorità regionali o grandi organizzazioni ambientali; una PMI del Cilento difficilmente può accedere direttamente come capofila, potendo al più partecipare come partner in progetti coordinati da soggetti istituzionali.</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>I progetti integrati strategici LIFE sono strumenti complessi pensati per enti pubblici, autorità regionali o grandi organizzazioni in grado di coordinare interventi su scala territoriale ampia; una PMI del Cilento difficilmente può candidarsi come capofila o sostenere i requisiti amministrativi e finanziari richiesti, potendo al massimo partecipare come partner secondario in un consorzio già strutturato.</t>
+          <t>I Strategic Integrated Projects LIFE sono strumenti complessi destinati a soggetti istituzionali o grandi consorzi pubblici per implementare piani climatici su scala territoriale ampia; una PMI del Cilento difficilmente può candidarsi autonomamente come lead partner, potendo al massimo partecipare come soggetto associato in progetti guidati da enti pubblici regionali.</t>
         </is>
       </c>
     </row>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="I341" s="2" t="inlineStr">
         <is>
-          <t>I progetti LIFE Strategic Integrated Projects sono strumenti complessi pensati per enti pubblici, autorità regionali e grandi organizzazioni ambientali, con requisiti di partenariato transnazionale e budget multimilionari difficilmente gestibili da una PMI. Una piccola impresa del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio, ma difficilmente come capofila o beneficiario diretto.</t>
+          <t>I progetti LIFE Strategic Integrated Projects sono strumenti complessi destinati principalmente a enti pubblici, autorità regionali e grandi organizzazioni ambientali, con requisiti di partenariato transnazionale e budget elevati difficilmente gestibili da una PMI. Una piccola impresa del Cilento potrebbe al massimo partecipare come partner associato, ma non come beneficiario principale.</t>
         </is>
       </c>
     </row>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/ON-nuove-imprese-tasso-zero?from=/per-chi-vuole-fare-impresa/incentivi</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/ON-nuove-imprese-tasso-zero</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/smartstart-italia?from=/per-chi-vuole-fare-impresa/incentivi</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/smartstart-italia</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19/06/2026 16:43</t>
+          <t>20/06/2026 12:41</t>
         </is>
       </c>
     </row>

--- a/bandi_campania.xlsx
+++ b/bandi_campania.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia pratiche di produzione integrata per aziende agricole campane, con contributi annuali per l'adozione di metodi colturali a basso impatto ambientale: particolarmente rilevante per le PMI agricole del Cilento che coltivano produzioni tipiche come olivo, vite e ortaggi, già orientate a standard di qualità certificata.</t>
+          <t>Il bando finanzia pratiche di produzione integrata per le aziende agricole campane, con pagamenti annuali per ettaro coltivato secondo disciplinari a basso impatto ambientale: particolarmente rilevante per le PMI agricole del Cilento che producono olivicoltura, orticoltura e frutticoltura tipiche del territorio. La scadenza al 30 giugno 2026 (con possibilità di presentazione tardiva fino al 25 luglio con penale progressiva) lascia tempo sufficiente per organizzare la documentazione necessaria.</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia le aziende agricole che adottano tecniche di lavorazione ridotta o minima del suolo (es. semina su sodo, strip-till), pratiche molto diffuse nelle aree collinari e olivicole del Cilento; per una PMI agricola campana rappresenta un contributo diretto a fronte di impegni agronomici già compatibili con le coltivazioni tipiche locali come olivo e cereali.</t>
+          <t>Il bando finanzia pratiche agricole a ridotta lavorazione del suolo nell'ambito del Piano Strategico PAC, con pagamenti diretti agli agricoltori attivi: particolarmente rilevante per le PMI agricole del Cilento che coltivano oliveti, vigneti o seminativi e possono accedere a contributi annuali adottando tecniche come la semina su sodo o la lavorazione minima. La scadenza al 30 giugno 2026 (con possibilità di proroga con penale fino al 25 luglio) lascia margini operativi concreti per presentare domanda tramite CAA.</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia direttamente gli allevatori che conservano razze animali autoctone a rischio di erosione genetica, una realtà diffusa nel Cilento dove sopravvivono razze come il Podolico e la capra Cilentana; i pagamenti annuali per ettaro/capo rappresentano un sostegno economico concreto e ricorrente per piccole aziende zootecniche che già praticano questo tipo di allevamento estensivo.</t>
+          <t>Il bando finanzia allevatori che conservano razze animali locali a rischio di estinzione, con pagamenti annuali per capo allevato: per una PMI zootecnica del Cilento — area ricca di razze autoctone come il Podolico o la Pezzata Rossa — rappresenta un'opportunità concreta di ottenere sostegno economico continuativo a fronte di pratiche già in essere. La scadenza al 30 giugno 2026, con possibilità di invio tardivo fino al 25 luglio con penale progressiva, lascia tempo sufficiente per organizzare la domanda.</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia impegni silvoambientali e climatici per superfici forestali e agricole, risultando particolarmente strategico per PMI agro-forestali del Cilento, area ad alta densità boschiva e vocazione rurale, che possono accedere a pagamenti annuali per pratiche di gestione sostenibile del bosco e del territorio. La scadenza al 30 giugno 2026 con possibilità di proroga al 25 luglio (con penale progressiva) offre tempo sufficiente per strutturare la domanda.</t>
+          <t>Il bando finanzia impegni silvoambientali e climatici per aziende agricole e forestali, categorie molto diffuse nel territorio del Cilento, dove la gestione di boschi, oliveti e pascoli è centrale: una PMI agricola può accedere a pagamenti compensativi per pratiche sostenibili come la gestione forestale, la tutela della biodiversità e la riduzione delle emissioni. La scadenza al 30 giugno 2026 (con possibilità di proroga al 25 luglio con penale progressiva) lascia tempo utile per preparare la documentazione tramite un CAA o consulente agricolo abilitato.</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Il bando sostiene imprese agricole e forestali del territorio campano, incluso il Cilento, riconoscendo pagamenti compensativi per il mantenimento di superfici forestate o sistemi agroforestali già impegnati nelle programmazioni precedenti: ideale per PMI agricole che gestiscono boschi, imboschimenti o colture miste albero-pascolo e vogliono continuare a percepire il sostegno annuale. La scadenza al 30 giugno 2026 (con possibilità di presentazione tardiva fino al 25 luglio con penale progressiva) lascia tempo sufficiente per la raccolta della documentazione.</t>
+          <t>Il bando finanzia il mantenimento di imboschimenti e sistemi agroforestali già avviati in precedenti programmazioni, risultando direttamente applicabile per aziende agricole e forestali del Cilento che hanno superfici boschive o agroforestali già in gestione. Le PMI del settore agricolo-forestale campano possono accedere ai pagamenti annuali per la conservazione di questi ecosistemi, con scadenza al 30 giugno 2026 e possibilità di presentazione tardiva fino al 25 luglio con penale progressiva.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia direttamente le aziende agricole che adottano o mantengono pratiche di produzione biologica, con pagamenti annuali a compensazione dei maggiori costi e mancati redditi: particolarmente rilevante per le PMI agricole del Cilento, territorio vocato a produzioni di qualità come olio, cereali e ortaggi tipici, dove la conversione al biologico rappresenta un vantaggio competitivo concreto e certificabile.</t>
+          <t>Il bando finanzia direttamente le aziende agricole che adottano pratiche di produzione biologica, con pagamenti annuali particolarmente rilevanti per le PMI agricole del Cilento, territorio vocato a colture tradizionali (oliveti, vigneti, orti) certificabili bio. La scadenza al 30 giugno 2026 consente una pianificazione agronomica adeguata per l'annualità.</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia pratiche di benessere animale per aziende agricole zootecniche, settore particolarmente radicato nel Cilento (allevamenti bufalini, bovini, ovicaprini per produzioni DOP come la Mozzarella di Bufala e formaggi locali). Una PMI agricola con allevamenti può accedere a pagamenti compensativi annuali adottando standard di benessere animale superiori alla norma, con scadenza estesa al 25 luglio 2026 con penale progressiva che lascia margine operativo.</t>
+          <t>Il bando finanzia pratiche di benessere animale nell'ambito del PSR Campania, con pagamenti annuali agli allevatori che adottano standard superiori a quelli obbligatori: particolarmente rilevante per le PMI zootecniche del Cilento, area vocata all'allevamento ovicaprino e bovino (es. produzioni DOP come la Mozzarella di Bufala e formaggi cilentani), che possono accedere a contributi ricorrenti a fronte di impegni gestionali pluriennali.</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Il bando sostiene le aziende agricole situate in zone montane svantaggiate della Campania, territorio che include ampie aree del Cilento: eroga pagamenti compensativi per i maggiori costi e i minori redditi derivanti dall'esercizio dell'attività agricola in aree difficili, rendendolo direttamente accessibile a PMI agricole locali senza necessità di progettualità complessa.</t>
+          <t>Il bando sostiene le aziende agricole situate in zone montane svantaggiate della Campania, area che include gran parte del territorio del Cilento: le PMI agricole locali possono ricevere un pagamento compensativo annuale per i maggiori costi e i minori redditi derivanti dall'operare in territori con limitazioni naturali, senza necessità di investimenti specifici ma semplicemente mantenendo l'attività agricola nell'area.</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Il bando SRB02 sostiene le aziende agricole localizzate in zone con svantaggi naturali significativi, tra cui rientrano esplicitamente i territori montani e collinari del Cilento: le PMI agricole di quest'area possono accedere a pagamenti compensativi annuali per ettaro di superficie agricola utilizzata, riducendo i costi aggiuntivi legati alle difficoltà orografiche e climatiche. La scadenza al 30 giugno 2026 (con possibilità di presentazione tardiva fino al 25 luglio con penale progressiva) lascia tempo sufficiente per preparare la documentazione richiesta.</t>
+          <t>Il bando SRB02 sostiene le aziende agricole localizzate in zone con svantaggi naturali significativi, tra cui molte aree del Cilento, attraverso pagamenti compensativi annuali che indennizzano i costi aggiuntivi e il mancato reddito derivanti dalle difficoltà territoriali. Una PMI agricola operante in questi comuni può accedere a contributi diretti senza necessità di progetto di investimento, semplicemente mantenendo l'attività agricola sul territorio ammissibile.</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Il bando SRB03 eroga pagamenti compensativi annuali alle aziende agricole situate in zone con vincoli naturali specifici, come quelle del Cilento (area montana e collinare vincolata), per compensare i maggiori costi di produzione e il mancato reddito derivante dai limiti territoriali: una PMI agricola cilentana con terreni in queste zone può accedere direttamente al sostegno, senza necessità di investimenti preventivi. La scadenza al 30 giugno 2026 (con possibilità di presentazione tardiva fino al 25 luglio con penale progressiva) rende l'intervento immediatamente pianificabile per la prossima annualità.</t>
+          <t>Il bando SRB03 sostiene le aziende agricole localizzate in zone con svantaggi naturali o specifici vincoli (come aree Natura 2000 o zone montane), condizione molto diffusa nel territorio del Cilento: le PMI agricole cilentane possono ricevere indennità compensative per i maggiori costi e le minori rese derivanti dai vincoli ambientali e territoriali, rendendo il sostegno direttamente accessibile senza necessità di investimenti specifici. La scadenza al 30 giugno 2026 (con possibilità di presentazione tardiva con penale progressiva fino al 25 luglio) lascia tempo sufficiente per preparare la documentazione necessaria.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia premi a superficie per l'imboschimento di terreni agricoli e non agricoli, risultando particolarmente strategico per aziende agricole del Cilento che dispongono di superfici marginali o abbandonate: i premi pluriennali garantiscono entrate stabili a fronte di investimenti contenuti in specie forestali autoctone. La scadenza al 30 giugno 2026 (con possibilità di presentazione entro il 25 luglio 2026 accettando penali progressive) lascia tempo sufficiente per pianificare la domanda.</t>
+          <t>Il bando finanzia l'imboschimento di superfici agricole e non agricole tramite premi a superficie, rendendolo direttamente accessibile ad aziende agricole del Cilento che dispongono di terreni marginali o in abbandono; il Cilento, con la sua vocazione rurale e le ampie superfici forestali, rappresenta un territorio ideale per accedere a questi contributi legati alla gestione sostenibile del suolo.</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia direttamente PMI del territorio cilentano che intendono avviare o diversificare attività legate al turismo esperienziale e all'artigianato tipico della Dieta Mediterranea, rendendolo altamente rilevante per chi opera nei settori food, artigianato locale o ricettività. Le spese finanziabili riguardano l'avvio concreto di nuove attività extra-agricole, con un focus territoriale che favorisce le imprese già radicate nel Cilento.</t>
+          <t>Il bando del GAL Cilento finanzia direttamente PMI che vogliono avviare o diversificare attività legate al turismo esperienziale e all'artigianato tipico della Dieta Mediterranea, un settore identitario del territorio cilentano. Sono finanziabili investimenti in strutture, attrezzature e servizi legati all'offerta turistica locale, rendendolo concretamente accessibile per piccole imprese artigiane e operatori del turismo rurale già radicati nel territorio.</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia direttamente l'avvio di attività artigianali legate alla Dieta Mediterranea e servizi per il turismo esperienziale nel territorio del Cilento, rendendolo ideale per PMI locali dei settori food, artigianato tipico e accoglienza turistica. Le spese finanziabili includono tipicamente investimenti in attrezzature, allestimenti e avvio di servizi, con accesso privilegiato per realtà di piccola dimensione radicate nel territorio GAL.</t>
+          <t>Il bando finanzia direttamente l'avvio di attività artigianali legate alla Dieta Mediterranea e servizi per il turismo esperienziale nel territorio del Cilento, rendendo eleggibili investimenti in attrezzature, allestimenti e costi di avviamento per PMI dei settori enogastronomico e turistico locali. Una piccola impresa del Cilento che voglia lanciare un'attività di laboratorio artigianale, degustazione o accoglienza esperienziale trova in questo bando una fonte di finanziamento mirata e territorialmente coerente.</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia percorsi formativi per operatori del turismo e dell'artigianato alimentare legati alla Dieta Mediterranea, ambito in cui le PMI del Cilento (agriturismi, botteghe artigiane, operatori turistici) possono accedere a risorse per qualificare il proprio personale e sviluppare offerte di turismo esperienziale. Le spese finanziabili riguardano tipicamente docenze, materiali didattici e organizzazione di attività formative, con un impatto diretto sulla competitività commerciale delle imprese locali.</t>
+          <t>Il bando finanzia percorsi formativi per operatori del turismo e dell'artigianato alimentare legati alla Dieta Mediterranea, rendendolo ideale per PMI cilentane attive nella ristorazione, nell'agriturismo o nella produzione artigianale tipica che vogliono strutturare offerte di turismo esperienziale. Le spese formative sono direttamente accessibili anche a piccole imprese locali, con un territorio di riferimento che coincide esattamente con il Cilento.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia modelli di economia sociale legati al turismo sostenibile e ai percorsi escursionistici di lunga percorrenza, ambito in cui il Cilento — con il suo sistema di sentieri, Parco Nazionale e tradizioni locali — rappresenta un territorio ideale. Una PMI operante nell'ospitalità, nell'organizzazione di esperienze outdoor o nei servizi turistici può accedere a fondi per sviluppare prodotti turistici innovativi e collaborazioni di rete nel territorio.</t>
+          <t>Il bando finanzia modelli di economia sociale e turismo sostenibile legati ai cammini e sentieri a lunga percorrenza, settore in cui il Cilento (con il Sentiero degli Dei, il Cammino di San Nilo e la rete dei borghi) ha un potenziale diretto e immediatamente spendibile. Una PMI locale attiva in ospitalità, guide turistiche, servizi culturali o ricettività rurale può accedere a fondi per sviluppare prodotti turistici innovativi e reti territoriali cofinanziate dall'UE.</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>GreenTour di Invitalia sostiene investimenti nel turismo sostenibile, settore in cui il Cilento — con il suo Parco Nazionale e la forte vocazione naturalistico-culturale — offre un contesto ideale per PMI che vogliono finanziare strutture ricettive, servizi turistici eco-compatibili o valorizzazione del territorio. Le spese tipicamente ammissibili includono ristrutturazione di immobili, acquisto di attrezzature e digitalizzazione dell'offerta turistica.</t>
+          <t>GreenTour di Invitalia sostiene investimenti nel turismo sostenibile, settore in cui il Cilento – con il suo Parco Nazionale e l'attrattività ambientale – offre un posizionamento ideale per PMI ricettive, agrituristiche e di servizi turistici. Le spese finanziabili tipicamente includono adeguamenti strutturali eco-compatibili, acquisto di attrezzature a basso impatto e promozione digitale, rendendolo concretamente accessibile anche per operatori di piccole dimensioni.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Il Fondo di partecipazione MUR gestito da Invitalia supporta progetti di ricerca e innovazione attraverso strumenti finanziari agevolativi (equity, quasi-equity o debito), accessibili anche a PMI con vocazione tecnologica o R&amp;S. Una PMI del Cilento attiva in settori come agroalimentare innovativo, turismo sostenibile o tecnologie ambientali potrebbe beneficiarne, ma la complessità dello strumento e i requisiti tipicamente orientati a startup e imprese innovative riducono l'accessibilità per realtà di piccola dimensione tradizionale.</t>
+          <t>Il Fondo di partecipazione MUR gestito da Invitalia eroga capitale di rischio (equity) o strumenti finanziari a favore di imprese innovative legate alla ricerca, rendendolo accessibile a PMI campane con progetti di R&amp;S o spin-off universitari, tipologia presente anche nel Cilento grazie alle attività dell'Università di Salerno. La pertinenza è media perché lo strumento richiede una componente di ricerca applicata e una struttura societaria adeguata, escludendo PMI tradizionali prive di profilo innovativo.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia la redazione di Piani di Gestione Forestale, strumento obbligatorio per accedere a molti incentivi agro-forestali europei: una PMI del Cilento attiva nella gestione boschiva, nell'agriturismo o nelle filiere del legno può coprire i costi di progettazione e consulenza tecnica specialistica. La pertinenza è media perché il beneficio è indiretto e legato a una fase preparatoria, non a investimenti produttivi immediati.</t>
+          <t>Il bando finanzia la redazione di Piani di Gestione Forestale, strumento obbligatorio per accedere a molti incentivi agroforestali europei: una PMI del Cilento attiva nella gestione boschiva, nel settore del legno o nell'agriturismo con superfici forestali può coprire i costi di progettazione e consulenza specialistica. La pertinenza è media perché il beneficio è indiretto e legato al possesso o alla gestione di superfici forestali certificate.</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Il bando 'Vita &amp; Opportunità' di Invitalia supporta iniziative legate all'inclusione sociale e alla creazione di impresa in aree svantaggiate, potenzialmente interessante per PMI del Cilento che operano in settori come servizi alla persona, welfare o economia sociale. Tuttavia, la natura spesso selettiva e la focalizzazione su specifici profili di beneficiari (es. soggetti vulnerabili o startup) può limitarne l'accessibilità per PMI già costituite e consolidate.</t>
+          <t>Il bando Vita &amp; Opportunità di Invitalia sostiene iniziative legate all'inclusione sociale e alla creazione di impresa in aree svantaggiate, potenzialmente accessibile per PMI del Cilento operanti nel welfare, nei servizi alla persona o nell'economia sociale. Tuttavia, la specificità dei requisiti e la natura del programma richiedono una verifica puntuale dell'aderenza al settore di attività prima di procedere con la candidatura.</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia tecnologie specifiche per le energie rinnovabili, potenzialmente accessibile a PMI del Cilento che intendono installare impianti fotovoltaici, eolici o da biomasse per ridurre i costi energetici o avviare produzioni di energia verde. La complessità procedurale tipica dei meccanismi UE diretti può però rappresentare una barriera per imprese di piccola dimensione senza supporto specialistico.</t>
+          <t>Il bando finanzia meccanismi e tecnologie per le energie rinnovabili, potenzialmente accessibile a PMI del Cilento che operano nel settore energetico o che intendono installare impianti rinnovabili (solare, eolico, biomasse). La pertinenza è media perché i bandi EU di questo tipo spesso privilegiano soggetti aggregati o enti pubblici, rendendo l'accesso diretto per una piccola PMI più complesso senza partnership strutturate.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Il bando ESF sostiene l'inclusione finanziaria e l'incubazione d'impresa, finanziando potenzialmente servizi di mentoring, accesso al credito agevolato e supporto alla creazione/sviluppo di imprese, con attenzione a soggetti svantaggiati; una PMI del Cilento operante in settori tradizionali o a rischio marginalizzazione potrebbe beneficiarne, ma l'accesso diretto richiede verifica dei requisiti specifici legati alla natura 'inclusiva' del programma.</t>
+          <t>Il bando ESF sostiene l'accesso a incubazione e finanza per nuovi imprenditori, potenzialmente utile per startup o micro-imprese del Cilento che vogliono avviare attività innovative o accedere a strumenti finanziari agevolati. La pertinenza è media perché si rivolge prevalentemente a nuovi imprenditori piuttosto che a PMI già consolidate, e i meccanismi attuativi ESF richiedono spesso intermediari locali attivi sul territorio.</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE finanzia ricerca e sviluppo su prodotti bio-based derivati da organismi marini, settore rilevante per PMI del Cilento attive nella pesca, acquacoltura o biotecnologie marine. Tuttavia, i bandi Horizon richiedono generalmente la partecipazione in consorzio transnazionale e capacità di R&amp;S strutturata, il che rende l'accesso complesso per PMI di piccola dimensione senza un partner di ricerca.</t>
+          <t>Il bando finanzia ricerca e sviluppo su prodotti bio-based derivati da organismi marini, settore rilevante per PMI del Cilento attive nella pesca, acquacoltura o biotecnologie marine. Tuttavia, la complessità dei progetti Horizon e i requisiti di consorzio internazionale rendono l'accesso difficile senza un partner scientifico (es. università o centro di ricerca) che guidi la proposta.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti di ricerca e innovazione su filiere alimentari sostenibili, bioeconomia e biodiversità, temi direttamente rilevanti per PMI agroalimentari del Cilento (es. produzione di fichi, olio, prodotti tipici DOP/IGP). Tuttavia, Horizon Europe richiede la partecipazione in consorzi transnazionali e una capacità progettuale elevata, rendendo l'accesso diretto complesso per una piccola impresa senza il supporto di un ente di ricerca o intermediario.</t>
+          <t>Il bando finanzia progetti di ricerca e innovazione per catene del valore sostenibili nel settore agroalimentare, area di forte vocazione per il Cilento (produzioni tipiche DOP/IGP, olivicoltura, pesca). Tuttavia, i bandi Horizon richiedono consorzio internazionale e capacità di gestione progettuale complessa, rendendo l'accesso diretto difficile per una PMI senza un partner capofila universitario o un ente di ricerca.</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e innovazione legati a prodotti e processi bio-based per stili di vita sostenibili, un'opportunità concreta per PMI del Cilento attive in agricoltura biologica, agroalimentare o cosmesi naturale che vogliano sviluppare nuovi prodotti a base biologica. Tuttavia, la complessità dei bandi Horizon e la necessità di costruire consorzi europei rendono l'accesso difficile per PMI di piccola dimensione senza un partner di ricerca.</t>
+          <t>Il bando Horizon finanzia progetti di ricerca e innovazione legati a prodotti e stili di vita bio-based, area in cui il Cilento ha potenziale nel settore agroalimentare e cosmesi naturale. Tuttavia, i bandi Horizon richiedono tipicamente partnership europee e capacità progettuali elevate, rendendo l'accesso diretto complesso per una PMI senza esperienza pregressa in programmi UE.</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca e innovazione sull'agrobiodiversità per la sicurezza alimentare, settore strategico per il Cilento ricco di produzioni tipiche (fico bianco, carciofo, fagioli antichi). Una PMI agricola o agroalimentare del territorio può partecipare come partner in un consorzio europeo, con copertura di costi di ricerca, personale e disseminazione, ma la complessità progettuale e il requisito di partenariato internazionale limitano l'accesso diretto alle realtà più piccole.</t>
+          <t>Il bando finanzia progetti di ricerca e innovazione sulla biodiversità agricola per la sicurezza alimentare, tema strategico per le PMI agroalimentari del Cilento che lavorano con cultivar tradizionali (es. fico bianco del Cilento, carciofo, fagioli tipici). L'accesso richiede però partnership con enti di ricerca e una proposta progettuale strutturata, il che rende la partecipazione diretta per una piccola PMI complessa senza un capofila accademico o consortile.</t>
         </is>
       </c>
     </row>
@@ -1742,29 +1742,29 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia lo sviluppo di tecniche di ricarica gestita delle falde acquifere (MAR) in contesti rurali, direttamente applicabile alle PMI agricole del Cilento che affrontano stress idrico stagionale. Una piccola impresa agricola o una cooperativa potrebbe partecipare in consorzio con enti di ricerca, finanziando investimenti in infrastrutture per la gestione sostenibile dell'acqua irrigua.</t>
+          <t>Il bando finanzia lo sviluppo di tecniche di ricarica gestita delle falde acquifere in contesti rurali, direttamente applicabile alle PMI agricole del Cilento che affrontano stress idrico stagionale. Una PMI del settore agricolo o agro-tecnologico può partecipare come partner di un consorzio europeo, con costi ammissibili per ricerca, sperimentazione sul campo e trasferimento tecnologico, ma la complessità dei bandi Horizon e la necessità di consorziarsi con enti di ricerca riduce l'accessibilità diretta per le piccole imprese.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
+          <t>Bio-based chemicals and/or materials from woody residues</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-03</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1784,34 +1784,34 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia attività di monitoraggio della salute del suolo e formazione degli stakeholder sull'analisi e interpretazione degli indicatori pedologici, settore rilevante per PMI agricole del Cilento (olivicoltura, viticoltura, orticoltura tipica). Tuttavia, trattandosi di un bando Horizon UE, richiede partecipazione in consorzio transnazionale e capacità progettuali elevate, rendendo l'accesso diretto complesso per una piccola impresa senza il supporto di un partner di ricerca o un ente capofila.</t>
+          <t>Il bando finanzia ricerca e sviluppo su materiali e prodotti chimici bio-based derivati da residui legnosi, settore rilevante per PMI del Cilento attive nella filiera forestale o agroalimentare con biomasse di scarto. Tuttavia, Horizon Europe richiede tipicamente partecipazione in consorzi internazionali e capacità di R&amp;S strutturata, il che rende l'accesso diretto complesso per una micro-PMI senza partner accademici o industriali già consolidati.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
+          <t>SSbD bio-based alternatives for fertilising and/or crop protection products</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1831,19 +1831,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Internazionalizzazione</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia partnership internazionali nel settore culturale e delle industrie creative (CCI), con possibilità per PMI creative del Cilento di accedere a reti europee e co-finanziare progetti di innovazione culturale. La complessità dei bandi Horizon e la necessità di consorziarsi con partner internazionali rende l'accesso impegnativo per una piccola PMI senza esperienza progettuale strutturata.</t>
+          <t>Il bando Horizon finanzia ricerca e sviluppo su alternative bio-based per fertilizzanti e protezione delle colture secondo principi Safe-and-Sustainable-by-Design, settore rilevante per le PMI agricole del Cilento (olivicoltura, orticoltura, cereali). Tuttavia, i bandi Horizon richiedono generalmente la partecipazione in consorzi europei e competenze di ricerca strutturate, rendendo l'accesso diretto complesso per una piccola PMI senza partnership con università o centri di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
+          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-01</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1878,19 +1878,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di co-gestione di ecosistemi marini e d'acqua dolce con il coinvolgimento diretto dei pescatori, rendendo il Cilento – area con forte tradizione nella pesca artigianale e risorse costiere distintive – un territorio potenzialmente strategico. Una PMI del settore ittico o della blue economy può partecipare come partner in consorzi internazionali, coprendo spese di ricerca, sviluppo di pratiche sostenibili e formazione degli operatori, ma la complessità progettuale di Horizon richiede esperienza nella gestione di fondi europei o l'appoggio di un ente di ricerca.</t>
+          <t>Il bando finanzia attività di monitoraggio della salute del suolo e formazione degli stakeholder sull'analisi e interpretazione degli indicatori, settore rilevante per PMI agricole del Cilento (olivicoltura, viticoltura, orticoltura tipica). Tuttavia, trattandosi di un bando Horizon EU, richiede generalmente la partecipazione in consorzi transnazionali e competenze progettuali elevate, rendendo l'accesso diretto complesso per una piccola impresa senza un partner capofila esperto.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
+          <t>Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1925,24 +1925,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Internazionalizzazione</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti dimostrativi per proteggere il patrimonio culturale dagli impatti climatici, settore rilevante per il Cilento con i suoi siti UNESCO e beni storici costieri vulnerabili. Una PMI specializzata in tecnologie di monitoraggio, restauro o soluzioni digitali per i beni culturali può partecipare come partner di un consorzio europeo, con costi di R&amp;S e sviluppo tecnologico finanziabili, ma la complessità progettuale Horizon richiede esperienza nella gestione di progetti europei.</t>
+          <t>Il bando finanzia partnership internazionali nel settore culturale e delle industrie creative (CCI), potenzialmente accessibile per PMI del Cilento attive in ambiti come artigianato, spettacolo, design o turismo culturale che vogliono costruire reti europee. Tuttavia, la complessità tipica dei progetti Horizon e la necessità di consorziarsi con partner internazionali rendono l'accesso difficile per piccole realtà senza esperienza pregressa in progetti UE.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Hop-On Facility</t>
+          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-03-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-03</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1972,39 +1972,39 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Il programma Hop-On consente a ricercatori e PMI di paesi con basso indice di innovazione (tra cui l'Italia meridionale) di agganciarsi a progetti Horizon già finanziati, coprendo costi di personale, attrezzature e trasferte per attività di ricerca collaborativa. Una PMI del Cilento attiva in settori come agroalimentare, turismo sostenibile o tecnologie ambientali può candidarsi per inserirsi in consorzi europei già avviati, ma richiede una capacità minima di gestione progettuale europea che può rappresentare una barriera concreta.</t>
+          <t>Il bando Horizon finanzia progetti di co-gestione delle risorse marine e delle acque dolci, con approccio partecipativo delle comunità di pescatori: una PMI ittica del Cilento (area con forte presenza di pesca artigianale e aree marine protette come Punta Campanella e Capo Palinuro) può partecipare come partner in un consorzio europeo, coprendo spese di ricerca, formazione e sviluppo di pratiche sostenibili. La complessità gestionale e la necessità di partnership internazionali rendono l'accesso indiretto più realistico rispetto a una candidatura autonoma.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EU support to Stakeholders to improve measurement of food waste and help implement food waste prevention in their operations and organisation - 2026-2027</t>
+          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SMP-FOOD-2026-FW-STAKEHOLDERS-PJ</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-05</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>UE - SMP</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2019,39 +2019,39 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Il bando supporta stakeholder (incluse PMI agroalimentari e della ristorazione) nell'implementare sistemi di misurazione e prevenzione degli sprechi alimentari, un tema rilevante per le imprese del Cilento attive nella filiera agroalimentare, agriturismi e trasformazione. L'accesso richiede però capacità di rendicontazione in ambito europeo e il focus è su strumenti operativi/organizzativi piuttosto che su investimenti diretti.</t>
+          <t>Il bando finanzia soluzioni dimostrative per proteggere il patrimonio culturale dagli impatti del cambiamento climatico, ambito rilevante per una PMI del Cilento (area con siti UNESCO e patrimonio storico-paesaggistico di rilievo) operante in settori come restauro, monitoraggio ambientale o tecnologie per la conservazione. Tuttavia, trattandosi di un bando Horizon UE, richiede partecipazione in consorzi internazionali e capacità progettuali elevate, il che rende l'accesso diretto complesso per una PMI di piccole dimensioni senza partner consolidati.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Fondo di contrasto alla deindustrializzazione 2026</t>
+          <t>EdTech Accelerator</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>30 ottobre 2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/fondo-di-contrasto-alla-deindustrializzazione-2026</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-SKILLS-10-EDTECH</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Invitalia</t>
+          <t>UE - DIGITAL</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2066,39 +2066,39 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Il fondo è pensato per contrastare la perdita di attività produttive in aree a rischio deindustrializzazione, potenzialmente accessibile a PMI manifatturiere o di servizi industriali del Cilento che intendano mantenere o rilanciare la propria capacità produttiva. Tuttavia, il Cilento ha una vocazione prevalentemente turistica e agricola, il che rende il bando meno centrato rispetto alle esigenze tipiche delle imprese locali.</t>
+          <t>Il bando supporta startup e PMI che sviluppano soluzioni tecnologiche per l'educazione (piattaforme e-learning, strumenti digitali per la didattica), offrendo accelerazione e possibile finanziamento seed. Una PMI campana del settore EdTech o con competenze digitali applicabili alla formazione può candidarsi, ma il profilo richiesto è molto specifico e orientato a realtà con vocazione innovativa e scalabile, il che può limitare l'accesso per imprese tradizionali del Cilento.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Accessible and available travel facilitation</t>
+          <t>EU support to Stakeholders to improve measurement of food waste and help implement food waste prevention in their operations and organisation - 2026-2027</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SMP-FOOD-2026-FW-STAKEHOLDERS-PJ</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - SMP</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2113,161 +2113,161 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia soluzioni per rendere i viaggi più accessibili e fruibili, un tema direttamente applicabile alle PMI turistiche del Cilento (strutture ricettive, operatori locali) che vogliono sviluppare servizi per turisti con disabilità o esigenze speciali. La complessità dei bandi Horizon e la necessità di partnership europee rende l'accesso difficile per una PMI senza esperienza pregressa in progetti UE.</t>
+          <t>Il bando supporta aziende della filiera agroalimentare — settore rilevante nel Cilento (produzione olearia, casearia, pesca) — nell'implementare sistemi di misurazione e prevenzione degli sprechi alimentari, con formazione e assistenza tecnica finanziata dall'UE. Una PMI del food&amp;beverage o della ristorazione può accedere a strumenti pratici per ridurre i costi operativi legati agli scarti e migliorare la propria conformità alle normative europee sulla sostenibilità.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>Fondo di contrasto alla deindustrializzazione 2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>30 ottobre 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Non specificata</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/fondo-di-contrasto-alla-deindustrializzazione-2026</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Invitalia</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>✅ Aperto</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Altro</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Il fondo è rivolto a imprese manifatturiere in aree a rischio deindustrializzazione, potenzialmente accessibile per PMI campane con attività produttive in crisi o in riconversione, ma il Cilento — a vocazione prevalentemente turistica e agricola — ha una base industriale limitata, riducendo concretamente il bacino di beneficiari locali eleggibili.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Accessible and available travel facilitation</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>12/12/2025</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>UE - HORIZON</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>✅ Aperto</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Turismo</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Il bando Horizon finanzia progetti di ricerca e innovazione per rendere i viaggi più accessibili e inclusivi, un'opportunità concreta per PMI del Cilento attive nel settore turistico che vogliano sviluppare soluzioni innovative per l'accessibilità (es. piattaforme digitali, servizi per turisti con disabilità). La complessità dei bandi Horizon richiede però la partecipazione in consorzio europeo, rendendo l'accesso più impegnativo per una piccola impresa senza esperienza pregressa in progetti UE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>Istituzione dell'elenco degli Organismi di Formazione e di Consulenza Qualificati ai fini
 dell'attuazione degli interventi SRH 01, SRH 03, e SRG 09</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>30 giugno 2026</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Non specificata</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>https://agricoltura.regione.campania.it/CSR_2023-2027/AKIS-avviso.html</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Regione Campania - Agricoltura</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>✅ Aperto</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Bassa</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>✅ Aperto</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Formazione</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Il bando non finanzia le PMI ma istituisce un elenco di organismi di formazione e consulenza qualificati per erogare servizi nell'ambito del PSR Campania: è rilevante solo per enti o società che intendono accreditarsi come fornitori di servizi formativi o consulenziali in ambito agricolo, non per aziende agricole o PMI del Cilento che cercano finanziamenti diretti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01-A: “Studi e ricerche per il rilevamento dei processi d’innovazione e l’impatto (ambientale,economico e sociale) delle attività artigianali tipiche legate alla Dieta Mediterranea e sulla loro territorializzazione, i fabbisogni, le ricadute e il funzionamento nella filiera”</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Non specificata</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-a-studi-e-ricerche-per-il-rilevamento-dei-processi-dinnovazione-e-limpatto-ambientaleeconomico-e-sociale-delle-at/</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>GAL Cilento</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>✅ Aperto</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Bassa</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Altro</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Il bando finanzia studi e ricerche accademiche/istituzionali sui processi di innovazione delle attività artigianali legate alla Dieta Mediterranea, con un focus analitico e territoriale difficilmente compatibile con le attività operative di una PMI standard. Una piccola impresa artigianale del Cilento potrebbe partecipare solo se in grado di condurre o commissionare ricerche strutturate sull'impatto ambientale, economico e sociale della propria filiera, il che richiede competenze e risorse tipicamente estranee alle PMI di piccola dimensione.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Backbone connectivity for Digital Global Gateways - Works</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>17/03/2026</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-WORKS</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>UE - CEF2027</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>✅ Aperto</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Bassa</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Infrastrutture</t>
-        </is>
-      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2 per la connettività backbone delle Digital Global Gateways finanzia grandi infrastrutture di telecomunicazione transeuropee, con requisiti tecnici e finanziari adatti a grandi operatori TLC o consorzi pubblici, non a PMI. Una piccola impresa del Cilento non ha né la capacità progettuale né la scala dimensionale per candidarsi direttamente a lavori infrastrutturali di questa portata.</t>
+          <t>Il bando riguarda l'iscrizione a un elenco regionale di Organismi di Formazione e Consulenza, quindi è rilevante solo per enti accreditati o società di consulenza agricola, non per PMI operative nel Cilento che cercano finanziamenti diretti. Una PMI del settore primario potrà eventualmente beneficiare indirettamente degli interventi SRH01, SRH03 e SRG09 del PSR Campania, ma non può candidarsi direttamente a questo avviso.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Backbone connectivity for Digital Global Gateways - Studies</t>
+          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01-A: “Studi e ricerche per il rilevamento dei processi d’innovazione e l’impatto (ambientale,economico e sociale) delle attività artigianali tipiche legate alla Dieta Mediterranea e sulla loro territorializzazione, i fabbisogni, le ricadute e il funzionamento nella filiera”</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-STUDIES</t>
+          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-a-studi-e-ricerche-per-il-rilevamento-dei-processi-dinnovazione-e-limpatto-ambientaleeconomico-e-sociale-delle-at/</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>UE - CEF2027</t>
+          <t>GAL Cilento</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 per la connettività backbone dei Digital Global Gateways finanzia studi su infrastrutture digitali transnazionali di grande scala, destinati tipicamente a grandi operatori di telecomunicazioni, enti pubblici o consorzi internazionali. Una PMI del Cilento non ha i requisiti dimensionali, tecnici né la capacità progettuale per partecipare a questo tipo di appalto europeo.</t>
+          <t>Il bando finanzia studi e ricerche accademiche/istituzionali sui processi di innovazione dell'artigianato tipico legato alla Dieta Mediterranea, non interventi diretti alle imprese: una PMI difficilmente possiede i requisiti tecnici e metodologici per condurre tali ricerche. L'unico interesse indiretto potrebbe riguardare PMI specializzate in consulenza o ricerca applicata al settore agroalimentare del Cilento, che potessero partecipare come soggetti attuatori.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Equipment for smart European cable systems - Works</t>
+          <t>Backbone connectivity for Digital Global Gateways - Works</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-SMART-CABLES-WORKS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-WORKS</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2354,34 +2354,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 sui sistemi di cavi europei (submarine/terrestrial cable infrastructure) è rivolto a grandi operatori di telecomunicazioni e consorzi internazionali, con requisiti tecnici e finanziari del tutto sproporzionati rispetto alla capacità di una PMI cilentana. Le spese finanziabili riguardano equipaggiamenti per infrastrutture di connettività su scala europea, escludendo di fatto realtà locali di piccole dimensioni.</t>
+          <t>Il bando CEF2 per la connettività backbone delle reti digitali globali finanzia opere infrastrutturali di grande scala (cavi sottomarini, dorsali intercontinentali) destinate a grandi operatori TLC e consorzi pubblici, con requisiti tecnici e finanziari del tutto fuori portata per una PMI campana. Una piccola impresa del Cilento non ha né la capacità esecutiva né i requisiti di eligibilità per partecipare direttamente a questo tipo di appalto europeo.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Networks of European Cinemas</t>
+          <t>Backbone connectivity for Digital Global Gateways - Studies</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-CINNET</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-STUDIES</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - CEF2027</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2396,39 +2396,39 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia reti europee di sale cinematografiche per la distribuzione e promozione di film europei transnazionali, richiedendo partnership internazionali strutturate e capacità organizzative complesse difficilmente accessibili a una PMI del Cilento. Salvo che l'azienda operi direttamente nel settore dell'esercizio cinematografico con vocazione europea, questo bando non offre opportunità concrete per il tessuto produttivo locale.</t>
+          <t>Il bando CEF2 finanzia studi di fattibilità per infrastrutture di connettività backbone a scala europea (cavi sottomarini, dorsali intercontinentali), destinati a grandi operatori TLC, consorzi pubblici o organismi internazionali. Una PMI campana, anche del settore ICT, non ha i requisiti tecnici, finanziari né la scala operativa per accedere a questo tipo di progettualità.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Films on the Move</t>
+          <t>Equipment for smart European cable systems - Works</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-FILMOVE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-SMART-CABLES-WORKS</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - CEF2027</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2443,39 +2443,39 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Il bando Films on the Move di Europa Creativa 2027 finanzia la distribuzione transnazionale di film europei non nazionali, rivolgendosi esclusivamente a distributori cinematografici con track record comprovato nel settore audiovisivo. Una PMI generica del Cilento, salvo operi specificatamente come distributore di film europei, non ha i requisiti soggettivi per accedere a questo finanziamento.</t>
+          <t>Il bando CEF 2027 finanzia grandi infrastrutture di cablaggio europeo (sistemi via cavo transeuropei) con requisiti tecnici, finanziari e di scala incompatibili con una PMI del Cilento o della Campania in generale. I beneficiari tipici sono grandi operatori delle telecomunicazioni o consorzi internazionali, non piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Europe’s Born-digital Heritage</t>
+          <t>Networks of European Cinemas</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-BORN-DIGITAL-HERITAGE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-CINNET</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Digitalizzazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato alla preservazione del patrimonio digitale europeo e richiede competenze altamente specializzate in ambito archivistico e tecnologico, con strutture di partenariato transnazionale difficilmente accessibili per una PMI del Cilento. Le opportunità concrete per realtà locali di piccola dimensione sono marginali, salvo partecipazione in qualità di partner minore in consorzi guidati da istituzioni culturali o università.</t>
+          <t>Il bando finanzia reti di sale cinematografiche europee nell'ambito del programma Creative Europe, richiedendo partnership transnazionali strutturate e competenze specifiche nel settore audiovisivo/esercizio cinematografico: un profilo molto distante dalla tipica PMI campana o cilentana. Solo esercenti di cinema organizzati in network europei potrebbero candidarsi, escludendo di fatto la quasi totalità delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Support for social dialogue</t>
+          <t>Films on the Move</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-SOC-DIALOG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-FILMOVE</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>UE - SOCPL</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2542,34 +2542,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Il bando 'Support for social dialogue' finanziato dalla DG EMPL dell'UE è destinato principalmente a organizzazioni sindacali, associazioni datoriali e parti sociali a livello europeo o nazionale, non a singole PMI. Una piccola impresa del Cilento non ha i requisiti soggettivi né la struttura per accedere direttamente a questo tipo di finanziamento.</t>
+          <t>Il bando Films on the Move (CREA 2027) finanzia la distribuzione cinematografica transnazionale in Europa e si rivolge a distributori cinematografici professionali con requisiti specifici di settore: difficilmente accessibile per una PMI generica del Cilento, a meno che non operi specificamente nella distribuzione di film europei su scala internazionale.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Empowering youth in the EU Outermost Regions – YOUTH 4 OUTERMOST REGIONS (#YOUTH4ORS)</t>
+          <t>Safeguarding Europe’s Born-digital Heritage</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-YOUTH4OR2</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-BORN-DIGITAL-HERITAGE</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>UE - ERDFTA</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2584,39 +2584,39 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Il bando è specificamente destinato alle Regioni Ultraperiferiche dell'UE (Azzorre, Canarie, Guadalupa, ecc.), territori che non includono la Campania né il Cilento: una PMI campana non rientra nei beneficiari ammissibili. Non esistono quindi basi concrete per accedere a questo finanziamento.</t>
+          <t>Il bando è focalizzato sulla conservazione del patrimonio culturale digitale a livello europeo, con requisiti di partenariato internazionale e capacità tecniche avanzate difficilmente compatibili con una PMI campana di piccole dimensioni. Una piccola impresa del Cilento non avrebbe il profilo tecnico-istituzionale richiesto, a meno di non operare già nel settore della digitalizzazione dei beni culturali con esperienza in progetti europei complessi.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>The European Capital of Innovation Award Rising Innovator Category HORIZON-EIC-2026-PRIZE-ICAPITAL</t>
+          <t>Support for social dialogue</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-SOC-DIALOG</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - SOCPL</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2631,39 +2631,39 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Il premio è destinato a città europee che si distinguono per ecosistemi di innovazione urbana, non a PMI o imprese private: una PMI del Cilento non può candidarsi direttamente né beneficiare di finanziamenti diretti. L'unico interesse indiretto sarebbe se il Comune o una città campana si candidasse, trascinando progetti locali nella propria narrativa di innovazione.</t>
+          <t>Il bando 'Support for social dialogue' della linea SOCPL è destinato a organizzazioni di parti sociali (sindacati e associazioni datoriali) a livello europeo o nazionale, non a PMI individuali. Una piccola impresa del Cilento non ha accesso diretto a questo tipo di finanziamento, che riguarda attività di dialogo sociale istituzionale tra rappresentanze del lavoro e del capitale.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>The European Capital of Innovation Award iCapital Category HORIZON-EIC-2026-ICAPITAL</t>
+          <t>Empowering youth in the EU Outermost Regions – YOUTH 4 OUTERMOST REGIONS (#YOUTH4ORS)</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-YOUTH4OR2</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ERDFTA</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2678,39 +2678,39 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Il bando premia intere città europee per le loro strategie di innovazione urbana: i destinatari sono amministrazioni municipali, non PMI. Una piccola impresa del Cilento non può candidarsi direttamente e non riceve finanziamenti per spese aziendali.</t>
+          <t>Il bando è specificamente destinato alle Regioni Ultraperiferiche dell'UE (come Canarie, Martinica, Azzorre, ecc.), territori che non includono la Campania né il Cilento, rendendo le PMI campane sostanzialmente non eleggibili come beneficiarie dirette. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio transnazionale, ma senza accesso diretto ai finanziamenti principali.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Support to awareness raising about the Arctic communities, including Indigenous People</t>
+          <t>The European Capital of Innovation Award Rising Innovator Category HORIZON-EIC-2026-PRIZE-ICAPITAL</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EMFAF-2026-PIA-ARCTIC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-02</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>UE - EMFAF</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2725,39 +2725,39 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda esclusivamente la sensibilizzazione sulle comunità artiche e i popoli indigeni, un ambito geografico e tematico completamente estraneo alle PMI del Cilento e della Campania. Non esistono spese finanziabili né settori beneficiari rilevanti per imprese locali di piccola/media dimensione operanti in questo territorio.</t>
+          <t>Il premio European Capital of Innovation è destinato a città e amministrazioni locali che dimostrano ecosistemi innovativi, non a PMI o imprese private: una PMI del Cilento non può candidarsi direttamente. L'unico interesse indiretto sarebbe partecipare a iniziative promosse da un comune campano che si candida, ma si tratta di uno scenario remoto e marginale per una piccola impresa.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Industrial Readiness for Affordable Ka-band User Terminals</t>
+          <t>The European Capital of Innovation Award iCapital Category HORIZON-EIC-2026-ICAPITAL</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-IRIS2-UT-IND-READINESS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-01</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2777,34 +2777,34 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo industriale di terminali utente in banda Ka per comunicazioni satellitari, un settore altamente specializzato che richiede competenze aerospaziali e capacità produttive difficilmente replicabili da una PMI del Cilento o della Campania in generale. L'orientamento verso grandi player dell'industria spaziale europea rende questo bando sostanzialmente inaccessibile per realtà di piccola-media dimensione non già inserite nella filiera satellitare.</t>
+          <t>Il bando premia capitali europee dell'innovazione ed è rivolto esclusivamente a città/autorità locali, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né accedere ai finanziamenti previsti. L'unica utilità indiretta sarebbe partecipare a ecosistemi di innovazione promossi da un comune candidato, scenario remoto per un territorio a vocazione rurale e turistica come il Cilento.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Capacity building for Ukrainian regional policy stakeholders</t>
+          <t>Support to awareness raising about the Arctic communities, including Indigenous People</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-UAACQUIS22</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EMFAF-2026-PIA-ARCTIC</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>UE - ERDFTA</t>
+          <t>UE - EMFAF</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2819,39 +2819,39 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto a stakeholder istituzionali e amministrazioni regionali ucraine per il rafforzamento delle capacità in materia di politica regionale UE, escludendo di fatto le PMI italiane come beneficiari diretti. Una piccola impresa del Cilento non ha titolo per partecipare né accesso concreto alle risorse previste.</t>
+          <t>Il bando riguarda la sensibilizzazione sulle comunità artiche e i popoli indigeni, un tema del tutto estraneo al contesto operativo di una PMI campana del Cilento. Non esistono settori beneficiari né spese finanziabili rilevanti per imprese locali di piccola o media dimensione operanti nel Mezzogiorno italiano.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ERC ADVANCED GRANTS</t>
+          <t>Industrial Readiness for Affordable Ka-band User Terminals</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-ADG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-IRIS2-UT-IND-READINESS</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2866,39 +2866,39 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Ricerca</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Gli ERC Advanced Grants sono destinati esclusivamente a ricercatori eccellenti con un curriculum scientifico di alto profilo internazionale, non a PMI: una piccola o media impresa del Cilento non può candidarsi direttamente e difficilmente dispone delle figure accademiche richieste per partecipare come soggetto trainante.</t>
+          <t>Il bando riguarda lo sviluppo industriale di terminali utente in banda Ka per comunicazioni satellitari, un settore altamente specializzato che richiede competenze aerospaziali e capacità produttive difficilmente disponibili in una PMI del Cilento o della Campania in generale. L'accesso è realisticamente riservato a grandi aziende o consorzi del settore spazio/difesa con forte vocazione tecnologica.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
+          <t>Capacity building for Ukrainian regional policy stakeholders</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-UAACQUIS22</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ERDFTA</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2913,34 +2913,34 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è focalizzato sulla ricerca sanitaria e l'IA applicata all'Africa subsahariana, un ambito altamente specializzato che richiede partnership internazionali con enti di ricerca e competenze difficilmente disponibili in una PMI del Cilento. Non vi è alcuna attinenza con il tessuto produttivo locale né con i settori trainanti del territorio come turismo, agricoltura o agroalimentare.</t>
+          <t>Il bando è destinato a stakeholder della politica regionale ucraina per attività di capacity building istituzionale, non a PMI italiane o campane. Una piccola impresa del Cilento non rientra tra i beneficiari ammissibili e non può accedere a questo tipo di finanziamento strutturale dedicato alla ricostruzione e al rafforzamento amministrativo dell'Ucraina.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
+          <t>ERC ADVANCED GRANTS</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-ADG</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2960,19 +2960,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a grandi consorzi di ricerca e istituzioni accademiche nel settore farmaceutico e regolatorio, con focus su reti internazionali di formazione in farmacovigilanza ed etica: una PMI del Cilento difficilmente possiede i requisiti tecnici e la struttura consortile necessari per candidarsi competitivamente. L'accesso reale richiederebbe un ruolo marginale in un partenariato già costituito, con benefici limitati e iter burocratico molto complesso.</t>
+          <t>Gli ERC Advanced Grants sono destinati esclusivamente a ricercatori individuali di eccellenza con track record scientifico consolidato, non a PMI: una piccola o media impresa del Cilento non può candidarsi direttamente e difficilmente riesce a strutturare una partnership utile per accedere a questi fondi. Il bando finanzia ricerca di frontiera in ambito accademico, senza una vocazione applicativa o territoriale compatibile con le esigenze operative di una PMI campana.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Dr Pascoal Mocumbi Prize</t>
+          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-DRPASCOALMOCUMBIPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3007,19 +3007,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Il Premio Dr Pascoal Mocumbi è un riconoscimento scientifico nell'ambito della ricerca su malattie infettive in Africa sub-sahariana (programma EDCTP3), destinato a ricercatori o istituzioni di eccellenza nel settore biomedico, non a PMI campane. Una piccola o media impresa del Cilento non ha i requisiti né il profilo necessari per candidarsi o beneficiare di questo bando.</t>
+          <t>Il bando Horizon è focalizzato su ricerca sanitaria e AI applicata all'Africa subsahariana, richiedendo partnership internazionali strutturate e capacità di ricerca avanzata difficilmente compatibili con una PMI campana di piccole dimensioni. Non vi è alcuna connessione con il territorio del Cilento né con i settori produttivi locali tipici.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Outstanding Female Scientist Prize</t>
+          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSFEMALESCIENTISTPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3054,19 +3054,19 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio individuale rivolto a ricercatrici eccellenti nell'ambito della salute globale (EDCTP3), non finanzia progetti aziendali né attività di PMI. Una piccola o media impresa del Cilento non ha accesso diretto a questo bando né può candidarsi come beneficiaria.</t>
+          <t>Il bando Horizon è orientato a reti internazionali di ricerca e formazione nel settore farmaceutico e della vigilanza regolatoria, con requisiti consortili complessi e capacità tecnico-scientifiche elevate difficilmente compatibili con una PMI del Cilento. Le PMI locali non operano tipicamente in ambiti di farmacovigilanza o piattaforme digitali regolatorie, rendendo l'accesso concreto quasi impraticabile senza un ruolo marginale all'interno di un grande consorzio.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Outstanding Research Team Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Dr Pascoal Mocumbi Prize</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSRESEARCHTEAMPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-DRPASCOALMOCUMBIPRIZE</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3106,14 +3106,14 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio per team di ricerca eccellente nell'ambito sanitario/globale (EDCTP3 riguarda malattie infettive nei paesi a basso reddito), strutturato come riconoscimento ex-post e non come finanziamento a progetto: non è accessibile a una PMI del Cilento priva di struttura di ricerca clinica certificata e di track record internazionale nel settore.</t>
+          <t>Il Premio Dr Pascoal Mocumbi è un riconoscimento nell'ambito della ricerca su malattie infettive e salute globale in Africa subsahariana, destinato a ricercatori o istituzioni scientifiche, non a PMI. Una piccola impresa del Cilento non ha né il profilo né l'attività richiesta per candidarsi.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Man EU Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Outstanding Female Scientist Prize</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPMANEUPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSFEMALESCIENTISTPRIZE</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3153,14 +3153,14 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo nell'ambito della ricerca su malattie infettive (EDCTP3), destinato a riconoscere la leadership scientifica in ambito biomedico: non prevede finanziamenti diretti a PMI né attività tipicamente svolgibili da piccole imprese del Cilento o della Campania. Una PMI manifatturiera, turistica o agroalimentare del territorio non ha i requisiti scientifici né il profilo idoneo per candidarsi.</t>
+          <t>Il bando è un premio individuale rivolto a scienziate eccellenti nell'ambito della ricerca su malattie infettive che colpiscono i paesi a basso reddito, senza alcuna componente di finanziamento a imprese o PMI. Una PMI del Cilento o della Campania non ha titolo per partecipare né può trarne beneficio diretto.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman EU Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Outstanding Research Team Prize</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANEUPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSRESEARCHTEAMPRIZE</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3200,14 +3200,14 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo dedicato alla leadership scientifica femminile nell'ambito del partenariato EDCTP3 (European &amp; Developing Countries Clinical Trials Partnership), orientato a ricercatrici nel settore delle malattie infettive globali. Non prevede finanziamenti diretti per attività aziendali né è accessibile a PMI del Cilento o della Campania in quanto tale.</t>
+          <t>Si tratta di un premio europeo destinato a team di ricerca eccellenti nell'ambito della salute globale e delle malattie infettive (programma EDCTP3), rivolto a istituti di ricerca e università, non a PMI. Una piccola impresa del Cilento non ha i requisiti né la struttura per candidarsi a questo tipo di riconoscimento competitivo.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman SSA Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Man EU Prize</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANSSAPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPMANEUPRIZE</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio (Prize) nell'ambito di Horizon Europe rivolto a ricercatrici con leadership scientifica, non a PMI: non finanzia attività aziendali né spese operative. Una PMI del Cilento non ha accesso diretto né benefici concreti da questo bando.</t>
+          <t>Si tratta di un premio europeo nell'ambito della ricerca scientifica sulla salute globale (EDCTP3), destinato a ricercatori e istituzioni scientifiche di eccellenza, non a PMI. Una piccola o media impresa del Cilento non ha i requisiti né il profilo scientifico richiesto per accedere a questo tipo di riconoscimento.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ERC PLUS GRANTS</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman EU Prize</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-PLUS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANEUPRIZE</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3289,39 +3289,39 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Gli ERC Plus Grants sono finanziamenti destinati a ricercatori di eccellenza che hanno già ottenuto un grant ERC, un profilo altamente specializzato difficilmente riconducibile a una PMI del Cilento. Una piccola impresa campana non possiede i requisiti accademici e scientifici richiesti per accedere a questo strumento Horizon.</t>
+          <t>Si tratta di un premio europeo dedicato alla leadership scientifica femminile nell'ambito del programma EDCTP3, orientato a ricercatrici e istituzioni scientifiche, non a PMI. Una piccola o media impresa del Cilento non ha i requisiti soggettivi né il profilo di attività per candidarsi o beneficiare direttamente di questo riconoscimento.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Centres of Vocational Excellence</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman SSA Prize</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2026-PEX-COVE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANSSAPRIZE</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>UE - ERASMUS2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3336,34 +3336,34 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Il bando Erasmus CoVE finanzia reti transnazionali tra istituti di istruzione e formazione professionale (IFP), enti pubblici e grandi organizzazioni: una PMI del Cilento può partecipare solo come partner secondario di un consorzio già strutturato, senza accesso diretto ai fondi. La complessità progettuale e la dimensione europea richiesta rendono la partecipazione autonoma di una piccola impresa di fatto impraticabile.</t>
+          <t>Si tratta di un premio (Prize) nell'ambito del programma EDCTP3 dedicato alla leadership scientifica femminile in ambito sanitario globale, rivolto a ricercatrici individuali e non a PMI. Una piccola impresa del Cilento non ha né i requisiti soggettivi né il profilo di ricerca richiesto per accedervi.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>ERC PLUS GRANTS</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-31</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-PLUS</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3388,14 +3388,14 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata in tecnologie spaziali, osservazione terrestre e telecomunicazioni satellitari, settori altamente specializzati con barriere tecnologiche e finanziarie elevate per una PMI campana o del Cilento. La partecipazione è concretamente accessibile solo come partner junior in consorzi internazionali guidati da grandi player del settore aerospaziale, rendendo l'accesso diretto quasi impraticabile per una piccola impresa locale.</t>
+          <t>Gli ERC Plus Grants sono fondi complementari agli ERC grants europei, destinati a ricercatori di eccellenza già vincitori di premi ERC: una PMI del Cilento non può candidarsi direttamente, poiché il bando è rivolto a istituzioni di ricerca e ricercatori individuali con profilo scientifico avanzato, non a imprese produttive di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Centres of Vocational Excellence</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3405,17 +3405,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-32</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2026-PEX-COVE</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ERASMUS2027</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata nel settore spaziale (Earth Observation e telecomunicazioni satellitari) e consorzialità internazionale, prerequisiti difficilmente raggiungibili per una PMI tradizionale del Cilento. Salvo che l'azienda non operi già come fornitore tecnologico specializzato in soluzioni spaziali o geospaziali, le barriere di accesso tecnico e amministrativo rendono questo bando di fatto non pertinente per il tessuto produttivo locale.</t>
+          <t>Il bando Erasmus CoVE finanzia reti transnazionali tra istituti di istruzione e formazione professionale (ITS, scuole tecniche, enti pubblici), non PMI in modo diretto; una PMI del Cilento potrebbe partecipare solo come partner secondario di un consorzio già strutturato, con ruolo marginale e oneri burocratici elevati rispetto ai benefici ottenibili.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
+          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-82</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-31</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3482,14 +3482,14 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Il bando richiede capacità industriali avanzate nella produzione di substrati SiC semi-isolanti e componenti GaN per applicazioni spaziali, tecnologie altamente specializzate tipiche di grandi player aerospaziali o centri di ricerca. Una PMI del Cilento o della Campania difficilmente possiede le infrastrutture, le certificazioni spaziali e il capitale tecnico-scientifico necessari per competere in questo settore di nicchia ad altissima barriera d'ingresso.</t>
+          <t>Il bando Horizon Europe richiede capacità di ricerca e sviluppo avanzate nel settore dell'osservazione della Terra e delle telecomunicazioni satellitari, con budget e requisiti tecnici difficilmente accessibili per una PMI tradizionale del Cilento. Solo PMI altamente specializzate in tecnologie spaziali o digitali potrebbero partecipare, tipicamente in qualità di partner junior in consorzi internazionali con università o grandi imprese tecnologiche.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
+          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-11</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-32</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3524,19 +3524,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di spazioporti europei e l'accesso autonomo dell'UE allo spazio, un settore altamente specializzato riservato a grandi operatori del settore aerospaziale, agenzie governative e consorzi industriali di rilievo. Una PMI del Cilento o della Campania, salvo rarissime eccezioni in nicchie tecnologiche aerospaziali avanzate, non possiede i requisiti tecnici, finanziari e infrastrutturali per partecipare concretamente a questo tipo di bando Horizon.</t>
+          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata nel settore spaziale (Earth Observation e telecomunicazioni satellitari) con budget elevati e partnership internazionali, requisiti difficilmente compatibili con una PMI di piccola dimensione del Cilento. Solo PMI altamente specializzate in tecnologie spaziali o telerilevamento potrebbero partecipare, tipicamente come partner junior di grandi consorzi europei.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
+          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-85</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-82</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di infrastrutture di test per irradiazione ad alta energia destinate a componenti elettronici per lo spazio, un settore altamente specializzato che richiede capacità tecnologiche e strutture di ricerca avanzate tipiche di grandi aziende aerospaziali o enti di ricerca. Una PMI del Cilento o della Campania difficilmente possiede i requisiti tecnici, le certificazioni e le infrastrutture necessarie per partecipare competitivamente a questo tipo di bando Horizon.</t>
+          <t>Il bando richiede capacità di R&amp;S altamente specializzate nella produzione di substrati SiC semi-isolanti e componenti elettronici per applicazioni spaziali (GaN MMICs), settori che richiedono infrastrutture industriali avanzate difficilmente compatibili con una PMI del Cilento o della Campania in generale. Si tratta di una filiera tecnologica di nicchia dominata da grandi player europei dell'industria aerospaziale e della microelettronica.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Scientific analysis and exploitation of space data</t>
+          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-61</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-11</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3618,19 +3618,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata nell'analisi di dati spaziali e satellitari, competenze tipiche di grandi centri di ricerca o aziende tech specializzate, difficilmente replicabili da una PMI del Cilento senza un solido partenariato con università o enti di ricerca. L'accesso è ulteriormente ostacolato dalla complessità progettuale e dalla necessità di co-finanziamento elevato, rendendo questo strumento poco pratico per realtà locali di piccola dimensione.</t>
+          <t>Il bando riguarda lo sviluppo di spazioporti europei e l'accesso autonomo dell'UE allo spazio, un settore ad altissima intensità tecnologica e finanziaria riservato a grandi operatori aerospaziali e istituzioni pubbliche. Una PMI del Cilento o della Campania non dispone delle competenze tecniche, delle certificazioni e della massa critica necessarie per partecipare competitivamente a questo tipo di progetto Horizon.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
+          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-86</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-85</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3670,14 +3670,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di tecnologie spaziali avanzate per il rifornimento orbitale e l'autonomia strategica europea nel settore space, richiedendo competenze altamente specializzate in ingegneria aerospaziale e capitali di ricerca significativi, del tutto fuori portata per una PMI del Cilento o della Campania priva di un posizionamento consolidato nella supply chain spaziale europea.</t>
+          <t>Il bando riguarda lo sviluppo di infrastrutture per test di irradiazione ad alta energia di componenti elettronici per il settore spaziale europeo, un ambito altamente specializzato che richiede capacità tecnologiche, laboratori certificati e competenze in fisica delle radiazioni difficilmente presenti in una PMI del Cilento o della Campania in generale. Si tratta di un'opportunità concreta solo per grandi laboratori di ricerca o aziende del settore aerospace/difesa con strutture dedicate.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
+          <t>Scientific analysis and exploitation of space data</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-81</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-61</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Il bando richiede lo sviluppo di componenti elettronici spaziali radiation-hard su nodo tecnologico 7nm, un settore ad altissima specializzazione che presuppone capacità R&amp;D avanzate, infrastrutture di microelettronica e certificazioni spaziali difficilmente accessibili per una PMI del Cilento o della Campania in generale. Le risorse e le competenze richieste sono tipiche di grandi player del settore aerospaziale o di laboratori di ricerca altamente specializzati.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata nell'analisi di dati spaziali e satellitari, competenze altamente specializzate difficilmente presenti in una PMI del Cilento; inoltre i progetti Horizon richiedono tipicamente partnership internazionali, budget elevati e strutture amministrative complesse, rendendo l'accesso diretto praticamente inaccessibile per una piccola impresa locale senza un consorzio dedicato.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Microelectronic – Front-End Module (FEM)</t>
+          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-86</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su moduli a radiofrequenza per microelettronica avanzata (FEM) richiede capacità di R&amp;D ad alto contenuto tecnologico tipiche di grandi consorzi industriali o centri di ricerca specializzati, rendendo l'accesso molto difficile per una PMI del Cilento che non operi specificamente nel settore dei semiconduttori o dell'elettronica di potenza. Le spese finanziabili riguardano ricerca industriale e sviluppo sperimentale in un comparto ad altissima specializzazione, quasi assente nel tessuto produttivo campano locale.</t>
+          <t>Il bando riguarda lo sviluppo di interfacce di rifornimento per veicoli spaziali nell'ambito dell'autonomia strategica europea nel settore spaziale, richiedendo competenze altamente specializzate in ingegneria aerospaziale e capitali di rischio elevati, del tutto fuori dalla portata di una PMI campana o cilentana operante in settori tradizionali. Solo aziende con laboratori R&amp;D dedicati all'industria spaziale potrebbero candidarsi, tipicamente in consorzio con grandi player del settore aerospaziale.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Trafficking in human beings</t>
+          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-THB</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-81</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>UE - ISF</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3806,19 +3806,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sul traffico di esseri umani è destinato primariamente a enti pubblici, forze dell'ordine e organizzazioni no-profit specializzate, rendendo praticamente inaccessibile la partecipazione diretta di una PMI del Cilento. Non finanzia attività produttive o commerciali, ma interventi di contrasto, prevenzione e supporto alle vittime di tratta.</t>
+          <t>Il bando richiede competenze altamente specializzate nello sviluppo di componenti elettronici per applicazioni spaziali (FPGA radiation-hard su processo 7nm), un settore dominato da grandi aziende aerospaziali e laboratori di ricerca avanzata, rendendo praticamente inaccessibile la partecipazione per una PMI del Cilento priva di infrastrutture tecnologiche dedicate e certificazioni spaziali ESA/NASA.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Organised crime and drug trafficking</t>
+          <t>Microelectronic – Front-End Module (FEM)</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-OCDT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>UE - ISF</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3853,39 +3853,39 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sulla criminalità organizzata e il traffico di droga è destinato principalmente a forze dell'ordine, autorità pubbliche e organizzazioni specializzate nella sicurezza interna, non a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti soggettivi né le competenze istituzionali richieste per accedere a questo tipo di finanziamento europeo.</t>
+          <t>Il bando Horizon EU sui moduli Front-End per microelettronica richiede capacità di R&amp;D avanzata in semiconduttori e componentistica elettronica, settori estremamente specializzati e lontani dal tessuto produttivo tipico del Cilento e della Campania interna. Una PMI locale difficilmente dispone delle infrastrutture di laboratorio, dei requisiti tecnici e dei partner di consorzio internazionale necessari per competere in questo ambito.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Framework Partnership Agreements for operating grants to support non-profit organisations</t>
+          <t>Trafficking in human beings</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-FPA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-THB</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - ISF</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3905,34 +3905,34 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Il bando è riservato esclusivamente a organizzazioni non profit tramite accordi quadro di partenariato con la Commissione Europea, escludendo per definizione le PMI a scopo di lucro. Una PMI del Cilento non ha accesso diretto a questo strumento, né come beneficiaria principale né come destinataria delle risorse.</t>
+          <t>Il bando ISF (Internal Security Fund) sul traffico di esseri umani è destinato primariamente a enti pubblici, forze dell'ordine, ONG e organismi specializzati nella sicurezza e protezione delle vittime, non a PMI commerciali. Una piccola impresa del Cilento non avrebbe i requisiti soggettivi né le competenze istituzionali richieste per accedere a questo tipo di finanziamento UE.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MSCA Postdoctoral Fellowships 2026</t>
+          <t>Organised crime and drug trafficking</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-PF-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-OCDT</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ISF</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3947,39 +3947,39 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Il bando MSCA Postdoctoral Fellowships finanzia la mobilità di ricercatori post-dottorato presso enti ospitanti (università, centri di ricerca, imprese), ma richiede una struttura amministrativa e scientifica complessa per gestire il fellowship; una PMI del Cilento difficilmente possiede i requisiti organizzativi e la capacità progettuale europea necessari per candidarsi come host institution. L'unico scenario di accesso indiretto sarebbe una partnership con un ente di ricerca capofila, ma il beneficio diretto per la PMI resterebbe marginale.</t>
+          <t>Il bando ISF (Internal Security Fund) sul crimine organizzato e traffico di droga è destinato principalmente a forze dell'ordine, autorità pubbliche e organizzazioni specializzate nella sicurezza interna, non a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti soggettivi né le competenze istituzionali richieste per accedere a questo tipo di finanziamento europeo.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ERA Fellowships</t>
+          <t>Framework Partnership Agreements for operating grants to support non-profit organisations</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-05-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-FPA</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3994,24 +3994,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Le ERA Fellowships sono destinate a ricercatori individuali e istituzioni accademiche/di ricerca nell'ambito del programma Horizon Europe, rendendo di fatto escluse le PMI di piccola dimensione come quelle tipiche del Cilento, che non dispongono di strutture di ricerca certificate. Solo PMI con dipartimenti R&amp;D strutturati e capacità di ospitare ricercatori potrebbero partecipare come host institution, scenario molto raro nel tessuto produttivo locale.</t>
+          <t>Il bando LIFE è riservato esclusivamente a organizzazioni non profit tramite accordi quadro di partenariato per sovvenzioni operative: le PMI, in quanto soggetti a scopo di lucro, sono esplicitamente escluse dalla partecipazione diretta. Una PMI del Cilento non può candidarsi né beneficiare direttamente di questi fondi.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
+          <t>MSCA Postdoctoral Fellowships 2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2026-02-DISEASE-12</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-PF-01-01</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4041,24 +4041,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Il bando ERDERA riguarda la ricerca sulle malattie rare nell'ambito del programma Horizon Europe e richiede consorzi di ricerca altamente specializzati, con competenze biomediche e infrastrutture scientifiche avanzate difficilmente reperibili in una PMI del Cilento. Non finanzia attività produttive o commerciali tipiche delle piccole imprese campane, rendendo l'accesso sostanzialmente impraticabile senza partnership con enti di ricerca primari.</t>
+          <t>Le MSCA Postdoctoral Fellowships finanziano ricercatori individuali post-dottorato che si spostano tra paesi, non le imprese direttamente: una PMI del Cilento potrebbe al massimo fungere da ente ospitante, ma la complessità gestionale, i requisiti accademici e la struttura del programma lo rendono poco accessibile senza un partner universitario consolidato.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Earlier and more precise palliative care</t>
+          <t>ERA Fellowships</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-05-WIDENING-01</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4088,19 +4088,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla cura palliativa precoce è destinato a consorzi di ricerca accademica e grandi istituzioni sanitarie europee, richiedendo capacità progettuali e infrastrutture difficilmente accessibili a una PMI del Cilento. Salvo che l'azienda operi specificamente nel settore delle tecnologie medicali o dei servizi sanitari innovativi con esperienza in progetti europei, le barriere di accesso (partnership internazionali, rendicontazione Horizon) rendono il bando poco praticabile.</t>
+          <t>Le ERA Fellowships finanziano mobilità e ricerca di singoli ricercatori tramite istituzioni accademiche o centri di ricerca, non PMI dirette beneficiarie; una PMI del Cilento potrebbe partecipare solo come partner host, ruolo complesso e poco remunerativo per realtà di piccole dimensioni.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
+          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2026-02-DISEASE-12</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4135,19 +4135,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata in ambito oncologico e modellazione digitale del corpo umano, con consorzio internazionale e competenze altamente specialistiche difficilmente disponibili in una PMI campana di piccole dimensioni. Il Cilento, con tessuto produttivo orientato a turismo e agricoltura, non esprime tipicamente filiere biotech o healthtech in grado di candidarsi competitivamente a questo tipo di finanziamento.</t>
+          <t>Il bando ERDERA riguarda la ricerca sulle malattie rare nell'ambito di Horizon Europe e richiede consorzi di ricerca accademici e istituzionali ad alto livello scientifico, rendendo l'accesso praticamente inaccessibile per una PMI campana del Cilento priva di specifiche competenze biomediche e di un network europeo consolidato. Solo PMI altamente specializzate in biotecnologie o diagnostica rara, con esperienza in progetti Horizon, potrebbero partecipare come partner minori.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
+          <t>Earlier and more precise palliative care</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-04</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo è orientato a consorzi di ricerca e organizzazioni sanitarie per sviluppare piattaforme digitali di supporto alla salute mentale dei giovani sopravvissuti al cancro, richiedendo capacità progettuali e partner internazionali difficilmente accessibili a una PMI del Cilento. Non finanzia attività produttive o commerciali tipiche delle piccole imprese locali.</t>
+          <t>Il bando Horizon Europe sulle cure palliative è orientato a consorzi di ricerca accademica e ospedali con forte componente scientifica, richiedendo capacità progettuali e partnership internazionali difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo in qualità di partner tecnologico (es. sviluppo software o dispositivi medicali), ma le barriere di accesso restano molto elevate.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
+          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-01</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4229,19 +4229,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia trial clinici pragmatici sull'immunoterapia oncologica nell'ambito del programma Horizon UE, richiedendo capacità di ricerca clinica avanzata, infrastrutture ospedaliere e competenze specialistiche difficilmente disponibili in una PMI campana del Cilento. Non sono previste tipologie di spesa o ruoli progettuali compatibili con le dimensioni e il profilo operativo di una piccola o media impresa locale.</t>
+          <t>Il bando richiede capacità di ricerca avanzata in ambito biomedico e modellazione digitale del corpo umano per applicazioni oncologiche, competenze tipiche di grandi centri di ricerca o università, non di PMI generiche del Cilento. L'accesso a fondi Horizon in questo settore richiede inoltre partnership consolidate con enti accademici internazionali e investimenti in R&amp;S difficilmente sostenibili per una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Microbiome for early cancer prediction before the onset of disease</t>
+          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-05</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4276,19 +4276,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sul microbioma per la predizione precoce dei tumori, con consorzio internazionale e competenze altamente specializzate difficilmente accessibili a una PMI del Cilento. Solo laboratori biotech o spin-off universitari con forte vocazione R&amp;S potrebbero partecipare, tipicamente in qualità di partner e non di capofila.</t>
+          <t>Il bando Horizon europeo richiede la partecipazione a consorzi internazionali di ricerca con forte componente clinica e accademica, focalizzato sulla salute mentale dei giovani sopravvissuti al cancro tramite piattaforme digitali: difficilmente accessibile per una PMI del Cilento priva di competenze specifiche in oncologia, psicologia clinica o sviluppo di infrastrutture digitali sanitarie a scala europea. Potrebbe avere senso solo per PMI ICT altamente specializzate in healthtech già inserite in reti di ricerca internazionali.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
+          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-03</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Il bando è focalizzato su programmi di ricerca oncologica in collaborazione con l'Ucraina, destinato principalmente a istituti di ricerca, università e organizzazioni sanitarie di grande struttura. Una PMI del Cilento non dispone né dei requisiti tecnici né della rete di partnership internazionale necessaria per partecipare competitivamente.</t>
+          <t>Il bando finanzia sperimentazioni cliniche pragmatiche su terapie immunologiche per tumori refrattari, richiedendo competenze altamente specializzate in ambito oncologico e infrastrutture di ricerca clinica avanzate del tutto estranee al tessuto produttivo di una PMI campana, specialmente nel Cilento. Non esistono margini concreti di partecipazione per imprese di piccola/media dimensione senza un profilo biomedico-scientifico strutturato.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Improve the Quality of Life of older cancer patients</t>
+          <t>Microbiome for early cancer prediction before the onset of disease</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-02</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4370,19 +4370,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi internazionali con forte componente di ricerca clinica e accademica, rendendo l'accesso diretto da parte di una PMI campana estremamente difficile senza partnership con centri oncologici o università. Una PMI del Cilento potrebbe partecipare solo come partner tecnologico (es. sviluppo di soluzioni digitali per pazienti anziani oncologici), ma i requisiti progettuali e amministrativi di Horizon restano proibitivi per strutture di piccole dimensioni.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata in ambito biotecnologico e microbioma oncologico, con requisiti di consorzio internazionale e strutture di R&amp;S difficilmente compatibili con una PMI di piccola dimensione del Cilento. L'accesso è realisticamente riservato a centri di ricerca, università o grandi imprese del settore biomedico.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Approaches and tools for security in software and hardware development and assessment</t>
+          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-06</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4417,19 +4417,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su sicurezza hardware/software richiede capacità di ricerca avanzata, partnership internazionali e strutture di R&amp;D difficilmente disponibili in una PMI del Cilento o della Campania interna. Il profilo tecnico richiesto (cybersecurity, sviluppo sicuro) e la complessità progettuale europea rendono questo strumento accessibile quasi esclusivamente a grandi aziende tech o università, non a PMI locali di piccola dimensione.</t>
+          <t>Il bando è focalizzato sul potenziamento della ricerca oncologica in collaborazione con l'Ucraina, richiedendo competenze scientifiche specializzate e strutture di ricerca avanzate tipiche di università e centri di ricerca, non di PMI. Una piccola o media impresa del Cilento non dispone dei requisiti tecnici, istituzionali e di rete internazionale necessari per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
+          <t>Improve the Quality of Life of older cancer patients</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-07</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4464,19 +4464,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon su schemi crittografici avanzati richiede capacità di ricerca scientifica di alto livello, partnership con enti accademici e investimenti ingenti in R&amp;S, requisiti difficilmente soddisfabili da una PMI del Cilento operante in settori tradizionali. L'ambito altamente specializzato (crittografia ad alte prestazioni) esclude di fatto imprese non operanti nel settore della cybersecurity o ICT avanzato.</t>
+          <t>Il bando Horizon EU sulla qualità della vita dei pazienti oncologici anziani richiede consorzi di ricerca internazionali con competenze cliniche e scientifiche specializzate, rendendo l'accesso diretto da parte di una PMI del Cilento estremamente difficile senza un ruolo marginale in un consorzio già strutturato. Non finanzia attività produttive o commerciali tipiche delle PMI locali, ma ricerca biomedica e sperimentazione clinica.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
+          <t>Approaches and tools for security in software and hardware development and assessment</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-01</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4516,14 +4516,14 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU sulla sicurezza e robustezza dei modelli AI richiede capacità di ricerca avanzata, consorzi internazionali e competenze tecniche specialistiche difficilmente disponibili in una PMI del Cilento. L'accesso è realistico solo per aziende tech con esperienza pregressa in progetti europei di R&amp;S, non per la tipica piccola impresa campana.</t>
+          <t>Il bando Horizon EU sulla sicurezza in ambito software e hardware richiede capacità di ricerca avanzata, consorzio internazionale e competenze tecniche specialistiche difficilmente disponibili in una PMI del Cilento. L'accesso è realisticamente limitato a grandi player tecnologici o spin-off universitari con track record in cybersecurity.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>R&amp;I in Support of the Clean Industrial Deal: Clean Technologies for Climate Action</t>
+          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-03</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4563,14 +4563,14 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e innovazione su tecnologie pulite per il clima, ma richiede consorzi internazionali, capacità di R&amp;D strutturata e budget elevati, rendendo l'accesso diretto estremamente difficile per una PMI del Cilento senza un partner universitario o un grande integratore capofila. Una PMI locale potrebbe partecipare solo in qualità di partner tecnico specializzato in un consorzio già formato, non come beneficiario principale.</t>
+          <t>Il bando Horizon riguarda ricerca avanzata in schemi crittografici e implementazioni ad alta velocità, richiedendo competenze specialistiche di livello universitario/R&amp;D e capacità progettuali europee difficilmente accessibili a una PMI del Cilento senza un solido partner accademico. Il settore cripto-informatico di frontiera è praticamente assente nel tessuto produttivo locale, rendendo la partecipazione diretta poco realistica senza una rete consolidata di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>R&amp;I in Support of the Clean Industrial Deal: Decarbonisation of energy intensive industries (IA) (Processes4Planet and Clean Steel partnerships)</t>
+          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-02</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4610,14 +4610,14 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti di ricerca e innovazione ad alta intensità tecnologica per la decarbonizzazione di industrie energivore (acciaio, chimica, cemento), con budget e requisiti consortili tipicamente adatti a grandi industrie e centri di ricerca europei. Una PMI del Cilento, territorio a vocazione turistica e agricola, difficilmente possiede le competenze industriali e la capacità progettuale richieste da partnership come Processes4Planet o Clean Steel.</t>
+          <t>Il bando Horizon Europe sulla sicurezza e robustezza dei modelli AI richiede capacità di ricerca avanzata, consorzi internazionali e competenze altamente specializzate in cybersecurity e AI, barriere difficilmente superabili per una PMI del Cilento senza un solido track record in R&amp;D. L'accesso è realistico solo come partner junior in un consorzio guidato da università o grandi player tecnologici, rendendo il beneficio diretto molto limitato.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Validating policies and business models for affordable and sustainable housing (Built4People Partnership)</t>
+          <t>R&amp;I in Support of the Clean Industrial Deal: Clean Technologies for Climate Action</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-02</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -4657,14 +4657,14 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi europei complessi con forte componente di ricerca e sviluppo, difficilmente accessibile per una PMI del Cilento senza esperienza pregressa in progetti UE. Le attività finanziate riguardano la validazione di modelli abitativi sostenibili e accessibili, settore poco strategico per il tessuto produttivo locale orientato a turismo e agricoltura.</t>
+          <t>Il bando Horizon UE finanzia ricerca e innovazione su tecnologie pulite per l'industria, ma richiede la partecipazione in consorzi internazionali con elevate competenze di R&amp;S e capacità amministrative che difficilmente una PMI del Cilento può sostenere autonomamente. I costi di progettazione, la competizione globale e i requisiti tecnici lo rendono di fatto inaccessibile senza il supporto di università o grandi partner industriali.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Coordinated topic with India on recycling of EV batteries</t>
+          <t>R&amp;I in Support of the Clean Industrial Deal: Decarbonisation of energy intensive industries (IA) (Processes4Planet and Clean Steel partnerships)</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-01</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4704,14 +4704,14 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Il bando richiede collaborazione internazionale con partner indiani su ricerca avanzata nel riciclo di batterie per veicoli elettrici, con requisiti tecnici e consorziali tipici di grandi enti di ricerca o multinazionali. Una PMI del Cilento difficilmente dispone delle competenze specialistiche in chimica elettrochimica e delle strutture necessarie per competere in un programma Horizon coordinato a livello bilaterale UE-India.</t>
+          <t>Il bando Horizon Europe è orientato a grandi consorzi di ricerca e industrie energivore (acciaio, chimica, cemento) nell'ambito di partnership europee strutturate come Processes4Planet e Clean Steel, con budget e requisiti tecnici incompatibili con le dimensioni tipiche di una PMI cilentana. Una piccola impresa del Cilento difficilmente possiede le capacità R&amp;D e le infrastrutture industriali richieste per partecipare competitivamente, salvo come partner junior in un consorzio guidato da grandi player.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Innovative technologies and solutions to improve wind energy systems supporting the Strategic Energy Technology (SET) Plan on wind</t>
+          <t>Validating policies and business models for affordable and sustainable housing (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D3-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-04</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -4751,14 +4751,14 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sul miglioramento dei sistemi eolici richiede capacità di ricerca e sviluppo avanzate, consorzi internazionali e budget elevati, caratteristiche difficilmente compatibili con una PMI di piccola dimensione in Campania. Il Cilento, pur avendo potenziale eolico, non presenta un tessuto industriale specializzato nel settore wind energy tale da giustificare la partecipazione diretta come capofila o partner tecnico qualificato.</t>
+          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi europei con elevata capacità di ricerca e sviluppo, rendicontazione complessa e co-finanziamento significativo, caratteristiche che lo rendono difficilmente accessibile per una PMI del Cilento senza esperienza pregressa in progetti UE. Il focus sull'edilizia abitativa sostenibile e affordable potrebbe teoricamente coinvolgere imprese locali del settore costruzioni come partner secondari, ma la struttura del bando privilegia grandi enti di ricerca e pubbliche amministrazioni.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Low disturbance prefabrication approaches for deep renovation of multi-storey buildings (Built4People Partnership)</t>
+          <t>Coordinated topic with India on recycling of EV batteries</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-04</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4798,14 +4798,14 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali di ricerca con elevata capacità tecnica e amministrativa, rendendo l'accesso diretto molto complesso per una PMI del Cilento. Finanzia approcci di prefabbricazione a basso impatto per la ristrutturazione profonda di edifici multipiano, settore di nicchia che difficilmente corrisponde al profilo produttivo delle PMI locali dell'area.</t>
+          <t>Il bando Horizon richiede partnership internazionali con enti indiani e competenze specialistiche nel riciclo di batterie per veicoli elettrici, strutture tipiche di grandi consorzi di ricerca o multinazionali. Una PMI del Cilento difficilmente dispone delle capacità tecniche, della rete internazionale e delle risorse amministrative necessarie per partecipare a un progetto di ricerca coordinato UE-India in questo settore altamente specializzato.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Producing battery-grade materials for electrodes through sustainable processing and refining of raw materials or developing bio-based materials (BATT4EU Partnership)</t>
+          <t>Innovative technologies and solutions to improve wind energy systems supporting the Strategic Energy Technology (SET) Plan on wind</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D3-03</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4845,14 +4845,14 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Il bando BATT4EU riguarda la produzione di materiali per elettrodi di batterie e la raffinazione di materie prime critiche, settori che richiedono infrastrutture di ricerca avanzata e competenze altamente specializzate, tipicamente fuori portata per una PMI del Cilento. Le call Horizon in questo ambito privilegiano grandi consorzi europei con laboratori certificati e capacità industriali su scala, rendendo l'accesso diretto di una piccola impresa campana estremamente difficile senza un partner accademico o industriale strutturato.</t>
+          <t>Il bando Horizon Europe richiede consorzi internazionali con forti capacità di R&amp;D avanzata nel settore eolico, requisiti difficilmente soddisfabili da una PMI campana di piccole dimensioni senza partnership consolidate. Per una PMI del Cilento, area a vocazione turistica e agricola, l'energia eolica industriale non rappresenta un settore core, e i costi di partecipazione a progetti Horizon sono elevati in termini di risorse umane e amministrative.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Researching the technical, social &amp; economic factors impacting the energy performance of Smart Buildings (Built4People Partnership)</t>
+          <t>Low disturbance prefabrication approaches for deep renovation of multi-storey buildings (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-02</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4892,14 +4892,14 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi di ricerca europei con capacità di R&amp;D avanzata, budget elevati e competenze tecniche specializzate sulle prestazioni energetiche degli edifici intelligenti, requisiti difficilmente compatibili con una PMI di piccola dimensione del Cilento. Solo aziende del settore edilizia/energia con un dipartimento R&amp;S strutturato e partner universitari già consolidati potrebbero candidarsi come partner di progetto, non come capofila.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali di ricerca con capacità tecnico-scientifica avanzata nel settore della prefabbricazione e ristrutturazione profonda di edifici multipiano, strutture tipicamente non accessibili a PMI edili di piccole dimensioni del Cilento. I requisiti di rendicontazione, la competizione europea e la necessità di partner universitari o centri di ricerca rendono questo strumento di fatto inaccessibile senza un ecosistema di alleanze già consolidato.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Advanced data platforms to integrate whole life carbon in building information tools, assessments, and certification (Built4People Partnership)</t>
+          <t>Producing battery-grade materials for electrodes through sustainable processing and refining of raw materials or developing bio-based materials (BATT4EU Partnership)</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-01</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi di ricerca internazionali con capacità tecniche avanzate in BIM e carbon lifecycle assessment, strutture tipiche di grandi enti di ricerca o imprese tech specializzate. Una PMI edile o di servizi del Cilento difficilmente dispone delle competenze e delle risorse amministrative necessarie per candidarsi direttamente, potendo al massimo partecipare come partner secondario in un consorzio già formato.</t>
+          <t>Il bando BATT4EU richiede capacità di ricerca avanzata nella produzione di materiali per batterie (elettrodi, raffinazione materie prime critiche, bio-materiali), con consorzio internazionale e budget tipicamente multimilionari, rendendo la partecipazione diretta quasi impossibile per una PMI del Cilento priva di laboratori R&amp;D specializzati. Il territorio cilentano non presenta filiere industriali legate alla chimica delle batterie o alla metallurgia estrattiva che possano giustificare un interesse concreto.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Full-scale demonstration of heat upgrade solutions in industrial processes</t>
+          <t>Researching the technical, social &amp; economic factors impacting the energy performance of Smart Buildings (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-01</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -4981,19 +4981,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede dimostrazioni su scala reale di tecnologie per l'aggiornamento del calore nei processi industriali, con requisiti tecnici e finanziari elevati (consorzi internazionali, co-finanziamento significativo) difficilmente accessibili per una PMI del Cilento priva di struttura R&amp;D dedicata e partnership europee consolidate.</t>
+          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi internazionali di ricerca con forte componente scientifica, rendendo l'accesso estremamente complesso per una PMI del Cilento senza struttura R&amp;D dedicata. Le PMI edilizie o impiantistiche locali potrebbero partecipare solo come partner junior di grandi enti di ricerca, con ruoli marginali e oneri burocratici sproporzionati rispetto ai benefici attesi.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>European Nuclear Skills Initiative – towards European Nuclear Skills Academy</t>
+          <t>Advanced data platforms to integrate whole life carbon in building information tools, assessments, and certification (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-NRT-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-03</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>UE - EURATOM2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -5028,19 +5028,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di competenze nel settore nucleare a livello europeo, un ambito altamente specializzato e distante dal tessuto produttivo del Cilento e della Campania in generale, dove non esistono impianti o filiere nucleari. Una PMI locale non dispone né dei requisiti tecnici né del profilo settoriale richiesto per partecipare.</t>
+          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi europei di ricerca con capacità di sviluppo di piattaforme dati avanzate per il ciclo di vita degli edifici (BIM, carbon assessment, certificazione), competenze tecniche e finanziarie difficilmente accessibili per una PMI campana di piccole dimensioni, soprattutto nel Cilento dove il tessuto produttivo edilizio è prevalentemente artigianale e locale. Una PMI del settore costruzioni o digitale potrebbe al massimo partecipare come partner junior in un consorzio già strutturato, ma difficilmente come capofila.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Protection of the euro against counterfeiting</t>
+          <t>Full-scale demonstration of heat upgrade solutions in industrial processes</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PERI-2026-ANTI-COUNTERFEIT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-08</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>UE - PERI</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -5075,19 +5075,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la protezione dell'euro dalla contraffazione ed è destinato a forze dell'ordine, istituzioni finanziarie e autorità pubbliche: una PMI del Cilento non rientra tra i beneficiari ammissibili e non ha leve operative su questo tema.</t>
+          <t>Il bando Horizon richiede dimostrazioni su scala reale di tecnologie di aggiornamento termico in processi industriali, con requisiti tecnici, consorziali e finanziari molto elevati, difficilmente compatibili con le capacità di una PMI del Cilento. Le imprese locali, prevalentemente nei settori turistico, agroalimentare e artigianale, non hanno strutture industriali adeguate né la capacità di cofinanziamento tipicamente richiesta da questi programmi europei.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Strengthening a European user facility for nuclear research</t>
+          <t>European Nuclear Skills Initiative – towards European Nuclear Skills Academy</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-NRT-01-01</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5122,19 +5122,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda il potenziamento di infrastrutture di ricerca nucleare a livello europeo, un ambito altamente specializzato destinato a grandi enti di ricerca, università e laboratori nazionali. Una PMI del Cilento o della Campania non dispone delle competenze nucleari certificate né delle strutture tecniche richieste per partecipare competitivamente a questo tipo di progetto.</t>
+          <t>Il bando EURATOM riguarda lo sviluppo di competenze nel settore nucleare a livello europeo, un ambito altamente specializzato e distante dalla struttura produttiva del Cilento e della Campania in generale, dove non esistono impianti nucleari né filiere industriali correlate. Una PMI locale non avrebbe i requisiti tecnici né il profilo settoriale per partecipare utilmente a questa iniziativa.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Co-funded European partnership for research in nuclear materials</t>
+          <t>Protection of the euro against counterfeiting</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PERI-2026-ANTI-COUNTERFEIT</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>UE - EURATOM2027</t>
+          <t>UE - PERI</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -5174,14 +5174,14 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la ricerca in materiali nucleari nell'ambito del programma EURATOM, un settore altamente specializzato che richiede competenze scientifiche avanzate e infrastrutture di ricerca nucleare del tutto estranee al tessuto produttivo di una PMI del Cilento o della Campania in generale. Non esistono filiere locali o settori manifatturieri del territorio che possano utilmente partecipare a una partnership europea focalizzata su questo ambito.</t>
+          <t>Il bando riguarda la protezione dell'euro dalla contraffazione ed è destinato principalmente a forze dell'ordine, istituti finanziari e autorità pubbliche competenti in materia, non a PMI del Cilento o della Campania. Non finanzia attività produttive, commerciali o di sviluppo aziendale tipiche delle piccole imprese.</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
+          <t>Strengthening a European user facility for nuclear research</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-04</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda tecnologie nucleari e applicazioni delle radiazioni ionizzanti, settori altamente specializzati e regolamentati che richiedono infrastrutture di ricerca avanzate e competenze scientifiche difficilmente disponibili in una PMI del Cilento o della Campania in generale. Non sono previste opportunità concrete per imprese di piccola-media dimensione operanti nei settori produttivi tipici del territorio.</t>
+          <t>Il bando EURATOM riguarda il potenziamento di infrastrutture di ricerca nucleare a livello europeo, un settore altamente specializzato che richiede competenze scientifiche avanzate e strutture dedicate, incompatibili con la tipica attività di una PMI campana o cilentana. Non sono previste opportunità concrete per imprese di piccola/media dimensione operanti in contesti territoriali come il Cilento.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
+          <t>Co-funded European partnership for research in nuclear materials</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-08</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5268,14 +5268,14 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la produzione industriale di isotopi stabili per terapie nucleari avanzate, un settore altamente specializzato che richiede infrastrutture nucleari e competenze scientifiche difficilmente accessibili a una PMI campana, specialmente nel Cilento dove non esistono filiere produttive in ambito nucleare o radiofarmaceutico. Le opportunità di partecipazione per realtà locali di piccola dimensione sono praticamente nulle senza partnership con grandi centri di ricerca nucleare europei.</t>
+          <t>Il bando riguarda la ricerca sui materiali nucleari nell'ambito del programma EURATOM, un settore altamente specializzato che richiede infrastrutture di ricerca avanzate e competenze scientifiche difficilmente presenti in una PMI del Cilento o della Campania. Il target reale sono grandi enti di ricerca, università e aziende dell'industria nucleare, rendendo questo bando sostanzialmente inaccessibile per una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the European nuclear competence  area</t>
+          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-06</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5310,19 +5310,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la competenza nucleare europea, un settore altamente specializzato estraneo al tessuto produttivo del Cilento e delle PMI campane in generale, che non operano in ambito nucleare. Le attività finanziabili (ricerca, formazione e infrastrutture nel settore nucleare) richiedono competenze tecnico-scientifiche e strutture di cui nessuna PMI locale tipica dispone.</t>
+          <t>Il bando EURATOM riguarda tecnologie nucleari avanzate e applicazioni delle radiazioni ionizzanti, settori altamente specializzati che richiedono infrastrutture di ricerca e competenze tecniche difficilmente presenti in una PMI del Cilento o della Campania in generale. Le attività finanziabili si orientano verso grandi centri di ricerca e consorzi scientifici internazionali, rendendo l'accesso praticamente inaccessibile per realtà produttive locali di piccola-media dimensione.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Safety of operating nuclear power plants and research reactors</t>
+          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-05</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5362,14 +5362,14 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la sicurezza di impianti nucleari e reattori di ricerca, un settore altamente specializzato e regolamentato che non ha applicabilità concreta per le PMI del Cilento o della Campania, territorio privo di infrastrutture nucleari e con un tessuto produttivo orientato a turismo, agricoltura e agroalimentare. I requisiti tecnici e istituzionali richiesti escludono di fatto qualsiasi piccola o media impresa generalista.</t>
+          <t>Il bando EURATOM riguarda la produzione di isotopi stabili per terapie nucleari avanzate, un settore altamente specializzato che richiede infrastrutture di ricerca nucleare e competenze scientifiche fuori dalla portata di una PMI del Cilento o della Campania in generale. Le risorse finanziabili (ricerca nucleare, produzione di radiofarmaci) sono destinate a consorzi di grandi enti di ricerca e laboratori europei, non a piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>European Partnership for research in radiation protection and detection of ionising radiation</t>
+          <t>Enhancing the European nuclear competence  area</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-09</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-03</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5404,19 +5404,19 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda ricerca specializzata in protezione dalle radiazioni e rilevamento di radiazioni ionizzanti, un settore altamente tecnico e normativo che richiede competenze scientifiche avanzate e infrastrutture di ricerca difficilmente disponibili in una PMI campana, specialmente nel Cilento dove il tessuto produttivo è orientato verso turismo, agricoltura e piccolo commercio. Le partnership europee di questo tipo privilegiano grandi enti di ricerca, università e aziende con laboratori accreditati nel nucleare, rendendo l'accesso concreto per una PMI locale praticamente impraticabile.</t>
+          <t>Il bando EURATOM riguarda la competenza nucleare europea e si rivolge principalmente a grandi enti di ricerca, università e operatori del settore nucleare: una PMI campana del Cilento, priva di attività nel comparto nucleare o nella ricerca specializzata correlata, non ha requisiti né ambiti operativi compatibili con questo finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
+          <t>Safety of operating nuclear power plants and research reactors</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-01</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5456,14 +5456,14 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la sicurezza dei reattori nucleari avanzati e dei combustibili innovativi, un settore altamente specializzato che richiede competenze nucleari e infrastrutture di ricerca incompatibili con la realtà produttiva di una PMI del Cilento o della Campania in generale. Non esistono imprese locali operanti in questo comparto né filiere nucleari nel territorio di riferimento.</t>
+          <t>Il bando EURATOM riguarda la sicurezza di reattori nucleari e reattori di ricerca, settore altamente specializzato che non ha alcuna applicabilità per una PMI del Cilento o della Campania in generale, regione priva di impianti nucleari e di filiere industriali collegate. Le attività finanziabili richiedono competenze nucleari certificate e partner istituzionali del settore energetico atomico, fuori dalla portata di qualsiasi piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Raising awareness of and building capacity for the EU Charter of Fundamental Rights</t>
+          <t>European Partnership for research in radiation protection and detection of ionising radiation</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5473,17 +5473,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CHARTER</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-09</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>UE - CERV</t>
+          <t>UE - EURATOM2027</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -5498,19 +5498,19 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Il bando CERV è orientato principalmente a organizzazioni della società civile, enti pubblici e ONG impegnati nella promozione dei diritti fondamentali UE, non a PMI produttive o commerciali del Cilento. Una piccola impresa campana difficilmente soddisfa i requisiti di eleggibilità e non trova finanziamenti per attività tipicamente aziendali come produzione, servizi o innovazione.</t>
+          <t>Il bando EURATOM riguarda la ricerca sulla protezione dalle radiazioni e il rilevamento delle radiazioni ionizzanti, un settore altamente specializzato che richiede capacità di ricerca scientifica avanzata tipiche di grandi enti o laboratori accreditati. Una PMI del Cilento, anche con profilo tecnologico, difficilmente possiede le competenze nucleari e le infrastrutture di ricerca necessarie per accedere a questo tipo di partenariato europeo.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Promoting an enabling civic space</t>
+          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5520,17 +5520,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CIVIC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-02</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>UE - CERV</t>
+          <t>UE - EURATOM2027</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -5550,14 +5550,14 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Il programma CERV (Citizens, Equality, Rights and Values) finanzia progetti legati alla società civile, democrazia e diritti fondamentali, destinati principalmente a ONG, enti pubblici e organizzazioni non profit. Una PMI del Cilento non rientra nel profilo tipico dei beneficiari e difficilmente può strutturare un progetto coerente con gli obiettivi di 'spazio civico' richiesti dal bando.</t>
+          <t>Il bando EURATOM riguarda la sicurezza dei reattori nucleari avanzati e dei combustibili innovativi, un settore altamente specializzato che richiede competenze nucleari specifiche e strutture di ricerca avanzate incompatibili con la realtà produttiva di una PMI campana, specialmente nel Cilento, territorio a vocazione agricola e turistica. Le attività finanziabili (ricerca sulla sicurezza nucleare, modellazione di reattori SMR) non sono pertinenti per nessuna tipologia di piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Safety of operating nuclear power plants and research reactors</t>
+          <t>Raising awareness of and building capacity for the EU Charter of Fundamental Rights</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5567,17 +5567,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CHARTER</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - CERV</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5592,19 +5592,19 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la sicurezza di reattori nucleari e impianti di ricerca, un settore altamente specializzato che non ha applicabilità concreta per una PMI campana del Cilento, dove non esistono infrastrutture nucleari né filiere industriali correlate. Le competenze tecniche e i requisiti progettuali richiesti sono incompatibili con la struttura tipica di una piccola o media impresa del territorio.</t>
+          <t>Il bando CERV è destinato principalmente a organizzazioni della società civile, enti pubblici e ONG impegnate nella promozione dei diritti fondamentali UE, non a PMI commerciali del Cilento o della Campania. Una piccola impresa manifatturiera o turistica del territorio avrebbe difficoltà a dimostrare la missione istituzionale richiesta e a competere con soggetti specializzati in advocacy e diritti civili.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
+          <t>Promoting an enabling civic space</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5614,17 +5614,17 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CIVIC</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - CERV</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -5639,19 +5639,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la piattaforma tecnologica per l'energia nucleare sostenibile e le applicazioni non energetiche delle radiazioni ionizzanti, settori altamente specializzati e lontani dal tessuto produttivo tipico del Cilento e della Campania. Una PMI locale difficilmente dispone delle competenze tecnico-scientifiche e dell'infrastruttura di ricerca necessarie per partecipare competitivamente a un programma Horizon di questa natura.</t>
+          <t>Il bando CERV 'Promoting an enabling civic space' finanzia organizzazioni della società civile e no-profit per attività di partecipazione democratica e spazio civico, non imprese commerciali: una PMI del Cilento non rientra nei beneficiari eleggibili e non trova leva su spese tipicamente aziendali. L'accesso è strutturalmente precluso a soggetti profit-oriented.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
+          <t>Safety of operating nuclear power plants and research reactors</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-01</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5686,19 +5686,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la produzione europea di isotopi stabili per terapie di medicina nucleare avanzata, un settore altamente specializzato che richiede infrastrutture di ricerca nucleare e competenze scientifiche di frontiera del tutto inaccessibili a una PMI del Cilento o della Campania in generale. Si tratta di un programma Horizon destinato a grandi consorzi di ricerca con laboratori nucleari certificati, escludendo di fatto qualsiasi piccola o media impresa del territorio.</t>
+          <t>Il bando riguarda esclusivamente la sicurezza di reattori nucleari operativi e reattori di ricerca, un settore altamente specializzato privo di impianti nucleari in Italia e completamente estraneo al tessuto produttivo del Cilento e della Campania. Nessuna PMI locale opera in questo ambito né possiede le competenze tecniche certificate richieste per partecipare a progetti Horizon di tale natura.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
+          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-06</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5733,34 +5733,34 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la sicurezza dei reattori nucleari di nuova generazione (SMR) e dei combustibili innovativi, un settore altamente specializzato che richiede competenze tecniche e infrastrutture di ricerca del tutto estranee al tessuto produttivo di una PMI campana, specialmente nel Cilento. Non esistono realtà produttive o di ricerca nucleare nel territorio che possano candidarsi con concrete possibilità di successo.</t>
+          <t>Il bando finanzia attività di ricerca e coordinamento sulla tecnologia nucleare sostenibile e applicazioni non energetiche delle radiazioni ionizzanti, ambiti altamente specializzati che richiedono competenze tecniche e infrastrutture difficilmente disponibili in una PMI del Cilento o della Campania in generale. Non esistono applicazioni pratiche o settori produttivi locali rilevanti che possano beneficiare concretamente di questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>EIC Transition Open</t>
+          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-TRANSITIONOPEN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-05</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5785,34 +5785,34 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>EIC Transition finanzia progetti di trasferimento tecnologico da ricerca di base a applicazioni di mercato, richiedendo tipicamente partnership con università o laboratori di ricerca e budget elevati (fino a 2,5 milioni di euro), il che lo rende difficilmente accessibile per una PMI di piccole dimensioni del Cilento senza un solido background in R&amp;S e collaborazioni accademiche strutturate.</t>
+          <t>Il bando Horizon SAMIRA/ERVI riguarda la produzione europea di isotopi stabili per terapie di medicina nucleare, un settore altamente specializzato che richiede infrastrutture nucleari, competenze scientifiche avanzate e grandi investimenti tecnologici, del tutto estranei alla struttura produttiva tipica di una PMI campana o cilentana. Non esistono filiere locali nel Cilento collegate a questo ambito, rendendo la partecipazione concretamente inaccessibile.</t>
         </is>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Supporting digitalisation of Distribution System Operators for a smart energy transition (Smart Grid Academy)</t>
+          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-DIGITAL</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-02</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -5832,14 +5832,14 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 2027 dedicato alla digitalizzazione dei Distribution System Operators (DSO) è rivolto principalmente a gestori di reti elettriche e grandi operatori del settore energetico, non a PMI generiche. Una piccola impresa del Cilento avrebbe difficoltà sia a qualificarsi come soggetto beneficiario diretto, sia a sostenere i requisiti tecnici e amministrativi di un progetto europeo LIFE in ambito smart grid.</t>
+          <t>Il bando riguarda la sicurezza dei reattori nucleari SMR e combustibili avanzati, un settore altamente specializzato che richiede competenze nucleari certificate e infrastrutture di ricerca fuori dalla portata di una PMI campana, specialmente nel Cilento dove il tessuto produttivo è orientato a turismo, agricoltura e artigianato. Non esistono spese finanziabili rilevanti per realtà locali di piccola-media dimensione prive di expertise nel nucleare.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Scaling up smart and clean energy solutions for affordability in EU cities</t>
+          <t>EIC Transition Open</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5849,17 +5849,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-EMPOWER</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-TRANSITIONOPEN</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -5874,19 +5874,19 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a soluzioni energetiche scalabili in contesti urbani europei, con requisiti progettuali complessi e partnership multi-attore difficilmente gestibili da una PMI del Cilento, territorio prevalentemente rurale e con scarsa infrastruttura urbana di riferimento. I costi di partecipazione, la necessità di consorziarsi a livello europeo e la focalizzazione su città di medio-grande dimensione rendono questo strumento di fatto inaccessibile per una piccola impresa campana.</t>
+          <t>EIC Transition è destinato a progetti di trasferimento tecnologico da ricerca di base ad applicazioni di mercato, con requisiti molto elevati in termini di TRL e capacità di R&amp;D: una PMI del Cilento difficilmente possiede i prerequisiti scientifici richiesti (risultati da progetti ERC o FET precedenti). Il bando è strutturalmente orientato a spin-off universitari e aziende deep-tech, non a PMI tradizionali di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Supporting the delivery of actionable, integrated, and comprehensive local heating and cooling plans</t>
+          <t>Supporting digitalisation of Distribution System Operators for a smart energy transition (Smart Grid Academy)</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-HEATCOOLPLAN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-DIGITAL</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5921,19 +5921,19 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE richiede la redazione di piani locali integrati per il riscaldamento e il raffrescamento, un'attività tipicamente destinata a enti pubblici, autorità locali o consorzi istituzionali, non a PMI. Una piccola impresa del Cilento difficilmente dispone delle competenze tecniche, della struttura amministrativa e della capacità di partenariato internazionale richiesta da LIFE per candidarsi autonomamente o come capofila.</t>
+          <t>Il bando LIFE 2027 è orientato a operatori di rete di distribuzione energetica (DSO) e grandi soggetti del settore elettrico per progetti di smart grid, non a PMI generiche del Cilento o della Campania. Le dimensioni dei progetti LIFE, i requisiti tecnici specifici e la complessità della rendicontazione europea rendono questo strumento di fatto inaccessibile per una piccola o media impresa locale senza un ruolo diretto nella gestione delle reti energetiche.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>One-Stop-Shops - Integrated services for clean energy transition in private buildings</t>
+          <t>Scaling up smart and clean energy solutions for affordability in EU cities</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-OSS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-EMPOWER</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5973,14 +5973,14 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE finanzia progetti di sistema per la creazione di sportelli integrati ('one-stop-shops') che supportino la transizione energetica negli edifici privati, richiedendo partnership transnazionali e capacità progettuali elevate tipiche di enti pubblici o grandi organizzazioni. Una PMI del Cilento difficilmente può accedervi direttamente, al massimo come partner secondario in un consorzio, senza un ruolo di capofila realistico.</t>
+          <t>Il bando LIFE 2027 è orientato a progetti su scala urbana e consortile per soluzioni energetiche pulite nelle città UE, con requisiti di partenariato transnazionale e budget elevati difficilmente gestibili da una PMI standalone del Cilento. Una piccola impresa campana potrebbe partecipare solo come partner di un consorzio guidato da enti pubblici o grandi organizzazioni, con ruolo marginale e accesso indiretto ai fondi.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Energy renovation solutions – Boosting building renovation through effective markets and instruments</t>
+          <t>Supporting the delivery of actionable, integrated, and comprehensive local heating and cooling plans</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BETTERRENO</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-HEATCOOLPLAN</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6020,14 +6020,14 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a consorzi pubblico-privati o enti di ricerca con capacità di gestione progettuale europea, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un partenariato consolidato. Le PMI edili o energetiche locali potrebbero al massimo partecipare come partner secondari, ma i costi di coordinamento e la complessità burocratica di un bando UE multi-paese scoraggiano un coinvolgimento autonomo.</t>
+          <t>Il bando LIFE è orientato a enti pubblici, autorità locali e organismi di pianificazione territoriale per la redazione di piani integrati di riscaldamento e raffreddamento urbano, non a PMI singole. Una piccola impresa del Cilento difficilmente può accedere come capofila, e il ruolo di partner richiede competenze specialistiche in pianificazione energetica comunale difficili da soddisfare senza strutture dedicate.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Towards an effective implementation of key legislation in the field of sustainable energy</t>
+          <t>One-Stop-Shops - Integrated services for clean energy transition in private buildings</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-POLICY</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-OSS</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6067,14 +6067,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti di scala europea con focus su policy e governance energetica, richiedendo capacità progettuali e finanziarie difficilmente accessibili a una PMI del Cilento senza partnership con enti di ricerca o istituzioni. Una piccola impresa campana troverebbe più adatto partecipare come partner secondario piuttosto che come soggetto capofila.</t>
+          <t>Il bando LIFE finanzia progetti di sistema per la creazione di sportelli integrati ('one-stop-shop') che accompagnano privati nella transizione energetica degli edifici, richiedendo partnership complesse e capacità progettuali europee difficilmente accessibili a una PMI del Cilento senza un consorzio strutturato. Una piccola impresa locale potrebbe partecipare solo come partner operativo (es. installatori, energy auditor), ma la leadership progettuale e la rendicontazione europea rendono l'accesso diretto molto improbabile.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Alleviating household energy poverty in Europe</t>
+          <t>Energy renovation solutions – Boosting building renovation through effective markets and instruments</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERPOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BETTERRENO</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6114,14 +6114,14 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è storicamente orientato a enti pubblici, università e organizzazioni no-profit con forte capacità progettuale europea; una PMI del Cilento difficilmente possiede le competenze tecniche e i partner istituzionali richiesti per guidare un progetto sulla povertà energetica domestica a scala europea. L'accesso è ulteriormente ostacolato dalla complessità rendicontativa e dalla necessità di consorziarsi con soggetti di più Paesi membri.</t>
+          <t>Il bando LIFE è orientato a progetti dimostrativi e di sistema su scala europea, richiedendo capacità progettuali, consorzio internazionale e budget elevati difficilmente gestibili da una PMI del Cilento. Le spese finanziabili riguardano sviluppo di strumenti di mercato per la riqualificazione energetica degli edifici, ambito più adatto a enti di ricerca, utilities o grandi operatori del settore edilizio.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Strengthening national frameworks for renewable and efficient heating and cooling in existing buildings</t>
+          <t>Towards an effective implementation of key legislation in the field of sustainable energy</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-RENEWHC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-POLICY</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6161,14 +6161,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a enti pubblici, autorità nazionali e organizzazioni no-profit per lo sviluppo di framework normativi e politiche sul riscaldamento/raffreddamento efficiente negli edifici esistenti, non al finanziamento diretto di interventi aziendali. Una PMI campana, anche operante nel settore edile o delle energie rinnovabili, difficilmente può candidarsi autonomamente senza essere partner di un consorzio istituzionale transnazionale.</t>
+          <t>Il programma LIFE è orientato a progetti di scala europea con forte componente tecnico-normativa e istituzionale, difficilmente gestibili da una PMI senza un consorzio strutturato con enti di ricerca o pubbliche amministrazioni. Per una PMI del Cilento, i costi di progettazione, i requisiti di co-finanziamento e la complessità burocratica rendono l'accesso diretto sostanzialmente impraticabile senza un ruolo da partner junior in un partenariato già costituito.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>BUILD UP Skills - National Platforms on energy efficiency skills for the clean energy transition</t>
+          <t>Alleviating household energy poverty in Europe</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BUILDSKILLS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERPOV</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6203,19 +6203,19 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Il bando BUILD UP Skills è orientato alla costruzione di piattaforme nazionali per la formazione professionale nell'efficienza energetica, rivolto tipicamente a consorzi istituzionali, enti di formazione e associazioni di categoria, non a singole PMI. Una piccola impresa edile o impiantistica del Cilento difficilmente ha la struttura per candidarsi direttamente, potendo al più partecipare come partner junior in un progetto guidato da soggetti più strutturati.</t>
+          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, ONG e consorzi di ricerca; una PMI campana del Cilento difficilmente dispone delle capacità progettuali e del co-finanziamento richiesto per affrontare un bando europeo sulla povertà energetica domestica, che non prevede attività commerciali dirette né investimenti produttivi tipici delle piccole imprese.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Crowding in private finance</t>
+          <t>Strengthening national frameworks for renewable and efficient heating and cooling in existing buildings</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PRIVAFIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-RENEWHC</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6250,19 +6250,19 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Credito/Finanza</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 'Crowding in private finance' è orientato a strumenti finanziari e meccanismi di blending per attrarre capitali privati su progetti ambientali su larga scala, rivolto principalmente a istituzioni finanziarie e soggetti pubblici, non a PMI operative. Una piccola impresa del Cilento difficilmente soddisfa i requisiti tecnici e dimensionali richiesti per accedere direttamente a questo tipo di strumento.</t>
+          <t>Il bando LIFE è orientato a soggetti istituzionali e organismi di ricerca per lo sviluppo di framework normativi nazionali sul riscaldamento/raffrescamento rinnovabile negli edifici esistenti: una PMI campana, anche del settore edile o impiantistico, difficilmente ha i requisiti tecnici e la struttura progettuale per candidarsi autonomamente. L'unica via di accesso realistico sarebbe come partner secondario in un consorzio guidato da enti pubblici o università.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Facilitating cooperation among energy communities</t>
+          <t>BUILD UP Skills - National Platforms on energy efficiency skills for the clean energy transition</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERCOM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BUILDSKILLS</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6297,19 +6297,19 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE finanzia progetti di cooperazione tra comunità energetiche a scala europea, richiedendo partenariati transnazionali complessi e capacità progettuali elevate difficilmente accessibili a una PMI di piccole dimensioni del Cilento. Le spese ammissibili (coordinamento di reti di energy communities, attività dimostrative) sono più adatte a consorzi, enti pubblici o grandi organizzazioni con esperienza nella rendicontazione europea.</t>
+          <t>Il bando BUILD UP Skills è orientato alla creazione di piattaforme nazionali per la formazione di lavoratori edili sull'efficienza energetica, con una struttura progettuale complessa tipica dei programmi LIFE che richiede partenariati istituzionali e capacità di gestione europea: difficilmente accessibile a una PMI del Cilento in modo diretto. Una piccola impresa edile o di installazione di impianti potrebbe beneficiarne solo indirettamente, come soggetto coinvolto in un partenariato guidato da enti formativi o associazioni di categoria.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Supporting the clean energy transition of European industry and businesses</t>
+          <t>Crowding in private finance</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-INDUSTRY</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PRIVAFIN</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6344,19 +6344,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Credito/Finanza</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e grandi consorzi con forte capacità progettuale europea; una PMI del Cilento difficilmente possiede le risorse tecniche e amministrative per candidarsi autonomamente a bandi UE diretti di questa complessità. Inoltre, il focus sulla transizione energetica pulita dell'industria richiede investimenti e partnership transnazionali che esulano dalla dimensione tipica delle piccole imprese locali.</t>
+          <t>Il bando LIFE 'Crowding in private finance' è orientato a strumenti finanziari e meccanismi di blending capital per progetti ambientali su larga scala, richiedendo capacità finanziarie e strutture organizzative tipiche di intermediari finanziari o grandi operatori, non di PMI del Cilento. L'accesso diretto per una piccola impresa campana è estremamente difficile sia per i requisiti tecnici che per le soglie di investimento previste.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Project Development Assistance for sustainable energy investments</t>
+          <t>Facilitating cooperation among energy communities</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PDA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERCOM</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE PDA è orientato a supportare la fase di sviluppo di progetti di investimento in energia sostenibile di scala medio-grande, tipicamente destinato a enti pubblici, autorità locali o grandi operatori energetici; una PMI del Cilento difficilmente possiede i requisiti tecnici e la capacità progettuale richiesta per accedere autonomamente a questo strumento europeo.</t>
+          <t>Il bando LIFE 2027 sulla cooperazione tra comunità energetiche è orientato a enti pubblici, consorzi e organizzazioni no-profit con forte capacità progettuale europea; una PMI del Cilento difficilmente ha le risorse e il profilo istituzionale per candidarsi autonomamente, potendo al più partecipare come partner secondario in un consorzio più ampio.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-RPJ Coal Research projects</t>
+          <t>Supporting the clean energy transition of European industry and businesses</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-RPJ</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-INDUSTRY</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>UE - RFCS2027</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -6438,19 +6438,19 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia ricerca tecnica nel settore carbonifero (carbone e acciaio) ed è destinato a consorzi di ricerca europei con competenze altamente specializzate, rendendo di fatto inaccessibile la partecipazione a una PMI del Cilento che opera in contesti produttivi locali non legati all'industria estrattiva o siderurgica. Non esistono filiere del carbone o dell'acciaio rilevanti nel territorio cilentano che possano giustificare un interesse concreto.</t>
+          <t>Il programma LIFE è orientato prevalentemente a progetti dimostrativi su larga scala e a soggetti con elevata capacità tecnica e finanziaria per cofinanziare iniziative sulla transizione energetica pulita; una PMI del Cilento difficilmente dispone delle risorse progettuali e della massa critica necessarie per competere in un bando europeo diretto di questa complessità, senza il supporto di un partenariato strutturato.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-AM Coal Accompanying measures</t>
+          <t>Project Development Assistance for sustainable energy investments</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6460,17 +6460,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-AM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PDA</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>UE - RFCS2027</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -6485,19 +6485,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS riguarda misure di accompagnamento per le regioni carbonifere europee in transizione, con focus su riconversione industriale e supporto ai lavoratori del settore carbone: il Cilento e la Campania non hanno tradizione mineraria carbonifera, rendendo questo bando di fatto inaccessibile per le PMI locali. Le misure finanziate (studi, formazione settoriale, sviluppo economico post-carbone) non sono pertinenti al tessuto produttivo dell'area.</t>
+          <t>Il bando LIFE è strutturalmente orientato a grandi consorzi, enti pubblici o organizzazioni ambientali con forte capacità progettuale europea; una PMI del Cilento difficilmente dispone delle risorse tecniche e amministrative per candidarsi autonomamente. La fase di 'Project Development Assistance' riguarda la preparazione di investimenti in energia sostenibile, utile solo come partner secondario in un consorzio guidato da soggetti più strutturati.</t>
         </is>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-AM Steel Accompanying measures</t>
+          <t>RFCS-2026-01-RPJ Coal Research projects</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-AM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-RPJ</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6537,14 +6537,14 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS riguarda misure di accompagnamento per il settore siderurgico europeo (ricerca, formazione e riconversione lavoratori nell'industria dell'acciaio), un comparto praticamente assente nel Cilento e marginale in Campania per le PMI locali. La complessità procedurale europea e la specificità settoriale rendono questo bando di fatto inaccessibile per una piccola impresa del territorio.</t>
+          <t>Il bando RFCS finanzia esclusivamente ricerca tecnica nel settore carbonifero (estrazione, utilizzo e sicurezza del carbone), un comparto industriale assente in Campania e nel Cilento, dove non esistono attività minerarie di carbone. Una PMI locale non ha né il profilo settoriale né la capacità di ricerca industriale richiesta per accedere a questo tipo di finanziamento europeo.</t>
         </is>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-RPJ Steel Research projects</t>
+          <t>RFCS-2026-01-AM Coal Accompanying measures</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-RPJ</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-AM</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6579,19 +6579,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia esclusivamente ricerca nel settore siderurgico (acciaio e carbone) a livello europeo, richiedendo consorzi transnazionali con forti competenze tecniche specializzate: una PMI del Cilento, operante tipicamente in settori come turismo, agricoltura o artigianato, non ha i requisiti tecnici né il profilo industriale per partecipare competitivamente.</t>
+          <t>Il bando RFCS riguarda misure di accompagnamento per le regioni carbonifere europee in transizione, destinato principalmente a enti pubblici, istituti di ricerca e grandi consorzi industriali legati al settore del carbone. La Campania e il Cilento non hanno tradizione estrattiva carbonifera rilevante, e una PMI locale difficilmente possiede i requisiti tecnici e istituzionali richiesti per partecipare a questo tipo di progetto europeo.</t>
         </is>
       </c>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-PDP Steel Pilot and demonstration projects</t>
+          <t>RFCS-2026-02-AM Steel Accompanying measures</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-PDP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-AM</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6626,19 +6626,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia progetti pilota e dimostrativi nel settore siderurgico europeo, richiedendo consorzi di ricerca con competenze industriali avanzate nell'acciaio: una PMI del Cilento o della Campania non operante nella filiera siderurgica difficilmente soddisfa i requisiti tecnici e dimensionali richiesti. Anche per aziende manifatturiere locali, i costi di partecipazione a progetti UE di questa complessità e il profilo altamente specializzato del programma lo rendono di fatto inaccessibile senza partnership con grandi industrie dell'acciaio.</t>
+          <t>Il bando RFCS riguarda misure di accompagnamento per il settore siderurgico europeo (ricerca, riqualificazione lavoratori, impatto sociale della transizione dell'acciaio) ed è rivolto principalmente a grandi consorzi industriali, università e centri di ricerca del settore steel. Una PMI del Cilento, territorio a vocazione turistica e agroalimentare, non ha quasi nessuna possibilità concreta di accesso né beneficio diretto da questo strumento.</t>
         </is>
       </c>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-PDP Coal Pilot and demonstration projects</t>
+          <t>RFCS-2026-02-RPJ Steel Research projects</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-PDP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-RPJ</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6673,19 +6673,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia progetti pilota e dimostrativi nel settore carbonifero, rivolto a grandi consorzi di ricerca e industrie estrattive europee: una PMI campana del Cilento, territorio privo di attività minerarie legate al carbone e orientato a turismo e agricoltura, non ha accesso pratico né profilo adeguato per partecipare. Le spese finanziabili riguardano ricerca industriale su processi minerari, sicurezza nelle miniere e valorizzazione del carbone, settori del tutto estranei al tessuto produttivo locale.</t>
+          <t>Il bando RFCS finanzia esclusivamente ricerca nel settore siderurgico (produzione e trasformazione dell'acciaio) con progetti di alto contenuto tecnico-scientifico, richiedendo partnership tra grandi industrie e centri di ricerca europei. Una PMI del Cilento, territorio a vocazione turistica e agricola, difficilmente opera in questo comparto e avrebbe difficoltà a costruire la rete di partner e le competenze tecniche richieste per accedere a fondi UE di questo livello.</t>
         </is>
       </c>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-Steel-Big Tickets under the steel and metals action plan dual-use</t>
+          <t>RFCS-2026-02-PDP Steel Pilot and demonstration projects</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-BT-STEEL-SMAP-DUAL-USE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-PDP</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6725,34 +6725,34 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia ricerca industriale su larga scala nel settore siderurgico e metallurgico con focus su applicazioni dual-use (civile/difesa), richiedendo consorzi transnazionali con centri di ricerca e grandi imprese: una PMI campana del Cilento, tipicamente attiva in turismo, agricoltura o artigianato, è esclusa di fatto sia per settore che per capacità progettuale e finanziaria richiesta.</t>
+          <t>Il bando RFCS finanzia progetti pilota e di dimostrazione nel settore siderurgico europeo, richiedendo consorzi di ricerca con forte componente industriale e scientifica: una PMI del Cilento, tipicamente orientata a turismo, agricoltura o artigianato, non ha né il profilo produttivo né le capacità progettuali per accedere a questo tipo di finanziamento UE altamente specializzato.</t>
         </is>
       </c>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>European mini-slate development</t>
+          <t>RFCS-2026-01-PDP Coal Pilot and demonstration projects</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-DEVMINISLATE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-PDP</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - RFCS2027</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -6772,34 +6772,34 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Il bando CREA2027 'European mini-slate development' è orientato a operatori del settore audiovisivo europeo per lo sviluppo di slate di progetti, richiedendo strutture produttive consolidate e track record internazionale difficilmente compatibili con una PMI del Cilento. Le spese finanziabili riguardano sviluppo di sceneggiature e pacchetti di produzione cinematografica/TV, settore non tipico del tessuto produttivo locale.</t>
+          <t>Il bando RFCS finanzia progetti pilota e dimostrativi legati all'industria carbonifera europea, un settore del tutto assente nel Cilento e in Campania in generale; i requisiti tecnici, la scala industriale richiesta e la complessità della rendicontazione europea lo rendono di fatto inaccessibile per una PMI locale di piccola o media dimensione.</t>
         </is>
       </c>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Toward a comprehensive assessment of the disturbance of marine ecosystems by anthropogenic underwater noise</t>
+          <t>RFCS-2026-Steel-Big Tickets under the steel and metals action plan dual-use</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-BT-STEEL-SMAP-DUAL-USE</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - RFCS2027</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a consorzi di ricerca scientifica sul rumore sottomarino antropico negli ecosistemi marini, richiedendo competenze altamente specializzate e strutture di ricerca che esulano dalle capacità tipiche di una PMI campana. Una piccola impresa del Cilento potrebbe partecipare solo in qualità di partner secondario, ad esempio come operatore nautico o di monitoraggio costiero, ma le probabilità di accesso diretto e autonomo sono molto limitate.</t>
+          <t>Il bando RFCS finanzia grandi progetti di ricerca nell'industria siderurgica e metallurgica con budget elevati tipici di consorzi industriali e centri di ricerca, rendendo l'accesso praticamente impossibile per una PMI del Cilento che non operi nel settore acciaio/metalli a livello industriale significativo. Le call 'Big Tickets' richiedono inoltre capacità progettuali e finanziarie fuori portata per la piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Improving circularity of multilayer flexible plastic food contact packaging</t>
+          <t>European mini-slate development</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6836,17 +6836,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-DEVMINISLATE</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -6861,19 +6861,19 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzio internazionale e competenze specifiche sull'imballaggio flessibile multistrato, struttura difficilmente accessibile per una PMI del Cilento priva di un dipartimento R&amp;D dedicato o di partnership con università. Potrebbe avere senso solo se la PMI opera nella filiera alimentare e si associa a un consorzio europeo già formato come partner tecnologico.</t>
+          <t>Il bando CREA2027 'European mini-slate development' è orientato alla produzione audiovisiva e culturale europea, con requisiti di co-produzione transnazionale e capacità finanziaria difficilmente compatibili con una PMI di piccola dimensione del Cilento. Le spese finanziabili riguardano sviluppo di slate di progetti audiovisivi, richiedendo competenze settoriali specifiche e strutture organizzative tipiche di società di produzione audiovisiva consolidate.</t>
         </is>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Supporting pre-normative research for standardization of the bio-based products</t>
+          <t>Toward a comprehensive assessment of the disturbance of marine ecosystems by anthropogenic underwater noise</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-01</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -6908,19 +6908,19 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca pre-normativa sulla standardizzazione di prodotti bio-based, richiedendo capacità di ricerca avanzata e consorzio europeo difficilmente accessibili a una PMI campana di piccole dimensioni. Le PMI del Cilento, prevalentemente attive in agricoltura, turismo o artigianato, non hanno struttura né profilo tecnico-scientifico adeguato per candidarsi autonomamente a questo tipo di progetto europeo.</t>
+          <t>Il bando Horizon riguarda la ricerca scientifica sull'impatto del rumore subacqueo antropico sugli ecosistemi marini, richiedendo capacità di ricerca avanzata e partenariati internazionali difficilmente accessibili a una PMI campana di piccole dimensioni. Sebbene il Cilento abbia una forte vocazione marinara, questo tipo di progetto è strutturalmente orientato a università, enti di ricerca e grandi consorzi scientifici, rendendo la partecipazione diretta di una PMI locale estremamente improbabile.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Understanding biomass flows in Europe</t>
+          <t>Improving circularity of multilayer flexible plastic food contact packaging</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-01</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -6955,19 +6955,19 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla mappatura dei flussi di biomassa è orientato a consorzi di ricerca accademica e grandi enti scientifici, rendendo l'accesso diretto per una PMI campana estremamente complesso senza un ruolo marginale in un partenariato. Non sono previsti finanziamenti per attività produttive, commerciali o di servizio tipiche delle PMI del Cilento.</t>
+          <t>Il bando Horizon richiede attività di ricerca avanzata su imballaggi plastici multistrato a contatto con alimenti, con consorzio europeo e capacità R&amp;D strutturata, requisiti difficilmente soddisfabili da una PMI del Cilento operante in settori tradizionali. L'unica finestra di accesso realistico è come partner secondario se la PMI produce o utilizza packaging alimentare e collabora con un ente di ricerca capofila.</t>
         </is>
       </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Developing methods to assess the presence, functions and sensitivity of groundwater ecosystems</t>
+          <t>Supporting pre-normative research for standardization of the bio-based products</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-08</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7007,14 +7007,14 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sugli ecosistemi delle acque sotterranee, strutture di R&amp;S consolidate e partnership accademiche internazionali, requisiti difficilmente soddisfabili da una PMI campana di piccole dimensioni. Sebbene il Cilento, con i suoi acquiferi carsici e aree protette, offra un contesto territoriale rilevante, la complessità progettuale e il profilo tecnico richiesto rendono questo bando accessibile solo a PMI altamente specializzate in scienze ambientali o idrologia, preferibilmente in consorzio con università.</t>
+          <t>Il bando Horizon finanzia ricerca pre-normativa sulla standardizzazione dei bio-prodotti, richiedendo capacità di ricerca avanzata e partnership con enti di ricerca europei, strutture difficilmente accessibili per una PMI cilentana di piccola dimensione. Le PMI del territorio, anche quelle agroalimentari o forestali che potrebbero trarre vantaggio dalla bio-economy, troverebbero barriere elevate in termini di requisiti tecnici, co-finanziamento e competenze progettuali necessarie per partecipare.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Advanced recovery of critical raw materials from Waste from Electrical and Electronic Equipment (WEEE)</t>
+          <t>Understanding biomass flows in Europe</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-05</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7049,19 +7049,19 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sul recupero avanzato di materie prime critiche dai RAEE richiede capacità di ricerca industriale avanzata, consorzi internazionali e budget elevati, risultando di fatto inaccessibile per la quasi totalità delle PMI campane e cilentane, che raramente operano nel settore del trattamento RAEE a livello tecnologico avanzato. Solo PMI specializzate in riciclo elettronico o metallurgia con partner universitari potrebbero candidarsi, ma non è il profilo tipico del tessuto produttivo locale.</t>
+          <t>Il bando Horizon focalizzato sui flussi di biomassa a scala europea richiede capacità di ricerca scientifica avanzata, partnership internazionali e strutture progettuali complesse, del tutto fuori dalla portata di una PMI campana di piccole dimensioni. Non sono previste spese operative o investimenti tipicamente accessibili alle imprese locali del Cilento.</t>
         </is>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Understanding and tackling the decline of insects</t>
+          <t>Developing methods to assess the presence, functions and sensitivity of groundwater ecosystems</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-02</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7101,14 +7101,14 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sul declino degli insetti è orientato a consorzi di ricerca accademica e istituti scientifici, richiedendo capacità di ricerca fondamentale difficilmente accessibili a una PMI campana. Solo PMI con forte vocazione R&amp;S nel settore entomologico o agro-ecologico potrebbero partecipare come partner secondari, non come capofila.</t>
+          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sugli ecosistemi delle acque sotterranee, con consorzî internazionali e competenze altamente specializzate difficilmente accessibili a una PMI standard del Cilento. Solo aziende con un profilo R&amp;D strutturato (es. laboratori ambientali, spin-off universitari) potrebbero partecipare come partner junior, non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Advancing integrated scenarios and prediction models for informing transition to a nature positive society</t>
+          <t>Advanced recovery of critical raw materials from Waste from Electrical and Electronic Equipment (WEEE)</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-03</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7148,14 +7148,14 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la costruzione di consorzi internazionali, capacità di ricerca avanzata e modellistica predittiva per scenari di transizione verso una 'nature positive society', competenze tipiche di enti di ricerca e università, non di PMI campane di piccola dimensione. Una PMI del Cilento potrebbe al massimo partecipare come partner minore in un consorzio, ma difficilmente come soggetto capofila o beneficiario diretto.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata sul recupero di materie prime critiche dai RAEE, con consorzio internazionale e budget elevati, struttura che esclude di fatto le PMI del Cilento non specializzate in questo settore industriale/tecnologico. Una piccola impresa campana difficilmente possiede le competenze di R&amp;S e la rete europea necessarie per competere su questa tipologia di progetto.</t>
         </is>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Pushing the frontier of knowledge and conservation action for deep sea ecosystems</t>
+          <t>Understanding and tackling the decline of insects</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-01</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7190,19 +7190,19 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla ricerca e conservazione degli ecosistemi marini profondi è orientato a consorzi di ricerca accademica e istituti scientifici internazionali, richiedendo competenze specialistiche e strutture di ricerca avanzate difficilmente disponibili in una PMI del Cilento. Sebbene il territorio abbia vicinanza al mare, la complessità progettuale e i requisiti tecnici rendono questo bando di fatto inaccessibile per una piccola o media impresa senza un partner di ricerca capofila.</t>
+          <t>Il bando Horizon UE sulla ricerca sul declino degli insetti è orientato a consorzi di ricerca accademica e istituti scientifici, con requisiti tecnici e amministrativi difficilmente compatibili con una PMI del Cilento. Solo aziende agricole o agrituristiche con un forte partner di ricerca potrebbero trovare uno spazio marginale come partner di progetto nel monitoraggio ambientale o nella produzione biologica.</t>
         </is>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Advancing recycling technologies for mixed post-consumer textiles waste from blended products</t>
+          <t>Advancing integrated scenarios and prediction models for informing transition to a nature positive society</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-05</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7242,14 +7242,14 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata nel settore del riciclo di tessuti misti post-consumo, con requisiti tecnici e burocratici elevati tipici dei programmi europei di R&amp;S, difficilmente accessibili a una PMI di piccole dimensioni del Cilento senza un consorzio strutturato con università o centri di ricerca. Il territorio del Cilento non presenta inoltre una filiera tessile consolidata che renderebbe il bando strategicamente rilevante per le imprese locali.</t>
+          <t>Il bando Horizon richiede la costruzione di consorzi internazionali di ricerca con forte componente scientifica per sviluppare modelli predittivi sulla transizione verso una società 'nature positive', un contesto che esclude di fatto le PMI di piccola dimensione prive di strutture R&amp;D dedicate. Una PMI del Cilento potrebbe partecipare solo come partner di un consorzio guidato da università o centri di ricerca, con ruolo marginale e oneri amministrativi molto elevati.</t>
         </is>
       </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Bioremediation of Ukraine’s ecosystems contaminated by conflicts</t>
+          <t>Pushing the frontier of knowledge and conservation action for deep sea ecosystems</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-03</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7284,19 +7284,19 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la bonifica degli ecosistemi ucraini contaminati da conflitti bellici, un tema lontano dalle attività tipiche di una PMI campana o cilentana; inoltre i progetti Horizon richiedono consorzi internazionali, elevate competenze di ricerca e capacità amministrative difficilmente accessibili a una piccola impresa senza un partner universitario o di ricerca strutturato.</t>
+          <t>Il bando Horizon Europa sulla ricerca e conservazione degli ecosistemi marini profondi è orientato a consorzi di grandi enti di ricerca e università, con requisiti tecnici e finanziari difficilmente accessibili per una PMI campana. Anche se il Cilento ha una costa con vocazione marina, una piccola impresa non dispone delle capacità scientifiche e progettuali richieste per partecipare da capofila o partner sostanziale in un progetto di frontiera di questo tipo.</t>
         </is>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating and deploying innovative collection, sorting-for-reuse and repair systems for textiles at city/region level (Circular Cities and Regions Initiative topic)</t>
+          <t>Advancing recycling technologies for mixed post-consumer textiles waste from blended products</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-02</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7331,19 +7331,19 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede progetti dimostrativi su scala urbana/regionale per sistemi innovativi di raccolta, smistamento e riparazione tessile, con budget elevati e consorziate internazionali: una PMI del Cilento difficilmente può guidare un progetto simile, al massimo potrebbe partecipare come partner in un consorzio capeggiato da enti di ricerca o grandi municipalità. Il settore tessile non è inoltre rappresentativo del tessuto produttivo locale del Cilento, orientato prevalentemente verso agroalimentare e turismo.</t>
+          <t>Il bando Horizon richiede partnership europee strutturate, capacità di R&amp;D avanzata e budget di progetto elevati, barriere difficilmente superabili per una PMI del Cilento senza un ecosistema industriale tessile consolidato. Il settore target (riciclo di tessuti misti post-consumo) è inoltre lontano dalle vocazioni produttive predominanti nell'area (turismo, agricoltura, agroalimentare).</t>
         </is>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Ensuring continuous effectiveness of protected areas in conserving habitats and species while facing intensifying drivers of biodiversity loss</t>
+          <t>Bioremediation of Ukraine’s ecosystems contaminated by conflicts</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-02</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -7378,19 +7378,19 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla conservazione delle aree protette è orientato a consorzi di ricerca e grandi enti scientifici, con requisiti progettuali e capacità amministrative difficilmente gestibili da una PMI autonomamente. Una PMI del Cilento (area Parco Nazionale) potrebbe partecipare solo in qualità di partner secondario in un consorzio internazionale, ruolo che richiede relazioni pregresse con università o centri di ricerca e competenze specifiche in biodiversità.</t>
+          <t>Il bando Horizon è focalizzato sulla bonifica ambientale di ecosistemi ucraini contaminati da conflitti bellici, un contesto operativo molto specifico e lontano dal territorio campano/cilentano. Le PMI del Cilento, anche quelle attive in ambito ambientale o agricolo, difficilmente possiedono le competenze tecnico-scientifiche in biorisanamento e i requisiti consortili richiesti da Horizon per competere in questo tipo di call.</t>
         </is>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Advancing the European bio-based innovation enabled by biotechnology and biomanufacturing concepts</t>
+          <t>Demonstrating and deploying innovative collection, sorting-for-reuse and repair systems for textiles at city/region level (Circular Cities and Regions Initiative topic)</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-04</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -7425,19 +7425,19 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata in biotecnologia e biomanufacturing, con consorzî internazionali e competenze scientifiche difficilmente disponibili in una PMI di piccola dimensione del Cilento. L'accesso è realisticamente limitato a spin-off universitari o imprese già inserite in reti di R&amp;S europee.</t>
+          <t>Il bando Horizon richiede la dimostrazione di sistemi innovativi di raccolta, smistamento e riparazione di tessili su scala urbana/regionale, con consorziate di livello europeo e capacità di gestione progettuale complessa, difficilmente accessibili a una PMI del Cilento senza un solido partenariato internazionale. Le spese finanziabili riguardano R&amp;S e pilotaggio su larga scala, ambienti tipicamente presidiati da grandi enti di ricerca o municipalità, non da piccole imprese manifatturiere o di servizi locali.</t>
         </is>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Bioeconomy policy support hub for Member States, regions and sectors</t>
+          <t>Ensuring continuous effectiveness of protected areas in conserving habitats and species while facing intensifying drivers of biodiversity loss</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-04</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -7472,19 +7472,19 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia principalmente enti di ricerca, istituzioni pubbliche e grandi consorzi per sviluppare politiche di bioeconomia a livello europeo, non attività operative di PMI. Una piccola impresa del Cilento non ha le capacità strutturali (rendicontazione Horizon, partenariati internazionali, overhead di progetto) per partecipare direttamente in modo competitivo.</t>
+          <t>Il bando Horizon europeo sulla conservazione delle aree protette e della biodiversità è orientato a consorzi di ricerca e istituzioni accademiche, con requisiti di partnership transnazionale complessi e budget elevati difficilmente gestibili da una PMI campana. Sebbene il Cilento rientri in aree protette rilevanti (Parco Nazionale), una piccola impresa difficilmente può assumere il ruolo di capofila o coprire i costi di accesso a questi programmi senza un forte partner di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>ERC PROOF OF CONCEPT GRANTS</t>
+          <t>Advancing the European bio-based innovation enabled by biotechnology and biomanufacturing concepts</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-POC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-07</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -7524,34 +7524,34 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Il grant ERC Proof of Concept è riservato esclusivamente a ricercatori già titolari di un grant ERC attivo, escludendo di fatto le PMI che non abbiano un Principal Investigator con questo requisito. Una PMI del Cilento potrebbe al massimo partecipare come partner di valorizzazione, ma non come beneficiario diretto del finanziamento.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata in biotecnologia e biomanufacturing, con consorzio internazionale e budget elevati tipicamente incompatibili con le dimensioni e le competenze di una PMI del Cilento. Una PMI potrebbe partecipare solo come partner junior in un consorzio già strutturato, ruolo difficile da costruire senza reti scientifiche consolidate.</t>
         </is>
       </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Quality Label Humanitarian Aid - Full Procedure</t>
+          <t>Bioeconomy policy support hub for Member States, regions and sectors</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>10/06/2021</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESC-HUMAID-2021-QUAL-LABEL-FP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-06</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>UE - ESC2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -7571,29 +7571,29 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Il bando ESC2027 Quality Label per gli aiuti umanitari riguarda organizzazioni del Corpo Europeo di Solidarietà che operano in contesti umanitari internazionali, non è destinato a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti strutturali né la missione istituzionale per accedere a questa tipologia di certificazione.</t>
+          <t>Il bando finanzia hub di supporto alle politiche di bioeconomia rivolti a istituzioni pubbliche, enti di ricerca e organismi governativi, non a PMI operative. Una piccola impresa del Cilento non ha i requisiti strutturali né il profilo istituzionale per candidarsi direttamente a questo tipo di progetto Horizon.</t>
         </is>
       </c>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>From lab to market: Strengthening the role of Technology Transfer Offices in bringing knowledge to the market</t>
+          <t>ERC PROOF OF CONCEPT GRANTS</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIE-2026-03-CONNECT-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-POC</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -7618,14 +7618,14 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto principalmente a università e uffici di trasferimento tecnologico (TTO), non a PMI come beneficiari diretti; una PMI del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio, ma senza accesso diretto ai finanziamenti né copertura di spese operative aziendali tipiche.</t>
+          <t>Il grant ERC Proof of Concept è riservato esclusivamente a ricercatori già beneficiari di un grant ERC attivo o concluso da meno di 12 mesi, escludendo di fatto le PMI che non abbiano un Principal Investigator ERC nel proprio organico. Una PMI del Cilento potrebbe partecipare solo in veste di partner commerciale di un ricercatore ERC, ruolo difficilmente accessibile senza solide reti con centri di ricerca europei.</t>
         </is>
       </c>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Environment governance</t>
+          <t>Quality Label Humanitarian Aid - Full Procedure</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -7635,17 +7635,17 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>10/06/2021</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-ENV-GOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESC-HUMAID-2021-QUAL-LABEL-FP</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - ESC2027</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -7660,19 +7660,19 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE - Environment Governance è orientato a progetti di scala europea con requisiti tecnici e amministrativi elevati, normalmente accessibili a enti pubblici, università o grandi organizzazioni ambientali; una PMI del Cilento difficilmente dispone delle risorse e dei partner transnazionali richiesti per candidarsi autonomamente. L'unica opportunità concreta sarebbe partecipare come partner secondario in un consorzio guidato da soggetti più strutturati, ad esempio nel settore della gestione costiera o della biodiversità del Parco Nazionale del Cilento.</t>
+          <t>Il bando ESC2027 Quality Label per gli Aiuti Umanitari è destinato a organizzazioni no-profit e ONG che operano in contesti di crisi internazionali, non a PMI commerciali. Una piccola o media impresa del Cilento non ha i requisiti soggettivi né il profilo operativo per accedere a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Circular Economy and Zero Pollution</t>
+          <t>From lab to market: Strengthening the role of Technology Transfer Offices in bringing knowledge to the market</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -7682,17 +7682,17 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-ENV-ENVIRONMENT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIE-2026-03-CONNECT-01</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -7707,19 +7707,19 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a consorzi, enti di ricerca e organismi pubblici con forte capacità progettuale europea; per una PMI del Cilento l'accesso diretto è molto difficile senza un partenariato consolidato, e i costi di gestione di un progetto LIFE (rendicontazione, co-finanziamento, durata pluriennale) superano spesso le capacità amministrative di una piccola impresa. Un coinvolgimento indiretto come partner tecnico in un consorzio guidato da un ente capofila rimane l'unica via realistica.</t>
+          <t>Il bando è rivolto principalmente agli uffici di trasferimento tecnologico (TTO) di università ed enti di ricerca, non direttamente alle PMI; una piccola impresa del Cilento potrebbe beneficiarne solo indirettamente come partner o destinataria finale dei servizi di technology transfer, ma non come soggetto beneficiario principale.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Climate Governance and Information</t>
+          <t>Environment governance</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-GOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-ENV-GOV</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -7759,14 +7759,14 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Climate Governance and Information finanzia principalmente campagne di comunicazione, advocacy e progetti pilota su scala europea sulla governance climatica, richiedendo partnership internazionali e capacità progettuali elevate difficilmente accessibili a una PMI del Cilento senza un consorzio strutturato. I costi ammissibili riguardano attività di disseminazione e sensibilizzazione climatica, non investimenti produttivi o operativi tipici delle PMI locali.</t>
+          <t>Il programma LIFE - Environment Governance è orientato principalmente a enti pubblici, ONG e organismi di ricerca per progetti di governance ambientale su scala europea; le PMI possono partecipare solo in qualità di partner secondari, con oneri amministrativi e co-finanziamento elevati difficilmente sostenibili per una piccola impresa del Cilento.</t>
         </is>
       </c>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Climate Change Adaptation</t>
+          <t>Circular Economy and Zero Pollution</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-CCA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-ENV-ENVIRONMENT</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -7806,14 +7806,14 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e consorzi con elevata capacità progettuale europea; una PMI del Cilento difficilmente può accedere autonomamente, poiché richiede partenariati transnazionali, co-finanziamento consistente e competenze specifiche nella redazione di progetti UE in materia di adattamento climatico. L'interesse residuo sussiste solo se la PMI intende partecipare come partner secondario in un consorzio guidato da un soggetto capofila strutturato.</t>
+          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, organismi di ricerca e grandi consorzi, con requisiti di partenariato europeo e capacità finanziaria difficilmente compatibili con una PMI del Cilento; i progetti finanziano azioni dimostrative su economia circolare e riduzione dell'inquinamento, ma la complessità gestionale e i cofinanziamenti richiesti rendono l'accesso diretto quasi impraticabile senza capofila istituzionale.</t>
         </is>
       </c>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Climate Change Mitigation</t>
+          <t>Climate Governance and Information</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-CCM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-GOV</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7853,14 +7853,14 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e consorzi con forte capacità progettuale europea; le PMI possono partecipare solo come partner in progetti complessi, rendendo l'accesso diretto molto difficile per una piccola impresa del Cilento senza esperienza nella rendicontazione UE. Le spese finanziabili riguardano azioni dimostrative per la mitigazione climatica, non attività produttive ordinarie.</t>
+          <t>Il programma LIFE Climate Governance and Information finanzia progetti di comunicazione, campagne di sensibilizzazione e policy sul clima a livello europeo, tipicamente gestiti da enti pubblici, ONG o grandi consorzi, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un partenariato strutturato. I costi di progettazione, la complessità burocratica europea e la natura istituzionale dei destinatari previsti scoraggiano una candidatura autonoma da parte di una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Nature and Biodiversity</t>
+          <t>Climate Change Adaptation</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-NAT-NATURE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-CCA</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Nature and Biodiversity finanzia progetti di conservazione della natura e biodiversità, ma è strutturalmente orientato a enti pubblici, ONG e istituti di ricerca, con budget minimi elevati e procedure complesse che lo rendono difficilmente accessibile a una PMI in autonomia. Una PMI del Cilento (area protetta con Parco Nazionale) potrebbe partecipare solo come partner di un consorzio capeggiato da soggetti istituzionali, con ruolo marginale e oneri amministrativi sproporzionati.</t>
+          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e grandi organizzazioni con capacità progettuale europea; una PMI del Cilento difficilmente può accedere direttamente senza essere parte di un consorzio capofila, e i costi di progettazione e gestione rendicontativa sono spesso proibitivi per realtà di piccole dimensioni. L'adattamento ai cambiamenti climatici può tuttavia interessare aziende agricole o turistiche cilentane come partner secondari, ma l'accesso autonomo resta poco praticabile.</t>
         </is>
       </c>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Nature Governance and Information</t>
+          <t>Climate Change Mitigation</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-NAT-GOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-CLIMA-CCM</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -7947,14 +7947,14 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Nature Governance and Information finanzia principalmente enti pubblici, ONG ambientali e istituti di ricerca per progetti di governance della natura e comunicazione ambientale, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un partenariato strutturato con soggetti istituzionali. Una piccola impresa potrebbe partecipare solo come partner secondario in progetti legati alla biodiversità o alla gestione del Parco Nazionale del Cilento, ma i costi di progettazione europei e i requisiti amministrativi rendono questa strada poco praticabile autonomamente.</t>
+          <t>Il programma LIFE è storicamente orientato a enti pubblici, università e grandi organizzazioni con forte capacità progettuale europea; una PMI del Cilento difficilmente può accedere autonomamente, data la complessità della rendicontazione e la necessità di partnership transnazionali per progetti di mitigazione climatica su larga scala.</t>
         </is>
       </c>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Projects on Legislative and Policy Priorities in the fields of Nature &amp; Biodiversity and Circular Economy &amp; Quality of Life</t>
+          <t>Nature and Biodiversity</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-NAT-ENV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-NAT-NATURE</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7994,14 +7994,14 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti di scala europea su biodiversità ed economia circolare, con requisiti tecnici e amministrativi elevati che rendono difficile la partecipazione diretta di una PMI senza un consorzio strutturato; tuttavia, una PMI del Cilento attiva in settori come gestione rifiuti, turismo naturalistico o agricoltura biologica potrebbe entrare come partner di un progetto coordinato da enti di ricerca o associazioni ambientali.</t>
+          <t>Il programma LIFE Nature and Biodiversity finanzia principalmente enti pubblici, ONG e istituti di ricerca per progetti di conservazione degli habitat naturali; una PMI campana, anche operante nel Cilento (area Parco Nazionale), trova difficoltà concrete di accesso per i requisiti di partenariato, le soglie di budget elevate e la complessità burocratica della rendicontazione europea diretta.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Ecodesign and energy labelling compliance support facility for suppliers and retailers</t>
+          <t>Nature Governance and Information</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-ENER-COMPLIANCE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-SAP-NAT-GOV</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a progetti complessi di sistema per supportare fornitori e retailer nella conformità alle normative ecodesign ed etichettatura energetica, con budget elevati e requisiti tecnici difficilmente alla portata di una PMI del Cilento senza partnership strutturate. Una piccola impresa campana troverebbe barriere significative in termini di capacità progettuale, cofinanziamento richiesto e scala europea dell'intervento atteso.</t>
+          <t>Il programma LIFE Nature Governance and Information finanzia principalmente enti pubblici, ONG ambientali e istituti di ricerca per progetti di governance della natura e biodiversità, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un partenariato strutturato con soggetti istituzionali. Una PMI potrebbe partecipare solo come partner secondario in progetti coordinati da enti come il Parco Nazionale del Cilento, con ruoli tecnici specifici (es. servizi di monitoraggio ambientale o comunicazione), ma non come beneficiario principale.</t>
         </is>
       </c>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Multilevel climate and energy dialogue to deliver the Governance Regulation and the post–2030 energy and climate policy framework</t>
+          <t>Projects on Legislative and Policy Priorities in the fields of Nature &amp; Biodiversity and Circular Economy &amp; Quality of Life</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-ENER-GOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-NAT-ENV</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8083,19 +8083,19 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE finanzia progetti di dialogo multilivello sulla governance climatica ed energetica, destinati principalmente a enti pubblici, organizzazioni non governative e istituti di ricerca con capacità di coordinamento transnazionale. Una PMI campana, anche del Cilento, difficilmente possiede i requisiti tecnici e organizzativi per candidarsi come capofila o partner rilevante in questo tipo di iniziativa policy-oriented.</t>
+          <t>Il programma LIFE è orientato a progetti di scala europea su policy e normativa ambientale, con requisiti di partenariato transnazionale e capacità gestionale elevate che difficilmente una PMI del Cilento può soddisfare autonomamente. Le PMI possono partecipare solo come partner junior in consorzi guidati da enti pubblici o grandi organizzazioni ambientali, rendendo l'accesso diretto ai fondi molto limitato.</t>
         </is>
       </c>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Technical Assistance preparation of SNaPs</t>
+          <t>Ecodesign and energy labelling compliance support facility for suppliers and retailers</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-NAT-SNAP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-ENER-COMPLIANCE</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8130,19 +8130,19 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE riguarda l'assistenza tecnica per la preparazione di Piani Nazionali d'Azione per la Natura (SNaPs), destinato principalmente a enti pubblici, autorità nazionali e organizzazioni ambientali, non a PMI. Una piccola impresa del Cilento non ha i requisiti soggettivi né le capacità tecniche richieste per candidarsi come beneficiario diretto.</t>
+          <t>Il bando LIFE è orientato a progetti di sistema su scala europea per supportare la conformità normativa sull'ecodesign e l'etichettatura energetica, con beneficiari tipici quali consorzi, enti pubblici o grandi organizzazioni di categoria, non PMI singole. Una piccola impresa del Cilento difficilmente possiede la capacità progettuale e le partnership transnazionali richieste per accedere direttamente a questo strumento.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Technical Assistance preparation of ENV SIPs</t>
+          <t>Multilevel climate and energy dialogue to deliver the Governance Regulation and the post–2030 energy and climate policy framework</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-ENV-SIP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-PLP-ENER-GOV</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8182,14 +8182,14 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE TA per la preparazione di ENV SIPs (Strategic Integrated Projects ambientali) è destinato principalmente a enti pubblici, autorità regionali e grandi organizzazioni ambientali, non a PMI: richiede competenze tecniche specializzate nella pianificazione ambientale strategica e capacità di coordinare progetti multi-stakeholder su scala nazionale/regionale. Una piccola impresa del Cilento non ha i requisiti strutturali né il profilo istituzionale per candidarsi come beneficiario principale.</t>
+          <t>Il bando LIFE 2027 sul dialogo multilivello per la governance climatica ed energetica è orientato a enti pubblici, organizzazioni non governative e istituzioni, non a PMI operative. Una piccola impresa del Cilento non ha la struttura né il profilo istituzionale per candidarsi come soggetto proponente in un progetto di policy dialogue europeo.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>technical Assistance preparation of CLIMA SIPs</t>
+          <t>Technical Assistance preparation of SNaPs</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-CLIMA-SIP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-NAT-SNAP</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE TA per la preparazione di Strategic Integrated Projects sul clima è destinato principalmente a enti pubblici, autorità regionali e grandi organizzazioni ambientali, non a PMI: richiede capacità progettuali complesse e un ruolo di capofila istituzionale difficilmente accessibile per una piccola impresa del Cilento. Una PMI potrebbe al massimo partecipare come partner tecnico specializzato in consulenza ambientale o climatica, ma le probabilità di accesso diretto sono molto limitate.</t>
+          <t>Si tratta di un bando LIFE dell'UE per assistenza tecnica alla preparazione di Piani Strategici Nazionali (SNaPs), destinato tipicamente a enti pubblici, autorità nazionali o grandi organizzazioni ambientali, non a PMI. Una piccola impresa del Cilento non ha i requisiti tecnici né istituzionali per accedere direttamente a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>SSbD bio-based solutions for home and/or personal care</t>
+          <t>Technical Assistance preparation of ENV SIPs</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -8246,17 +8246,17 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-ENV-SIP</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -8271,19 +8271,19 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzi internazionali e budget elevati, rendendo l'accesso diretto molto difficile per una PMI campana di piccole dimensioni; il focus su soluzioni bio-based per cura della casa e persona può essere rilevante solo se la PMI opera già in R&amp;S chimica/green con partner universitari consolidati.</t>
+          <t>Il bando LIFE 2027 per la preparazione di Strategic Integrated Projects ambientali è orientato a enti pubblici, autorità nazionali e organismi di coordinamento istituzionale, non a PMI; la complessità procedurale e i requisiti di capacità tecnica in materia di policy ambientale europea rendono questo strumento di fatto inaccessibile per una piccola impresa del Cilento.</t>
         </is>
       </c>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Bio-based chemicals and/or materials from woody residues</t>
+          <t>technical Assistance preparation of CLIMA SIPs</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -8293,17 +8293,17 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-TA-PP-CLIMA-SIP</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -8318,19 +8318,19 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzi internazionali e investimenti elevati tipici di grandi enti o università, rendendo l'accesso diretto quasi impossibile per una PMI del Cilento senza un partner capofila strutturato. Il focus su chimica e materiali da residui legnosi potrebbe teoricamente interessare aziende della filiera forestale locale, ma le barriere amministrative e finanziarie sono proibitive per una piccola impresa autonoma.</t>
+          <t>Il bando LIFE 2027 per l'assistenza tecnica alla preparazione di CLIMA SIPs (Strategic Integrated Projects) è destinato principalmente a enti pubblici, autorità regionali e grandi consorzi istituzionali, non a PMI singole. Una piccola impresa del Cilento non ha i requisiti strutturali né la capacità progettuale per guidare un SIP climatico europeo, sebbene potrebbe partecipare marginalmente come partner tecnico specializzato in soluzioni ambientali.</t>
         </is>
       </c>
     </row>
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Develop breakthrough and sustainable bio-based textile fibres</t>
+          <t>SSbD bio-based solutions for home and/or personal care</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-03</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8370,14 +8370,14 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede ricerca di frontiera su fibre tessili bio-based con elevata componente scientifica e consorzio internazionale, requisiti difficilmente soddisfacibili da una PMI del Cilento senza partnership strutturate con università o grandi player del settore tessile. Il finanziamento è orientato a progetti ad alto contenuto tecnologico con budget rilevanti, lontani dalla dimensione operativa tipica delle piccole imprese campane.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, consorzio internazionale e budget elevati, rendendo l'accesso diretto estremamente difficile per una PMI del Cilento senza un partner universitario o un centro R&amp;S strutturato. Una PMI del settore cosmetico o detergenti bio-based potrebbe partecipare solo come partner industriale in un consorzio già formato, non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>High-performance, circular-by-design, bio-based thermosets</t>
+          <t>Develop breakthrough and sustainable bio-based textile fibres</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-03</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8417,14 +8417,14 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede attività di ricerca avanzata su materiali biobasati e termoindurenti circolari, con consorzio internazionale e capacità R&amp;D strutturata: barriere tecniche, amministrative e finanziarie lo rendono inaccessibile per la maggior parte delle PMI campane, specialmente nel Cilento dove mancano filiere industriali di chimica verde. Una PMI potrebbe partecipare solo come partner di un consorzio europeo già formato, con ruolo marginale.</t>
+          <t>Il bando Horizon richiede attività di ricerca di frontiera su fibre tessili bio-based, con consorzî internazionali e capacità R&amp;D avanzate difficilmente sostenibili da una PMI del Cilento senza partner universitari o industriali consolidati. Le PMI del territorio, prevalentemente orientate ad agricoltura, turismo e artigianato, non dispongono in genere delle infrastrutture tecnologiche e dei profili di ricercatori necessari per competere su questo tipo di call.</t>
         </is>
       </c>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Bio-based additives as alternatives to unlock and increase recyclability and/or biodegradability</t>
+          <t>High-performance, circular-by-design, bio-based thermosets</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-04</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8464,14 +8464,14 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, consorzi internazionali e competenze specialistiche in chimica dei materiali bio-based, requisiti difficilmente accessibili per una PMI del Cilento senza un solido track record in R&amp;D europeo. Potrebbe avere senso solo come partner junior in un consorzio guidato da università o grandi aziende del settore packaging/plastica sostenibile.</t>
+          <t>Il bando Horizon UE richiede attività di ricerca avanzata su materiali biobasati e termoindurenti ad alte prestazioni progettati per la circolarità, con consorzio internazionale e capacità R&amp;S strutturata: barriere tecniche, amministrative e finanziarie troppo elevate per una PMI campana di piccole dimensioni, specialmente nel Cilento dove mancano hub industriali del settore chimico-materiali. Solo PMI con laboratori interni o partnership con università potrebbe candidarsi come partner di progetto.</t>
         </is>
       </c>
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>SSbD bio-based alternatives for fertilising and/or crop protection products</t>
+          <t>Bio-based additives as alternatives to unlock and increase recyclability and/or biodegradability</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-02</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede capacità di ricerca e sviluppo avanzate, consorzio internazionale e budget di progetto elevati, elementi difficilmente gestibili da una PMI autonomamente; tuttavia, una PMI agricola del Cilento attiva in produzioni biologiche o agrofarmaci potrebbe partecipare come partner in un consorzio guidato da enti di ricerca, contribuendo con know-how locale su colture tipiche come olivo o ortaggi DOP.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, consorzi internazionali e competenze specifiche in chimica dei materiali bio-based e riciclabilità, strutture tipiche di grandi centri di ricerca o multinazionali. Una PMI del Cilento difficilmente possiede le risorse tecniche e amministrative per partecipare autonomamente, salvo come partner junior in un consorzio già formato.</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede capacità di ricerca avanzata in bioraffinerie e tecnologie di separazione/purificazione, con consorzzi internazionali e budget elevati difficilmente accessibili a una PMI campana di piccole dimensioni; il Cilento, pur con vocazione agricola e agroalimentare, difficilmente dispone di infrastrutture R&amp;D adeguate per competere in questo specifico ambito biotecnologico industriale.</t>
+          <t>Il bando Horizon UE sulla separazione e purificazione nelle bioraffinerie richiede competenze di ricerca avanzata, consorzi internazionali e capacità progettuali difficilmente accessibili a una PMI del Cilento senza un partner universitario o un centro di ricerca. Solo aziende del settore biotecnologico o chimico-industriale con già esperienza in progetti europei potrebbero candidarsi, tipicamente in qualità di partner e non come capofila.</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8605,7 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede consorzi internazionali, capacità di ricerca avanzata e budget elevati difficilmente gestibili da una PMI del Cilento senza un partner capofila universitario o industriale strutturato. Le attività finanziate riguardano sviluppo di polimeri bio-based con approccio SSbD (Safe and Sustainable by Design), lontano dalle filiere produttive tipiche del territorio cilentano.</t>
+          <t>Il bando Horizon richiede attività di ricerca avanzata su polimeri bio-based con approccio Safe and Sustainable by Design, richiedendo capacità di R&amp;D, partnership internazionali e strutture scientifiche difficilmente compatibili con una PMI di piccole dimensioni del Cilento. Il settore chimico-industriale di riferimento è praticamente assente nel territorio cilentano, rendendo la partecipazione concreta molto improbabile senza un consorzio europeo già strutturato.</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede consorzi internazionali, elevata capacità di ricerca e sviluppo e budget di progetto tipicamente superiori ai 5-10 milioni di euro, rendendo l'accesso diretto molto difficile per una PMI campana di piccola dimensione; tuttavia, una PMI del Cilento attiva in settori come agroalimentare, cosmesi naturale o trasformazione di biomasse potrebbe partecipare come partner in un consorzio, coprendo spese di ricerca applicata, personale tecnico e attrezzature per lo sviluppo di processi bio-based circolari.</t>
+          <t>Il bando Horizon Europe richiede consorzi internazionali, capacità di ricerca avanzata e budget elevati, rendendolo poco accessibile per una PMI di piccola dimensione del Cilento senza partner universitari o industriali consolidati; tuttavia, una PMI agroalimentare o forestale del territorio potrebbe partecipare come partner in progetti su bioeconomia circolare, valorizzazione di scarti agricoli o biomasse locali.</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, partnership internazionali e budget progettuali elevati, strutturalmente incompatibili con le dimensioni e le risorse tipiche di una PMI cilentana. Solo aziende del settore packaging o chimica dei materiali con laboratori R&amp;D interni potrebbero partecipare, preferibilmente in consorzio con università o grandi imprese.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, partnership internazionali e co-finanziamenti elevati, barriere difficilmente superabili per una PMI del Cilento. Il focus su film e rivestimenti per imballaggi circolari riguarda settori industriali (chimica, packaging) scarsamente presenti nel tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede consorzi internazionali, capacità di ricerca avanzata e risorse amministrative difficilmente accessibili a una PMI di piccola dimensione del Cilento; tuttavia, una PMI agroalimentare o forestale del territorio con sottoprodotti vegetali (es. sanse, scarti ortofrutticoli) potrebbe partecipare come partner industriale in un consorzio guidato da università o centri di ricerca, coprendo attività di sviluppo e dimostrazione.</t>
+          <t>Il bando Horizon UE richiede consorzi internazionali, elevata capacità di ricerca e sviluppo e competenze biotech avanzate, barriere difficilmente superabili per una PMI del Cilento senza un solido network europeo. Tuttavia, una PMI agricola o agroalimentare locale potrebbe partecipare come partner in un consorzio guidato da un ente di ricerca, valorizzando biomasse residuali tipiche del territorio (olive, castagne, fichi).</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla competitività delle bioraffinerie tramite biotecnologie richiede capacità di ricerca avanzata, consorzi internazionali e budget elevati, risultando di difficile accesso per una PMI campana di piccole dimensioni. Tuttavia, imprese del Cilento attive in agricoltura, trasformazione agroalimentare o gestione di biomasse potrebbero partecipare come partner junior in progetti guidati da enti di ricerca, valorizzando scarti agricoli o colture locali.</t>
+          <t>Il bando Horizon Europe sulla bioraffineria richiede capacità di ricerca biotecnologica avanzata, partnership internazionali e budget progettuali elevati, difficilmente accessibili a una PMI di piccola dimensione del Cilento. Sebbene il territorio offra biomasse agricole e forestali potenzialmente valorizzabili, la complessità tecnica e burocratica di Horizon lo rende di fatto inaccessibile senza un consorzio con università o grandi imprese.</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede consorzi internazionali di ricerca con elevata capacità progettuale e scientifica, difficilmente accessibili in modo autonomo da una PMI campana di piccole dimensioni; tuttavia, un'azienda agroalimentare del Cilento (es. produttori di legumi, cereali antichi o ingredienti tipici locali) potrebbe partecipare come partner industriale in un consorzio coordinato da università o centri di ricerca, valorizzando materie prime territoriali nel contesto della diversificazione delle fonti nutrizionali europee.</t>
+          <t>Il bando Horizon UE richiede consorzi internazionali di ricerca con elevata capacità tecnico-scientifica e finanziaria, strutturalmente difficili da costruire per una PMI del Cilento. Una piccola impresa agroalimentare locale potrebbe partecipare solo come partner secondario in un progetto già strutturato da università o grandi enti di ricerca, rendendo l'accesso diretto sostanzialmente impraticabile.</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>I LIFE Operating Grants sono destinati principalmente a organizzazioni non governative e associazioni attive nella tutela ambientale e climatica, non a PMI commerciali; inoltre richiedono struttura organizzativa consolidata a livello europeo e capacità amministrativa elevata, difficilmente compatibili con una piccola impresa del Cilento.</t>
+          <t>I LIFE Operating Grants sono destinati esclusivamente a organizzazioni non governative e associazioni no-profit attive nella tutela ambientale e climatica, non a PMI commerciali; inoltre richiedono struttura organizzativa consolidata a livello europeo e capacità amministrative complesse, del tutto incompatibili con una piccola impresa del Cilento.</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la creazione di consorzi di ricerca internazionali con capacità di sviluppo di sistemi AI per la gestione del suolo, strutture organizzative e budget tipici di università o grandi enti di ricerca, rendendo la partecipazione diretta di una PMI del Cilento estremamente difficile senza un ruolo marginale come partner tecnico specializzato.</t>
+          <t>Il bando Horizon richiede la costruzione di consorzi di ricerca internazionali e competenze avanzate in AI e sperimentazione agronomica di lungo periodo, barriere difficilmente superabili per una PMI del Cilento senza un partner universitario o di ricerca già consolidato. Una piccola impresa agricola o agritech potrebbe partecipare solo come soggetto terzo in un consorzio capofila, con ruolo marginale e accesso indiretto ai fondi.</t>
         </is>
       </c>
     </row>
@@ -8976,12 +8976,12 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la salute del suolo in Ucraina con focus su innovazione aperta e centrata sull'utente: si tratta di una call europea con requisiti consortili complessi e ambito geografico specifico (Ucraina) che rende l'accesso diretto estremamente difficile per una PMI campana del Cilento, priva di struttura dedicata alla ricerca e di partnership internazionali già consolidate. Solo una PMI con competenze tecnologiche in agritech o telerilevamento potrebbe valutare un ruolo marginale in un consorzio più ampio.</t>
+          <t>Il bando Horizon riguarda la salute del suolo in Ucraina e richiede consorzi internazionali di ricerca con competenze molto specializzate, struttura progettuale complessa e capacità amministrative difficilmente sostenibili da una PMI campana di piccola dimensione. Il focus geografico sull'Ucraina esclude qualsiasi ricaduta diretta sul territorio del Cilento o sulla produzione agricola locale.</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla resistenza antimicrobica nei suoli richiede capacità di ricerca scientifica avanzata, partnership internazionali e strutture di laboratorio difficilmente accessibili a una PMI del Cilento. Le risorse finanziabili riguardano attività di R&amp;S ad alto contenuto scientifico, più adatte a università, centri di ricerca o grandi imprese con divisioni R&amp;D dedicate.</t>
+          <t>Il bando Horizon richiede partnership internazionali, capacità di ricerca scientifica avanzata e strutture dedicate alla R&amp;S che difficilmente una PMI del Cilento possiede autonomamente; il tema specifico (resistenza antimicrobica e biosintesi di antibiotici nel suolo con approccio One-Health) è altamente specialistico e orientato a centri di ricerca universitari, rendendo l'accesso diretto per una PMI locale molto improbabile senza un ruolo marginale in un consorzio guidato da enti accademici.</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sui 'beni comuni globali' è orientato a grandi consorzi di ricerca accademica e istituzionale a livello europeo, con requisiti di partnership transnazionale complessi e processi di candidatura che richiedono competenze specializzate difficilmente accessibili a una PMI del Cilento senza un solido network scientifico preesistente. Non finanzia attività produttive o commerciali tipiche delle piccole imprese locali.</t>
+          <t>Il bando Horizon Europe sulla governance sostenibile dei beni comuni globali è orientato a consorzi di ricerca universitari e grandi organizzazioni internazionali, con requisiti di partenariato transnazionale complessi e budget elevati difficilmente gestibili da una PMI del Cilento. Non finanzia attività produttive o commerciali dirette, rendendo l'accesso concreto per una piccola impresa locale sostanzialmente impraticabile senza un ruolo marginale in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla long-term care policy è orientato a enti di ricerca, università e grandi consorzi internazionali per produrre analisi di policy demografica a livello UE, non a PMI operative. Una piccola impresa del Cilento, anche del settore sociosanitario o assistenziale, difficilmente dispone della struttura progettuale e dei partner transnazionali richiesti per competere in questo tipo di call.</t>
+          <t>Il bando Horizon europeo sulla riforma delle politiche di long-term care è orientato a enti di ricerca, università e consorzi transnazionali, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un ruolo da partner secondario. Non finanzia prodotti o servizi commerciali, ma ricerca policy-oriented su scala europea, con requisiti di consorzio internazionale incompatibili con le capacità organizzative di una piccola impresa.</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca accademica sulla trasformazione della pubblica amministrazione e la formazione del personale civile governativo: non è accessibile a una PMI del Cilento, che non rientra tra i beneficiari tipici (università, centri di ricerca, enti pubblici). Non sono finanziabili attività produttive, commerciali o di sviluppo aziendale.</t>
+          <t>Il bando Horizon riguarda la ricerca sulla trasformazione dei governi e la preparazione della pubblica amministrazione al futuro: si rivolge tipicamente a università, think tank e istituti di ricerca, non a PMI. Una piccola impresa del Cilento non ha profilo adeguato né oggetto di business compatibile con questo tipo di progetto di ricerca istituzionale.</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU è orientato a startup creative ad alto potenziale di innovazione dirompente, con requisiti tecnici e amministrativi complessi che lo rendono difficilmente accessibile per una PMI tradizionale del Cilento; inoltre, la competizione europea e la necessità di partnership internazionali scoraggiano candidature di piccole imprese locali senza esperienza progettuale europea.</t>
+          <t>Il bando Horizon europeo è orientato a startup creative ad alto potenziale di innovazione dirompente, con requisiti di scala e capacità di ricerca difficilmente compatibili con una PMI tradizionale del Cilento. Le procedure competitive europee e la necessità di partnership internazionali rendono l'accesso concreto molto complesso per realtà locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulla violenza di genere contro donne politicamente attive e persone LGBTIQ+ è destinato principalmente a enti di ricerca, università e organizzazioni della società civile, non a PMI commerciali. Una piccola impresa del Cilento non ha né il profilo né la struttura per partecipare competitivamente a progetti di ricerca europea di questo tipo.</t>
+          <t>Il bando Horizon focalizzato sulla violenza di genere contro donne politicamente attive e persone LGBTIQ+ è orientato a consorzi di ricerca, università e organizzazioni del terzo settore, con requisiti progettuali e capacità amministrative difficilmente compatibili con una PMI del Cilento. Non finanzia attività produttive o servizi tipici delle piccole imprese campane.</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda politiche di migrazione, asilo e integrazione a livello europeo, con destinatari tipici quali enti di ricerca, università e organizzazioni no-profit specializzate: una PMI del Cilento non ha i requisiti tecnici né il profilo istituzionale per accedere competitivamente a questo tipo di finanziamento. Non sono previste spese o attività riconducibili alle attività produttive o commerciali tipiche di una piccola impresa campana.</t>
+          <t>Il bando Horizon focalizzato sull'implementazione del Patto UE su Migrazione e Asilo è orientato a enti di ricerca, ONG, istituzioni pubbliche e organizzatori di politiche sociali, non a PMI produttive. Una piccola impresa del Cilento non troverebbe linee di finanziamento concrete per attività commerciali o produttive proprie.</t>
         </is>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sul contrasto al traffico illecito di beni culturali è orientato a consorzi di ricerca, università e istituzioni pubbliche, con requisiti progettuali e capacità amministrative difficilmente compatibili con una PMI standard del Cilento. Anche se il territorio cilentano è ricco di patrimonio culturale, una piccola impresa locale avrebbe estrema difficoltà ad accedere autonomamente a questo tipo di finanziamento europeo senza essere parte di un consorzio internazionale strutturato.</t>
+          <t>Il bando Horizon focalizzato sul contrasto al traffico illecito di beni culturali è orientato a consorzi di ricerca, università e grandi enti pubblici, con requisiti progettuali complessi difficilmente accessibili a una PMI del Cilento. Sebbene il territorio cilentano sia ricco di patrimonio culturale, una piccola impresa locale avrebbe difficoltà a competere senza una partnership strutturata con istituti di ricerca e capofila internazionali.</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si concentra sulla ricerca accademica sulla democrazia locale nei paesi a basso reddito, un tema lontano dalle attività produttive di una PMI campana o cilentana. Non sono previste spese finanziabili rilevanti per imprese private di piccola dimensione, né settori applicativi legati al territorio del Cilento.</t>
+          <t>Il bando Horizon riguarda la ricerca accademica sulla democrazia locale nei paesi a basso reddito, un ambito lontano dalle attività produttive tipiche di una PMI campana o cilentana. Non sono previste spese finanziabili rilevanti per imprese di piccola dimensione, né settori applicabili al contesto economico locale.</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE mira a integrare ricerca umanistica/sociale (SSH) con STEM in progetti europei ad alto contenuto scientifico, richiedendo consorzi internazionali e competenze di ricerca avanzata difficilmente accessibili a una PMI del Cilento senza un solido partenariato con università o centri di ricerca. Le PMI di piccola dimensione raramente dispongono delle risorse amministrative e progettuali necessarie per partecipare autonomamente a bandi Horizon di questa natura.</t>
+          <t>Il bando Horizon UE mira a integrare ricerca umanistica/sociale (SSH) con ricerca STEM a livello europeo, richiedendo consorzi internazionali e capacità di ricerca avanzata tipiche di università ed enti di ricerca. Una PMI del Cilento difficilmente dispone delle strutture, dei partner qualificati e delle competenze progettuali necessarie per competere in questo tipo di call, salvo un ruolo marginale come partner industriale in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione in consorzi internazionali con forte componente di ricerca accademica, rendendo l'accesso diretto quasi impossibile per una PMI del Cilento senza un partner universitario consolidato; inoltre i temi sulla competitività sostenibile e il modello sociale europeo sono orientati a progetti di ricerca su larga scala, non a interventi aziendali concreti e localizzati.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali di ricerca con elevata capacità progettuale e scientifica, rendendo l'accesso diretto da parte di una PMI del Cilento molto difficile senza un partner accademico o industriale strutturato; il focus su produttività e modello sociale europeo è inoltre troppo macro per tradursi in benefici concreti e immediati per realtà locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sul supporto alla democrazia post-conflitto e alla ricostruzione è orientato a enti di ricerca, università e organizzazioni internazionali, con tematiche geopolitiche lontane dal tessuto produttivo di una PMI del Cilento o della Campania. Non sono previste spese o attività tipicamente accessibili a imprese di piccola dimensione operanti in settori produttivi locali.</t>
+          <t>Il bando Horizon focalizzato sul supporto alla democrazia post-conflitto e alla ricostruzione è destinato prevalentemente a enti di ricerca, università e organizzazioni internazionali, con scarsa rilevanza operativa per una PMI campana o cilentana. Non finanzia attività produttive, commerciali o di servizio tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a enti di ricerca, università e organizzazioni no-profit impegnate nel contrasto alla povertà infantile e nell'accesso all'educazione della prima infanzia: una PMI campana, anche operante nel Cilento in ambito educativo o sociale, difficilmente possiede i requisiti tecnici e il profilo consortile richiesto per accedere a questo tipo di finanziamento europeo.</t>
+          <t>Il bando Horizon UE è orientato a enti di ricerca, università e organizzazioni no-profit focalizzate su povertà infantile e accesso ai servizi educativi per la prima infanzia, contesti istituzionali lontani dal profilo operativo di una PMI campana o cilentana. Una piccola impresa non dispone né della struttura progettuale né del posizionamento richiesto per candidarsi competitivamente a questo tipo di finanziamento europeo alla ricerca.</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a enti di ricerca, università e consorzi accademici per studiare l'impatto degli strumenti digitali sull'istruzione e la salute mentale: una PMI campana del Cilento difficilmente possiede i requisiti tecnico-scientifici e la struttura progettuale per candidarsi come capofila o partner rilevante. L'accesso indiretto come fornitore di servizi digitali o tecnologici è teoricamente possibile ma richiede partnership accademiche consolidate e competenze di ricerca non tipiche di una piccola impresa locale.</t>
+          <t>Si tratta di un bando di ricerca Horizon EU focalizzato su studi accademici sull'impatto degli strumenti digitali sulla salute mentale e i risultati educativi, destinato principalmente a università, enti di ricerca e consorzi scientifici. Una PMI del Cilento avrebbe difficoltà concrete di accesso senza un forte profilo R&amp;S e una partnership con istituti di ricerca accreditati.</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sulla salvaguardia della diversità linguistica è orientato a consorzi di ricerca accademica e istituti specializzati, con requisiti tecnici e amministrativi difficilmente sostenibili da una PMI campana di piccole dimensioni. Per una realtà del Cilento, l'ambito tematico risulta distante dai settori produttivi locali come turismo, agricoltura o agroalimentare, rendendo l'accesso concreto molto improbabile.</t>
+          <t>Il bando Horizon sulla salvaguardia della diversità linguistica è orientato a consorzi di ricerca, università e istituzioni accademiche europee, non a PMI operative. Una piccola impresa del Cilento non avrebbe i requisiti tecnici né la struttura per partecipare a progetti di ricerca fondamentale di questo tipo.</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla media literacy e resilienza democratica è orientato a consorzi di ricerca, università e grandi organizzazioni del terzo settore, con processi competitivi complessi e budget elevati difficilmente gestibili da una PMI del Cilento in autonomia. Una piccola impresa campana non avrebbe né le competenze progettuali né il profilo istituzionale richiesto per guidare o partecipare efficacemente a questi progetti.</t>
+          <t>Il bando Horizon Europe sulla media literacy e resilienza democratica è orientato a consorzi di ricerca accademici e organizzazioni della società civile su scala europea, richiedendo capacità progettuali e di rendicontazione molto avanzate. Una PMI del Cilento difficilmente può guidare o partecipare come partner principale, potendo al massimo aspirare a un ruolo marginale in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU sull'integrità elettorale in ambito digitale è orientato a enti di ricerca, università e grandi consorzi transnazionali, con requisiti tecnici e amministrativi difficilmente soddisfabili da una PMI del Cilento. Non finanzia attività produttive, commerciali o di sviluppo locale tipiche delle piccole imprese campane.</t>
+          <t>Il bando Horizon focalizzato sull'integrità elettorale in contesti digitali è orientato a enti di ricerca, università e organizzazioni specializzate in scienze politiche e cybersecurity, richiedendo competenze altamente specifiche e capacità di partecipazione a consorzi internazionali. Una PMI del Cilento, anche tecnologica, difficilmente possiede i requisiti tecnico-scientifici e la struttura progettuale necessaria per competere in questo ambito.</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe è orientato a consorzi di ricerca istituzionali e università, con requisiti amministrativi e di cofinanziamento difficilmente sostenibili da una PMI del Cilento senza un partner capofila accademico strutturato. L'accesso è teoricamente possibile come partner secondario, ma la complessità progettuale e i tempi lunghi lo rendono poco pratico per realtà di piccola dimensione.</t>
+          <t>Il bando Horizon focalizzato su ricerca e uguaglianza richiede consorzi internazionali con capacità di ricerca strutturata, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un partner universitario o un centro di ricerca. Le spese finanziabili riguardano attività R&amp;I complesse, lontane dalle esigenze operative tipiche di una piccola impresa locale.</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sull'integrazione dell'AI nei servizi di comunicazione e supporto ai clienti (CCSI) è orientato a consorzi di ricerca e grandi organizzazioni con forte capacità progettuale europea, rendendo l'accesso diretto da parte di una PMI del Cilento estremamente complesso senza un partenariato strutturato. Una piccola impresa locale potrebbe partecipare solo come partner junior in un consorzio internazionale, con oneri amministrativi e gestionali sproporzionati rispetto alle risorse tipicamente disponibili.</t>
+          <t>Il bando Horizon UE sull'integrazione dell'AI nei processi CCSI (Customer Care e Servizi Innovativi) richiede tipicamente partnership internazionali, capacità di rendicontazione complessa e profili di ricerca avanzati difficilmente sostenibili da una PMI del Cilento senza un consorzio strutturato. Una piccola impresa campana difficilmente accede direttamente come capofila, potendo al massimo partecipare come partner in un consorzio guidato da università o grandi aziende tech.</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede consorzi di ricerca internazionali con capacità tecnico-scientifiche avanzate sul tema dell'IA generativa applicata ai contenuti culturali e creativi, struttura progettuale complessa difficilmente gestibile da una PMI del Cilento senza partner accademici qualificati. Le risorse finanziabili riguardano ricerca e sviluppo tecnologico su scala europea, non attività operative tipiche di una piccola impresa locale.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, partnership internazionali e progettualità complessa, strutturalmente difficili da gestire per una PMI del Cilento senza un consorzio o un ente di ricerca capofila. Il focus su AI generativa e mercati dei contenuti creativi è distante dalle filiere produttive locali (turismo, agricoltura, artigianato).</t>
         </is>
       </c>
     </row>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede consorzi internazionali di ricerca con capacità progettuali elevate, rendendo l'accesso diretto quasi impossibile per una PMI del Cilento senza un partner universitario o un centro di ricerca capofila. L'obiettivo di integrare le arti per lo sviluppo di soft skills e innovazione è interessante ma troppo distante dal core business tipico delle PMI locali (turismo, agroalimentare, artigianato).</t>
+          <t>Il bando Horizon è orientato a consorzi di ricerca e grandi organizzazioni con capacità di progettazione europea, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un partner capofila accademico o istituzionale. Il focus sull'uso delle arti per sviluppare soft skills e innovazione ha scarsa applicabilità concreta per le tipiche PMI manifatturiere, turistiche o agricole del territorio cilentano.</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sull'educazione civica nell'apprendimento permanente è orientato principalmente a università, enti di ricerca e organizzazioni no-profit, con requisiti consortili complessi e procedure competitive che rendono l'accesso diretto per una PMI del Cilento molto difficile senza un ruolo marginale come partner. Non finanzia attività produttive o di sviluppo aziendale tipiche di una PMI manifatturiera o di servizi.</t>
+          <t>Il bando Horizon focalizzato sull'educazione alla cittadinanza nel lifelong learning è orientato principalmente a consorzi di ricerca, università e grandi organizzazioni educative europee, richiedendo partnership transnazionali complesse e capacità progettuali difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio, ma difficilmente come capofila, rendendo l'accesso diretto ai fondi marginale.</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Fostering competences for the green transition' è orientato a consorzi di ricerca, università e grandi organizzazioni europee, con requisiti di partenariato transnazionale complessi e budget elevati difficilmente accessibili a una PMI del Cilento in autonomia. Una piccola impresa potrebbe partecipare solo come partner junior in un consorzio guidato da enti di ricerca, ruolo che richiede connessioni istituzionali e capacità progettuali avanzate raramente disponibili a livello locale.</t>
+          <t>Il bando Horizon europeo è orientato a grandi consorzi di ricerca e università per sviluppare metodologie sistemiche sulla transizione verde, con requisiti progettuali e amministrativi difficilmente sostenibili da una PMI del Cilento senza un partner capofila accademico. Le PMI possono partecipare solo come partner secondari in consorzio, rendendo l'accesso diretto molto complesso.</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si rivolge principalmente a università, enti di ricerca e organismi istituzionali per progettare politiche europee di attrazione di talenti internazionali: una PMI del Cilento non ha né la struttura né il profilo richiesto per candidarsi come soggetto capofila o partner rilevante. L'ambito è troppo macro-politico e accademico per generare un beneficio diretto o un'opportunità concreta di finanziamento per una piccola impresa locale.</t>
+          <t>Il bando Horizon è orientato a enti di ricerca, università e istituzioni pubbliche impegnate nell'attrazione di talenti internazionali su scala europea: una PMI del Cilento difficilmente possiede i requisiti strutturali e la capacità progettuale per partecipare direttamente. Le attività finanziabili riguardano policy, mobilità e sistemi di accoglienza per ricercatori e lavoratori altamente qualificati extra-UE, ambiti lontani dalla operatività tipica di una piccola impresa locale.</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe è orientato a progetti di ricerca accademica e su larga scala sul contributo delle competenze di base alla produttività, richiedendo consorzi internazionali e capacità di ricerca avanzata difficilmente accessibili a una PMI del Cilento. Una piccola impresa campana non dispone tipicamente delle strutture progettuali e dei partner richiesti per competere su questo tipo di call europea.</t>
+          <t>Il bando Horizon focalizzato sulle competenze di base e la produttività è orientato principalmente a enti di ricerca, università e consorzi transnazionali, rendendo difficile l'accesso diretto per una PMI del Cilento senza un partner accademico strutturato. Le PMI potrebbero partecipare solo come partner secondari in progetti di ricerca applicata sulla formazione dei lavoratori, ma la complessità gestionale e i requisiti di rendicontazione Horizon scoraggiano candidature autonome di piccole imprese.</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo 'Sustainable paths to media viability' è orientato a enti di ricerca, università e organizzazioni media di scala europea, rendendo di fatto inaccessibile la partecipazione diretta a una PMI del Cilento non operante nel settore media o della ricerca accademica. Le PMI locali potrebbero al massimo partecipare come partner secondari in consorzi internazionali, scenario poco praticabile per realtà di piccola dimensione senza precedenti esperienze Horizon.</t>
+          <t>Il bando Horizon 'Sustainable paths to media viability' è orientato a organizzazioni di ricerca e media company di scala europea, con requisiti di consorzio transnazionale difficilmente gestibili per una PMI del Cilento. Il settore media/informazione è marginale nell'economia locale e i costi di partecipazione a progetti Horizon sono sproporzionati rispetto alle capacità amministrative di una piccola impresa campana.</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe per il Digital Twin Ocean richiede capacità di ricerca avanzata, consori internazionali e competenze tecnologiche specialistiche difficilmente accessibili a una PMI campana di piccole dimensioni; il Cilento potrebbe teoricamente beneficiare di ricadute legate al monitoraggio marino e costiero, ma la partecipazione diretta come capofila o partner è praticamente inaccessibile senza un solido profilo R&amp;D e partnership con enti di ricerca qualificati.</t>
+          <t>Il bando Horizon riguarda lo sviluppo di un Digital Twin dell'Oceano a scala regionale per bacini marini europei, destinato principalmente a grandi consorzi di ricerca, università e enti pubblici con elevate competenze in oceanografia e modellistica digitale. Una PMI del Cilento potrebbe partecipare solo come partner marginale in un consorzio, senza possibilità concreta di essere capofila o beneficiaria principale.</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi internazionali di ricerca con capacità tecnico-scientifiche elevate e budget multimilionari, strutturalmente incompatibili con una PMI campana di piccole dimensioni che non abbia già partnership consolidate con università o enti di ricerca. Una PMI del Cilento potrebbe al massimo partecipare come soggetto associato in un consorzio guidato da istituti di ricerca, ma difficilmente come capofila o beneficiario principale.</t>
+          <t>Il bando Horizon EU richiede consorzi internazionali di ricerca con capacità scientifiche elevate, budget multimilionari e competenze specialistiche in ecologia acquatica difficilmente reperibili in una PMI campana. Una piccola impresa del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio guidato da università o enti di ricerca, ma difficilmente come soggetto capofila.</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata per la mappatura degli habitat marini su larga scala, con consorzio internazionale e competenze tecniche specialistiche difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario se operante nel settore marino o ambientale, ma difficilmente come soggetto capofila.</t>
+          <t>Il bando Horizon richiede capacità di coordinamento di progetti di ricerca su larga scala per la mappatura degli habitat marini, strutture che difficilmente una PMI campana possiede autonomamente; il Cilento, pur avendo coste e un Parco Nazionale con aree marine protette, non compensa la complessità tecnica e burocratica di questo tipo di call europee, più adatte a consorzi universitari o enti di ricerca.</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la costituzione di reti europee per testing di tecnologie oceaniche, con complessità progettuale e requisiti consortili tipici di grandi enti di ricerca o cluster industriali specializzati. Una PMI campana, anche del Cilento con accesso al mare, difficilmente possiede le capacità tecniche e amministrative per candidarsi autonomamente o come partner rilevante in questo tipo di progetto.</t>
+          <t>Il bando Horizon richiede la costruzione di una rete europea di siti di test per tecnologie oceaniche, con requisiti tecnici, consortili e finanziari difficilmente accessibili per una PMI campana di piccole dimensioni. Pur essendo il Cilento affacciato sul mare, si tratta di un progetto ad alta complessità scientifica e istituzionale, pensato per enti di ricerca, grandi imprese o cluster tecnologici marini.</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede la partecipazione in consorzi internazionali con forti competenze di ricerca su gestione del rischio climatico e adattamento, strutture tipiche di università o grandi enti di ricerca, rendendo l'accesso diretto a una PMI del Cilento estremamente complesso senza un partner accademico consolidato. Una piccola impresa potrebbe al massimo partecipare come partner tecnico in un consorzio già formato, ma difficilmente come soggetto capofila o beneficiario principale.</t>
+          <t>Il bando Horizon richiede consorzi internazionali di ricerca con elevata capacità progettuale e budget multimilionari, strutturalmente incompatibili con una PMI di piccola dimensione del Cilento. Sebbene il territorio sia esposto a rischi idrogeologici e climatici rilevanti, una PMI locale potrebbe al massimo partecipare come partner junior in un consorzio guidato da università o enti di ricerca, ruolo difficile da costruire senza reti europee consolidate.</t>
         </is>
       </c>
     </row>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a enti di ricerca, istituzioni finanziarie e autorità pubbliche per sviluppare strumenti di finanza mista per l'adattamento climatico, non è accessibile direttamente a una PMI del Cilento. Una piccola impresa non possiede i requisiti tecnici e il profilo istituzionale richiesti per partecipare come beneficiario principale.</t>
+          <t>Il bando Horizon si rivolge principalmente a enti di ricerca, istituzioni finanziarie e autorità pubbliche per sviluppare strumenti finanziari misti (pubblico-privato) per l'adattamento climatico locale, non a PMI come beneficiarie dirette. Una piccola impresa del Cilento difficilmente possiede i requisiti tecnici e consortili richiesti da Horizon per partecipare come soggetto capofila o partner qualificato.</t>
         </is>
       </c>
     </row>
@@ -10527,12 +10527,12 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a consorzi di ricerca, enti pubblici e grandi organizzazioni per sviluppare soluzioni sistemiche di adattamento climatico a scala regionale e locale, con requisiti di partnership transnazionale complessi e difficilmente accessibili a una PMI autonoma. Una piccola impresa del Cilento potrebbe partecipare solo come partner secondario in un consorzio già strutturato, ruolo che richiede connessioni istituzionali e capacità progettuali europee non comuni nelle PMI locali.</t>
+          <t>Il bando Horizon EU è orientato a consorzi di ricerca e autorità locali per lo sviluppo di soluzioni sistemiche all'adattamento climatico, con requisiti di partnership transnazionale e capacità progettuali elevate difficilmente accessibili a una PMI autonomamente. Una piccola impresa del Cilento potrebbe partecipare solo come partner secondario in un consorzio guidato da enti di ricerca o pubbliche amministrazioni, ruolo raramente remunerativo e di difficile costruzione senza reti consolidate.</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE si concentra sulla resilienza climatica delle vie navigabili interne e delle infrastrutture idriche correlate, un settore con scarsa rilevanza per il Cilento e per le PMI campane in generale, che non operano tipicamente in contesti di navigazione fluviale. Inoltre, i bandi Horizon richiedono consorzi internazionali e capacità di ricerca avanzata difficilmente accessibili a una piccola o media impresa senza un partner universitario o un grande ente capofila.</t>
+          <t>Il bando Horizon europeo riguarda la resilienza climatica di vie navigabili interne e infrastrutture idriche correlate, un ambito molto distante dalla realtà produttiva del Cilento e delle PMI campane tipiche. Richiede inoltre capacità di ricerca avanzata, consorzio internazionale e risorse progettuali difficilmente accessibili per una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi di ricerca europei con competenze scientifiche avanzate nella climatologia e nei servizi climatici, strutture difficilmente alla portata di una PMI del Cilento. I costi di partecipazione, la complessità progettuale e la necessità di partner accademici o istituzionali rendono questo bando sostanzialmente inaccessibile senza un ruolo marginale all'interno di un consorzio già formato.</t>
+          <t>Il bando Horizon richiede la partecipazione in consorzi internazionali con capacità di ricerca avanzata sui servizi climatici, strutture difficilmente accessibili per una PMI del Cilento senza un solido track record europeo. Le attività finanziate riguardano sviluppo e standardizzazione di strumenti scientifici per l'adattamento climatico, ambito troppo specialistico per la maggior parte delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon mira a costruire hub nazionali di governance multilivello per l'adattamento climatico, coinvolgendo principalmente enti pubblici, autorità regionali e centri di ricerca: una PMI del Cilento difficilmente può candidarsi come soggetto capofila o anche come partner, data la natura istituzionale e la complessità consorziale richiesta. Non sono previsti finanziamenti diretti per attività produttive o investimenti aziendali tipici delle PMI.</t>
+          <t>Il bando Horizon finanzia enti pubblici, centri di ricerca e istituzioni per costruire hub nazionali di governance multilivello sull'adattamento climatico: non è uno strumento diretto per PMI, che non possono candidarsi autonomamente né accedere a finanziamenti diretti per attività produttive o commerciali. Una PMI del Cilento non troverebbe canali concreti di accesso a fondi o commesse attraverso questo specifico bando.</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede la costituzione di consorzi internazionali con capacità di ricerca avanzata e rendicontazione europea, strutture difficilmente gestibili da una PMI agricola del Cilento senza il supporto di un ente capofila. Pur essendo tematicamente rilevante per aziende agricole locali che affrontano siccità e alluvioni, la complessità amministrativa e le soglie di partecipazione rendono l'accesso diretto praticamente inaccessibile senza partnership con università o centri di ricerca.</t>
+          <t>Il bando Horizon UE richiede la formazione di consorzi internazionali e capacità di ricerca avanzata difficilmente accessibili a una PMI autonoma; tuttavia, un'azienda agricola del Cilento attiva nella gestione del suolo o nella produzione alimentare potrebbe partecipare come partner operativo in un progetto guidato da un ente di ricerca, contribuendo alla dimostrazione di pratiche di resilienza del suolo agli eventi climatici estremi.</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>Il programma CERV Town Twinning finanzia gemellaggi tra comuni europei e attività di cittadinanza attiva, con beneficiari tipici enti locali e associazioni no-profit: una PMI del Cilento non rientra tra i soggetti ammissibili e non può candidarsi direttamente. L'unica opportunità indiretta sarebbe partecipare come partner operativo in un progetto guidato da un Comune, ma senza accesso diretto ai fondi.</t>
+          <t>Il programma CERV Town Twinning finanzia gemellaggi tra comuni e attività di cittadinanza europea rivolte a enti locali e associazioni civiche, non a imprese private: una PMI del Cilento non è beneficiaria eleggibile e non può accedere direttamente ai fondi. L'unica utilità indiretta sarebbe partecipare come partner operativo di un comune cilentano in un progetto di scambio, ma senza possibilità di rendicontare costi aziendali tipici.</t>
         </is>
       </c>
     </row>
@@ -10814,14 +10814,14 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto a intermediari della finanza sociale (fondi, istituzioni finanziarie) per coprire i costi di transazione nella strutturazione di strumenti di finanza sociale, non alle PMI direttamente. Una piccola impresa del Cilento non può accedere come beneficiaria diretta, essendo il target istituti finanziari specializzati.</t>
+          <t>Il bando è rivolto a intermediari della finanza sociale (fondi, istituzioni finanziarie) per coprire i costi di transazione legati a strumenti di finanza sociale, non alle PMI come beneficiarie dirette. Una piccola impresa del Cilento non può accedere direttamente a questo finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="221" ht="30" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Teaming Synergies</t>
+          <t>Hop-On Facility</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-01-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-03-WIDENING-01</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -10861,14 +10861,14 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>Teaming Synergies è uno strumento Horizon Europe pensato per costruire o rafforzare centri di eccellenza in ricerca e innovazione, richiedendo partnership con istituzioni accademiche di alto livello e investimenti istituzionali regionali di scala molto elevata. Una PMI del Cilento difficilmente può accedere direttamente a questo bando, che è strutturalmente orientato a consorzi tra università, centri di ricerca e autorità pubbliche, non a imprese di piccola dimensione.</t>
+          <t>Il bando Hop-On Facility di Horizon Europe è destinato a consentire a enti di paesi terzi o paesi meno rappresentati di agganciarsi a progetti già finanziati da Horizon, richiedendo strutture di ricerca e capacità progettuali complesse, lontane dalla operatività tipica di una PMI cilentana di piccola dimensione. L'accesso risulta estremamente difficoltoso senza un consorzio europeo preesistente e competenze specifiche nella ricerca e sviluppo a livello internazionale.</t>
         </is>
       </c>
     </row>
     <row r="222" ht="30" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Research Management Facility</t>
+          <t>Teaming Synergies</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-04-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-01-WIDENING-01</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -10903,19 +10903,19 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>Il bando Research Management Facility è orientato a strutture di gestione della ricerca istituzionale (università, enti pubblici, grandi organizzazioni R&amp;I) e non a PMI operative sul territorio come quelle del Cilento. L'accesso diretto per una piccola impresa campana è estremamente improbabile, mancando i requisiti strutturali e la capacità amministrativa richiesta da Horizon Europe per questo tipo di facility.</t>
+          <t>Teaming Synergies è uno strumento Horizon Europe pensato per costruire centri di eccellenza in ricerca e innovazione in regioni meno sviluppate, richiedendo partnership istituzionali tra università, centri di ricerca e autorità pubbliche: una PMI del Cilento difficilmente può accedere direttamente senza essere parte di un consorzio guidato da un ente di ricerca. I costi ammissibili riguardano infrastrutture scientifiche e capacity building istituzionale, non le esigenze operative tipiche di una piccola impresa.</t>
         </is>
       </c>
     </row>
     <row r="223" ht="30" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Call for proposals on the fight against corruption.</t>
+          <t>Research Management Facility</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -10925,17 +10925,17 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-CORRUPT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-04-WIDENING-01</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>UE - ISF</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
@@ -10955,34 +10955,34 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sulla lotta alla corruzione è destinato principalmente a enti pubblici, forze dell'ordine e organizzazioni specializzate nella sicurezza interna, rendendo di fatto inaccessibile la partecipazione diretta a una PMI del Cilento. Non sono previsti finanziamenti per spese tipiche delle imprese private come investimenti produttivi, formazione aziendale ordinaria o innovazione di prodotto.</t>
+          <t>Il bando Research Management Facility di Horizon UE è orientato a strutture di ricerca e grandi organizzazioni con capacità amministrativa complessa, richiedendo competenze specialistiche in gestione della ricerca difficilmente disponibili in una PMI del Cilento. Le spese finanziabili riguardano attività di coordinamento e supporto alla ricerca istituzionale, non attività produttive o commerciali tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="224" ht="30" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Non-thematic development actions by SMEs</t>
+          <t>Call for proposals on the fight against corruption.</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DA-SME-NT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-CORRUPT</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>UE - EDF</t>
+          <t>UE - ISF</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -11002,14 +11002,14 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa europea, richiedendo consorzi internazionali e competenze tecnologiche militari altamente specializzate, del tutto estranee al tessuto produttivo tipico delle PMI del Cilento, orientato verso turismo, agricoltura e agroalimentare. L'accesso è di fatto precluso a piccole imprese locali prive di certificazioni NATO o contratti con industrie della difesa.</t>
+          <t>Il bando ISF (Internal Security Fund) sulla lotta alla corruzione è destinato principalmente a enti pubblici, forze dell'ordine e organizzazioni specializzate nel settore della sicurezza e antifrode, non a PMI commerciali. Una piccola impresa del Cilento non rientra nei beneficiari tipici e non troverebbe spese finanziabili legate alla propria attività produttiva o commerciale.</t>
         </is>
       </c>
     </row>
     <row r="225" ht="30" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>New abilities in over-the-horizon sensing</t>
+          <t>Non-thematic development actions by SMEs</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DA-DIS-OTHR</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DA-SME-NT</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -11049,14 +11049,14 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo tecnologico nel settore della difesa, specificamente su sistemi di rilevamento oltre l'orizzonte, un ambito altamente specializzato che richiede capacità tecnologiche avanzate, certificazioni militari e partnership con grandi contractor della difesa. Una PMI del Cilento o della Campania senza expertise consolidata nel settore difesa/aerospazio difficilmente può accedere in modo competitivo a questo tipo di finanziamento.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia attività di ricerca e sviluppo nel settore della difesa europea, richiedendo capacità tecnologiche avanzate e spesso la partecipazione in consorzi multinazionali: contesto difficilmente accessibile per una PMI del Cilento senza specializzazione nel comparto difesa. Le spese finanziabili riguardano R&amp;S militare/dual-use, lontane dalle filiere produttive tipiche del territorio cilentano.</t>
         </is>
       </c>
     </row>
     <row r="226" ht="30" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>AI-based tactical situational awareness using swarms of small robots and drones – organisation of a  technological challenge"</t>
+          <t>New abilities in over-the-horizon sensing</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-CHALLENGE-DIGIT-AISAO</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DA-DIS-OTHR</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -11091,19 +11091,19 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di tecnologie di difesa avanzate basate su sciami di robot e droni con AI per la sorveglianza tattica, richiedendo competenze altamente specializzate nel settore della difesa e capacità di partecipazione a consorzi internazionali complessi. Per una PMI del Cilento, l'accesso è estremamente difficile per gli elevati requisiti tecnici, la natura militare del progetto e la necessità di certificazioni e partnership nel settore difesa difficilmente disponibili nel tessuto produttivo locale.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa su tecnologie avanzate di rilevamento oltre l'orizzonte, richiedendo capacità tecnologiche militari, consorzi internazionali strutturati e competenze altamente specializzate del tutto estranee al tessuto produttivo tipico del Cilento e delle PMI campane. Una piccola o media impresa locale non possiede i requisiti tecnici né le certificazioni necessarie per partecipare competitivamente a questo tipo di bando.</t>
         </is>
       </c>
     </row>
     <row r="227" ht="30" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>AI-based tactical situational awareness using swarms of small robots and drones – participation in a  technological challenge"</t>
+          <t>AI-based tactical situational awareness using swarms of small robots and drones – organisation of a  technological challenge"</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-CHALLENGE-DIGIT-AISAP-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-CHALLENGE-DIGIT-AISAO</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -11143,14 +11143,14 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo su sistemi di intelligenza artificiale per la difesa con sciami di droni e robot, richiedendo competenze tecnologiche altamente specializzate nel settore difesa/dual-use e capacità di partecipare a consorzi europei complessi: requisiti difficilmente raggiungibili per una PMI del Cilento priva di un solido profilo R&amp;D in ambito militare. Le PMI campane potrebbero accedere solo come partner junior in consorzi guidati da grandi aziende della difesa, con margini di coinvolgimento molto limitati.</t>
+          <t>Il bando EDF finanzia sfide tecnologiche nel settore difesa/sicurezza legate a sciami di robot e droni per la sorveglianza tattica: richiede capacità R&amp;S avanzate, consorzialità europea e competenze aerospazio-militari che difficilmente una PMI del Cilento possiede. I requisiti tecnici e burocratici lo rendono praticamente inaccessibile senza partnership con grandi player del settore difesa.</t>
         </is>
       </c>
     </row>
     <row r="228" ht="30" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CBRN decontamination systems and technologies</t>
+          <t>AI-based tactical situational awareness using swarms of small robots and drones – participation in a  technological challenge"</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>11/02/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-MCBRN-DST</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-CHALLENGE-DIGIT-AISAP-STEP</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -11185,19 +11185,19 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per sistemi di decontaminazione CBRN (Chimico, Biologico, Radiologico, Nucleare) è orientato a grandi consorzi industriali della difesa con capacità R&amp;D avanzate, richiedendo competenze tecnologiche altamente specializzate e partnership internazionali difficilmente accessibili a una PMI del Cilento. I requisiti tecnici, finanziari e la natura militare del programma rendono la partecipazione diretta di una piccola impresa campana sostanzialmente impraticabile.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo avanzato su sciami di robot e droni per la difesa tattica, richiedendo capacità tecnologiche militari di alto livello, consorziate con grandi player della difesa europea: una PMI del Cilento difficilmente possiede le competenze specialistiche e la struttura necessarie per partecipare competitivamente. Il settore difesa/aerospazio è quasi assente nel tessuto produttivo campano del Cilento, rendendo l'accesso concreto a questo bando estremamente improbabile senza un ruolo marginale in un grande consorzio guidato da prime contractor della difesa.</t>
         </is>
       </c>
     </row>
     <row r="229" ht="30" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Future multirole light aircraft</t>
+          <t>CBRN decontamination systems and technologies</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-PROTMOB-FMLA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-MCBRN-DST</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -11237,14 +11237,14 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per aeromobili leggeri multiruolo è destinato a consorzi industriali del settore difesa e aerospazio con capacità tecnologiche avanzate, richiedendo investimenti e competenze fuori dalla portata di una PMI del Cilento. Non vi è alcuna coerenza con il tessuto produttivo locale, orientato verso turismo, agricoltura e artigianato.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa CBRN (chimico, biologico, radiologico, nucleare), richiedendo capacità tecnologiche avanzate, consorzi multinazionali e requisiti di sicurezza NATO/UE difficilmente accessibili a una PMI del Cilento. Le spese finanziabili riguardano R&amp;S per sistemi di decontaminazione militare, un settore lontano dal tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="230" ht="30" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Modelling &amp; simulation supported AI framework for military decision-making and training</t>
+          <t>Future multirole light aircraft</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SIMTRAIN-MSAI</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-PROTMOB-FMLA</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -11284,14 +11284,14 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia progetti di ricerca e sviluppo nel settore della difesa militare (AI, simulazione, decision-making), richiedendo consorzi internazionali complessi e competenze altamente specializzate difficilmente presenti in una PMI del Cilento. I requisiti tecnici e amministrativi per accedere ai fondi EDF sono proibitivi per realtà di piccola-media dimensione senza un solido track record nel settore difesa.</t>
+          <t>Il bando EDF per aeromobili militari multiruolo leggeri è destinato a consorzi industriali del settore difesa e aerospaziale con capacità R&amp;S avanzate, requisiti tecnici e finanziari del tutto fuori portata per una PMI del Cilento. Non esistono filiere aeronautico-difensive rilevanti nel territorio che possano giustificare una partecipazione anche in qualità di subappaltatore.</t>
         </is>
       </c>
     </row>
     <row r="231" ht="30" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Multidomain sensors demonstrator and test</t>
+          <t>Modelling &amp; simulation supported AI framework for military decision-making and training</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SENS-MSDT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SIMTRAIN-MSAI</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -11326,19 +11326,19 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia lo sviluppo di dimostratori di sensori multi-dominio per applicazioni difensive, richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze nel settore della difesa che difficilmente una PMI del Cilento possiede. I requisiti tecnici e burocratici sono orientati a grandi aziende della difesa o centri di ricerca specializzati, rendendo l'accesso praticamente inaccessibile per realtà produttive locali di piccola dimensione.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa militare su modellazione, simulazione e AI per il decision-making, richiedendo consorzi europei con competenze altamente specializzate e strutture di R&amp;D avanzate, del tutto fuori portata per una PMI tipica del Cilento. I requisiti tecnici, burocratici e le soglie di investimento tipiche dell'EDF rendono questo bando inaccessibile senza partnership con grandi player della difesa o centri di ricerca qualificati.</t>
         </is>
       </c>
     </row>
     <row r="232" ht="30" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Quantum secured tactical networks</t>
+          <t>Multidomain sensors demonstrator and test</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-CYBER-QSTN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SENS-MSDT</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -11378,14 +11378,14 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sulle reti tattiche quantum-secured è destinato a consorzi industriali con elevate capacità di ricerca in tecnologie quantistiche e difesa, requisiti che esulano dalla portata di una PMI del Cilento. I costi di partecipazione, la complessità tecnica e il contesto militare rendono questo bando di fatto inaccessibile per realtà produttive locali di piccola o media dimensione.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia lo sviluppo di dimostratori di sensori multi-dominio per applicazioni difensive, richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze nel settore della difesa che una PMI del Cilento difficilmente possiede. L'accesso è praticamente precluso senza partnership con grandi contractor della difesa o centri di ricerca specializzati.</t>
         </is>
       </c>
     </row>
     <row r="233" ht="30" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Autonomous and automatic air-to-air refuelling</t>
+          <t>Quantum secured tactical networks</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-AIR-A4R</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-CYBER-QSTN</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -11420,19 +11420,19 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di tecnologie avanzate per il rifornimento autonomo aria-aria in ambito difesa, richiedendo capacità aerospaziali, competenze ingegneristiche altamente specializzate e strutture di R&amp;S difficilmente compatibili con una PMI del Cilento o della Campania in generale. L'accesso è di fatto riservato a grandi contractor della difesa o a consorzi guidati da industrie aeronautiche con esperienza certificata nel settore militare.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa su reti tattiche con crittografia quantistica, richiedendo capacità tecnologiche altamente specializzate e consorzi internazionali complessi, barriere di accesso quasi insormontabili per una PMI del Cilento priva di competenze specifiche in tecnologie quantistiche e contrattualistica con la difesa.</t>
         </is>
       </c>
     </row>
     <row r="234" ht="30" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Development and validation of models predicting flow-related underwater noise</t>
+          <t>Autonomous and automatic air-to-air refuelling</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-UWW-FUWN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-AIR-A4R</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -11467,19 +11467,19 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF richiede capacità di ricerca e sviluppo avanzata in acustica subacquea e modellistica idrodinamica, tipicamente appannaggio di grandi contractor della difesa o centri di ricerca specializzati. Una PMI campana, anche del Cilento con vocazione marittima, difficilmente possiede le competenze tecniche certificate e la struttura necessaria per partecipare autonomamente a bandi della Difesa Europea di questo profilo.</t>
+          <t>Il bando EDF riguarda lo sviluppo di tecnologie avanzate per il rifornimento aereo autonomo in volo, un settore altamente specializzato della difesa che richiede competenze aerospaziali e capacità industriali difficilmente replicabili da una PMI campana, specialmente nel contesto del Cilento. I requisiti tecnici, i consorzio multinazionali e i capitali necessari rendono questo bando di fatto inaccessibile per imprese di piccola e media dimensione senza una solida base nel comparto aerospazio-difesa.</t>
         </is>
       </c>
     </row>
     <row r="235" ht="30" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Layered critical seabed infrastructure protection</t>
+          <t>Development and validation of models predicting flow-related underwater noise</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SI-UWW-CSBI-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-UWW-FUWN</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -11514,19 +11514,19 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sulla protezione delle infrastrutture sottomarine critiche è destinato a consorzi industriali della difesa e centri di ricerca specializzati in tecnologie militari/navali, con requisiti tecnici e finanziari del tutto incompatibili con una PMI del Cilento o della Campania. Non esistono linee di spesa né settori beneficiari applicabili a realtà produttive locali di piccola-media dimensione.</t>
+          <t>Il bando EDF finanzia ricerca militare/difesa avanzata sulla modellazione del rumore subacqueo generato dal flusso idrodinamico, richiedendo competenze ingegneristiche navali e capacità R&amp;D altamente specializzate tipiche di grandi contractor della difesa o centri di ricerca. Una PMI del Cilento, anche con vocazione marittima o turistica, non possiede i requisiti tecnici e il profilo industriale necessari per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>New turbofan engine</t>
+          <t>Layered critical seabed infrastructure protection</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-SI-ENERENV-NTFE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-RA-SI-UWW-CSBI-STEP</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -11561,19 +11561,19 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per lo sviluppo di nuovi motori turbofan è destinato a grandi consorzi aerospaziali e difesa con capacità tecnologiche avanzate: una PMI del Cilento o della Campania difficilmente possiede le competenze ingegneristiche e le certificazioni di settore richieste per partecipare. L'accesso sarebbe possibile solo come partner secondario di un consorzio guidato da un grande player aerospaziale, scenario improbabile per una piccola impresa locale.</t>
+          <t>Il bando EDF per la protezione delle infrastrutture sottomarine critiche è destinato a consorzi di difesa e grandi aziende del settore aerospaziale/navale, con requisiti tecnologici e finanziari del tutto inaccessibili per una PMI campana del Cilento. Non sono previste spese finanziabili né settori di attività compatibili con il tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="237" ht="30" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>High-end endo-atmospheric interception</t>
+          <t>New turbofan engine</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ACC-AIRDEF-EATMI</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-RA-SI-ENERENV-NTFE</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -11613,14 +11613,14 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di sistemi avanzati di intercettazione endo-atmosferica ad alta quota, un settore della difesa missilistica che richiede capacità industriali, tecnologiche e certificazioni del tutto inaccessibili a una PMI del Cilento o della Campania in generale. I requisiti tecnici e i partner necessari (prime contractor della difesa) escludono di fatto qualsiasi piccola o media impresa non già inserita in filiere aerospaziali/difesa consolidate.</t>
+          <t>Il bando EDF per lo sviluppo di nuovi motori turbofan è destinato a consorzi industriali del settore difesa/aerospaziale con elevate capacità tecnologiche e finanziarie, requisiti difficilmente compatibili con una PMI del Cilento. Le spese finanziabili riguardano R&amp;S avanzata su propulsione militare, ambito lontano dal tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="238" ht="30" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Smart and multifunctional textiles</t>
+          <t>High-end endo-atmospheric interception</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-MATCOMP-SMT-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ACC-AIRDEF-EATMI</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -11655,19 +11655,19 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (Fondo Europeo per la Difesa) finanzia ricerca e sviluppo nel settore dei tessili intelligenti e multifunzionali per applicazioni militari/difesa, richiedendo consorzi transnazionali con capacità tecnologiche avanzate e budget di progetto nell'ordine dei milioni di euro, strutturalmente incompatibili con una PMI del Cilento priva di specializzazione nel settore difesa. L'accesso è realisticamente riservato a grandi imprese del comparto aerospazio-difesa o centri di ricerca con track record specifico.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa missilistica ad alta quota, richiedendo capacità tecnologiche, certificazioni e strutture industriali tipiche di grandi contractor della difesa. Una PMI del Cilento non dispone delle competenze aerospaziali/militari né dei requisiti consorziali necessari per partecipare a questo tipo di programma europeo.</t>
         </is>
       </c>
     </row>
     <row r="239" ht="30" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Integration of Galileo PRS receivers on weapon systems and NAVWAR operational centres in military C2</t>
+          <t>Smart and multifunctional textiles</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-SPACE-PRS-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-MATCOMP-SMT-STEP</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -11702,19 +11702,19 @@
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di ricevitori Galileo PRS per sistemi d'arma e centri C2 militari, un settore altamente specializzato della difesa che richiede certificazioni di sicurezza NATO/UE, capacità industriali avanzate e accesso a tecnologie classificate, del tutto inaccessibili per una PMI del Cilento o della Campania priva di esperienza nel comparto difesa aerospaziale.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa, richiedendo consorzi multinazionali con capacità industriali avanzate nel campo dei tessuti intelligenti per applicazioni militari: una PMI del Cilento difficilmente possiede le certificazioni, i partner internazionali e le competenze tecnologiche specifiche richieste per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="240" ht="30" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Ammunition Waste Collection and Disposal Unmanned Platform</t>
+          <t>Integration of Galileo PRS receivers on weapon systems and NAVWAR operational centres in military C2</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ENERENV-AWC-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-SPACE-PRS-STEP</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -11754,14 +11754,14 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di piattaforme robotiche/droni per la raccolta e smaltimento di residui bellici, richiedendo competenze altamente specializzate in difesa, robotica avanzata e ingegneria militare difficilmente presenti in una PMI del Cilento. I requisiti tecnici e i partenariati europei richiesti rendono questo bando sostanzialmente inaccessibile per realtà produttive locali di piccola-media dimensione.</t>
+          <t>Il bando EDF riguarda l'integrazione di ricevitori Galileo PRS su sistemi d'arma e centri operativi militari C2, un settore altamente specializzato della difesa che richiede certificazioni di sicurezza NATO/EU classificate e capacità tecnologiche avanzate difficilmente accessibili a una PMI del Cilento. Le aziende beneficiarie sono tipicamente grandi contractor della difesa o istituti di ricerca militare con autorizzazioni specifiche.</t>
         </is>
       </c>
     </row>
     <row r="241" ht="30" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Self-protection systems</t>
+          <t>Ammunition Waste Collection and Disposal Unmanned Platform</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-AIR-SPS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ENERENV-AWC-STEP</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -11801,14 +11801,14 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) sui sistemi di auto-protezione è destinato a consorzi di ricerca e industria della difesa con capacità tecnologiche avanzate, rendendo l'accesso estremamente difficile per una PMI campana del Cilento priva di competenze specifiche nel settore militare. I requisiti di partecipazione tipici dell'EDF prevedono collaborazioni transnazionali complesse e investimenti in R&amp;S di difesa incompatibili con le dimensioni e il profilo produttivo di una piccola impresa locale.</t>
+          <t>Il bando EDF riguarda lo sviluppo di piattaforme robotiche/unmanned per la raccolta e smaltimento di munizioni belliche, un settore altamente specializzato della difesa che richiede competenze aerospaziali, militari e tecnologiche di altissimo livello difficilmente accessibili a una PMI del Cilento. I requisiti tecnici, i consorzî internazionali necessari e i capitali coinvolti lo rendono sostanzialmente inaccessibile per realtà produttive locali di piccola-media dimensione.</t>
         </is>
       </c>
     </row>
     <row r="242" ht="30" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Multiple rocket launcher</t>
+          <t>Self-protection systems</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-GROUND-MRL</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-AIR-SPS</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -11848,14 +11848,14 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di sistemi missilistici multipli (Multiple Rocket Launcher), un settore della difesa ad altissima specializzazione tecnologica e industriale che richiede capacità produttive, certificazioni e investimenti del tutto fuori dalla portata di una PMI del Cilento o della Campania. I destinatari reali sono grandi contractor della difesa europei.</t>
+          <t>Il bando EDF (European Defence Fund) sui sistemi di auto-protezione è destinato a consorzi di ricerca e industrie della difesa con capacità tecnologiche avanzate, escludendo di fatto le PMI generaliste del Cilento prive di expertise nel settore militare/aerospaziale. I requisiti tecnici e le partnership transnazionali obbligatorie rendono l'accesso estremamente complesso per realtà locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="243" ht="30" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>High-performance energy systems</t>
+          <t>Multiple rocket launcher</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ENERENV-HPES-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-GROUND-MRL</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -11895,14 +11895,14 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (Fondo Europeo per la Difesa) finanzia progetti di ricerca e sviluppo nel settore della difesa militare, richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni specifiche del settore: una PMI del Cilento difficilmente possiede i requisiti tecnici, industriali e le partnership necessarie per partecipare competitivamente. I sistemi energetici ad alte prestazioni in questo contesto sono destinati ad applicazioni militari e non civili, escludendo di fatto le tipiche PMI campane operanti in settori tradizionali.</t>
+          <t>Il bando EDF per sistemi di lancio multiplo di razzi è destinato a grandi contractor della difesa con capacità industriali e tecnologiche avanzate, del tutto fuori portata per una PMI del Cilento. Non esistono requisiti tecnici, finanziari o progettuali compatibili con una piccola o media impresa operante in un territorio a vocazione turistica e agricola.</t>
         </is>
       </c>
     </row>
     <row r="244" ht="30" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Secure digital military mobility system</t>
+          <t>High-performance energy systems</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-PROTMOB-DMM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-ENERENV-HPES-STEP</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -11942,14 +11942,14 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa militare, richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni di sicurezza difficilmente accessibili a una PMI del Cilento. Il focus su sistemi di mobilità militare digitale sicura presuppone competenze altamente specializzate e strutture organizzative tipiche di grandi industrie della difesa, non di piccole imprese locali.</t>
+          <t>Il bando EDF (Fondo Europeo per la Difesa) finanzia sistemi energetici ad alte prestazioni in ambito militare/difesa, richiedendo capacità tecnologiche avanzate, consorzi internazionali e accreditamenti nel settore difesa che sono fuori dalla portata di una PMI tipica del Cilento. Non sono previste spese finanziabili rilevanti per realtà produttive locali di piccola dimensione operanti in settori civili.</t>
         </is>
       </c>
     </row>
     <row r="245" ht="30" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Enhanced cognitive EW system with intelligent RESM CESM signal analysis</t>
+          <t>Secure digital military mobility system</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-SENS-CEW-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-PROTMOB-DMM</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -11989,14 +11989,14 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia sistemi avanzati di guerra elettronica cognitiva (EW) con analisi intelligente dei segnali RESM/CESM, un settore altamente specializzato della difesa che richiede capacità tecnologiche, certificazioni e investimenti fuori portata per una PMI del Cilento. I requisiti di consorzio internazionale e le competenze necessarie in elettronica militare rendono questo bando di fatto inaccessibile per realtà produttive locali di piccola-media dimensione.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa militare, richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni di sicurezza difficilmente accessibili a una PMI del Cilento. Le tematiche di mobilità militare digitale sicura sono distanti dal tessuto produttivo locale, orientato verso turismo, agroalimentare e artigianato.</t>
         </is>
       </c>
     </row>
     <row r="246" ht="30" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Enhanced medium-size semi-autonomous surface vessels</t>
+          <t>Enhanced cognitive EW system with intelligent RESM CESM signal analysis</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-NAVAL-EMSAS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-SENS-CEW-STEP</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -12036,14 +12036,14 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per vascelli semi-autonomi di media taglia è destinato a consorzi industriali della difesa con capacità R&amp;D avanzate e certificazioni militari, del tutto fuori dalla portata di una PMI campana o cilentana priva di expertise nel settore navale-militare. I requisiti tecnici, finanziari e di sicurezza rendono l'accesso praticamente impossibile senza essere inseriti in supply chain di grandi prime contractor della difesa.</t>
+          <t>Il bando EDF finanzia sistemi avanzati di guerra elettronica cognitiva (EW) con analisi intelligente dei segnali RESM/CESM, richiedendo competenze altamente specializzate in difesa, elettronica militare e ingegneria dei sistemi complessi, tipiche di grandi contractor della difesa o centri di ricerca. Una PMI del Cilento o della Campania difficilmente possiede le certificazioni di sicurezza, i requisiti tecnici e la capacità consortile necessari per accedere a questo tipo di bando europeo nel settore difesa.</t>
         </is>
       </c>
     </row>
     <row r="247" ht="30" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Smart technologies for next generation fighter systems</t>
+          <t>Enhanced medium-size semi-autonomous surface vessels</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-AIR-STFS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-NAVAL-EMSAS</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -12078,19 +12078,19 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo tecnologico per sistemi d'arma di nuova generazione, richiedendo capacità industriali e tecnologiche di alto livello tipiche di grandi imprese della difesa o centri di ricerca specializzati. Una PMI del Cilento difficilmente possiede i requisiti tecnici, i partenariati internazionali e le certificazioni necessarie per accedere a questo tipo di programma europeo nel settore difesa.</t>
+          <t>Il bando EDF finanzia lo sviluppo di navi di superficie semi-autonome di media taglia per uso militare/difesa, richiedendo capacità tecnologiche navali avanzate, consorzi internazionali e certificazioni difficilmente accessibili a una PMI del Cilento. Il settore della difesa europea è dominato da grandi contractor industriali, rendendo la partecipazione diretta di una piccola impresa campana estremamente improbabile senza un ruolo marginale in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="248" ht="30" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Future main battle tank platform systems</t>
+          <t>Smart technologies for next generation fighter systems</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-GROUND-MBT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-AIR-STFS</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -12125,19 +12125,19 @@
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di sistemi per carri armati da combattimento di nuova generazione, un settore della difesa ad altissima specializzazione tecnologica e con requisiti consortili complessi, del tutto fuori portata per una PMI del Cilento priva di expertise militare-industriale. I finanziamenti sono destinati a grandi consorzi europei della difesa, rendendo la partecipazione diretta di una piccola impresa campana sostanzialmente impossibile.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo su tecnologie avanzate per sistemi d'arma di nuova generazione, richiedendo competenze altamente specializzate in difesa aeronautica e consorzi multinazionali di grandi dimensioni. Una PMI del Cilento difficilmente dispone delle certificazioni, delle capacità tecniche e delle partnership internazionali necessarie per partecipare competitivamente a questo tipo di programma europeo per la difesa.</t>
         </is>
       </c>
     </row>
     <row r="249" ht="30" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Non-thematic research actions by SMEs and research organisations</t>
+          <t>Future main battle tank platform systems</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026</t>
+          <t>11/02/2026</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DIS-RA-SMERO-NT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-DA-GROUND-MBT</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -12177,14 +12177,14 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca nel settore della difesa europea, richiedendo consorzi internazionali, capacità tecnologiche avanzate e competenze militari del tutto estranee al tessuto produttivo tipico del Cilento e della PMI campana media. I costi di partecipazione, la complessità procedurale e i requisiti tecnici lo rendono praticamente inaccessibile senza partnership con grandi industrie della difesa o centri di ricerca specializzati.</t>
+          <t>Il bando EDF riguarda lo sviluppo di sistemi per carri armati da combattimento di nuova generazione, un settore della difesa ad altissima intensità tecnologica e finanziaria riservato di fatto a grandi industrie della difesa e consorzi internazionali. Una PMI del Cilento, anche con competenze manifatturiere o ingegneristiche, non dispone delle certificazioni militari, delle capacità R&amp;D e delle partnerships interistituzionali richieste per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="250" ht="30" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Non-thematic actions targeting disruptive technologies for defence</t>
+          <t>Non-thematic research actions by SMEs and research organisations</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DIS-NT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DIS-RA-SMERO-NT</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -12219,19 +12219,19 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo su tecnologie dirompenti per la difesa, richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze nel settore difesa/dual-use che difficilmente una PMI del Cilento possiede. I requisiti di partecipazione e la complessità progettuale lo rendono di fatto inaccessibile senza un partenariato con grandi player industriali o centri di ricerca specializzati.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca nel settore della difesa europea, richiedendo consorzi internazionali, capacità tecnologiche avanzate e allineamento con priorità militari strategiche: contesto del tutto estraneo alla tipica PMI del Cilento o della Campania operante in settori civili. Le barriere di accesso (competenze, certificazioni di sicurezza, partenariati con enti di difesa) lo rendono di fatto inaccessibile per le PMI di piccola/media dimensione non già inserite nella filiera della difesa.</t>
         </is>
       </c>
     </row>
     <row r="251" ht="30" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Sustainable Gender Equality Champions</t>
+          <t>Non-thematic actions targeting disruptive technologies for defence</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -12241,17 +12241,17 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>02/03/2026</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-2026-LS-DIS-NT</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - EDF</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
@@ -12266,19 +12266,19 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Sustainable Gender Equality Champions' è orientato a enti di ricerca, università e grandi consorzi europei, richiedendo capacità progettuali e amministrative complesse difficilmente accessibili a una PMI del Cilento. Le spese finanziabili riguardano principalmente attività di ricerca e disseminazione scientifica su parità di genere, con scarsa applicabilità diretta per imprese di piccola dimensione operanti in settori produttivi locali.</t>
+          <t>Il bando EDF finanzia ricerca su tecnologie dirompenti per la difesa (es. quantum, AI militare, materiali avanzati), richiedendo consorzi europei e capacità di R&amp;D avanzata tipiche di grandi imprese o centri di ricerca; una PMI del Cilento difficilmente dispone delle competenze tecnologiche militari e della struttura consortile necessaria per competere in questo contesto altamente specializzato.</t>
         </is>
       </c>
     </row>
     <row r="252" ht="30" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Newcomer Gender Equality Champions</t>
+          <t>Sustainable Gender Equality Champions</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-01</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -12313,19 +12313,19 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla parità di genere è orientato a enti di ricerca, università e grandi organizzazioni con capacità progettuali complesse, rendendo molto difficile l'accesso diretto per una PMI del Cilento senza un consorzio strutturato. Le PMI di piccole dimensioni difficilmente dispongono delle risorse amministrative e della rendicontazione richiesta dai bandi Horizon.</t>
+          <t>Il bando Horizon 'Sustainable Gender Equality Champions' è orientato a organismi di ricerca, università e grandi consorzi europei, richiedendo capacità progettuali e amministrative difficilmente compatibili con una PMI del Cilento. Le spese finanziabili riguardano attività di ricerca e implementazione di politiche di genere in contesti istituzionali, non attività produttive o commerciali tipiche di una piccola impresa campana.</t>
         </is>
       </c>
     </row>
     <row r="253" ht="30" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Inclusive Gender Equality Champions</t>
+          <t>Newcomer Gender Equality Champions</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-02</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -12365,34 +12365,34 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Inclusive Gender Equality Champions' è orientato a consorzi di ricerca e grandi organizzazioni con capacità progettuale europea, rendendo l'accesso diretto di una PMI del Cilento molto difficile senza un partner capofila accademico o istituzionale. Una piccola impresa potrebbe al massimo partecipare come partner in un consorzio, ma i requisiti amministrativi e la complessità rendicontativa di Horizon scoraggiano un coinvolgimento autonomo.</t>
+          <t>Il bando Horizon 'Newcomer Gender Equality Champions' è orientato a consorzi di ricerca e organizzazioni accademiche/istituzionali impegnate nella promozione della parità di genere in contesti migratori, con requisiti di partnership transnazionale complessi e capacità di rendicontazione europea difficilmente gestibili da una PMI del Cilento. Le spese finanziabili riguardano attività di ricerca e disseminazione, non investimenti produttivi o operativi tipici delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="254" ht="30" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Works</t>
+          <t>Inclusive Gender Equality Champions</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-WORKS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-GENDER-Prize-03</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>UE - CEF2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -12407,19 +12407,19 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2 finanzia grandi opere infrastrutturali transnazionali su reti energetiche (elettricità, gas, idrogeno, CO₂), con requisiti tecnici e finanziari fuori portata per una PMI del Cilento: i beneficiari tipici sono gestori di rete, grandi utility o consorzi pubblici europei. Non sono previste spese ammissibili rilevanti per imprese di piccola dimensione.</t>
+          <t>Il bando Horizon promuove la parità di genere nelle organizzazioni di ricerca e innovazione, richiedendo strutture con capacità progettuale europea e piani istituzionali complessi (Gender Equality Plans) difficilmente gestibili da una PMI del Cilento senza un dipartimento R&amp;D dedicato. I costi di partecipazione a consorzi Horizon e la complessità amministrativa lo rendono poco accessibile per realtà di piccole dimensioni.</t>
         </is>
       </c>
     </row>
     <row r="255" ht="30" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Studies</t>
+          <t>Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Works</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-STUDIES</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-WORKS</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -12459,14 +12459,14 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 finanzia studi su reti energetiche transeuropee (smart grid, idrogeno, CO₂) con una scala progettuale e requisiti tecnico-amministrativi tipici di grandi operatori energetici o consorzi pubblici, rendendo l'accesso diretto di una PMI del Cilento sostanzialmente impraticabile. Le spese finanziabili riguardano studi di fattibilità su infrastrutture di interesse europeo, ambito lontano dall'operatività ordinaria di una piccola o media impresa campana.</t>
+          <t>Il bando CEF2027 finanzia opere infrastrutturali su reti energetiche transeuropee (elettricità, gas, idrogeno, CO₂) di scala europea, destinate tipicamente a grandi operatori di rete e consorzi pubblici-privati di rilevanza transfrontaliera. Una PMI del Cilento non ha le dimensioni, i requisiti tecnici né la capacità progettuale per accedere direttamente a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="256" ht="30" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Standards for Quantum Technologies</t>
+          <t>Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Studies</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -12476,17 +12476,17 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-STAND-05-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-STUDIES</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - CEF2027</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
@@ -12501,19 +12501,19 @@
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sugli standard per le tecnologie quantistiche è orientato a grandi consorzi di ricerca, università e aziende tech specializzate: una PMI del Cilento difficilmente dispone delle competenze tecniche e della capacità progettuale per accedere a questi finanziamenti competitivi a livello europeo. L'assenza di una filiera quantistica consolidata in Campania rende questo bando sostanzialmente inaccessibile per realtà locali di piccola dimensione.</t>
+          <t>Il bando CEF2027 finanzia studi su reti energetiche transeuropee (smart grid, idrogeno, CO₂) con una scala e una complessità progettuale tipicamente riservata a grandi operatori di rete, enti pubblici o consorzi multinazionali, rendendo di fatto inaccessibile la partecipazione a una PMI campana, anche del settore energetico. Per una realtà del Cilento non vi sono spese finanziabili concretamente aggredibili né requisiti soddisfabili in autonomia.</t>
         </is>
       </c>
     </row>
     <row r="257" ht="30" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Large-Scale Photonic Quantum Computing Platform Technologies</t>
+          <t>Standards for Quantum Technologies</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-PQC-06-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-STAND-05-01</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -12553,34 +12553,34 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda tecnologie avanzate di quantum computing fotonico su larga scala, un settore altamente specializzato che richiede capacità di ricerca fondamentale e infrastrutture tecnologiche fuori dalla portata di una PMI campana, specialmente nel contesto del Cilento. Si tratta di progetti destinati a grandi consorzi di ricerca europei con competenze specifiche in fisica quantistica e fotonica.</t>
+          <t>Il bando riguarda lo sviluppo di standard per tecnologie quantistiche nell'ambito di Horizon Europe, un programma con requisiti tecnici, scientifici e burocratici molto elevati, tipicamente accessibili solo a grandi imprese, università o centri di ricerca. Una PMI del Cilento difficilmente dispone delle competenze specialistiche e della struttura necessarie per partecipare competitivamente a questo tipo di call.</t>
         </is>
       </c>
     </row>
     <row r="258" ht="30" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Apply AI: Piloting AI-based image screening in medical centres</t>
+          <t>Large-Scale Photonic Quantum Computing Platform Technologies</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-AI-PILOTING-10-SCREENING</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-PQC-06-01</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>UE - DIGITAL</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
@@ -12600,14 +12600,14 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato a centri medici e soggetti con capacità di sviluppare e pilotare soluzioni AI avanzate per lo screening di immagini mediche, richiedendo competenze tecnologiche molto specializzate e strutture sanitarie come partner. Una PMI generica del Cilento, salvo che operi specificamente in healthtech o sviluppo software medicale, difficilmente soddisfa i requisiti tecnici e organizzativi richiesti.</t>
+          <t>Il bando finanzia lo sviluppo di piattaforme tecnologiche per il calcolo quantistico fotonico su larga scala, richiedendo competenze altamente specializzate e infrastrutture di ricerca avanzata tipiche di grandi consorzi europei o laboratori universitari. Una PMI del Cilento o della Campania difficilmente possiede i requisiti tecnici e la capacità progettuale necessaria per partecipare competitivamente a questo tipo di iniziativa Horizon.</t>
         </is>
       </c>
     </row>
     <row r="259" ht="30" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Digital solutions for regulatory compliance  through data</t>
+          <t>Apply AI: Piloting AI-based image screening in medical centres</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-AI-DATA-10-COMPLIANCE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-AI-PILOTING-10-SCREENING</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -12642,19 +12642,19 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>Digitalizzazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>Il bando UE-DIGITAL focalizzato su soluzioni digitali per la conformità normativa tramite dati è orientato tipicamente a grandi consorzi tecnologici, enti di ricerca o scale-up con forti competenze in data management e regulatory tech, rendendo l'accesso molto complesso per una PMI del Cilento priva di tali infrastrutture. Le PMI locali, spesso operanti in turismo, agricoltura o artigianato, difficilmente dispongono delle capacità tecniche e amministrative richieste per candidarsi autonomamente a bandi diretti europei di questo profilo.</t>
+          <t>Il bando finanzia progetti pilota di screening medico basati su intelligenza artificiale applicata alle immagini, rivolto a centri medici e attori del settore sanitario con competenze tecnologiche avanzate in AI. Una PMI generica del Cilento difficilmente possiede i requisiti tecnici e il profilo settoriale richiesto, salvo rare eccezioni nel campo delle tecnologie medicali o dell'healthtech.</t>
         </is>
       </c>
     </row>
     <row r="260" ht="30" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Support to Dissemination and Exploitation (D&amp;E) for the Digital Europe Programme</t>
+          <t>Digital solutions for regulatory compliance  through data</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-SUPPORT-10-DISSEMINATION</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-AI-DATA-10-COMPLIANCE</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -12694,14 +12694,14 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia attività di disseminazione e sfruttamento dei risultati del Programma Digital Europe, rivolto principalmente a consorzi di grandi organizzazioni, enti pubblici e centri di ricerca, non a PMI singole. Una piccola impresa del Cilento non ha struttura né capacità progettuale per partecipare direttamente a questo tipo di azione europea.</t>
+          <t>Il bando finanzia soluzioni digitali avanzate per la conformità normativa basate sui dati, un ambito tipicamente orientato a grandi operatori tecnologici o consorzi di ricerca con capacità R&amp;D strutturate. Una PMI del Cilento difficilmente dispone delle competenze tecniche e della massa critica necessarie per competere su bandi diretti UE-DIGITAL, che richiedono partnership transnazionali e proposal complesse.</t>
         </is>
       </c>
     </row>
     <row r="261" ht="30" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Research Support Framework for Situational Awareness on information integrity</t>
+          <t>Support to Dissemination and Exploitation (D&amp;E) for the Digital Europe Programme</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-RSF-10-AWARENESS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-SUPPORT-10-DISSEMINATION</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -12736,19 +12736,19 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia attività di ricerca avanzata sulla integrità dell'informazione e situational awareness in ambito digitale, richiedendo capacità di ricerca specializzata e strutture tipiche di enti accademici o grandi aziende tech; una PMI del Cilento difficilmente possiede i requisiti tecnici e le risorse per competere in questo contesto europeo altamente specializzato.</t>
+          <t>Il bando finanzia attività di disseminazione e sfruttamento dei risultati nell'ambito del programma Digital Europe, rivolto principalmente a consorzi di grandi organizzazioni, enti di ricerca e istituzioni pubbliche. Una PMI del Cilento difficilmente ha i requisiti strutturali e le capacità progettuali per accedere autonomamente a questo tipo di call, pensata per chi già gestisce progetti DEP e deve valorizzarne i risultati a livello europeo.</t>
         </is>
       </c>
     </row>
     <row r="262" ht="30" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Support to the implementation of Multi-Country Projects: EDIC Support Hub</t>
+          <t>Research Support Framework for Situational Awareness on information integrity</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-MCP-10-HUB</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-RSF-10-AWARENESS</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -12783,19 +12783,19 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>Digitalizzazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato a supportare la creazione e gestione di strutture hub per progetti digitali multi-paese (EDIC), con destinatari tipicamente enti pubblici, consorzi istituzionali o grandi organizzazioni: una PMI del Cilento difficilmente accede direttamente come beneficiaria principale. L'utilità indiretta è limitata e richiederebbe partnership con soggetti istituzionali già coinvolti in reti EDIC.</t>
+          <t>Il bando finanzia attività di ricerca avanzata sull'integrità dell'informazione e la consapevolezza situazionale, ambiti tipicamente riservati a grandi enti di ricerca, università o consorzi specializzati in cybersecurity e analisi dei media. Una PMI del Cilento, salvo rari casi di startup tecnologiche altamente specializzate, difficilmente possiede i requisiti tecnici e la capacità progettuale per competere in questo contesto europeo.</t>
         </is>
       </c>
     </row>
     <row r="263" ht="30" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Building capacity to deploy the EEHRxF and digital  health services and systems to support the rights of  citizens and reuse of health data under EHDS</t>
+          <t>Support to the implementation of Multi-Country Projects: EDIC Support Hub</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-10-EHDS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-MCP-10-HUB</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -12835,14 +12835,14 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo dell'infrastruttura europea per la condivisione di dati sanitari (EHDS) e i sistemi EEHRxF, con destinatari tipici come autorità sanitarie nazionali, enti pubblici e grandi consorzi tecnologici. Una PMI del Cilento difficilmente possiede i requisiti tecnici, istituzionali e la capacità progettuale per partecipare autonomamente a un bando UE di questa complessità nel settore della sanità digitale.</t>
+          <t>Il bando è rivolto principalmente a soggetti capofila di progetti multi-paese nell'ambito delle EDIC (European Digital Infrastructure Consortia), strutture complesse che richiedono partnership internazionali e capacità istituzionali difficilmente accessibili a una PMI del Cilento. Una piccola impresa campana difficilmente potrà candidarsi direttamente, al massimo potrebbe beneficiare indirettamente come soggetto coinvolto da un consorzio più grande.</t>
         </is>
       </c>
     </row>
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Ensuring comprehensive geographical coverage of the Network of Safer Internet Centres (SICs)</t>
+          <t>Building capacity to deploy the EEHRxF and digital  health services and systems to support the rights of  citizens and reuse of health data under EHDS</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-10-NETWORKSICs</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-10-EHDS</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -12882,14 +12882,14 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia la creazione e gestione di Centri per un Internet più Sicuro (SICs) a copertura geografica europea, rivolgendosi a consorzi istituzionali o enti specializzati nella protezione online di minori, non a PMI commerciali del Cilento o della Campania. Una piccola impresa non ha i requisiti strutturali né la mission istituzionale per candidarsi a questo tipo di appalto UE.</t>
+          <t>Il bando finanzia la costruzione di infrastrutture per lo Spazio Europeo dei Dati Sanitari (EHDS) e sistemi digitali per la salute, con destinatari tipicamente enti pubblici, autorità sanitarie nazionali e grandi consorzi istituzionali. Una PMI del Cilento, anche operante nel settore sanitario o digitale, difficilmente possiede i requisiti tecnici, la scala organizzativa e le partnership istituzionali richieste per partecipare competitivamente a questo tipo di bando europeo.</t>
         </is>
       </c>
     </row>
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>EdTech Accelerator</t>
+          <t>Ensuring comprehensive geographical coverage of the Network of Safer Internet Centres (SICs)</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-SKILLS-10-EDTECH</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/DIGITAL-2026-BESTUSE-10-NETWORKSICs</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato a startup e scaleup del settore EdTech (tecnologie per l'educazione) con forte componente digitale e scalabilità internazionale, caratteristiche difficilmente riscontrabili in una PMI tradizionale del Cilento. Una piccola impresa locale non operante nel mercato dell'istruzione digitale avrebbe scarsissime possibilità di accesso e valorizzazione concreta.</t>
+          <t>Il bando UE-DIGITAL è orientato alla creazione e gestione di una rete europea di Centri per un Internet Sicuro (SICs), destinato principalmente a enti pubblici, organizzazioni no-profit e grandi consorzi con copertura geografica nazionale o transnazionale. Una PMI del Cilento non ha i requisiti strutturali né la dimensione istituzionale per candidarsi come beneficiario diretto in questo tipo di progetto infrastrutturale europeo.</t>
         </is>
       </c>
     </row>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto principalmente a grandi coalizioni nazionali e organizzazioni strutturate che promuovono competenze digitali su scala nazionale, non a singole PMI del Cilento. Una piccola impresa campana difficilmente può accedere direttamente a questo strumento UE, che richiede partnership istituzionali complesse e capacità progettuali di livello europeo.</t>
+          <t>Il bando è rivolto a coalizioni nazionali e grandi organizzazioni impegnate nella promozione delle competenze digitali a livello sistemico, non a singole PMI: una piccola impresa del Cilento non può accedere direttamente come beneficiaria. L'unica utilità indiretta sarebbe aderire a una coalizione già esistente, ma si tratta di un percorso complesso e poco praticabile per realtà di dimensioni ridotte.</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>Il bando UE DIGITAL per competenze avanzate in AI applicata alla salute è tipicamente rivolto a università, centri di ricerca e grandi consorzi, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un partner istituzionale capofila. Una PMI del settore sanitario o healthtech potrebbe partecipare solo come partner secondario in un consorzio, con ruolo e budget limitati.</t>
+          <t>Il bando EU Digital finanzia progetti su competenze digitali avanzate per l'adozione dell'IA in sanità, ma è tipicamente riservato a consorzi di università, centri di ricerca o grandi organizzazioni sanitarie, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un ruolo marginale di partner. Una piccola impresa locale avrebbe scarsa capacità progettuale e competitiva in un bando europeo di questo livello tecnico e settoriale.</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la cooperazione amministrativa tra autorità pubbliche e l'accesso alle informazioni sul distacco dei lavoratori transfrontalieri, ed è destinato principalmente a enti pubblici e istituzioni, non a PMI. Una piccola impresa del Cilento non ha titolo diretto per candidarsi né spese operative finanziabili in questo contesto.</t>
+          <t>Il bando riguarda la cooperazione amministrativa tra autorità pubbliche degli Stati membri sul distacco dei lavoratori, ed è destinato a enti istituzionali e pubbliche amministrazioni, non a PMI. Una piccola impresa del Cilento non ha titolo né capacità strutturale per candidarsi a questo tipo di progetto ESF a valenza transnazionale.</t>
         </is>
       </c>
     </row>
@@ -13117,7 +13117,7 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 Rail finanzia studi e lavori su infrastrutture ferroviarie transeuropee (TEN-T), destinato principalmente a gestori di rete, enti pubblici e grandi consorzi infrastrutturali: una PMI del Cilento non ha i requisiti tecnici né la scala dimensionale per accedere direttamente a progetti di questo tipo.</t>
+          <t>Il bando CEF2027 Rail finanzia studi e opere infrastrutturali ferroviarie di scala europea, rivolto principalmente a gestori di rete, enti pubblici e grandi consorzi: una PMI del Cilento non ha né la dimensione né il profilo istituzionale per accedere direttamente a questi fondi. Il territorio del Cilento, già marginale rispetto alle reti TEN-T, difficilmente rientrerebbe tra le aree prioritarie di intervento.</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 Rail finanzia studi e lavori infrastrutturali ferroviari su scala europea, rivolto principalmente a gestori di rete e grandi enti pubblici: una PMI del Cilento non ha i requisiti tecnici, dimensionali né la capacità progettuale per accedere direttamente a questo tipo di finanziamento.</t>
+          <t>Il bando CEF (Connecting Europe Facility) finanzia studi e lavori infrastrutturali ferroviari su scala europea, rivolto tipicamente a grandi gestori di rete, enti pubblici e grandi contractor: una PMI del Cilento non ha né la dimensione né il profilo tecnico-finanziario per accedere direttamente a questo tipo di finanziamento. L'unica via indiretta sarebbe partecipare come subappaltatore in un consorzio guidato da grandi player, scenario comunque molto difficile per una realtà locale di piccole-medie dimensioni.</t>
         </is>
       </c>
     </row>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 sulle vie navigabili interne finanzia grandi opere infrastrutturali su corsi d'acqua europei, richiedendo capacità tecniche e finanziarie da grandi consorzi o enti pubblici. Una PMI del Cilento non ha né la dimensione né il posizionamento settoriale per accedere a questo tipo di appalto.</t>
+          <t>Il bando CEF 2027 finanzia opere infrastrutturali sulle vie navigabili interne europee, un settore che non riguarda il territorio del Cilento né è accessibile a PMI di piccole dimensioni, richiedendo capacità tecniche e finanziarie tipiche di grandi operatori pubblici o consorzi infrastrutturali. Una PMI campana non avrebbe i requisiti soggettivi né la scala progettuale necessaria per partecipare.</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia opere infrastrutturali su reti di trasporto stradale transeuropeo (TEN-T), destinato principalmente a enti pubblici, grandi operatori di trasporto e consorzi nazionali: una PMI del Cilento non ha né la dimensione né il profilo istituzionale per candidarsi direttamente. Il territorio cilentano inoltre non è attraversato da corridoi TEN-T prioritari, rendendo ancora più remota qualsiasi ricaduta diretta.</t>
+          <t>Il bando CEF (Connecting Europe Facility) finanzia opere infrastrutturali per la digitalizzazione del trasporto stradale a scala europea, richiedendo capacità progettuali, tecniche e finanziarie tipiche di grandi operatori pubblici o consorzi internazionali. Una PMI del Cilento non ha i requisiti dimensionali né il profilo istituzionale per accedere direttamente a questo tipo di strumento.</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 sui confini esterni finanzia grandi infrastrutture di frontiera (studi, lavori o interventi misti) destinate a stati membri e autorità pubbliche, non a PMI private. Una piccola impresa del Cilento non ha i requisiti soggettivi né la scala dimensionale per accedere direttamente a questo tipo di finanziamento.</t>
+          <t>Il bando CEF 2027 'External Borders' finanzia studi e opere infrastrutturali per la gestione delle frontiere esterne dell'UE, destinato tipicamente ad autorità pubbliche e grandi enti statali. Una PMI del Cilento non ha i requisiti soggettivi né la capacità progettuale per accedere a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2 finanzia opere infrastrutturali su scala europea per porti marittimi e vie navigabili interne, con requisiti tecnici e finanziari adatti a grandi enti pubblici o consorzi industriali, non a PMI. Una piccola impresa del Cilento non ha le capacità progettuali né la dimensione necessaria per candidarsi direttamente a lavori infrastrutturali di questa portata.</t>
+          <t>Il bando CEF 2027 finanzia grandi opere infrastrutturali per spazi marittimi e porti interni europei, con dimensioni progettuali e requisiti tecnico-finanziari tipici di enti pubblici o grandi operatori portuali, rendendo l'accesso sostanzialmente inaccessibile per una PMI del Cilento. Pur essendo un territorio costiero, una piccola impresa campana non dispone della capacità istituzionale e finanziaria necessaria per candidarsi a works di questa natura.</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 finanzia studi e lavori infrastrutturali sulla rete di trasporto transeuropea TEN-T con finalità di doppio uso civile-militare, destinato tipicamente a enti pubblici, gestori di infrastrutture e grandi operatori di trasporto. Una PMI del Cilento non ha titolo né capacità finanziaria per candidarsi direttamente a progetti di questa scala e natura strategica.</t>
+          <t>Il bando CEF2027 finanzia studi e lavori infrastrutturali sulla rete transeuropea dei trasporti (TEN-T) ad uso duale civile-militare, destinato tipicamente a enti pubblici, gestori di infrastrutture e grandi consorzi internazionali. Una PMI del Cilento non ha i requisiti dimensionali né la natura giuridica per candidarsi direttamente, potendo al massimo partecipare come subappaltatore in progetti di scala europea.</t>
         </is>
       </c>
     </row>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia infrastrutture per carburanti alternativi (stazioni di ricarica/rifornimento) nel settore stradale e aeroportuale, con investimenti di scala europea difficilmente accessibili a una PMI campana. I beneficiari tipici sono enti pubblici, gestori di reti infrastrutturali o grandi consorzi, rendendo questo strumento di fatto inaccessibile per una piccola impresa del Cilento.</t>
+          <t>Il bando CEF2027 finanzia la realizzazione di infrastrutture per carburanti alternativi nel settore stradale e aereo, con progetti di scala europea che richiedono capacità tecniche, finanziarie e amministrative tipiche di grandi operatori pubblici o consorzi infrastrutturali. Una PMI del Cilento non ha dimensioni né profilo adeguati per candidarsi direttamente, potendo al massimo partecipare come subappaltatore in un consorzio più ampio.</t>
         </is>
       </c>
     </row>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede consorzi internazionali di ricerca con capacità progettuali elevate e budget multimilionari, barriere difficilmente superabili per una PMI edile del Cilento; tuttavia, una PMI del settore costruzioni potrebbe partecipare come partner industriale in un consorzio guidato da università o centri di ricerca, portando competenze pratiche sull'edilizia locale e accedendo a finanziamenti per sviluppare soluzioni di economia circolare nei cantieri.</t>
+          <t>Il bando Horizon UE richiede consorzi internazionali di ricerca con elevata capacità progettuale e finanziaria, risultando di fatto inaccessibile per una PMI autonoma del Cilento; una PMI edile o del settore costruzioni potrebbe partecipare solo come partner junior in un consorzio guidato da università o grandi imprese, con ruoli limitati e oneri amministrativi molto elevati.</t>
         </is>
       </c>
     </row>
@@ -13540,7 +13540,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si focalizza su sistemi di trasporto pubblico urbano ed extraurbano a basse emissioni con mobilità condivisa, destinato principalmente a grandi consorzi di ricerca, enti pubblici e grandi aziende di trasporto; una PMI del Cilento difficilmente dispone delle competenze tecniche, della capacità progettuale e dei partner istituzionali necessari per competere in un bando europeo di questa complessità e dimensione finanziaria.</t>
+          <t>Il bando Horizon finanzia progetti di ricerca e innovazione su larga scala per il trasporto pubblico urbano efficiente e la mobilità condivisa, richiedendo consorzi internazionali e competenze altamente specializzate difficilmente accessibili a una PMI campana di piccole dimensioni. Per una realtà del Cilento, territorio a vocazione turistica e rurale, il focus su trasporto urbano rende il bando ancora meno pertinente, salvo partecipazione come partner secondario in progetti con enti pubblici o università.</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a consorzi di ricerca e grandi player del settore energetico per sviluppare soluzioni di riscaldamento a bassa temperatura in edifici plurifamiliari, con requisiti di partnership transnazionale e capacità di R&amp;S difficilmente compatibili con una PMI del Cilento. Una piccola impresa campana del settore impiantistico o edile troverebbe barriere tecniche e amministrative molto elevate per partecipare autonomamente.</t>
+          <t>Il bando Horizon UE richiede consorzi internazionali, capacità di ricerca avanzata e budget elevati, caratteristiche incompatibili con una PMI di piccola dimensione operante nel Cilento. Una PMI locale del settore impiantistico o edilizio potrebbe partecipare solo come partner junior in un consorzio già strutturato, scenario difficilmente accessibile senza reti consolidate a livello europeo.</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe CCAM riguarda dimostrazioni su larga scala di mobilità connessa e automatizzata, richiedendo consorzi internazionali con capacità tecniche e finanziarie elevate, del tutto fuori portata per una PMI campana di piccole dimensioni operante nel Cilento. Le spese finanziabili (R&amp;S avanzata, infrastrutture pilota, testing su scala) presuppongono competenze specialistiche nel settore automotive/tech che difficilmente una PMI locale possiede.</t>
+          <t>Il bando finanzia dimostrazioni su larga scala di sistemi di mobilità connessa e automatizzata (CCAM), richiedendo consorzi internazionali con capacità tecnologiche e finanziarie elevate, del tutto sproporzionate rispetto alle dimensioni e alle competenze tipiche di una PMI campana, specialmente nel Cilento. Le spese finanziate riguardano R&amp;S avanzata su veicoli autonomi e infrastrutture smart, settori lontani dal tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede progetti di ricerca e innovazione su trasporto merci multimodale e logistica su scala europea, con requisiti di consorzio internazionale e capacità di R&amp;D difficilmente compatibili con una PMI di piccola dimensione del Cilento, territorio peraltro privo di infrastrutture logistiche multimodali rilevanti. Le risorse finanziarie, la complessità progettuale e il profilo tecnico-scientifico richiesto lo rendono sostanzialmente inaccessibile senza il supporto di un grande partner capofila.</t>
+          <t>Il bando Horizon UE finanzia ricerca e innovazione su trasporto merci multimodale e logistica, con requisiti di consorzio internazionale e capacità di ricerca avanzata difficilmente accessibili per una PMI del Cilento. Le risorse necessarie per partecipare (partnership europee, attività R&amp;D strutturate) e la natura del settore target (freight logistics su scala europea) rendono questo bando sostanzialmente inaccessibile per una piccola impresa campana operante in un territorio periferico.</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>Il bando CCAM (Connected, Cooperative and Automated Mobility) di Horizon Europe è focalizzato sulla mobilità automatizzata e connessa in chiave geopolitica europea, richiedendo consorzi internazionali con forti componenti di ricerca avanzata. Una PMI del Cilento difficilmente possiede le capacità tecniche e la rete partenariale transnazionale richieste per competere in questo tipo di call.</t>
+          <t>Il bando Horizon CCAM (Connected, Cooperative and Automated Mobility) è orientato a grandi consorzi di ricerca europei con focus sulla mobilità automatizzata e geopolitica dell'innovazione, richiedendo capacità progettuali e budget molto superiori a quelli tipici di una PMI campana del Cilento. L'ambito tematico (mobilità connessa e autonoma in chiave competitività UE) è lontano dal tessuto produttivo locale, prevalentemente agricolo, turistico e artigianale.</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su sicurezza stradale e resilienza delle aree rurali richiede capacità di ricerca avanzata, consorzio internazionale e risorse progettuali difficilmente accessibili a una PMI di piccole dimensioni del Cilento. Pur essendo il territorio rurale e le infrastrutture viarie tematiche rilevanti per l'area, la complessità burocratica e i requisiti di R&amp;I di Horizon lo rendono praticabile solo come partner junior in un consorzio guidato da università o enti di ricerca.</t>
+          <t>Il bando Horizon UE sulla sicurezza stradale e resilienza delle aree rurali è orientato a consorzi di ricerca, enti pubblici e grandi organizzazioni con capacità di progettazione europea, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un ruolo marginale in un partenariato internazionale. Le spese finanziabili riguardano ricerca e sviluppo su infrastrutture stradali e gestione del rischio, ambiti lontani dalle attività tipiche delle PMI locali.</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi europei con capacità di ricerca avanzata in AI e trasporti multimodali, con budget e strutture tipicamente fuori portata per una PMI del Cilento. Le PMI locali, prevalentemente legate al turismo e ai servizi, difficilmente possiedono le competenze tecnologiche in AI discriminativa/generativa applicate ai trasporti richieste come requisito base.</t>
+          <t>Il bando Horizon EU richiede consorzi internazionali, capacità di R&amp;D avanzata e competenze specifiche in AI applicata ai trasporti multimodali, requisiti difficilmente soddisfacibili da una PMI campana di piccole dimensioni senza un solido track record europeo. Per una PMI del Cilento, il focus su trasporto passeggeri e resilienza digitale è lontano dal tessuto produttivo locale, prevalentemente orientato a turismo, agricoltura e agroalimentare.</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>Il bando CIVITAS si rivolge principalmente a città e autorità locali per progetti di mobilità urbana sostenibile su larga scala, con requisiti di partenariato e capacità progettuale difficilmente compatibili con una PMI del Cilento, territorio a vocazione rurale e turistico-costiero, lontano dai contesti metropolitani target. Una PMI potrebbe al massimo partecipare come partner secondario in un consorzio, ma l'accesso diretto ai finanziamenti risulta estremamente complesso.</t>
+          <t>Il bando CIVITAS finanzia progetti di mobilità urbana sostenibile su scala europea, richiede partnership con enti pubblici e municipalità come soggetti guida, con budget e complessità progettuali difficilmente gestibili da una PMI del Cilento autonomamente. Il territorio cilentano, prevalentemente rurale e a bassa densità urbana, non corrisponde al target primario del programma, orientato a contesti urbani strutturati.</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13916,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>Il bando HORIZON CCAM finanzia ricerca avanzata su intelligenza artificiale generativa applicata alla mobilità connessa e autonoma (guida autonoma, sistemi di percezione e decision-making), richiedendo consorzi internazionali con forti competenze R&amp;D e capacità di rendicontazione europea: barriere difficilmente superabili per una PMI del Cilento non specializzata in questo settore. Solo aziende tech con laboratori di ricerca o spin-off universitari potrebbero candidarsi come partner junior in un consorzio già strutturato.</t>
+          <t>Il bando Horizon CCAM richiede consorzi internazionali con forte componente di R&amp;S avanzata sull'intelligenza artificiale applicata alla mobilità connessa e automatizzata, richiedendo capacità tecniche e finanziarie difficilmente accessibili per una PMI campana del Cilento senza un solido network europeo preesistente. Le PMI di piccola dimensione possono partecipare solo come partner subordinati, con oneri amministrativi e rendicontativi molto elevati e nessun vantaggio competitivo territoriale specifico per quest'area.</t>
         </is>
       </c>
     </row>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulle batterie al litio di nuova generazione è orientato a grandi consorzi di ricerca industriale con capacità tecnologiche avanzate nel settore dell'elettromobilità, rendendo l'accesso estremamente difficile per una PMI del Cilento priva di strutture R&amp;D specifiche in chimica dei materiali o manifattura di celle. Non esistono filiere produttive legate a questo settore nel territorio cilentano che possano giustificare una partecipazione concreta.</t>
+          <t>Il bando Horizon Europe sulle batterie al litio di nuova generazione per la mobilità richiede capacità di R&amp;S avanzata, infrastrutture industriali e partenariati europei difficilmente accessibili per una PMI campana del Cilento, territorio privo di un tessuto produttivo legato alla filiera delle batterie o dell'automotive elettrico. Le risorse finanziabili riguardano sviluppo tecnologico e produzione industriale ad alta intensità di capitale, lontane dalle vocazioni economiche locali (turismo, agricoltura, artigianato).</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia opere infrastrutturali per la riparazione di cavi sottomarini nell'ambito del programma CEF2027, destinato a grandi operatori delle telecomunicazioni o consorzi specializzati con capacità tecniche e finanziarie elevate. Una PMI del Cilento o della Campania non dispone delle competenze navali e infrastrutturali richieste né della scala operativa necessaria per partecipare a questo tipo di appalto europeo.</t>
+          <t>Il bando CEF2027 finanzia lavori infrastrutturali per la riparazione di cavi sottomarini di telecomunicazione, un settore altamente specializzato che richiede capacità tecniche, navali e finanziarie tipiche di grandi imprese o consorzi internazionali. Una PMI campana, anche del Cilento con la sua posizione costiera, non dispone strutturalmente dei requisiti tecnici e dimensionali per partecipare a questo tipo di appalto europeo.</t>
         </is>
       </c>
     </row>
@@ -14057,7 +14057,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di una Partnership europea co-finanziata nell'ambito di Horizon Europe, orientata alla ricerca accademica e istituzionale su trasformazioni sociali e resilienza: il accesso diretto per una PMI del Cilento è estremamente difficile, richiedendo consorziate con enti di ricerca europei e capacità progettuali complesse. Non sono previsti finanziamenti diretti per attività produttive o servizi tipici delle piccole imprese locali.</t>
+          <t>Il bando Horizon Europe sulle Partnership per le Trasformazioni Sociali è orientato a consorzi di ricerca accademica e istituzioni pubbliche europee, non a PMI operative. Una piccola impresa del Cilento non ha né la struttura né i requisiti per guidare o partecipare autonomamente a questo tipo di partenariato co-finanziato a livello europeo.</t>
         </is>
       </c>
     </row>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda munizioni, missili e armi esplosive, un settore della difesa ad altissima specializzazione tecnica e industriale che richiede requisiti di sicurezza, certificazioni e capacità produttive del tutto incompatibili con una PMI del Cilento o della Campania in generale. Le risorse sono destinate a grandi contractor della difesa, non a piccole e medie imprese territoriali.</t>
+          <t>Il bando EDF riguarda munizioni, missili e armamenti esplosivi, settore altamente specializzato riservato a grandi contractor della difesa con requisiti tecnici, certificazioni e capacità produttive del tutto incompatibili con una PMI del Cilento o della Campania in generale. Non esistono spese finanziabili rilevanti per realtà produttive locali di piccola-media dimensione.</t>
         </is>
       </c>
     </row>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi counter-drone è orientato a grandi consorzi industriali della difesa con capacità R&amp;D avanzate e certificazioni militari, requisiti difficilmente raggiungibili da una PMI del Cilento senza partnership strutturate con prime contractor della difesa. L'accesso è possibile solo come subappaltatore specializzato in elettronica, sensori o software embedded, contesti produttivi quasi assenti nel tessuto imprenditoriale cilentano.</t>
+          <t>Il bando EDF sui sistemi counter-drone è destinato a consorzi di grandi aziende della difesa e centri di ricerca avanzata, con requisiti tecnici e finanziari difficilmente compatibili con una PMI del Cilento. L'accesso è possibile solo come partner junior in un consorzio europeo, scenario molto improbabile per realtà produttive locali senza esperienza nel settore difesa.</t>
         </is>
       </c>
     </row>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di missili, munizioni e bombe nell'ambito della difesa europea, un settore altamente specializzato che richiede certificazioni, infrastrutture e capacità industriali inaccessibili a una PMI del Cilento o della Campania in generale. Le barriere tecniche, normative e finanziarie rendono questo bando di fatto non perseguibile per una piccola o media impresa locale.</t>
+          <t>Il bando EDF riguarda missili, munizioni e sistemi d'arma, settore altamente specializzato riservato a grandi contractor della difesa con certificazioni NATO/militari specifiche. Una PMI del Cilento o della Campania, salvo rarissimi casi di componentistica aerospaziale/difesa già consolidata, non ha i requisiti tecnici, le abilitazioni di sicurezza né la capacità finanziaria per partecipare a questo tipo di programma europeo.</t>
         </is>
       </c>
     </row>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la sorveglianza avanzata delle frontiere e la consapevolezza situazionale, settori che richiedono competenze altamente specializzate in difesa e sicurezza nazionale, tipicamente riservati a grandi aziende tecnologiche o enti di ricerca. Una PMI del Cilento, salvo rarissime specializzazioni in tecnologie di sorveglianza, droni o sistemi ICT per la sicurezza, difficilmente può competere in questo contesto per complessità tecnica e dimensione dei consorzi richiesti.</t>
+          <t>Il bando Horizon riguarda tecnologie avanzate per la sorveglianza delle frontiere e la sicurezza, settore dominato da grandi aziende della difesa e centri di ricerca specializzati, con requisiti tecnici e consorziali difficilmente accessibili per una PMI campana del Cilento. Non è pertinente per attività produttive o di servizio tipiche del tessuto economico locale.</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi europei con elevata capacità di ricerca e sviluppo, budget e competenze tecnico-scientifiche difficilmente accessibili a una PMI di piccola dimensione del Cilento. Il focus sulla gestione del rischio da catastrofi naturali potrebbe in teoria interessare aziende locali del settore ambientale o della protezione civile, ma le barriere burocratiche e finanziarie di Horizon lo rendono praticamente inaccessibile senza un partner capofila universitario o industriale strutturato.</t>
+          <t>Il bando Horizon richiede consorzi internazionali, capacità di R&amp;D avanzata e risorse amministrative elevate, rendendolo di fatto inaccessibile a una PMI di piccola dimensione del Cilento senza un partner capofila strutturato. Il focus sulla gestione del rischio disastri può essere rilevante per il territorio (frane, alluvioni), ma la complessità progettuale esclude un accesso diretto e autonomo.</t>
         </is>
       </c>
     </row>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi europei con forte componente di ricerca scientifica sulla gestione dei rischi e la preparazione ai disastri, struttura progettuale complessa e budget elevati difficilmente gestibili da una PMI campana di piccole dimensioni. Sebbene il territorio del Cilento sia soggetto a rischi idrogeologici e sismici che potrebbero teoricamente giustificare interesse, le PMI locali raramente dispongono delle capacità tecniche e amministrative richieste per partecipare direttamente a bandi Horizon di questa natura.</t>
+          <t>Si tratta di un bando Horizon EU orientato alla ricerca e innovazione sulla gestione del rischio e la preparazione ai disastri, tipicamente accessibile a consorzi con università ed enti pubblici come capofila; una PMI campana del Cilento potrebbe partecipare solo come partner secondario in progetti di ricerca applicata, ruolo difficilmente praticabile senza una rete istituzionale già consolidata.</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede capacità di ricerca avanzata su tecnologie emergenti applicate alla sicurezza e al contrasto criminale, con consorzio internazionale e competenze specialistiche difficilmente accessibili a una PMI del Cilento. L'ambito tematico (lawful access, cybercrime, misuse of emerging tech) è lontano dalle filiere produttive tipiche del territorio come turismo, agricoltura e agroalimentare.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata su tecnologie emergenti e criminalità informatica, con consorzî internazionali e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. Le risorse finanziabili (R&amp;S, personale ricercatore, attrezzature di laboratorio) sono orientate a grandi enti di ricerca o aziende tech strutturate, non a realtà produttive locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -14428,12 +14428,12 @@
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede attività di ricerca scientifica avanzata sulla valutazione dell'età in contesti di sicurezza e gestione delle frontiere, con necessità di competenze specialistiche e partnership istituzionali internazionali difficilmente accessibili per una PMI del Cilento. Il tema è lontano dal tessuto produttivo locale (turismo, agricoltura, artigianato) e i requisiti tecnici e burocratici di Horizon lo rendono praticabile solo con il supporto di enti di ricerca o università.</t>
+          <t>Il bando Horizon riguarda la ricerca scientifica sui metodi di valutazione dell'età in contesti di sicurezza e gestione delle frontiere, un ambito altamente specializzato che richiede competenze forensi, mediche e di ricerca avanzata difficilmente presenti in una PMI del Cilento. La natura del programma Horizon, con requisiti consortili internazionali e focus su ricerca fondamentale, lo rende sostanzialmente inaccessibile per una piccola o media impresa locale senza un posizionamento specifico nel settore della sicurezza o delle tecnologie forensi.</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14480,7 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca e sviluppo avanzate, consorzi internazionali e competenze specialistiche in sicurezza e antiterrorismo difficilmente accessibili a una PMI del Cilento. Le risorse finanziabili (R&amp;S, tecnologie di protezione per spazi confinati) sono pensate per grandi enti di ricerca o aziende del settore difesa/sicurezza, non per il tessuto produttivo locale.</t>
+          <t>Il bando Horizon si concentra su ricerca e sviluppo tecnologico in ambito sicurezza antiterrorismo in spazi confinati come scuole, richiedendo capacità di ricerca avanzata, partnership internazionali e strutture progettuali complesse che sono tipicamente fuori dalla portata di una PMI del Cilento senza esperienza pregressa in progetti europei di questa natura. Le PMI campane potrebbero partecipare solo come partner junior in consorzi guidati da università o grandi enti di ricerca, con ruoli marginali e difficoltà nel sostenere i costi di gestione progettuale richiesti.</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sulla prevenzione e investigazione delle persone scomparse è orientato a enti di ricerca, forze dell'ordine e consorzi accademici, richiedendo capacità progettuali e infrastrutture di ricerca difficilmente disponibili in una PMI campana o cilentana. Non sono previste spese tipicamente accessibili a piccole imprese locali, né settori produttivi del territorio come turismo, agricoltura o artigianato risultano beneficiari target.</t>
+          <t>Il bando Horizon sulla prevenzione e investigazione delle persone scomparse è orientato a consorzi di ricerca, forze dell'ordine e grandi enti pubblici, rendendo l'accesso estremamente difficile per una PMI campana o del Cilento priva di competenze specifiche in sicurezza pubblica e criminologia. Non finanzia attività produttive, commerciali o di servizio tipiche delle PMI locali.</t>
         </is>
       </c>
     </row>
@@ -14574,7 +14574,7 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla prevenzione del crimine legato alle dipendenze è orientato a consorzi di ricerca, università e istituzioni pubbliche, con requisiti di partenariato transnazionale complessi e capacità di rendicontazione europea difficilmente compatibili con una PMI campana di piccole dimensioni. Per una PMI del Cilento non esistono spese finanziabili rilevanti né settori produttivi locali (turismo, agricoltura, artigianato) direttamente coinvolti.</t>
+          <t>Il bando Horizon si focalizza su ricerca accademica e istituzionale per la prevenzione del crimine legato alle dipendenze, richiedendo consorzi europei con forte componente scientifica e forze dell'ordine: una PMI campana, anche del Cilento, difficilmente possiede i requisiti tecnici e le partnership necessarie per candidarsi come capofila o partner rilevante.</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su innovazioni disruptive per la sicurezza civile richiede capacità di ricerca avanzata, consorzi internazionali e investimenti elevati, rendendolo difficilmente accessibile per una PMI del Cilento senza partnership con università o centri di ricerca. Le PMI di piccola dimensione raramente hanno i requisiti tecnici e amministrativi per competere su bandi Horizon di questa natura, pensati per grandi player tecnologici o spin-off ad alta intensità R&amp;D.</t>
+          <t>Il bando Horizon focalizzato su innovazioni tecnologiche dirompenti per la sicurezza civile richiede capacità di ricerca avanzata, consorzi internazionali e risorse progettuali tipicamente fuori portata per una PMI del Cilento senza esperienza pregressa in progetti europei R&amp;D. Una piccola impresa campana difficilmente può competire autonomamente in questo contesto altamente specializzato e competitivo, salvo partecipare come partner junior di un consorzio guidato da università o grandi aziende tech.</t>
         </is>
       </c>
     </row>
@@ -14663,12 +14663,12 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione in consorzi internazionali con forte componente di ricerca applicata su scenari climatici e preparazione civile, struttura poco compatibile con le capacità progettuali e amministrative di una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo come partner secondario di un consorzio guidato da università o enti di ricerca, con ruoli molto limitati e alta complessità burocratica.</t>
+          <t>Il bando Horizon richiede la partecipazione a consorzi internazionali di ricerca con elevate competenze tecnico-scientifiche in gestione delle crisi climatiche e sicurezza civile, contesti tipicamente appannaggio di università, centri di ricerca e grandi organizzazioni. Una PMI del Cilento difficilmente dispone delle strutture progettuali e dei partner necessari per competere in questo tipo di call.</t>
         </is>
       </c>
     </row>
@@ -14715,7 +14715,7 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede la partecipazione in consorzi internazionali con forte componente di ricerca applicata su resilienza e gestione dei disastri, richiedendo capacità progettuali e tecniche difficilmente accessibili a una PMI di piccola dimensione del Cilento senza un partner di ricerca strutturato. Il focus su scenari ibridi e infrastrutture critiche è lontano dalla tipologia produttiva prevalente nell'area.</t>
+          <t>Il bando Horizon europeo richiede la partecipazione in consorzi internazionali con elevata capacità di ricerca e sviluppo, rendendo l'accesso diretto molto difficile per una PMI campana di piccole dimensioni; il focus sulla resilienza delle infrastrutture critiche a disastri naturali potrebbe teoricamente coinvolgere aziende del Cilento (territorio sismico e idrogeologicamente fragile), ma solo come partner junior in progetti guidati da enti di ricerca o grandi organizzazioni.</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede consorzi internazionali con forte componente di ricerca e sviluppo tecnologico avanzato (strumenti per search and rescue in ambienti pericolosi), con budget e capacità progettuali difficilmente accessibili per una PMI campana di piccola dimensione operante nel Cilento. Solo PMI con specifiche competenze in robotica, sensori, tecnologie di emergenza e consolidata esperienza in progetti europei potrebbero ambire a partecipare come partner junior in un consorzio già strutturato.</t>
+          <t>Il bando Horizon europeo richiede consorzi internazionali con forte componente di ricerca e sviluppo tecnologico avanzato (strumenti e tecnologie per ricerca e soccorso in condizioni pericolose), strutture difficilmente accessibili per una PMI campana di piccole dimensioni senza partnership consolidate con centri di ricerca o grandi imprese. Il focus su disastri ed emergenze è poco allineato con il tessuto produttivo tipico del Cilento, orientato a turismo, agricoltura e servizi locali.</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sui rischi multi-hazard e impatti a cascata (alluvioni, frane, sismi) è orientato a consorzi di ricerca e università, richiedendo capacità progettuali e scientifiche difficilmente accessibili a una PMI campana di piccole dimensioni; il Cilento, pur essendo territorio ad alto rischio idrogeologico e sismico, non costituisce un vantaggio competitivo sufficiente a giustificare la partecipazione autonoma senza un partenariato strutturato con enti di ricerca.</t>
+          <t>Il bando Horizon sul rischio multi-hazard e impatti a cascata è orientato a consorzi di ricerca europei e grandi enti scientifici, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un ruolo da partner tecnico specializzato in gestione dei rischi naturali (alluvioni, frane, terremoti). Una PMI potrebbe partecipare solo come soggetto terzo in un consorzio già strutturato, con capacità R&amp;S documentate e competenze specifiche in monitoraggio ambientale o modellazione dei rischi.</t>
         </is>
       </c>
     </row>
@@ -14856,7 +14856,7 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda lo sviluppo di sistemi di comunicazione critica per la sicurezza civile a livello europeo, richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze specialistiche difficilmente accessibili a una PMI del Cilento. Le risorse finanziabili (R&amp;S su reti di comunicazione sicure) sono orientate a grandi player tecnologici e centri di ricerca, non a piccole imprese locali.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali di ricerca ad alto contenuto tecnologico nel settore delle comunicazioni critiche per la sicurezza civile, ambito dominato da grandi aziende tech e centri di ricerca specializzati. Una PMI del Cilento difficilmente dispone delle competenze in cybersecurity e infrastrutture di comunicazione avanzata richieste, né della capacità amministrativa per gestire progetti Horizon di questa complessità.</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata su infrastrutture critiche e stress test sistemici, ambiti tipicamente riservati a grandi consorzi, università e centri di ricerca specializzati. Una PMI del Cilento difficilmente possiede le competenze tecniche, la struttura amministrativa e i partner internazionali necessari per competere in questo tipo di progettualità europea.</t>
+          <t>Il bando Horizon richiede la partecipazione a consorzi europei con capacità di ricerca avanzata su infrastrutture critiche e stress test, competenze tipiche di grandi enti di ricerca o aziende tecnologiche specializzate, non accessibili a una PMI del Cilento senza un partner scientifico strutturato. Il tema — sicurezza e resilienza delle infrastrutture critiche — è lontano dal tessuto produttivo locale, prevalentemente orientato a turismo, agricoltura e artigianato.</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è rivolto a consorzi di ricerca e forze dell'ordine per sviluppare tecnologie e metodologie di contrasto alle sfide climatiche in ambito sicurezza pubblica: una PMI del Cilento difficilmente possiede i requisiti tecnici e la capacità progettuale per partecipare come capofila o partner qualificato. L'accesso richiederebbe una partnership strutturata con enti di ricerca o istituzioni pubbliche, rendendo il percorso complesso e poco realistico per una piccola impresa locale.</t>
+          <t>Il bando Horizon è rivolto principalmente a enti di ricerca, università e forze dell'ordine per sviluppare capacità investigative legate ai reati climatici, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un ruolo specifico in un consorzio di ricerca. Non sono finanziate attività produttive o commerciali tipiche delle PMI locali.</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulla sicurezza (demand-led innovation) è orientato a grandi consorzi di ricerca e soggetti istituzionali con capacità tecnologiche avanzate, rendendo l'accesso molto complesso per una PMI campana di piccole dimensioni, specialmente nel Cilento dove mancano ecosistemi R&amp;D strutturati. Le PMI potrebbero partecipare solo come partner junior in consorzi internazionali, con oneri amministrativi e progettuali sproporzionati rispetto alle loro dimensioni.</t>
+          <t>Il bando Horizon 'Demand-led innovation in security' è orientato a grandi consorzi di ricerca e industrie della difesa/sicurezza con elevate capacità tecnologiche e finanziarie, rendendo l'accesso estremamente difficile per una PMI del Cilento. I requisiti di partecipazione internazionale, i budget tipicamente milionari e la specializzazione in sicurezza avanzata lo rendono di fatto inaccessibile senza un ruolo marginale all'interno di un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la prevenzione del bioterrorismo tramite biologia sintetica, un ambito altamente specializzato che richiede competenze di ricerca avanzata e strutture di sicurezza difficilmente disponibili in una PMI del Cilento. Non sono previste attività finanziabili rilevanti per il tessuto produttivo locale (turismo, agricoltura, artigianato).</t>
+          <t>Il bando riguarda la prevenzione del bioterrorismo legato alla biologia sintetica, un ambito altamente specializzato che richiede competenze scientifiche avanzate e strutture di ricerca dedicate, del tutto estranee al tessuto produttivo di una PMI campana, specialmente nel Cilento dove prevalgono turismo, agricoltura e agroalimentare. Non esistono spese finanziabili né settori beneficiari rilevanti per realtà imprenditoriali di piccola-media dimensione in questo territorio.</t>
         </is>
       </c>
     </row>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda appalti pubblici pre-commerciali per soluzioni innovative nel settore della sicurezza, rivolti principalmente a grandi consorzi di ricerca e PA come acquirenti pubblici: una PMI del Cilento difficilmente ha le capacità tecnologiche e strutturali per partecipare come fornitore di soluzioni di sicurezza ad alto contenuto R&amp;S in ambito europeo. L'accesso diretto è ulteriormente limitato dalla complessità procedurale tipica dei bandi Horizon e dalla necessità di partnership internazionali consolidate.</t>
+          <t>Il bando riguarda appalti pubblici pre-commerciali per soluzioni innovative nel settore della sicurezza, strumento pensato per grandi enti pubblici e aziende strutturate con capacità di R&amp;S avanzata. Una PMI del Cilento difficilmente dispone delle competenze tecniche specializzate e della struttura organizzativa necessarie per competere in procurement di innovazione a livello europeo nel comparto sicurezza.</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione in consorzi internazionali con forte componente di ricerca applicata su sicurezza e transizione verde in aree urbane/periurbane, struttura che favorisce università e grandi enti di ricerca piuttosto che PMI del Cilento, territorio prevalentemente rurale e privo delle infrastrutture consortili necessarie. I costi di progettazione, gestione e rendicontazione Horizon sono inoltre sproporzionati rispetto alle capacità amministrative tipiche di una piccola impresa campana.</t>
+          <t>Il bando Horizon EU richiede la partecipazione in consorzi internazionali con forte componente di ricerca applicata su sicurezza e transizione verde in aree urbane/periurbane, struttura difficilmente accessibile per una PMI del Cilento senza un partner accademico o un grande integratore. Il territorio cilentano, prevalentemente rurale e a bassa densità urbana, non rientra nel focus geografico del bando.</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>Il programma I3 finanzia investimenti innovativi interregionali con logiche di cooperazione tra regioni europee, richiedendo partnership transnazionali e capacità progettuali elevate difficilmente compatibili con le dimensioni e le risorse di una PMI del Cilento. La complessità amministrativa e la scala richiesta rendono l'accesso diretto quasi impraticabile senza il supporto di enti aggregatori o cluster industriali.</t>
+          <t>Il bando I3 Strand 1 finanzia investimenti interregionali in innovazione con logica di cooperazione tra regioni europee, richiedendo partnership transnazionali complesse e capacità progettuali elevate che difficilmente una PMI del Cilento può sostenere autonomamente. Le risorse sono orientate a ecosistemi di innovazione su larga scala, rendendo l'accesso diretto per una piccola impresa molto improbabile senza il coinvolgimento di intermediari o cluster.</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>Il bando I3 Strand 2a è uno strumento interregionale europeo orientato a grandi progetti di innovazione transfrontaliera, con requisiti di partnership multi-regionale e capacità progettuali complesse che difficilmente una PMI del Cilento può soddisfare autonomamente. L'accesso realistico richiederebbe l'inserimento in reti di innovazione strutturate, rendendo la partecipazione diretta poco praticabile per realtà di piccola dimensione.</t>
+          <t>Il programma I3 finanzia investimenti interregionali in innovazione con logiche di rete tra regioni europee, strutture progettuali complesse e partnership istituzionali che rendono difficile l'accesso diretto a una PMI del Cilento senza il supporto di un soggetto capofila qualificato. Le PMI possono partecipare come partner, ma raramente come beneficiarie principali, e i requisiti di scala e coordinamento transnazionale sono penalizzanti per realtà di piccole dimensioni.</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>Il programma MSCA Doctoral Networks finanzia reti internazionali di dottorato tra università e centri di ricerca, con requisiti organizzativi e burocratici molto complessi che escludono di fatto le PMI di piccola dimensione come soggetti capofila. Una PMI del Cilento potrebbe partecipare solo come partner secondario in un consorzio già strutturato con enti accademici, ruolo difficile da costruire senza relazioni pregresse nel mondo della ricerca europea.</t>
+          <t>Le MSCA Doctoral Networks finanziano reti internazionali di dottorato coordinate da università e centri di ricerca, con requisiti organizzativi e amministrativi molto elevati: una PMI del Cilento può partecipare solo come partner secondario in un consorzio già strutturato, senza possibilità di candidarsi autonomamente né di ricevere finanziamenti diretti significativi.</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia reti dottorali in ambito AI per istituzioni accademiche e di ricerca, non per PMI: richiede la costituzione di consorzi universitari con capacità di supervisione dottorale, struttura del tutto estranea a una piccola impresa del Cilento. Una PMI potrebbe al massimo partecipare come partner associato, ma senza accesso diretto ai fondi.</t>
+          <t>Il bando RAISE finanzia reti dottorali europee per la ricerca sull'intelligenza artificiale in ambito scientifico, richiedendo la costituzione di consorzi accademici internazionali con università e centri di ricerca come soggetti capofila. Una PMI del Cilento difficilmente possiede la struttura organizzativa e le partnership accademiche necessarie per accedere direttamente, e il finanziamento copre borse di dottorato e attività di ricerca fondamentale, non investimenti aziendali concreti.</t>
         </is>
       </c>
     </row>
@@ -15373,7 +15373,7 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>Il programma EIC STEP Scale Up è rivolto a startup e scale-up tecnologiche ad alto potenziale già finanziate da EIC, con requisiti di accesso molto selettivi e soglie di fatturato/crescita difficilmente raggiungibili per una PMI tradizionale del Cilento. Una piccola impresa campana priva di precedenti finanziamenti EIC e di un profilo deeptech consolidato ha chances minime di accesso.</t>
+          <t>Il programma EIC STEP Scale Up è orientato a startup e PMI deeptech già finanziate da EIC e con ambizioni di crescita europea ad alto impatto tecnologico, requisiti difficilmente soddisfatti da una PMI tradizionale del Cilento. L'accesso richiede track record di innovazione radicale e capacità di scaling internazionale, caratteristiche distanti dal tessuto produttivo locale prevalentemente basato su turismo, agricoltura e artigianato.</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe riguarda la ricerca e l'innovazione nel contrasto al disagio abitativo grave e ai senza fissa dimora, con focus su infrastrutture sociali coordinate a livello urbano: si rivolge principalmente a enti di ricerca, università, municipalità e organizzazioni del terzo settore, rendendo l'accesso di una PMI del Cilento sostanzialmente impraticabile senza un consorzio strutturato. Una piccola impresa non avrebbe i requisiti tecnici né il profilo istituzionale richiesto per guidare o partecipare utilmente a questo tipo di progetto.</t>
+          <t>Il bando Horizon Europe riguarda la ricerca e l'innovazione sociale sul tema dei senzatetto e delle infrastrutture di welfare urbano, destinato principalmente a consorzi di enti di ricerca, università e organizzazioni non profit. Una PMI del Cilento non ha i requisiti tipici né il profilo operativo per partecipare a questo tipo di progetto europeo complesso.</t>
         </is>
       </c>
     </row>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi internazionali con forte componente di ricerca e sviluppo, capacità progettuali elevate e cofinanziamento significativo, barriere difficilmente superabili per una PMI del Cilento senza un partner universitario o un grande integratore. Il focus su soluzioni di comfort termico negli edifici potrebbe in teoria interessare imprese edili o di impiantistica, ma le condizioni di partecipazione Horizon rendono l'accesso diretto quasi impraticabile senza strutture dedicate alla ricerca.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca e sviluppo avanzate, consorzio internazionale e risorse amministrative difficilmente gestibili da una PMI del Cilento senza esperienza europea; il focus sul comfort termico negli edifici potrebbe in teoria interessare imprese edili o di efficienza energetica, ma le barriere di accesso (progettazione europea, rendicontazione complessa, cofinanziamento) lo rendono poco praticabile in autonomia.</t>
         </is>
       </c>
     </row>
@@ -15514,7 +15514,7 @@
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi internazionali di ricerca con elevata capacità progettuale e scientifica, risultando poco accessibile per una PMI del Cilento senza esperienza pregressa in progetti europei complessi. Il focus sulla progettazione spaziale dei quartieri urbani è inoltre poco rilevante per il tessuto produttivo rurale e turistico tipico del territorio cilentano.</t>
+          <t>Il bando Horizon si rivolge principalmente a consorzi di ricerca europei e università per progettare quartieri innovativi, richiedendo capacità progettuali e partenariati internazionali difficilmente accessibili a una PMI del Cilento. Una piccola impresa campana potrebbe partecipare solo come partner secondario in un consorzio guidato da enti di ricerca, senza reali opportunità di beneficio diretto.</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a progetti di ricerca e innovazione su scala europea per il riutilizzo di spazi vuoti o sottoutilizzati, richiedendo consorzi internazionali e capacità progettuali elevate difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe astrattamente candidarsi come partner in iniziative legate al recupero di borghi abbandonati o spazi rurali, ma la complessità amministrativa e i requisiti di Horizon la rendono di fatto poco praticabile senza il supporto di un ente di ricerca capofila.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, partenariati internazionali e strutture amministrative complesse, difficilmente accessibili a una PMI del Cilento senza un consorzio dedicato. Una PMI potrebbe partecipare solo come partner secondario in progetti guidati da università o enti di ricerca, con ruolo marginale e costi di gestione elevati.</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si focalizza sulla ricerca accademica e istituzionale per analizzare le dinamiche dei mercati di capitali a supporto di progetti New European Bauhaus in ambito urbano: non è uno strumento diretto di finanziamento per PMI, ma richiede consorzi di ricerca con competenze specialistiche in finanza e pianificazione urbana, difficilmente accessibili a una piccola impresa del Cilento.</t>
+          <t>Il bando Horizon finanzia ricerca accademica e istituzionale sulle dinamiche dei mercati di capitali per investimenti urbani legati al New European Bauhaus, un contesto lontano dalle esigenze operative di una PMI campana o cilentana. Non prevede finanziamenti diretti per attività produttive, né è pensato per imprese di piccola dimensione prive di struttura di ricerca dedicata.</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca e sviluppo avanzate, partnership internazionali e progettazione complessa che una PMI del Cilento difficilmente può sostenere autonomamente. Le soluzioni innovative per l'uso sostenibile degli spazi verticali (es. facciate verdi, urban farming verticale) potrebbero teoricamente interessare aziende edili o agricole locali, ma i requisiti tecnici e amministrativi di Horizon lo rendono accessibile principalmente a grandi consorzi o centri di ricerca.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca e sviluppo avanzate, partnership internazionali e strutture progettuali complesse, difficilmente accessibili per una PMI di piccola dimensione del Cilento senza un consorzio dedicato. Le soluzioni per l'utilizzo sostenibile degli spazi verticali (es. facciate verdi, architettura urbana) sono inoltre lontane dai settori produttivi tipici dell'area cilentana come agricoltura, turismo e artigianato.</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede consorzi internazionali di ricerca con elevata capacità progettuale e amministrativa, difficilmente accessibili per una PMI del Cilento senza un partner capofila accademico o industriale strutturato. Il focus su manutenzione sostenibile degli edifici esistenti potrebbe in teoria coinvolgere imprese edili o di costruzione, ma le barriere burocratiche e la competizione europea rendono la partecipazione diretta poco praticabile.</t>
+          <t>Il bando Horizon Europe richiede consorzi internazionali con forte componente di ricerca e sviluppo, budget elevati e capacità progettuali difficilmente accessibili per una PMI del Cilento in autonomia; il focus sulla manutenzione sostenibile degli edifici esistenti potrebbe coinvolgere imprese edili o energetiche solo come partner junior in un consorzio più ampio, ruolo complesso da ottenere senza reti europee consolidate.</t>
         </is>
       </c>
     </row>
@@ -15749,7 +15749,7 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulla ricerca accademica sull'esperienza degli abitanti nei quartieri urbani è orientato a consorzi di ricerca, università ed enti pubblici, rendendo l'accesso diretto per una PMI campana del Cilento estremamente difficile senza un ruolo marginale in un consorzio. Il territorio cilentano, prevalentemente rurale e turistico, non rientra nei contesti urbani tipicamente oggetto di questi studi.</t>
+          <t>Il bando Horizon focalizzato sulla ricerca accademica sull'esperienza degli abitanti nei quartieri urbani richiede capacità di ricerca scientifica, partnership con università e strutture consortili complesse, rendendo l'accesso praticamente impossibile per una PMI del Cilento senza un solido track record in progetti europei di ricerca. Il territorio cilentano, prevalentemente rurale, è lontano dal contesto urbano-metropolitano su cui si concentra il bando.</t>
         </is>
       </c>
     </row>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE si focalizza su soluzioni abitative per i senzatetto secondo i principi del New European Bauhaus, richiedendo consorzi di ricerca internazionali e competenze specialistiche difficilmente accessibili a una PMI del Cilento. Non finanzia attività produttive o commerciali tipiche delle piccole imprese campane, ma progetti di ricerca applicata con forte componente accademica e istituzionale.</t>
+          <t>Il bando Horizon europeo si focalizza sulla ricerca e innovazione per affrontare il problema dei senzatetto attraverso approcci abitativi allineati al New European Bauhaus, richiedendo consorzi di ricerca transnazionali e competenze altamente specializzate difficilmente accessibili a una PMI del Cilento. Una piccola impresa campana non ha i requisiti strutturali né il profilo scientifico necessari per candidarsi direttamente, e il tema non è direttamente collegato ai settori produttivi locali.</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>L'EIC Accelerator è rivolto a startup e PMI deep-tech con potenziale di scala globale e richiede innovazioni altamente disruptive con forte componente scientifica, criteri difficilmente soddisfatti da una PMI tradizionale del Cilento. Il processo selettivo è estremamente competitivo a livello europeo e richiede strutture dedicate alla gestione di progetti Horizon, rendendo l'accesso concreto molto impegnativo senza un ecosistema di supporto specializzato.</t>
+          <t>L'EIC Accelerator è rivolto a startup e PMI con innovazioni deep-tech ad alto potenziale di scala globale, con finanziamenti fino a 2,5M€ in grant e 15M€ in equity: il livello di competitività europeo e i requisiti tecnico-scientifici richiesti lo rendono difficilmente accessibile per una PMI tradizionale del Cilento, salvo realtà con brevetti o tecnologie dirompenti già validate sul mercato.</t>
         </is>
       </c>
     </row>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>Il bando richiede competenze altamente specializzate in fisica quantistica e navigazione inerziale, tipiche di grandi consorzi di ricerca o aziende deep-tech con laboratori avanzati: una PMI del Cilento o della Campania, salvo rarissime eccezioni nel settore aerospaziale o della strumentazione scientifica, non dispone delle capacità tecniche né delle infrastrutture necessarie per partecipare competitivamente. Il profilo dei beneficiari attesi esclude di fatto le piccole imprese generaliste.</t>
+          <t>Il bando finanzia ricerca avanzata su sensori quantistici per la navigazione inerziale, un settore ad altissima specializzazione tecnologica (difesa, aerospazio, fisica quantistica) accessibile quasi esclusivamente a grandi aziende, università e centri di ricerca. Una PMI del Cilento, anche tecnologicamente orientata, difficilmente possiede le competenze e le infrastrutture richieste per partecipare competitivamente a una Grand Challenge di questo livello.</t>
         </is>
       </c>
     </row>
@@ -15937,7 +15937,7 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>Il programma Horizon UE sul Quantum Machine Learning richiede capacità di ricerca avanzata, partnership internazionali e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. Le call Horizon sono strutturalmente orientate a consorzi di grandi enti di ricerca e università, rendendo l'accesso diretto per una piccola impresa campana estremamente complesso senza un ruolo marginale di partner industriale.</t>
+          <t>Il bando Horizon focalizzato su Quantum Machine Learning richiede capacità di ricerca avanzata, partnership internazionali e competenze altamente specializzate che difficilmente una PMI del Cilento possiede autonomamente. L'accesso è realistico solo come partner junior in consorzi europei guidati da università o grandi centri di ricerca, rendendo il percorso estremamente complesso per realtà locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>I Framework Loans BEI/JTM sono strumenti finanziari strutturati destinati tipicamente a intermediari bancari o grandi progetti infrastrutturali nelle regioni in transizione, non direttamente accessibili da una PMI individuale senza passare da banche convenzionate. Per una piccola impresa del Cilento, l'accesso è indiretto e complesso, rendendo più conveniente rivolgersi a strumenti regionali dedicati alle PMI campane.</t>
+          <t>I Framework Loans BEI/JTF sono strumenti finanziari destinati a intermediari bancari o grandi enti pubblici per aggregare progetti in aree di transizione, non accessibili direttamente da una PMI del Cilento senza passare da bandi attuativi regionali dedicati. Una piccola impresa campana dovrebbe monitorare i successivi avvisi operativi che Regione Campania o istituti finanziari convenzionati potrebbero attivare a valle di questo framework.</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>I bandi 'Standalone Projects' del Just Transition Mechanism UE sono tipicamente rivolti a grandi progetti infrastrutturali o industriali in territori specifici di transizione energetica, e la Campania (incluso il Cilento) non rientra tra le aree JTM prioritarie italiane (che sono Sulcis, Taranto e altri). L'accesso diretto per una PMI locale è estremamente complesso data la scala e la struttura burocratica richiesta.</t>
+          <t>I bandi 'Standalone Projects' del Just Transition Mechanism UE sono tipicamente destinati a grandi investimenti infrastrutturali o progetti complessi in territori di transizione energetica, con requisiti tecnici e finanziari difficilmente sostenibili da una PMI del Cilento senza partnership strutturate. Inoltre, la Campania non rientra tra le aree prioritarie JTM italiane (concentrate su Sulcis, Taranto e Trieste), riducendo ulteriormente le possibilità di accesso diretto.</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi di difesa missilistica è destinato a grandi consorzi industriali del settore difesa con capacità tecnologiche e finanziarie molto elevate, escludendo di fatto le PMI del Cilento o della Campania prive di expertise specifico in sistemi d'arma. Non sono previste spese finanziabili compatibili con le attività tipiche di una piccola o media impresa locale.</t>
+          <t>Il bando EDF sui sistemi di difesa aerea e missilistica è destinato a grandi contractor della difesa e consorzi industriali con capacità tecnologiche e certificazioni militari specifiche, del tutto fuori dalla portata di una PMI del Cilento o della Campania in generale. Le spese finanziabili riguardano R&amp;S avanzata in ambito difesa, settore altamente regolamentato e inaccessibile per realtà di piccola-media dimensione senza esperienza pregressa nel comparto militare.</t>
         </is>
       </c>
     </row>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa su sistemi C5ISR (Command, Control, Communications, Computers, Cyber, Intelligence, Surveillance and Reconnaissance) e tecnologie spaziali correlate, ambiti che richiedono capacità industriali e tecnologiche altamente specializzate, certificazioni militari e partnership con grandi prime contractor della difesa. Una PMI del Cilento difficilmente possiede i requisiti tecnici, i consorzi necessari e le abilitazioni di sicurezza richieste per accedere concretamente a questi fondi.</t>
+          <t>Il bando EDF sui sistemi C5ISR (Command, Control, Communications, Computers, Combat Systems, Intelligence, Surveillance and Reconnaissance) è orientato a grandi contractor della difesa e aerospazio, con requisiti tecnici, di sicurezza e consorziali che rendono l'accesso estremamente difficile per una PMI del Cilento priva di certificazioni NATO/difesa e di partnership consolidate con prime contractor europei.</t>
         </is>
       </c>
     </row>
@@ -16167,12 +16167,12 @@
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per piattaforme terrestri e navali richiede capacità industriali di difesa di scala significativa, consorzî internazionali e requisiti di sicurezza NATO/UE difficilmente accessibili a una PMI del Cilento priva di precedenti nel settore difesa. L'unica via di accesso realistica sarebbe come subfornitori specializzati all'interno di un consorzio guidato da prime contractor, scenario improbabile senza reti consolidate nel comparto.</t>
+          <t>Il bando EDF su piattaforme terrestri e navali finanzia ricerca e sviluppo nel settore della difesa con requisiti consortili complessi e capacità tecnologiche avanzate, difficilmente accessibili a una PMI del Cilento priva di specializzazione in difesa/aerospazio. I costi di partecipazione e le competenze richieste rendono questo bando adatto a grandi contractor della difesa, non a piccole imprese locali.</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi unmanned e counter-unmanned è orientato a grandi consorzi industriali della difesa con capacità di R&amp;S avanzata: richiede competenze tecnologiche militari, partnership transnazionali e investimenti ingenti, fuori dalla portata di una PMI campana del Cilento priva di profilo aerospaziale-difesa. Una piccola impresa locale difficilmente soddisfa i requisiti minimi di partecipazione senza essere integrata in supply chain di grandi prime contractor.</t>
+          <t>Il bando EDF sui sistemi unmanned e counter-unmanned è orientato a grandi industrie della difesa e consorzi di ricerca ad alta tecnologia militare, con requisiti tecnici, finanziari e di sicurezza (es. nulla osta NATO/UE) del tutto incompatibili con le capacità operative di una PMI del Cilento o della Campania in generale. L'accesso è di fatto riservato a player industriali del settore difesa con consolidata esperienza in sistemi aeronautici autonomi e tecnologie di guerra elettronica.</t>
         </is>
       </c>
     </row>
@@ -16261,12 +16261,12 @@
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) sui componenti elettronici chiave è destinato a consorzi di grandi aziende e centri di ricerca del settore difesa, con requisiti tecnici e finanziari molto elevati difficilmente compatibili con una PMI del Cilento. L'ambito militare/dual-use e la complessità progettuale richiesta rendono di fatto inaccessibile questo finanziamento per realtà produttive di piccola dimensione.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia la ricerca e sviluppo di componenti elettronici chiave per la difesa europea, richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze in ambito militare/duale che sono fuori dalla portata di una PMI tipica del Cilento o della Campania senza una specializzazione specifica nel settore difesa. Le PMI possono partecipare solo come partner junior in consorzi guidati da grandi prime contractor della difesa, rendendo l'accesso diretto estremamente difficile.</t>
         </is>
       </c>
     </row>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia lo sviluppo di piattaforme e prodotti finali per la difesa europea, richiedendo consorzi transnazionali con capacità industriali e tecnologiche avanzate del settore difesa: una PMI del Cilento difficilmente dispone delle certificazioni, delle competenze specifiche e della rete di partner internazionali necessarie per partecipare competitivamente. I requisiti minimi di accesso e i budget tipici dell'EDF sono strutturati per grandi prime contractor o PMI altamente specializzate nel comparto aerospaziale/difesa, settori praticamente assenti nel tessuto produttivo cilentano.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia lo sviluppo di piattaforme e prodotti finali nel settore della difesa, richiedendo consorzi transnazionali con capacità industriali e tecnologiche avanzate del comparto militare. Una PMI del Cilento difficilmente possiede i requisiti tecnici, le certificazioni di sicurezza e le partnership nel settore difesa necessari per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
@@ -16360,7 +16360,7 @@
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Strategic Nature Projects è orientato a grandi interventi sistemici di conservazione della natura su scala nazionale o macroregionale, con budget elevati e strutture di governance complesse che richiedono tipicamente enti pubblici o grandi organizzazioni come capofila. Una PMI del Cilento difficilmente può accedere direttamente, al massimo come partner tecnico in un consorzio più ampio.</t>
+          <t>Il programma LIFE Strategic Nature Projects è rivolto principalmente a enti pubblici, autorità nazionali e grandi organizzazioni ambientali per interventi su scala strategica nella conservazione della natura e della biodiversità; una PMI del Cilento difficilmente può candidarsi direttamente, potendo al massimo partecipare come partner di progetto in ruolo marginale.</t>
         </is>
       </c>
     </row>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>I progetti strategici integrati LIFE sono strumenti complessi pensati per enti pubblici, autorità regionali e grandi organizzazioni ambientali, con budget multimilionari e requisiti di partenariato transnazionale difficilmente gestibili da una PMI. Una piccola impresa del Cilento potrebbe al massimo partecipare come soggetto associato, ma non come beneficiario principale.</t>
+          <t>I progetti LIFE Strategic Integrated Projects sono strumenti complessi pensati per interventi sistemici su scala nazionale o macroregionale, gestiti tipicamente da autorità pubbliche o grandi enti. Una PMI del Cilento difficilmente può candidarsi come lead partner, e i requisiti di co-finanziamento e governance rendono l'accesso diretto praticamente impraticabile senza essere inserita in una grande partnership istituzionale.</t>
         </is>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>I progetti LIFE Strategic Integrated Projects sono strumenti complessi destinati a soggetti istituzionali (autorità regionali, enti pubblici, agenzie ambientali) per attuare piani ambientali su scala territoriale ampia; una PMI del Cilento non ha i requisiti strutturali né la capacità amministrativa per candidarsi come lead partner, potendo al massimo partecipare come soggetto associato in un consorzio già formato.</t>
+          <t>I progetti LIFE Strategic Integrated Projects sono strumenti complessi destinati principalmente a enti pubblici, autorità regionali e grandi organizzazioni ambientali, con budget multimilionari e requisiti di partenariato transnazionale difficilmente accessibili a una PMI. Una piccola impresa del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio, ma difficilmente come beneficiario diretto.</t>
         </is>
       </c>
     </row>
@@ -17787,7 +17787,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27/06/2026 08:19</t>
+          <t>28/06/2026 08:49</t>
         </is>
       </c>
     </row>

--- a/bandi_campania.xlsx
+++ b/bandi_campania.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I380"/>
+  <dimension ref="A1:I377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia modelli di economia sociale applicati al turismo sostenibile e ai percorsi a lunga distanza, settore in cui il Cilento eccelle con il Sentiero degli Dei e i cammini del Parco Nazionale: una PMI turistica locale (agriturismo, guida escursionistica, cooperativa di servizi) può accedere a fondi per sviluppare prodotti turistici integrati e reti territoriali. Le spese finanziabili includono tipicamente progettazione di itinerari, digitalizzazione dell'offerta turistica e azioni di promozione, rendendo il bando concretamente sfruttabile anche da operatori di piccola dimensione.</t>
+          <t>Il bando finanzia modelli di economia sociale applicati al turismo sostenibile su percorsi a lunga distanza, ambito in cui il Cilento — con il suo sistema di sentieri, cammini e borghi — rappresenta un territorio ideale. Una PMI locale attiva in hospitality, guide turistiche o servizi outdoor può accedere a fondi per sviluppare prodotti turistici innovativi e inclusivi lungo tracciati come il Sentiero degli Dei o i percorsi del Parco Nazionale del Cilento.</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Il bando GreenTour di Invitalia sostiene investimenti nel turismo sostenibile, settore strategico per il Cilento con il suo Parco Nazionale e la costa: una PMI locale può finanziare interventi come riqualificazione strutture ricettive, mobilità green e servizi eco-turistici. La gestione Invitalia garantisce procedure standardizzate accessibili anche a imprese di piccola dimensione.</t>
+          <t>GreenTour di Invitalia finanzia progetti di turismo sostenibile, categoria in cui il Cilento — con il suo Parco Nazionale e la vocazione naturalistico-culturale — rappresenta un territorio ideale per PMI del settore ricettivo, escursionistico e dell'ospitalità. Le spese tipicamente ammissibili includono investimenti in strutture eco-compatibili, servizi turistici innovativi e promozione territoriale verde, rendendolo concretamente accessibile anche a imprese di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Il Fondo di partecipazione MUR gestito da Invitalia eroga capitale di rischio (equity o quasi-equity) a favore di spin-off universitari e imprese innovative ad alta intensità di ricerca, quindi è accessibile soprattutto a PMI con componente R&amp;S strutturata o nate da enti di ricerca; una PMI del Cilento può candidarsi se opera in settori a vocazione innovativa (agroalimentare tecnologico, blue economy, turismo digitale), ma la natura dello strumento finanziario — partecipazione al capitale, non contributo a fondo perduto — richiede solidità gestionale e disponibilità a cedere quote societarie.</t>
+          <t>Il Fondo di partecipazione MUR gestito da Invitalia supporta progetti di ricerca e innovazione attraverso strumenti finanziari agevolati (equity, quasi-equity o prestiti), potenzialmente accessibili anche a PMI campane con vocazione tecnologica o di ricerca applicata. Tuttavia, la complessità dello strumento e la necessità di coinvolgimento con il sistema universitario/ricerca rendono l'accesso più difficile per le PMI di piccola dimensione del Cilento, spesso operanti in settori tradizionali come turismo e agricoltura.</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia la redazione di Piani di Gestione Forestale, strumento obbligatorio per accedere a molti incentivi agro-forestali europei: una PMI del Cilento con superfici boschive o attività di gestione forestale può coprire i costi di progettazione tecnica altrimenti elevati. La pertinenza è media perché il beneficio è indiretto e limitato alle imprese con patrimonio boschive da valorizzare, escludendo settori produttivi non forestali.</t>
+          <t>Il bando finanzia la redazione di Piani di Gestione Forestale, strumento obbligatorio per accedere a molti incentivi forestali e agroforestali, ed è particolarmente rilevante per PMI del Cilento con superfici boschive o attività legate alla gestione del territorio montano e collinare. La pertinenza è media perché si tratta di un contributo tecnico-pianificatorio, utile come leva per futuri finanziamenti ma non immediatamente operativo per imprese non direttamente coinvolte nella silvicoltura.</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Il bando 'Vita &amp; Opportunità' di Invitalia supporta iniziative legate all'inclusione sociale e all'imprenditoria, potenzialmente accessibile a PMI del Cilento che operano in ambiti sociali o culturali, ma la natura generalista del titolo e l'assenza di dettagli specifici sulle spese finanziabili rendono difficile valutarne l'applicabilità concreta senza consultare il testo integrale del bando.</t>
+          <t>Il bando Vita &amp; Opportunità di Invitalia supporta progetti a valenza sociale e territoriale, potenzialmente accessibili a PMI del Cilento attive in settori come welfare, servizi alla persona o sviluppo locale, ma la natura del programma richiede verifica puntuale dei requisiti soggettivi e delle spese ammissibili prima di candidarsi.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Il meccanismo finanzia tecnologie specifiche per le energie rinnovabili, potenzialmente accessibile a PMI del Cilento che operano nel settore energetico o che intendono installare impianti fotovoltaici, eolici o da biogas per autoconsumo o vendita. La complessità procedurale tipica dei bandi UE diretti può richiedere supporto specialistico, ma il territorio del Cilento, con vocazione rurale e turistica, si presta bene a progetti di comunità energetiche o agrivoltaico.</t>
+          <t>Il meccanismo finanzia tecnologie specifiche per energie rinnovabili, potenzialmente accessibile a PMI del Cilento che intendono investire in impianti fotovoltaici, eolici o bioenergia, settori coerenti con la vocazione rurale e turistica del territorio. La pertinenza è media perché i bandi UE di questo tipo richiedono spesso capacità progettuali e finanziarie elevate, rendendo necessario l'affiancamento di consulenti o aggregazioni tra imprese.</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Il bando ESF sostiene l'accesso a servizi di incubazione e finanza inclusiva per nuovi imprenditori e microimprese, potenzialmente utile per PMI del Cilento che vogliono avviare o consolidare attività in aree svantaggiate. Tuttavia, essendo un bando europeo diretto, richiede capacità di progettazione complessa e spesso si rivolge a enti intermediari piuttosto che a singole PMI come beneficiarie dirette.</t>
+          <t>Il bando ESF sostiene l'inclusione finanziaria e i servizi di incubazione per nuovi imprenditori, potenzialmente utile per PMI del Cilento che vogliono accedere a strumenti di finanza alternativa o percorsi di mentoring/accelerazione. Tuttavia, il focus su 'nuovi imprenditori' e la natura europea del programma richiedono verifica della catena attuativa regionale prima di candidarsi direttamente.</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca e sviluppo su prodotti bio-based derivati da organismi marini, settore potenzialmente interessante per PMI del Cilento attive nella pesca, acquacoltura o trasformazione ittica che vogliano valorizzare scarti o biomasse marine. Tuttavia, la complessità dei bandi Horizon e la necessità di partnership internazionali rendono l'accesso difficile per PMI di piccola dimensione senza esperienza in progetti europei.</t>
+          <t>Il bando Horizon UE finanzia ricerca e sviluppo su prodotti bio-based derivati da organismi marini, settore rilevante per PMI del Cilento attive nella pesca, acquacoltura o biotecnologie marine, ma richiede partnership con enti di ricerca e capacità progettuali europee che possono risultare ostative per piccole imprese. Una PMI potrebbe partecipare come partner industriale in un consorzio, coprendo spese di R&amp;S, prototipazione e valorizzazione commerciale dei risultati.</t>
         </is>
       </c>
     </row>
@@ -943,14 +943,14 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e innovazione per filiere agroalimentari sostenibili, bioeconomia e biodiversità, settori in cui le PMI del Cilento (produzione olivicola, zootecnia, pesca, agriturismi) potrebbero partecipare come partner industriali in consorzi con università o enti di ricerca. La complessità progettuale e la necessità di aggregarsi in partenariati europei rende l'accesso indiretto ma praticabile per PMI già strutturate o associate a consorzi di filiera.</t>
+          <t>Il bando finanzia progetti di ricerca e innovazione su filiere alimentari sostenibili, bioeconomia e biodiversità, temi direttamente applicabili alle produzioni tipiche del Cilento (olio DOP, mozzarella, legumi tradizionali). Tuttavia, Horizon richiede partecipazione in consorzio transnazionale e capacità di ricerca strutturata, il che rende l'accesso diretto complesso per una PMI senza un partner universitario o un centro di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Bio-based innovation in society: supporting the sustainable way of living</t>
+          <t>Boosting agrobiodiversity for food security and sustainable competitiveness</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-10</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -985,19 +985,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti di ricerca e innovazione legati all'economia bio-based e agli stili di vita sostenibili, settori rilevanti per PMI del Cilento attive in agricoltura biologica, agroalimentare o turismo eco-sostenibile. Tuttavia, trattandosi di un bando Horizon UE, richiede la partecipazione in consorzi internazionali e capacità di gestione progettuale complessa, il che limita l'accesso diretto per le PMI più piccole senza un partner capofila.</t>
+          <t>Il bando finanzia progetti di ricerca e innovazione sulla biodiversità agricola per la sicurezza alimentare, settore particolarmente rilevante per il Cilento ricco di produzioni tipiche locali (fico bianco, carciofo di Paestum, fagioli antichi). Tuttavia, Horizon richiede partnership internazionali e capacità progettuali elevate, rendendo l'accesso diretto complesso per una PMI senza il supporto di un ente di ricerca o consorzio.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Boosting agrobiodiversity for food security and sustainable competitiveness</t>
+          <t>Developing managed aquifer recharge techniques (MAR) in a rural context</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-03</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1037,29 +1037,29 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti di ricerca e innovazione per la valorizzazione dell'agrobiodiversità locale a fini di sicurezza alimentare e competitività sostenibile, aree in cui il Cilento — con i suoi prodotti tipici e paesaggi agrari tradizionali — ha un potenziale elevato. Tuttavia, il programma Horizon richiede generalmente la partecipazione a consorzi internazionali e capacità progettuali strutturate, il che rende l'accesso diretto per una PMI agricola di piccole dimensioni complesso senza il supporto di un ente di ricerca o un aggregatore.</t>
+          <t>Il bando finanzia lo sviluppo di tecniche di ricarica artificiale delle falde acquifere (MAR) in contesti rurali, direttamente applicabile alle aziende agricole del Cilento che affrontano stress idrico stagionale. Una PMI agricola o una cooperativa del territorio può partecipare come partner in un consorzio europeo, accedendo a finanziamenti per sperimentazione, infrastrutture idriche e innovazione nella gestione delle risorse idriche.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Developing managed aquifer recharge techniques (MAR) in a rural context</t>
+          <t>SSbD bio-based alternatives for fertilising and/or crop protection products</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1084,29 +1084,29 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia lo sviluppo di tecniche di ricarica artificiale delle falde acquifere in contesti rurali, direttamente applicabile alle PMI agricole del Cilento che soffrono di stress idrico stagionale. Tuttavia, la complessità dei bandi Horizon e la necessità di partnership europee rendono l'accesso difficile per una piccola impresa senza il supporto di un ente di ricerca.</t>
+          <t>Il bando finanzia ricerca e sviluppo di fertilizzanti e prodotti fitosanitari bio-based secondo i principi SSbD (Safe and Sustainable by Design), un'opportunità concreta per PMI agricole o agrochimiche del Cilento che operano in filiere biologiche o vogliono sviluppare soluzioni sostenibili per colture tipiche locali. La complessità della rendicontazione Horizon e la necessità di partecipare in consorzio europeo rendono l'accesso impegnativo per una PMI di piccola dimensione senza un partner di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Bio-based chemicals and/or materials from woody residues</t>
+          <t>Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1126,34 +1126,34 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Internazionalizzazione</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia ricerca e sviluppo su materiali e sostanze chimiche bio-based derivati da residui legnosi, settore rilevante per PMI del Cilento attive nella filiera del legno, olivicoltura o gestione forestale con capacità di R&amp;S. La complessità tipica di Horizon e la necessità di consorziarsi con enti di ricerca europei rendono l'accesso impegnativo per una PMI di piccole dimensioni senza esperienza progettuale europea.</t>
+          <t>Il bando Horizon finanzia partnership internazionali nel settore culturale e delle industrie creative (CCI), ambiti rilevanti per PMI del Cilento attive in turismo culturale, artigianato o produzioni creative locali. Tuttavia, la complessità dei bandi Horizon e il requisito di consorzio transnazionale rendono l'accesso difficoltoso per una piccola impresa senza un partner capofila o un intermediario esperto.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SSbD bio-based alternatives for fertilising and/or crop protection products</t>
+          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1173,19 +1173,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia ricerca e sviluppo di alternative bio-based per fertilizzanti e prodotti fitosanitari secondo i principi SSbD (Safe and Sustainable by Design), settore rilevante per le PMI agricole e agrochimiche del Cilento, area vocata alla coltivazione di produzioni DOP/IGP. La pertinenza è media perché i bandi Horizon richiedono tipicamente partnership con enti di ricerca e una capacità progettuale elevata, spesso difficile da sostenere autonomamente per una piccola PMI senza supporto specializzato.</t>
+          <t>Il bando Horizon finanzia progetti di ricerca e co-gestione delle risorse marine e delle acque dolci, con focus sulla pesca sostenibile: una PMI ittica del Cilento (area con forte tradizione nella pesca artigianale e nel mare protetto del Parco Nazionale) può partecipare come partner in un consorzio, contribuendo con competenze pratiche di settore e accedendo a finanziamenti per innovazione gestionale e ambientale. La complessità progettuale tipica di Horizon e la necessità di formare un consorzio europeo riducono però l'accessibilità diretta per una piccola impresa senza supporto specialistico.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
+          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-05</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1220,19 +1220,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Internazionalizzazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia partnership internazionali nel settore culturale e delle industrie creative (CCI), ambito rilevante per PMI del Cilento attive in artigianato, produzioni culturali locali o turismo creativo. Tuttavia, la complessità dei progetti Horizon e la necessità di costruire consorzi europei rendono l'accesso difficile per PMI di piccola dimensione senza esperienza pregressa in progetti UE.</t>
+          <t>Il bando Horizon finanzia progetti dimostrativi per proteggere il patrimonio culturale dagli impatti del cambiamento climatico, settore rilevante per il Cilento con i suoi siti UNESCO e aree costiere vulnerabili. Una PMI specializzata in tecnologie di monitoraggio, restauro o diagnostica ambientale può partecipare come partner in un consorzio europeo, ma l'accesso diretto come capofila è complesso per una piccola impresa data la natura competitiva e consortile di Horizon Europe.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
+          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-06-CLIMA-SOIL</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1267,39 +1267,39 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti di co-gestione partecipativa delle risorse marine e delle acque interne, coinvolgendo direttamente i pescatori: una PMI del Cilento operante nella pesca artigianale o nell'acquacoltura può partecipare come partner in consorzi europei, con spese ammissibili per ricerca, attività pilota e trasferimento di pratiche sostenibili. La pertinenza è media perché Horizon richiede tipicamente la formazione di consorzi internazionali e una capacità progettuale strutturata, non sempre alla portata di piccole imprese senza supporto di un ente di ricerca.</t>
+          <t>Il bando finanzia progetti dimostrativi su tecnologie e pratiche per aumentare la resilienza del suolo agli eventi climatici estremi e garantire la sicurezza alimentare, ambiti direttamente rilevanti per PMI agricole del Cilento (olivicoltura, orticoltura, cerealicoltura) esposte a siccità e alluvioni. La complessità dei bandi Horizon e la necessità di consorziarsi con partner europei riducono l'accessibilità diretta per una piccola impresa, che dovrebbe partecipare come partner operativo all'interno di un consorzio coordinato da enti di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
+          <t>EU support to Stakeholders to improve measurement of food waste and help implement food waste prevention in their operations and organisation - 2026-2027</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SMP-FOOD-2026-FW-STAKEHOLDERS-PJ</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - SMP</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia soluzioni tecnologiche e metodologie per proteggere il patrimonio culturale dagli effetti del cambiamento climatico, settore rilevante per il Cilento ricco di siti UNESCO e borghi storici. Una PMI campana attiva in ambito ICT, ingegneria del restauro o sensoristica ambientale può partecipare come partner di un consorzio europeo, coprendo spese di R&amp;S, personale e attrezzature, ma la complessità gestionale di Horizon rende l'accesso diretto difficile senza un coordinatore di progetto esperto.</t>
+          <t>Il bando supporta operatori della filiera alimentare — incluse PMI della ristorazione, trasformazione e distribuzione tipiche del territorio cilentano — nell'adottare sistemi di misurazione e prevenzione degli sprechi alimentari, con attività di formazione e implementazione organizzativa finanziabili. La pertinenza è media perché si tratta di un bando UE con procedure complesse e requisiti di rendicontazione impegnativi per strutture di piccole dimensioni.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EU support to Stakeholders to improve measurement of food waste and help implement food waste prevention in their operations and organisation - 2026-2027</t>
+          <t>Fondo di contrasto alla deindustrializzazione 2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>30 ottobre 2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SMP-FOOD-2026-FW-STAKEHOLDERS-PJ</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/fondo-di-contrasto-alla-deindustrializzazione-2026</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>UE - SMP</t>
+          <t>Invitalia</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1361,39 +1361,39 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia azioni di misurazione e prevenzione degli sprechi alimentari rivolte a stakeholder della filiera food, il che lo rende rilevante per PMI campane attive nella trasformazione, distribuzione o ristorazione agroalimentare – settori presenti nel Cilento. Tuttavia, essendo un bando UE diretto (SMP), richiede capacità progettuale europea e spesso favorisce consorzi o organizzazioni di rappresentanza piuttosto che singole PMI, riducendone l'accessibilità diretta.</t>
+          <t>Il fondo è pensato per contrastare la perdita di capacità produttiva industriale, quindi può interessare PMI manifatturiere o artigianali del Cilento che rischiano di ridurre o chiudere attività, finanziando potenzialmente investimenti in macchinari, riconversione produttiva o mantenimento dei livelli occupazionali. La pertinenza è media perché il Cilento ha una base industriale limitata e il bando Invitalia tende a privilegiare aree a maggiore concentrazione industriale o crisi conclamata.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Fondo di contrasto alla deindustrializzazione 2026</t>
+          <t>Open topic on driving innovation uptake of disaster risk solutions</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>30 ottobre 2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/fondo-di-contrasto-alla-deindustrializzazione-2026</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-04</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Invitalia</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1408,19 +1408,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Il fondo è pensato per contrastare la perdita di capacità produttiva industriale, quindi è rilevante per PMI manifatturiere o di trasformazione presenti nel Cilento che rischiano ridimensionamenti occupazionali o chiusure; tuttavia, l'area cilentana ha una vocazione prevalentemente turistica e agricola, rendendo la platea dei beneficiari locali limitata rispetto ad aree più industrializzate della Campania.</t>
+          <t>Il bando finanzia soluzioni innovative per la gestione del rischio da disastri naturali (alluvioni, frane, terremoti), tematiche particolarmente rilevanti per il territorio del Cilento. Una PMI attiva in settori come protezione civile, monitoraggio ambientale, edilizia sismica o tecnologie di early warning può partecipare, preferibilmente in consorzio con enti di ricerca, coprendo costi di R&amp;S, sviluppo tecnologico e dimostrazione sul campo.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Open topic on driving innovation uptake of disaster risk solutions</t>
+          <t>Accessible and available travel facilitation</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1455,39 +1455,39 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia soluzioni innovative per la gestione del rischio da catastrofi naturali (alluvioni, frane, terremoti), settore rilevante per il Cilento dato il suo territorio fragile e ad alto rischio idrogeologico. Una PMI attiva in tecnologie ambientali, monitoraggio del territorio o protezione civile può partecipare, idealmente in consorzio con enti di ricerca, coprendo attività di R&amp;S e sviluppo di prototipi.</t>
+          <t>Il bando Horizon finanzia soluzioni innovative per rendere i viaggi più accessibili e inclusivi, settore rilevante per una PMI turistica del Cilento dato l'alto potenziale di turismo lento e accessibile nell'area. Tuttavia, i bandi Horizon richiedono tipicamente consorzi transnazionali e capacità di ricerca, rendendo l'accesso diretto complesso per una PMI di piccola dimensione senza partnership con università o enti di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Accessible and available travel facilitation</t>
+          <t>Standalone projects</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>16/02/2027</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/JTM-2026-PSLF-STANDALONE-PROJECTS</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - JTM</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1502,39 +1502,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca e innovazione per rendere i viaggi più accessibili e inclusivi, ambito direttamente rilevante per PMI turistiche del Cilento che vogliono sviluppare soluzioni o servizi per il turismo accessibile. Tuttavia, i bandi Horizon richiedono tipicamente consorzi transnazionali e capacità di ricerca, il che rende l'accesso complesso per una PMI di piccola dimensione senza partner istituzionali.</t>
+          <t>Il fondo JTM (Just Transition Mechanism) finanzia progetti standalone per la transizione verde e industriale nelle aree in transizione, potenzialmente accessibili a PMI campane in settori manifatturieri o energetici; tuttavia la complessità burocratica europea e la necessità di rispettare requisiti territoriali specifici (zone JTM designate) rendono l'accesso più difficile per micro e piccole imprese del Cilento senza supporto specializzato.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>I3-2026-INV2a - Interregional Innovation Investments Strand 2a</t>
+          <t>Networks of European Cinemas</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>12/11/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/I3-2026-INV2a</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-CINNET</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>UE - I3</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1544,39 +1544,39 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Bassa</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Il bando I3 Strand 2a finanzia investimenti interregionali in innovazione, potenzialmente accessibili a PMI campane che collaborano con partner di altre regioni UE su progetti di R&amp;S e trasferimento tecnologico. Per una PMI del Cilento, la pertinenza dipende dalla capacità di costruire reti interregionali e dalla disponibilità di co-finanziamento, barriere non trascurabili per realtà di piccola dimensione.</t>
+          <t>Il bando finanzia reti di sale cinematografiche europee nell'ambito del programma CREA2027, rivolto a operatori del settore audiovisivo e cinematografico organizzati in network transnazionali: una PMI generica del Cilento difficilmente possiede i requisiti strutturali e settoriali per partecipare, salvo gestisca direttamente una sala cinema e abbia già partnership europee consolidate.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Networks of European Cinemas</t>
+          <t>Films on the Move</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-CINNET</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-FILMOVE</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1601,14 +1601,14 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia reti di sale cinematografiche europee nell'ambito del programma Creative Europe, richiedendo partnership transnazionali strutturate tra esercenti cinema: una PMI del Cilento potrebbe partecipare solo se gestisce una sala cinematografica e riesce a entrare in un network internazionale già consolidato, scenario poco probabile per realtà locali di piccole dimensioni.</t>
+          <t>Il bando Films on the Move (MEDIA/CREA 2027) finanzia la distribuzione transnazionale di film europei ed è riservato a distributori cinematografici con attività specifica nel settore audiovisivo, escludendo di fatto le PMI generiche del Cilento non operanti in questo comparto. Una piccola impresa campana non audiovisiva non ha i requisiti soggettivi per accedere.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Films on the Move</t>
+          <t>Safeguarding Europe’s Born-digital Heritage</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1618,17 +1618,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-FILMOVE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-BORN-DIGITAL-HERITAGE</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1643,39 +1643,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Films on the Move è un programma MEDIA/Creative Europe destinato a distributori cinematografici europei per la circolazione transnazionale di film, non a PMI generiche del Cilento o della Campania. Salvo che l'azienda operi specificamente nella distribuzione cinematografica europea, il bando non è applicabile.</t>
+          <t>Il bando riguarda la salvaguardia del patrimonio culturale digitale europeo, un tema molto specifico e orientato a istituzioni culturali, archivi e organismi pubblici piuttosto che a PMI commerciali. Una piccola impresa del Cilento difficilmente possiede i requisiti tecnici e istituzionali per partecipare, salvo rarissimi casi di aziende specializzate in digitalizzazione e conservazione di beni culturali.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Europe’s Born-digital Heritage</t>
+          <t>Support for social dialogue</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-BORN-DIGITAL-HERITAGE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-SOC-DIALOG</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>UE - SOCPL</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1690,39 +1690,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Digitalizzazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la salvaguardia del patrimonio culturale digitale nativo a livello europeo, con focus su istituzioni archivistiche, biblioteche e grandi enti pubblici: una PMI del Cilento difficilmente ha le dimensioni, le competenze tecniche specialistiche e la struttura organizzativa per competere in questo tipo di call europea diretta. Non sono previste spese tipicamente accessibili a piccole imprese locali né settori produttivi del territorio come turismo, agricoltura o artigianato.</t>
+          <t>Il bando UE 'Support for social dialogue' finanzia organizzazioni di rappresentanza (sindacati, associazioni datoriali) per attività di dialogo sociale a livello europeo, non è destinato direttamente alle PMI. Una piccola impresa del Cilento non ha accesso diretto a questi fondi né può candidarsi come beneficiaria principale.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Support for social dialogue</t>
+          <t>Empowering youth in the EU Outermost Regions – YOUTH 4 OUTERMOST REGIONS (#YOUTH4ORS)</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-SOC-DIALOG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-YOUTH4OR2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>UE - SOCPL</t>
+          <t>UE - ERDFTA</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1737,39 +1737,39 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Il bando UE 'Support for social dialogue' finanzia organizzazioni rappresentative del dialogo sociale (sindacati, associazioni datoriali a livello europeo/nazionale), non PMI singole. Una piccola impresa del Cilento non rientra tra i beneficiari diretti ammissibili.</t>
+          <t>Il bando è destinato alle Regioni Ultraperiferiche dell'UE (come Azzorre, Canarie, Martinica, ecc.), territori che per definizione non includono la Campania né il Cilento: una PMI campana non rientra tra i beneficiari eleggibili. Non esistono spese finanziabili né opportunità concrete per imprese localizzate nel Sud Italia continentale.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Empowering youth in the EU Outermost Regions – YOUTH 4 OUTERMOST REGIONS (#YOUTH4ORS)</t>
+          <t>The European Capital of Innovation Award Rising Innovator Category HORIZON-EIC-2026-PRIZE-ICAPITAL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-YOUTH4OR2</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-02</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>UE - ERDFTA</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1784,19 +1784,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Il bando è destinato alle Regioni Ultraperiferiche dell'UE (come Canarie, Azzorre, Martinica, ecc.), territori che non includono la Campania né il Cilento: una PMI campana non rientra nei beneficiari eleggibili e non può accedere ai finanziamenti previsti.</t>
+          <t>Il premio European Capital of Innovation è destinato esclusivamente a città e amministrazioni locali europee, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né beneficiare di finanziamenti diretti. L'unica utilità indiretta sarebbe se il proprio Comune si candidasse, trascinando iniziative territoriali di innovazione.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>The European Capital of Innovation Award Rising Innovator Category HORIZON-EIC-2026-PRIZE-ICAPITAL</t>
+          <t>The European Capital of Innovation Award iCapital Category HORIZON-EIC-2026-ICAPITAL</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1836,34 +1836,34 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Il premio European Capital of Innovation è destinato a città e amministrazioni locali europee che eccellono nell'innovazione urbana, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né beneficiare di finanziamenti diretti. L'unico interesse indiretto sarebbe partecipare a ecosistemi di innovazione promossi da un comune candidato, scenario poco probabile per territori rurali come il Cilento.</t>
+          <t>Il premio iCapital è destinato esclusivamente a città e capitali europee dell'innovazione, non a PMI o imprese private: una piccola impresa del Cilento non può candidarsi direttamente né accedere ai fondi come beneficiaria. L'unico interesse indiretto sarebbe partecipare a iniziative promosse da un comune candidato, scenario poco probabile per i piccoli centri del territorio cilentano.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>The European Capital of Innovation Award iCapital Category HORIZON-EIC-2026-ICAPITAL</t>
+          <t>Support to awareness raising about the Arctic communities, including Indigenous People</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EMFAF-2026-PIA-ARCTIC</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - EMFAF</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1878,39 +1878,39 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Il premio iCapital è destinato esclusivamente a città e capitali europee dell'innovazione, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né beneficiare di finanziamenti diretti da questo bando. L'unica utilità indiretta sarebbe per una PMI già inserita in ecosistemi urbani di innovazione candidati, scenario improbabile per il territorio cilentano.</t>
+          <t>Il bando riguarda la sensibilizzazione sulle comunità artiche e i Popoli Indigeni, un tema geograficamente e tematicamente lontano dalla realtà delle PMI campane e del Cilento, senza alcuna connessione con i settori produttivi locali come pesca, turismo o agroalimentare. Non esistono requisiti o ambiti di spesa compatibili con le attività tipiche di una piccola impresa del territorio.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Support to awareness raising about the Arctic communities, including Indigenous People</t>
+          <t>Industrial Readiness for Affordable Ka-band User Terminals</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EMFAF-2026-PIA-ARCTIC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-IRIS2-UT-IND-READINESS</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>UE - EMFAF</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la sensibilizzazione sulle comunità artiche e i popoli indigeni, un tema del tutto estraneo al contesto geografico, culturale e produttivo del Cilento e della Campania. Non esistono spese finanziabili né settori di attività rilevanti per una PMI locale di questa area.</t>
+          <t>Il bando finanzia lo sviluppo industriale di terminali utente in banda Ka per telecomunicazioni satellitari, un settore altamente specializzato che richiede competenze aerospaziali e capacità produttive avanzate difficilmente presenti in una PMI del Cilento. L'orientamento verso grandi player dell'industria spaziale europea rende l'accesso diretto sostanzialmente inaccessibile per una piccola o media impresa campana.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Industrial Readiness for Affordable Ka-band User Terminals</t>
+          <t>Capacity building for Ukrainian regional policy stakeholders</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-IRIS2-UT-IND-READINESS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-UAACQUIS22</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>UE - ERDFTA</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1972,39 +1972,39 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo industriale di terminali utente in banda Ka per comunicazioni satellitari, un settore altamente specializzato che richiede competenze aerospaziali e capacità produttive difficilmente disponibili in una PMI del Cilento o della Campania in generale. Il profilo dei beneficiari attesi è quello di grandi aziende o consorzi con esperienza nel settore spaziale/difesa, rendendo di fatto l'accesso non realistico per una piccola o media impresa locale.</t>
+          <t>Il bando è destinato a stakeholder istituzionali della politica regionale ucraina nell'ambito di programmi di capacity building finanziati da ERDF/TA, senza alcuna apertura diretta a PMI italiane o campane. Una piccola impresa del Cilento non rientra tra i beneficiari eleggibili né può accedere alle spese finanziabili, che riguardano assistenza tecnica e rafforzamento amministrativo in contesto ucraino.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Capacity building for Ukrainian regional policy stakeholders</t>
+          <t>ERC ADVANCED GRANTS</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-UAACQUIS22</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-ADG</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>UE - ERDFTA</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2019,34 +2019,34 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto a stakeholder istituzionali della politica regionale ucraina per attività di capacity building, escludendo di fatto le PMI italiane come beneficiari diretti. Una PMI del Cilento non ha titolo per partecipare né accesso diretto ai fondi previsti.</t>
+          <t>Gli ERC Advanced Grants sono finanziamenti destinati esclusivamente a ricercatori individuali di eccellenza con track record scientifico consolidato, non a PMI: una piccola o media impresa del Cilento non può candidarsi direttamente e difficilmente può partecipare nemmeno come partner. Il bando non copre spese operative aziendali né attività produttive tipiche delle PMI campane.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ERC ADVANCED GRANTS</t>
+          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-ADG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Gli ERC Advanced Grants sono destinati esclusivamente a ricercatori individuali di eccellenza con track record scientifico consolidato, non a PMI: una piccola impresa del Cilento non ha i requisiti soggettivi per candidarsi direttamente. Il bando finanzia ricerca fondamentale di frontiera, senza previsione di accesso diretto per soggetti imprenditoriali.</t>
+          <t>Il bando Horizon è focalizzato su ricerca sanitaria e AI applicata all'Africa sub-sahariana, un ambito molto specifico e lontano dalle attività tipiche di una PMI campana o del Cilento. Richiede inoltre capacità di ricerca avanzata e partenariati internazionali difficilmente accessibili per una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
+          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2113,19 +2113,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è focalizzato sulla ricerca sanitaria digitale e sull'AI applicata all'Africa sub-sahariana, un contesto geografico e tematico lontano dalle attività tipiche di una PMI campana o del Cilento. Richiede inoltre capacità di ricerca avanzata e partnership internazionali difficilmente accessibili per realtà di piccola dimensione.</t>
+          <t>Il bando Horizon finanzia reti di formazione e innovazione nel settore farmaceutico/regolatorio con focus su etica, farmacovigilanza e piattaforme digitali regolatorie, ambiti altamente specializzati e tipicamente accessibili a grandi consorzi accademici o industrie farmaceutiche strutturate. Una PMI del Cilento, salvo operi specificamente in health-tech o consulenza regolatoria farmaceutica, difficilmente possiede i requisiti tecnici e la capacità progettuale per competere in un bando Horizon di questa complessità.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
+          <t>HORIZON-JU-EDCTP3-2026-Dr Pascoal Mocumbi Prize</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-DRPASCOALMOCUMBIPRIZE</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2160,19 +2160,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a consorzi di ricerca e grandi organizzazioni del settore farmaceutico/regolatorio, con focus su etica, farmacovigilanza e piattaforme digitali regolatorie: ambiti molto distanti dalla struttura produttiva tipica di una PMI del Cilento. I requisiti di partenariato internazionale e la complessità progettuale rendono l'accesso diretto estremamente difficile per una piccola impresa campana non specializzata in life sciences o regulatory affairs.</t>
+          <t>Il Premio Dr Pascoal Mocumbi è un riconoscimento nell'ambito della ricerca sulle malattie infettive in Africa subsahariana, destinato a ricercatori o istituzioni scientifiche, non a PMI. Una piccola impresa del Cilento non ha i requisiti soggettivi né il profilo di attività per accedere a questo tipo di bando.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Dr Pascoal Mocumbi Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Outstanding Female Scientist Prize</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-DRPASCOALMOCUMBIPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSFEMALESCIENTISTPRIZE</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2212,14 +2212,14 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Il premio Dr Pascoal Mocumbi è un riconoscimento nell'ambito della ricerca su malattie infettive della povertà in Africa subsahariana, destinato a ricercatori o istituzioni scientifiche, non a PMI. Una piccola o media impresa del Cilento non ha alcun accesso diretto né beneficio concreto da questo bando.</t>
+          <t>Si tratta di un premio internazionale destinato esclusivamente a ricercatrici eccellenti nell'ambito della salute globale e delle malattie infettive, senza alcuna componente di finanziamento diretto a imprese o PMI. Una PMI del Cilento non ha titolo per partecipare né beneficia di alcuna ricaduta diretta da questo bando.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Outstanding Female Scientist Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Outstanding Research Team Prize</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSFEMALESCIENTISTPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSRESEARCHTEAMPRIZE</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio individuale destinato a ricercatrici eccellenti nell'ambito della ricerca su malattie infettive legate allo sviluppo globale: non è uno strumento finanziario accessibile a una PMI del Cilento o della Campania, né prevede finanziamenti per attività aziendali, progetti imprenditoriali o spese operative.</t>
+          <t>Si tratta di un premio europeo destinato a team di ricerca eccellenti nell'ambito della salute globale e delle malattie infettive (programma EDCTP3), non un finanziamento diretto a PMI. Una piccola impresa del Cilento non ha i requisiti strutturali né il profilo di ricerca richiesto per accedere a questo tipo di riconoscimento.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Outstanding Research Team Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Man EU Prize</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSRESEARCHTEAMPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPMANEUPRIZE</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2306,14 +2306,14 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo rivolto a team di ricerca eccellenti nell'ambito della salute globale e delle malattie infettive (programma EDCTP3), destinato a organizzazioni di ricerca e istituzioni accademiche, non a PMI. Una piccola impresa del Cilento non ha i requisiti né il profilo scientifico richiesto per accedere a questo tipo di riconoscimento.</t>
+          <t>Si tratta di un premio europeo nell'ambito della ricerca medica e sanitaria globale (EDCTP3), destinato a ricercatori scientifici di eccellenza operanti su malattie infettive nei paesi a basso reddito: non è uno strumento di finanziamento diretto per PMI campane o del Cilento e non prevede spese finanziabili per attività d'impresa ordinarie.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Man EU Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman EU Prize</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPMANEUPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANEUPRIZE</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2353,14 +2353,14 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo nell'ambito della ricerca scientifica su malattie infettive (EDCTP3), destinato a ricercatori e istituzioni scientifiche di eccellenza, non a PMI. Una piccola impresa del Cilento non ha i requisiti né il profilo per candidarsi a questo tipo di riconoscimento accademico-scientifico.</t>
+          <t>Si tratta di un premio europeo per il riconoscimento della leadership scientifica femminile nell'ambito del partenariato EDCTP3 (malattie infettive nei paesi a basso reddito), non di un finanziamento diretto a PMI. Una piccola impresa del Cilento non ha possibilità concrete di accesso né benefici operativi diretti.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman EU Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman SSA Prize</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANEUPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANSSAPRIZE</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2400,14 +2400,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo dedicato alla leadership scientifica femminile nell'ambito del partenariato EDCTP3 (ricerca su malattie infettive in paesi a basso reddito), non di un finanziamento a progetti aziendali: non prevede sovvenzioni per attività operative o investimenti di una PMI. Una piccola impresa del Cilento non ha possibilità concrete di beneficiarne direttamente.</t>
+          <t>Si tratta di un premio (Prize) nell'ambito di EDCTP3 dedicato alla leadership scientifica femminile in ambito medico-sanitario globale: non finanzia progetti aziendali né spese operative di una PMI, ma riconosce eccellenze di ricerca individuale o istituzionale. Una PMI del Cilento non ha i requisiti scientifici né il profilo istituzionale per candidarsi utilmente.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman SSA Prize</t>
+          <t>ERC PLUS GRANTS</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANSSAPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-PLUS</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2442,39 +2442,39 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio (Prize) nell'ambito di Horizon Europe dedicato alla leadership scientifica femminile, destinato a ricercatrici in contesti accademici o di ricerca avanzata. Una PMI del Cilento non rientra nei beneficiari tipici di questo strumento, che non finanzia attività aziendali né spese operative.</t>
+          <t>Gli ERC Plus Grants sono destinati a ricercatori eccellenti già beneficiari di finanziamenti ERC, richiedendo una base di ricerca scientifica di frontiera incompatibile con la struttura tipica di una PMI del Cilento o della Campania. Una piccola impresa non dispone generalmente dei requisiti accademici e istituzionali necessari per accedere a questo strumento.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ERC PLUS GRANTS</t>
+          <t>Centres of Vocational Excellence</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-PLUS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2026-PEX-COVE</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ERASMUS2027</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2489,19 +2489,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Gli ERC Plus Grants sono progettati per supportare ricercatori di eccellenza già vincitori di grant ERC, rendendoli di fatto inaccessibili per una PMI del Cilento priva di un profilo di ricerca scientifica certificato a livello europeo. Una piccola impresa campana non possiede i requisiti soggettivi richiesti né le strutture di ricerca necessarie per candidarsi autonomamente.</t>
+          <t>Il bando Erasmus+ Centres of Vocational Excellence è rivolto a consorzi transnazionali di istituti di istruzione e formazione professionale (IeFP), enti pubblici e organizzazioni del lavoro: una PMI del Cilento può partecipare solo come partner secondario di un consorzio guidato da un istituto formativo, con ruolo marginale e accesso indiretto ai fondi. La complessità gestionale e la necessità di partnership europee strutturate rendono questo strumento poco praticabile per una piccola impresa locale senza esperienza in progetti Erasmus.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Centres of Vocational Excellence</t>
+          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2511,17 +2511,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2026-PEX-COVE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-31</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>UE - ERASMUS2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2536,19 +2536,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Il bando Erasmus+ Centres of Vocational Excellence è rivolto principalmente a istituzioni di istruzione e formazione professionale (IFP), università e consorzi pubblici, non a PMI singole; una piccola impresa del Cilento potrebbe partecipare solo come partner secondario in un consorzio transnazionale, ruolo complesso da gestire senza struttura dedicata a progettazione europea.</t>
+          <t>Il bando Horizon Europe si focalizza su tecnologie avanzate di osservazione terrestre e telecomunicazioni satellitari, richiedendo capacità di ricerca e sviluppo di livello europeo difficilmente accessibili a una PMI del Cilento senza un consorzio con centri di ricerca qualificati. Le spese finanziabili riguardano R&amp;S ad alta intensità tecnologica, lontane dalle esigenze operative tipiche delle piccole imprese locali nei settori trainanti del territorio (turismo, agricoltura, artigianato).</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-31</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-32</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2588,14 +2588,14 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca e sviluppo avanzate nel settore spaziale (osservazione della Terra, telecomunicazioni satellitari), con consorzio internazionale e budget elevati, rendendo l'accesso diretto quasi impossibile per una PMI del Cilento senza un ruolo marginale in un partenariato guidato da grandi attori industriali o universitari. Non finanzia attività operative o di digitalizzazione ordinaria, ma progetti di R&amp;S frontier nel comparto aerospace.</t>
+          <t>Il bando Horizon Europe riguarda missioni dimostrative per l'osservazione terrestre e telecomunicazioni satellitari, settori altamente specializzati che richiedono capacità tecnologiche e strutture di ricerca difficilmente disponibili per una PMI tradizionale del Cilento. I requisiti tecnici e la complessità dei consorzi internazionali richiesti rendono questo bando praticamente inaccessibile senza una partnership con grandi player del settore spaziale.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-32</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-82</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2635,14 +2635,14 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata in tecnologie spaziali, osservazione terrestre e telecomunicazioni satellitari, ambiti altamente specializzati e lontani dal tessuto produttivo tipico delle PMI cilentane. I requisiti tecnici, la dimensione dei consorzi internazionali e la complessità renditcontativa rendono questo bando di fatto inaccessibile per una PMI locale di piccola o media dimensione senza un partner scientifico strutturato.</t>
+          <t>Il bando richiede lo sviluppo di substrati in carburo di silicio semi-isolante per componenti spaziali GaN ad alta frequenza, tecnologie altamente specializzate che richiedono laboratori di ricerca avanzati e competenze da grande player del settore aerospaziale/semiconduttori. Una PMI del Cilento o della Campania difficilmente possiede le infrastrutture produttive e le certificazioni spaziali ESA necessarie per partecipare competitivamente, anche in qualità di partner.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
+          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-82</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-11</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2677,19 +2677,19 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di substrati in carburo di silicio (SiC) semi-isolante per componenti elettronici spaziali ad altissima tecnologia (GaN MMIC in banda millimetrica), richiedendo capacità industriali e di R&amp;D avanzatissime tipiche di grandi player del settore aerospaziale e della microelettronica. Una PMI del Cilento o della Campania in generale difficilmente dispone delle infrastrutture, delle certificazioni spaziali e del know-how tecnico specialistico necessari per competere in questo contesto ESA/Horizon.</t>
+          <t>Il bando riguarda lo sviluppo di infrastrutture spaziali europee (spazioporti) e si rivolge a grandi consorzi con competenze aerospaziali altamente specializzate, rendendo l'accesso praticamente impossibile per una PMI campana del Cilento priva di radicamento nel settore space economy. Non esistono linee di finanziamento applicabili a produzioni, servizi o attività tipiche del tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
+          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-11</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-85</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2724,19 +2724,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di spazioporti europei e l'accesso autonomo dell'UE allo spazio, un settore altamente specializzato che richiede infrastrutture e competenze tecnologiche di livello industriale difficilmente compatibili con una PMI campana del Cilento. Non esistono applicazioni pratiche dirette per realtà produttive locali di piccola o media dimensione operanti in questo territorio.</t>
+          <t>Il bando riguarda lo sviluppo di infrastrutture critiche per test di irradiazione ad alta energia di componenti elettronici spaziali (EEE), un settore altamente specializzato che richiede competenze avanzate in ingegneria spaziale e fisica nucleare, difficilmente accessibili a una PMI del Cilento o della Campania in generale. Le risorse e le capacità tecniche richieste sono tipiche di grandi laboratori di ricerca o aziende del settore difesa/spazio, escludendo di fatto le piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
+          <t>Scientific analysis and exploitation of space data</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-85</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-61</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2776,14 +2776,14 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di infrastrutture critiche per test di irradiazione ad alta energia di componenti elettronici spaziali (EEE), un settore altamente specializzato che richiede competenze, laboratori e certificazioni tipici di grandi player aerospaziali o centri di ricerca. Una PMI del Cilento o della Campania difficilmente dispone delle capacità tecniche e infrastrutturali necessarie per partecipare competitivamente.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata nell'analisi di dati spaziali e satellitari, con requisiti tecnici e di consorzio internazionale difficilmente accessibili per una PMI del Cilento senza un forte partenariato con enti di ricerca. Solo PMI tecnologiche specializzate in remote sensing, geospaziale o Earth Observation potrebbero candidarsi come partner, non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Scientific analysis and exploitation of space data</t>
+          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-61</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-86</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2823,14 +2823,14 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata nell'analisi di dati spaziali satellitari, strutture di R&amp;S consolidate e partnership internazionali difficilmente accessibili a una PMI di piccola dimensione del Cilento. L'ambito altamente specializzato e la competizione europea rendono questo bando sostanzialmente fuori portata per realtà locali prive di un dipartimento tecnico-scientifico dedicato.</t>
+          <t>Il bando finanzia lo sviluppo di tecnologie spaziali avanzate (interfacce di rifornimento per satelliti) nell'ambito del programma Horizon EU, richiedendo competenze altamente specializzate in ingegneria aerospaziale e capacità R&amp;D di livello industriale difficilmente disponibili in una PMI del Cilento. Il profilo dei beneficiari attesi è quello di grandi aziende o centri di ricerca del settore spaziale europeo, rendendo questo bando sostanzialmente inaccessibile per una piccola o media impresa campana.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
+          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-86</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-81</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di tecnologie spaziali avanzate per sistemi di rifornimento orbitale e riduzione della dipendenza europea in componenti critici per lo spazio, settore che richiede competenze altamente specializzate, infrastrutture di ricerca e capitali ben oltre le capacità tipiche di una PMI campana, specialmente nel contesto del Cilento. L'accesso è realisticamente limitato a grandi aziende aerospaziali o consorzi con laboratori R&amp;D dedicati.</t>
+          <t>Il bando richiede lo sviluppo di componenti elettronici spaziali radiation-hard su tecnologia 7nm, un settore ad altissima specializzazione che presuppone capacità di R&amp;D avanzata, infrastrutture tecnologiche di livello industriale e know-how nel settore aerospaziale difficilmente presenti in una PMI del Cilento o della Campania interna. Le barriere tecniche, normative e competitive rendono questo bando sostanzialmente inaccessibile per una piccola o media impresa locale non già inserita in filiere spaziali europee.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
+          <t>Microelectronic – Front-End Module (FEM)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2887,12 +2887,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-81</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2917,14 +2917,14 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Il bando richiede lo sviluppo di componenti elettronici spaziali radiation-hard su processo a 7nm, tecnologia altamente specializzata che presuppone capacità R&amp;D avanzate nel settore aerospace/semiconduttori, del tutto fuori portata per una PMI del Cilento o della Campania in generale. L'orientamento è verso grandi player industriali europei del settore spaziale o laboratori di ricerca con competenze specifiche in microelettronica per ambienti critici.</t>
+          <t>Il bando Horizon UE sui moduli a radiofrequenza per microelettronica (FEM) richiede capacità di R&amp;D avanzata nel settore dei semiconduttori e dell'elettronica di potenza, competenze altamente specializzate difficilmente presenti in una PMI del Cilento o della Campania interna. La complessità tecnica, i requisiti di consorzio internazionale e l'orientamento a grandi player industriali del settore elettronico rendono questo bando sostanzialmente inaccessibile per una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Microelectronic – Front-End Module (FEM)</t>
+          <t>Trafficking in human beings</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-THB</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ISF</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2959,19 +2959,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su moduli front-end per microelettronica richiede competenze altamente specializzate in R&amp;D su semiconduttori e infrastrutture di ricerca avanzata, difficilmente disponibili in una PMI del Cilento. Il settore microelettronico non è rappresentativo del tessuto produttivo locale, rendendo l'accesso concreto quasi impraticabile senza partnership con grandi centri di ricerca.</t>
+          <t>Il bando ISF (Internal Security Fund) sul traffico di esseri umani è destinato prevalentemente a forze dell'ordine, ONG specializzate e autorità pubbliche, non a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti soggettivi né le competenze istituzionali richieste per accedere a questo tipo di finanziamento europeo per la sicurezza interna.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Trafficking in human beings</t>
+          <t>Organised crime and drug trafficking</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-THB</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-OCDT</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3011,34 +3011,34 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sul traffico di esseri umani è destinato principalmente a enti pubblici, forze dell'ordine, ONG e organizzazioni specializzate nel contrasto alla tratta: una PMI del Cilento non rientra tra i beneficiari tipici e non finanzierebbe attività produttive o commerciali. L'unica eccezione potrebbe riguardare enti di formazione privati con specifica expertise in materia, ma si tratta di un caso molto marginale.</t>
+          <t>Il bando ISF (Internal Security Fund) sulla criminalità organizzata e il traffico di droga è destinato a forze dell'ordine, autorità pubbliche e organizzazioni specializzate nella sicurezza interna, non a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti soggettivi né le competenze istituzionali richieste per accedere a questo tipo di finanziamento europeo.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Organised crime and drug trafficking</t>
+          <t>Framework Partnership Agreements for operating grants to support non-profit organisations</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-OCDT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-FPA</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>UE - ISF</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3058,34 +3058,34 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sulla criminalità organizzata e il traffico di droga è destinato prevalentemente a forze dell'ordine, enti pubblici e organizzazioni specializzate nel settore della sicurezza, non a PMI commerciali. Una piccola o media impresa del Cilento non ha i requisiti soggettivi né le competenze istituzionali richieste per accedere a questo tipo di finanziamento.</t>
+          <t>Il bando LIFE2027 per Framework Partnership Agreements è destinato esclusivamente a organizzazioni non-profit operanti nel settore ambientale a livello europeo, escludendo per definizione le PMI a scopo di lucro. Una piccola impresa del Cilento non può accedere direttamente a questo strumento, che finanzia costi operativi di enti del terzo settore con struttura e capacità amministrativa sovranazionale.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Framework Partnership Agreements for operating grants to support non-profit organisations</t>
+          <t>MSCA Postdoctoral Fellowships 2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-FPA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-PF-01-01</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3100,19 +3100,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE2027 è riservato esclusivamente a organizzazioni non profit tramite accordi quadro di partenariato per sovvenzioni operative: una PMI con scopo di lucro è strutturalmente esclusa dalla partecipazione diretta. Il Cilento, pur area ad alto valore naturalistico, non rappresenta un vantaggio competitivo per accedere a questo specifico strumento.</t>
+          <t>Le MSCA Postdoctoral Fellowships sono destinate a ricercatori individuali post-dottorato e richiedono una struttura ospitante con capacità di supervisione scientifica avanzata, requisiti difficilmente compatibili con una PMI di piccola dimensione del Cilento. L'onere amministrativo elevato e la necessità di gestire progetti di ricerca internazionale rendono questo bando di fatto inaccessibile senza un partenariato strutturato con un ente di ricerca o università.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>MSCA Postdoctoral Fellowships 2026</t>
+          <t>ERA Fellowships</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-PF-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-05-WIDENING-01</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3152,19 +3152,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Il bando MSCA Postdoctoral Fellowships finanzia ricercatori individuali post-dottorato per progetti di mobilità internazionale, non è rivolto direttamente alle PMI come beneficiarie principali. Una PMI del Cilento potrebbe partecipare solo come host institution secondaria, con burocrazia europea complessa e requisiti di ricerca avanzata difficilmente compatibili con la struttura di una piccola impresa locale.</t>
+          <t>Le ERA Fellowships finanziano mobilità e ricerca di singoli ricercatori nell'ambito del programma Horizon Europe, rivolgendosi principalmente a università, enti di ricerca e grandi organizzazioni scientifiche. Una PMI del Cilento difficilmente possiede la struttura amministrativa e la capacità progettuale per candidarsi come ente ospitante o coordinatore in questo tipo di bando altamente competitivo e burocraticamente complesso.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ERA Fellowships</t>
+          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-WIDERA-2026-05-WIDENING-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2026-02-DISEASE-12</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3194,19 +3194,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Le ERA Fellowships finanziano la mobilità di ricercatori individuali tra istituzioni accademiche e di ricerca, con un modello progettuale complesso e requisiti istituzionali difficilmente soddisfabili da una PMI del Cilento senza un partner di ricerca strutturato. Il bando è pensato principalmente per enti di ricerca e università, rendendo l'accesso diretto da parte di una piccola impresa molto improbabile senza una partnership formale con un istituto accreditato.</t>
+          <t>Il bando ERDERA riguarda la ricerca sulle malattie rare nell'ambito di Horizon Europe e richiede consorzi scientifici internazionali con elevate competenze biomediche, rendendo di fatto inaccessibile la partecipazione per una PMI generalista del Cilento. Solo laboratori o aziende biotech altamente specializzate in diagnostica o terapie per malattie rare potrebbero trovare uno spazio marginale come partner.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>European Partnership on Rare Diseases (ERDERA) (Phase 2)</t>
+          <t>Earlier and more precise palliative care</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-HLTH-2026-02-DISEASE-12</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-04</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3246,14 +3246,14 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Il bando ERDERA è focalizzato sulla ricerca clinica e traslazionale sulle malattie rare, rivolto principalmente a consorzi di enti di ricerca, ospedali e grandi organizzazioni scientifiche europee. Una PMI campana, anche del Cilento, difficilmente possiede i requisiti tecnici e il profilo di ricerca biomedica necessari per partecipare competitivamente, salvo rarissimi casi di aziende specializzate in diagnostica o biotech.</t>
+          <t>Il bando Horizon Europe sulla palliative care precoce è orientato a consorzi di ricerca accademica e ospedali universitari europei, richiedendo competenze scientifiche specializzate e capacità progettuali internazionali difficilmente accessibili a una PMI del Cilento. Non finanzia attività produttive o servizi commerciali tipici delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Earlier and more precise palliative care</t>
+          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-01</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3288,19 +3288,19 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulle cure palliative precoci è orientato a consorzi di ricerca accademica e ospedali universitari, richiedendo capacità scientifiche e infrastrutture cliniche difficilmente compatibili con una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo come partner tecnologico di supporto (es. soluzioni digitali per la telemedicina), ma il ruolo sarebbe marginale e la competizione a livello europeo rende l'accesso estremamente difficile.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata in modellistica digitale oncologica e consorzio europeo, struttura tipicamente accessibile solo a centri di ricerca, università o grandi aziende biotech. Una PMI del Cilento, salvo specializzazione in digital health o bioinformatica con partnership consolidate, difficilmente possiede i requisiti tecnici e amministrativi per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Virtual Human Twin (VHT) Models for Cancer Research</t>
+          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-05</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3335,19 +3335,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su modelli digitali gemelli per la ricerca oncologica richiede capacità di R&amp;S avanzate, partnership con istituti di ricerca e competenze in ambito biomedico/computazionale che difficilmente una PMI del Cilento possiede autonomamente; l'accesso è realistico solo come partner junior in un consorzio internazionale guidato da università o grandi centri di ricerca.</t>
+          <t>Il bando Horizon è focalizzato sulla salute mentale dei giovani sopravvissuti al cancro tramite una piattaforma digitale europea, richiedendo competenze specialistiche in oncologia, psicologia e ricerca clinica che esulano completamente dall'attività tipica di una PMI del Cilento. I progetti Horizon di questo tipo sono strutturati per consorzi di università, ospedali e centri di ricerca, rendendo la partecipazione diretta di una PMI locale estremamente improbabile senza un ruolo tecnico-digitale molto specifico.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Boosting mental health of young cancer survivors through the European Cancer Patient Digital Centre (ECPDC)</t>
+          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-03</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è focalizzato sulla salute mentale dei giovani sopravvissuti al cancro tramite una piattaforma digitale europea, richiedendo consorzi di ricerca clinica e sanitaria specializzati. Una PMI campana del Cilento difficilmente possiede i requisiti tecnico-scientifici e le partnership istituzionali necessarie per partecipare competitivamente a questo tipo di progetto europeo.</t>
+          <t>Il bando Horizon finanzia trial clinici pragmatici sull'immunoterapia oncologica, richiedendo competenze altamente specializzate in ambito medico-scientifico e capacità di gestione di sperimentazioni cliniche complesse, del tutto fuori portata per una PMI generica del Cilento o della Campania. Non esistono spese finanziabili né attività riconducibili a settori produttivi locali tipici.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Pragmatic clinical trials to optimise immunotherapeutic interventions for patients with refractory cancers</t>
+          <t>Microbiome for early cancer prediction before the onset of disease</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-02</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3429,19 +3429,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia trial clinici pragmatici su immunoterapie oncologiche nell'ambito di Horizon Europe, richiedendo competenze altamente specializzate in oncologia clinica e infrastrutture di ricerca biomedica che esulano completamente dal tessuto produttivo tipico delle PMI del Cilento e della Campania. L'accesso è di fatto riservato a consorzi guidati da grandi centri ospedalieri universitari o istituti di ricerca oncologica, rendendo la partecipazione di una PMI locale praticamente inattuabile.</t>
+          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sul microbioma come biomarcatore oncologico, con consorzio internazionale e strutture di R&amp;S dedicate, caratteristiche difficilmente compatibili con una PMI del Cilento non specializzata in biotecnologie o diagnostica medica. L'accesso è realistico solo per spin-off universitari o aziende biotech con track record in progetti europei di ricerca traslazionale.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Microbiome for early cancer prediction before the onset of disease</t>
+          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-06</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3476,19 +3476,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata sul microbioma e predizione oncologica, con consorzio internazionale e competenze scientifiche altamente specializzate, difficilmente accessibili a una PMI del Cilento senza un solido partner universitario o di ricerca. Solo PMI biotech/medtech con laboratori R&amp;S strutturati potrebbero partecipare come partner junior.</t>
+          <t>Il bando finanzia programmi di ricerca oncologica in collaborazione con l'Ucraina, richiedendo competenze scientifiche specializzate e strutture di ricerca avanzate tipiche di università e centri di ricerca, non di PMI. Una piccola o media impresa del Cilento, anche operante in ambito sanitario o formativo, non possiede i requisiti tecnici e istituzionali necessari per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Development of a research capacity building programme on cancer with and for Ukraine</t>
+          <t>Improve the Quality of Life of older cancer patients</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-07</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3528,14 +3528,14 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la costruzione di capacità di ricerca oncologica in collaborazione con l'Ucraina, ed è destinato principalmente a istituzioni accademiche, centri di ricerca e ospedali universitari. Una PMI del Cilento non dispone delle competenze scientifiche né della struttura istituzionale richiesta per partecipare a un programma Horizon di questa natura.</t>
+          <t>Il bando Horizon EU richiede la partecipazione in consorzi internazionali di ricerca con competenze specialistiche in oncologia e gerontologia, strutture di ricerca certificate e capacità progettuali complesse, barriere difficilmente superabili per una PMI campana di piccola/media dimensione. Una PMI del Cilento potrebbe partecipare solo come partner secondario in un consorzio già strutturato, con ruolo marginale e alta complessità burocratica.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Improve the Quality of Life of older cancer patients</t>
+          <t>Approaches and tools for security in software and hardware development and assessment</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-02-CANCER-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-01</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3570,19 +3570,19 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi internazionali di ricerca con competenze altamente specializzate in oncologia e gerontologia, rendendo l'accesso diretto praticamente impossibile per una PMI campana del Cilento senza un solido network europeo preesistente. Una PMI potrebbe partecipare solo come partner tecnologico (es. sviluppo di dispositivi o software medicali) all'interno di un consorzio già strutturato, scenario poco realistico per realtà di piccola dimensione.</t>
+          <t>Il bando Horizon focalizzato su sicurezza software/hardware richiede capacità di ricerca avanzata, consorzio europeo e competenze tecniche molto specialistiche, caratteristiche difficilmente compatibili con una PMI tradizionale del Cilento. Solo aziende ICT con un dipartimento R&amp;D strutturato e partnership universitarie potrebbero candidarsi realisticamente.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Approaches and tools for security in software and hardware development and assessment</t>
+          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-03</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3622,14 +3622,14 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla sicurezza hardware/software richiede capacità di ricerca avanzata, consorzio internazionale e competenze tecniche specialistiche difficilmente disponibili in una PMI del Cilento. I costi di partecipazione e la complessità progettuale lo rendono accessibile solo a grandi realtà tech o enti di ricerca.</t>
+          <t>Il bando Horizon focalizzato su schemi crittografici avanzati e implementazioni ad alta sicurezza richiede competenze altamente specializzate in ricerca crittografica e capacità di partecipare a consorzi europei, requisiti difficilmente soddisfabili da una PMI del Cilento priva di un dipartimento R&amp;D strutturato. L'ambito tecnico-scientifico estremamente verticale e la complessità gestionale dei progetti Horizon lo rendono accessibile solo a realtà con esperienza consolidata in cybersecurity e partnership universitarie attive.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Advanced cryptographic schemes and High-Assurance high-speed cryptographic implementations</t>
+          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-02</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3669,14 +3669,14 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla crittografia avanzata richiede competenze altamente specializzate in ricerca e sviluppo crittografico, con requisiti tecnici e burocratici difficilmente sostenibili per una PMI del Cilento o della Campania priva di un dipartimento R&amp;D strutturato. Il settore target è quello della cybersecurity e della ricerca accademica/tecnologica avanzata, lontano dal tessuto produttivo locale basato su turismo, agricoltura e artigianato.</t>
+          <t>Il bando Horizon Europe sulla sicurezza e robustezza dei modelli AI richiede capacità di ricerca avanzata, consorzi internazionali e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. I costi di partecipazione, la complessità progettuale e la necessità di partner accademici/industriali qualificati lo rendono poco accessibile senza un solido ecosistema di ricerca già consolidato.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the Security, Privacy and Robustness of AI Models and Systems (SecureAI)</t>
+          <t>R&amp;I in Support of the Clean Industrial Deal: Clean Technologies for Climate Action</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-02-CS-ECCC-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-02</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata in sicurezza e robustezza dei sistemi AI, con consorzî internazionali e risorse umane altamente specializzate che una PMI del Cilento difficilmente possiede internamente. L'accesso è realistico solo come partner junior in un progetto coordinato da università o grandi tech company, rendendo la partecipazione autonoma praticamente impossibile.</t>
+          <t>Il bando Horizon UE richiede progetti di ricerca e innovazione su tecnologie pulite per il clima, con requisiti di consorzio internazionale, elevata capacità tecnico-scientifica e budget tipicamente superiori al milione di euro, caratteristiche strutturalmente incompatibili con una PMI di piccola dimensione del Cilento priva di esperienza pregressa in progetti europei complessi. Una PMI locale potrebbe al massimo partecipare come partner junior in un consorzio guidato da grandi imprese o università, ma difficilmente assumere un ruolo da capofila.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>R&amp;I in Support of the Clean Industrial Deal: Clean Technologies for Climate Action</t>
+          <t>R&amp;I in Support of the Clean Industrial Deal: Decarbonisation of energy intensive industries (IA) (Processes4Planet and Clean Steel partnerships)</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-01</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -3763,14 +3763,14 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo richiede capacità di ricerca avanzata, partnership internazionali e strutture dedicate a R&amp;S difficilmente disponibili in una PMI di piccole dimensioni del Cilento; i budget tipici di questi progetti superano il milione di euro e privilegiano consorzi con università o grandi imprese tecnologiche nel settore delle tecnologie pulite e della transizione climatica.</t>
+          <t>Il bando Horizon Europe è orientato a grandi partnership industriali (Processes4Planet e Clean Steel) per la decarbonizzazione di industrie energivore come acciaio, cemento e chimica, settori scarsamente presenti nel tessuto produttivo del Cilento e della Campania interna. Le PMI locali difficilmente possono accedere autonomamente, trattandosi di progetti di ricerca e innovazione ad alta intensità tecnologica e finanziaria che richiedono consorziarsi con grandi industrie e centri di ricerca europei.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>R&amp;I in Support of the Clean Industrial Deal: Decarbonisation of energy intensive industries (IA) (Processes4Planet and Clean Steel partnerships)</t>
+          <t>Validating policies and business models for affordable and sustainable housing (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CID-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-04</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe finanzia grandi progetti di R&amp;I sulla decarbonizzazione delle industrie energivore (acciaio, chimica, cemento) tramite partnership europee strutturate, con budget tipicamente superiori ai 5-10 milioni di euro e requisiti consortili internazionali difficilmente accessibili a una PMI del Cilento. Una piccola impresa campana non dispone generalmente né della capacità tecnico-scientifica né delle risorse per partecipare come partner in programmi come Processes4Planet o Clean Steel.</t>
+          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi europei con capacità di ricerca e sviluppo avanzate, rendicontazione complessa e cofinanziamento, requisiti difficilmente sostenibili per una PMI del Cilento operante nell'edilizia o nel settore immobiliare. Le opportunità concrete riguardano imprese con esperienza consolidata in progetti R&amp;I europei, non realtà di piccola dimensione locale.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Validating policies and business models for affordable and sustainable housing (Built4People Partnership)</t>
+          <t>Coordinated topic with India on recycling of EV batteries</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-04</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -3857,14 +3857,14 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi europei di ricerca con capacità progettuali e amministrative elevate, difficilmente accessibili a una PMI del Cilento senza un solido network internazionale. Il focus su modelli di housing sostenibile e affordable è distante dal tessuto produttivo locale, orientato prevalentemente a turismo, agricoltura e piccolo artigianato.</t>
+          <t>Il bando Horizon richiede partnership internazionali con soggetti indiani, capacità di ricerca avanzata sul riciclo di batterie per veicoli elettrici e strutture progettuali complesse, elementi difficilmente accessibili per una PMI del Cilento senza un consorzio con università o grandi imprese. Il settore è altamente specializzato e lontano dal tessuto produttivo locale, orientato prevalentemente verso turismo, agricoltura e artigianato.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Coordinated topic with India on recycling of EV batteries</t>
+          <t>Innovative technologies and solutions to improve wind energy systems supporting the Strategic Energy Technology (SET) Plan on wind</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D3-03</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3904,14 +3904,14 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi internazionali con India, elevate capacità di R&amp;D e rendicontazione europea complessa, barriere difficilmente superabili per una PMI del Cilento senza struttura di ricerca dedicata. Il focus sul riciclo di batterie EV riguarda un settore industriale molto specifico, lontano dal tessuto produttivo prevalente nell'area (turismo, agricoltura, artigianato).</t>
+          <t>Il bando Horizon EU richiede consorzi internazionali con forte componente di ricerca e sviluppo avanzato nel settore eolico, con budget elevati e requisiti tecnici difficilmente accessibili a una PMI di piccola dimensione del Cilento. Il territorio, pur ventoso, non dispone di un ecosistema industriale eolico strutturato che giustifichi un investimento progettuale di questa complessità.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Innovative technologies and solutions to improve wind energy systems supporting the Strategic Energy Technology (SET) Plan on wind</t>
+          <t>Low disturbance prefabrication approaches for deep renovation of multi-storey buildings (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D3-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-02</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca e sviluppo avanzata nel settore eolico, con budget elevati e necessità di consorzio internazionale, risultando di fatto inaccessibile per una PMI campana di piccole dimensioni senza un solido profilo R&amp;D. Il Cilento, pur avendo potenziale eolico, non esprime generalmente un tessuto industriale specializzato in tecnologie energetiche wind-tech compatibile con le richieste progettuali di questo tipo di bando.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione in consorzi internazionali di ricerca con capacità tecniche e finanziarie elevate, rendendo l'accesso diretto molto difficile per una PMI del Cilento. Riguarda la prefabbricazione a basso impatto per la ristrutturazione profonda di edifici multipiano, settore di nicchia con requisiti progettuali complessi e budget tipicamente superiori ai 3-5 milioni di euro.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Low disturbance prefabrication approaches for deep renovation of multi-storey buildings (Built4People Partnership)</t>
+          <t>Producing battery-grade materials for electrodes through sustainable processing and refining of raw materials or developing bio-based materials (BATT4EU Partnership)</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-01</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3998,14 +3998,14 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali con capacità di R&amp;S avanzata e prefabbricazione industriale per la riqualificazione profonda di edifici multipiano, competenze difficilmente accessibili per una PMI cilentana di piccola dimensione. I requisiti tecnici e amministrativi di Horizon, uniti alla necessità di partnership europee strutturate, rendono questo bando praticamente inaccessibile senza una rete consolidata di partner universitari o industriali.</t>
+          <t>Il bando BATT4EU richiede capacità di ricerca avanzata nella chimica dei materiali per batterie (elettrodi, materiali bio-based) e si inserisce in un partenariato europeo ad alta intensità tecnologica, strutturalmente inaccessibile per la quasi totalità delle PMI campane e cilentane, che non dispongono di laboratori R&amp;D né di competenze specialistiche nel settore. Il territorio del Cilento, vocato ad agricoltura, turismo e artigianato, non presenta filiere produttive affini all'industria delle batterie.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Producing battery-grade materials for electrodes through sustainable processing and refining of raw materials or developing bio-based materials (BATT4EU Partnership)</t>
+          <t>Researching the technical, social &amp; economic factors impacting the energy performance of Smart Buildings (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-01</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4045,14 +4045,14 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Il bando BATT4EU richiede capacità di ricerca avanzata nella produzione di materiali per batterie (elettrodi, raffinazione materie prime critiche, biomateriali), ambiti lontani dal tessuto produttivo del Cilento e dalla tipica PMI campana. I requisiti tecnici, la complessità dei consorzi europei richiesti e gli investimenti in R&amp;D necessari rendono questo bando praticamente inaccessibile senza una partnership con università o grandi industrie del settore energetico.</t>
+          <t>Il bando Horizon Built4People richiede la partecipazione a consorzi di ricerca europei con forte componente accademica e tecnologica, strutture progettuali complesse e capacità di R&amp;S difficilmente accessibili a una PMI del Cilento senza un partner universitario o un centro di ricerca. Solo PMI con specifiche competenze in efficienza energetica degli edifici smart potrebbero partecipare come partner secondari, non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Researching the technical, social &amp; economic factors impacting the energy performance of Smart Buildings (Built4People Partnership)</t>
+          <t>Advanced data platforms to integrate whole life carbon in building information tools, assessments, and certification (Built4People Partnership)</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-03</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4092,14 +4092,14 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe Built4People richiede la partecipazione a consorzi internazionali di ricerca con elevata capacità tecnico-scientifica, budget e struttura organizzativa difficilmente sostenibili da una PMI del Cilento. Una piccola impresa edile o impiantistica campana potrebbe partecipare solo come partner junior in un consorzio già formato, con ruolo marginale e bassa probabilità di accesso autonomo ai fondi.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali con capacità di ricerca avanzata su piattaforme dati per il carbonio incorporato negli edifici (whole life carbon e BIM), ambito altamente specializzato difficilmente accessibile a una PMI del Cilento senza solide competenze R&amp;D nel settore costruzioni digitali. I requisiti di co-finanziamento, la complessità burocratica europea e la natura tecnica del progetto lo rendono poco praticabile senza un partner universitario o un grande integratore tecnologico.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Advanced data platforms to integrate whole life carbon in building information tools, assessments, and certification (Built4People Partnership)</t>
+          <t>Full-scale demonstration of heat upgrade solutions in industrial processes</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-08</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4139,14 +4139,14 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione a consorzi internazionali con elevata capacità di ricerca e sviluppo, budget progettuali nell'ordine dei milioni di euro e competenze specialistiche su piattaforme dati e carbon footprint negli edifici: barriere difficilmente superabili per una PMI del Cilento senza un partner accademico o industriale già strutturato. Il focus su Building Information Modelling e ciclo di vita del carbonio nelle costruzioni potrebbe interessare imprese edili innovative, ma l'accesso diretto rimane molto complesso.</t>
+          <t>Il bando Horizon richiede dimostrazioni su scala industriale di tecnologie avanzate per l'aggiornamento termico nei processi produttivi, con requisiti tecnici, consorziali e finanziari difficilmente sostenibili da una PMI del Cilento. È pensato per grandi player industriali o consorzi di ricerca con capacità di co-finanziamento elevate e infrastrutture industriali consolidate.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Full-scale demonstration of heat upgrade solutions in industrial processes</t>
+          <t>European Nuclear Skills Initiative – towards European Nuclear Skills Academy</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-NRT-01-01</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - EURATOM2027</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -4181,19 +4181,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede dimostrazioni su scala industriale di soluzioni avanzate per l'aggiornamento del calore nei processi industriali, con consorzî internazionali e budget elevati tipicamente superiori ai 5-10 milioni di euro: una PMI del Cilento, salvo sia specializzata in tecnologie termiche industriali e abbia già partner europei consolidati, difficilmente può accedere autonomamente a questo tipo di progetto.</t>
+          <t>Il bando EURATOM riguarda esclusivamente il settore nucleare e lo sviluppo di competenze specializzate in ambito energetico nucleare a livello europeo, un settore del tutto assente nel tessuto produttivo del Cilento e della Campania in generale. Una PMI locale non possiede i requisiti tecnici, la filiera di riferimento né i partner istituzionali necessari per accedere a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>European Nuclear Skills Initiative – towards European Nuclear Skills Academy</t>
+          <t>Protection of the euro against counterfeiting</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-NRT-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PERI-2026-ANTI-COUNTERFEIT</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>UE - EURATOM2027</t>
+          <t>UE - PERI</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4228,19 +4228,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM è destinato a sviluppare competenze nel settore nucleare a livello europeo, un ambito altamente specializzato e regolamentato che non ha applicabilità concreta per le PMI del Cilento, territorio privo di infrastrutture o filiere industriali collegate al nucleare. Le risorse sono tipicamente assorbite da grandi enti di ricerca, università e operatori del settore energetico nucleare, rendendo di fatto inaccessibile il bando per una piccola o media impresa campana.</t>
+          <t>Il bando riguarda la protezione dell'euro dalla contraffazione ed è destinato principalmente a forze dell'ordine, istituti finanziari e autorità pubbliche competenti, non a PMI commerciali o produttive del Cilento. Una piccola impresa campana non ha titolo né struttura per partecipare a progetti di questo tipo.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Protection of the euro against counterfeiting</t>
+          <t>Strengthening a European user facility for nuclear research</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PERI-2026-ANTI-COUNTERFEIT</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-04</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>UE - PERI</t>
+          <t>UE - EURATOM2027</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4280,14 +4280,14 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la protezione dell'euro dalla contraffazione e si rivolge principalmente a forze dell'ordine, istituti finanziari e autorità competenti, non a PMI commerciali o produttive. Una piccola impresa del Cilento non ha titolo né struttura per partecipare a progetti di questo tipo.</t>
+          <t>Il bando EURATOM riguarda il potenziamento di infrastrutture di ricerca nucleare a livello europeo, un settore altamente specializzato che richiede competenze tecniche e strutture del tutto estranee alla tipica PMI campana o cilentana. Non esistono spese finanziabili né attività progettuali compatibili con le dimensioni e i settori produttivi prevalenti nel Cilento (turismo, agricoltura, artigianato, piccola manifattura).</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Strengthening a European user facility for nuclear research</t>
+          <t>Co-funded European partnership for research in nuclear materials</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-08</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4327,14 +4327,14 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda il potenziamento di infrastrutture di ricerca nucleare a livello europeo, un settore altamente specializzato accessibile quasi esclusivamente a grandi enti di ricerca, università e laboratori nazionali. Una PMI campana, incluso il territorio del Cilento, non dispone delle competenze tecniche nucleari né della capacità strutturale per partecipare a questo tipo di progetto.</t>
+          <t>Il bando EURATOM riguarda la ricerca avanzata sui materiali nucleari nell'ambito di una partnership europea co-finanziata, un settore altamente specializzato che richiede competenze scientifiche e infrastrutture di ricerca nucleare incompatibili con la realtà delle PMI del Cilento o della Campania in generale. Non sono previste attività finanziabili rilevanti per piccole imprese locali operanti in settori tradizionali o manifatturieri.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Co-funded European partnership for research in nuclear materials</t>
+          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-06</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4374,14 +4374,14 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la ricerca sui materiali nucleari nell'ambito di partnership europee co-finanziate, un settore altamente specializzato che richiede infrastrutture di ricerca avanzate e competenze scientifiche difficilmente riconducibili a una PMI del Cilento. Non esistono filiere produttive o di servizio nel territorio campano di riferimento che possano beneficiare concretamente di questo tipo di finanziamento.</t>
+          <t>Il bando EURATOM riguarda la ricerca sull'energia nucleare e le applicazioni delle radiazioni ionizzanti, settori altamente specializzati che richiedono infrastrutture scientifiche e competenze tecniche inaccessibili a una PMI del Cilento. Non sono finanziabili attività produttive o commerciali tipiche delle piccole imprese del territorio campano.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
+          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-05</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la piattaforma tecnologica per l'energia nucleare sostenibile e le applicazioni non energetiche delle radiazioni ionizzanti, settori altamente specializzati che richiedono competenze scientifiche avanzate e infrastrutture di ricerca nucleare del tutto estranee al tessuto produttivo delle PMI del Cilento e della Campania in generale. Non esistono filiere locali o attività d'impresa tipiche dell'area che possano beneficiare concretamente di questo finanziamento.</t>
+          <t>Il bando EURATOM riguarda la produzione di isotopi stabili per la medicina nucleare, un settore altamente specializzato che richiede infrastrutture nucleari, competenze scientifiche avanzate e certificazioni specifiche del tutto inaccessibili a una PMI del Cilento o della Campania in generale. Non sono previste tipologie di spesa o attività compatibili con le capacità operative di una piccola o media impresa del territorio.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
+          <t>Enhancing the European nuclear competence  area</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-03</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4468,14 +4468,14 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la produzione di isotopi stabili per terapie di medicina nucleare avanzata, un settore altamente specializzato che richiede infrastrutture di ricerca nucleare e competenze scientifiche difficilmente reperibili in una PMI del Cilento o della Campania in generale. Le risorse finanziabili sono orientate a grandi consorzi di ricerca, laboratori nucleari e istituzioni accademiche, rendendo l'accesso praticamente inaccessibile per una piccola o media impresa locale.</t>
+          <t>Il bando EURATOM riguarda esclusivamente il settore nucleare (ricerca, formazione e competenze in ambito energia nucleare), un dominio del tutto estraneo al tessuto produttivo del Cilento e della Campania, dove non esistono impianti né filiere industriali nucleari. Una PMI locale non possiede i requisiti tecnici, scientifici o strutturali per partecipare competitivamente a questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the European nuclear competence  area</t>
+          <t>Safety of operating nuclear power plants and research reactors</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-01</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM è focalizzato sul settore nucleare europeo, un ambito altamente specializzato che non ha alcuna rilevanza per le PMI del Cilento o della Campania in generale, regione priva di infrastrutture o filiere industriali nucleari. I requisiti tecnici e scientifici richiesti rendono di fatto inaccessibile questo tipo di finanziamento per qualsiasi piccola o media impresa del territorio.</t>
+          <t>Il bando EURATOM riguarda esclusivamente la sicurezza di reattori nucleari e reattori di ricerca, un settore altamente specializzato che non ha applicabilità per una PMI campana o del Cilento, territorio privo di infrastrutture nucleari e con un tessuto produttivo orientato a turismo, agricoltura e agroalimentare. I requisiti tecnici e istituzionali richiesti escludono di fatto qualsiasi piccola o media impresa generalista.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Safety of operating nuclear power plants and research reactors</t>
+          <t>European Partnership for research in radiation protection and detection of ionising radiation</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-09</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4557,19 +4557,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda esclusivamente la sicurezza di reattori nucleari e impianti di ricerca, un settore altamente specializzato che non ha applicabilità per le PMI campane e del Cilento, territorio privo di infrastrutture nucleari e con economia basata su turismo, agricoltura e servizi. I requisiti tecnici e istituzionali richiesti escludono di fatto qualsiasi piccola o media impresa locale.</t>
+          <t>Il bando EURATOM riguarda la ricerca sulla protezione dalle radiazioni ionizzanti e richiede capacità di ricerca nucleare specializzata, strutture tecniche avanzate e partnership europee consolidate, caratteristiche lontane dal profilo tipico di una PMI campana del Cilento. L'accesso è di fatto riservato a grandi enti di ricerca, università o aziende del settore nucleare/medicale strutturate.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>European Partnership for research in radiation protection and detection of ionising radiation</t>
+          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-09</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-02</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -4604,19 +4604,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la ricerca avanzata sulla protezione dalle radiazioni ionizzanti e richiede competenze scientifiche altamente specializzate, strutture di ricerca accreditate e partnership europee consolidate, requisiti difficilmente soddisfabili da una PMI del Cilento non operante nel settore nucleare o radiologico. Le PMI campane non specializzate in fisica delle radiazioni, dosimetria o tecnologie di rilevamento non hanno concreta possibilità di accesso diretto a questo tipo di partenariato europeo.</t>
+          <t>Il bando EURATOM riguarda la sicurezza dei reattori nucleari SMR e combustibili avanzati, un settore altamente specializzato che richiede competenze nucleari certificate e strutture di ricerca avanzate, del tutto estranee al tessuto produttivo delle PMI campane e del Cilento, prevalentemente orientato verso agroalimentare, turismo e artigianato. Non esistono beneficiari plausibili in questo territorio per attività di ricerca nucleare finanziabili da questo programma.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
+          <t>Raising awareness of and building capacity for the EU Charter of Fundamental Rights</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CHARTER</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>UE - EURATOM2027</t>
+          <t>UE - CERV</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -4651,19 +4651,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Il bando EURATOM riguarda la ricerca sulla sicurezza dei reattori nucleari SMR e combustibili avanzati, un settore altamente specializzato che richiede competenze nucleari certificate e infrastrutture di ricerca dedicate, del tutto estranee al tessuto produttivo delle PMI campane e del Cilento. Non esistono beneficiari plausibili in questo territorio per un programma di ricerca nucleare europeo.</t>
+          <t>Il bando CERV è orientato principalmente a organizzazioni della società civile, enti pubblici e istituzioni educative per attività di sensibilizzazione sui diritti fondamentali UE, non a PMI commerciali. Una piccola impresa del Cilento non troverebbe finanziamenti per attività produttive o di sviluppo aziendale, e la rendicontazione europea richiede strutture amministrative difficilmente sostenibili per una PMI di piccole dimensioni.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Raising awareness of and building capacity for the EU Charter of Fundamental Rights</t>
+          <t>Promoting an enabling civic space</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CHARTER</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CIVIC</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -4698,19 +4698,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Il bando CERV è orientato principalmente a organizzazioni della società civile, enti pubblici e ONG impegnati nella promozione dei diritti fondamentali UE, non a PMI con attività commerciali. Una piccola impresa del Cilento difficilmente soddisfa i requisiti di eleggibilità e non trae vantaggi competitivi diretti dalle attività finanziabili (sensibilizzazione, capacity building sui diritti).</t>
+          <t>Il programma CERV (Citizens, Equality, Rights and Values) finanzia progetti su democrazia, cittadinanza attiva e spazio civico, destinati principalmente a organizzazioni della società civile, enti pubblici e ONG, non a PMI con finalità commerciali. Una PMI del Cilento non troverebbe linee di spesa coerenti con attività produttive o di sviluppo aziendale.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Promoting an enabling civic space</t>
+          <t>Safety of operating nuclear power plants and research reactors</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4720,17 +4720,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CIVIC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-01</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>UE - CERV</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -4750,14 +4750,14 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Il programma CERV (Citizens, Equality, Rights and Values) finanzia principalmente organizzazioni della società civile, enti pubblici e ONG impegnate nella promozione dei valori democratici e dei diritti civili, non PMI commerciali. Una piccola impresa del Cilento non rientra nei beneficiari tipici e difficilmente soddisfa i requisiti tematici e istituzionali richiesti.</t>
+          <t>Il bando riguarda esclusivamente la sicurezza di reattori nucleari operativi e reattori di ricerca, un settore altamente specializzato senza alcuna rilevanza per il tessuto produttivo del Cilento o della Campania, dove non esistono impianti nucleari né PMI attive in questo ambito. I requisiti tecnici e i partner necessari (enti nucleari, laboratori di ricerca avanzata) sono inaccessibili per una PMI di piccola o media dimensione.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Safety of operating nuclear power plants and research reactors</t>
+          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-06</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la sicurezza di reattori nucleari e reattori di ricerca, un settore altamente specializzato che non ha applicabilità concreta per una PMI campana del Cilento, territorio a vocazione agricola e turistica privo di infrastrutture nucleari. Le competenze richieste e i costi di partecipazione a progetti Horizon di questo tipo sono inaccessibili per una piccola o media impresa locale.</t>
+          <t>Il bando riguarda la tecnologia nucleare sostenibile e le applicazioni delle radiazioni ionizzanti, settori altamente specializzati che richiedono competenze scientifiche avanzate e infrastrutture di ricerca difficilmente accessibili a una PMI del Cilento o della Campania in generale. Non è destinato a piccole imprese tradizionali, ma a grandi consorzi di ricerca, università e operatori del settore energetico nucleare.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Support for the Sustainable Nuclear Energy Technology Platform to address cross-sectoral challenges and non-power applications of ionising radiation</t>
+          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-05</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -4844,14 +4844,14 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la piattaforma tecnologica per l'energia nucleare sostenibile e le applicazioni delle radiazioni ionizzanti, settori altamente specializzati che richiedono competenze tecnico-scientifiche avanzate e infrastrutture di ricerca difficilmente disponibili per una PMI del Cilento. L'accesso è praticamente riservato a grandi centri di ricerca, università o consorzi industriali operanti nel nucleare, escludendo di fatto le piccole imprese locali.</t>
+          <t>Il bando riguarda la produzione europea di isotopi stabili per terapie di medicina nucleare avanzata, un settore altamente specializzato che richiede infrastrutture scientifiche e competenze tecniche difficilmente presenti in una PMI del Cilento. L'accesso è realisticamente limitato a grandi centri di ricerca, laboratori nucleari o aziende farmaceutiche ad alta tecnologia, escludendo di fatto le piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Towards a European production of stable isotopes for novel nuclear medicine therapies (SAMIRA/ERVI)</t>
+          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-02</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -4891,29 +4891,29 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon SAMIRA/ERVI riguarda la produzione europea di isotopi stabili per terapie di medicina nucleare avanzata, richiedendo infrastrutture scientifiche specializzate, laboratori nucleari certificati e competenze altamente specifiche del tutto estranee al tessuto produttivo di una PMI campana del Cilento. L'accesso è di fatto riservato a grandi centri di ricerca, ospedali universitari o aziende del settore farmaceutico-nucleare con capacità tecniche e finanziarie incompatibili con le dimensioni di una piccola o media impresa locale.</t>
+          <t>Il bando riguarda la sicurezza dei reattori nucleari di nuova generazione (SMR) e dei combustibili avanzati, un settore altamente specializzato che richiede competenze tecniche nucleari e strutture di ricerca difficilmente presenti in una PMI campana del Cilento. Le risorse finanziabili sono orientate a consorzi di ricerca europei con expertise nucleare certificata, escludendo di fatto le imprese di piccola-media dimensione operanti in territori a vocazione rurale o turistica.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Safety of SMRs, advanced and innovative nuclear reactors and fuels</t>
+          <t>EIC Transition Open</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EURATOM-LS-2026-01-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-TRANSITIONOPEN</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -4938,14 +4938,14 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la sicurezza dei reattori nucleari SMR e combustibili avanzati, un settore altamente specializzato che richiede competenze tecnologiche nucleari e infrastrutture di ricerca inaccessibili per una PMI campana, specialmente nel Cilento dove non esistono filiere industriali collegate al nucleare. Le PMI di piccola dimensione non dispongono delle certificazioni, dei laboratori e dei partner istituzionali necessari per partecipare a progetti di questa complessità tecnica e regolatoria.</t>
+          <t>L'EIC Transition è destinato a progetti di ricerca e innovazione tecnologica ad alto rischio con budget elevati (fino a 2,5 milioni di euro) e richiede competenze scientifiche avanzate, partnership con enti di ricerca e una proposta di proof-of-concept, requisiti difficilmente accessibili per una PMI di piccole dimensioni del Cilento senza una solida base R&amp;S. Il bando è competitivo a livello europeo e premia tecnologie deep-tech lontane dal mercato, contesti tipicamente estranei al tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>EIC Transition Open</t>
+          <t>Supporting digitalisation of Distribution System Operators for a smart energy transition (Smart Grid Academy)</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4955,17 +4955,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-TRANSITIONOPEN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-DIGITAL</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4980,19 +4980,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>EIC Transition finanzia progetti di trasferimento tecnologico da TRL 3-4 a TRL 5-6, richiedendo una solida base di ricerca pregressa (es. risultati da progetti ERC o FET) e capacità tecnico-scientifiche elevate che raramente una PMI del Cilento possiede autonomamente. I budget tipicamente superiori a 1-2 milioni di euro e la complessità procedurale del programma Horizon Europe lo rendono poco accessibile senza un partner di ricerca strutturato.</t>
+          <t>Il bando LIFE 2027 è orientato a soggetti come DSO (Distribution System Operators) e grandi operatori del settore energetico per sviluppare smart grid e competenze digitali nella transizione energetica: una PMI campana del Cilento difficilmente possiede i requisiti tecnici e dimensionali per candidarsi come capofila o partner rilevante. Le attività finanziabili riguardano formazione e digitalizzazione delle reti di distribuzione, ambito quasi esclusivo di utility pubbliche o grandi aziende energetiche.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Supporting digitalisation of Distribution System Operators for a smart energy transition (Smart Grid Academy)</t>
+          <t>Scaling up smart and clean energy solutions for affordability in EU cities</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-DIGITAL</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-EMPOWER</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5027,19 +5027,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 2027 è orientato a supportare i Gestori di Reti di Distribuzione (DSO) per la transizione verso smart grid, ovvero grandi operatori del settore energetico regolamentato, non PMI generiche. Una piccola o media impresa del Cilento non rientra nella tipologia di beneficiario prevista, a meno che non operi specificamente come fornitore tecnologico o partner di un DSO in un progetto consortile strutturato.</t>
+          <t>Il bando LIFE 2027 è orientato a progetti su scala urbana e di sistema per soluzioni energetiche pulite nelle città europee, con budget e requisiti progettuali che richiedono consorzi istituzionali o grandi soggetti. Una PMI del Cilento, territorio prevalentemente rurale, difficilmente soddisfa i criteri di scala e partenariato richiesti, salvo come partner minore in un consorzio guidato da enti pubblici o grandi operatori energetici.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Scaling up smart and clean energy solutions for affordability in EU cities</t>
+          <t>Supporting the delivery of actionable, integrated, and comprehensive local heating and cooling plans</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-EMPOWER</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-HEATCOOLPLAN</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5079,14 +5079,14 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a progetti di scala urbana e sistemica su energia pulita e accessibile nelle città EU, richiedendo partenariati complessi e capacità progettuali elevate che difficilmente una PMI del Cilento può sostenere autonomamente. Il territorio cilentano, prevalentemente rurale e a bassa densità urbana, non rientra nel profilo target di intervento previsto dal programma.</t>
+          <t>Il bando LIFE è orientato a enti pubblici, autorità locali e organismi di pianificazione territoriale per la redazione di piani integrati di riscaldamento e raffreddamento urbano, non a PMI private. Una piccola impresa del Cilento difficilmente possiede i requisiti tecnici e istituzionali per candidarsi come lead partner, potendo al massimo partecipare come partner secondario in un consorzio guidato da un ente pubblico.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Supporting the delivery of actionable, integrated, and comprehensive local heating and cooling plans</t>
+          <t>One-Stop-Shops - Integrated services for clean energy transition in private buildings</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-HEATCOOLPLAN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-OSS</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5126,14 +5126,14 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE richiede la redazione di piani locali integrati per il riscaldamento e il raffreddamento, un'attività tipicamente rivolta a enti pubblici, autorità locali o grandi consorzi energetici, non a PMI. Una piccola impresa del Cilento difficilmente dispone delle competenze tecniche, della struttura organizzativa e della capacità di co-finanziamento necessarie per guidare o partecipare come capofila in progetti di questo tipo.</t>
+          <t>Il bando LIFE finanzia la creazione di sportelli integrati ('one-stop-shop') per accompagnare la transizione energetica negli edifici privati, un modello pensato per consorzi, enti pubblici o grandi aggregazioni, non per singole PMI. Una piccola impresa del Cilento difficilmente possiede la capacità progettuale e finanziaria per guidare un'iniziativa di scala europea richiesta da LIFE.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>One-Stop-Shops - Integrated services for clean energy transition in private buildings</t>
+          <t>Energy renovation solutions – Boosting building renovation through effective markets and instruments</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-OSS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BETTERRENO</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5173,14 +5173,14 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE finanzia progetti di sistema per la creazione di sportelli integrati (One-Stop-Shops) dedicati alla transizione energetica negli edifici privati, richiedendo partnership complesse e capacità progettuali europee difficilmente accessibili a una PMI del Cilento in modo autonomo. Una piccola impresa potrebbe partecipare solo come partner secondario di un consorzio più strutturato, ruolo che richiede comunque competenze specifiche in efficienza energetica e gestione di progetti UE.</t>
+          <t>Il programma LIFE è orientato a progetti dimostrativi su scala europea con budget elevati e partnership istituzionali complesse, rendendolo difficilmente accessibile a una PMI del Cilento senza un consorzio strutturato. Una piccola impresa edile o energetica locale potrebbe partecipare solo come partner tecnico in un progetto guidato da enti di ricerca o pubblici, con ruolo marginale nella gestione dei fondi.</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Energy renovation solutions – Boosting building renovation through effective markets and instruments</t>
+          <t>Towards an effective implementation of key legislation in the field of sustainable energy</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BETTERRENO</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-POLICY</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5220,14 +5220,14 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti dimostrativi su larga scala promossi da consorzi pubblico-privati con elevata capacità progettuale e finanziaria; una PMI del Cilento difficilmente può accedere autonomamente, potendo al più partecipare come partner di un ente capofila. Il focus sulla renovazione energetica degli edifici potrebbe coinvolgere imprese edili o di efficienza energetica, ma la complessità burocratica e i requisiti UE rendono l'accesso diretto poco praticabile per una piccola impresa.</t>
+          <t>Il programma LIFE è orientato a enti pubblici, ONG e organismi di ricerca per attività di capacity building normativo sull'energia sostenibile, con procedure di candidatura complesse e budget elevati difficilmente accessibili a una PMI del Cilento senza un partenariato strutturato. Una piccola impresa campana avrebbe scarsa competitività rispetto a soggetti istituzionali europei con esperienza consolidata in progetti LIFE.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Towards an effective implementation of key legislation in the field of sustainable energy</t>
+          <t>Alleviating household energy poverty in Europe</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-POLICY</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERPOV</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5267,14 +5267,14 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, associazioni e grandi organizzatori di progetti europei; una PMI del Cilento difficilmente dispone delle capacità amministrative e del co-finanziamento richiesto per guidare o partecipare autonomamente a un progetto focalizzato sull'implementazione normativa in materia di energia sostenibile. L'accesso realistico sarebbe solo come partner minore in un consorzio già formato.</t>
+          <t>Il programma LIFE è orientato a progetti dimostrativi su scala europea con requisiti di partenariato transnazionale e budget elevati, difficilmente accessibili a una PMI autonomamente; il focus sulla povertà energetica domestica riguarda principalmente enti pubblici, utility e organizzazioni no-profit, rendendo marginale il ruolo diretto di una piccola impresa del Cilento salvo in qualità di partner tecnico specializzato in efficienza energetica o edilizia.</t>
         </is>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Alleviating household energy poverty in Europe</t>
+          <t>Strengthening national frameworks for renewable and efficient heating and cooling in existing buildings</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERPOV</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-RENEWHC</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5314,14 +5314,14 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è strutturalmente orientato a enti pubblici, ONG e organismi di ricerca; una PMI del Cilento difficilmente possiede la capacità progettuale e i requisiti di partenariato transnazionale richiesti per affrontare tematiche di povertà energetica domestica a scala europea. L'accesso diretto come capofila è quasi impraticabile, mentre il ruolo di partner risulta marginale e poco remunerativo per una piccola impresa.</t>
+          <t>Il bando LIFE è orientato a soggetti istituzionali e organismi di ricerca per lo sviluppo di framework normativi nazionali sul riscaldamento/raffrescamento rinnovabile negli edifici esistenti, non a PMI operative. Una piccola impresa del Cilento, anche nel settore edile o impiantistico, difficilmente possiede la struttura progettuale e i requisiti per candidarsi direttamente a bandi LIFE di questa natura.</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Strengthening national frameworks for renewable and efficient heating and cooling in existing buildings</t>
+          <t>BUILD UP Skills - National Platforms on energy efficiency skills for the clean energy transition</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-RENEWHC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BUILDSKILLS</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5356,19 +5356,19 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a enti pubblici, istituti di ricerca e organizzazioni no-profit per lo sviluppo di framework normativi nazionali sul riscaldamento/raffreddamento rinnovabile negli edifici esistenti: una PMI campana, anche operante nel settore edilizio o energetico del Cilento, difficilmente può candidarsi come soggetto capofila e troverebbe scarsa applicabilità diretta senza un consorzio strutturato con partner istituzionali.</t>
+          <t>Il bando BUILD UP Skills è orientato alla costruzione di piattaforme nazionali per la formazione professionale nell'efficienza energetica, tipicamente rivolto a enti pubblici, associazioni di categoria o grandi consorzi, non a singole PMI. Una piccola impresa edile o impiantistica del Cilento difficilmente può candidarsi direttamente, anche se potrebbe beneficiarne indirettamente come destinataria delle attività formative finanziate.</t>
         </is>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>BUILD UP Skills - National Platforms on energy efficiency skills for the clean energy transition</t>
+          <t>Crowding in private finance</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-BUILDSKILLS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PRIVAFIN</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5403,19 +5403,19 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Credito/Finanza</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Il bando BUILD UP Skills è orientato alla creazione di piattaforme nazionali per la formazione nel settore dell'efficienza energetica nell'edilizia, rivolgendosi tipicamente a enti di formazione, associazioni di categoria e soggetti istituzionali piuttosto che a singole PMI. Una piccola impresa del Cilento difficilmente ha la struttura progettuale e il profilo richiesto per candidarsi direttamente, pur potendo beneficiare indirettamente dei percorsi formativi che ne derivano.</t>
+          <t>Il bando LIFE 'Crowding in private finance' è orientato a strumenti finanziari innovativi e meccanismi di blending per attrarre capitali privati su progetti ambientali su larga scala, destinato principalmente a intermediari finanziari, fondi e istituzioni, non a PMI singole. Una piccola impresa del Cilento difficilmente soddisfa i requisiti dimensionali e tecnici richiesti per candidarsi direttamente.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Crowding in private finance</t>
+          <t>Facilitating cooperation among energy communities</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PRIVAFIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERCOM</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5450,19 +5450,19 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Credito/Finanza</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 'Crowding in private finance' è orientato a strumenti finanziari e meccanismi di blending capital per attirare investimenti privati su progetti ambientali su larga scala, rivolgendosi tipicamente a intermediari finanziari, fondi e grandi operatori istituzionali. Una PMI del Cilento difficilmente accede direttamente a questo tipo di strumento, che non finanzia attività produttive ordinarie ma meccanismi di leva finanziaria complessi.</t>
+          <t>Il bando LIFE è orientato a progetti transnazionali di cooperazione tra comunità energetiche, richiedendo capacità progettuali elevate, partenariati internazionali e cofinanziamento significativo, barriere difficilmente superabili per una PMI del Cilento. Una piccola impresa campana potrebbe al massimo partecipare come partner secondario in un consorzio già strutturato, ma difficilmente come capofila.</t>
         </is>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Facilitating cooperation among energy communities</t>
+          <t>Supporting the clean energy transition of European industry and businesses</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-ENERCOM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-INDUSTRY</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5502,14 +5502,14 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a progetti complessi di cooperazione tra comunità energetiche, con requisiti tecnici e finanziari elevati tipicamente accessibili a consorzi, enti pubblici o grandi organizzazioni; una PMI del Cilento potrebbe partecipare solo in qualità di partner secondario in un consorzio strutturato, non come capofila autonomo.</t>
+          <t>Il programma LIFE è orientato a progetti di scala europea con requisiti tecnici e amministrativi complessi, budget elevati e necessità di partenariati internazionali, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza il supporto di enti di ricerca o grandi organizzatori. Le PMI potrebbero partecipare solo come partner secondari in consorzi già strutturati, non come soggetti capofila.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Supporting the clean energy transition of European industry and businesses</t>
+          <t>Project Development Assistance for sustainable energy investments</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-INDUSTRY</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PDA</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5549,14 +5549,14 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti di scala europea con forte componente dimostrativa e partenariati transnazionali, richiedendo capacità progettuali e cofinanziamenti difficilmente gestibili da una PMI del Cilento senza un consorzio strutturato. Le spese finanziabili riguardano transizione energetica pulita nell'industria, settore rilevante ma con procedure competitive complesse e budget minimi elevati che penalizzano le piccole imprese locali.</t>
+          <t>Il bando LIFE PDA (Project Development Assistance) è orientato a supportare la strutturazione di progetti complessi di investimento in energia sostenibile, con iter tecnico-amministrativi adatti a enti pubblici o grandi aggregazioni, non a singole PMI. Una piccola impresa del Cilento avrebbe difficoltà a soddisfare i requisiti di scala e capacità progettuale richiesti.</t>
         </is>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Project Development Assistance for sustainable energy investments</t>
+          <t>RFCS-2026-01-RPJ Coal Research projects</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-CET-PDA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-RPJ</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - RFCS2027</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -5591,19 +5591,19 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE PDA è orientato a supportare lo sviluppo di progetti complessi di investimento in energia sostenibile, tipicamente rivolto a enti pubblici, utility o grandi organizzazioni con capacità progettuale strutturata; per una PMI del Cilento risulta difficilmente accessibile per gli elevati requisiti tecnico-amministrativi e la complessità della rendicontazione europea diretta.</t>
+          <t>Il bando RFCS finanzia esclusivamente ricerca nel settore carbonifero e dell'acciaio a livello europeo, richiedendo consorzi internazionali e competenze tecnico-scientifiche altamente specializzate: nessuna PMI del Cilento opera in questo settore estrattivo. Le risorse finanziabili riguardano R&amp;S su carbone e coke, ambito del tutto estraneo al tessuto produttivo campano e cilentano.</t>
         </is>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-RPJ Coal Research projects</t>
+          <t>RFCS-2026-01-AM Coal Accompanying measures</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-RPJ</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-AM</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -5643,14 +5643,14 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia esclusivamente ricerca tecnica nel settore carbonifero (estrazione, utilizzo e trasformazione del carbone), un comparto industriale assente nel Cilento e marginale in Campania. Una PMI locale non ha i requisiti tecnici né il settore di attività compatibile per accedere a questi fondi europei altamente specializzati.</t>
+          <t>Il bando RFCS riguarda misure di accompagnamento per le regioni carbonifere europee in transizione, destinato principalmente a grandi enti di ricerca, università e autorità pubbliche, non a PMI generiche. Il Cilento e la Campania non hanno un tessuto industriale legato al carbone, rendendo questo bando sostanzialmente inaccessibile e irrilevante per una PMI locale.</t>
         </is>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-AM Coal Accompanying measures</t>
+          <t>RFCS-2026-02-AM Steel Accompanying measures</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-AM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-AM</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -5690,14 +5690,14 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS riguarda misure di accompagnamento per le regioni carbonifere europee in fase di transizione, con focus su ricerca industriale e studi tecnici legati all'industria del carbone: la Campania e il Cilento non hanno un tessuto produttivo carbonifero rilevante, rendendo questo bando sostanzialmente inaccessibile per una PMI locale. Inoltre i progetti RFCS richiedono consorzi di ricerca transnazionali e capacità progettuali elevate, poco compatibili con le dimensioni di una PMI del territorio.</t>
+          <t>Il bando RFCS riguarda misure di accompagnamento per il settore siderurgico europeo (ricerca, formazione, riconversione) ed è destinato principalmente a grandi consorzi industriali, centri di ricerca e associazioni di categoria del comparto acciaio. Una PMI del Cilento, territorio a vocazione turistica e agricola, non opera nel settore siderurgico e difficilmente soddisfa i requisiti tecnici e partenariali richiesti da questo tipo di call europea.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-AM Steel Accompanying measures</t>
+          <t>RFCS-2026-02-RPJ Steel Research projects</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-AM</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-RPJ</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -5732,19 +5732,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS riguarda misure di accompagnamento per il settore siderurgico europeo (ricerca, formazione, riconversione lavoratori dell'acciaio) e si rivolge principalmente a grandi consorzi industriali, centri di ricerca e associazioni di categoria del comparto metallurgico. Una PMI del Cilento, territorio a vocazione turistico-agricola, non opera in questo settore e difficilmente soddisfa i requisiti tecnici e dimensionali richiesti.</t>
+          <t>Il bando RFCS finanzia esclusivamente ricerca nel settore siderurgico (acciaio e carbone) con progetti di grande scala in consorzio europeo, richiedendo competenze tecnico-scientifiche specializzate e strutture di ricerca dedicate. Una PMI campana del Cilento, tipicamente attiva in settori come turismo, agricoltura o artigianato, non ha i requisiti tecnici né la massa critica per partecipare competitivamente a questo tipo di call.</t>
         </is>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-RPJ Steel Research projects</t>
+          <t>RFCS-2026-02-PDP Steel Pilot and demonstration projects</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-RPJ</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-PDP</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5784,14 +5784,14 @@
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia esclusivamente ricerca nel settore siderurgico (produzione e trasformazione dell'acciaio) a livello europeo, richiedendo consorzi internazionali e capacità di ricerca industriale avanzata. Una PMI del Cilento, territorio a vocazione agricola, turistica e agroalimentare, non ha i requisiti tecnici né il profilo settoriale per partecipare competitivamente.</t>
+          <t>Il bando RFCS finanzia progetti pilota e dimostrativi nel settore siderurgico europeo, richiedendo consorzi di ricerca con competenze altamente specializzate e capacità industriali legate all'acciaio: una PMI campana del Cilento, territorio a vocazione turistica e agricola, non ha quasi nessuna possibilità concreta di partecipazione per mancanza di settore produttivo pertinente e di massa critica tecnico-finanziaria richiesta.</t>
         </is>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-02-PDP Steel Pilot and demonstration projects</t>
+          <t>RFCS-2026-01-PDP Coal Pilot and demonstration projects</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-02-PDP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-PDP</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5831,14 +5831,14 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia progetti pilota e di dimostrazione nel settore siderurgico (acciaio) con budget tipicamente superiori ai 2-3 milioni di euro, richiedendo consorzi industriali di grandi dimensioni e competenze di ricerca avanzata. Una PMI del Cilento, territorio a vocazione turistica e agricola, non ha praticamente possibilità di accesso né rilevanza settoriale rispetto a questo programma europeo dedicato all'industria pesante dell'acciaio.</t>
+          <t>Il bando RFCS finanzia progetti pilota e dimostrativi nel settore carbonifero (estrazione, utilizzo pulito del carbone), un comparto industriale del tutto assente nel Cilento e marginale in Campania, rendendo questo bando di fatto inaccessibile per una PMI locale. Inoltre, i progetti RFCS richiedono tipicamente consorzi di ricerca con competenze altamente specializzate e budget elevati, inadatti alla dimensione di una PMI di piccola-media taglia.</t>
         </is>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-01-PDP Coal Pilot and demonstration projects</t>
+          <t>RFCS-2026-Steel-Big Tickets under the steel and metals action plan dual-use</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-01-PDP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-BT-STEEL-SMAP-DUAL-USE</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5878,34 +5878,34 @@
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS finanzia progetti pilota e dimostrativi legati alle tecnologie del carbone e dell'acciaio, settori industriali pesanti del tutto estranei al tessuto produttivo del Cilento e della Campania in generale, dove dominano turismo, agricoltura e PMI di servizi. I requisiti tecnici e le dimensioni dei consorzi richiesti rendono questo bando di fatto inaccessibile per una PMI locale di piccola o media dimensione.</t>
+          <t>Il bando RFCS finanzia ricerca e innovazione nel settore siderurgico e metallurgico con progetti di grande scala ('Big Tickets'), richiedendo consorzi internazionali e capacità di ricerca industriale avanzata del tutto incompatibili con le dimensioni e il profilo produttivo di una PMI del Cilento, area a vocazione turistica e agricola priva di un tessuto manifatturiero pesante.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>RFCS-2026-Steel-Big Tickets under the steel and metals action plan dual-use</t>
+          <t>European mini-slate development</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/RFCS-2026-BT-STEEL-SMAP-DUAL-USE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-DEVMINISLATE</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>UE - RFCS2027</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5920,19 +5920,19 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Il bando RFCS è destinato a grandi progetti di ricerca nel settore siderurgico e dei metalli, con budget elevati e requisiti tecnici complessi tipicamente alla portata di grandi industrie, centri di ricerca e consorzi internazionali. Una PMI del Cilento, territorio a vocazione turistica e agricola, difficilmente opera nel comparto dell'acciaio con la capacità progettuale e finanziaria richiesta da un 'Big Ticket' europeo.</t>
+          <t>Il bando CREA2027 'European mini-slate development' è orientato a progetti di sviluppo di cataloghi audiovisivi europei (mini-slate), richiedendo capacità produttive, track record internazionale e partnership transnazionali difficilmente accessibili a una PMI del Cilento non operante nel settore creativo-audiovisivo. Le spese finanziabili riguardano sviluppo di contenuti audiovisivi, sceneggiature e packaging di progetti, ambiti estranei alla tipica struttura produttiva delle PMI campane del territorio.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>European mini-slate development</t>
+          <t>Toward a comprehensive assessment of the disturbance of marine ecosystems by anthropogenic underwater noise</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5942,17 +5942,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-DEVMINISLATE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-01</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5967,19 +5967,19 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Il bando CREA2027 'European mini-slate development' è orientato alla produzione audiovisiva e allo sviluppo di slate cinematografiche a livello europeo, richiedendo capacità produttive, network internazionali e track record nel settore creativo difficilmente compatibili con una PMI generica del Cilento. Le spese finanziabili riguardano sviluppo di progetti audiovisivi e non attività tipiche del tessuto produttivo locale.</t>
+          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sul rumore sottomarino e impatto sugli ecosistemi marini, con iter progettuali complessi e partnership europee difficilmente accessibili a una PMI campana senza struttura R&amp;D dedicata. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario se opera nel settore della tecnologia marina o del monitoraggio ambientale, ma non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Toward a comprehensive assessment of the disturbance of marine ecosystems by anthropogenic underwater noise</t>
+          <t>Improving circularity of multilayer flexible plastic food contact packaging</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-01</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6014,19 +6014,19 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca scientifica sul rumore sottomarino antropogenico negli ecosistemi marini, destinato principalmente a enti di ricerca e università, con requisiti consortili complessi e capacità di rendicontazione europea difficilmente gestibili da una PMI campana di piccole dimensioni. Sebbene il Cilento abbia una costa marina rilevante, una PMI locale non possiede le competenze tecnico-scientifiche né la struttura amministrativa per partecipare autonomamente a questo tipo di progetto Horizon.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzio internazionale e focus specifico su imballaggi plastici multistrato per alimenti, ambito molto tecnico e di nicchia che difficilmente corrisponde al profilo produttivo di una PMI del Cilento. I requisiti burocratici e la competizione europea lo rendono quasi inaccessibile senza un partner universitario o un grande coordinatore di progetto.</t>
         </is>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Improving circularity of multilayer flexible plastic food contact packaging</t>
+          <t>Supporting pre-normative research for standardization of the bio-based products</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-08</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6066,14 +6066,14 @@
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzio internazionale e budget elevati, rendendo l'accesso diretto quasi impossibile per una PMI del Cilento; solo aziende del settore imballaggio alimentare con laboratori R&amp;D strutturati potrebbero partecipare come partner junior in un consorzio europeo più ampio.</t>
+          <t>Il bando Horizon finanzia ricerca pre-normativa sulla standardizzazione dei prodotti bio-based, richiedendo capacità di ricerca avanzata e partnership con enti di ricerca europei, strutture difficilmente accessibili per una PMI di piccola dimensione del Cilento. Sebbene il territorio presenti filiere agricole e agroalimentari compatibili con i bio-based products, la complessità gestionale e i requisiti tecnici di un progetto Horizon lo rendono concreto solo per PMI con già consolidata esperienza in R&amp;S e reti internazionali.</t>
         </is>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Supporting pre-normative research for standardization of the bio-based products</t>
+          <t>Understanding biomass flows in Europe</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-05</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6113,14 +6113,14 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca pre-normativa sulla standardizzazione dei prodotti bio-based, richiedendo capacità di ricerca avanzata e partnership con enti di ricerca europei, strutture tipicamente fuori portata per una PMI cilentana di piccola dimensione. Una PMI agricola o agroalimentare del Cilento potrebbe al massimo partecipare come partner secondario, ma la complessità progettuale e i requisiti tecnici rendono l'accesso diretto estremamente difficile.</t>
+          <t>Il bando Horizon EU sulla mappatura dei flussi di biomassa in Europa è orientato a consorzi di ricerca accademica e grandi enti scientifici, richiedendo competenze altamente specializzate e capacità progettuali complesse difficilmente accessibili a una PMI del Cilento. Una piccola impresa agricola o forestale locale non troverebbe un canale diretto di partecipazione né finanziamenti operativi immediati per la propria attività.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Understanding biomass flows in Europe</t>
+          <t>Developing methods to assess the presence, functions and sensitivity of groundwater ecosystems</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-02</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6160,14 +6160,14 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla mappatura dei flussi di biomassa è orientato a consorzi di ricerca accademica e grandi enti scientifici internazionali, rendendo l'accesso diretto a una PMI del Cilento estremamente difficile senza un ruolo marginale in un consorzio già strutturato. Una PMI agricola o forestale del territorio potrebbe al massimo partecipare come partner associato, ma senza finanziamento diretto e con oneri burocratici sproporzionati rispetto ai benefici.</t>
+          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sugli ecosistemi delle acque sotterranee, tipicamente accessibile a università, enti di ricerca o grandi consorzi, rendendo molto difficile la partecipazione diretta di una PMI campana senza un solido track record in R&amp;D idrogeologico. Sebbene il Cilento, con le sue risorse idriche del Parco Nazionale, potrebbe offrire un contesto territoriale rilevante, una PMI difficilmente possiede le competenze tecniche e la struttura progettuale necessarie per candidarsi autonomamente.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Developing methods to assess the presence, functions and sensitivity of groundwater ecosystems</t>
+          <t>Advanced recovery of critical raw materials from Waste from Electrical and Electronic Equipment (WEEE)</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-03</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6207,14 +6207,14 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca scientifica avanzata sugli ecosistemi delle acque sotterranee, con consorzio europeo e rendicontazione complessa, strutturalmente adatto a università e centri di ricerca piuttosto che a PMI. Una piccola impresa del Cilento potrebbe partecipare solo in qualità di partner tecnico specializzato (es. monitoraggio ambientale, strumentazione), ruolo difficilmente accessibile senza precedente esperienza in progetti europei H2020/Horizon.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata sul recupero di materie prime critiche dai RAEE, con consorzи internazionali e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. L'onere progettuale, la competizione europea e l'assenza di focus territoriale rendono questo strumento sostanzialmente inaccessibile per realtà produttive locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Advanced recovery of critical raw materials from Waste from Electrical and Electronic Equipment (WEEE)</t>
+          <t>Understanding and tackling the decline of insects</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-01</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6254,14 +6254,14 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede attività di ricerca avanzata sul recupero di materie prime critiche dai RAEE, con requisiti tecnici e consorzio internazionale difficilmente accessibili per una PMI del Cilento non specializzata in questo settore. Le PMI campane potrebbero partecipare solo come partner secondari di grandi consorzi di ricerca, rendendo l'accesso diretto praticamente impossibile per realtà locali di piccola dimensione.</t>
+          <t>Il bando Horizon UE sul declino degli insetti è orientato a consorzi di ricerca accademica e grandi enti scientifici, con requisiti progettuali complessi e budget elevati difficilmente accessibili a una PMI campana. Solo aziende con forte vocazione R&amp;S nel settore agronomico o ambientale potrebbero partecipare come partner secondari, ma non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Understanding and tackling the decline of insects</t>
+          <t>Advancing integrated scenarios and prediction models for informing transition to a nature positive society</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-05</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla ricerca sul declino degli insetti è orientato a consorzi di ricerca accademica e istituti scientifici, con requisiti tecnici e amministrativi complessi che rendono la partecipazione diretta di una PMI del Cilento molto difficile senza un ruolo marginale di partner. Non finanzia attività produttive o commerciali tipiche delle piccole imprese locali.</t>
+          <t>Il bando Horizon richiede la costruzione di consorzi internazionali e capacità di ricerca scientifica avanzata per sviluppare modelli predittivi sulla transizione verso una società nature positive, competenze e strutture difficilmente disponibili in una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio guidato da università o enti di ricerca, ma le probabilità di accesso diretto sono molto ridotte.</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Advancing integrated scenarios and prediction models for informing transition to a nature positive society</t>
+          <t>Pushing the frontier of knowledge and conservation action for deep sea ecosystems</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-03</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6343,19 +6343,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la costruzione di consorzi europei con istituti di ricerca e università per sviluppare modelli predittivi sulla transizione verso una società nature positive, con requisiti tecnico-scientifici molto elevati e processi di candidatura complessi. Una PMI del Cilento difficilmente dispone delle competenze progettuali e dei partner internazionali necessari per competere, salvo che operi come partner junior in un consorzio già strutturato.</t>
+          <t>Il bando Horizon riguarda ricerca scientifica avanzata sugli ecosistemi degli abissi marini, destinato principalmente a enti di ricerca e università con capacità di ricerca oceanografica specializzata. Una PMI campana, anche del Cilento con accesso al mare, difficilmente possiede i requisiti tecnici e scientifici per candidarsi come capofila o partner rilevante in questo tipo di progetto.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Pushing the frontier of knowledge and conservation action for deep sea ecosystems</t>
+          <t>Advancing recycling technologies for mixed post-consumer textiles waste from blended products</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-BIODIV-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-02</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6390,19 +6390,19 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulla ricerca degli ecosistemi degli abissi marini richiede capacità di ricerca scientifica avanzata e partnership con enti accademici internazionali, rendendolo di fatto inaccessibile per una PMI standard del Cilento. Solo laboratori privati specializzati in biologia marina o tecnologie subacquee potrebbero partecipare, e unicamente come partner junior in consorzi europei già strutturati.</t>
+          <t>Il bando Horizon UE richiede attività di ricerca avanzata su tecnologie di riciclo per tessuti misti post-consumo, con consorzio internazionale e capacità R&amp;D strutturate, requisiti difficilmente accessibili per una PMI campana di piccole dimensioni senza partner di ricerca consolidati. Il Cilento, territorio a vocazione agricola e turistica, non presenta un tessuto industriale tessile rilevante che giustifichi investimenti in questa direzione.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Advancing recycling technologies for mixed post-consumer textiles waste from blended products</t>
+          <t>Bioremediation of Ukraine’s ecosystems contaminated by conflicts</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-02</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6442,14 +6442,14 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede attività di ricerca avanzata sul riciclo di tessuti misti post-consumo, con consorzî internazionali e capacità R&amp;D difficilmente accessibili a una PMI del Cilento non specializzata nel settore tessile/tecnologico. L'onere amministrativo e la competitività europea rendono questo strumento praticamente inaccessibile senza un partner di ricerca strutturato.</t>
+          <t>Il bando Horizon è focalizzato sulla bonifica ambientale di ecosistemi ucraini contaminati da conflitti bellici, con requisiti di ricerca avanzata e consorzio internazionale che rendono l'accesso estremamente complesso per una PMI campana di piccole dimensioni. Il contesto geografico e tematico specifico (Ucraina post-conflitto) esclude di fatto qualsiasi ricaduta diretta sul territorio del Cilento o su attività produttive locali.</t>
         </is>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Bioremediation of Ukraine’s ecosystems contaminated by conflicts</t>
+          <t>Demonstrating and deploying innovative collection, sorting-for-reuse and repair systems for textiles at city/region level (Circular Cities and Regions Initiative topic)</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-ZEROPOLLUTION-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-04</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6484,19 +6484,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è focalizzato sulla bonifica degli ecosistemi contaminati da conflitti in Ucraina, richiedendo capacità di ricerca avanzata, partnership internazionali e competenze specifiche in biorisanamento ambientale che difficilmente una PMI del Cilento possiede autonomamente. L'elevata complessità procedurale di Horizon e la natura geopolitica del tema lo rendono sostanzialmente inaccessibile senza il supporto di grandi enti di ricerca o università capofila.</t>
+          <t>Il bando Horizon richiede progetti di scala urbana/regionale con consorzio internazionale e capacità di R&amp;I avanzata, struttura difficilmente accessibile per una PMI del Cilento senza un ruolo di partner secondario in un grande progetto. Le PMI tessili campane potrebbero partecipare solo come subappaltatori o partner minori in consorzi guidati da enti di ricerca o grandi municipalità.</t>
         </is>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating and deploying innovative collection, sorting-for-reuse and repair systems for textiles at city/region level (Circular Cities and Regions Initiative topic)</t>
+          <t>Bio-based innovation in society: supporting the sustainable way of living</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL6-2026-01-CIRCBIO-10</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede progetti dimostrativi su scala urbana/regionale per sistemi innovativi di raccolta e riparazione di tessili, con consorziate di ricerca e budget elevati tipicamente superiori ai 2-3 milioni di euro: barriere progettuali e finanziarie molto alte per una PMI del Cilento. Una piccola impresa tessile o di riparazione potrebbe partecipare solo come partner operativo in un consorzio guidato da enti di ricerca o Comuni, ruolo difficile da costruire senza reti europee consolidate.</t>
+          <t>Il bando Horizon europeo richiede consorzi internazionali, capacità di ricerca avanzata e burocrazia complessa, risultando difficilmente accessibile a una PMI del Cilento senza un partner universitario o un centro di ricerca. Solo PMI già inserite in reti R&amp;I con esperienza in bioeconomia circolare potrebbero candidarsi in qualità di partner di progetto, non come capofila.</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla conservazione delle aree protette e della biodiversità è orientato principalmente a consorzi di ricerca, università ed enti pubblici, con requisiti di partnership internazionale e capacità tecnico-scientifica difficilmente accessibili a una PMI campana. Sebbene il Cilento, con il suo Parco Nazionale, offra un contesto territoriale rilevante per i temi trattati, una PMI avrebbe margini di partecipazione solo in qualità di partner secondario in progetti coordinati da soggetti di ricerca.</t>
+          <t>Il bando Horizon europeo è orientato a consorzi di ricerca e grandi enti scientifici per attività di conservazione della biodiversità nelle aree protette; una PMI campana, anche del Cilento (area Parco Nazionale), difficilmente può accedere in autonomia senza essere partner junior di un progetto coordinato da università o centri di ricerca, con oneri amministrativi e co-finanziamento molto impegnativi per strutture di piccole dimensioni.</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata in biotecnologie e biomanufacturing, con consorzî internazionali e competenze scientifiche difficilmente accessibili a una PMI di piccola dimensione del Cilento. Le spese finanziabili riguardano R&amp;S ad alto contenuto tecnologico, lontane dal tessuto produttivo locale prevalentemente agro-alimentare e turistico.</t>
+          <t>Il bando Horizon Europe richiede attività di ricerca avanzata in biotecnologia e biomanufacturing con consorzio internazionale, requisiti tecnici e finanziari difficilmente accessibili a una PMI di piccola dimensione del Cilento senza una solida struttura di R&amp;S. Una PMI locale potrebbe partecipare solo come partner junior di un consorzio guidato da università o grandi imprese, con ruolo marginale e oneri burocratici elevati.</t>
         </is>
       </c>
     </row>
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato a supportare policy maker e istituzioni nella definizione di strategie di bioeconomia a livello europeo, non a finanziare direttamente PMI. Una piccola impresa del Cilento difficilmente può accedere come beneficiario principale, pur operando in settori bioeconomici come agroalimentare o forestale.</t>
+          <t>Il bando finanzia attività di supporto politico e coordinamento istituzionale sulla bioeconomia a livello europeo, regionale e settoriale, destinato principalmente a enti di ricerca, agenzie governative e grandi consorzi, non a PMI operative. Una piccola impresa del Cilento, anche se attiva in settori bioeconomici come agricoltura o pesca, non ha i requisiti strutturali né il profilo istituzionale richiesto per partecipare direttamente.</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>L'ERC Proof of Concept è riservato esclusivamente a ricercatori già beneficiari di un grant ERC attivo, rendendo di fatto inaccessibile il bando per una PMI del Cilento priva di tale prerequisito. Non finanzia direttamente imprese, ma singoli ricercatori che vogliono valorizzare commercialmente risultati della loro ricerca ERC.</t>
+          <t>Il grant ERC Proof of Concept è destinato esclusivamente a ricercatori già beneficiari di un finanziamento ERC attivo, rendendo di fatto inaccessibile il bando a una PMI del Cilento senza un precedente progetto ERC. Anche in caso di collaborazione con un ricercatore ERC, la struttura del bando è pensata per ambienti accademici e di ricerca, non per PMI di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Il bando BeActive EU Sport Awards è un riconoscimento europeo legato alla promozione dell'attività fisica e dello sport nell'ambito del programma Erasmus+, destinato principalmente a organizzazioni sportive, enti pubblici e associazioni no-profit, non a PMI commerciali. Una piccola impresa campana del Cilento non rientra nei profili tipicamente ammissibili e non sono previsti finanziamenti diretti per attività imprenditoriali.</t>
+          <t>Il bando è orientato a organizzazioni sportive, enti pubblici e associazioni no-profit che promuovono attività fisica e valori europei attraverso lo sport, non a PMI commerciali. Una piccola impresa del Cilento non rientra tipicamente tra i beneficiari ammissibili e non troverebbe finanziabilità per attività produttive o di business.</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Il bando #BeActive è un premio europeo legato al volontariato sportivo promosso da Erasmus+, destinato a individui, organizzazioni no-profit e associazioni sportive, non a PMI con finalità commerciali. Una piccola impresa del Cilento non rientra nei beneficiari tipici e non può finanziare attività produttive o investimenti aziendali attraverso questo strumento.</t>
+          <t>Il bando BeActive EU Sport Awards è un premio europeo dedicato alla promozione del volontariato nello sport e non prevede finanziamenti diretti a PMI né copertura di spese aziendali; il target principale sono organizzazioni sportive, enti pubblici e associazioni no-profit. Una PMI del Cilento non ha concrete possibilità di accesso né benefici economici diretti.</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Il bando #BeActive-EU-SPORT-AWARDS è un premio europeo legato alla promozione dell'attività fisica e non un finanziamento diretto: premia campagne e iniziative di sensibilizzazione sportiva, risultando poco accessibile per una PMI del Cilento orientata a obiettivi produttivi o commerciali. Solo imprese attive nel settore sportivo, fitness o benessere potrebbero valutarne la partecipazione per visibilità europea, ma senza un ritorno economico diretto.</t>
+          <t>Il bando #BeActive EU Sport Awards è un riconoscimento europeo per iniziative di promozione dell'attività fisica, non un finanziamento diretto: non eroga fondi a PMI ma premia progetti già realizzati, rendendolo poco rilevante per una piccola impresa del Cilento in cerca di contributi concreti. Una PMI del settore sportivo o del turismo attivo potrebbe valutarlo solo come strumento di visibilità, ma senza alcun ritorno economico diretto.</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Il bando BeActive EU Sport Awards è un riconoscimento europeo dedicato a organizzazioni che promuovono l'attività fisica e l'inclusione attraverso lo sport, non un finanziamento diretto a PMI: non prevede rimborso di spese aziendali né investimenti produttivi. Una PMI del Cilento non trova in questo bando un'opportunità concreta di accesso a risorse finanziarie o sviluppo del business.</t>
+          <t>Il bando BeActive EU Sport Awards è un riconoscimento/premio europeo dedicato a organizzazioni che promuovono l'attività fisica e l'inclusione attraverso lo sport, rivolto principalmente ad enti pubblici, associazioni sportive e no-profit, non a PMI commerciali. Una piccola impresa del Cilento non avrebbe titolo sostanziale per candidarsi, salvo operi specificamente nel settore dell'inclusione sportiva in forma associativa.</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Il bando BeActive EU Sport Awards è un riconoscimento europeo dedicato a iniziative di promozione dell'attività fisica intergenerazionale, rivolto principalmente a enti pubblici, associazioni sportive e organizzazioni no-profit, non a PMI commerciali. Una piccola impresa del Cilento non ha strumenti concreti per candidarsi né spese finanziabili tipiche dell'attività d'impresa.</t>
+          <t>Il bando #BeActive EU Sport Awards è un riconoscimento europeo per iniziative che promuovono l'attività fisica tra generazioni, destinato principalmente ad enti pubblici, associazioni sportive e organizzazioni no-profit, non a PMI con finalità commerciali. Una piccola impresa del Cilento non avrebbe titolo né struttura adeguata per concorrere in modo competitivo a questo tipo di premio europeo.</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Il bando ESC2027 Quality Label per gli aiuti umanitari è destinato a organizzazioni del volontariato e della società civile che operano in contesti di crisi internazionale, non a PMI commerciali. Una piccola impresa del Cilento non rientra nei requisiti soggettivi né nelle attività finanziabili.</t>
+          <t>Il bando ESC2027 Quality Label per gli aiuti umanitari è rivolto a organizzazioni no-profit e ONG che operano nel settore dell'aiuto umanitario internazionale, non a PMI commerciali. Una piccola impresa del Cilento non rientra nei requisiti soggettivi e non trarrebbe alcun beneficio diretto da questa procedura di certificazione.</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto principalmente a università e uffici di trasferimento tecnologico (TTO), non a PMI come beneficiari diretti; una piccola impresa del Cilento potrebbe al più partecipare indirettamente come partner industriale in un consorzio, ma difficilmente come capofila o beneficiario principale.</t>
+          <t>Il bando è rivolto principalmente a università, enti di ricerca e Technology Transfer Offices per potenziare il trasferimento tecnologico verso il mercato, non a PMI come beneficiarie dirette. Una PMI del Cilento potrebbe al massimo essere coinvolta come partner secondario in un consorzio, ma difficilmente come soggetto proponente o principale destinatario dei fondi.</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE 2027 - Environment Governance è orientato principalmente a enti pubblici, ONG e organismi di ricerca per progetti di governance ambientale su scala europea, con requisiti di partenariato transnazionale e capacità amministrativa elevata che rendono l'accesso diretto per una PMI del Cilento molto difficile. Una piccola impresa potrebbe partecipare solo come partner secondario in un consorzio già strutturato, senza ruolo di capofila né accesso diretto ai fondi.</t>
+          <t>Il programma LIFE - Environment Governance è orientato principalmente a enti pubblici, ONG e organismi di ricerca per progetti di governance ambientale su scala europea, con requisiti di partenariato internazionale e capacità progettuali complesse che rendono l'accesso diretto per una PMI del Cilento estremamente difficile. Una piccola impresa potrebbe partecipare solo come partner secondario in un consorzio già strutturato, ma non come beneficiario principale.</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e grandi consorzi con capacità tecniche e finanziarie elevate; una PMI del Cilento difficilmente può sostenere i costi di progettazione europea e la quota di cofinanziamento richiesta senza un partenariato consolidato. L'accesso resta teoricamente possibile come partner secondario in progetti su economia circolare o riduzione dell'inquinamento, ma non come soggetto capofila.</t>
+          <t>Il programma LIFE è orientato a progetti dimostrativi su larga scala in ambito ambientale e antiinquinamento, con budget elevati e requisiti tecnico-amministrativi complessi che richiedono tipicamente partnership con enti di ricerca o pubblici; una PMI del Cilento difficilmente può candidarsi autonomamente, al più come partner secondario in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Climate Governance and Information finanzia principalmente campagne di comunicazione, advocacy e progetti di governance climatica su scala europea, richiedendo partenariati internazionali e capacità progettuali elevate difficilmente accessibili a una PMI del Cilento senza un ente capofila strutturato. Non copre investimenti produttivi o attività commerciali tipiche delle PMI locali.</t>
+          <t>Il programma LIFE Climate Governance and Information finanzia principalmente campagne di sensibilizzazione, disseminazione e governance climatica su scala europea, rivolte a enti pubblici, ONG e organismi di ricerca, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un partenariato strutturato con soggetti istituzionali. Le spese finanziabili riguardano comunicazione e capacity building climatico, settori distanti dalle attività operative tipiche di una piccola impresa campana.</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e organizzazioni no-profit con forte capacità progettuale europea; una PMI del Cilento difficilmente accede in modo diretto, potendo al massimo partecipare come partner in consorzi guidati da soggetti più strutturati. I costi di adattamento climatico finanziabili (es. gestione risorse idriche, resilienza costiera) sono rilevanti per il territorio, ma la complessità burocratica e la necessità di partnership transnazionali rendono l'accesso concreto molto limitato per una piccola impresa.</t>
+          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, università e grandi consorzi, con requisiti di partenariato europeo e capacità amministrative difficilmente sostenibili da una PMI del Cilento; i progetti finanziabili riguardano misure di adattamento climatico su scala territoriale (gestione idrica, coste, biodiversità) che richiedono investimenti e competenze tecniche elevate, rendendo la partecipazione diretta di una piccola impresa quasi impraticabile se non come partner junior di un consorzio già formato.</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE è orientato a progetti dimostrativi e di scala europea con budget elevati e requisiti tecnico-amministrativi complessi, difficilmente accessibili a una PMI campana senza un consorzio strutturato o un ente capofila. Le PMI del Cilento potrebbero partecipare solo come partner di progetti coordinati da università o enti pubblici, con un ruolo marginale e tempi di ritorno molto lunghi.</t>
+          <t>Il programma LIFE è strutturalmente orientato a enti pubblici, organizzazioni no-profit e consorzi di ricerca, con requisiti progettuali complessi e budget minimi elevati che rendono difficile l'accesso diretto a una PMI del Cilento; le spese finanziabili riguardano azioni dimostrative su mitigazione climatica (energie rinnovabili, efficienza, carbon sink), settori in cui una piccola impresa difficilmente può costruire un progetto autonomo competitivo senza un partenariato istituzionale solido.</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Nature and Biodiversity finanzia principalmente enti pubblici, ONG e istituti di ricerca per progetti di conservazione degli habitat naturali su larga scala; una PMI campana, pur operante nel Cilento (area Parco Nazionale), troverebbe difficile accedere autonomamente per gli elevati requisiti di partenariato transnazionale e la complessità gestionale dei grant europei diretti.</t>
+          <t>Il programma LIFE Nature and Biodiversity finanzia principalmente enti pubblici, ONG ambientali e istituti di ricerca per progetti di conservazione della biodiversità su larga scala; una PMI del Cilento potrebbe partecipare solo in qualità di partner secondario, con oneri burocratici elevati e budget minimi richiesti difficilmente compatibili con le dimensioni di una piccola impresa.</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE Nature Governance and Information finanzia principalmente enti pubblici, ONG e istituzioni di ricerca per progetti di governance ambientale su larga scala; una PMI del Cilento potrebbe partecipare solo in qualità di partner secondario all'interno di consorzi strutturati, con oneri amministrativi e cofinanziamenti difficilmente sostenibili per una piccola impresa.</t>
+          <t>Il programma LIFE Nature Governance and Information finanzia principalmente enti pubblici, ONG ambientali e istituti di ricerca per attività di governance della natura e comunicazione ambientale, con procedure complesse e cofinanziamento elevato difficilmente sostenibile da una PMI. Una piccola impresa del Cilento potrebbe partecipare solo in qualità di partner associato in progetti coordinati da soggetti istituzionali, senza accesso diretto ai fondi.</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>Il programma LIFE finanzia prevalentemente progetti di policy e governance ambientale destinati a enti pubblici, ONG e grandi organizzazioni, con procedure complesse e co-finanziamento elevato difficilmente sostenibile da una PMI. Una piccola impresa del Cilento può tuttavia intercettare indirettamente il bando come partner di progetto in iniziative legate alla biodiversità del Parco Nazionale del Cilento o all'economia circolare, ma difficilmente come capofila.</t>
+          <t>Il programma LIFE è orientato a progetti di scala europea su biodiversità ed economia circolare, con requisiti di partenariato transnazionale e capacità gestionale elevata che lo rendono difficilmente accessibile a una PMI autonomamente; una PMI del Cilento potrebbe partecipare solo come partner secondario di un consorzio guidato da enti di ricerca o pubblici, con ruolo marginale e bassa probabilità di ottenere finanziamento diretto.</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE è orientato a progetti di sistema su scala europea per supportare la conformità normativa in materia di ecodesign ed etichettatura energetica, con beneficiari tipici quali enti pubblici, associazioni di categoria o grandi organizzazioni; una PMI del Cilento difficilmente possiede la capacità progettuale, i partner transnazionali e le risorse amministrative richieste per partecipare direttamente. L'utilità pratica è quasi nulla senza il supporto di una rete europea consolidata.</t>
+          <t>Il bando LIFE è orientato a progetti di sistema su scala europea per supportare fornitori e retailer nella conformità all'ecodesign e all'etichettatura energetica, richiedendo capacità progettuali e partenariali complesse tipiche di enti o consorzi, non di singole PMI locali. Una piccola impresa del Cilento difficilmente può accedere autonomamente a questo strumento senza un consorzio europeo strutturato.</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE riguarda il dialogo multilevel su governance climatica ed energetica post-2030, ed è tipicamente riservato a consorzi istituzionali, enti pubblici, ONG e organizzazioni di ricerca; una PMI del Cilento difficilmente può candidarsi come capofila o trarre benefici diretti, salvo come partner molto specializzato in advocacy energetica.</t>
+          <t>Il bando LIFE riguarda il dialogo multilivello su clima ed energia nell'ambito della governance europea post-2030, ed è tipicamente destinato a enti pubblici, associazioni e organizzazioni di ricerca con capacità di coordinamento transnazionale. Una PMI del Cilento difficilmente possiede i requisiti strutturali e la massa critica progettuale per candidarsi autonomamente a questo tipo di azione LIFE.</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE 2027 per l'assistenza tecnica alla preparazione di SNaPs (Strategic Nature Plans) è orientato a enti pubblici, autorità nazionali e organizzazioni ambientali di livello strategico, non a PMI. Una piccola impresa del Cilento non ha i requisiti soggettivi né la capacità istituzionale per candidarsi direttamente a questo tipo di strumento tecnico-pianificatorio europeo.</t>
+          <t>Il bando LIFE TA per la preparazione di SNaPs (Strategic Nature Plans) è destinato principalmente a enti pubblici, autorità nazionali e organizzazioni ambientali istituzionali, non a PMI. Una piccola impresa del Cilento difficilmente accede direttamente come beneficiario, e le spese finanziabili riguardano assistenza tecnica per pianificazione naturalistica strategica, non attività produttive o commerciali tipiche di una PMI.</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un bando LIFE per assistenza tecnica alla preparazione di Piani di Investimento Strategico in campo ambientale (ENV SIPs), destinato principalmente a enti pubblici, autorità nazionali o grandi organizzazioni con capacità progettuale europea: una PMI del Cilento difficilmente possiede i requisiti tecnici e istituzionali per candidarsi autonomamente. L'accesso indiretto come partner è teoricamente possibile ma richiede competenze specialistiche in policy ambientale difficili da trovare in una piccola impresa locale.</t>
+          <t>Si tratta di un bando di assistenza tecnica UE destinato a enti pubblici o grandi organizzazioni per la preparazione di Piani di Investimento Strategico ambientali (SIPs) nell'ambito del programma LIFE, non accessibile direttamente a PMI. Una piccola impresa del Cilento non ha i requisiti tecnici né la struttura organizzativa per candidarsi come beneficiario principale.</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>Il bando LIFE TA per la preparazione di Strategic Integrated Projects (SIPs) sul clima è destinato principalmente a enti pubblici, autorità regionali o grandi organizzazioni ambientali per attività di assistenza tecnica complessa; una PMI del Cilento difficilmente ha i requisiti istituzionali e la capacità progettuale per candidarsi direttamente come soggetto capofila in questo tipo di strumento europeo.</t>
+          <t>Il bando LIFE 2027 per assistenza tecnica alla preparazione di CLIMA SIPs (Strategic Integrated Projects) è destinato principalmente a enti pubblici, autorità regionali o grandi consorzi con capacità di coordinamento europeo, non a PMI singole. Una piccola impresa del Cilento difficilmente possiede i requisiti tecnici e amministrativi per candidarsi autonomamente a questo tipo di strumento complesso.</t>
         </is>
       </c>
     </row>
@@ -7711,14 +7711,14 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede consorzi internazionali, capacità di ricerca avanzata e budget elevati, rendendolo difficilmente accessibile per una PMI del Cilento senza partner universitari o industriali strutturati. Tuttavia, una PMI campana attiva nella chimica verde, cosmetica naturale o prodotti per la casa a base bio potrebbe partecipare come partner industriale in un consorzio, coprendo attività di sviluppo prodotto e industrializzazione.</t>
+          <t>Il bando Horizon Europe richiede capacità di ricerca e sviluppo avanzate su soluzioni bio-based per cura della persona/casa secondo i principi SSbD (Safe and Sustainable by Design), con budget elevati e partnership internazionali che risultano difficilmente accessibili per una PMI del Cilento senza un solido consorzio di ricerca già strutturato. Una piccola impresa campana potrebbe partecipare solo come partner secondario in un consorzio europeo, non come capofila.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Develop breakthrough and sustainable bio-based textile fibres</t>
+          <t>Bio-based chemicals and/or materials from woody residues</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-03</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -7758,14 +7758,14 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzi internazionali e investimenti significativi in R&amp;S su fibre tessili bio-based, rendendo l'accesso diretto molto difficile per una PMI del Cilento priva di strutture di ricerca dedicate o partnership con università; il settore tessile innovativo è inoltre scarsamente radicato nel tessuto produttivo locale.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzi internazionali e investimenti significativi in R&amp;S su chimica verde da residui legnosi, barriere difficilmente superabili per una PMI di piccola dimensione del Cilento senza una solida struttura di progettazione europea. Una PMI locale potrebbe partecipare solo come partner junior in un consorzio guidato da università o grandi aziende, con ruolo marginale e accesso indiretto ai fondi.</t>
         </is>
       </c>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>High-performance, circular-by-design, bio-based thermosets</t>
+          <t>Develop breakthrough and sustainable bio-based textile fibres</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-03</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo richiede attività di ricerca avanzata su materiali biobasati e termoindurenti ad alta performance progettati per la circolarità, con consorzio internazionale e capacità R&amp;D significative difficilmente accessibili a una PMI del Cilento senza un solido partner universitario o tecnologico. Le spese finanziabili riguardano ricerca industriale e sviluppo sperimentale, ma la complessità progettuale e la competizione a livello europeo rendono questo strumento poco praticabile per realtà produttive locali di piccole dimensioni.</t>
+          <t>Il bando Horizon richiede ricerca di frontiera su fibre tessili bio-based, con consorzî internazionali e capacità R&amp;D elevate difficilmente compatibili con una PMI di piccola dimensione del Cilento. Il settore tessile non è rappresentativo dell'economia locale, e i requisiti progettuali (budget, partner, rendicontazione EU) rendono l'accesso diretto quasi impraticabile senza un ruolo da subappaltatore in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Bio-based additives as alternatives to unlock and increase recyclability and/or biodegradability</t>
+          <t>High-performance, circular-by-design, bio-based thermosets</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-04</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7852,14 +7852,14 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede attività di ricerca e sviluppo su additivi bio-based per migliorare riciclabilità e biodegradabilità dei materiali, con budget elevati e obbligo di consorzio internazionale, caratteristiche che lo rendono difficilmente accessibile a una PMI del Cilento senza solide competenze R&amp;D e partnership europee già strutturate. Una piccola impresa campana potrebbe partecipare solo come partner junior in un consorzio guidato da università o grandi player industriali del settore chimico/materiali.</t>
+          <t>Il bando Horizon richiede attività di ricerca avanzata su materiali biobasati e design circolare, con consorzî internazionali e capacità R&amp;D strutturate che difficilmente una PMI del Cilento possiede autonomamente; l'accesso è realistico solo come partner junior in un progetto guidato da università o grandi aziende chimiche.</t>
         </is>
       </c>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Addressing separation and purification challenges in biorefineries</t>
+          <t>Bio-based additives as alternatives to unlock and increase recyclability and/or biodegradability</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-02</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -7899,14 +7899,14 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata in ingegneria dei processi di separazione e purificazione per bioraffinerie, con consorzio internazionale e budget elevati tipicamente superiori al milione di euro: barriere proibitive per una PMI del Cilento senza laboratori R&amp;D strutturati. Una piccola impresa locale potrebbe partecipare solo come partner junior in un consorzio già formato, scenario altamente improbabile senza reti europee consolidate.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, consorzi internazionali e competenze specifiche in chimica dei biopolimeri e materiali bio-based, elementi difficilmente disponibili in una PMI tradizionale del Cilento. Salvo che l'azienda operi nel settore della bio-chimica o della plastica riciclabile con un dipartimento R&amp;D strutturato, il bando risulta inaccessibile senza partnership con università o centri di ricerca qualificati.</t>
         </is>
       </c>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>SSbD bio-based polymers from alternative sources</t>
+          <t>Addressing separation and purification challenges in biorefineries</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-01</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -7946,14 +7946,14 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede attività di ricerca avanzata su polimeri bio-based con approccio SSbD (Safe and Sustainable by Design), con consorzio internazionale e capacità di R&amp;S strutturata difficilmente accessibile a una PMI del Cilento senza un solido partner universitario o centro di ricerca. Le PMI di piccola dimensione raramente dispongono delle competenze tecniche e della massa critica progettuale richiesta da questo tipo di call competitiva a livello europeo.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata in bioraffinerie e processi di separazione/purificazione, tipiche di grandi consorzi accademici o industrie chimiche specializzate, rendendo molto difficile la partecipazione diretta di una PMI del Cilento priva di laboratori R&amp;D certificati. L'unica via di accesso sarebbe come partner junior in un consorzio europeo, scenario poco probabile per una piccola impresa locale senza precedenti esperienze Horizon.</t>
         </is>
       </c>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Supporting industry in the switch to sustainable and circular bio-based products and processes</t>
+          <t>SSbD bio-based polymers from alternative sources</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-CSA-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-RIA-02</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7993,14 +7993,14 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede consorzi internazionali con elevata capacità di ricerca e sviluppo, budget molto elevati e competenze scientifiche avanzate nella bioeconomia circolare, caratteristiche difficilmente compatibili con una PMI di piccola dimensione del Cilento. Una PMI potrebbe partecipare solo come partner junior in un consorzio già strutturato, ma l'accesso autonomo è praticamente precluso.</t>
+          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata, consorzi internazionali e competenze in chimica dei polimeri bio-based, barriere difficilmente superabili per una PMI del Cilento senza un solido track record europeo. Una piccola impresa potrebbe partecipare solo come partner junior in un consorzio guidato da università o grandi centri di ricerca, con ruolo marginale e bassa probabilità di accesso diretto ai fondi.</t>
         </is>
       </c>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Films and coatings for circular packaging</t>
+          <t>Supporting industry in the switch to sustainable and circular bio-based products and processes</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-CSA-01</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8040,14 +8040,14 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede attività di ricerca e sviluppo su imballaggi circolari (film e rivestimenti), con consorzio transnazionale e capacità R&amp;D avanzate difficilmente accessibili a una PMI del Cilento senza partner universitari o industriali già strutturati. Le risorse necessarie per partecipare (co-finanziamento, gestione progettuale europea, competenze tecniche specifiche) superano tipicamente le possibilità di una piccola impresa locale.</t>
+          <t>Il bando Horizon EU richiede progetti di ricerca e innovazione ad alta intensità tecnologica con consorzio europeo, strutture di R&amp;S dedicate e capacità di rendicontazione complessa, barriere difficilmente superabili per una PMI del Cilento senza un solido track record europeo. Resta marginalmente accessibile solo per PMI già inserite in reti di ricerca o filiere bioeconomiche (es. agroalimentare, chimica verde) come partner di un consorzio coordinato da un ente di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Biotech routes for valorisation of residual biomass</t>
+          <t>Films and coatings for circular packaging</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-05</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8087,14 +8087,14 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzi internazionali e competenze biotecnologiche difficilmente disponibili in una PMI di piccola dimensione del Cilento; le spese finanziabili (R&amp;S, personale ricercatore, attrezzature di laboratorio) presuppongono strutture scientifiche consolidate. Una PMI locale potrebbe al massimo partecipare come partner secondario in un consorzio guidato da università o centri di ricerca.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata, consorzio internazionale e budget elevati, barriere difficilmente superabili per una PMI del Cilento. Il tema riguarda lo sviluppo di film e rivestimenti per imballaggi circolari, settore non rappresentativo del tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Boosting biorefinery competitiveness through biotech</t>
+          <t>Biotech routes for valorisation of residual biomass</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-01</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8134,14 +8134,14 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla bioraffineria richiede capacità di ricerca avanzata, consorzi internazionali e investimenti elevati tipici di grandi player industriali o università; una PMI del Cilento difficilmente possiede i requisiti tecnici e le risorse per partecipare direttamente, salvo come partner junior in un consorzio già strutturato nel settore biotech/agro-industriale.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzio internazionale e investimenti significativi in R&amp;D biotecnologico, barriere difficilmente superabili per una PMI del Cilento senza un solido partner universitario o un laboratorio interno. L'unica opportunità concreta sarebbe per aziende agroalimentari o agricole già attive nel recupero di sottoprodotti (es. olive, agrumi) che riuscissero ad agganciarsi come partner industriali a un progetto guidato da enti di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Diversification of nutritional food ingredient sources for increased EU resilience and strategic autonomy</t>
+          <t>Boosting biorefinery competitiveness through biotech</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-01</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8181,14 +8181,14 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede consorzi internazionali con forte componente di ricerca applicata e capacità progettuali elevate, generalmente non accessibili direttamente a una PMI del Cilento senza un partner universitario o un centro di ricerca. Una PMI agroalimentare locale potrebbe partecipare solo come partner di un consorzio più ampio, con ruolo marginale nella gestione del progetto.</t>
+          <t>Il bando Horizon UE sulla competitività delle bioraffinerie richiede capacità di ricerca biotecnologica avanzata, partnership internazionali e budget di progetto elevati, barriere difficilmente superabili per una PMI del Cilento senza una consolidata rete di R&amp;S. Potrebbe essere rilevante solo per PMI già attive in settori bio-based (es. agroalimentare, biomasse) con esperienza pregressa in progetti europei e accesso a consorzi di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>LIFE Operating Grants</t>
+          <t>Diversification of nutritional food ingredient sources for increased EU resilience and strategic autonomy</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -8198,17 +8198,17 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-SGA</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-04</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -8223,39 +8223,39 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>I LIFE Operating Grants sono destinati esclusivamente a organizzazioni non governative e enti no-profit attivi nella tutela ambientale e climatica, escludendo di fatto le PMI commerciali. Una piccola impresa del Cilento non rientra tra i beneficiari ammissibili e non può accedere a questo finanziamento.</t>
+          <t>Il bando Horizon UE sulla diversificazione delle fonti di ingredienti alimentari richiede capacità di ricerca avanzata, consorzi internazionali e budget elevati, rendendolo difficilmente accessibile per una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo come partner secondario all'interno di un consorzio europeo, ad esempio valorizzando prodotti tipici locali come l'olio DOP o i legumi cilentani, ma la complessità gestionale e rendicontativa di Horizon rimane un ostacolo concreto.</t>
         </is>
       </c>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Leveraging long-term field experiments and other datasets to develop AI-ready decision support systems for sustainable soil management</t>
+          <t>LIFE Operating Grants</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-NGO-OG-SGA</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -8270,19 +8270,19 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la costituzione di consorzi internazionali di ricerca ad alto contenuto scientifico per sviluppare sistemi AI di supporto decisionale per la gestione sostenibile del suolo, struttura difficilmente accessibile a una PMI del Cilento senza un partner universitario o di ricerca consolidato. Una piccola impresa agricola o agritech potrebbe partecipare solo come soggetto associato, con ruolo marginale e oneri burocratici elevati rispetto ai benefici diretti attesi.</t>
+          <t>I LIFE Operating Grants sono destinati esclusivamente a organizzazioni non governative e enti no-profit attivi nella tutela ambientale e climatica, escludendo di fatto le PMI a scopo di lucro. Una piccola impresa del Cilento non rientra tra i beneficiari ammissibili e non può accedere direttamente a questo finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Enabling user-centred and open innovation initiatives to enhance soil health in Ukraine</t>
+          <t>Leveraging long-term field experiments and other datasets to develop AI-ready decision support systems for sustainable soil management</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-04</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8322,14 +8322,14 @@
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la salute del suolo in Ucraina tramite innovazione aperta e centrata sull'utente, con focus geografico esclusivo sul territorio ucraino: una PMI campana del Cilento non ha accesso diretto ai benefici né al contesto operativo richiesto. Horizon prevede inoltre requisiti consortili complessi e competenze di ricerca avanzata difficilmente compatibili con una piccola impresa locale.</t>
+          <t>Il bando Horizon richiede la costruzione di consorzi di ricerca internazionali e competenze avanzate in AI applicata alla gestione del suolo, strutture tipicamente fuori dalla portata di una PMI campana di piccole dimensioni senza un partner universitario o di ricerca già consolidato. Una PMI agricola del Cilento potrebbe al massimo partecipare come stakeholder o utente finale all'interno di un consorzio guidato da enti di ricerca, ma difficilmente come capofila o beneficiario diretto.</t>
         </is>
       </c>
     </row>
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Antimicrobial resistance and antibiotic biosynthesis in soils: developing key understanding and counteractive strategies using a One-Health approach</t>
+          <t>Enabling user-centred and open innovation initiatives to enhance soil health in Ukraine</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-03</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -8364,19 +8364,19 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata su resistenza antimicrobica e biosintesi di antibiotici nel suolo con approccio One-Health, competenze tipiche di istituti di ricerca o grandi consorzi scientifici, rendendo l'accesso diretto da parte di una PMI del Cilento estremamente difficile senza un ruolo marginale in un partenariato internazionale. Una PMI agricola o agroalimentare locale potrebbe al massimo partecipare come partner terzo, ma senza reale capacità di guidare o beneficiare direttamente dei finanziamenti.</t>
+          <t>Il bando è focalizzato esclusivamente sull'Ucraina e riguarda la salute del suolo in un contesto di innovazione aperta e centrata sull'utente, rendendo praticamente impossibile la partecipazione diretta di una PMI campana del Cilento come soggetto beneficiario principale. Inoltre, i bandi Horizon di questa natura richiedono consorzi internazionali strutturati e competenze di ricerca avanzata difficilmente accessibili a una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
+          <t>Antimicrobial resistance and antibiotic biosynthesis in soils: developing key understanding and counteractive strategies using a One-Health approach</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-02</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -8411,19 +8411,19 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca e sviluppo sul monitoraggio della salute del suolo, destinato principalmente a enti di ricerca, università e consorzi scientifici: una PMI del Cilento difficilmente può partecipare direttamente senza un partner accademico strutturato. Le aziende agricole o agri-tech locali potrebbero al massimo intervenire come partner associate, ma i requisiti progettuali e amministrativi Horizon rendono l'accesso concreto molto complesso per una piccola impresa.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata sulla resistenza antimicrobica e biosintesi di antibiotici nel suolo con approccio One-Health, richiedendo competenze scientifiche specialistiche e partnership internazionali difficilmente accessibili per una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo in qualità di partner secondario all'interno di un consorzio guidato da università o centri di ricerca, con ruolo molto marginale.</t>
         </is>
       </c>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Governing global commons sustainably</t>
+          <t>Monitoring soil health in practice: equipping stakeholders to sample, analyse, and interpret soil health indicators</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-05-SOIL-01</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8458,19 +8458,19 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla governance sostenibile dei beni comuni globali è orientato a consorzi di ricerca accademica e grandi enti istituzionali, con requisiti di partenariato transnazionale complessi e budget elevati difficilmente gestibili da una PMI del Cilento. Una piccola impresa campana non dispone tipicamente delle strutture amministrative e della capacità progettuale necessarie per accedere autonomamente a questo tipo di chiamata.</t>
+          <t>Il bando Horizon è orientato a consorzi di ricerca e stakeholder istituzionali per sviluppare metodologie di monitoraggio della salute del suolo, non a PMI singole; una piccola impresa agricola del Cilento potrebbe al massimo partecipare come partner associato, ma difficilmente come beneficiario diretto con spese finanziabili autonome.</t>
         </is>
       </c>
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Rethinking long-term care policy in the face of EU demographic shifts</t>
+          <t>Governing global commons sustainably</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-09</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-06</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -8510,14 +8510,14 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulla ricerca politica sull'assistenza a lungo termine in ottica demografica europea è destinato principalmente a consorzi di ricerca, università e think tank, con requisiti di partnership internazionale e capacità di ricerca scientifica difficilmente soddisfabili da una PMI del Cilento. Non sono previste attività finanziabili tipiche delle piccole imprese locali, né settori produttivi del territorio come turismo, agricoltura o servizi alla persona in chiave imprenditoriale.</t>
+          <t>Il bando Horizon Europe sui 'beni comuni globali' è orientato a consorzi di ricerca accademica e grandi enti internazionali, con requisiti di partnership transnazionale e capacità scientifica difficilmente accessibili a una PMI campana del Cilento. Non finanzia attività produttive o commerciali tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Government in transition – how governments change the way they work and prepare the civil service for the future</t>
+          <t>Rethinking long-term care policy in the face of EU demographic shifts</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-09</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -8557,14 +8557,14 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca accademica sulla trasformazione della pubblica amministrazione e la preparazione del personale civile governativo al cambiamento: si rivolge a enti di ricerca, università e istituzioni pubbliche, non a PMI. Una piccola o media impresa del Cilento non ha i requisiti soggettivi né le competenze progettuali per partecipare a questo tipo di call.</t>
+          <t>Il bando Horizon Europe sulla long-term care policy è orientato a enti di ricerca, università e grandi consorzi internazionali per produrre analisi e policy recommendations sui sistemi di cura agli anziani nell'UE: difficilmente accessibile a una PMI del Cilento senza un forte profilo di ricerca e partner accademici consolidati. L'unica finestra di partecipazione indiretta potrebbe essere per PMI specializzate in servizi socio-sanitari o tecnologie assistive, ma richiederebbe di entrare in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Boosting creative startups for disruptive innovation</t>
+          <t>Government in transition – how governments change the way they work and prepare the civil service for the future</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-03</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -8599,19 +8599,19 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe è orientato a startup creative con forte potenziale di innovazione dirompente a scala europea, richiedendo capacità di ricerca, partnership internazionali e rendicontazione complessa che risultano difficilmente accessibili per una PMI tradizionale del Cilento. Le PMI di piccola dimensione raramente dispongono delle risorse amministrative e del profilo tecnologico necessari per competere in questo tipo di call.</t>
+          <t>Il bando Horizon si concentra sulla ricerca accademica e istituzionale relativa alla trasformazione della pubblica amministrazione e alla formazione del personale civile governativo, ambiti estranei all'operatività di una PMI campana o cilentana. Non sono previste spese finanziabili né attività compatibili con imprese private di piccola e media dimensione.</t>
         </is>
       </c>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Tackling gender-based violence against politically active women and LGBTIQ people</t>
+          <t>Boosting creative startups for disruptive innovation</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-02</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8646,19 +8646,19 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a enti di ricerca, università e organizzazioni della società civile per progetti di studio e contrasto alla violenza di genere in ambito politico, con requisiti consortili complessi e procedure di rendicontazione europee difficilmente gestibili da una PMI del Cilento. Non sono previste spese tipicamente legate all'attività produttiva o commerciale di una piccola impresa.</t>
+          <t>Il bando Horizon Europe è orientato a startup creative con alto potenziale di innovazione dirompente a livello europeo, richiedendo capacità progettuali, partner internazionali e competenze in rendicontazione comunitaria che difficilmente una PMI di piccola dimensione del Cilento può sostenere autonomamente. I requisiti competitivi e la complessità gestionale lo rendono poco accessibile senza il supporto di un ente di ricerca o un consorzio strutturato.</t>
         </is>
       </c>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Strengthened implementation of the EU Pact on Migration and Asylum and a focus on inclusion, integration, and health</t>
+          <t>Tackling gender-based violence against politically active women and LGBTIQ people</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-01</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -8698,14 +8698,14 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sull'attuazione del Patto UE su Migrazione e Asilo è destinato principalmente a enti di ricerca, università, ONG e istituzioni pubbliche, non a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti tecnici né la struttura progettuale per partecipare a bandi di ricerca europei su politiche migratorie e sanitarie legate all'integrazione.</t>
+          <t>Il bando Horizon focalizzato sulla violenza di genere contro donne politicamente attive e persone LGBTIQ+ è orientato a enti di ricerca, università e organizzazioni del terzo settore, rendendo l'accesso estremamente difficile per una PMI del Cilento senza esperienza consolidata in progetti europei di ricerca sociale. Non sono previste spese tipicamente rendicontabili da una PMI manifatturiera o di servizi, né vi è alcuna connessione con i settori produttivi locali come turismo, agricoltura o artigianato.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Preventing and fighting illicit trafficking of cultural goods</t>
+          <t>Strengthened implementation of the EU Pact on Migration and Asylum and a focus on inclusion, integration, and health</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-08</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sul contrasto al traffico illecito di beni culturali è orientato a consorzi di ricerca, istituzioni pubbliche e grandi organizzazioni specializzate, con requisiti progettuali complessi difficilmente accessibili a una PMI del Cilento. Pur essendo un territorio ricco di patrimonio culturale, una piccola impresa locale non ha le strutture amministrative e scientifiche necessarie per partecipare competitivamente a bandi Horizon di questa natura.</t>
+          <t>Il bando Horizon riguarda l'implementazione del Patto UE su Migrazione e Asilo, con focus su inclusione e salute: si tratta di un programma destinato principalmente a enti pubblici, ONG, università e centri di ricerca, non a PMI commerciali. Una piccola impresa del Cilento non ha struttura né profilo istituzionale per candidarsi utilmente a questo tipo di call.</t>
         </is>
       </c>
     </row>
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Understanding the forms of local democracy in low-income and low-middle income countries</t>
+          <t>Preventing and fighting illicit trafficking of cultural goods</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-07</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8792,14 +8792,14 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca accademica sulla democrazia locale nei paesi a basso reddito, un ambito lontano dalle attività produttive di una PMI campana o cilentana. Non finanziano attività imprenditoriali, prodotti o servizi commerciali, ma progetti di ricerca condotti tipicamente da università e istituti di ricerca.</t>
+          <t>Il bando Horizon focalizzato sul contrasto al traffico illecito di beni culturali è orientato a consorzi di ricerca, forze dell'ordine e istituzioni accademiche, rendendo l'accesso estremamente difficile per una PMI del Cilento senza una consolidata rete di partner europei e competenze specifiche in sicurezza dei beni culturali. Le spese finanziabili riguardano principalmente attività di ricerca applicata e sviluppo tecnologico in ambito investigativo, lontane dal profilo operativo tipico di una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Fostering cooperation and integration between SSH and STEM research and innovation in the EU</t>
+          <t>Understanding the forms of local democracy in low-income and low-middle income countries</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-10</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-02</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8834,19 +8834,19 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE mira a integrare ricerca umanistica/sociale (SSH) con discipline STEM a livello europeo, richiedendo consorzi internazionali e capacità di ricerca avanzata difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo come partner junior in un consorzio guidato da università o centri di ricerca, con ruolo marginale e oneri burocratici elevati.</t>
+          <t>Il bando Horizon focalizzato sulla democrazia locale in paesi a basso reddito è destinato a consorzi di ricerca accademica e organizzazioni specializzate in scienze politiche e governance, non a PMI operative nel Cilento o in Campania. Non finanzia attività produttive, commerciali o di servizio tipiche di una piccola impresa.</t>
         </is>
       </c>
     </row>
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Open topic: Strengthen Europe's social model and sustainable competitiveness through productivity</t>
+          <t>Fostering cooperation and integration between SSH and STEM research and innovation in the EU</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-10</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8886,14 +8886,14 @@
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede progetti di ricerca su scala europea con consorzio internazionale e capacità di rendicontazione complessa, strutturalmente inadatto a una PMI del Cilento senza esperienza pregressa in programmi quadro. L'accesso realistico è possibile solo come partner junior in un consorzio guidato da università o grandi aziende, ruolo difficile da costruire senza reti consolidate.</t>
+          <t>Il bando Horizon focalizzato sull'integrazione tra scienze sociali/umanistiche (SSH) e STEM è orientato principalmente a consorzi di ricerca, università e grandi organizzazioni con capacità progettuali europee, rendendo l'accesso estremamente complesso per una PMI del Cilento senza solide partnership accademiche internazionali. I requisiti di rendicontazione, la competitività globale e la natura fondamentale della ricerca lo rendono di fatto inaccessibile come capofila per una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Supporting post-conflict democracy and reconstruction</t>
+          <t>Open topic: Strengthen Europe's social model and sustainable competitiveness through productivity</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-02</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -8928,19 +8928,19 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su democrazia post-conflitto e ricostruzione è orientato a istituti di ricerca, università e organizzazioni internazionali, non a PMI operative in settori produttivi tipici del Cilento. Una piccola impresa campana non dispone né dei requisiti consortili né delle competenze tematiche richieste per partecipare competitivamente a questo tipo di call.</t>
+          <t>Si tratta di un bando Horizon Europe orientato alla ricerca accademica e a consorzi transnazionali su temi macroeconomici (produttività e modello sociale europeo), con requisiti di partecipazione complessi e budget elevati difficilmente gestibili da una PMI del Cilento senza un solido partenariato scientifico internazionale. Una piccola impresa campana troverebbe barriere concrete di accesso sia nella struttura del consorzio richiesto sia nell'impostazione della proposta progettuale.</t>
         </is>
       </c>
     </row>
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Tackling child poverty and ensuring disadvantaged children's access to Early Childhood Education and Care</t>
+          <t>Supporting post-conflict democracy and reconstruction</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-07</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8975,19 +8975,19 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a enti di ricerca, università e organizzazioni non profit impegnate nella lotta alla povertà infantile e nell'accesso all'educazione della prima infanzia, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un consorzio specifico. Una PMI potrebbe partecipare solo in qualità di partner secondario all'interno di un progetto coordinato da istituzioni accademiche o sociali, con margini operativi molto limitati.</t>
+          <t>Il bando Horizon focalizzato su democrazia post-conflitto e ricostruzione è destinato principalmente a consorzi di ricerca, università e ONG con competenze specialistiche in contesti di crisi internazionali, rendendo di fatto inaccessibile la partecipazione a una PMI campana del Cilento. Non esistono linee di finanziamento per attività produttive, servizi locali o investimenti aziendali tipici delle piccole imprese del territorio.</t>
         </is>
       </c>
     </row>
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>The impact of the use of digital tools outside school and for communication on educational outcomes and mental health</t>
+          <t>Tackling child poverty and ensuring disadvantaged children's access to Early Childhood Education and Care</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-03</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9027,14 +9027,14 @@
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato alla ricerca accademica su impatto degli strumenti digitali su apprendimento e salute mentale, richiedendo consorzi di enti di ricerca e università: una PMI campana, anche del Cilento, difficilmente può candidarsi come capofila e avrebbe ruolo marginale. Non finanzia attività produttive o servizi aziendali diretti.</t>
+          <t>Il bando Horizon UE è orientato a enti di ricerca, università e organizzazioni no-profit per progetti sulla povertà infantile e accesso ai servizi educativi della prima infanzia, contesti in cui una PMI del Cilento difficilmente ricopre il ruolo di beneficiario principale. Le PMI potrebbero partecipare solo come partner secondari in consorzi altamente specializzati, rendendo l'accesso concreto molto improbabile.</t>
         </is>
       </c>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding linguistic diversity in Europe</t>
+          <t>The impact of the use of digital tools outside school and for communication on educational outcomes and mental health</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-04</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9069,19 +9069,19 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sulla salvaguardia della diversità linguistica europea è orientato a consorzi di ricerca accademica e organizzazioni culturali di scala europea, richiedendo capacità progettuali e partnership internazionali difficilmente accessibili a una PMI del Cilento. Non finanzia attività produttive o commerciali tipiche delle piccole imprese locali.</t>
+          <t>Il bando Horizon riguarda ricerca accademica sull'impatto degli strumenti digitali sulla salute mentale e i risultati scolastici, destinato principalmente a università e centri di ricerca: una PMI del Cilento difficilmente possiede i requisiti scientifici e il profilo da principal investigator richiesti. L'accesso come partner secondario è possibile ma marginale e non giustifica l'investimento per una piccola impresa.</t>
         </is>
       </c>
     </row>
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Digital and media literacy as drivers for democratic and civic resilience</t>
+          <t>Safeguarding linguistic diversity in Europe</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-10</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-06</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9116,19 +9116,19 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su alfabetizzazione digitale e mediatica per la resilienza democratica è orientato a consorzi di ricerca, università e grandi organizzazioni del terzo settore, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un ruolo marginale in un partenariato internazionale. Le PMI di piccola dimensione non rappresentano il target primario e i requisiti di rendicontazione e co-finanziamento Horizon sono spesso incompatibili con strutture organizzative ridotte.</t>
+          <t>Il bando Horizon sulla diversità linguistica è orientato a enti di ricerca, università e consorzi accademici europei, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un ruolo marginale in un consorzio. Non finanzia attività produttive o commerciali tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Electoral integrity in the digital context</t>
+          <t>Digital and media literacy as drivers for democratic and civic resilience</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-08</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-10</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9163,19 +9163,19 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sull'integrità elettorale in contesto digitale è orientato a enti di ricerca, università e organizzazioni specializzate in scienze politiche e sicurezza informatica istituzionale, ambiti estranei alla struttura tipica di una PMI campana o cilentana. Non esistono linee di finanziamento applicabili ad attività produttive, commerciali o di servizio locali.</t>
+          <t>Il bando Horizon focalizzato su alfabetizzazione digitale e mediatica per la resilienza democratica è orientato a consorzi di ricerca, università e grandi organizzazioni, con procedure complesse e cofinanziamenti elevati difficilmente gestibili da una PMI del Cilento. Una piccola impresa campana avrebbe scarse possibilità di accesso diretto, salvo come partner minore in un progetto guidato da enti accademici.</t>
         </is>
       </c>
     </row>
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Research and Innovation Network for a Union of Equality</t>
+          <t>Electoral integrity in the digital context</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-08</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9210,19 +9210,19 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo è orientato a consorzi di ricerca, università e grandi organizzazioni, con requisiti di partenariato internazionale e capacità di rendicontazione molto elevati, difficilmente accessibili a una PMI del Cilento senza una struttura dedicata alla progettazione europea. L'accesso diretto è poco praticabile, ma una PMI potrebbe partecipare indirettamente come partner di un soggetto capofila accademico o di ricerca.</t>
+          <t>Il bando Horizon focalizzato sull'integrità elettorale in contesti digitali è destinato principalmente a centri di ricerca, università e consorzi accademici, richiedendo competenze altamente specializzate in scienze politiche e cybersecurity che esulano dall'operatività tipica di una PMI del Cilento. Non sono previste spese finanziabili rilevanti per attività produttive, commerciali o di servizio locali.</t>
         </is>
       </c>
     </row>
     <row r="187" ht="30" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>AI integration in CCSI work practice: catalysing innovation and competitiveness</t>
+          <t>Research and Innovation Network for a Union of Equality</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-05</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9262,14 +9262,14 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede consorzi internazionali, capacità di ricerca avanzata e rendicontazione complessa, requisiti difficilmente soddisfacibili da una PMI del Cilento senza un partner universitario o un centro di ricerca. L'integrazione dell'AI nei processi CCSI (Customer Care &amp; Service Innovation) è lontana dal tessuto produttivo locale, prevalentemente orientato a turismo, agricoltura e artigianato.</t>
+          <t>Il bando Horizon focalizzato su ricerca e uguaglianza si rivolge principalmente a università, enti di ricerca e grandi consorzi europei, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un partner capofila accademico. I requisiti burocratici, la necessità di costruire reti internazionali e i cofinanziamenti richiesti rappresentano barriere concrete per strutture di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Towards a fair and transparent market for cultural and creative content in the era of generative AI</t>
+          <t>AI integration in CCSI work practice: catalysing innovation and competitiveness</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-03</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9309,14 +9309,14 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, partnership internazionali e strutture progettuali complesse, difficilmente accessibili per una PMI di piccola dimensione del Cilento senza un consorzio universitario o un ente di ricerca capofila. Il focus su AI generativa e mercato dei contenuti creativi è lontano dal tessuto produttivo locale, orientato prevalentemente a turismo, agricoltura e artigianato.</t>
+          <t>Il bando Horizon UE sull'integrazione dell'AI nei processi CCSI (Customer Care &amp; Service Innovation) è orientato a consorzi di ricerca e grandi organizzazioni con capacità progettuale europea, rendendo l'accesso diretto estremamente difficile per una PMI del Cilento senza partnership consolidate con enti di ricerca. Una piccola impresa campana potrebbe partecipare solo come partner junior in un consorzio internazionale, con oneri amministrativi e di co-finanziamento spesso incompatibili con le dimensioni tipiche delle PMI locali.</t>
         </is>
       </c>
     </row>
     <row r="189" ht="30" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>“Artistic intelligence” : harnessing the power of the arts to address complex challenges, enhance soft skills and boost innovation and competitiveness</t>
+          <t>Towards a fair and transparent market for cultural and creative content in the era of generative AI</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-04</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9351,19 +9351,19 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è orientato a consorzi di ricerca e grandi enti accademici o istituzionali, rendendo l'accesso diretto da parte di una PMI del Cilento estremamente complesso senza un ruolo da partner secondario. Il focus sull'uso delle arti per sviluppare soft skills e innovazione è distante dalle priorità operative tipiche di una piccola impresa locale, con procedure di rendicontazione europee molto onerose.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca avanzata, consorzi internazionali e competenze specifiche sull'IA generativa e diritti d'autore, strutture tipiche di università o grandi enti di ricerca. Una PMI del Cilento difficilmente dispone delle risorse progettuali e del profilo tecnico-scientifico necessari per partecipare come capofila o anche come partner qualificato.</t>
         </is>
       </c>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Citizenship education as part of lifelong learning</t>
+          <t>“Artistic intelligence” : harnessing the power of the arts to address complex challenges, enhance soft skills and boost innovation and competitiveness</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-09</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-01</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9403,14 +9403,14 @@
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla cittadinanza attiva e l'apprendimento permanente è orientato a enti di ricerca, università e organizzazioni no-profit, richiedendo partnership internazionali complesse e capacità progettuali elevate difficilmente accessibili a una PMI del Cilento. Le spese finanziabili riguardano ricerca e sviluppo di metodologie educative, ambito lontano dalle attività produttive tipiche delle imprese locali.</t>
+          <t>Il bando Horizon europeo è orientato a consorzi di ricerca e grandi organizzazioni, rendendo l'accesso diretto per una PMI del Cilento molto complesso senza un partenariato strutturato con università o enti di ricerca. Il focus sull'uso delle arti per sviluppare soft skills e innovazione è interessante ma richiede capacità progettuali e risorse amministrative difficilmente sostenibili da una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Fostering competences for the green transition</t>
+          <t>Citizenship education as part of lifelong learning</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-09</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -9450,14 +9450,14 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla transizione verde è orientato a consorzi di ricerca, università e grandi organizzazioni con capacità progettuali complesse, rendendo l'accesso diretto di una PMI del Cilento molto difficile senza un partner capofila accademico. Una piccola impresa campana potrebbe partecipare solo come partner in un consorzio più ampio, con costi amministrativi e burocratici spesso sproporzionati rispetto ai benefici ottenibili.</t>
+          <t>Il bando Horizon focalizzato sull'educazione civica e l'apprendimento permanente è orientato principalmente a consorzi di ricerca, università e organizzazioni no-profit europee, richiedendo partnership transnazionali complesse e capacità di gestione progettuale difficilmente accessibili a una PMI del Cilento. Le spese finanziabili riguardano ricerca e sviluppo di metodologie educative, non attività produttive o commerciali tipiche delle piccole imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="192" ht="30" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Making Europe a global magnet for talent - Attracting and retaining students, researchers and high-skilled workers from outside the EU</t>
+          <t>Fostering competences for the green transition</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-07</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -9497,14 +9497,14 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si rivolge principalmente a università, enti di ricerca e grandi istituzioni pubbliche per sviluppare politiche europee di attrazione di talenti internazionali, non a PMI del Cilento o della Campania. Una piccola impresa non ha né la struttura progettuale né il profilo richiesto per partecipare come soggetto capofila o partner rilevante in questo tipo di iniziativa.</t>
+          <t>Il bando Horizon UE richiede la partecipazione in consorzi di ricerca internazionali con elevata capacità progettuale e finanziaria, risultando di fatto inaccessibile per una PMI del Cilento senza un partner accademico o un grande ente capofila. Le PMI possono partecipare solo come partner secondari in progetti complessi, con bassa probabilità di successo autonomo.</t>
         </is>
       </c>
     </row>
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Contribution of basic skills to productivity, innovation, competitiveness and economic growth</t>
+          <t>Making Europe a global magnet for talent - Attracting and retaining students, researchers and high-skilled workers from outside the EU</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-06</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -9544,14 +9544,14 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo è orientato alla ricerca accademica e istituzionale sulle competenze di base e la produttività, richiedendo consorzi internazionali e capacità di ricerca scientifica difficilmente accessibili a una PMI del Cilento. Una piccola impresa campana non ha le strutture né i requisiti tipicamente richiesti da questi grant per partecipare direttamente come beneficiario principale.</t>
+          <t>Il bando Horizon si rivolge principalmente a enti di ricerca, università e grandi organizzazioni con capacità di gestire progetti europei complessi focalizzati sull'attrazione di talenti internazionali: una PMI del Cilento difficilmente possiede i requisiti tecnici e amministrativi per candidarsi autonomamente. L'ambito tematico (policy sull'immigrazione qualificata a livello UE) è inoltre distante dalle priorità operative quotidiane di una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="194" ht="30" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Sustainable paths to media viability</t>
+          <t>Contribution of basic skills to productivity, innovation, competitiveness and economic growth</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-05</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9586,19 +9586,19 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo 'Sustainable paths to media viability' è orientato a organizzazioni del settore mediatico e a consorzi di ricerca per sviluppare modelli di sostenibilità economica per i media, escludendo di fatto PMI generiche del Cilento non operanti nell'editoria o nel giornalismo. La complessità procedurale di Horizon e la necessità di partnership internazionali rendono questo bando praticamente inaccessibile per una piccola impresa locale.</t>
+          <t>Il bando Horizon è orientato a progetti di ricerca accademica e istituzionale sulla correlazione tra competenze di base e crescita economica, richiedendo consorzi internazionali e capacità di ricerca che esulano dalle possibilità operative di una PMI del Cilento. Non finanzia direttamente attività formative aziendali né percorsi di upskilling interni, ma studi e analisi di policy a livello europeo.</t>
         </is>
       </c>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Regional  (sea-basins) components of the EU Digital Twin Ocean</t>
+          <t>Sustainable paths to media viability</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-04</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -9633,19 +9633,19 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon per il Digital Twin Ocean richiede capacità di ricerca avanzata, consorzi internazionali e competenze altamente specializzate in oceanografia e modellazione digitale, rendendo l'accesso diretto estremamente difficile per una PMI del Cilento. Una piccola impresa locale potrebbe partecipare solo come partner secondario in un consorzio guidato da enti di ricerca, con ruoli molto marginali e prospettive di ritorno economico incerte.</t>
+          <t>Il bando Horizon è orientato a progetti di ricerca su sostenibilità dei media e informazione, richiedendo consorzi europei con forte componente accademica e capacità progettuali elevate, incompatibili con la struttura tipica di una PMI del Cilento. Le spese finanziabili riguardano ricerca applicata sul settore mediatico, un ambito non rilevante per il tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Addressing aquatic pollution and biodiversity loss through nature positive solutions from source to sea</t>
+          <t>Regional  (sea-basins) components of the EU Digital Twin Ocean</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-05</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -9680,19 +9680,19 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede consorzi internazionali di ricerca con capacità tecnico-scientifiche elevate, budget multimilionari e competenze specialistiche in ecologia acquatica e biodiversità marina, caratteristiche difficilmente compatibili con una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe al massimo partecipare come partner minore in un consorzio guidato da università o enti di ricerca, senza possibilità di essere capofila.</t>
+          <t>Il bando Horizon per il Digital Twin Ocean richiede capacità di ricerca avanzata, consorzi internazionali e competenze tecniche elevate in oceanografia e modellazione digitale, caratteristiche tipiche di grandi enti di ricerca o aziende tech strutturate. Una PMI del Cilento avrebbe difficoltà concrete ad accedere come partner principale, salvo rare eccezioni nel settore della tecnologia marina o dei servizi dati costieri.</t>
         </is>
       </c>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Large-scale demonstration for mapping the distribution and condition of marine habitats to implement the Nature Restoration Regulation</t>
+          <t>Addressing aquatic pollution and biodiversity loss through nature positive solutions from source to sea</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-02</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -9732,14 +9732,14 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di gestione di progetti europei complessi, consorzio internazionale e competenze tecnico-scientifiche avanzate nel monitoraggio degli habitat marini, caratteristiche difficilmente compatibili con una PMI di piccole dimensioni. Sebbene il Cilento presenti habitat costieri e marini rilevanti (come il Parco Nazionale), il bando è orientato a enti di ricerca e grandi organizzazioni, rendendo l'accesso diretto per una PMI locale sostanzialmente impraticabile.</t>
+          <t>Il bando Horizon EU è orientato a consorzi di ricerca europei e grandi enti scientifici per progetti su inquinamento acquatico e biodiversità marina; una PMI campana del Cilento potrebbe partecipare solo come partner secondario in un consorzio già strutturato, con oneri burocratici e competitivi molto elevati rispetto alle capacità tipiche di una piccola impresa.</t>
         </is>
       </c>
     </row>
     <row r="198" ht="30" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Towards a European network of ocean technology testing sites</t>
+          <t>Large-scale demonstration for mapping the distribution and condition of marine habitats to implement the Nature Restoration Regulation</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-01</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -9779,14 +9779,14 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon mira a costruire una rete europea di siti di test per tecnologie oceaniche, richiedendo capacità di ricerca avanzata, infrastrutture specializzate e partenariati internazionali difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo come partner junior in un consorzio guidato da enti di ricerca marittima, con un ruolo molto marginale e costi di partecipazione elevati.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzio internazionale e competenze specifiche in mappatura degli habitat marini, barriere difficilmente superabili per una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo come partner junior in un consorzio già formato, con un ruolo molto marginale e bassa probabilità di accesso diretto ai fondi.</t>
         </is>
       </c>
     </row>
     <row r="199" ht="30" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Bridging the gap between disaster risk management and climate adaptation</t>
+          <t>Towards a European network of ocean technology testing sites</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-04</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -9826,14 +9826,14 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede consorzi internazionali di ricerca con capacità tecnico-scientifiche elevate, budget ingenti e strutture amministrative complesse, barriere difficilmente superabili per una PMI del Cilento. Sebbene il territorio sia esposto a rischi idrogeologici e climatici rilevanti, una PMI potrebbe al massimo partecipare come partner secondario all'interno di un consorzio guidato da università o enti di ricerca.</t>
+          <t>Il bando Horizon richiede la creazione di reti europee per siti di test di tecnologie oceaniche, con requisiti di consorzio internazionale e capacità di R&amp;S avanzata difficilmente compatibili con una PMI del Cilento. Solo aziende già operative nel settore marino-tecnologico con partner europei consolidati potrebbero partecipare realisticamente.</t>
         </is>
       </c>
     </row>
     <row r="200" ht="30" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Supporting financing of local adaptation actions with combination of public funding and private financing</t>
+          <t>Bridging the gap between disaster risk management and climate adaptation</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-07</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-04</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9868,19 +9868,19 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>Credito/Finanza</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e sviluppo per modelli innovativi di finanziamento dell'adattamento climatico locale, rivolti principalmente a enti pubblici, istituti finanziari e grandi consorzi di ricerca. Una PMI del Cilento difficilmente accede direttamente come capofila, e i requisiti di consorzio internazionale e la complessità amministrativa Horizon rendono la partecipazione autonoma quasi impraticabile.</t>
+          <t>Il bando Horizon richiede la partecipazione a consorzi di ricerca europei con capacità progettuali e scientifiche elevate, difficilmente accessibili a una PMI campana di piccole dimensioni senza un partner universitario o un centro di ricerca. Una PMI del Cilento potrebbe teoricamente partecipare come partner secondario in progetti legati alla gestione del rischio idrogeologico o all'adattamento climatico costiero, settori rilevanti per il territorio, ma l'onere burocratico e finanziario rende la partecipazione diretta poco praticabile.</t>
         </is>
       </c>
     </row>
     <row r="201" ht="30" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Facilitating implementation of actionable solutions for climate adaptation of regions and local authorities</t>
+          <t>Supporting financing of local adaptation actions with combination of public funding and private financing</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-07</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9915,19 +9915,19 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Credito/Finanza</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo è orientato a consorzi di ricerca, enti pubblici e grandi organizzazioni capaci di guidare progetti multi-paese sull'adattamento climatico delle regioni, con requisiti tecnici e amministrativi difficilmente accessibili per una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio più ampio, ma non come capofila o beneficiario diretto.</t>
+          <t>Il bando Horizon finanzia soggetti istituzionali e intermediari finanziari per sviluppare strumenti di blending pubblico-privato per l'adattamento climatico locale, non PMI dirette. Una piccola impresa del Cilento non ha i requisiti tecnici né la capacità progettuale per accedere direttamente a questa tipologia di call europea.</t>
         </is>
       </c>
     </row>
     <row r="202" ht="30" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Improving climate resilience of navigable inland waterways, their surroundings and related water infrastructure</t>
+          <t>Facilitating implementation of actionable solutions for climate adaptation of regions and local authorities</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-02</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9962,19 +9962,19 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si concentra sulla resilienza climatica delle vie navigabili interne e delle infrastrutture idriche collegate, un settore poco rilevante per il Cilento che non ha significative vie d'acqua navigabili; inoltre i bandi Horizon richiedono consorzi di ricerca europei e capacità progettuali complesse, risultando di fatto inaccessibili per una PMI locale di piccola dimensione senza partner accademici o industriali internazionali.</t>
+          <t>Il bando Horizon è orientato a consorzi di ricerca, enti pubblici e grandi organizzazioni con capacità di coordinamento europeo per sviluppare soluzioni sistemiche all'adattamento climatico; una PMI del Cilento potrebbe partecipare solo come partner minore in un consorzio già strutturato, senza possibilità di essere capofila né di accedere autonomamente ai fondi.</t>
         </is>
       </c>
     </row>
     <row r="203" ht="30" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Standardising and supporting climate services for  climate adaptation</t>
+          <t>Improving climate resilience of navigable inland waterways, their surroundings and related water infrastructure</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-06</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10009,19 +10009,19 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata, consorzio internazionale e competenze tecniche specializzate sui servizi climatici, requisiti difficilmente soddisfabili da una PMI del Cilento senza un solido track record europeo. Le risorse finanziarie e amministrative necessarie per partecipare a progetti Horizon superano tipicamente le capacità di una piccola impresa locale, salvo che non partecipi come partner junior in un consorzio già strutturato.</t>
+          <t>Il bando Horizon EU è orientato a grandi consorzi di ricerca e infrastrutture idriche navigabili interne, un contesto lontano dalla realtà produttiva del Cilento e delle PMI campane, che non dispongono né delle competenze tecniche specialistiche né della capacità progettuale richiesta per partecipare a programmi europei di questa complessità. Il territorio cilentano, pur costiero, non presenta vie d'acqua navigabili interne rilevanti che giustifichino un interesse concreto.</t>
         </is>
       </c>
     </row>
     <row r="204" ht="30" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>National Adaptation Hubs - Bringing together the national level with the engaged regional and local levels (multi-level governance)</t>
+          <t>Standardising and supporting climate services for  climate adaptation</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-03</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -10056,19 +10056,19 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si rivolge principalmente a consorzi di enti pubblici, istituzioni di ricerca e autorità nazionali/regionali per costruire hub di governance multilivello sull'adattamento climatico, non a PMI singole. Una piccola impresa del Cilento non ha i requisiti strutturali né il profilo istituzionale per guidare o partecipare direttamente a questo tipo di progetto.</t>
+          <t>Il bando Horizon richiede la partecipazione a consorzi europei di ricerca con capacità tecnico-scientifiche avanzate nello sviluppo di servizi climatici, strutture di progetto complesse e budget elevati difficilmente accessibili a una PMI del Cilento senza partner universitari o centri di ricerca già consolidati. Una piccola impresa campana avrebbe margini di partecipazione molto limitati, se non come partner minore in un consorzio già formato.</t>
         </is>
       </c>
     </row>
     <row r="205" ht="30" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
+          <t>National Adaptation Hubs - Bringing together the national level with the engaged regional and local levels (multi-level governance)</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-06-CLIMA-SOIL</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-01</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la costituzione di consorzi internazionali multi-partner con forte componente di ricerca applicata, rendendo l'accesso diretto molto difficile per una PMI campana di piccole dimensioni; una PMI agricola del Cilento potrebbe partecipare solo come partner secondario all'interno di un progetto coordinato da enti di ricerca o università, con ruolo dimostrativo su pratiche di resilienza del suolo alle siccità e agli eventi estremi.</t>
+          <t>Il bando Horizon finanzia consorzi istituzionali e di ricerca per costruire hub nazionali di governance multilivello sull'adattamento climatico, non PMI singole; una piccola impresa del Cilento non ha i requisiti di coordinamento istituzionale né la capacità progettuale richiesta per partecipare come partner significativo.</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>Il programma CERV Town Twinning finanzia gemellaggi tra comuni europei e attività di cittadinanza attiva, non è destinato a imprese private o PMI ma a enti locali e organizzazioni della società civile. Una PMI del Cilento non può candidarsi direttamente e difficilmente rientra tra i soggetti beneficiari ammissibili.</t>
+          <t>Il programma CERV Town Twinning finanzia gemellaggi tra comuni europei e attività di cittadinanza attiva, ed è riservato ad enti locali e organizzazioni della società civile, non a imprese private. Una PMI del Cilento non può candidarsi direttamente e non rientra tra i beneficiari ammissibili.</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto a intermediari di finanza sociale (fondi, istituzioni finanziarie) per coprire i loro costi di transazione, non alle PMI direttamente. Una piccola impresa del Cilento non può candidarsi come beneficiaria diretta.</t>
+          <t>Il bando è destinato a intermediari della finanza sociale (fondi, istituzioni finanziarie) per coprire i costi di transazione legati a strumenti di finanza sociale ESF, non alle PMI come beneficiarie dirette. Una piccola impresa del Cilento non può accedere direttamente a questo finanziamento.</t>
         </is>
       </c>
     </row>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Hop-On Facility è uno strumento Horizon Europe pensato per integrare ricercatori di paesi a bassa performance R&amp;I in progetti già finanziati, richiedendo capacità di gestione della ricerca e partnership con consorzi europei attivi che difficilmente una PMI del Cilento possiede o può costruire in tempi brevi. L'accesso presuppone competenze scientifiche avanzate e strutture di ricerca che esulano dalla dimensione tipica delle PMI locali.</t>
+          <t>Il programma Hop-On Facility è rivolto a ricercatori e organizzazioni di paesi con bassa partecipazione a Horizon Europe, con l'obiettivo di integrarsi in progetti già finanziati: non è uno strumento diretto per PMI campane che cercano finanziamenti per attività produttive o commerciali. Una PMI del Cilento troverebbe barriere elevate in termini di requisiti tecnico-scientifici e necessità di partnership con consorzi di ricerca europei già attivi.</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>Teaming Synergies è uno strumento Horizon Europe pensato per creare o potenziare centri di eccellenza in R&amp;I, richiedendo partnership tra istituzioni di ricerca di paesi avanzati e regioni meno sviluppate: una PMI del Cilento difficilmente può guidare un progetto di questa portata, potendo al più partecipare come soggetto associato a un consorzio guidato da università o enti di ricerca.</t>
+          <t>Teaming Synergies è uno strumento Horizon Europe pensato per costruire Centri di Eccellenza in ricerca avanzata, richiedendo partnership con istituzioni accademiche di alto livello e investimenti strutturali pluriennali difficilmente accessibili per una PMI del Cilento senza un solido consorzio già costituito. L'accesso diretto per una piccola impresa è estremamente complesso, poiché il bando privilegia enti di ricerca e grandi organizzazioni con capacità amministrativa e finanziaria elevata.</t>
         </is>
       </c>
     </row>
@@ -10338,12 +10338,12 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Il bando Research Management Facility di Horizon UE è orientato a strutture di ricerca e gestione della conoscenza scientifica, tipicamente accessibili a università, enti pubblici o grandi organizzazioni R&amp;D, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile senza un ruolo marginale di partner. Non sono previste spese finanziabili direttamente rilevanti per attività produttive o commerciali tipiche di una piccola impresa locale.</t>
+          <t>Il bando Research Management Facility di Horizon UE è orientato a strutture di ricerca e gestione della conoscenza scientifica, con requisiti progettuali e amministrativi complessi difficilmente sostenibili da una PMI del Cilento senza un partner istituzionale (università, ente di ricerca). Una piccola impresa campana avrebbe scarse possibilità di accesso diretto e dovrebbe necessariamente partecipare come soggetto associato in un consorzio internazionale.</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Il bando ISF (Internal Security Fund) sulla lotta alla corruzione è destinato principalmente a enti pubblici, forze dell'ordine e organizzazioni specializzate nel settore della sicurezza e dell'antimafia, non a PMI commerciali. Una piccola impresa del Cilento non ha i requisiti soggettivi né le competenze istituzionali richieste per accedere a questo tipo di finanziamento.</t>
+          <t>Il bando ISF (Internal Security Fund) sulla lotta alla corruzione è destinato principalmente a enti pubblici, forze dell'ordine e organizzazioni specializzate in sicurezza e governance, non a PMI commerciali. Una piccola impresa del Cilento non rientrerebbe nei beneficiari ammissibili e non vi sono spese tipicamente sostenute da PMI tra quelle finanziabili.</t>
         </is>
       </c>
     </row>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia azioni di sviluppo nel settore della difesa europea, richiedendo capacità tecnologiche avanzate, consorzio tra imprese di più Stati membri e competenze in ambito militare/aerospaziale, caratteristiche difficilmente compatibili con una PMI manifatturiera o di servizi tipica del Cilento. I costi di partecipazione, la complessità progettuale e i requisiti tecnici lo rendono di fatto inaccessibile senza un partenariato strategico già consolidato con grandi player della difesa.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia azioni di sviluppo nel settore della difesa e delle tecnologie militari, un ambito quasi inaccessibile per una PMI tradizionale del Cilento, che richiederebbe competenze certificiate in R&amp;S difensiva e partnership con grandi prime contractor. Le spese finanziabili riguardano sviluppo di sistemi d'arma, tecnologie dual-use e prototipazione militare, settori estranei al tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo tecnologico militare avanzato nel settore della sorveglianza e rilevamento oltre l'orizzonte, richiedendo consorzi internazionali con capacità di difesa e sicurezza che esulano completamente dal profilo di una PMI campana del Cilento. I requisiti tecnici, le certificazioni di sicurezza e la natura difensiva del progetto rendono questo bando di fatto inaccessibile per realtà produttive locali di piccola-media dimensione.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa su tecnologie di rilevamento oltre l'orizzonte, richiedendo consorzi multinazionali con competenze altamente specializzate in ambito militare/aerospaziale. Una PMI del Cilento difficilmente dispone delle capacità tecniche certificate, dei requisiti di sicurezza e delle partnership internazionali nel settore difesa necessari per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di sistemi di sorveglianza tattica basati su sciami di robot e droni con AI per scopi militari/difesa, richiedendo capacità tecnologiche avanzate e consorziate tipiche di grandi industrie della difesa o centri di ricerca specializzati. Una PMI del Cilento, salvo rarissime eccezioni nel settore aerospazio o robotica avanzata, non dispone delle competenze certificabili, dei requisiti di sicurezza e della rete di partner istituzionali necessari per partecipare competitivamente.</t>
+          <t>Il bando EDF finanzia lo sviluppo di sistemi di sorveglianza tattica basati su sciami di robot e droni per uso militare/difesa, richiedendo competenze altamente specializzate in robotica, AI e difesa che esulano dalle capacità tipiche di una PMI del Cilento. Inoltre, i bandi EDF sono generalmente accessibili solo a grandi consorzi industriali del settore difesa, con requisiti tecnici e finanziari proibitivi per realtà di piccola-media dimensione.</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo militare/difesa su sciami di robot e droni per la consapevolezza situazionale tattica, richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze nel settore difesa difficilmente accessibili a una PMI del Cilento. Le risorse necessarie in termini di R&amp;S, certificazioni e partnership strategiche rendono questo bando non adatto a piccole imprese locali senza un posizionamento consolidato nell'industria della difesa.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo tecnologico militare/difesa su sciami di droni e robot per la sorveglianza tattica: richiede capacità R&amp;D avanzate, consorzi internazionali e competenze aerospaziali/robotiche difficilmente accessibili a una PMI del Cilento. Le barriere tecniche, amministrative e il contesto geopolitico del programma lo rendono praticamente inaccessibile senza partnership con grandi player della difesa.</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per sistemi di decontaminazione CBRN richiede capacità di ricerca e sviluppo in ambito difesa e sicurezza avanzata, con consorzio di partner europei e requisiti tecnici altamente specializzati difficilmente soddisfabili da una PMI del Cilento. Le risorse finanziarie, le certificazioni di sicurezza e le competenze necessarie sono tipiche di grandi industrie della difesa o centri di ricerca istituzionali.</t>
+          <t>Il bando EDF per sistemi di decontaminazione CBRN (chimico-biologico-radiologico-nucleare) è orientato a consorzi industriali della difesa con elevate capacità tecnologiche e finanziarie, richiedendo competenze altamente specializzate difficilmente presenti in una PMI del Cilento. I requisiti di partecipazione tipici dell'EDF prevedono partnership transnazionali complesse e investimenti in R&amp;S di scala industriale incompatibili con le dimensioni e il profilo produttivo delle piccole imprese campane.</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per aeromobili leggeri multiruolo è destinato a consorzi industriali della difesa con capacità di R&amp;S aeronautica avanzata, requisiti tecnici e finanziari del tutto fuori portata per una PMI del Cilento o della Campania senza specializzazione nel settore aerospazio/difesa. Solo PMI altamente specializzate in avionica, materiali compositi o sistemi di volo potrebbero partecipare come subfornitrici di un grande prime contractor, scenario comunque molto improbabile per il tessuto produttivo locale.</t>
+          <t>Il bando EDF per aeromobili leggeri multiruolo è destinato a consorzi industriali del settore difesa e aerospaziale con capacità di R&amp;S avanzata, requisiti tecnici e finanziari del tutto fuori portata per una PMI del Cilento o della Campania non specializzata in questo comparto. Solo PMI già inserite come subfornitrici in filiere aerospaziali (es. distretto di Pomigliano) potrebbero valutare una partecipazione indiretta come partner junior di grandi prime contractor.</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa militare (modellazione, simulazione e AI per il decision-making), richiedendo consorzi internazionali con competenze altamente specializzate e capacità tecnologiche avanzate, del tutto fuori portata per una PMI tipica del Cilento. Le PMI campane potrebbero partecipare solo come partner minori in consorzi guidati da grandi aziende della difesa, scenario estremamente difficile da costruire senza relazioni consolidate nel settore militare europeo.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa militare, richiedendo capacità tecnologiche avanzate in AI, modellazione e simulazione tipiche di grandi contractor o centri di ricerca specializzati; una PMI del Cilento difficilmente possiede i requisiti tecnici, i partner istituzionali e la certificazione di sicurezza necessari per partecipare a progetti di questo tipo.</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per dimostratori di sensori multidominio è orientato a grandi consorzi industriali della difesa con capacità R&amp;S avanzate: una PMI del Cilento difficilmente possiede le competenze tecnologiche militari richieste e la capacità di partecipare a progetti europei complessi di questo tipo. L'accesso è realisticamente possibile solo come subappaltatore di un grande prime contractor, scenario poco probabile per una piccola realtà locale.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia lo sviluppo di dimostratori di sensori multidominio per applicazioni militari e di difesa, richiedendo consorzi internazionali con capacità tecnologiche e industriali avanzate nel settore difesa. Una PMI del Cilento difficilmente dispone delle certificazioni, delle infrastrutture di ricerca e dei partner strategici necessari per competere in questo ambito altamente specializzato e regolamentato.</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di reti tattiche militari basate su crittografia quantistica, un settore altamente specializzato che richiede competenze avanzate in tecnologie quantistiche e difesa: barriere tecnologiche, finanziarie e burocratiche lo rendono sostanzialmente inaccessibile per una PMI del Cilento. Questo tipo di bando è pensato per grandi aziende della difesa o consorzi con importanti partner industriali e istituti di ricerca di alto livello.</t>
+          <t>Il bando EDF sulle reti tattiche quantistiche è destinato a consorzi di difesa con elevate capacità tecnologiche e di ricerca nel settore militare, richiedendo investimenti e competenze fuori dalla portata di una PMI del Cilento. Le tecnologie quantistiche applicate alle comunicazioni sicure in ambito tattico/militare presuppongono strutture di R&amp;S e certificazioni difficilmente accessibili per realtà di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di tecnologie militari avanzate per il rifornimento autonomo aria-aria, richiedendo competenze aerospaziali e difesa di altissimo livello, consorzî internazionali e capacità R&amp;D straordinarie del tutto fuori portata per una PMI del Cilento o della Campania in generale. L'accesso è di fatto riservato a grandi prime contractor della difesa o a istituti di ricerca specializzati nel settore aeronautico militare.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa aeronautica avanzata (rifornimento autonomo aria-aria), richiedendo competenze altamente specializzate, consorzi internazionali e capacità tecnologiche difficilmente disponibili in una PMI del Cilento o della Campania. I requisiti tecnici e le barriere di accesso lo rendono sostanzialmente inaccessibile per realtà produttive locali di piccola-media dimensione.</t>
         </is>
       </c>
     </row>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca militare/difesa ad alta specializzazione tecnica sulla modellazione del rumore sottomarino generato dai flussi, richiedendo competenze scientifiche avanzate e infrastrutture di ricerca navale difficilmente disponibili per una PMI campana del Cilento. Il profilo richiesto è quello di enti di ricerca o grandi aziende della difesa, non di PMI manifatturiere o di servizi tipiche del territorio.</t>
+          <t>Il bando EDF finanzia ricerca militare/difesa avanzata sulla modellazione del rumore sottomarino generato da flussi idrici, richiedendo capacità di R&amp;S specializzate in acustica navale e ingegneria militare che esulano completamente dal profilo tipico di una PMI campana o cilentana. L'accesso è riservato a consorzi con enti di ricerca e industria della difesa, rendendo la partecipazione diretta di una PMI locale praticamente impossibile senza un ruolo marginale in una cordata già strutturata.</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) per la protezione delle infrastrutture sottomarine critiche è destinato a consorzi di difesa e ricerca con capacità tecnologiche avanzate nel settore militare/dual-use, richiedendo competenze specializzate in sonar, robotica subacquea o cybersecurity navale che una PMI campana tipica del Cilento difficilmente possiede. L'accesso è inoltre condizionato a partnership con entità della difesa di almeno 3 Stati membri UE, rendendo la partecipazione diretta praticamente inaccessibile per una piccola o media impresa locale.</t>
+          <t>Il bando EDF per la protezione delle infrastrutture sottomarine critiche è destinato a consorzi di difesa e grandi industrie del settore aerospaziale/navale-militare, con requisiti tecnici e finanziari del tutto incompatibili con una PMI campana, anche del Cilento. Non sono previste spese finanziabili accessibili a realtà di piccola dimensione né ambiti applicativi rilevanti per il tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per lo sviluppo di nuovi motori turbofan è destinato a grandi aziende aerospaziali e consorzi industriali con capacità R&amp;S avanzate nel settore difesa, rendendo l'accesso praticamente impossibile per una PMI del Cilento priva di competenze aeronautiche specifiche e della massa critica richiesta da questi programmi europei di difesa.</t>
+          <t>Il bando EDF per lo sviluppo di nuovi motori turbofan è destinato a grandi consorzi industriali del settore aerospazio e difesa, con requisiti tecnici, finanziari e di sicurezza del tutto incompatibili con una PMI campana del Cilento. Non esistono realistiche condizioni di accesso diretto né come capofila né come partner autonomo per realtà di piccola-media dimensione.</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa missilistica ad alta quota, un ambito riservato a grandi contractor della difesa e consorzi industriali specializzati. Una PMI del Cilento o della Campania priva di certificazioni NATO/difesa e capacità tecnologiche aerospaziali non ha accesso pratico a questa tipologia di finanziamento.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa missilistica atmosferica ad alta quota, un ambito riservato a grandi industrie della difesa e consorzi specializzati con capacità tecnologiche avanzate. Una PMI del Cilento o della Campania non dispone delle certificazioni, delle infrastrutture e dei requisiti tecnico-industriali necessari per partecipare a progetti di intercettazione endo-atmosferica.</t>
         </is>
       </c>
     </row>
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa, richiedendo consorzi internazionali e capacità tecnologiche avanzate nel campo dei tessuti intelligenti per applicazioni militari: requisiti strutturali e finanziari del tutto fuori portata per una PMI del Cilento, anche se operante nel settore tessile. L'orientamento alla difesa esclude di fatto le imprese manifatturiere locali non inserite in filiere aerospaziali o militari.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa europea, richiedendo consorzi internazionali con capacità tecnologiche avanzate nel campo dei tessuti intelligenti per applicazioni militari: struttura e requisiti incompatibili con una PMI di piccola dimensione del Cilento, che difficilmente possiede le competenze difensive e i partner istituzionali necessari per partecipare.</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di ricevitori Galileo PRS per sistemi d'arma militari e centri C2 NAVWAR, un settore altamente specializzato della difesa che richiede capacità tecnologiche, certificazioni e requisiti di sicurezza NATO/UE difficilmente accessibili a una PMI del Cilento o della Campania priva di esperienza consolidata nel comparto difesa. Le risorse finanziabili riguardano R&amp;S avanzata in elettronica militare e navigazione, ambiti estranei al tessuto produttivo locale.</t>
+          <t>Il bando EDF riguarda sistemi d'arma militari con tecnologia PRS Galileo e centri C2 per la guerra elettronica (NAVWAR), ambiti che richiedono certificazioni di sicurezza NATO/UE, capacità industriali della difesa e requisiti tecnici del tutto inaccessibili a una PMI del Cilento o della Campania in generale. Non esistono spese finanziabili né settori applicabili al tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di piattaforme robotiche/droni per la raccolta e smaltimento di munizioni inesplose, richiedendo capacità tecnologiche avanzate nel settore della difesa e consorzio multinazionale: barriere d'accesso (requisiti tecnici, industriali e finanziari) praticamente insuperabili per una PMI del Cilento senza consolidata esperienza nel comparto difesa/robotica militare.</t>
+          <t>Il bando EDF riguarda lo sviluppo di piattaforme robotiche/droni per la raccolta e smaltimento di munizioni inesplose, un settore altamente specializzato della difesa che richiede capacità tecnologiche e certificazioni difficilmente accessibili per una PMI del Cilento. I requisiti tecnici, i partner istituzionali necessari e i volumi di investimento tipici dell'EDF lo rendono di fatto inaccessibile per realtà produttive locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) sui sistemi di auto-protezione è destinato a consorzi di imprese della difesa con elevate capacità tecnologiche e di R&amp;S militare, requisiti del tutto estranei alla struttura tipica di una PMI del Cilento. I costi di partecipazione, la complessità burocratica e i requisiti di sicurezza/clearance lo rendono di fatto inaccessibile senza partnership con grandi prime contractor della difesa.</t>
+          <t>Il bando EDF (European Defence Fund) sui sistemi di auto-protezione è destinato a consorzi di aziende della difesa con elevate capacità tecnologiche e certificazioni specifiche del settore militare, requisiti difficilmente soddisfatti da una PMI del Cilento. I costi di partecipazione, la complessità burocratica e la necessità di partnership internazionali rendono questo bando di fatto inaccessibile per realtà produttive locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF per sistemi lanciarazzi multipli è destinato a consorzi industriali della difesa con capacità tecnologiche e produttive altamente specializzate, del tutto fuori portata per una PMI del Cilento. Non esistono requisiti tecnici, finanziari o settoriali compatibili con la struttura tipica di una piccola impresa campana.</t>
+          <t>Il bando EDF 'Multiple Rocket Launcher' finanzia lo sviluppo di sistemi d'arma complessi nell'ambito della difesa europea, richiedendo capacità tecnologiche, certificazioni e requisiti di sicurezza tipici di grandi contractor della difesa. Una PMI del Cilento non possiede strutturalmente le competenze industriali né le accreditazioni necessarie per partecipare a progetti di questo tipo.</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa ad alte prestazioni energetiche, richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni specifiche del settore difesa. Una PMI del Cilento difficilmente possiede i requisiti tecnici, le partnership internazionali e le abilitazioni di sicurezza necessarie per partecipare competitivamente a questa tipologia di bando.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa europea, richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni militari che esulano completamente dal profilo di una PMI campana del Cilento. I requisiti di partecipazione, i budget coinvolti e la natura difensiva del programma rendono questo bando di fatto inaccessibile per realtà produttive locali di piccola e media dimensione.</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa militare, richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni di sicurezza difficilmente accessibili a una PMI del Cilento. Il tema della mobilità militare digitale sicura presuppone competenze altamente specializzate in cybersecurity e sistemi di difesa, lontane dal tessuto produttivo locale.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia progetti di ricerca e sviluppo nel settore della difesa militare, richiedendo consorzi internazionali con capacità tecnologiche avanzate e certificazioni di sicurezza difficilmente accessibili per una PMI del Cilento. Il focus su sistemi di mobilità militare digitale sicura lo rende di fatto riservato a grandi industrie della difesa o istituti di ricerca specializzati.</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia sistemi avanzati di guerra elettronica cognitiva (EW) e analisi di segnali RESM/CESM, ambito riservato a grandi aziende della difesa con capacità tecnologiche e certificazioni militari specifiche. Una PMI del Cilento o della Campania in generale difficilmente possiede i requisiti tecnici, le clearance di sicurezza e la massa critica per partecipare, se non come partner junior in un consorzio guidato da player come Leonardo o Thales.</t>
+          <t>Il bando EDF finanzia sistemi avanzati di guerra elettronica cognitiva (EW) con analisi intelligente dei segnali RESM/CESM, richiedendo competenze altamente specializzate in difesa e tecnologie militari tipiche di grandi contractor della difesa o centri di ricerca. Una PMI del Cilento difficilmente dispone delle certificazioni di sicurezza NATO, delle capacità tecniche e dei requisiti di compliance necessari per partecipare a questo tipo di progetto europeo nel settore difesa.</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia lo sviluppo di navi di superficie semi-autonome di medie dimensioni per scopi difensivi, richiedendo capacità tecnologiche avanzate, consorzi industriali e requisiti di sicurezza tipici della difesa europea, del tutto fuori portata per una PMI del Cilento. Non sono previste spese finanziabili rilevanti per realtà produttive locali di piccola-media dimensione senza expertise nel settore navale-militare.</t>
+          <t>Il bando EDF riguarda lo sviluppo di vascelli semi-autonomi di media taglia per la difesa europea, richiedendo capacità tecnologiche avanzate, consorzi internazionali e investimenti ingenti tipici di grandi aziende della difesa e aerospazio. Una PMI del Cilento, anche operante nel settore nautico o marittimo, difficilmente possiede i requisiti tecnici, finanziari e di certificazione necessari per partecipare.</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo su tecnologie avanzate per sistemi d'arma di nuova generazione, un settore altamente specializzato che richiede capacità industriali e tecnologiche tipiche di grandi prime contractor della difesa. Una PMI del Cilento, salvo rari casi di nicchia in elettronica o sistemi embedded per il comparto difesa, non dispone dei requisiti tecnici, dei partner consortili né delle certificazioni necessarie per accedere competitivamente a questo tipo di bando europeo.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa per sistemi avanzati da combattimento aereo, richiedendo consorzi transnazionali con capacità tecnologiche e industriali di alto livello difficilmente accessibili a una PMI del Cilento. Le risorse finanziabili riguardano R&amp;S in aeronautica militare e tecnologie critiche, ambiti estranei al tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda lo sviluppo di sistemi per carri armati da combattimento di nuova generazione, un settore della difesa ad altissima specializzazione tecnologica e industriale accessibile solo a grandi contractor della difesa o consorzi multinazionali. Una PMI del Cilento o della Campania non dispone delle certificazioni, delle capacità produttive né dei requisiti di sicurezza necessari per partecipare a questo tipo di programma europeo di armamento.</t>
+          <t>Il bando EDF riguarda lo sviluppo di piattaforme per carri armati da combattimento di nuova generazione, un settore della difesa ad altissima specializzazione tecnologica che richiede capacità industriali, certificazioni e partnership difficilmente accessibili a una PMI del Cilento o della Campania in generale. Le opportunità di partecipazione diretta sono riservate a grandi contractor della difesa o a PMI già integrate in consorzi industriali militari europei consolidati.</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca nel settore della difesa europea, richiedendo consorzi internazionali e competenze tecnologiche altamente specializzate difficilmente accessibili a una PMI del Cilento. I costi di partecipazione, la complessità burocratica e la necessità di essere inseriti in supply chain della difesa rendono questo strumento di fatto inaccessibile per le piccole imprese locali senza esperienza pregressa nel settore militare.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca nel settore della difesa europea, richiedendo consorzi internazionali con capacità tecnologiche avanzate e competenze militari difficilmente replicabili da una PMI manifatturiera o di servizi del Cilento. I costi di partecipazione, la complessità procedurale e i requisiti di sicurezza/abilitazione industriale rendono questo bando di fatto inaccessibile per la quasi totalità delle PMI campane di piccola dimensione.</t>
         </is>
       </c>
     </row>
@@ -11654,12 +11654,12 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca su tecnologie dirompenti per la difesa, richiedendo consorzi multinazionali con elevate competenze tecnico-militari e capacità di R&amp;S avanzata: barriere difficilmente superabili per una PMI del Cilento senza una specializzazione specifica nel settore difesa e senza partnership internazionali già consolidate.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo su tecnologie dirompenti per la difesa, con requisiti consortili complessi e capacità tecnologiche avanzate tipiche di grandi aziende del settore difesa o centri di ricerca specializzati. Una PMI del Cilento o della Campania difficilmente dispone delle competenze certificate in ambito militare e delle risorse necessarie per partecipare a questo tipo di bando europeo ad alta specializzazione.</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Sustainable Gender Equality Champions' è orientato a consorzi di ricerca e grandi organizzazioni con capacità progettuale europea, richiedendo competenze amministrative e budget elevati difficilmente sostenibili da una PMI del Cilento. L'approccio gender equality in chiave di ricerca e innovazione sistemica lo rende poco accessibile senza un partenariato accademico strutturato.</t>
+          <t>Il bando Horizon 'Sustainable Gender Equality Champions' è orientato a consorzi di ricerca e grandi organizzazioni con capacità progettuale europea, richiedendo partnership internazionali e rendicontazione complessa tipica di Horizon Europe, del tutto sproporzionata per una PMI del Cilento. Non prevede finanziamenti diretti per attività produttive, commerciali o di sviluppo locale tipiche delle piccole imprese campane.</t>
         </is>
       </c>
     </row>
@@ -11748,12 +11748,12 @@
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon dedicato alla parità di genere è orientato tipicamente a enti di ricerca, università e grandi consorzi transnazionali, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un partner capofila accademico. Le PMI potrebbero partecipare solo come soggetti associati in progetti coordinati da istituzioni di ricerca, con margini operativi e finanziari limitati.</t>
+          <t>Il bando Horizon 'Newcomer Gender Equality Champions' è orientato a consorzi di ricerca e organizzazioni con forte componente scientifica e istituzionale, richiedendo competenze progettuali europee avanzate e partnership internazionali difficilmente accessibili a una PMI del Cilento. Il tema della parità di genere per 'newcomers' (nuovi arrivati/migranti) non intercetta i settori produttivi tipici dell'area come turismo, agricoltura o artigianato.</t>
         </is>
       </c>
     </row>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU dedicato alla parità di genere è orientato principalmente a enti di ricerca, università e grandi consorzi europei, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza un partenariato strutturato. Le spese finanziabili riguardano ricerca, disseminazione e implementazione di politiche di inclusione, ambiti distanti dalle priorità operative tipiche di una piccola impresa campana.</t>
+          <t>Il bando Horizon sulla parità di genere è orientato principalmente a enti di ricerca, università e grandi consorzi europei, con requisiti di partecipazione transnazionale e capacità progettuale elevata difficilmente sostenibili da una PMI del Cilento. Le spese finanziabili riguardano ricerca e disseminazione su politiche di inclusione, non attività produttive o commerciali tipiche delle PMI locali.</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 finanzia grandi opere infrastrutturali su reti energetiche transeuropee (smart grid, idrogeno, CO₂), con requisiti tecnici e finanziari accessibili solo a grandi operatori di rete o consorzi pubblici-privati di scala europea. Una PMI del Cilento non ha le dimensioni, le competenze né la capacità progettuale per candidarsi direttamente a questo tipo di appalto.</t>
+          <t>Il bando CEF 2027 finanzia grandi opere infrastrutturali su reti energetiche transnazionali (smart grid, idrogeno, CO₂, elettricità e gas) tipicamente riservate a operatori di rete, consorzi pubblici o grandi operatori del settore energetico, rendendo l'accesso di una PMI del Cilento di fatto inaccessibile senza partnership con soggetti di rilevanza europea. Le spese finanziabili riguardano costruzione e ammodernamento di infrastrutture critiche, ambito incompatibile con la scala operativa di una piccola o media impresa locale.</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia studi su reti energetiche transeuropee (smart grid, idrogeno, CO₂) con target primario enti pubblici, gestori di rete e grandi operatori energetici: una PMI del Cilento difficilmente possiede i requisiti tecnici e la scala progettuale richiesta. Le spese finanziabili riguardano studi di fattibilità su infrastrutture critiche di interesse europeo, ambito praticamente inaccessibile per realtà di piccola-media dimensione.</t>
+          <t>Il bando CEF 2027 finanzia studi su reti energetiche transeuropee (smart grid, idrogeno, CO₂) e si rivolge tipicamente a gestori di rete, enti pubblici e grandi consorzi, non a PMI campane. Una piccola impresa del Cilento non ha né la struttura né il profilo tecnico-finanziario per accedere a questo tipo di progettualità infrastrutturale a scala europea.</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di standard tecnici per le tecnologie quantistiche nell'ambito del programma Horizon UE, un settore altamente specializzato che richiede competenze di ricerca avanzata e infrastrutture tecnologiche difficilmente accessibili a una PMI del Cilento o della Campania in generale. Non sono previste attività finanziabili tipiche delle piccole imprese locali, e il contesto operativo richiede partnership con grandi centri di ricerca o università di settore specifico.</t>
+          <t>Il bando riguarda lo sviluppo di standard tecnici per tecnologie quantistiche nell'ambito del programma Horizon UE, un settore altamente specializzato che richiede competenze di ricerca avanzata e infrastrutture difficilmente compatibili con una PMI di piccola dimensione nel Cilento. L'accesso è di fatto limitato a grandi enti di ricerca, università o aziende tech strutturate con capacità di partecipazione a consorzi europei.</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia lo sviluppo di piattaforme tecnologiche per il quantum computing fotonico su larga scala, richiedendo capacità di ricerca avanzata, infrastrutture specializzate e consorzi internazionali tipicamente riservati a grandi laboratori e multinazionali del settore tech. Una PMI del Cilento, anche se operante nell'ICT o nell'elettronica, difficilmente possiede le competenze scientifiche e la massa critica necessarie per partecipare competitivamente a questo tipo di progetto Horizon.</t>
+          <t>Il bando finanzia ricerca avanzata su piattaforme di quantum computing fotonico su scala industriale, richiedendo capacità tecnologiche e infrastrutture di ricerca tipiche di grandi consorzi europei o centri universitari specializzati. Una PMI del Cilento o della Campania in generale non possiede le competenze tecniche né la massa critica per partecipare competitivamente a questo tipo di progetto Horizon.</t>
         </is>
       </c>
     </row>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti pilota di intelligenza artificiale applicata allo screening di immagini mediche, richiedendo competenze tecnologiche avanzate e partnership con centri medici strutturati, il che lo rende difficilmente accessibile per una PMI generalista del Cilento. Solo aziende già attive nello sviluppo di software medicale o diagnostica digitale potrebbero candidarsi con realistica possibilità di successo.</t>
+          <t>Il bando è orientato a progetti pilota di AI applicata allo screening di immagini mediche, richiedendo competenze tecnologiche avanzate e partnership con centri medici strutturati, caratteristiche difficilmente compatibili con una PMI generalista del Cilento. Solo aziende già attive nello sviluppo di software medicale o diagnostica digitale potrebbero candidarsi con realistica possibilità di successo.</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato allo sviluppo di soluzioni digitali per la conformità normativa basate sui dati, con un focus su grandi progetti di ricerca e infrastrutture digitali europee che difficilmente rientrano nelle capacità operative e progettuali di una PMI del Cilento. Le PMI di piccola dimensione trovano solitamente barriere elevate nei bandi DIGITAL EU per requisiti tecnici, consorzio e cofinanziamento richiesti.</t>
+          <t>Il bando UE-DIGITAL sulle soluzioni digitali per la compliance normativa è tipicamente orientato a grandi consorzi tecnologici o enti di ricerca capaci di sviluppare infrastrutture dati complesse, rendendo difficile l'accesso diretto per una PMI del Cilento senza un partenariato strutturato. Le PMI di piccola dimensione difficilmente possiedono le competenze tecniche e la capacità progettuale richiesta da bandi Horizon/Digital Europe di questa natura.</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia attività di disseminazione e sfruttamento dei risultati nell'ambito del Programma Europa Digitale, rivolto principalmente a enti di ricerca, consorzi pubblici e grandi organizzazioni con capacità di gestione di progetti europei complessi. Una PMI del Cilento difficilmente possiede i requisiti tecnici e amministrativi per candidarsi autonomamente, e i costi ammissibili riguardano comunicazione istituzionale e trasferimento tecnologico su scala europea, non investimenti aziendali diretti.</t>
+          <t>Il bando finanzia attività di disseminazione e sfruttamento dei risultati del Programma Europa Digitale, rivolgendosi principalmente a enti di ricerca, consorzi e grandi organizzazioni con capacità di comunicazione istituzionale a livello europeo. Una PMI del Cilento non ha le strutture né il profilo richiesto per partecipare direttamente a questo tipo di azione.</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>Il bando è orientato a enti di ricerca e organizzazioni con capacità tecniche avanzate nel campo della sicurezza informativa e della disinformazione, richiedendo competenze specialistiche difficilmente disponibili in una PMI del Cilento. Non prevede spese tipicamente accessibili a piccole imprese locali né ha connessione con i settori produttivi prevalenti dell'area come turismo, agricoltura o artigianato.</t>
+          <t>Il bando è orientato a finanziare enti di ricerca e grandi organizzazioni per sviluppare framework di analisi sull'integrità dell'informazione e la consapevolezza situazionale, ambiti altamente specialistici che esulano dalle capacità operative e progettuali tipiche di una PMI campana, specie nel Cilento. L'accesso richiede competenze tecniche avanzate in cybersecurity e information science difficilmente presenti in una piccola impresa locale.</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti multi-paese nell'ambito degli EDIC (European Digital Infrastructure Consortia), strutture sovranazionali destinate a grandi consorzi pubblici e istituzionali: una PMI del Cilento non ha i requisiti dimensionali né la capacità di coordinamento internazionale per partecipare direttamente. L'accesso indiretto come partner minore è teoricamente possibile ma estremamente difficile senza una rete europea consolidata.</t>
+          <t>Il bando finanzia hub di supporto per progetti digitali multi-paese nell'ambito delle EDIC (European Digital Infrastructure Consortia), strutture di governance sovranazionale non accessibili direttamente a PMI singole o a realtà locali come quelle del Cilento. Una PMI campana potrebbe al massimo beneficiarne indirettamente come soggetto coinvolto da un consorzio già costituito, ma non può candidarsi autonomamente.</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia la costruzione di infrastrutture e capacità istituzionali per lo Spazio Europeo dei Dati Sanitari (EHDS) e servizi di sanità digitale, targeting principalmente enti pubblici, autorità sanitarie nazionali e grandi consorzi istituzionali. Una PMI del Cilento, anche operante in ambito healthtech o ICT sanitario, difficilmente ha la struttura tecnica e amministrativa per guidare o partecipare competitivamente a progetti di questa complessità europea.</t>
+          <t>Il bando riguarda lo sviluppo dell'infrastruttura europea per la condivisione di dati sanitari (EHDS) e i sistemi di cartella clinica elettronica, ed è rivolto principalmente a enti pubblici, autorità sanitarie nazionali e grandi consorzi istituzionali. Una PMI del Cilento, anche operante nel settore ICT o sanità digitale, difficilmente possiede i requisiti tecnici e istituzionali per candidarsi in autonomia, potendo al massimo partecipare come partner secondario in un consorzio europeo.</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>Il bando è destinato alla costruzione di una rete europea di Safer Internet Centres con copertura geografica capillare, richiedendo capacità organizzative e infrastrutturali tipiche di enti pubblici, università o grandi consorzi; una PMI del Cilento difficilmente possiede i requisiti dimensionali e istituzionali per candidarsi come soggetto capofila o partner rilevante in un progetto di questa portata.</t>
+          <t>Il bando finanzia la creazione e gestione di Centri Internet Sicuro (SIC) a copertura geografica europea, richiedendo strutture istituzionali complesse e reti consolidate: non è pensato per PMI tradizionali del Cilento, ma per enti pubblici, università o grandi consorzi specializzati nella sicurezza online per minori.</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto specificamente al settore EdTech (tecnologie per l'educazione) e tende a premiare startup o scaleup digitali con forte vocazione innovativa, risultando poco accessibile per una PMI tradizionale del Cilento non operante in questo settore. Una PMI locale difficilmente possiede i requisiti tecnici e il profilo digitale richiesto da un acceleratore europeo di questo tipo.</t>
+          <t>Il bando è focalizzato su startup e scale-up del settore EdTech (tecnologie per l'educazione), con requisiti di innovazione digitale avanzata difficilmente compatibili con la struttura tipica di una PMI tradizionale del Cilento. Salvo che l'impresa operi specificamente nello sviluppo di piattaforme o soluzioni digitali per la formazione, le barriere tecnologiche e competitive rendono l'accesso molto improbabile per realtà locali di piccole dimensioni.</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto principalmente a coalizioni nazionali e grandi organizzazioni impegnate nella promozione delle competenze digitali su scala sistemica, non a singole PMI. Una piccola impresa del Cilento non può accedere direttamente ai fondi, ma potrebbe beneficiarne indirettamente aderendo a iniziative promosse dalla coalizione italiana (Repubblica Digitale).</t>
+          <t>Il bando è rivolto a coalizioni nazionali e organizzazioni di grande scala per lo sviluppo di competenze digitali a livello sistemico, non a singole PMI: una piccola impresa del Cilento non può candidarsi direttamente ma solo come partner subordinato di grandi consorzi. Le spese finanziabili riguardano programmi formativi su competenze digitali strutturati a livello nazionale, difficilmente accessibili in autonomia da una realtà locale di piccole dimensioni.</t>
         </is>
       </c>
     </row>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti su competenze digitali avanzate per l'adozione dell'AI in ambito sanitario, ma è rivolto tipicamente a grandi consorzi, università e organizzazioni del settore salute, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza una partnership strutturata. Una piccola impresa potrebbe al massimo partecipare come partner secondario, ma la complessità progettuale e i requisiti europei scoraggiano un coinvolgimento autonomo.</t>
+          <t>Il bando finanzia progetti per lo sviluppo di competenze digitali avanzate sull'IA in ambito sanitario, ma è tipicamente rivolto a consorzi di università, enti di ricerca e grandi organizzazioni, rendendo l'accesso diretto per una PMI del Cilento estremamente complesso. Una piccola impresa potrebbe al massimo partecipare come partner secondario in un consorzio, ma difficilmente come beneficiario principale.</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la cooperazione amministrativa tra autorità pubbliche sul distacco dei lavoratori transfrontalieri, rivolto principalmente a enti pubblici e istituzioni, non a PMI. Una piccola impresa del Cilento non ha titolo per candidarsi direttamente né beneficia di finanziamenti per attività produttive o investimenti aziendali.</t>
+          <t>Il bando ESF riguarda la cooperazione amministrativa tra autorità pubbliche sul distacco transnazionale dei lavoratori (Direttiva 96/71/CE), ed è destinato a enti pubblici, parti sociali o organismi istituzionali, non a PMI. Una piccola impresa del Cilento non ha titolo per candidarsi direttamente né trae vantaggi finanziari immediati da questo tipo di iniziativa.</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 Rail finanzia studi e lavori su infrastrutture ferroviarie trans-europee, destinato tipicamente a gestori di rete, enti pubblici e grandi consorzi: una PMI del Cilento non ha né la scala dimensionale né il profilo istituzionale per candidarsi direttamente. Il territorio del Cilento, inoltre, è scarsamente integrato nella rete TEN-T ferroviaria prioritaria, rendendo improbabile anche una partecipazione indiretta come subappaltatore.</t>
+          <t>Il bando CEF 2027 per infrastrutture ferroviarie finanzia studi di fattibilità e lavori su reti TEN-T, rivolto principalmente a gestori di infrastrutture pubbliche e grandi consorzi: una PMI del Cilento non ha i requisiti dimensionali né il ruolo istituzionale per candidarsi direttamente. L'unica via di accesso indiretta sarebbe come subappaltatore specializzato in ingegneria ferroviaria o costruzioni, ma con margini di coinvolgimento molto limitati.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 Rail finanzia studi e opere infrastrutturali ferroviarie di rilevanza europea, rivolti tipicamente a gestori di rete, enti pubblici e grandi consorzi: una PMI del Cilento non ha né la scala dimensionale né il profilo istituzionale per accedervi direttamente. L'unica possibilità residua sarebbe partecipare come subappaltatore in un consorzio, ma rimane uno scenario estremamente remoto per una piccola impresa locale.</t>
+          <t>Il bando CEF 2027 finanzia studi e lavori infrastrutturali ferroviari su scala europea, rivolto principalmente a gestori di rete e grandi consorzi pubblici: una PMI del Cilento non ha né la dimensione né il profilo istituzionale per accedere direttamente a questi fondi. Il territorio del Cilento, peraltro, non rientra nei corridoi della rete TEN-T prioritaria che il bando intende sviluppare.</t>
         </is>
       </c>
     </row>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia opere infrastrutturali su vie navigabili interne di rilevanza europea, richiedendo soggetti proponenti di natura pubblica o grandi operatori del settore dei trasporti: una PMI del Cilento, territorio privo di vie d'acqua navigabili di interesse transeuropeo, non ha né i requisiti soggettivi né il contesto geografico per partecipare. Le spese ammissibili riguardano costruzione e ammodernamento di infrastrutture fluviali, ambito del tutto estraneo al tessuto produttivo locale.</t>
+          <t>Il bando CEF 2027 per le vie navigabili interne finanzia grandi opere infrastrutturali su corridoi di trasporto europei, richiedendo capacità progettuali e finanziarie tipiche di enti pubblici o grandi imprese. Il Cilento, inoltre, non è attraversato da vie navigabili interne rilevanti ai fini del bando, rendendo il territorio sostanzialmente escluso dall'ambito geografico di applicazione.</t>
         </is>
       </c>
     </row>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF (Connecting Europe Facility) finanzia opere infrastrutturali su reti di trasporto transeuropee, con importi e requisiti tecnici-amministrativi pensati per grandi enti pubblici o consorzi di operatori del settore trasporti, non per PMI. Una piccola impresa del Cilento non avrebbe né la capacità progettuale né il profilo richiesto per partecipare direttamente a questo tipo di gara.</t>
+          <t>Il bando CEF 2027 finanzia grandi opere infrastrutturali per la digitalizzazione del trasporto stradale (es. sistemi ITS, corridoi TEN-T), rivolte tipicamente a enti pubblici, gestori di reti o grandi consorzi europei. Una PMI del Cilento non ha le dimensioni né la capacità progettuale per accedere direttamente a questo tipo di call.</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF2027 sulle frontiere esterne finanzia grandi infrastrutture di controllo e gestione dei confini dell'UE, rivolto principalmente a Stati membri e grandi enti pubblici: una PMI del Cilento non ha né i requisiti soggettivi né la capacità progettuale per accedervi. Non sono previste spese tipicamente sostenibili da imprese private di piccola dimensione.</t>
+          <t>Il bando CEF2027 'External Borders' finanzia studi e opere infrastrutturali per la gestione delle frontiere esterne dell'UE, con destinatari tipici quali Stati membri, autorità doganali e enti pubblici di grande scala. Una PMI del Cilento non ha titolo né capacità strutturale per partecipare direttamente a questo tipo di appalti sovranazionali.</t>
         </is>
       </c>
     </row>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia opere infrastrutturali di grande scala nel settore marittimo e portuale europeo, tipicamente riservate a enti pubblici, autorità portuali o grandi consorzi. Una PMI del Cilento non dispone della capacità tecnico-finanziaria né della titolarità istituzionale richiesta per candidarsi direttamente a interventi di questo tipo.</t>
+          <t>Il bando CEF (Connecting Europe Facility) finanzia grandi opere infrastrutturali nel settore marittimo e portuale, richiedendo capacità progettuali e finanziarie tipiche di enti pubblici o grandi operatori del settore. Una PMI del Cilento non ha accesso diretto a questo tipo di finanziamento, riservato a progetti di scala europea con investimenti nell'ordine di decine di milioni di euro.</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia studi e opere per l'adeguamento della rete TEN-T ad uso civile-militare, ed è destinato a Stati membri, gestori di infrastrutture e organismi pubblici, non a PMI. Una piccola o media impresa del Cilento non ha i requisiti soggettivi né la capacità progettuale per accedere direttamente a questo tipo di finanziamento infrastrutturale strategico.</t>
+          <t>Il bando CEF2 riguarda studi e lavori sulla rete transeuropea di trasporto (TEN-T) ad uso duale civile-militare, destinato principalmente a Stati membri, gestori di infrastrutture e grandi enti pubblici. Una PMI del Cilento non ha titolarità diretta per partecipare né capacità tecnico-finanziaria per interventi di questa scala infrastrutturale.</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF finanzia grandi opere infrastrutturali per carburanti alternativi (stazioni di ricarica/rifornimento su strade e aeroporti) destinate tipicamente a grandi consorzi, enti pubblici o grandi imprese. Una PMI del Cilento non ha né la capacità finanziaria né il profilo tecnico-amministrativo richiesto per accedere direttamente a finanziamenti europei di questa scala e complessità.</t>
+          <t>Il bando CEF2027 finanzia opere infrastrutturali su larga scala per carburanti alternativi nel trasporto stradale e aereo, con requisiti tecnici, finanziari e amministrativi pensati per grandi operatori pubblici o consorzi internazionali. Una PMI del Cilento non ha le dimensioni né le capacità progettuali per candidarsi direttamente come beneficiaria principale.</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede consorzi internazionali, elevata capacità di ricerca e sviluppo e budget progettuali nell'ordine dei milioni di euro, rendendolo praticamente inaccessibile per una PMI edile del Cilento senza un solido network europeo e competenze specifiche in economia circolare a scala urbana. Una piccola impresa delle costruzioni potrebbe al massimo partecipare come partner minore, ma difficilmente assumere un ruolo guida.</t>
+          <t>Il bando Horizon UE richiede progetti di ricerca e innovazione su modelli di economia circolare nell'edilizia a scala urbana, con consorziate internazionali e capacità di ricerca avanzata difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento nel settore costruzioni potrebbe partecipare solo come partner secondario di un consorzio europeo, con oneri amministrativi e progettuali molto elevati rispetto alle capacità tipiche di una piccola impresa locale.</t>
         </is>
       </c>
     </row>
@@ -12970,12 +12970,12 @@
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si concentra su soluzioni di trasporto pubblico urbano e suburbano ad alta efficienza energetica e mobilità condivisa, con requisiti progettuali e consorziali tipici di grandi enti pubblici o consorzi di ricerca. Una PMI del Cilento, territorio prevalentemente rurale e a bassa densità urbana, difficilmente possiede le competenze tecniche e la capacità aggregativa necessarie per candidarsi competitivamente a un programma Horizon di questa complessità.</t>
+          <t>Il bando Horizon europeo sul trasporto pubblico urbano efficiente richiede consorzi di ricerca, capacità progettuali elevate e focus su sistemi di mobilità collettiva, ambiti difficilmente gestibili da una PMI campana di piccole dimensioni senza partnership strutturate. Il Cilento, territorio prevalentemente rurale e a mobilità privata, risulta scarsamente allineato con i requisiti tipici di questo tipo di call orientata a contesti urbani e infrastrutture di trasporto pubblico.</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede progetti di ricerca e innovazione ad alta complessità tecnica e amministrativa, con consorzio internazionale e budget elevati, struttura difficilmente accessibile per una PMI del Cilento senza un solido network europeo e competenze specifiche nel settore riscaldamento a bassa temperatura per edifici condominiali. Il territorio cilentano, caratterizzato prevalentemente da edilizia sparsa e turistica piuttosto che da grandi condomini, rende ulteriormente poco strategico questo specifico topic.</t>
+          <t>Il bando Horizon UE richiede la partecipazione in consorzi internazionali con capacità di ricerca avanzata e budget elevati, rendendo l'accesso estremamente difficile per una PMI campana di piccola dimensione operante nel Cilento. Il focus sulle soluzioni di riscaldamento a bassa temperatura per edifici multi-appartamento implica competenze tecniche specialistiche e strutture di progetto tipiche di grandi player o centri di ricerca, non di PMI locali del settore edilizio o impiantistico.</t>
         </is>
       </c>
     </row>
@@ -13069,7 +13069,7 @@
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>Il bando CCAM (Connected, Cooperative and Automated Mobility) finanzia dimostrazioni su larga scala di mobilità autonoma e connessa, richiedendo consorzi di grandi dimensioni con capacità tecniche e finanziarie elevate, del tutto fuori dalla portata di una PMI campana tipica. Per una realtà del Cilento, priva di infrastrutture di test per veicoli autonomi e lontana dai cluster automotive europei, le possibilità di partecipazione attiva o di ruolo significativo nel progetto sono praticamente nulle.</t>
+          <t>Il bando CCAM (Connected, Cooperative and Automated Mobility) finanzia dimostratori su larga scala per la mobilità autonoma e connessa, richiedendo consorzi internazionali con capacità tecniche e finanziarie elevate, del tutto fuori dalla portata di una PMI campana di piccole dimensioni. Il contesto del Cilento, caratterizzato da mobilità rurale e infrastrutture limitate, non offre le condizioni né le partnership necessarie per partecipare a progetti pilota di questa complessità.</t>
         </is>
       </c>
     </row>
@@ -13111,12 +13111,12 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE sulla competitività del trasporto merci multimodale è orientato a consorzi di grandi organizzazioni, università e centri di ricerca, con requisiti tecnici e amministrativi difficilmente sostenibili da una PMI del Cilento. Il settore logistico/trasporti non rappresenta una filiera trainante per le piccole imprese di quest'area, prevalentemente attive in turismo, agricoltura e artigianato.</t>
+          <t>Il bando Horizon UE è orientato a progetti di ricerca e innovazione su scala europea nel settore della logistica multimodale, richiedendo consorzi internazionali e capacità progettuali elevate difficilmente accessibili a una PMI campana di piccola dimensione. Per una realtà del Cilento, territorio periferico con logistica ancora poco strutturata, le barriere di accesso (co-finanziamento, partnership transnazionali, rendicontazione Horizon) rendono la partecipazione diretta quasi impraticabile senza un ente capofila universitario o industriale.</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>Il bando HORIZON riguarda la ricerca sulla mobilità connessa e automatizzata (CCAM) in chiave geopolitica e di resilienza socioeconomica europea, un ambito altamente specializzato che richiede capacità di ricerca avanzata e partenariati internazionali strutturati, difficilmente accessibili per una PMI del Cilento senza una consolidata esperienza in R&amp;S nel settore automotive/mobilità. Le PMI campane potrebbero partecipare solo come partner junior in consorzi europei guidati da grandi enti di ricerca o multinazionali.</t>
+          <t>Il bando Horizon CCAM riguarda la mobilità connessa e automatizzata in chiave geopolitica ed è progettato per consorzi di grandi attori (università, centri di ricerca, multinazionali), con livelli di complessità progettuale e capacità finanziaria incompatibili con una PMI del Cilento. Il territorio cilentano, inoltre, non esprime una filiera produttiva legata alla mobilità autonoma che possa giustificare la partecipazione anche in ruolo secondario.</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su sicurezza stradale e resilienza delle aree rurali è orientato a consorzi di ricerca, università ed enti pubblici, richiedendo capacità progettuali e finanziarie difficilmente sostenibili da una PMI campana di piccole dimensioni. Sebbene il Cilento rientri nelle aree rurali target, una PMI dovrebbe partecipare solo come partner di un consorzio guidato da soggetti di ricerca, con un ruolo marginale e risorse dedicate alla gestione amministrativa europea.</t>
+          <t>Il bando Horizon focalizzato sulla sicurezza stradale e resilienza delle aree rurali è tipicamente destinato a consorzi di ricerca, università ed enti pubblici, con requisiti tecnici e finanziari difficilmente accessibili per una PMI campana di piccole dimensioni. Sebbene il Cilento rientri nelle aree rurali di riferimento, una PMI avrebbe bisogno di partecipare come partner junior in un consorzio europeo, rendendo l'accesso diretto molto improbabile.</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede la partecipazione a consorzi internazionali con capacità di R&amp;D avanzata in intelligenza artificiale e trasporto multimodale, competenze difficilmente disponibili in una PMI del Cilento. I requisiti tecnici e amministrativi di Horizon Europe rendono questo bando accessibile solo a grandi player tecnologici o centri di ricerca, con budget e strutture dedicate alla progettazione europea.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata su AI e trasporti multimodali, con consorzio internazionale e budget tipicamente superiori ai 3-5M€, strutture difficilmente accessibili per una PMI campana di piccole dimensioni senza un ruolo di partner tecnico specializzato. Una PMI del Cilento potrebbe partecipare solo come partner secondario all'interno di un consorzio guidato da università o grandi aziende del settore trasporti, senza possibilità concreta di essere capofila.</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>Il bando CIVITAS di Horizon Europe è orientato a progetti di mobilità urbana sostenibile su scala cittadina, richiedendo consorzi internazionali e capacità tecniche e finanziarie tipiche di grandi enti pubblici o grandi imprese. Una PMI del Cilento, territorio prevalentemente rurale e a bassa densità urbana, difficilmente rientra tra i soggetti capofila o beneficiari diretti di questo tipo di iniziativa.</t>
+          <t>Il bando CIVITAS di Horizon Europe è orientato a progetti di mobilità urbana sostenibile su larga scala, richiedendo consorzi internazionali e competenze tecniche elevate, con budget e complessità gestionale fuori dalla portata di una PMI del Cilento, territorio peraltro a vocazione rurale e non urbana. Una piccola impresa campana difficilmente può fungere da capofila o partner strategico in un progetto di trasformazione della mobilità cittadina europea.</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sul tema CCAM (Connected, Cooperative and Automated Mobility) con focus su AI generativa richiede consorzi internazionali complessi, capacità di R&amp;D avanzata e risorse di co-finanziamento elevate, rendendolo di fatto inaccessibile per la grande maggioranza delle PMI campane e cilentane, che operano prevalentemente in settori tradizionali come turismo, agricoltura e artigianato. Una PMI del Cilento potrebbe partecipare solo come partner minore in un consorzio guidato da grandi player tecnologici o università, scenario difficilmente praticabile senza reti consolidate nel settore automotive/AI.</t>
+          <t>Il bando Horizon CCAM riguarda lo sviluppo di sistemi di trasporto connesso e automatizzato tramite intelligenza artificiale generativa, un settore altamente specializzato che richiede capacità di R&amp;S avanzata e partnership internazionali difficilmente accessibili per una PMI del Cilento. I costi di partecipazione elevati e la complessità dei consorzi europei richiesti lo rendono di fatto poco fruibile senza strutture dedicate alla ricerca.</t>
         </is>
       </c>
     </row>
@@ -13398,7 +13398,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulle batterie al litio di nuova generazione per la mobilità richiede capacità di R&amp;D avanzata, infrastrutture industriali e partnership internazionali difficilmente accessibili per una PMI del Cilento, territorio privo di filiere automotive o manifatturiero-energetiche strutturate in questo settore. Le spese finanziabili riguardano ricerca industriale e sviluppo sperimentale su tecnologie di cella e produzione di batterie, ambiti estranei al tessuto produttivo locale.</t>
+          <t>Il bando Horizon Europe sulle batterie al litio di nuova generazione è orientato a grandi consorzi industriali e centri di ricerca con capacità di R&amp;D avanzata nel settore automotive/energy storage, ambiti lontani dalla struttura produttiva e dalla vocazione economica del Cilento e delle PMI campane tipiche. Una PMI locale difficilmente possiede le competenze tecnologiche specifiche e la massa critica necessaria per partecipare competitivamente a partnership europee di questa complessità.</t>
         </is>
       </c>
     </row>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>Il bando CEF 2027 finanzia opere infrastrutturali per la riparazione di cavi sottomarini di telecomunicazione, richiedendo capacità tecniche, finanziarie e operative di scala industriale del tutto incompatibili con una PMI del Cilento. Si tratta di appalti destinati a grandi consorzi o aziende specializzate nel settore navale e delle telecomunicazioni subacquee.</t>
+          <t>Il bando CEF 2027 finanzia lavori di riparazione di cavi sottomarini per le reti di telecomunicazione transeuropee, un settore che richiede capacità tecniche, certificazioni e investimenti di scala incompatibili con una PMI del Cilento. I destinatari sono tipicamente grandi operatori di telecomunicazioni o consorzi specializzati.</t>
         </is>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di una Partnership europea co-finanziata nell'ambito di Horizon, orientata a consorzi di ricerca e istituzioni pubbliche su temi di trasformazione sociale e resilienza: le PMI del Cilento difficilmente accedono direttamente a questi bandi senza essere parte di progetti guidati da università o enti di ricerca. L'architettura finanziaria e i requisiti di partenariato transnazionale rendono questo strumento di fatto inaccessibile per una piccola impresa locale senza un solido network accademico europeo.</t>
+          <t>Si tratta di una Partnership europea co-finanziata Horizon focalizzata su ricerca accademica e policy su trasformazioni sociali e resilienza, destinata principalmente a università, enti di ricerca e istituzioni pubbliche. Una PMI del Cilento difficilmente può accedere direttamente, salvo come partner secondario in consorzi di ricerca con ruolo marginale.</t>
         </is>
       </c>
     </row>
@@ -13539,7 +13539,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF riguarda munizioni, missili e armamenti esplosivi, settore altamente specializzato riservato a grandi aziende della difesa con capacità industriali e certificazioni militari specifiche. Una PMI del Cilento o della Campania non dispone strutturalmente dei requisiti tecnici, produttivi e di sicurezza necessari per partecipare a questo tipo di gara europea.</t>
+          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa (munizioni, missili e armi esplosive), un ambito che richiede capacità industriali altamente specializzate, certificazioni NATO/militari e investimenti strutturali incompatibili con le dimensioni e il profilo produttivo tipico di una PMI del Cilento o della Campania in generale.</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13586,7 @@
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi counter-drone è destinato a consorzi industriali con elevate capacità di R&amp;S in ambito difesa, richiedendo competenze tecnologiche avanzate e strutture di compliance normativa tipiche di grandi imprese o centri di ricerca specializzati. Una PMI del Cilento difficilmente possiede i requisiti tecnici, finanziari e le certificazioni di sicurezza necessarie per partecipare autonomamente a progetti di difesa europea di questa natura.</t>
+          <t>Il bando EDF sui sistemi counter-drone è destinato a consorzi industriali con elevate capacità di R&amp;S in ambito difesa, richiedendo investimenti e competenze tecnologiche difficilmente accessibili a una PMI del Cilento priva di una filiera aerospaziale o della difesa consolidata. Una piccola impresa campana potrebbe partecipare solo come subcontraente di un grande prime contractor, ruolo che richiede certificazioni specifiche e relazioni industriali preesistenti nel settore difesa.</t>
         </is>
       </c>
     </row>
@@ -13633,29 +13633,29 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF finanzia ricerca e sviluppo nel settore della difesa (missili, munizioni, bombe), richiedendo capacità tecnologiche, certificazioni e partnership industriali di livello militare del tutto inaccessibili per una PMI del Cilento o della Campania non specializzata nel comparto difesa. I requisiti di accesso, i costi di partecipazione e la natura del programma lo rendono di fatto esclusivo per grandi contractor della difesa o consorzi internazionali specializzati.</t>
+          <t>Il bando EDF riguarda lo sviluppo di missili, munizioni e bombe nell'ambito della difesa europea, un settore altamente specializzato che richiede capacità industriali, certificazioni e requisiti di sicurezza inaccessibili per una PMI tipica del Cilento o della Campania. Non esistono realistiche possibilità di partecipazione diretta per una piccola o media impresa locale non operante nel comparto difesa/aerospazio.</t>
         </is>
       </c>
     </row>
     <row r="281" ht="30" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Advanced border surveillance and situational awareness</t>
+          <t>EIC defence call</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-DEFENCE-01</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -13680,14 +13680,14 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato sulla sorveglianza avanzata dei confini richiede competenze altamente specializzate in tecnologie di difesa e sicurezza (droni, AI, sistemi radar) tipicamente appannaggio di grandi aziende del settore difesa o centri di ricerca, rendendo l'accesso estremamente difficile per una PMI del Cilento. Inoltre, i bandi Horizon di questo tipo richiedono la partecipazione a consorzi europei complessi e risorse progettuali significative, incompatibili con le dimensioni medie delle imprese locali.</t>
+          <t>Il bando EIC Defence è orientato a tecnologie dual-use e difesa con requisiti tecnici e finanziari molto elevati, pensati per grandi imprese o spin-off ad alta tecnologia con capacità di R&amp;S strutturata. Una PMI del Cilento difficilmente possiede i requisiti tecnici, i partner internazionali e la capacità progettuale necessaria per competere in questo contesto.</t>
         </is>
       </c>
     </row>
     <row r="282" ht="30" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Designing new ways of risk awareness and enhanced disaster preparedness</t>
+          <t>Advanced border surveillance and situational awareness</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-01</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -13727,14 +13727,14 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sulla gestione del rischio e preparazione ai disastri è orientato principalmente a consorzi di ricerca, università e grandi organizzazioni pubbliche, rendendo molto difficile l'accesso diretto per una PMI del Cilento senza un ruolo marginale in un partenariato internazionale. Le spese finanziabili riguardano attività di ricerca e sviluppo su larga scala, lontane dalle esigenze operative tipiche di una piccola impresa locale.</t>
+          <t>Il bando Horizon riguarda tecnologie avanzate per la sorveglianza delle frontiere e la situational awareness, ambiti tipicamente riservati a grandi aziende della difesa, centri di ricerca e consorzi internazionali. Una PMI del Cilento difficilmente possiede i requisiti tecnici, la capacità progettuale e i partner necessari per competere in questo settore altamente specializzato.</t>
         </is>
       </c>
     </row>
     <row r="283" ht="30" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Open topic on preventing and countering the misuse of emerging technologies for criminal purposes, including issues related to lawful access to data</t>
+          <t>Designing new ways of risk awareness and enhanced disaster preparedness</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-01</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -13774,14 +13774,14 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede competenze specialistiche in cybersecurity e tecnologie emergenti applicate al contrasto criminale, con requisiti di consorzio internazionale e capacità di ricerca avanzata difficilmente compatibili con una PMI del Cilento. Le spese finanziabili riguardano R&amp;S in ambito sicurezza digitale e lawful access ai dati, settori distanti dal tessuto produttivo locale.</t>
+          <t>Il bando Horizon richiede consorzi internazionali, capacità di ricerca avanzata e rendicontazione complessa, elementi difficilmente gestibili da una PMI di piccole dimensioni senza partner accademici o industriali strutturati. Il focus su risk awareness e disaster preparedness potrebbe teoricamente coinvolgere realtà del Cilento (area sismica e idrogeologica sensibile), ma solo come partner junior in progetti guidati da enti di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="284" ht="30" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Reliability of age assessment methods in the context of security and border management</t>
+          <t>Open topic on preventing and countering the misuse of emerging technologies for criminal purposes, including issues related to lawful access to data</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-02</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -13821,14 +13821,14 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon riguarda la ricerca sulla valutazione dell'età in contesti di sicurezza e gestione delle frontiere, un ambito altamente specializzato che richiede competenze forensi, mediche e di sicurezza difficilmente presenti in una PMI campana o del Cilento. La struttura competitiva di Horizon, che privilegia consorzi internazionali con enti di ricerca e istituzioni pubbliche, rende l'accesso diretto estremamente improbabile per una piccola-media impresa locale.</t>
+          <t>Il bando Horizon EU richiede capacità di ricerca avanzata su tecnologie emergenti applicate alla sicurezza e al contrasto criminale, con consorzio internazionale e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. I requisiti progettuali e amministrativi di Horizon sono strutturati per enti di ricerca e grandi organizzazioni, rendendo l'accesso diretto per una PMI di piccola dimensione praticamente impraticabile senza partnership con università o centri di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="285" ht="30" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>Enhancing the security of citizens against terrorism and lone-actor violence in confined spaces such as schools</t>
+          <t>Reliability of age assessment methods in the context of security and border management</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-03</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -13863,19 +13863,19 @@
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo sulla sicurezza anti-terrorismo in spazi confinati come le scuole è orientato a consorzi di ricerca, università e grandi aziende della difesa/sicurezza, con requisiti tecnici e burocratici difficilmente accessibili a una PMI campana del Cilento. Non sono previste spese tipicamente sostenibili da piccole imprese locali, né settori produttivi del territorio risultano beneficiari diretti.</t>
+          <t>Il bando Horizon riguarda la ricerca scientifica sui metodi di valutazione dell'età in contesti di sicurezza e gestione delle frontiere, un ambito altamente specialistico che richiede competenze di ricerca avanzata (forense, biometrica, medica) tipicamente appartenenti a università o grandi enti di ricerca. Una PMI del Cilento, anche operante in settori tecnologici, difficilmente possiede i requisiti scientifici e consortili necessari per competere in questo tipo di call europea.</t>
         </is>
       </c>
     </row>
     <row r="286" ht="30" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Missing persons: prevention and investigation</t>
+          <t>Enhancing the security of citizens against terrorism and lone-actor violence in confined spaces such as schools</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-05</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -13910,19 +13910,19 @@
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon sulla ricerca e prevenzione delle persone scomparse è orientato a consorzi di ricerca, forze dell'ordine e grandi enti istituzionali, rendendo l'accesso estremamente complesso per una PMI campana del Cilento priva di un solido track record in sicurezza pubblica o criminologia. Le PMI del territorio, prevalentemente attive in turismo, agricoltura e artigianato, non trovano alcuna coerenza con le attività finanziabili da questo bando.</t>
+          <t>Il bando Horizon UE sulla sicurezza antiterrorismo in spazi confinati richiede capacità di ricerca avanzata, consorzi internazionali e competenze specialistiche difficilmente accessibili a una PMI campana di piccole dimensioni, specialmente nel Cilento dove il tessuto produttivo è prevalentemente orientato a turismo e agricoltura. L'ambito tematico (sicurezza pubblica e lone-actor violence) è lontano dalle filiere produttive locali e richiede partner istituzionali come forze dell'ordine o università, rendendo la partecipazione diretta di una PMI locale molto improbabile.</t>
         </is>
       </c>
     </row>
     <row r="287" ht="30" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>Crime prevention approaches, online and off-line, tackling the nexus between addictions and crime</t>
+          <t>Missing persons: prevention and investigation</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-03</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -13962,14 +13962,14 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si focalizza su ricerca scientifica per la prevenzione della criminalità legata alle dipendenze, richiedendo consorzi accademici e istituzionali altamente specializzati, con budget e requisiti tecnici fuori dalla portata di una PMI del Cilento. Non finanzia attività produttive, commerciali o servizi tipici delle piccole imprese locali.</t>
+          <t>Il bando Horizon sulla prevenzione e investigazione delle persone scomparse è orientato a enti di ricerca, forze dell'ordine e consorzi specializzati in sicurezza pubblica, rendendo l'accesso estremamente complesso per una PMI campana senza consolidata esperienza in progetti europei di sicurezza. Una piccola impresa del Cilento difficilmente possiede le competenze tecniche e i partner istituzionali richiesti per competere in questo specifico ambito.</t>
         </is>
       </c>
     </row>
     <row r="288" ht="30" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Open topic on supporting disruptive technological innovations for civil security</t>
+          <t>Crime prevention approaches, online and off-line, tackling the nexus between addictions and crime</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-04</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -14004,19 +14004,19 @@
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su innovazioni tecnologiche dirompenti per la sicurezza civile è orientato principalmente a grandi consorzi di ricerca, università e aziende con elevata capacità R&amp;D, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza partnership strutturate. Una piccola impresa potrebbe partecipare solo come partner in un consorzio internazionale, con costi di gestione amministrativa e requisiti tecnici sproporzionati rispetto alle capacità medie di una PMI locale.</t>
+          <t>Il bando Horizon si rivolge principalmente a consorzi di ricerca, università e grandi organizzazioni specializzate nella criminologia e nelle politiche sociali, richiedendo capacità progettuali e partnership transnazionali difficilmente accessibili a una PMI del Cilento. Il tema specifico — prevenzione del crimine legata alle dipendenze — non interseca i settori produttivi tipici del tessuto imprenditoriale locale come turismo, agricoltura o artigianato.</t>
         </is>
       </c>
     </row>
     <row r="289" ht="30" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>Climate security and civil preparedness – new ways to develop pre- and post-crisis climate-change related scenarios for a more resilient Europe</t>
+          <t>Open topic on supporting disruptive technological innovations for civil security</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-01</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -14051,19 +14051,19 @@
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si concentra su ricerca e innovazione in materia di sicurezza climatica e preparazione civile, richiedendo consorzi internazionali con forte componente accademica e istituzionale: una PMI del Cilento difficilmente ha le competenze tecniche e la rete di partner necessarie per guidare o partecipare competitivamente a progetti di questa natura. Inoltre, i costi di partecipazione (gestione amministrativa, co-progettazione europea) risultano sproporzionati rispetto alle capacità organizzative tipiche di una piccola impresa campana.</t>
+          <t>Il bando Horizon Europe sulla sicurezza civile richiede capacità di ricerca avanzata, consorzi internazionali e tecnologie dirompenti difficilmente accessibili a una PMI di piccola dimensione del Cilento, che raramente dispone delle risorse tecniche e amministrative per partecipare a programmi europei di questa complessità. Potrebbe avere senso solo come partner junior in un consorzio guidato da università o grandi imprese del settore difesa/sicurezza.</t>
         </is>
       </c>
     </row>
     <row r="290" ht="30" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>Targeted innovative capabilities for the resilience of critical entities to natural and human-induced disasters, including hybrid scenarios</t>
+          <t>Climate security and civil preparedness – new ways to develop pre- and post-crisis climate-change related scenarios for a more resilient Europe</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-05</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -14103,14 +14103,14 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione in consorzi internazionali con capacità di ricerca avanzata e budget elevati, strutture tipicamente incompatibili con una PMI di piccola dimensione del Cilento; il focus su resilienza delle infrastrutture critiche a disastri naturali potrebbe in teoria coinvolgere aziende del settore ambientale o protezione civile, ma le barriere di accesso (rendicontazione complessa, co-finanziamento, partner transnazionali) rendono la partecipazione diretta molto difficile senza il supporto di un ente di ricerca capofila.</t>
+          <t>Il bando Horizon richiede la partecipazione in consorzi internazionali con forte componente di ricerca su scenari climatici e sicurezza civile, ambito difficilmente accessibile per una PMI del Cilento senza solide competenze scientifiche pregresse e reti europee consolidate. Il focus su pre e post-crisis climate scenarios è orientato a centri di ricerca e grandi enti pubblici, lasciando alle PMI un ruolo marginale e subordinato nel consorzio.</t>
         </is>
       </c>
     </row>
     <row r="291" ht="30" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>Development of innovative tools, processes, equipment and technologies through responses to disasters and emergencies for search and rescue in hazardous conditions</t>
+          <t>Targeted innovative capabilities for the resilience of critical entities to natural and human-induced disasters, including hybrid scenarios</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-03</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -14150,14 +14150,14 @@
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede consorzi internazionali, capacità di R&amp;S strutturata e budget elevati, rendendolo di fatto inaccessibile per una PMI del Cilento senza un solido track record europeo e partnership con enti di ricerca. Il focus su tecnologie per ricerca e soccorso in ambienti pericolosi è molto settoriale e difficilmente applicabile al tessuto produttivo locale.</t>
+          <t>Il bando Horizon UE richiede la partecipazione in consorzi internazionali con capacità di ricerca avanzata e budget elevati, strutture tipicamente inaccessibili per una PMI campana di piccole dimensioni senza un partner universitario o un grande integratore. Una PMI del Cilento potrebbe al limite partecipare come partner secondario in un consorzio su tematiche di resilienza a disastri naturali (rilevante per l'area), ma la complessità gestionale e rendicontativa di Horizon la rende concretamente poco praticabile in autonomia.</t>
         </is>
       </c>
     </row>
     <row r="292" ht="30" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Multi-hazard approach and cumulative / cascading impacts</t>
+          <t>Development of innovative tools, processes, equipment and technologies through responses to disasters and emergencies for search and rescue in hazardous conditions</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-03</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -14197,14 +14197,14 @@
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe sulla gestione multi-rischio e impatti a cascata (alluvioni, frane, sismi) è orientato a consorzi di ricerca e università, con requisiti tecnici e amministrativi difficilmente sostenibili da una PMI autonomamente. Una PMI del Cilento potrebbe partecipare solo come partner junior in un consorzio guidato da enti di ricerca, con ruoli molto marginali e budget limitati.</t>
+          <t>Il bando Horizon richiede progetti altamente tecnologici su strumenti e processi per ricerca e soccorso in condizioni di pericolo, con consorzî internazionali e capacità R&amp;S avanzate difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe partecipare solo come partner specializzato in sensoristica, droni o materiali innovativi, ma i requisiti progettuali e finanziari restano elevati.</t>
         </is>
       </c>
     </row>
     <row r="293" ht="30" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>Development of ecosystem and next-generation capabilities for a secured European Critical Communication System in civil security</t>
+          <t>Multi-hazard approach and cumulative / cascading impacts</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-04</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-02</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -14244,14 +14244,14 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe riguarda lo sviluppo di sistemi di comunicazione critica per la sicurezza civile a livello europeo, richiedendo competenze altamente specializzate in cybersecurity e telecomunicazioni critiche, oltre a capacità di partecipazione a consorzi internazionali complessi. Una PMI del Cilento difficilmente possiede i requisiti tecnici e la struttura organizzativa necessari per competere in questo tipo di progetto ad alto contenuto tecnologico e strategico.</t>
+          <t>Il bando Horizon Europe sui rischi multi-hazard e impatti a cascata è orientato a consorzi di ricerca internazionali con forte componente scientifica, rendendo l'accesso diretto per una PMI del Cilento molto difficile senza partnership con università o enti di ricerca. Una PMI potrebbe partecipare solo come soggetto specializzato in monitoraggio ambientale, gestione del rischio idrogeologico o tecnologie di early warning, settori rilevanti per il territorio cilentano ma che richiedono capacità progettuali e amministrative elevate.</t>
         </is>
       </c>
     </row>
     <row r="294" ht="30" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Tools and processes to support stress tests of critical infrastructure</t>
+          <t>Development of ecosystem and next-generation capabilities for a secured European Critical Communication System in civil security</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-04</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -14291,14 +14291,14 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata su infrastrutture critiche e stress test sistemici, ambiti tipicamente riservati a grandi consorzi europei con università e centri di ricerca. Una PMI del Cilento difficilmente dispone delle competenze tecniche specialistiche e della massa critica progettuale necessarie per candidarsi autonomamente o come partner rilevante.</t>
+          <t>Il bando Horizon riguarda lo sviluppo di sistemi critici di comunicazione per la sicurezza civile europea, un settore altamente specializzato che richiede capacità tecnologiche avanzate, consorzi internazionali e competenze in cybersecurity difficilmente accessibili per una PMI del Cilento. Le dimensioni del progetto, la complessità burocratica di Horizon Europe e la natura del tema (infrastrutture critiche di comunicazione) lo rendono praticabile solo per grandi player tecnologici o centri di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="295" ht="30" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>Improving capabilities of law enforcement to counter climate-related challenges</t>
+          <t>Tools and processes to support stress tests of critical infrastructure</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-01</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -14333,19 +14333,19 @@
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è destinato a soggetti specializzati in sicurezza, forze dell'ordine e ricerca applicata, con requisiti tecnici e consorziali molto elevati, del tutto estranei alle attività tipiche di una PMI del Cilento. Non finanzia prodotti o servizi commerciali standard, ma progetti di ricerca su tecnologie di contrasto agli effetti del cambiamento climatico in ambito law enforcement.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata su infrastrutture critiche e stress test, ambiti tipici di grandi consorzi europei, università o aziende tecnologiche specializzate. Una PMI del Cilento difficilmente possiede i requisiti tecnici e la massa critica per partecipare competitivamente, salvo come partner junior in un consorzio già strutturato.</t>
         </is>
       </c>
     </row>
     <row r="296" ht="30" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>Demand-led innovation in security</t>
+          <t>Improving capabilities of law enforcement to counter climate-related challenges</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-01</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -14380,19 +14380,19 @@
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon 'Demand-led innovation in security' è orientato a grandi consorzi di ricerca e soggetti pubblici/istituzionali del settore sicurezza (difesa, cybersecurity, protezione civile), con requisiti tecnici e amministrativi difficilmente accessibili per una PMI del Cilento priva di una struttura R&amp;D dedicata e di partnership internazionali consolidate. Le PMI manifatturiere o turistiche tipiche dell'area non trovano filiera applicativa diretta in questo specifico topic.</t>
+          <t>Il bando Horizon è orientato a consorzi di ricerca, università e forze dell'ordine per sviluppare tecnologie e metodologie di contrasto alle sfide climatiche in ambito sicurezza pubblica: una PMI del Cilento non ha profilo né struttura adeguati per candidarsi autonomamente. L'accesso sarebbe possibile solo come partner tecnico specializzato in un grande consorzio europeo, scenario poco realistico per una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="297" ht="30" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>Prevention and mitigation of misuse of synthetic biology for bioterrorism purposes</t>
+          <t>Demand-led innovation in security</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-06</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-02</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -14427,19 +14427,19 @@
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la prevenzione del bioterrorismo legato alla biologia sintetica, un ambito altamente specializzato che richiede competenze di ricerca avanzata e infrastrutture di sicurezza difficilmente disponibili in una PMI del Cilento. Non esistono benefici diretti per settori produttivi locali come turismo, agricoltura o manifattura leggera, tipici dell'economia cilentana.</t>
+          <t>Il bando Horizon 'Demand-led innovation in security' è orientato a grandi consorzi europei di ricerca e sviluppo nel settore della sicurezza pubblica e delle infrastrutture critiche, con requisiti tecnici e finanziari difficilmente accessibili per una PMI del Cilento. Le spese finanziabili riguardano R&amp;S avanzata, prototipazione e test in ambito security, settori molto distanti dal tessuto produttivo locale (turismo, agricoltura, artigianato).</t>
         </is>
       </c>
     </row>
     <row r="298" ht="30" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>Public procurement of innovation for security</t>
+          <t>Prevention and mitigation of misuse of synthetic biology for bioterrorism purposes</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-06</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -14474,19 +14474,19 @@
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia appalti pubblici pre-commerciali per lo sviluppo di soluzioni innovative nella sicurezza, rivolti principalmente a grandi consorzi o enti pubblici con capacità R&amp;S strutturata. Una PMI del Cilento difficilmente dispone delle competenze tecniche e della massa critica necessarie per competere in questo tipo di procurement europeo ad alta complessità.</t>
+          <t>Il bando riguarda la prevenzione del bioterrorismo tramite biologia sintetica, un ambito altamente specializzato che richiede competenze scientifiche avanzate e strutture di ricerca dedicate, tipiche di grandi enti pubblici o centri di ricerca. Una PMI del Cilento, anche operante in ambito biotech o agroalimentare, difficilmente possiede i requisiti tecnici e istituzionali per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="299" ht="30" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>Security challenges of the green transition in urban und peri urban areas</t>
+          <t>Public procurement of innovation for security</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-03</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -14526,34 +14526,34 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la partecipazione in consorzi internazionali con forte componente di ricerca e sviluppo su tematiche di sicurezza urbana nella transizione verde, con budget elevati e procedure complesse tipicamente accessibili a grandi enti di ricerca o aziende strutturate. Una PMI del Cilento, area prevalentemente rurale e non urbana, difficilmente rientra nel target geografico e organizzativo richiesto.</t>
+          <t>Il bando riguarda appalti pubblici pre-commerciali per soluzioni innovative nel settore della sicurezza, strumento tipicamente riservato a grandi imprese o spin-off tecnologici con capacità di R&amp;S avanzata. Una PMI del Cilento difficilmente possiede i requisiti tecnici e organizzativi per competere in procurement di innovazione a livello europeo in ambito security.</t>
         </is>
       </c>
     </row>
     <row r="300" ht="30" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>I3-2026-INV1 - Interregional Innovation Investments Strand 1</t>
+          <t>Security challenges of the green transition in urban und peri urban areas</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>12/11/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/I3-2026-INV1</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-02</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>UE - I3</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -14573,34 +14573,34 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>Il bando I3 Strand 1 finanzia investimenti interregionali in innovazione con focus su collaborazioni tra regioni europee e richiede partnership transnazionali strutturate, rendendo l'accesso diretto molto complesso per una PMI del Cilento che opera prevalentemente su scala locale. Le dimensioni progettuali e i requisiti amministrativi tipici dei programmi interregionali UE scoraggiano la partecipazione autonoma di piccole imprese senza un lead partner istituzionale.</t>
+          <t>Il bando Horizon Europe richiede la partecipazione in consorzi internazionali con forte componente di ricerca applicata su sicurezza e transizione verde in aree urbane/periurbane, struttura tipicamente accessibile a grandi enti di ricerca e università piuttosto che a PMI del Cilento, che opera in contesto prevalentemente rurale. I costi di partecipazione, la complessità progettuale e la necessità di partner europei rendono questo bando poco praticabile per una piccola impresa campana senza esperienza pregressa in progetti europei.</t>
         </is>
       </c>
     </row>
     <row r="301" ht="30" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>MSCA Doctoral Networks 2026</t>
+          <t>I3-2026-INV1 - Interregional Innovation Investments Strand 1</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>24/11/2026</t>
+          <t>12/11/2026</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-DN-01-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/I3-2026-INV1</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - I3</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
@@ -14615,39 +14615,39 @@
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>Il programma MSCA Doctoral Networks finanzia reti transnazionali per il dottorato di ricerca, richiedendo la costituzione di consorzi multi-istituzionali con università e centri di ricerca europei: una struttura organizzativa e amministrativa del tutto sproporzionata per una PMI del Cilento. L'accesso diretto è praticamente impossibile senza essere partner di un consorzio accademico già strutturato.</t>
+          <t>Il bando I3 Strand 1 finanzia investimenti interregionali in innovazione con focus su grandi partnership tra regioni e attori istituzionali, rendendo l'accesso diretto per una PMI del Cilento estremamente complesso senza essere parte di un consorzio strutturato. Le spese finanziabili riguardano progetti di innovazione ad ampio respiro transfrontaliero, con burocrazia europea elevata e requisiti difficilmente compatibili con le capacità gestionali di una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="302" ht="30" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>RAISE Doctoral Networks for AI in Science (RAISE pilot)</t>
+          <t>I3-2026-INV2a - Interregional Innovation Investments Strand 2a</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>24/11/2026</t>
+          <t>12/11/2026</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-RAISE-2026-01-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/I3-2026-INV2a</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - I3</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
@@ -14662,34 +14662,34 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>Il bando RAISE finanzia reti dottorali per la ricerca in AI nell'ambito di grandi consorzi universitari europei: il soggetto beneficiario principale è l'istituzione accademica, non la PMI. Una piccola impresa del Cilento difficilmente possiede la struttura organizzativa e i partner internazionali richiesti per partecipare come ente ospitante o co-beneficiario in questo tipo di progetto Horizon.</t>
+          <t>Il bando I3 Strand 2a è uno strumento interregionale europeo orientato a investimenti in innovazione di scala medio-grande, tipicamente rivolto a consorzi transregionali o enti pubblici/cluster, rendendo l'accesso diretto per una singola PMI del Cilento molto difficile senza una rete strutturata di partner. La complessità gestionale e i requisiti di cooperazione interregionale lo rendono poco praticabile per realtà locali di piccole dimensioni senza supporto specializzato.</t>
         </is>
       </c>
     </row>
     <row r="303" ht="30" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>EIC STEP Scale Up</t>
+          <t>MSCA Doctoral Networks 2026</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>25/11/2026</t>
+          <t>24/11/2026</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-STEP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-DN-01-01</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -14709,24 +14709,24 @@
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>Il programma EIC STEP Scale Up è rivolto a imprese tecnologiche ad alta crescita già selezionate dall'European Innovation Council, con requisiti di scala e maturità tecnologica difficilmente compatibili con una PMI tradizionale del Cilento. Una piccola impresa locale senza pregressa partecipazione all'ecosistema EIC non ha accesso diretto a questo strumento.</t>
+          <t>Le MSCA Doctoral Networks finanziano reti internazionali di dottorato guidate da università e grandi enti di ricerca: una PMI del Cilento può partecipare solo come partner secondario in un consorzio già strutturato, senza possibilità di candidatura autonoma e con oneri amministrativi elevati incompatibili con le risorse tipiche di una piccola impresa.</t>
         </is>
       </c>
     </row>
     <row r="304" ht="30" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>Structurally addressing homelessness through coordinated social infrastructure and services in neighbourhoods</t>
+          <t>RAISE Doctoral Networks for AI in Science (RAISE pilot)</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>24/11/2026</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-RAISE-2026-01-03</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -14756,34 +14756,34 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è focalizzato sulla ricerca applicata per il contrasto alla homelessness e l'infrastruttura sociale urbana, tematiche lontane dall'operatività tipica di una PMI campana o cilentana. I beneficiari attesi sono enti di ricerca, comuni e organizzazioni no-profit, rendendo l'accesso diretto per una PMI di piccole dimensioni estremamente difficile senza un ruolo marginale in un consorzio.</t>
+          <t>Il bando finanzia reti dottorali per la ricerca in intelligenza artificiale nell'ambito del programma Marie Skłodowska-Curie, destinato principalmente a università, centri di ricerca e grandi consorzi accademici: una PMI del Cilento difficilmente possiede la struttura organizzativa e i requisiti per candidarsi come soggetto capofila o partner. L'unica finestra di accesso indiretto sarebbe come partner industriale in un consorzio guidato da enti di ricerca, ma con margini di beneficio concreto molto limitati per una piccola impresa.</t>
         </is>
       </c>
     </row>
     <row r="305" ht="30" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>Sustainable, inclusive, affordable and beautiful solutions for thermal comfort in buildings</t>
+          <t>EIC STEP Scale Up</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>25/11/2026</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-STEP</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -14808,14 +14808,14 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE richiede progetti di ricerca e innovazione ad alto contenuto tecnologico su soluzioni di comfort termico negli edifici, con requisiti di consorzio internazionale e capacità di R&amp;S difficilmente compatibili con una PMI di piccola dimensione del Cilento. L'accesso è praticabile solo per PMI innovative con esperienza in edilizia sostenibile e partnership già consolidate con centri di ricerca europei.</t>
+          <t>Il programma EIC STEP Scale Up è destinato a startup e PMI deep-tech già finanziate da EIC con elevato potenziale di scala europea, requisito difficilmente soddisfabile da una PMI tradizionale del Cilento. Le spese finanziabili (R&amp;S avanzata, espansione internazionale) e la competizione a livello europeo rendono questo bando poco accessibile per realtà locali di piccola dimensione senza un profilo tecnologico d'eccellenza già riconosciuto.</t>
         </is>
       </c>
     </row>
     <row r="306" ht="30" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Innovative approaches for the spatial design of neighbourhoods</t>
+          <t>Structurally addressing homelessness through coordinated social infrastructure and services in neighbourhoods</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-01</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -14850,19 +14850,19 @@
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede consorzi europei di ricerca con elevata capacità progettuale e scientifica, difficilmente accessibile per una PMI del Cilento senza un solido network internazionale. Il focus sulla progettazione spaziale urbana dei quartieri è inoltre poco aderente al contesto territoriale rurale e alle attività tipiche delle PMI locali.</t>
+          <t>Il bando Horizon si concentra sulla ricerca e innovazione per affrontare il problema dei senzatetto attraverso infrastrutture sociali coordinate, un ambito lontano dalle attività tipiche di una PMI campana o cilentana. I soggetti beneficiari ideali sono enti pubblici, università e organizzazioni del terzo settore, rendendo la partecipazione diretta di una PMI marginale e priva di valore commerciale concreto.</t>
         </is>
       </c>
     </row>
     <row r="307" ht="30" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>Approaches to reuse vacant, obsolete or underutilised spaces</t>
+          <t>Sustainable, inclusive, affordable and beautiful solutions for thermal comfort in buildings</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-01</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -14902,14 +14902,14 @@
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon UE è orientato a progetti di ricerca e sviluppo su larga scala per il riutilizzo di spazi vuoti o sottoutilizzati, richiedendo consorzi internazionali e capacità progettuali elevate difficilmente accessibili a una PMI campana di piccole dimensioni. Una PMI del Cilento potrebbe teoricamente partecipare come partner secondario in progetti legati alla rigenerazione di borghi abbandonati o strutture turistiche dismesse, ma il livello di complessità amministrativa e finanziaria rende l'accesso diretto poco praticabile.</t>
+          <t>Il bando Horizon UE richiede consorzi internazionali, capacità di ricerca avanzata e rendicontazione complessa, elementi difficilmente gestibili da una PMI del Cilento senza un partner universitario o un grande integratore. Una piccola impresa edile o di impiantistica locale potrebbe partecipare solo come subappaltatore o partner minore in un consorzio già strutturato, con margini di beneficio diretto molto limitati.</t>
         </is>
       </c>
     </row>
     <row r="308" ht="30" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Understanding capital market dynamics for increased investment in New European Bauhaus projects in neighbourhoods</t>
+          <t>Innovative approaches for the spatial design of neighbourhoods</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-02</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -14944,19 +14944,19 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>Credito/Finanza</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca accademica e istituzionale sulle dinamiche dei mercati di capitali per investimenti nel programma New European Bauhaus, non attività operative di PMI. Una piccola impresa del Cilento non ha le strutture di ricerca né i requisiti consortili per partecipare a questo tipo di progetto europeo.</t>
+          <t>Il bando Horizon UE richiede la partecipazione a consorzi di ricerca internazionali con forte componente accademica e scientifica, rendendo l'accesso diretto molto difficile per una PMI del Cilento senza un partner universitario consolidato. Il focus sulla progettazione spaziale dei quartieri è lontano dalle filiere produttive tipiche dell'area (turismo, agricoltura, artigianato).</t>
         </is>
       </c>
     </row>
     <row r="309" ht="30" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>Innovative solutions for the sustainable and beautiful use of vertical space</t>
+          <t>Approaches to reuse vacant, obsolete or underutilised spaces</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-03</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -14996,14 +14996,14 @@
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon EU richiede tipicamente capacità di ricerca avanzata, partnership internazionali e strutture di rendicontazione complesse, barriere difficilmente superabili per una PMI del Cilento. Il tema del 'vertical space' (edifici, facciate verdi, architettura verticale sostenibile) è settorialmente distante dalle filiere produttive dominanti nell'area, come agricoltura, turismo e artigianato.</t>
+          <t>Il bando Horizon UE è orientato a consorzi di ricerca e soggetti pubblici per progetti di rigenerazione urbana su spazi dismessi, con procedure complesse e co-finanziamenti elevati difficilmente gestibili da una PMI autonoma. Una piccola impresa del Cilento potrebbe partecipare solo come partner secondario in un consorzio guidato da università o enti locali, senza accesso diretto ai fondi.</t>
         </is>
       </c>
     </row>
     <row r="310" ht="30" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>Advancing sustainable maintenance and repair measures for existing buildings</t>
+          <t>Understanding capital market dynamics for increased investment in New European Bauhaus projects in neighbourhoods</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-02</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -15038,19 +15038,19 @@
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Credito/Finanza</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede consorzi internazionali con forte componente di ricerca e sviluppo, rendendo l'accesso diretto molto difficile per una PMI del Cilento senza partnership consolidate con università o centri di ricerca. Le spese finanziabili riguardano attività R&amp;S su manutenzione sostenibile degli edifici esistenti, settore rilevante per il territorio ma con barriere burocratiche e finanziarie elevate per soggetti di piccola dimensione.</t>
+          <t>Il bando Horizon finanzia ricerca accademica e istituzionale sulle dinamiche dei mercati di capitali per investimenti nel programma New European Bauhaus, un ambito altamente specializzato che richiede consorziate con forti competenze in finanza urbana e policy. Una PMI del Cilento non ha struttura né profilo adatto per guidare o partecipare utilmente a questo tipo di progetto europeo.</t>
         </is>
       </c>
     </row>
     <row r="311" ht="30" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>Understanding inhabitant’s experiences of neighbourhoods to support their health and well-being</t>
+          <t>Innovative solutions for the sustainable and beautiful use of vertical space</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -15065,7 +15065,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-03</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -15085,19 +15085,19 @@
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon si concentra sulla ricerca accademica relativa al benessere degli abitanti nei quartieri urbani, richiedendo capacità di ricerca scientifica e partenariati internazionali difficilmente accessibili a una PMI del Cilento. Non finanzia attività produttive o commerciali tipiche delle piccole imprese campane, e il focus urbano risulta distante dal contesto rurale e costiero del territorio cilentano.</t>
+          <t>Il bando Horizon UE richiede capacità di ricerca e sviluppo avanzate, partnership internazionali e risorse amministrative difficilmente compatibili con una PMI di piccola dimensione del Cilento. Il focus sulle soluzioni innovative per lo spazio verticale sostenibile è molto tecnico e orientato a consorzi di grandi enti, rendendo l'accesso diretto per una PMI locale estremamente complesso senza un partner capofila strutturato.</t>
         </is>
       </c>
     </row>
     <row r="312" ht="30" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>Addressing homelessness through housing-led approaches aligned with the New European Bauhaus</t>
+          <t>Advancing sustainable maintenance and repair measures for existing buildings</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-02</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -15132,34 +15132,34 @@
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon europeo si focalizza su ricerca e innovazione per il contrasto al disagio abitativo attraverso approcci housing-led e i principi del New European Bauhaus, richiedendo tipicamente consorzi internazionali di enti di ricerca e istituzioni pubbliche. Una PMI del Cilento difficilmente ha i requisiti tecnici, la struttura progettuale e i partner necessari per accedere a questo tipo di finanziamento.</t>
+          <t>Il bando Horizon UE richiede la partecipazione a consorzi internazionali di ricerca con elevate competenze tecnico-scientifiche e capacità progettuali complesse, risultando difficilmente accessibile per una PMI del Cilento senza solidi partner accademici o industriali già attivi in R&amp;S sull'edilizia sostenibile. Le spese finanziabili riguardano attività di ricerca e innovazione su manutenzione e riqualificazione di edifici esistenti, settore potenzialmente interessante per imprese edili locali, ma le barriere burocratiche e dimensionali di Horizon rendono la partecipazione diretta quasi impraticabile senza intermediari specializzati.</t>
         </is>
       </c>
     </row>
     <row r="313" ht="30" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>EIC Accelerator 2026 - Short proposal</t>
+          <t>Understanding inhabitant’s experiences of neighbourhoods to support their health and well-being</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>17/12/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>06/11/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-ACCELERATOR-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-03</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -15179,34 +15179,34 @@
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>L'EIC Accelerator è riservato a startup e PMI con innovazioni deep-tech ad alto rischio e scala europea, con finanziamenti fino a 2,5 milioni in grant e 15 milioni in equity: la complessità progettuale, la necessità di scalabilità internazionale e la competizione globale lo rendono poco accessibile per una PMI tradizionale del Cilento, salvo casi di spin-off tecnologici con brevetti o prodotti disruptivi già validati sul mercato.</t>
+          <t>Il bando Horizon UE si focalizza sulla ricerca accademica sull'esperienza degli abitanti nei quartieri urbani in relazione alla salute e al benessere, richiedendo consorzi di ricerca internazionali e competenze scientifiche specialistiche. Una PMI del Cilento difficilmente possiede i requisiti tecnici e la struttura per partecipare come partner principale, e il tema ha scarsa applicabilità diretta al tessuto produttivo locale.</t>
         </is>
       </c>
     </row>
     <row r="314" ht="30" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>Grand Challenge on Quantum Sensors for Inertial Navigation</t>
+          <t>Addressing homelessness through housing-led approaches aligned with the New European Bauhaus</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>14/01/2027</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-NGC-04-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-01</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -15226,34 +15226,34 @@
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di sensori quantistici per la navigazione inerziale, un settore altamente specializzato che richiede competenze di ricerca avanzata in fisica quantistica e ingegneria aerospaziale, tipicamente accessibile solo a grandi consorzi tecnologici, università e centri di ricerca. Una PMI del Cilento, salvo rarissime eccezioni nel deep-tech, non dispone delle infrastrutture né del profilo scientifico richiesto per competere in questo tipo di Grand Challenge europeo.</t>
+          <t>Il bando Horizon europeo sul contrasto all'homelessness tramite approcci housing-led e New European Bauhaus è orientato a consorzi di ricerca, università ed enti pubblici, con requisiti di partnership transnazionale complessi e budget elevati difficilmente accessibili a una PMI campana del Cilento. Il settore edilizio/sociale di riferimento non coincide con le attività tipiche delle PMI locali del territorio.</t>
         </is>
       </c>
     </row>
     <row r="315" ht="30" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>Quantum Machine Learning</t>
+          <t>EIC Accelerator 2026 - Short proposal</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>28/01/2027</t>
+          <t>17/12/2026</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-QML-07-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-ACCELERATOR-01</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -15278,34 +15278,35 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su Quantum Machine Learning richiede capacità di ricerca avanzata, partenariati internazionali e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. Le risorse necessarie per partecipare competitivamente (consorzio europeo, budget elevato, team R&amp;D dedicato) rendono questo bando di fatto inaccessibile per la quasi totalità delle piccole imprese locali.</t>
+          <t>L'EIC Accelerator è rivolto a startup e PMI deep-tech con innovazioni ad alto impatto scalabile a livello europeo, richiedendo profili tecnologici avanzati e capacità di crescita internazionale difficilmente compatibili con la struttura tipica di una PMI del Cilento. Il finanziamento (fino a 2,5M€ grant + equity) è molto competitivo e presuppone un'innovazione dirompente già validata sul mercato.</t>
         </is>
       </c>
     </row>
     <row r="316" ht="30" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>Framework Loans</t>
+          <t>Istituzione dell'elenco degli Organismi di Formazione e di Consulenza Qualificati ai fini
+dell'attuazione degli interventi SRH 01, SRH 03, e SRG 09</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>16/02/2027</t>
+          <t>31 dicembre 2026</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/JTM-2026-PSLF-FRAMEWORK-LOANS</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/AKIS-avviso.html</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>UE - JTM</t>
+          <t>Regione Campania - Agricoltura</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
@@ -15320,39 +15321,39 @@
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>Credito/Finanza</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>I Framework Loans BEI/JTF sono strumenti finanziari strutturati destinati principalmente a intermediari finanziari e grandi progetti territoriali, con soglie minime di accesso raramente compatibili con le dimensioni di una PMI del Cilento; l'accesso indiretto tramite banche convenzionate è teoricamente possibile ma nella pratica limitato e poco documentato per questa specifica area geografica.</t>
+          <t>Il bando non finanzia direttamente le PMI ma istituisce un elenco di Organismi di Formazione e Consulenza abilitati a erogare servizi nell'ambito dello sviluppo rurale: è rilevante solo per enti o società che intendono accreditarsi come fornitori di formazione/consulenza agricola, non per chi cerca finanziamenti produttivi o di sviluppo aziendale.</t>
         </is>
       </c>
     </row>
     <row r="317" ht="30" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>Standalone projects</t>
+          <t>Grand Challenge on Quantum Sensors for Inertial Navigation</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>16/02/2027</t>
+          <t>14/01/2027</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>23/10/2025</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/JTM-2026-PSLF-STANDALONE-PROJECTS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-NGC-04-01</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>UE - JTM</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
@@ -15367,39 +15368,39 @@
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>I bandi 'Standalone Projects' del Just Transition Mechanism UE sono tipicamente rivolti a enti pubblici, grandi organizzazioni o consorzi con capacità progettuali elevate, richiedendo strutture amministrative e co-finanziamenti difficilmente sostenibili da una PMI del Cilento. Inoltre, la Campania non rientra tra le regioni prioritarie del JTM italiano, che si concentra su aree carbonifere come Sulcis e Taranto, riducendo ulteriormente l'accessibilità concreta per questo territorio.</t>
+          <t>Il bando riguarda lo sviluppo di sensori quantistici per la navigazione inerziale, un settore ad altissima intensità tecnologica e scientifica tipicamente riservato a grandi consorzi di ricerca, università e aziende della difesa/aerospazio. Una PMI del Cilento, anche tecnologica, difficilmente dispone delle competenze in fisica quantistica e delle infrastrutture di R&amp;S necessarie per competere in questa challenge europea.</t>
         </is>
       </c>
     </row>
     <row r="318" ht="30" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>Air and missile defence systems</t>
+          <t>Quantum Machine Learning</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>16/02/2027</t>
+          <t>28/01/2027</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-FNLC-CPA-AMDS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-QML-07-01</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>UE - EDF</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
@@ -15414,19 +15415,19 @@
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi di difesa aerea e missilistica è destinato a grandi contractor della difesa e consorzi industriali ad alta specializzazione tecnologica e militare, con requisiti tecnici, certificazioni e capacità produttive del tutto fuori portata per una PMI del Cilento. Non esistono realistiche opportunità di partecipazione diretta per imprese di piccola o media dimensione operanti in questo territorio.</t>
+          <t>Il bando Horizon sul Quantum Machine Learning è orientato a consorzi di ricerca e grandi enti accademici o tecnologici, con requisiti tecnici e amministrativi molto elevati che rendono la partecipazione diretta di una PMI del Cilento estremamente difficile senza un partner istituzionale forte. Le PMI di piccola dimensione difficilmente dispongono delle competenze in informatica quantistica e del track record scientifico richiesto per competere a livello europeo in questo settore.</t>
         </is>
       </c>
     </row>
     <row r="319" ht="30" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>C5ISR and other space-related products</t>
+          <t>Framework Loans</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -15436,17 +15437,17 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>23/10/2025</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-FNLC-CPA-C5ISRS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/JTM-2026-PSLF-FRAMEWORK-LOANS</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>UE - EDF</t>
+          <t>UE - JTM</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
@@ -15461,19 +15462,19 @@
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Credito/Finanza</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore difesa/spazio (C5ISR: Command, Control, Communications, Computers, Cyber, Intelligence, Surveillance, Reconnaissance), richiedendo capacità tecnologiche avanzate, consorzi internazionali e competenze aerospaziali/militari difficilmente accessibili a una PMI del Cilento priva di un posizionamento specifico in questi settori.</t>
+          <t>I Framework Loans BEI sono strumenti finanziari strutturati destinati tipicamente a intermediari finanziari o grandi enti pubblici, non direttamente accessibili da una PMI del Cilento senza passare per banche convenzionate; inoltre il collegamento con il Just Transition Mechanism riguarda aree in transizione da combustibili fossili, contesto poco rilevante per il tessuto produttivo del Cilento.</t>
         </is>
       </c>
     </row>
     <row r="320" ht="30" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>Ground and naval platforms and systems</t>
+          <t>Air and missile defence systems</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -15488,7 +15489,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-FNLC-CPA-GNPS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-FNLC-CPA-AMDS</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -15508,19 +15509,19 @@
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF su piattaforme terrestri e navali richiede capacità industriali di difesa, consorzialità internazionale e investimenti in R&amp;S di scala difficilmente sostenibili da una PMI del Cilento senza un ruolo da subfornitore specializzato in un consorzio europeo strutturato. L'accesso diretto è praticamente precluso a realtà di piccola dimensione prive di certificazioni NATO o contratti difesa preesistenti.</t>
+          <t>Il bando EDF per sistemi di difesa aerea e missilistica è orientato a grandi contractor della difesa e consorzi industriali ad alta intensità tecnologica, con requisiti di sicurezza, certificazioni e capacità produttive del tutto fuori portata per una PMI del Cilento. Il settore difesa richiede accreditamenti NATO/UE e investimenti strutturali incompatibili con la dimensione tipica delle imprese locali.</t>
         </is>
       </c>
     </row>
     <row r="321" ht="30" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>Unmanned systems and counter-unmanned systems</t>
+          <t>C5ISR and other space-related products</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -15535,7 +15536,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-USI-2027-LS-IRA-CUXS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-FNLC-CPA-C5ISRS</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -15560,14 +15561,14 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF sui sistemi unmanned e counter-unmanned è destinato a consorzi di ricerca e industria della difesa con capacità tecnologiche avanzate e budget di progetto nell'ordine dei milioni di euro, requisiti del tutto fuori portata per una PMI campana del Cilento priva di specializzazione aerospazio/difesa. L'accesso diretto è praticamente impossibile senza essere integrati in una supply chain di grandi prime contractor del settore difesa europeo.</t>
+          <t>Il bando EDF per sistemi C5ISR (Command, Control, Communications, Computers, Cyber, Intelligence, Surveillance and Reconnaissance) è orientato a grandi consorzi industriali della difesa e dello spazio, richiedendo capacità tecnologiche, certificazioni e investimenti fuori dalla portata di una PMI del Cilento. L'accesso è realistico solo come subappaltatore di prime contractor come Leonardo o Thales, scenario improbabile senza relazioni consolidate nel settore difesa.</t>
         </is>
       </c>
     </row>
     <row r="322" ht="30" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>Key electronic components</t>
+          <t>Ground and naval platforms and systems</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -15582,7 +15583,7 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-LS-IRA-KEC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-FNLC-CPA-GNPS</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -15602,19 +15603,19 @@
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) sui componenti elettronici chiave è destinato a consorzi di grandi imprese e centri di ricerca nel settore della difesa, con requisiti tecnici e finanziari difficilmente raggiungibili da una PMI del Cilento. L'ambito difesa/aerospazio richiede certificazioni specifiche e capacità produttive industriali che esulano dalla struttura tipica di una piccola impresa campana.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia ricerca e sviluppo nel settore della difesa per piattaforme terrestri e navali, con requisiti tecnici, consorziali e di compliance molto elevati, difficilmente accessibili a una PMI del Cilento priva di specializzazione difensiva certificata. Salvo partnership con grandi prime contractor del settore aerospazio-difesa, una PMI campana di piccole dimensioni non dispone delle credenziali industriali né delle strutture di R&amp;S richieste per partecipare competitivamente.</t>
         </is>
       </c>
     </row>
     <row r="323" ht="30" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>Platforms and end-products</t>
+          <t>Unmanned systems and counter-unmanned systems</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -15629,7 +15630,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-LS-IRA-PE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-USI-2027-LS-IRA-CUXS</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -15649,39 +15650,39 @@
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>Il bando EDF (European Defence Fund) finanzia lo sviluppo di piattaforme e prodotti finali nel settore della difesa, richiedendo consorzi multinazionali con capacità tecnologiche e industriali avanzate del comparto difesa: una PMI del Cilento difficilmente possiede i requisiti tecnici, le certificazioni di sicurezza e i partner istituzionali necessari per partecipare competitivamente.</t>
+          <t>Il bando EDF sui sistemi unmanned e counter-unmanned è orientato a grandi consorzi industriali della difesa con elevate capacità R&amp;D militare, requisiti di sicurezza complessi e budget di progetto nell'ordine delle decine di milioni di euro, rendendo la partecipazione diretta di una PMI del Cilento estremamente difficile senza un ruolo marginale in un consorzio già strutturato. Una PMI campana potrebbe al massimo ambire a una subcontrattazione da parte di prime contractor nazionali come Leonardo, ma difficilmente come proponente autonoma.</t>
         </is>
       </c>
     </row>
     <row r="324" ht="30" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>Strategic Nature Projects</t>
+          <t>Key electronic components</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>16/02/2027</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-STRAT-NAT-SNAP-two-stage</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-LS-IRA-KEC</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - EDF</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
@@ -15696,39 +15697,39 @@
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>I progetti LIFE Strategic Nature sono progettati per grandi partenariati istituzionali (enti pubblici, autorità ambientali, ONG) con budget plurimilionari e complessità gestionale elevata, rendendo l'accesso diretto per una PMI del Cilento estremamente difficile. Una piccola impresa potrebbe al massimo partecipare come partner associato in un consorzio, ma non come beneficiario principale.</t>
+          <t>Il bando EDF (European Defence Fund) sui componenti elettronici chiave è destinato a consorzi di grandi aziende e centri di ricerca del settore difesa, con requisiti tecnici e finanziari molto elevati difficilmente accessibili a una PMI del Cilento. Salvo che l'impresa non operi specificamente nella filiera elettronica per la difesa e possa aggregarsi come partner junior a un consorzio internazionale, le barriere di accesso rendono questo strumento di fatto non praticabile.</t>
         </is>
       </c>
     </row>
     <row r="325" ht="30" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>Strategic Integrated Projects - Climate Action</t>
+          <t>Platforms and end-products</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>04/03/2027</t>
+          <t>16/02/2027</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>31/03/2026</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-STRAT-CLIMA-SIP-two-stage</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2027-LS-IRA-PE</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>UE - LIFE2027</t>
+          <t>UE - EDF</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
@@ -15743,19 +15744,19 @@
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>I progetti LIFE Strategic Integrated Projects sono strumenti complessi destinati a enti pubblici, autorità regionali o grandi consorzi, con budget multimilionari e requisiti di coordinamento multi-attore difficilmente accessibili a una PMI del Cilento. Una piccola impresa potrebbe al massimo partecipare come partner associato, ma non come beneficiario principale.</t>
+          <t>Il bando EDF (European Defence Fund) finanzia lo sviluppo di piattaforme e prodotti finali in ambito difesa, richiedendo capacità tecnologiche avanzate, consorzi multinazionali e competenze industriali militari del tutto estranee alla struttura tipica di una PMI del Cilento. I requisiti di accesso e la complessità progettuale lo rendono di fatto inaccessibile senza essere parte di grandi supply chain della difesa.</t>
         </is>
       </c>
     </row>
     <row r="326" ht="30" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>Strategic Integrated Projects - Environment</t>
+          <t>Strategic Nature Projects</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -15770,7 +15771,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-STRAT-ENV-SIP-two-stage</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-STRAT-NAT-SNAP-two-stage</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -15795,84 +15796,108 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>I progetti LIFE Strategic Integrated Projects sono strumenti complessi destinati ad autorità pubbliche e grandi organizzazioni per implementare piani ambientali su scala territoriale ampia; una PMI del Cilento difficilmente può candidarsi direttamente, ma potrebbe partecipare come partner associato in consorzi guidati da enti pubblici locali (es. Parco Nazionale del Cilento) nel settore ambientale o eco-turistico.</t>
+          <t>I Strategic Nature Projects LIFE sono strumenti pensati per enti pubblici, autorità nazionali e grandi consorzi istituzionali con capacità di coordinamento su scala territoriale ampia; una PMI del Cilento può al massimo partecipare come partner secondario, ma difficilmente accede come beneficiario principale o copre i requisiti di governance richiesti.</t>
         </is>
       </c>
     </row>
     <row r="327" ht="30" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>Credito d’imposta per incubatori e acceleratori certificati</t>
+          <t>Strategic Integrated Projects - Climate Action</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>04/03/2027</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/credito-dimposta-incubatori-e-acceleratori-certificati</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-STRAT-CLIMA-SIP-two-stage</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>Invitalia</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
-        </is>
-      </c>
-      <c r="G327" s="2" t="inlineStr"/>
-      <c r="H327" s="2" t="inlineStr"/>
-      <c r="I327" s="2" t="inlineStr"/>
+          <t>✅ Aperto</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>Sostenibilità</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>I progetti LIFE Strategic Integrated Projects richiedono partnership multi-istituzionali complesse, budget elevati e capacità progettuali europee avanzate, strutturalmente incompatibili con le dimensioni di una PMI. Una piccola impresa del Cilento potrebbe al massimo partecipare come soggetto associato, ma difficilmente come capofila o beneficiario diretto.</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="30" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>Cultura Cresce</t>
+          <t>Strategic Integrated Projects - Environment</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>04/03/2027</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/cultura-cresce?from=/per-le-imprese/incentivi</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/LIFE-2026-STRAT-ENV-SIP-two-stage</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>Invitalia</t>
+          <t>UE - LIFE2027</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
-        </is>
-      </c>
-      <c r="G328" s="2" t="inlineStr"/>
-      <c r="H328" s="2" t="inlineStr"/>
-      <c r="I328" s="2" t="inlineStr"/>
+          <t>✅ Aperto</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>Bassa</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>Sostenibilità</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>I progetti LIFE Strategic Integrated sono strumenti complessi destinati a grandi enti pubblici, autorità regionali o consorzi istituzionali per l'attuazione di piani ambientali su scala territoriale ampia; una PMI del Cilento difficilmente può candidarsi autonomamente, al massimo come partner secondario in un consorzio guidato da soggetti pubblici.</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="30" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>ON - Oltre Nuove imprese a tasso zero</t>
+          <t>Credito d’imposta per incubatori e acceleratori certificati</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -15887,7 +15912,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/ON-nuove-imprese-tasso-zero?from=/per-le-imprese/incentivi</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/credito-dimposta-incubatori-e-acceleratori-certificati</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -15907,7 +15932,7 @@
     <row r="330" ht="30" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Imprenditoria femminile</t>
+          <t>Cultura Cresce</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -15922,7 +15947,7 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/imprenditoria-femminile</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/cultura-cresce?from=/per-chi-vuole-fare-impresa/incentivi</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -15942,7 +15967,7 @@
     <row r="331" ht="30" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>Legge 181</t>
+          <t>ON - Oltre Nuove imprese a tasso zero</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -15957,7 +15982,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/legge-181</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/ON-nuove-imprese-tasso-zero</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -15977,7 +16002,7 @@
     <row r="332" ht="30" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Smart&amp;Start Italia</t>
+          <t>Imprenditoria femminile</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -15992,7 +16017,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/smartstart-italia</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/imprenditoria-femminile?from=/per-chi-vuole-fare-impresa/incentivi</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -16012,7 +16037,7 @@
     <row r="333" ht="30" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Beni strumentali - Nuova Sabatini</t>
+          <t>Legge 181</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -16027,7 +16052,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/beni-strumentali-nuova-sabatini?from=/per-le-imprese/incentivi</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/legge-181</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -16047,7 +16072,7 @@
     <row r="334" ht="30" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Agevolazioni per le imprese confiscate o sequestrate alla criminalità</t>
+          <t>Smart&amp;Start Italia</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -16062,7 +16087,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>https://www.invitalia.it/incentivi-e-strumenti/agevolazioni-le-imprese-confiscate-o-sequestrate-alla-criminalita</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/smartstart-italia?from=/per-chi-vuole-fare-impresa/incentivi</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -16082,12 +16107,12 @@
     <row r="335" ht="30" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRG09 - Avviso per la selezione di partenariati per la realizzazione e gestione dei “Centri territoriali per la Divulgazione Agricola e la Diffusione delle Innovazioni - CeDADI”</t>
+          <t>Beni strumentali - Nuova Sabatini</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Prima fase: 10 luglio 2026 ore 17:00</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -16097,12 +16122,12 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/CEDADI-avviso.html</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/beni-strumentali-nuova-sabatini</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>Regione Campania - Agricoltura</t>
+          <t>Invitalia</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
@@ -16117,12 +16142,12 @@
     <row r="336" ht="30" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Avviso per la partecipazione a SIAL Parigi 2026 - Salone Internazionale dell'Alimentazione (Parigi 17-21 ottobre) - filiera ittica</t>
+          <t>Agevolazioni per le imprese confiscate o sequestrate alla criminalità</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>prorogato al 2 luglio - ore 18:00</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -16132,12 +16157,12 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/fiere/SIAL-PARIS-2026-ittico.html</t>
+          <t>https://www.invitalia.it/incentivi-e-strumenti/agevolazioni-le-imprese-confiscate-o-sequestrate-alla-criminalita?from=/per-le-imprese/incentivi</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>Regione Campania - Agricoltura</t>
+          <t>Invitalia</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
@@ -16152,12 +16177,12 @@
     <row r="337" ht="30" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Avviso per la partecipazione a SEA FOOD EXPO - (Singapore 2-4 settembre) - filiera ittica</t>
+          <t>Intervento SRG09 - Avviso per la selezione di partenariati per la realizzazione e gestione dei “Centri territoriali per la Divulgazione Agricola e la Diffusione delle Innovazioni - CeDADI”</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>2 luglio - ore 18:00</t>
+          <t>Prima fase: 10 luglio 2026 ore 17:00</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -16167,7 +16192,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/fiere/sea-food-asia-2026.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/CEDADI-avviso.html</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -16187,12 +16212,12 @@
     <row r="338" ht="30" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Avviso per la partecipazione a Vinitaly USA - (New York 26-27 ottobre 2026) - filiera vitivinicola</t>
+          <t>Avviso per la partecipazione a SIAL Parigi 2026 - Salone Internazionale dell'Alimentazione (Parigi 17-21 ottobre) - filiera ittica</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>20 luglio - ore 13:00</t>
+          <t>prorogato al 2 luglio - ore 18:00</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -16202,7 +16227,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/fiere/pdf/vinitaly-usa-2026.pdf</t>
+          <t>https://agricoltura.regione.campania.it/fiere/SIAL-PARIS-2026-ittico.html</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -16222,13 +16247,12 @@
     <row r="339" ht="30" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>OCM Vino - Bando regionale Intervento
-Investimenti vino per la campagna 2026/2027</t>
+          <t>Avviso per la partecipazione a SEA FOOD EXPO - (Singapore 2-4 settembre) - filiera ittica</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>ulteriormente prorogato al 30 giugno 2026</t>
+          <t>2 luglio - ore 18:00</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -16238,7 +16262,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/comunicati/comunicato_06-03-26T.html</t>
+          <t>https://agricoltura.regione.campania.it/fiere/sea-food-asia-2026.html</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -16258,12 +16282,12 @@
     <row r="340" ht="30" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>Beneficiari PSR</t>
+          <t>Avviso per la partecipazione a Vinitaly USA - (New York 26-27 ottobre 2026) - filiera vitivinicola</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Bandi Misura 16 e Tipologia 10.2.1</t>
+          <t>20 luglio - ore 13:00</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -16273,7 +16297,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/PSR_2014_2020/bandi-beneficiari.html</t>
+          <t>https://agricoltura.regione.campania.it/fiere/pdf/vinitaly-usa-2026.pdf</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -16293,12 +16317,12 @@
     <row r="341" ht="30" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>GAL</t>
+          <t>Beneficiari PSR</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Bandi PSR a cura dei GAL</t>
+          <t>Bandi Misura 16 e Tipologia 10.2.1</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -16308,7 +16332,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/PSR_2014_2020/bandi-GAL.html</t>
+          <t>https://agricoltura.regione.campania.it/PSR_2014_2020/bandi-beneficiari.html</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -16333,7 +16357,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Bandi CSR a cura dei GAL</t>
+          <t>Bandi PSR a cura dei GAL</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -16343,7 +16367,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRG06_BANDI_GAL.html</t>
+          <t>https://agricoltura.regione.campania.it/PSR_2014_2020/bandi-GAL.html</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -16363,12 +16387,12 @@
     <row r="343" ht="30" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>GAL Pesca</t>
+          <t>GAL</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Bandi FEAMPA a cura dei GAL Pesca</t>
+          <t>Bandi CSR a cura dei GAL</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -16378,7 +16402,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/FEAMPA/GAL-bandi.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRG06_BANDI_GAL.html</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -16398,27 +16422,27 @@
     <row r="344" ht="30" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>AVVISO PROROGA TERMINI BANDI: Azione specifica n. 01-A; Azione specifica n. 01-B; Azione ordinaria n. 01-E; Azione specifica n. 01-G – AL 31/07/2026 ORE 13:00</t>
+          <t>GAL Pesca</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
+          <t>Bandi FEAMPA a cura dei GAL Pesca</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
           <t>Non specificata</t>
         </is>
       </c>
-      <c r="C344" s="2" t="inlineStr">
-        <is>
-          <t>Non specificata</t>
-        </is>
-      </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/avviso-proroga-termini-bandi-azione-specifica-n-01-a-azione-specifica-n-01-b-azione-ordinaria-n-01-e-azione-specifica-n-01-g-al-31-07-2026-ore-1300/</t>
+          <t>https://agricoltura.regione.campania.it/FEAMPA/GAL-bandi.html</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>GAL Cilento</t>
+          <t>Regione Campania - Agricoltura</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr">
@@ -16433,7 +16457,7 @@
     <row r="345" ht="30" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>ALBO FORNITORI – CSR 2023-2027</t>
+          <t>AVVISO PROROGA TERMINI BANDI: Azione specifica n. 01-A; Azione specifica n. 01-B; Azione ordinaria n. 01-E; Azione specifica n. 01-G – AL 31/07/2026 ORE 13:00</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -16448,7 +16472,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/albo-fornitori-csr-2023-2027/</t>
+          <t>https://www.galcilento.it/bandi/avviso-proroga-termini-bandi-azione-specifica-n-01-a-azione-specifica-n-01-b-azione-ordinaria-n-01-e-azione-specifica-n-01-g-al-31-07-2026-ore-1300/</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -16468,7 +16492,7 @@
     <row r="346" ht="30" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>SHORT LIST CSR 2023-2027 PROFESSIONISTI</t>
+          <t>ALBO FORNITORI – CSR 2023-2027</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -16483,7 +16507,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/short-list-csr-2023-2027-professionisti/</t>
+          <t>https://www.galcilento.it/bandi/albo-fornitori-csr-2023-2027/</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -16503,7 +16527,7 @@
     <row r="347" ht="30" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>AVVISO PER LA RACCOLTA DI MANIFESTAZIONI DI INTERESSE AI FINI DELLA COSTITUZIONE DEL PARTENARIATO PER L’ADESIONE AL BANDO SRG 07 AZIONE A</t>
+          <t>SHORT LIST CSR 2023-2027 PROFESSIONISTI</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -16518,7 +16542,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/avviso-per-la-raccolta-di-manifestazioni-di-interesse-ai-fini-della-costituzione-del-partenariato-per-ladesione-al-bando-srg-07-azione-a/</t>
+          <t>https://www.galcilento.it/bandi/short-list-csr-2023-2027-professionisti/</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -16538,7 +16562,7 @@
     <row r="348" ht="30" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Strengthening the capacities of the National institutions in environmental sector for infrastructure projects management</t>
+          <t>AVVISO PER LA RACCOLTA DI MANIFESTAZIONI DI INTERESSE AI FINI DELLA COSTITUZIONE DEL PARTENARIATO PER L’ADESIONE AL BANDO SRG 07 AZIONE A</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -16548,17 +16572,17 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>16/10/2023</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/BEG/2023/EA-RP/0169</t>
+          <t>https://www.galcilento.it/bandi/avviso-per-la-raccolta-di-manifestazioni-di-interesse-ai-fini-della-costituzione-del-partenariato-per-ladesione-al-bando-srg-07-azione-a/</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>UE - UE</t>
+          <t>GAL Cilento</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr">
@@ -16573,7 +16597,7 @@
     <row r="349" ht="30" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Interpreting Services</t>
+          <t>Strengthening the capacities of the National institutions in environmental sector for infrastructure projects management</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -16583,12 +16607,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>03/10/2023</t>
+          <t>16/10/2023</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/UCA 23/028</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/BEG/2023/EA-RP/0169</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -16608,7 +16632,7 @@
     <row r="350" ht="30" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Supervision of Works Contracts for Establishment of Integrated and Self Sustainable Waste Management System in East and North-East Regions</t>
+          <t>Interpreting Services</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -16618,12 +16642,12 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>08/09/2023</t>
+          <t>03/10/2023</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/SKP/2021/EA-RP/0156</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/UCA 23/028</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -16643,7 +16667,7 @@
     <row r="351" ht="30" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>Technical Assistance for establishing a regional waste management system for the City of Novi Sad and municipalities within the Novi Sad region</t>
+          <t>Supervision of Works Contracts for Establishment of Integrated and Self Sustainable Waste Management System in East and North-East Regions</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -16653,12 +16677,12 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>14/08/2023</t>
+          <t>08/09/2023</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/BEG/2023/EA-RP/0159</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/SKP/2021/EA-RP/0156</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -16678,7 +16702,7 @@
     <row r="352" ht="30" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Further strengthening of administrative capacities of the competent authority in the area of food safety, veterinary and phytosanitary affairs</t>
+          <t>Technical Assistance for establishing a regional waste management system for the City of Novi Sad and municipalities within the Novi Sad region</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -16688,12 +16712,12 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>01/08/2023</t>
+          <t>14/08/2023</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/TGD/2023/EA-RP/0156</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/BEG/2023/EA-RP/0159</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -16713,7 +16737,7 @@
     <row r="353" ht="30" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>Supervision of construction of wastewater collection and treatment system including FOPIP in municipality of Sokobanja</t>
+          <t>Further strengthening of administrative capacities of the competent authority in the area of food safety, veterinary and phytosanitary affairs</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -16723,12 +16747,12 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>31/07/2023</t>
+          <t>01/08/2023</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/BEG/2023/EA-RP/0151</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/TGD/2023/EA-RP/0156</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -16748,32 +16772,32 @@
     <row r="354" ht="30" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA 01 (Produzione integrata) - domande annualità 2026</t>
+          <t>Supervision of construction of wastewater collection and treatment system including FOPIP in municipality of Sokobanja</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
+          <t>31/07/2023</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/NEAR/BEG/2023/EA-RP/0151</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>UE - UE</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
           <t>Non specificata</t>
-        </is>
-      </c>
-      <c r="D354" s="2" t="inlineStr">
-        <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA01_ACA1.html</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="inlineStr">
-        <is>
-          <t>Regione Campania - Agricoltura</t>
-        </is>
-      </c>
-      <c r="F354" s="2" t="inlineStr">
-        <is>
-          <t>❌ Scaduto</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr"/>
@@ -16783,7 +16807,7 @@
     <row r="355" ht="30" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>Tipologia di intervento 8.1.1: Imboschimento di superfici agricole e non agricole (per i premi a superficie)</t>
+          <t>Intervento SRA 01 (Produzione integrata) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -16798,7 +16822,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/comunicati/comunicato_23-12-25B.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA01_ACA1.html</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -16818,27 +16842,27 @@
     <row r="356" ht="30" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Backbone connectivity for Digital Global Gateways - Studies</t>
+          <t>Intervento SRB02 (Sostegno zone con altri svantaggi naturali significativi) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-STUDIES</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB02.html</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>UE - CEF2027</t>
+          <t>Regione Campania - Agricoltura</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr">
@@ -16853,7 +16877,7 @@
     <row r="357" ht="30" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>Backbone connectivity for Digital Global Gateways - Works</t>
+          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01-B: “Formazione per l’organizzazione e la gestione di attività di turismo esperienziale legate alla tipicità artigianale della Dieta Mediterranea”</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -16863,17 +16887,17 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-GATEWAYS-WORKS</t>
+          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-b/</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>UE - CEF2027</t>
+          <t>GAL Cilento</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
@@ -16888,7 +16912,7 @@
     <row r="358" ht="30" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01-B: “Formazione per l’organizzazione e la gestione di attività di turismo esperienziale legate alla tipicità artigianale della Dieta Mediterranea”</t>
+          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01-A: “Studi e ricerche per il rilevamento dei processi d’innovazione e l’impatto (ambientale,economico e sociale) delle attività artigianali tipiche legate alla Dieta Mediterranea e sulla loro territorializzazione, i fabbisogni, le ricadute e il funzionamento nella filiera”</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -16903,7 +16927,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-b/</t>
+          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-a-studi-e-ricerche-per-il-rilevamento-dei-processi-dinnovazione-e-limpatto-ambientaleeconomico-e-sociale-delle-at/</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -16923,7 +16947,7 @@
     <row r="359" ht="30" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01-A: “Studi e ricerche per il rilevamento dei processi d’innovazione e l’impatto (ambientale,economico e sociale) delle attività artigianali tipiche legate alla Dieta Mediterranea e sulla loro territorializzazione, i fabbisogni, le ricadute e il funzionamento nella filiera”</t>
+          <t>BANDO DI ATTUAZIONE DELL’AZIONE ORDINARIA N. 01- E:”Start-Up di attività artigianali tipiche legate alla Dieta Mediterranea collaterali ai prodotti eno-agroalimentari e/o di strutture e servizi per il turismo esperienziale legato al settore”</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -16938,7 +16962,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-a-studi-e-ricerche-per-il-rilevamento-dei-processi-dinnovazione-e-limpatto-ambientaleeconomico-e-sociale-delle-at/</t>
+          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-ordinaria-n-01-estart-up-di-attivita-artigianali-tipiche-legate-alla-dieta-mediterranea-collaterali-ai-prodotti-eno-agroalimentari-e-o-di-strutture-e-servi/</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -16993,12 +17017,12 @@
     <row r="361" ht="30" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01- G: “Avvio di attività di diversificazione nell’extra-agricolo volte al turismo esperienziale incentrato sull’artigianato tipico della Dieta Mediterranea; e di attività artigianali tipiche, relative alla dieta mediterranea”</t>
+          <t>Tipologia di intervento 8.1.1: Imboschimento di superfici agricole e non agricole (per i premi a superficie)</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
@@ -17008,12 +17032,12 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-g/</t>
+          <t>https://agricoltura.regione.campania.it/comunicati/comunicato_23-12-25B.html</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>GAL Cilento</t>
+          <t>Regione Campania - Agricoltura</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr">
@@ -17028,13 +17052,12 @@
     <row r="362" ht="30" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>Istituzione dell'elenco degli Organismi di Formazione e di Consulenza Qualificati ai fini
-dell'attuazione degli interventi SRH 01, SRH 03, e SRG 09</t>
+          <t>Intervento SRB03 (Sostegno zone con vincoli specifici) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>30 giugno 2026</t>
+          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -17044,7 +17067,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/AKIS-avviso.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB03.html</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -17064,7 +17087,7 @@
     <row r="363" ht="30" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>BANDO DI ATTUAZIONE DELL’AZIONE ORDINARIA N. 01- E:”Start-Up di attività artigianali tipiche legate alla Dieta Mediterranea collaterali ai prodotti eno-agroalimentari e/o di strutture e servizi per il turismo esperienziale legato al settore”</t>
+          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01- G: “Avvio di attività di diversificazione nell’extra-agricolo volte al turismo esperienziale incentrato sull’artigianato tipico della Dieta Mediterranea; e di attività artigianali tipiche, relative alla dieta mediterranea”</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -17079,7 +17102,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-ordinaria-n-01-estart-up-di-attivita-artigianali-tipiche-legate-alla-dieta-mediterranea-collaterali-ai-prodotti-eno-agroalimentari-e-o-di-strutture-e-servi/</t>
+          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-g/</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -17099,7 +17122,7 @@
     <row r="364" ht="30" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRB03 (Sostegno zone con vincoli specifici) - domande annualità 2026</t>
+          <t>Intervento SRB01 (Sostegno zone con svantaggi naturali di montagna) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -17114,7 +17137,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB03.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB01.html</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -17134,7 +17157,7 @@
     <row r="365" ht="30" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA28 (Sostegno per mantenimento della forestazione/imboschimento e sistemi agroforestali) - annualità 2026 - impegni precedenti programmazioni</t>
+          <t>Intervento SRA30 Azione B (benessere animale) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -17149,7 +17172,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA28.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA30.html</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -17169,7 +17192,7 @@
     <row r="366" ht="30" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA 14 (Allevatori custodi dell'agrobiodiversità) - domande annualità 2026</t>
+          <t>Intervento SRA 29 - Pagamento al fine di adottare e mantenere pratiche e metodi di produzione biologica - domande annualità 2026</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -17184,7 +17207,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA14_ACA14.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA29.html</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -17204,7 +17227,7 @@
     <row r="367" ht="30" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA 27 (Impegni silvoambientali e in materia di clima) - domande annualità 2026</t>
+          <t>Intervento SRA28 (Sostegno per mantenimento della forestazione/imboschimento e sistemi agroforestali) - annualità 2026 - impegni precedenti programmazioni</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -17219,7 +17242,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA27.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA28.html</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -17239,7 +17262,7 @@
     <row r="368" ht="30" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRB02 (Sostegno zone con altri svantaggi naturali significativi) - domande annualità 2026</t>
+          <t>Intervento SRA 27 (Impegni silvoambientali e in materia di clima) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -17254,7 +17277,7 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB02.html</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA27.html</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -17274,27 +17297,27 @@
     <row r="369" ht="30" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>Equipment for smart European cable systems - Works</t>
+          <t>Intervento SRA 14 (Allevatori custodi dell'agrobiodiversità) - domande annualità 2026</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-DIG-2026-SMART-CABLES-WORKS</t>
+          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA14_ACA14.html</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>UE - CEF2027</t>
+          <t>Regione Campania - Agricoltura</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
@@ -17309,27 +17332,27 @@
     <row r="370" ht="30" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA 29 - Pagamento al fine di adottare e mantenere pratiche e metodi di produzione biologica - domande annualità 2026</t>
+          <t>Erasmus Charter for Higher Education</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
+          <t>24/03/2026</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>22/02/2022</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA29.html</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2022-ECHE-CERT-FP</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>Regione Campania - Agricoltura</t>
+          <t>UE - ERASMUS2027</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
@@ -17344,12 +17367,12 @@
     <row r="371" ht="30" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRA30 Azione B (benessere animale) - domande annualità 2026</t>
+          <t>CSR CAMPANIA 2023/2027AVVISO PUBBLICO PER LA SELEZIONEDEL PERSONALE PER L’ATTUAZIONE E GESTIONECOMPLEMENTO DI SVILUPPO RURALE CAMPANIA 2023/2027INTERVENTO SRG06 ATTUAZIONE STRATEGIA DI SVILUPPO LOCALE:“L’ARTIGIANATO DELLA DIETA MEDITERRANEA”N. 2 AGENTI DI SVILUPPO</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
+          <t>29/08/2025</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
@@ -17359,12 +17382,12 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRA30.html</t>
+          <t>https://www.galcilento.it/bandi/csr-campania-2023-2027avviso-pubblico-per-la-selezionedel-personale-per-lattuazione-e-gestionecomplemento-di-sviluppo-rurale-campania-2023-2027intervento-srg06-attuazione-strategia-di-svilupp/</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>Regione Campania - Agricoltura</t>
+          <t>GAL Cilento</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr">
@@ -17379,12 +17402,12 @@
     <row r="372" ht="30" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>Intervento SRB01 (Sostegno zone con svantaggi naturali di montagna) - domande annualità 2026</t>
+          <t>RETTIFICA BANDO – Misura 19 – Sviluppo locale di tipo partecipativo LEADER – Sottomisura 19.3 – Tipologia di intervento 19.3.1 “Preparazione e realizzazione delle attività di cooperazione del gruppo di azione locale” – Procedura di gara aperta per l’affidamento dell’Azione Comune del Progetto “Rural Food Revolution” afferente i servizi di “Brandizzazione e strumenti di Comunicazione”.</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>30 giugno 2026 - 25.07.2026 con penale progressiva</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -17394,12 +17417,12 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>https://agricoltura.regione.campania.it/CSR_2023-2027/SRB01.html</t>
+          <t>https://www.galcilento.it/bandi/rettifica-bando-misura-19-sviluppo-locale-di-tipo-partecipativo-leader-sottomisura-19-3-tipologia-di-intervento-19-3-1-preparazione-e-realizzazione-delle-attivita-di-cooperazione-del/</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>Regione Campania - Agricoltura</t>
+          <t>GAL Cilento</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
@@ -17414,27 +17437,27 @@
     <row r="373" ht="30" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>Erasmus Charter for Higher Education</t>
+          <t>Outreach to and engagement with young people in EU External Action</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>24/03/2026</t>
+          <t>28/09/2024</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>22/02/2022</t>
+          <t>03/10/2023</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2022-ECHE-CERT-FP</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INTPA/2023/EA-RP/0177-PIN</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>UE - ERASMUS2027</t>
+          <t>UE - UE</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
@@ -17449,27 +17472,27 @@
     <row r="374" ht="30" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CSR CAMPANIA 2023/2027AVVISO PUBBLICO PER LA SELEZIONEDEL PERSONALE PER L’ATTUAZIONE E GESTIONECOMPLEMENTO DI SVILUPPO RURALE CAMPANIA 2023/2027INTERVENTO SRG06 ATTUAZIONE STRATEGIA DI SVILUPPO LOCALE:“L’ARTIGIANATO DELLA DIETA MEDITERRANEA”N. 2 AGENTI DI SVILUPPO</t>
+          <t>Support to ERERA in its mission to implement effective regulatory mechanisms contributing to the development of a regional electricity market</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>29/08/2025</t>
+          <t>20/09/2024</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>25/09/2023</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/csr-campania-2023-2027avviso-pubblico-per-la-selezionedel-personale-per-lattuazione-e-gestionecomplemento-di-sviluppo-rurale-campania-2023-2027intervento-srg06-attuazione-strategia-di-svilupp/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INTPA/ACC/2023/EA-RP/0171-PIN</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>GAL Cilento</t>
+          <t>UE - UE</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
@@ -17484,27 +17507,27 @@
     <row r="375" ht="30" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>RETTIFICA BANDO – Misura 19 – Sviluppo locale di tipo partecipativo LEADER – Sottomisura 19.3 – Tipologia di intervento 19.3.1 “Preparazione e realizzazione delle attività di cooperazione del gruppo di azione locale” – Procedura di gara aperta per l’affidamento dell’Azione Comune del Progetto “Rural Food Revolution” afferente i servizi di “Brandizzazione e strumenti di Comunicazione”.</t>
+          <t>Design, installation works and maintenance services of Faraday cages in the EEAS buildings</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>09/05/2025</t>
+          <t>20/09/2024</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>06/09/2023</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/rettifica-bando-misura-19-sviluppo-locale-di-tipo-partecipativo-leader-sottomisura-19-3-tipologia-di-intervento-19-3-1-preparazione-e-realizzazione-delle-attivita-di-cooperazione-del/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EEAS/2023/RP/0360</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>GAL Cilento</t>
+          <t>UE - UE</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
@@ -17519,22 +17542,22 @@
     <row r="376" ht="30" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>Outreach to and engagement with young people in EU External Action</t>
+          <t>Infrastructure development works: new construction works, renovation works and other smaller scale works</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>28/09/2024</t>
+          <t>14/09/2024</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>03/10/2023</t>
+          <t>21/09/2023</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INTPA/2023/EA-RP/0177-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/AO/020/23</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -17554,22 +17577,22 @@
     <row r="377" ht="30" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>Support to ERERA in its mission to implement effective regulatory mechanisms contributing to the development of a regional electricity market</t>
+          <t>NDICI Cooperation Facility Economics</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>20/09/2024</t>
+          <t>09/09/2024</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>25/09/2023</t>
+          <t>20/09/2023</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INTPA/ACC/2023/EA-RP/0171-PIN</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INTPA/PRY/2023/EA-RP/0175</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -17585,111 +17608,6 @@
       <c r="G377" s="2" t="inlineStr"/>
       <c r="H377" s="2" t="inlineStr"/>
       <c r="I377" s="2" t="inlineStr"/>
-    </row>
-    <row r="378" ht="30" customHeight="1">
-      <c r="A378" s="2" t="inlineStr">
-        <is>
-          <t>Design, installation works and maintenance services of Faraday cages in the EEAS buildings</t>
-        </is>
-      </c>
-      <c r="B378" s="2" t="inlineStr">
-        <is>
-          <t>20/09/2024</t>
-        </is>
-      </c>
-      <c r="C378" s="2" t="inlineStr">
-        <is>
-          <t>06/09/2023</t>
-        </is>
-      </c>
-      <c r="D378" s="2" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EEAS/2023/RP/0360</t>
-        </is>
-      </c>
-      <c r="E378" s="2" t="inlineStr">
-        <is>
-          <t>UE - UE</t>
-        </is>
-      </c>
-      <c r="F378" s="2" t="inlineStr">
-        <is>
-          <t>❌ Scaduto</t>
-        </is>
-      </c>
-      <c r="G378" s="2" t="inlineStr"/>
-      <c r="H378" s="2" t="inlineStr"/>
-      <c r="I378" s="2" t="inlineStr"/>
-    </row>
-    <row r="379" ht="30" customHeight="1">
-      <c r="A379" s="2" t="inlineStr">
-        <is>
-          <t>Infrastructure development works: new construction works, renovation works and other smaller scale works</t>
-        </is>
-      </c>
-      <c r="B379" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2024</t>
-        </is>
-      </c>
-      <c r="C379" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2023</t>
-        </is>
-      </c>
-      <c r="D379" s="2" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/AO/020/23</t>
-        </is>
-      </c>
-      <c r="E379" s="2" t="inlineStr">
-        <is>
-          <t>UE - UE</t>
-        </is>
-      </c>
-      <c r="F379" s="2" t="inlineStr">
-        <is>
-          <t>❌ Scaduto</t>
-        </is>
-      </c>
-      <c r="G379" s="2" t="inlineStr"/>
-      <c r="H379" s="2" t="inlineStr"/>
-      <c r="I379" s="2" t="inlineStr"/>
-    </row>
-    <row r="380" ht="30" customHeight="1">
-      <c r="A380" s="2" t="inlineStr">
-        <is>
-          <t>NDICI Cooperation Facility Economics</t>
-        </is>
-      </c>
-      <c r="B380" s="2" t="inlineStr">
-        <is>
-          <t>09/09/2024</t>
-        </is>
-      </c>
-      <c r="C380" s="2" t="inlineStr">
-        <is>
-          <t>20/09/2023</t>
-        </is>
-      </c>
-      <c r="D380" s="2" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/INTPA/PRY/2023/EA-RP/0175</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>UE - UE</t>
-        </is>
-      </c>
-      <c r="F380" s="2" t="inlineStr">
-        <is>
-          <t>❌ Scaduto</t>
-        </is>
-      </c>
-      <c r="G380" s="2" t="inlineStr"/>
-      <c r="H380" s="2" t="inlineStr"/>
-      <c r="I380" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17724,7 +17642,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30/06/2026 08:59</t>
+          <t>01/07/2026 09:19</t>
         </is>
       </c>
     </row>
@@ -17777,7 +17695,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13">
@@ -17787,7 +17705,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14">
@@ -17797,7 +17715,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -17807,7 +17725,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/bandi_campania.xlsx
+++ b/bandi_campania.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Il bando del GAL Cilento finanzia direttamente PMI locali che vogliono avviare o diversificare attività legate al turismo esperienziale e all'artigianato tipico della Dieta Mediterranea, settori fortemente radicati nel territorio cilentano. Sono finanziabili investimenti per laboratori artigianali, attrezzature, allestimenti e strutture ricettive/esperienziali, rendendolo concretamente accessibile a piccole imprese agricole, artigianali e turistiche del comprensorio.</t>
+          <t>Il bando del GAL Cilento finanzia direttamente PMI che vogliono avviare o diversificare attività legate al turismo esperienziale e all'artigianato tipico della Dieta Mediterranea, settore identitario del territorio cilentano. Sono finanziabili investimenti per laboratori artigianali, attrezzature e strutture per esperienze turistiche legate alle tradizioni locali, rendendolo concretamente accessibile per piccole imprese del food, artigianato e ospitalità del Cilento.</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia direttamente l'avvio di attività artigianali tipiche legate alla Dieta Mediterranea e servizi per il turismo esperienziale enogastronomico, settori core per le PMI del Cilento; sono quindi finanziabili spese per attrezzature, allestimenti e avvio operativo di nuove imprese o rami d'azienda in questi ambiti specifici del territorio GAL.</t>
+          <t>Il bando finanzia direttamente l'avvio di attività artigianali tipiche legate alla Dieta Mediterranea e/o strutture per il turismo esperienziale, settori core del territorio cilentano, rendendolo ideale per PMI locali che vogliono avviare o diversificare in ambito eno-gastronomico o ricettivo-esperienziale. Le spese finanziabili includono tipicamente investimenti materiali e immateriali per la start-up dell'attività, con un target perfettamente calibrato su realtà di piccola dimensione radicate nel territorio GAL Cilento.</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia percorsi formativi per operatori del turismo e dell'artigianato agroalimentare legati alla Dieta Mediterranea, rendendolo ideale per PMI del Cilento attive in ristorazione, produzione tipica o ospitalità che vogliono strutturare offerte di turismo esperienziale. Le spese formative ammissibili rappresentano un'opportunità concreta per qualificare il personale e differenziare il prodotto turistico locale senza investimenti strutturali onerosi.</t>
+          <t>Il bando è promosso direttamente dal GAL Cilento e finanzia attività formative per operatori locali che intendono sviluppare o rafforzare offerte di turismo esperienziale legate all'artigianato e alla Dieta Mediterranea, settori fortemente radicati nel territorio. Una PMI cilentana attiva nel turismo, nell'artigianato alimentare o nella ristorazione tipica può accedere a contributi per formare il proprio personale e strutturare nuovi prodotti turistici esperienziali, con scadenza ampia (luglio 2026) che consente una pianificazione adeguata.</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia modelli di economia sociale legati ai percorsi escursionistici e al turismo lento, settore in cui il Cilento — con il Sentiero degli Dei e la rete dei cammini — ha un posizionamento strategico naturale; una PMI locale (agriturismo, guida turistica, cooperativa di servizi) può accedere a fondi per sviluppare prodotti turistici sostenibili e reti territoriali lungo i trail. Le spese finanziabili tipicamente includono progettazione di servizi, formazione degli operatori e attività di promozione internazionale dei percorsi.</t>
+          <t>Il bando finanzia modelli di economia sociale legati al turismo sostenibile e ai percorsi a lunga distanza, settore in cui il Cilento eccelle con il Parco Nazionale e i cammini storici (es. Cammino di San Nilo, Via Silente): una PMI locale attiva in ospitalità, guide turistiche o servizi outdoor può accedere a fondi per sviluppare prodotti turistici integrati e partnership territoriali. Le spese tipicamente finanziabili includono progettazione di itinerari, formazione degli operatori e sviluppo di piattaforme digitali di promozione.</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>GreenTour di Invitalia finanzia investimenti per la valorizzazione turistica sostenibile, settore particolarmente strategico per le PMI del Cilento grazie al patrimonio naturale e culturale del territorio (Parco Nazionale, costa, borghi). Le spese ammissibili tipicamente includono strutture ricettive, servizi turistici eco-compatibili e promozione territoriale, ambiti in cui le micro e piccole imprese locali possono accedere con progettualità concrete.</t>
+          <t>Il bando GreenTour di Invitalia sostiene investimenti nel turismo sostenibile, settore strategico per il Cilento grazie al Parco Nazionale e alla costa: una PMI locale può finanziare interventi di riqualificazione strutture ricettive, mobilità green e valorizzazione ambientale. È direttamente accessibile a piccole imprese del comparto turistico-ricettivo campano.</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Credito/Finanza</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Il Fondo di partecipazione MUR gestito da Invitalia supporta progetti di ricerca e innovazione con strumenti di equity o quasi-equity, rendendolo accessibile a PMI campane con vocazione tecnologica o spin-off universitari, settori presenti anche nel Cilento in ambiti come agroalimentare e turismo sostenibile. Tuttavia, la complessità dello strumento finanziario e i requisiti di solidità aziendale lo rendono più adatto a PMI strutturate che a micro-imprese.</t>
+          <t>Il Fondo di partecipazione MUR gestito da Invitalia supporta progetti di ricerca e innovazione, potenzialmente accessibili a PMI campane che collaborano con università o enti di ricerca, incluse realtà del Cilento in settori come agroalimentare o turismo sostenibile. La struttura del fondo (partecipazione al capitale o strumenti finanziari) richiede però una solidità finanziaria e progettuale che può rappresentare una barriera per le micro-imprese.</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia la redazione di Piani di Gestione Forestale, strumento obbligatorio per accedere a molti incentivi forestali e agroambientali: una PMI agricola o forestale del Cilento, territorio ricco di boschi e aree protette, può coprire i costi di progettazione e consulenza tecnica altrimenti onerosi. La pertinenza è media perché il beneficio è indiretto e condizionato al possesso o alla gestione di superfici boschive.</t>
+          <t>Il bando finanzia la redazione di Piani di Gestione Forestale, strumento obbligatorio per accedere a molti incentivi agro-forestali: una PMI del Cilento con proprietà boschive o attività di gestione del territorio (es. aziende agro-silvo-pastorali) può coprire i costi di progettazione e consulenza tecnica forestale. La pertinenza è media perché il target è specifico e limitato alle realtà con superfici boscate da gestire.</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Il bando 'Vita &amp; Opportunità' di Invitalia supporta iniziative legate all'inclusione sociale e alla creazione di impresa in aree svantaggiate, potenzialmente rilevante per PMI del Cilento operanti nei settori dei servizi alla persona o del welfare di comunità. Tuttavia, la natura spesso selettiva e progettuale di questi strumenti Invitalia richiede una verifica puntuale dei requisiti soggettivi e delle spese ammissibili prima di investire risorse nella candidatura.</t>
+          <t>Il bando Vita &amp; Opportunità di Invitalia sostiene progetti a valenza sociale e di inclusione, potenzialmente accessibili a PMI del Cilento operanti in settori come welfare, servizi alla persona o economia sociale, ma la natura spesso orientata al terzo settore può limitare l'accesso diretto alle imprese profit di piccola dimensione. È opportuno verificare se la PMI rientra tra i soggetti beneficiari ammessi prima di procedere con la candidatura.</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Il meccanismo finanzia tecnologie specifiche per le energie rinnovabili (solare, eolico, biomasse), settori in cui le PMI del Cilento possono investire data la vocazione territoriale e le risorse naturali disponibili. L'accesso diretto per una PMI può richiedere intermediari finanziari o partnership, ma rappresenta un'opportunità concreta per chi opera nella produzione energetica o nell'efficienza industriale.</t>
+          <t>Il meccanismo finanzia tecnologie specifiche per le energie rinnovabili, potenzialmente accessibile a PMI del Cilento che intendono investire in impianti fotovoltaici, eolici o da biomasse, sfruttando le risorse naturali del territorio. La pertinenza è media perché i bandi UE di questo tipo richiedono spesso capacità progettuali e finanziarie non sempre alla portata di piccole imprese senza supporto di consulenza specializzata.</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Il bando ESF sostiene l'accesso a servizi di incubazione e finanza inclusiva per nuovi imprenditori e microimprese, potenzialmente utile per PMI del Cilento che vogliono avviare o sviluppare attività in aree a rischio esclusione economica. Tuttavia, il focus su 'inclusive incubation' suggerisce una priorità verso soggetti svantaggiati o startup nascenti, limitando la rilevanza per PMI già consolidate.</t>
+          <t>Il bando ESF sostiene l'inclusione finanziaria e l'incubazione d'impresa, potenzialmente utile per PMI del Cilento che vogliono accedere a strumenti finanziari alternativi o percorsi di accompagnamento all'avvio/crescita aziendale. Tuttavia, essendo un bando europeo diretto, richiede spesso la partecipazione tramite partenariati strutturati o intermediari, il che può limitare l'accesso diretto per una piccola impresa locale.</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia R&amp;S su prodotti bio-based derivati da organismi marini, settore potenzialmente rilevante per PMI del Cilento attive nella pesca, acquacoltura o bioeconomia marina. Tuttavia, i requisiti tecnici elevati e la necessità di consorziarsi con partner europei rendono l'accesso complesso per PMI di piccola dimensione senza esperienza in progetti UE.</t>
+          <t>Il bando Horizon UE finanzia ricerca e sviluppo su prodotti bio-based derivati da organismi marini, settore rilevante per PMI del Cilento attive nella pesca, acquacoltura o biotecnologie marine. Tuttavia, i requisiti tecnici elevati e la necessità di partecipare a consorzi internazionali rendono l'accesso complesso per una PMI di piccola dimensione senza partner di ricerca.</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e innovazione per filiere alimentari sostenibili, bioeconomia e biodiversità, ambiti direttamente rilevanti per PMI agroalimentari del Cilento (produzioni DOP/IGP, filiera corta, agricoltura biologica). Tuttavia, i bandi Horizon richiedono tipicamente la partecipazione in consorzio europeo e competenze progettuali elevate, rendendo l'accesso diretto complesso per una PMI di piccole dimensioni senza un partner di ricerca.</t>
+          <t>Il bando Horizon finanzia ricerca e innovazione per catene del valore sostenibili nel settore agroalimentare, un'opportunità concreta per PMI del Cilento attive in produzioni tipiche (olio DOP, mozzarella, legumi antichi) che vogliono sviluppare progetti su biodiversità agricola e bioeconomia. La partecipazione richiede però la costruzione di un consorzio europeo, il che rende l'accesso complesso per PMI di piccola dimensione senza partner di ricerca già consolidati.</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti di ricerca e innovazione legati all'economia bio-based e agli stili di vita sostenibili, settori rilevanti per PMI agricole e agroalimentari del Cilento. Tuttavia, i bandi Horizon richiedono partnership europee strutturate e capacità di gestione progettuale complessa, rendendo l'accesso diretto difficile per una piccola impresa senza il supporto di un ente di ricerca o consorzio.</t>
+          <t>Il bando Horizon finanzia progetti di ricerca e innovazione legati a stili di vita sostenibili e bioeconomia, settori rilevanti per PMI del Cilento attive in agricoltura biologica, agroalimentare o turismo eco-sostenibile. Tuttavia, i bandi Horizon richiedono tipicamente la partecipazione a consorzi transnazionali e una capacità progettuale elevata, il che rende l'accesso diretto complesso per una PMI di piccole dimensioni senza il supporto di un partner scientifico o di una rete europea.</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia ricerca e innovazione sull'agrobiodiversità per la sicurezza alimentare, un tema particolarmente rilevante per PMI agricole del Cilento che valorizzano produzioni locali tipiche (es. fico bianco del Cilento, carciofo di Paestum). La pertinenza è media perché Horizon richiede solitamente la partecipazione in consorzi transnazionali e profili tecnico-scientifici elevati, rendendo l'accesso diretto complesso per una PMI senza partnership con enti di ricerca.</t>
+          <t>Il bando finanzia progetti di ricerca e innovazione sulla biodiversità agroalimentare per la sicurezza alimentare, ambito in cui il Cilento — con prodotti DOP/IGP e varietà autoctone — ha un potenziale concreto; tuttavia Horizon richiede partenariati internazionali e capacità progettuali elevate, rendendo l'accesso diretto per una PMI isolata complesso senza il supporto di un ente di ricerca capofila.</t>
         </is>
       </c>
     </row>
@@ -1225,14 +1225,14 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia lo sviluppo di tecniche di ricarica artificiale delle falde acquifere (MAR) in contesti rurali, direttamente applicabile alle PMI agricole del Cilento che affrontano stress idrico stagionale. Una piccola impresa agricola o cooperativa può partecipare come partner di un consorzio europeo, coprendo investimenti in sistemi di gestione idrica sostenibile, ma la complessità dei progetti Horizon richiede alleanze con enti di ricerca.</t>
+          <t>Il bando Horizon finanzia lo sviluppo di tecniche di ricarica artificiale delle falde acquifere (MAR) in contesti rurali, settore direttamente rilevante per le PMI agricole del Cilento che soffrono di stress idrico stagionale. La complessità dei bandi Horizon e la necessità di partnership internazionali riducono l'accessibilità diretta per una piccola impresa, che dovrebbe partecipare come partner tecnico locale in un consorzio guidato da enti di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Bio-based chemicals and/or materials from woody residues</t>
+          <t>SSbD bio-based alternatives for fertilising and/or crop protection products</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IA-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-IAFlag-02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1267,34 +1267,34 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Agricoltura</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia ricerca e sviluppo su chimica e materiali bio-based da residui legnosi, settore rilevante per il Cilento data la presenza di filiere forestali e agricole con scarti di legno (olivicoltura, boschi). Una PMI del settore agro-forestale o chimico-green può partecipare in consorzio con enti di ricerca, ma la complessità dei requisiti Horizon e la necessità di partnership internazionali rendono l'accesso impegnativo senza un soggetto capofila strutturato.</t>
+          <t>Il bando Horizon finanzia ricerca e sviluppo su fertilizzanti e prodotti fitosanitari bio-based progettati secondo i principi SSbD (Safe and Sustainable by Design), settore rilevante per le PMI agricole del Cilento che operano in produzioni tipiche e biologiche. Tuttavia, la complessità dei requisiti Horizon e la necessità di partecipare in consorzio europeo rendono l'accesso difficile per PMI di piccole dimensioni senza un partner di ricerca strutturato.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
+          <t>Supporting industry in the switch to sustainable and circular bio-based products and processes</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-CBE-2026-CSA-01</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1314,19 +1314,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Internazionalizzazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia partnership internazionali nel settore delle industrie culturali e creative (CCI), ambito rilevante per PMI del Cilento attive in artigianato, turismo culturale o produzioni creative. Tuttavia, la complessità progettuale di Horizon e il requisito di consorzio transnazionale rendono l'accesso difficile per una PMI piccola senza un soggetto capofila universitario o istituzionale.</t>
+          <t>Il bando Horizon Europe finanzia ricerca e sviluppo per la transizione verso prodotti e processi bio-based circolari, con opportunità concrete per PMI campane operanti in agricoltura, agroalimentare o bioeconomia, settori radicati nel Cilento. La pertinenza è media perché richiede capacità progettuale elevata e partnership con enti di ricerca, ma le PMI possono partecipare come partner industriali coprendo costi di R&amp;S, prototipazione e scale-up di processi sostenibili.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
+          <t>Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-03</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1361,19 +1361,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Sostenibilità</t>
+          <t>Internazionalizzazione</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti di co-gestione degli ecosistemi marini e delle acque interne, con forte coinvolgimento dei pescatori: una PMI del Cilento attiva nella pesca professionale o nell'acquacoltura può partecipare come partner in un consorzio europeo, contribuendo alla gestione sostenibile delle risorse ittiche locali. Le spese finanziabili includono ricerca applicata, attività dimostrative e trasferimento di conoscenze, ma la complessità dei progetti Horizon richiede necessariamente la collaborazione con enti di ricerca o università.</t>
+          <t>Il bando finanzia partnership internazionali nel settore culturale e delle industrie creative (CCI), ambito rilevante per PMI del Cilento attive in artigianato, produzione culturale o turismo esperienziale; tuttavia Horizon richiede consorzio transnazionale e capacità progettuale elevata, rendendo l'accesso complesso per micro-imprese senza esperienza europea.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
+          <t>By fishers, for fishers: co-management of marine and freshwaters ecosystems and resources</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-05</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-03-OCEAN-03</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1408,19 +1408,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Sostenibilità</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia progetti dimostrativi per proteggere il patrimonio culturale dagli impatti del cambiamento climatico, un'opportunità concreta per PMI del Cilento operanti nel settore della conservazione, del restauro o delle tecnologie ambientali, considerata la ricchezza di siti UNESCO e borghi storici dell'area. Tuttavia, i bandi Horizon richiedono tipicamente partnership europee e capacità progettuali elevate, rendendo l'accesso diretto complesso per una PMI di piccola dimensione senza esperienza pregressa in progetti europei.</t>
+          <t>Il bando Horizon finanzia progetti di co-gestione delle risorse marine e delle acque dolci, rilevante per PMI del settore pesca e acquacoltura del Cilento (area costiera e fiumi come il Calore). Tuttavia, i bandi Horizon richiedono partnership internazionali e capacità progettuali elevate, rendendo l'accesso diretto complesso per una PMI piccola, che dovrebbe partecipare come partner all'interno di un consorzio guidato da enti di ricerca.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joint demonstration of solutions to build soil resilience to extreme weather events and support food security </t>
+          <t>Demonstrating solutions to protect and preserve cultural heritage from the impacts of climate change</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-06-CLIMA-SOIL</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MISS-2026-01-CLIMA-05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Agricoltura</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti dimostrativi per la resilienza del suolo agli eventi climatici estremi e la sicurezza alimentare, temi centrali per le PMI agricole del Cilento esposte a siccità e dissesto idrogeologico. L'accesso richiede però la partecipazione a consorzi europei multi-partner, il che rende complessa la candidatura per una PMI di piccola dimensione senza esperienza pregressa in progetti Horizon.</t>
+          <t>Il bando finanzia soluzioni dimostrative per proteggere il patrimonio culturale dagli impatti del cambiamento climatico, settore molto rilevante per il Cilento ricco di siti UNESCO e beni storici. Tuttavia, i bandi Horizon richiedono consorzi internazionali e capacità di R&amp;S elevate, rendendo la partecipazione diretta di una PMI locale complessa senza un ruolo in un partenariato più ampio.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Il programma Hop-On consente a ricercatori e organizzazioni di paesi meno rappresentati in Horizon Europe (tra cui l'Italia meridionale) di agganciarsi a progetti già finanziati, coprendo costi di personale di ricerca e attività di networking con consorzi europei. Una PMI campana con attività R&amp;S può accedere come partner 'hop-on' senza dover costruire un progetto da zero, abbassando la barriera di ingresso ai fondi europei.</t>
+          <t>Il programma Hop-On consente a ricercatori e organizzazioni di paesi meno rappresentati in Horizon Europe (tra cui l'Italia meridionale) di agganciarsi a progetti già finanziati, coprendo costi di personale e mobilità per attività di ricerca e innovazione. Una PMI campana con vocazione tecnologica o manifatturiera può candidarsi come 'hop-on partner' su progetti europei esistenti, accedendo a finanziamenti UE senza dover costruire un consorzio da zero.</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Il bando supporta stakeholder della filiera alimentare — incluse PMI della trasformazione, ristorazione e distribuzione — nell'implementare sistemi di misurazione e prevenzione degli sprechi alimentari, un tema rilevante per le imprese agroalimentari del Cilento (es. conservieri, frantoi, cantine). L'accessibilità è media perché i bandi SMP di questo tipo tendono a finanziare principalmente attività di consulenza, formazione e strumenti operativi, ma richiedono capacità di rendicontazione europea e spesso preferiscono consorzi o reti di imprese rispetto a singole PMI.</t>
+          <t>Il bando supporta imprese della filiera agroalimentare — particolarmente rilevante per PMI del Cilento attive in produzione, trasformazione o distribuzione alimentare — nell'implementare sistemi di misurazione e riduzione degli sprechi alimentari, con potenziale accesso a strumenti formativi e metodologie operative finanziate dall'UE. La pertinenza è media perché il bando è orientato principalmente a stakeholder di filiera e organizzazioni di settore, richiedendo una struttura minima per partecipare attivamente ai programmi di supporto.</t>
         </is>
       </c>
     </row>
@@ -1596,19 +1596,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Il fondo è rivolto a contrastare la perdita di attività produttive e occupazione in aree colpite da crisi industriali, quindi può interessare PMI manifatturiere o di servizi industriali del Cilento che operano in settori a rischio dismissione o ridimensionamento. Tuttavia, il focus su 'deindustrializzazione' tende a privilegiare territori e imprese con forte vocazione industriale consolidata, rendendo l'accesso meno immediato per le micro-realtà artigianali o turistiche tipiche del Cilento.</t>
+          <t>Il fondo è rivolto a imprese manifatturiere e industriali in aree a rischio deindustrializzazione, finanziando investimenti produttivi e mantenimento dei livelli occupazionali; una PMI del Cilento operante in settori industriali o di trasformazione può accedere, ma la vocazione prevalentemente turistica e agricola del territorio riduce la platea dei potenziali beneficiari locali.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Accessible and available travel facilitation</t>
+          <t>Open topic on driving innovation uptake of disaster risk solutions</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1643,39 +1643,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Turismo</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia progetti per rendere i viaggi più accessibili e inclusivi, ambito rilevante per le PMI turistiche del Cilento (agenzie, strutture ricettive, operatori di mobilità) che vogliono sviluppare servizi per persone con disabilità o mobilità ridotta. Tuttavia, Horizon richiede generalmente partenariati europei e capacità progettuali elevate, rendendo l'accesso diretto complesso per una piccola impresa senza un consorzio o un intermediario.</t>
+          <t>Il bando finanzia soluzioni innovative per la gestione del rischio da disastri naturali (frane, alluvioni, terremoti), tematiche particolarmente rilevanti per il territorio del Cilento, area ad alto rischio idrogeologico. Una PMI campana attiva in settori come monitoraggio ambientale, ingegneria, ICT o protezione civile può partecipare come partner di un consorzio europeo, ma la complessità progettuale di Horizon Europe rende l'accesso difficile senza un capofila esperto o un ente di ricerca come partner.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Networks of European Cinemas</t>
+          <t>Accessible and available travel facilitation</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-CINNET</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>UE - CREA2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1685,39 +1685,39 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Turismo</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia reti di sale cinematografiche europee nell'ambito del programma Creative Europe, richiedendo strutture già organizzate in network transnazionali: una PMI del Cilento difficilmente soddisfa i requisiti di aggregazione e capacità progettuale europea richiesti. Il settore cinematografico/culturale ha scarsa rappresentanza imprenditoriale privata di piccola dimensione nel territorio cilentano.</t>
+          <t>Il bando finanzia soluzioni innovative per rendere i viaggi più accessibili e inclusivi, un'opportunità concreta per PMI turistiche del Cilento che vogliono sviluppare servizi o tecnologie per il turismo accessibile (es. accessibilità nelle strutture ricettive, trasporti, esperienze per persone con disabilità). La complessità dei bandi Horizon e la necessità di partnership europee rende però l'accesso difficile per PMI di piccole dimensioni senza esperienza pregressa in progetti UE.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Films on the Move</t>
+          <t>Networks of European Cinemas</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-FILMOVE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-CINNET</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1742,14 +1742,14 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Films on the Move è un bando MEDIA/Creative Europe destinato a distributori cinematografici europei per sostenere la circolazione transnazionale di film non nazionali: non è accessibile a una PMI generica del Cilento, ma solo a società di distribuzione cinematografica con track record specifico nel settore audiovisivo europeo. Le spese finanziabili riguardano acquisto diritti, doppiaggio, sottotitolazione e marketing di film, attività estranee al tessuto produttivo tipico dell'area.</t>
+          <t>Il bando finanzia reti di sale cinematografiche europee nell'ambito del programma Creative Europe, richiedendo partnership transnazionali strutturate tra esercenti cinema: una PMI del Cilento potrebbe partecipare solo se gestisce una sala cinematografica e ha già relazioni consolidate con operatori di altri Paesi UE, condizione difficilmente verificabile per realtà locali di piccola dimensione.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Europe’s Born-digital Heritage</t>
+          <t>Films on the Move</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-BORN-DIGITAL-HERITAGE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CREA-MEDIA-2026-FILMOVE</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>UE - CREA2027</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1784,39 +1784,39 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Digitalizzazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la salvaguardia del patrimonio culturale digitale nativo a livello europeo, con obiettivi e scala che si rivolgono principalmente a istituzioni culturali, archivi, biblioteche e grandi enti pubblici. Una PMI del Cilento difficilmente possiede i requisiti tecnici, la capacità progettuale transnazionale e le competenze specializzate richieste per accedere a finanziamenti PPPA2027 di questo tipo.</t>
+          <t>Films on the Move è un programma MEDIA/Creative Europe dedicato esclusivamente a distributori cinematografici europei per supportare la circolazione transnazionale di film non nazionali: non è accessibile a PMI generiche del Cilento o della Campania al di fuori del settore distribuzione cinematografica professionale. Solo una società specializzata nella distribuzione di film in sala potrebbe candidarsi, rendendo il bando irrilevante per la stragrande maggioranza delle PMI locali.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Support for social dialogue</t>
+          <t>Safeguarding Europe’s Born-digital Heritage</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-SOC-DIALOG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-BORN-DIGITAL-HERITAGE</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>UE - SOCPL</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1831,39 +1831,39 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Digitalizzazione</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Il bando UE 'Support for social dialogue' finanzia organizzazioni di rappresentanza (sindacati, associazioni datoriali) per attività di dialogo sociale a livello europeo, non è accessibile direttamente a una PMI operativa nel Cilento. Una piccola impresa manifatturiera o turistica del territorio non rientra tra i beneficiari ammissibili.</t>
+          <t>Il bando riguarda la salvaguardia del patrimonio culturale digitale a livello europeo, con focus su istituzioni pubbliche, archivi e biblioteche: una PMI del Cilento avrebbe difficoltà a qualificarsi come beneficiario diretto e i requisiti progettuali richiedono partnership transnazionali complesse e competenze specialistiche difficilmente presenti in una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Empowering youth in the EU Outermost Regions – YOUTH 4 OUTERMOST REGIONS (#YOUTH4ORS)</t>
+          <t>Support for social dialogue</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-YOUTH4OR2</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/SOCPL-2026-SOC-DIALOG</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>UE - ERDFTA</t>
+          <t>UE - SOCPL</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1878,39 +1878,39 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Il bando è rivolto alle Regioni Ultraperiferiche dell'UE (come Canarie, Azzorre, Martinica ecc.), territori che per definizione escludono la Campania e il Cilento. Una PMI campana non ha accesso geografico a questo finanziamento.</t>
+          <t>Il bando 'Support for social dialogue' della Commissione Europea è destinato a organizzazioni sindacali e associazioni datoriali europee per rafforzare la contrattazione collettiva e il dialogo sociale, non a PMI individuali. Una piccola impresa del Cilento non ha titolo diretto per candidarsi né accede a finanziamenti per spese operative o investimenti aziendali.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01-A: “Studi e ricerche per il rilevamento dei processi d’innovazione e l’impatto (ambientale,economico e sociale) delle attività artigianali tipiche legate alla Dieta Mediterranea e sulla loro territorializzazione, i fabbisogni, le ricadute e il funzionamento nella filiera”</t>
+          <t>Empowering youth in the EU Outermost Regions – YOUTH 4 OUTERMOST REGIONS (#YOUTH4ORS)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Non specificata</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-a-studi-e-ricerche-per-il-rilevamento-dei-processi-dinnovazione-e-limpatto-ambientaleeconomico-e-sociale-delle-at/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-YOUTH4OR2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>GAL Cilento</t>
+          <t>UE - ERDFTA</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1930,34 +1930,34 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Il bando finanzia studi e ricerche accademiche/istituzionali sui processi d'innovazione nelle attività artigianali legate alla Dieta Mediterranea, una tipologia di intervento orientata a enti di ricerca o istituzioni piuttosto che a PMI operative. Una piccola impresa del Cilento nel settore agroalimentare o artigianale difficilmente rientra tra i soggetti beneficiari diretti, trovando scarsa applicabilità concreta al proprio modello di business.</t>
+          <t>Il bando è specificamente destinato alle Regioni Ultraperiferiche dell'UE (come Azzorre, Canarie, Guadalupa, ecc.), territori che non includono la Campania né il Cilento: una PMI campana non rientra nei beneficiari ammissibili e non può accedere ai finanziamenti previsti.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>The European Capital of Innovation Award Rising Innovator Category HORIZON-EIC-2026-PRIZE-ICAPITAL</t>
+          <t>BANDO DI ATTUAZIONE DELL’AZIONE SPECIFICA N. 01-A: “Studi e ricerche per il rilevamento dei processi d’innovazione e l’impatto (ambientale,economico e sociale) delle attività artigianali tipiche legate alla Dieta Mediterranea e sulla loro territorializzazione, i fabbisogni, le ricadute e il funzionamento nella filiera”</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>Non specificata</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-02</t>
+          <t>https://www.galcilento.it/bandi/bando-di-attuazione-dellazione-specifica-n-01-a-studi-e-ricerche-per-il-rilevamento-dei-processi-dinnovazione-e-limpatto-ambientaleeconomico-e-sociale-delle-at/</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>GAL Cilento</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Il premio European Capital of Innovation è destinato a città e capitali europee dell'innovazione, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente. L'unico vantaggio indiretto potrebbe derivare dal coinvolgimento in ecosistemi urbani candidati, scenario poco probabile per territori rurali come il Cilento.</t>
+          <t>Il bando finanzia studi e ricerche istituzionali sull'impatto delle attività artigianali legate alla Dieta Mediterranea, una tipologia di progetto più adatta a enti di ricerca, università o associazioni di categoria che a una PMI operativa. Una piccola impresa difficilmente dispone delle competenze metodologiche e delle strutture per condurre rilevamenti scientifici su filiere territoriali, rendendo l'accesso concreto molto limitato.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>The European Capital of Innovation Award iCapital Category HORIZON-EIC-2026-ICAPITAL</t>
+          <t>The European Capital of Innovation Award Rising Innovator Category HORIZON-EIC-2026-PRIZE-ICAPITAL</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2024,34 +2024,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Il bando premia città europee per le loro strategie di innovazione urbana: i destinatari sono amministrazioni comunali e capitali europee dell'innovazione, non PMI. Una piccola impresa del Cilento non può candidarsi direttamente e difficilmente beneficia di ricadute dirette da questo premio.</t>
+          <t>Il premio European Capital of Innovation è destinato a città e capitali europee dell'innovazione, non a PMI: una piccola o media impresa del Cilento non può candidarsi direttamente. Anche indirettamente, il bando non prevede finanziamenti a fondo perduto né accesso a risorse per le imprese, ma solo un riconoscimento istituzionale per enti pubblici territoriali.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Support to awareness raising about the Arctic communities, including Indigenous People</t>
+          <t>The European Capital of Innovation Award iCapital Category HORIZON-EIC-2026-ICAPITAL</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EMFAF-2026-PIA-ARCTIC</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PRIZE-ICAPITAL-01</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>UE - EMFAF</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2066,39 +2066,39 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda la sensibilizzazione sulle comunità artiche e i popoli indigeni, un ambito del tutto estraneo alle attività produttive e al contesto territoriale di una PMI campana del Cilento. Non esistono spese finanziabili o settori beneficiari rilevanti per realtà locali di piccola dimensione operanti in questo territorio.</t>
+          <t>Il premio iCapital è destinato esclusivamente a città e capitali europee dell'innovazione, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né ottenere finanziamenti diretti da questo bando. L'unica utilità indiretta sarebbe partecipare a progetti promossi da un Comune candidato, scenario poco probabile per i piccoli centri del territorio cilentano.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Industrial Readiness for Affordable Ka-band User Terminals</t>
+          <t>Support to awareness raising about the Arctic communities, including Indigenous People</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-IRIS2-UT-IND-READINESS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EMFAF-2026-PIA-ARCTIC</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>UE - PPPA2027</t>
+          <t>UE - EMFAF</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2113,19 +2113,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo industriale di terminali utente in banda Ka per comunicazioni satellitari, un settore altamente specializzato che richiede capacità produttive e tecnologiche avanzate nell'elettronica e nelle telecomunicazioni spaziali, del tutto estranee al tessuto produttivo tipico di una PMI del Cilento o della Campania in generale. Le barriere tecniche, finanziarie e di qualificazione industriale lo rendono inaccessibile per quasi qualsiasi piccola o media impresa del territorio.</t>
+          <t>Il bando riguarda la sensibilizzazione sulle comunità artiche e i popoli indigeni del nord Europa, un tema geograficamente e settorialmente lontano dalla realtà produttiva di una PMI campana o del Cilento. Non esistono spese finanziabili rilevanti per attività locali nel settore pesca, turismo o agroalimentare tipici del territorio cilentano.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Capacity building for Ukrainian regional policy stakeholders</t>
+          <t>Industrial Readiness for Affordable Ka-band User Terminals</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-UAACQUIS22</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/PPPA-2026-IRIS2-UT-IND-READINESS</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>UE - ERDFTA</t>
+          <t>UE - PPPA2027</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2160,39 +2160,39 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Il bando è destinato a stakeholder della politica regionale ucraina per attività di capacity building istituzionale, un contesto completamente estraneo alle PMI campane o cilentane. Non prevede finanziamenti diretti a imprese private né attività riconducibili a settori produttivi locali.</t>
+          <t>Il bando finanzia lo sviluppo industriale di terminali utente in banda Ka per comunicazioni satellitari, richiedendo competenze ingegneristiche aerospaziali e capacità produttive hi-tech difficilmente presenti in una PMI del Cilento o della Campania interna. Si tratta di un programma ESA/UE orientato a grandi player dell'industria spaziale e della difesa, non accessibile a piccole imprese prive di un posizionamento specifico nella supply chain satellitare.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ERC ADVANCED GRANTS</t>
+          <t>Capacity building for Ukrainian regional policy stakeholders</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-ADG</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERDFTA-2026-UAACQUIS22</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ERDFTA</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2207,34 +2207,34 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Gli ERC Advanced Grants sono destinati esclusivamente a ricercatori individuali di eccellenza con track record scientifico consolidato, non a PMI: una piccola o media impresa del Cilento non può candidarsi direttamente e difficilmente rientra tra i soggetti ospitanti eleggibili. Il bando finanzia ricerca fondamentale di frontiera in ambito accademico, senza benefici diretti o immediati per attività produttive o commerciali tipiche di una PMI campana.</t>
+          <t>Il bando è destinato a stakeholder della politica regionale ucraina nell'ambito del capacity building istituzionale, una finalità completamente estranea all'operatività di una PMI campana o cilentana. Non sono previsti beneficiari privati né spese tipiche delle imprese.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
+          <t>ERC ADVANCED GRANTS</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-ADG</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon è focalizzato su ricerca sanitaria digitale e AI in Africa sub-sahariana, un ambito altamente specializzato e distante dalle attività tipiche di una PMI campana o del Cilento. Richiede partnership internazionali strutturate, capacità di ricerca avanzata e competenze specifiche in sanità digitale difficilmente accessibili a una piccola o media impresa locale.</t>
+          <t>Gli ERC Advanced Grants sono destinati esclusivamente a ricercatori individuali di eccellenza con track record scientifico consolidato, non a PMI: una piccola impresa del Cilento non può candidarsi direttamente né beneficiare dei fondi in modo autonomo. L'unico scenario marginale sarebbe una partnership con un ente di ricerca capofila, ma il bando non prevede ruoli per soggetti imprenditoriali come beneficiari.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
+          <t>Enhancing integrated research and healthcare in sub-Saharan Africa through digital innovation and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-DIGIT-02</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2301,19 +2301,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon finanzia reti di formazione e innovazione in ambito farmaceutico, etico-regolatorio e piattaforme digitali regolatorie, settori altamente specializzati e lontani dal tessuto produttivo tipico del Cilento e della Campania interna. Le PMI locali difficilmente dispongono delle competenze tecniche, dei partner internazionali e della struttura progettuale richiesta da Horizon per partecipare competitivamente a questo tipo di call.</t>
+          <t>Il bando Horizon è focalizzato su ricerca sanitaria e AI applicata all'Africa sub-sahariana, richiedendo partnership internazionali complesse e capacità di ricerca avanzata difficilmente accessibili a una PMI campana di piccole dimensioni. Non prevede benefici diretti per il territorio del Cilento né finanzia attività commerciali tipiche delle PMI locali.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Dr Pascoal Mocumbi Prize</t>
+          <t>Training and innovation networks for sustained capacity development related to ethics, regulatory, pharmacovigilance, and related digital regulatory platforms</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-DRPASCOALMOCUMBIPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-GH-EDCTP3-2026-03-SERP-01</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2348,19 +2348,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Altro</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Il Premio Dr Pascoal Mocumbi è un riconoscimento internazionale nell'ambito della ricerca clinica su malattie infettive in Africa subsahariana, destinato a ricercatori e istituzioni scientifiche, non a PMI. Una piccola impresa del Cilento non ha né il profilo né le attività richieste per candidarsi o beneficiare di questo bando.</t>
+          <t>Il bando Horizon finanzia reti di formazione e innovazione nel settore farmaceutico/regolatorio (etica, farmacovigilanza, piattaforme digitali regolatorie), con requisiti di consorzio internazionale e capacità di ricerca avanzata difficilmente compatibili con una PMI del Cilento non operante in ambito biomedico o farmaceutico. La struttura Horizon richiede partnership europee strutturate e budget di progetto elevati, rendendo l'accesso diretto sostanzialmente inaccessibile per una piccola impresa locale.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Outstanding Female Scientist Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Dr Pascoal Mocumbi Prize</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSFEMALESCIENTISTPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-DRPASCOALMOCUMBIPRIZE</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2400,14 +2400,14 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo dedicato esclusivamente a scienziate di eccellenza nel campo della ricerca su malattie infettive legate alla povertà: non è uno strumento finanziario accessibile a PMI e non prevede finanziamenti per attività aziendali, investimenti o progetti imprenditoriali. Una PMI del Cilento non ha alcuna possibilità concreta di beneficiarne.</t>
+          <t>Il Premio Dr Pascoal Mocumbi è un riconoscimento nell'ambito della partnership Europa-Africa per la ricerca su malattie infettive neglette (EDCTP3), destinato a ricercatori o istituzioni scientifiche operanti in Africa subsahariana. Una PMI campana, anche del Cilento, non ha i requisiti soggettivi né il profilo di attività per accedervi.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Outstanding Research Team Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Outstanding Female Scientist Prize</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSRESEARCHTEAMPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSFEMALESCIENTISTPRIZE</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2447,14 +2447,14 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo destinato a team di ricerca eccellenti nell'ambito della salute globale e delle malattie infettive (programma EDCTP3), pensato per istituti di ricerca e università, non per PMI. Una piccola impresa del Cilento non ha i requisiti strutturali né il profilo scientifico richiesto per candidarsi.</t>
+          <t>Si tratta di un premio individuale destinato a ricercatrici di eccellenza nell'ambito della salute globale (programma EDCTP3), non finanzia progetti aziendali né attività di PMI. Una piccola impresa del Cilento non ha alcun accesso diretto a questo strumento.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Man EU Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Outstanding Research Team Prize</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPMANEUPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-OUTSRESEARCHTEAMPRIZE</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo nell'ambito della ricerca scientifica su malattie infettive (EDCTP3), destinato a ricercatori e istituzioni accademiche di eccellenza, non a PMI. Una piccola o media impresa del Cilento non ha i requisiti né il profilo scientifico richiesto per candidarsi.</t>
+          <t>Si tratta di un premio europeo destinato a team di ricerca di eccellenza nell'ambito della salute globale e delle malattie infettive (programma EDCTP3), pensato per istituzioni accademiche e centri di ricerca, non per PMI. Una piccola impresa del Cilento non ha i requisiti né il profilo per accedere a questo tipo di riconoscimento.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman EU Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Man EU Prize</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANEUPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPMANEUPRIZE</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2541,14 +2541,14 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio europeo dedicato alla leadership scientifica femminile nell'ambito del partenariato EDCTP3 (ricerca su malattie infettive in paesi a basso reddito), non di un finanziamento a progetti aziendali: non prevede contributi per spese operative, investimenti o sviluppo d'impresa. Una PMI del Cilento non ha concreta possibilità di beneficio diretto.</t>
+          <t>Si tratta di un premio europeo nell'ambito della ricerca scientifica su malattie infettive (EDCTP3), destinato a ricercatori o istituzioni accademiche con leadership scientifica a livello internazionale. Una PMI del Cilento non ha i requisiti né il profilo adeguato per accedere a questo tipo di riconoscimento.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman SSA Prize</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman EU Prize</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANSSAPRIZE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANEUPRIZE</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2588,14 +2588,14 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Si tratta di un premio (Prize) nell'ambito di Horizon Europe dedicato alla leadership scientifica femminile, rivolto a ricercatrici e istituzioni di ricerca, non a PMI operative. Una piccola impresa del Cilento non ha i requisiti né il profilo scientifico richiesto per accedere a questo tipo di strumento competitivo.</t>
+          <t>Si tratta di un premio europeo per il riconoscimento della leadership scientifica femminile nell'ambito del partenariato EDCTP3 (malattie infettive nei paesi a basso reddito), non di un finanziamento a fondo perduto o agevolazione accessibile a una PMI campana. Non prevede spese finanziabili né benefici diretti per imprese del Cilento.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ERC PLUS GRANTS</t>
+          <t>HORIZON-JU-EDCTP3-2026-Scientific Leadership Woman SSA Prize</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-PLUS</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EDCTP3-2026-SCILEADERSHIPWOMANSSAPRIZE</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2630,39 +2630,39 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Altro</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Gli ERC Plus Grants sono destinati a ricercatori individuali di eccellenza già vincitori di grants ERC, rendendo di fatto inaccessibile il bando a una PMI del Cilento che non abbia un ricercatore ERC-funded nel proprio organico. Non sono previsti finanziamenti diretti per attività produttive o commerciali tipiche delle piccole imprese campane.</t>
+          <t>Si tratta di un premio (Prize) nell'ambito di EDCTP3 focalizzato sulla leadership scientifica femminile in salute globale, destinato a ricercatrici di istituzioni accademiche o di ricerca africane e europee. Una PMI campana, anche del Cilento, non rientra nei beneficiari tipici di questo strumento e non prevede finanziamenti diretti per attività aziendali.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Centres of Vocational Excellence</t>
+          <t>ERC PLUS GRANTS</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2026-PEX-COVE</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERC-2026-PLUS</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>UE - ERASMUS2027</t>
+          <t>UE - HORIZON</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2677,19 +2677,19 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Formazione</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Il bando Erasmus Centres of Vocational Excellence è rivolto principalmente a consorzi di istituti di istruzione e formazione professionale (IFP), enti pubblici e organizzazioni del settore educativo, non a PMI come beneficiari diretti; una PMI del Cilento potrebbe al massimo partecipare come partner associato in un consorzio guidato da un istituto formativo, con ruolo e accesso ai fondi molto limitati.</t>
+          <t>Gli ERC Plus Grants sono destinati a ricercatori già vincitori di finanziamenti ERC, richiedono strutture di ricerca avanzate e non sono accessibili direttamente a PMI del Cilento o della Campania senza un ente di ricerca partner qualificato. Una PMI di piccola dimensione difficilmente possiede i requisiti soggettivi e l'infrastruttura scientifica necessari per candidarsi autonomamente.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Centres of Vocational Excellence</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2699,17 +2699,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-31</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ERASMUS-EDU-2026-PEX-COVE</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>UE - HORIZON</t>
+          <t>UE - ERASMUS2027</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2724,19 +2724,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Formazione</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede capacità di ricerca avanzata in tecnologie spaziali, osservazione della Terra e telecomunicazioni satellitari, ambiti molto distanti dalle tipologie produttive e dimensionali delle PMI del Cilento e della Campania in generale. L'accesso richiede partnership internazionali strutturate e competenze tecnico-scientifiche specialistiche che rendono il bando di fatto inaccessibile per la quasi totalità delle piccole e medie imprese locali.</t>
+          <t>Il bando Erasmus+ Centres of Vocational Excellence è rivolto principalmente a reti transnazionali di istituti di istruzione e formazione professionale (ITS, enti pubblici, università), non a PMI come soggetti capofila o beneficiari diretti. Una PMI del Cilento potrebbe al massimo partecipare come partner secondario in un consorzio guidato da un ente formativo, con ruolo marginale e bassa capacità di influenza sulla progettazione.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
+          <t>Digital enablers and building-blocks for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-32</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-31</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2776,14 +2776,14 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon Europe richiede la preparazione di missioni dimostrative per l'osservazione terrestre e le telecomunicazioni satellitari, settori altamente specializzati che richiedono capacità tecnologiche avanzate e partnership internazionali difficilmente accessibili per una PMI tradizionale del Cilento. Le PMI campane potrebbero partecipare solo come partner secondari all'interno di consorzi guidati da grandi attori del settore spaziale, con budget e competenze che esulano dalla realtà produttiva locale.</t>
+          <t>Il bando Horizon Europe focalizzato su tecnologie spaziali avanzate (osservazione della Terra e telecomunicazioni satellitari) richiede capacità di R&amp;D altamente specializzate e partnership internazionali difficilmente accessibili per una PMI del Cilento. Le risorse finanziabili riguardano sviluppo tecnologico frontier, prototipazione spaziale e integrazione di sistemi complessi, ambiti lontani dalla struttura produttiva tipica del tessuto imprenditoriale locale.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
+          <t>Preparing demonstration missions for Earth Observation and Satellite telecommunication for Space solutions (Space Partnership)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-82</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-32</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2823,14 +2823,14 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Il bando richiede capacità industriali avanzate nello sviluppo di substrati SiC semi-isolanti e componenti GaN per applicazioni spaziali, con un profilo tecnologico altamente specializzato tipico di grandi player del settore aerospace/difesa. Una PMI del Cilento o della Campania difficilmente possiede le infrastrutture produttive, le certificazioni spaziali e il know-how necessari per partecipare in modo competitivo, nemmeno come partner junior di un consorzio.</t>
+          <t>Il bando Horizon Europe richiede capacità di R&amp;S avanzata nel settore spaziale (Earth Observation e telecomunicazioni satellitari) con consorzio internazionale, requisiti tecnici e finanziari difficilmente accessibili per una PMI campana di piccole dimensioni operante nel Cilento. Solo PMI altamente specializzate in tecnologie spaziali o telerilevamento potrebbero partecipare come partner junior in un consorzio europeo.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
+          <t>Space critical EEE components for EU non-dependence – GaN MMICs mm-Wave Foundations (Phase A): Development and Industrialization of Semi-insulating SiC Substrate Capabilities</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-11</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-82</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2865,19 +2865,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Infrastrutture</t>
+          <t>Innovazione</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di spazioporti europei e l'accesso autonomo dell'UE allo spazio, un settore che richiede investimenti e competenze tecnologiche di scala industriale ben oltre le capacità di una PMI campana, soprattutto nel Cilento. Non esistono filiere spaziali locali rilevanti a cui agganciarsi per partecipare realisticamente.</t>
+          <t>Il bando riguarda lo sviluppo di substrati SiC semi-isolanti per componenti elettronici spaziali ad altissima tecnologia (GaN MMICs in banda millimetrica), un settore che richiede competenze e infrastrutture di R&amp;S avanzatissime tipiche di grandi aziende aerospaziali o centri di ricerca specializzati. Una PMI del Cilento o della Campania difficilmente possiede le capacità tecniche, i laboratori certificati e il posizionamento nella supply chain spaziale europea necessari per partecipare competitivamente a questo tipo di progetto Horizon.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
+          <t>Reinforcing EU autonomous access to space through EU-based spaceports</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-85</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-11</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2912,19 +2912,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Innovazione</t>
+          <t>Infrastrutture</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di infrastrutture di test per irradiazione ad alta energia di componenti elettronici spaziali (EEE components), un settore altamente specializzato che richiede competenze in fisica nucleare, ingegneria spaziale e infrastrutture di ricerca avanzata, del tutto estranee al tessuto produttivo tipico delle PMI campane e del Cilento. Si tratta di un'azione rivolta a grandi consorzi di ricerca o operatori di facilities scientifiche, rendendo praticamente inaccessibile la partecipazione per una PMI locale di piccole o medie dimensioni.</t>
+          <t>Il bando riguarda lo sviluppo di spazioporti europei e l'accesso autonomo dell'UE allo spazio, un settore altamente specializzato che richiede investimenti e competenze tecnologiche del tutto fuori dalla portata di una PMI campana, specialmente nel Cilento. Non esistono filiere spaziali rilevanti nel territorio cilentano che possano beneficiare concretamente di questo tipo di finanziamento.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Scientific analysis and exploitation of space data</t>
+          <t>Critical Facilities Serving Space EEE components for EU non-dependence – High and Very High Energy Irradiation Test Facility Market Deployment</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-61</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-85</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2964,14 +2964,14 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon richiede capacità di ricerca avanzata nell'analisi di dati spaziali/satellitari, con consorzî internazionali e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. Le spese finanziabili riguardano R&amp;S ad alto contenuto tecnologico, lontane dai settori produttivi locali dominanti (turismo, agricoltura, agroalimentare).</t>
+          <t>Il bando riguarda lo sviluppo di infrastrutture critiche per test di irradiazione ad alta energia di componenti elettronici spaziali (EEE), un settore altamente specializzato che richiede capacità tecnologiche avanzate tipiche di grandi laboratori o aziende aerospaziali. Una PMI del Cilento o della Campania difficilmente possiede le competenze tecniche, le certificazioni e le infrastrutture necessarie per partecipare competitivamente a questo tipo di bando Horizon.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
+          <t>Scientific analysis and exploitation of space data</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-86</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-61</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3011,14 +3011,14 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Il bando riguarda lo sviluppo di interfacce di rifornimento per veicoli spaziali nell'ambito del programma Horizon EU, un settore altamente specializzato che richiede competenze aerospaziali avanzate, certificazioni specifiche e capacità R&amp;S difficilmente disponibili in una PMI del Cilento o della Campania in generale. L'accesso è realisticamente limitato a grandi player industriali o spin-off aerospaziali con esperienza pregressa in programmi ESA/NASA.</t>
+          <t>Il bando Horizon richiede capacità di ricerca avanzata sull'analisi di dati spaziali/satellitari, consorzio internazionale e competenze altamente specializzate difficilmente disponibili in una PMI del Cilento. Le PMI possono partecipare solo come partner in progetti coordinati da grandi enti di ricerca, con oneri burocratici e cofinanziamenti elevati che ne scoraggiano l'accesso diretto.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
+          <t>Space critical Equipment for EU non-dependence – Space Refuelling Interface</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-81</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-86</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3058,14 +3058,14 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Il bando richiede lo sviluppo di componenti elettronici spaziali radiation-hard su tecnologia 7nm, un settore altamente specializzato che presuppone capacità di R&amp;D avanzata, infrastrutture tecnologiche e competenze nel settore spaziale/difesa difficilmente disponibili in una PMI del Cilento o della Campania in generale. Si tratta di un'opportunità rivolta a grandi player dell'industria aerospaziale europea o spin-off tecnologici ultra-specializzati, non a PMI tradizionali del territorio.</t>
+          <t>Il bando riguarda lo sviluppo di tecnologie critiche per il rifornimento di carburante nello spazio nell'ambito dell'autonomia strategica europea nel settore spaziale, un ambito altamente specializzato che richiede competenze ingegneristiche aerospaziali avanzate e infrastrutture di ricerca difficilmente disponibili in una PMI del Cilento o della Campania in generale. Le PMI di piccola/media dimensione del territorio non dispongono tipicamente né del profilo tecnico né delle partnership istituzionali necessarie per accedere competitivamente a questo tipo di call Horizon.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Microelectronic – Front-End Module (FEM)</t>
+          <t>Space critical EEE components for EU non-dependence – Radiation Hard FPGA on 7nm</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL4-2026-SPACE-03-81</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3105,14 +3105,14 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Il bando Horizon focalizzato su moduli Front-End per microelettronica richiede capacità di R&amp;D avanzata, infrastrutture di ricerca e partnership con grandi player del settore semiconduttori, rendendo l'accesso estremamente difficile per una PMI del Cilento che difficilmente opera in questo comparto ad alta intensità tecnologica. Non sono previste spese finanziabili rilevanti per realtà produttive locali non specializzate in elettronica avanzata.</t>
+          <t>Il bando richiede lo sviluppo di componenti elettronici spaziali ad altissima tecnologia (FPGA radiation-hard su nodo a 7nm), destinato a grandi player dell'industria spaziale europea con capacità R&amp;D avanzate; una PMI del Cilento o della Campania difficilmente dispone delle infrastrutture, certificazioni spaziali e competenze specialistiche necessarie per competere in questo settore di nicchia ad elevatissima barriera d'ingresso.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Trafficking in human beings</t>
+          <t>Microelectronic – Front-End Module (FEM)</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3122,17 +3122,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ISF-2026-TF2-AG-THB</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
  